--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -529,7 +529,7 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="C2" s="2">
         <v>46213</v>
@@ -585,7 +585,7 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="C3" s="2">
         <v>46213</v>
@@ -641,7 +641,7 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="C4" s="2">
         <v>46213</v>
@@ -697,7 +697,7 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="C5" s="2">
         <v>46213</v>
@@ -753,7 +753,7 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="C6" s="2">
         <v>46213</v>
@@ -809,7 +809,7 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="C7" s="2">
         <v>46213</v>
@@ -865,7 +865,7 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="C8" s="2">
         <v>46213</v>
@@ -921,7 +921,7 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="C9" s="2">
         <v>46213</v>
@@ -977,7 +977,7 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="C10" s="2">
         <v>46213</v>
@@ -1033,7 +1033,7 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="C11" s="2">
         <v>46213</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -529,10 +529,10 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
+        <v>46217</v>
+      </c>
+      <c r="C2" s="2">
         <v>46216</v>
-      </c>
-      <c r="C2" s="2">
-        <v>46213</v>
       </c>
       <c r="D2" t="s">
         <v>28</v>
@@ -541,16 +541,16 @@
         <v>-1</v>
       </c>
       <c r="F2">
-        <v>0.8095472615621123</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>1.119724379993362</v>
+        <v>1.262735121503479</v>
       </c>
       <c r="H2">
-        <v>0.9665987370978917</v>
+        <v>0.9755998101461715</v>
       </c>
       <c r="I2">
-        <v>0.2473380674129221</v>
+        <v>0.2488973841090405</v>
       </c>
       <c r="J2">
         <v>6</v>
@@ -562,19 +562,19 @@
         <v>148</v>
       </c>
       <c r="M2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="N2">
-        <v>1.190657591695217</v>
+        <v>1.231287094204865</v>
       </c>
       <c r="O2">
-        <v>27.42593047554739</v>
+        <v>30.54545011671695</v>
       </c>
       <c r="P2">
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>1.119724379993362</v>
+        <v>1.262735121503479</v>
       </c>
       <c r="R2" t="b">
         <v>1</v>
@@ -585,10 +585,10 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
+        <v>46217</v>
+      </c>
+      <c r="C3" s="2">
         <v>46216</v>
-      </c>
-      <c r="C3" s="2">
-        <v>46213</v>
       </c>
       <c r="D3" t="s">
         <v>28</v>
@@ -597,16 +597,16 @@
         <v>-1</v>
       </c>
       <c r="F3">
-        <v>0.096826474372876</v>
+        <v>0.324162191047089</v>
       </c>
       <c r="G3">
-        <v>1.4406523881995</v>
+        <v>1.640007613092572</v>
       </c>
       <c r="H3">
-        <v>1.785637159908837</v>
+        <v>1.790719014253743</v>
       </c>
       <c r="I3">
-        <v>0.4278365886905946</v>
+        <v>0.428552317782609</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -618,19 +618,19 @@
         <v>224</v>
       </c>
       <c r="M3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N3">
-        <v>0.1379891579838571</v>
+        <v>0.1437743632472434</v>
       </c>
       <c r="O3">
-        <v>29.62957380021479</v>
+        <v>34.17387241869977</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>1.4406523881995</v>
+        <v>1.640007613092572</v>
       </c>
       <c r="R3" t="b">
         <v>1</v>
@@ -641,10 +641,10 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
+        <v>46217</v>
+      </c>
+      <c r="C4" s="2">
         <v>46216</v>
-      </c>
-      <c r="C4" s="2">
-        <v>46213</v>
       </c>
       <c r="D4" t="s">
         <v>28</v>
@@ -653,16 +653,16 @@
         <v>-1</v>
       </c>
       <c r="F4">
-        <v>0.4306304101394878</v>
+        <v>0.5316513436573271</v>
       </c>
       <c r="G4">
-        <v>1.92666694182994</v>
+        <v>2.028489328445747</v>
       </c>
       <c r="H4">
-        <v>1.994309443459021</v>
+        <v>1.997589031298029</v>
       </c>
       <c r="I4">
-        <v>0.4875515464708409</v>
+        <v>0.4881356299160646</v>
       </c>
       <c r="J4">
         <v>6</v>
@@ -674,19 +674,19 @@
         <v>145</v>
       </c>
       <c r="M4">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N4">
-        <v>4.736882475867772</v>
+        <v>4.786209206083992</v>
       </c>
       <c r="O4">
-        <v>145.4306023292733</v>
+        <v>144.1319184452051</v>
       </c>
       <c r="P4">
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>1.92666694182994</v>
+        <v>2.028489328445747</v>
       </c>
       <c r="R4" t="b">
         <v>1</v>
@@ -697,10 +697,10 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
+        <v>46217</v>
+      </c>
+      <c r="C5" s="2">
         <v>46216</v>
-      </c>
-      <c r="C5" s="2">
-        <v>46213</v>
       </c>
       <c r="D5" t="s">
         <v>28</v>
@@ -709,16 +709,16 @@
         <v>-1</v>
       </c>
       <c r="F5">
-        <v>0.8754661615499069</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>1.540624850535451</v>
+        <v>1.678908595448022</v>
       </c>
       <c r="H5">
-        <v>1.314396947589922</v>
+        <v>1.3137746863267</v>
       </c>
       <c r="I5">
-        <v>0.3012627050220334</v>
+        <v>0.2994669264841681</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -730,19 +730,19 @@
         <v>225</v>
       </c>
       <c r="M5">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N5">
-        <v>0.2071922991660241</v>
+        <v>0.2141515298539654</v>
       </c>
       <c r="O5">
-        <v>37.3800539732516</v>
+        <v>40.21085592751474</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>1.540624850535451</v>
+        <v>1.678908595448022</v>
       </c>
       <c r="R5" t="b">
         <v>1</v>
@@ -753,10 +753,10 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
+        <v>46217</v>
+      </c>
+      <c r="C6" s="2">
         <v>46216</v>
-      </c>
-      <c r="C6" s="2">
-        <v>46213</v>
       </c>
       <c r="D6" t="s">
         <v>28</v>
@@ -768,37 +768,37 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0.01320757137988905</v>
+        <v>0.0917218933108295</v>
       </c>
       <c r="H6">
-        <v>0.9359288945213657</v>
+        <v>0.9366427066752979</v>
       </c>
       <c r="I6">
-        <v>0.2545748930355656</v>
+        <v>0.2545638107358331</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K6">
-        <v>0.8333333333333334</v>
+        <v>1</v>
       </c>
       <c r="L6">
         <v>155</v>
       </c>
       <c r="M6">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N6">
-        <v>1.897812286126242</v>
+        <v>1.903027606882467</v>
       </c>
       <c r="O6">
-        <v>26.26859657498382</v>
+        <v>26.87404072742496</v>
       </c>
       <c r="P6">
-        <v>0.7574584144317615</v>
+        <v>0.3555823862547436</v>
       </c>
       <c r="Q6">
-        <v>0.05445487357949644</v>
+        <v>0.1423330016970764</v>
       </c>
       <c r="R6" t="b">
         <v>1</v>
@@ -809,10 +809,10 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
+        <v>46217</v>
+      </c>
+      <c r="C7" s="2">
         <v>46216</v>
-      </c>
-      <c r="C7" s="2">
-        <v>46213</v>
       </c>
       <c r="D7" t="s">
         <v>28</v>
@@ -824,37 +824,37 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>0.01892761058849605</v>
+        <v>0.006632915408631916</v>
       </c>
       <c r="H7">
-        <v>1.357259420618889</v>
+        <v>1.355564317725071</v>
       </c>
       <c r="I7">
-        <v>0.3116993519780225</v>
+        <v>0.3112918871410577</v>
       </c>
       <c r="J7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K7">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="L7">
         <v>237</v>
       </c>
       <c r="M7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N7">
-        <v>0.146365469190245</v>
+        <v>0.1467203261278615</v>
       </c>
       <c r="O7">
-        <v>20.03046499182246</v>
+        <v>20.48451324647288</v>
       </c>
       <c r="P7">
-        <v>0.5300589076973492</v>
+        <v>0.79978830916189</v>
       </c>
       <c r="Q7">
-        <v>0.04027655997425805</v>
+        <v>0.03312951097343888</v>
       </c>
       <c r="R7" t="b">
         <v>1</v>
@@ -865,10 +865,10 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
+        <v>46217</v>
+      </c>
+      <c r="C8" s="2">
         <v>46216</v>
-      </c>
-      <c r="C8" s="2">
-        <v>46213</v>
       </c>
       <c r="D8" t="s">
         <v>29</v>
@@ -877,16 +877,16 @@
         <v>1</v>
       </c>
       <c r="F8">
-        <v>0.7614406039998592</v>
+        <v>0.9944810556946149</v>
       </c>
       <c r="G8">
-        <v>1.580300249130866</v>
+        <v>1.74281019230603</v>
       </c>
       <c r="H8">
-        <v>1.393618843744826</v>
+        <v>1.391737109727528</v>
       </c>
       <c r="I8">
-        <v>0.3570245067712219</v>
+        <v>0.3549914385348268</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -898,19 +898,19 @@
         <v>111</v>
       </c>
       <c r="M8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N8">
-        <v>-0.1636875302937589</v>
+        <v>-0.170088617208698</v>
       </c>
       <c r="O8">
-        <v>-34.10156881119982</v>
+        <v>-33.70475075614682</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>1.580300249130866</v>
+        <v>1.74281019230603</v>
       </c>
       <c r="R8" t="b">
         <v>1</v>
@@ -921,10 +921,10 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
+        <v>46217</v>
+      </c>
+      <c r="C9" s="2">
         <v>46216</v>
-      </c>
-      <c r="C9" s="2">
-        <v>46213</v>
       </c>
       <c r="D9" t="s">
         <v>29</v>
@@ -936,13 +936,13 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>0.2304796023442486</v>
+        <v>0.349964848679059</v>
       </c>
       <c r="H9">
-        <v>2.937312617082786</v>
+        <v>2.937314811243364</v>
       </c>
       <c r="I9">
-        <v>0.618370792466725</v>
+        <v>0.6195650322855143</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -951,22 +951,22 @@
         <v>0.1666666666666667</v>
       </c>
       <c r="L9">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M9">
-        <v>228</v>
+        <v>0</v>
       </c>
       <c r="N9">
-        <v>4.984765762035098</v>
+        <v>0</v>
       </c>
       <c r="O9">
-        <v>293.0983648403656</v>
+        <v>0</v>
       </c>
       <c r="P9">
-        <v>0.1124271220770822</v>
+        <v>0.02987501255093562</v>
       </c>
       <c r="Q9">
-        <v>0.2596740032025458</v>
+        <v>0.3607420210866732</v>
       </c>
       <c r="R9" t="b">
         <v>1</v>
@@ -977,10 +977,10 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
+        <v>46217</v>
+      </c>
+      <c r="C10" s="2">
         <v>46216</v>
-      </c>
-      <c r="C10" s="2">
-        <v>46213</v>
       </c>
       <c r="D10" t="s">
         <v>29</v>
@@ -989,16 +989,16 @@
         <v>1</v>
       </c>
       <c r="F10">
-        <v>0.1828580646515154</v>
+        <v>0.1691622367477087</v>
       </c>
       <c r="G10">
-        <v>1.674548379147616</v>
+        <v>1.667529779394976</v>
       </c>
       <c r="H10">
-        <v>1.94872924931686</v>
+        <v>1.9541061796288</v>
       </c>
       <c r="I10">
-        <v>0.4322683940677328</v>
+        <v>0.4331071480725815</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1010,19 +1010,19 @@
         <v>232</v>
       </c>
       <c r="M10">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N10">
-        <v>-27.75136585782225</v>
+        <v>-28.71822488418185</v>
       </c>
       <c r="O10">
-        <v>-38.2777460107894</v>
+        <v>-38.39701541195165</v>
       </c>
       <c r="P10">
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>1.674548379147616</v>
+        <v>1.667529779394976</v>
       </c>
       <c r="R10" t="b">
         <v>1</v>
@@ -1033,10 +1033,10 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
+        <v>46217</v>
+      </c>
+      <c r="C11" s="2">
         <v>46216</v>
-      </c>
-      <c r="C11" s="2">
-        <v>46213</v>
       </c>
       <c r="D11" t="s">
         <v>28</v>
@@ -1048,13 +1048,13 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>1.370828324607074</v>
+        <v>1.52672893408051</v>
       </c>
       <c r="H11">
-        <v>3.105010947310545</v>
+        <v>3.105010826467173</v>
       </c>
       <c r="I11">
-        <v>0.6654491383546762</v>
+        <v>0.6634812152484243</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -1066,19 +1066,19 @@
         <v>211</v>
       </c>
       <c r="M11">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N11">
-        <v>8719.699454656116</v>
+        <v>8836.663396414076</v>
       </c>
       <c r="O11">
-        <v>84.30939767615288</v>
+        <v>83.94911177522582</v>
       </c>
       <c r="P11">
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>1.370828324607074</v>
+        <v>1.52672893408051</v>
       </c>
       <c r="R11" t="b">
         <v>1</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -529,10 +529,10 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
+        <v>46218</v>
+      </c>
+      <c r="C2" s="2">
         <v>46217</v>
-      </c>
-      <c r="C2" s="2">
-        <v>46216</v>
       </c>
       <c r="D2" t="s">
         <v>28</v>
@@ -541,16 +541,16 @@
         <v>-1</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>0.6913151086580912</v>
       </c>
       <c r="G2">
-        <v>1.262735121503479</v>
+        <v>1.080685084071596</v>
       </c>
       <c r="H2">
-        <v>0.9755998101461715</v>
+        <v>0.9848875514255921</v>
       </c>
       <c r="I2">
-        <v>0.2488973841090405</v>
+        <v>0.2503658318413536</v>
       </c>
       <c r="J2">
         <v>6</v>
@@ -562,19 +562,19 @@
         <v>148</v>
       </c>
       <c r="M2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N2">
-        <v>1.231287094204865</v>
+        <v>1.270311484681898</v>
       </c>
       <c r="O2">
-        <v>30.54545011671695</v>
+        <v>30.44537402942188</v>
       </c>
       <c r="P2">
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>1.262735121503479</v>
+        <v>1.080685084071596</v>
       </c>
       <c r="R2" t="b">
         <v>1</v>
@@ -585,10 +585,10 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
+        <v>46218</v>
+      </c>
+      <c r="C3" s="2">
         <v>46217</v>
-      </c>
-      <c r="C3" s="2">
-        <v>46216</v>
       </c>
       <c r="D3" t="s">
         <v>28</v>
@@ -597,16 +597,16 @@
         <v>-1</v>
       </c>
       <c r="F3">
-        <v>0.324162191047089</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>1.640007613092572</v>
+        <v>1.286430796385193</v>
       </c>
       <c r="H3">
-        <v>1.790719014253743</v>
+        <v>1.795316882470563</v>
       </c>
       <c r="I3">
-        <v>0.428552317782609</v>
+        <v>0.4292081118174051</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -618,19 +618,19 @@
         <v>224</v>
       </c>
       <c r="M3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N3">
-        <v>0.1437743632472434</v>
+        <v>0.1491289096965135</v>
       </c>
       <c r="O3">
-        <v>34.17387241869977</v>
+        <v>34.19547515766435</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>1.640007613092572</v>
+        <v>1.286430796385193</v>
       </c>
       <c r="R3" t="b">
         <v>1</v>
@@ -641,10 +641,10 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
+        <v>46218</v>
+      </c>
+      <c r="C4" s="2">
         <v>46217</v>
-      </c>
-      <c r="C4" s="2">
-        <v>46216</v>
       </c>
       <c r="D4" t="s">
         <v>28</v>
@@ -653,16 +653,16 @@
         <v>-1</v>
       </c>
       <c r="F4">
-        <v>0.5316513436573271</v>
+        <v>0.4204862932025254</v>
       </c>
       <c r="G4">
-        <v>2.028489328445747</v>
+        <v>1.92283086552391</v>
       </c>
       <c r="H4">
-        <v>1.997589031298029</v>
+        <v>2.000556277438084</v>
       </c>
       <c r="I4">
-        <v>0.4881356299160646</v>
+        <v>0.4887548011825462</v>
       </c>
       <c r="J4">
         <v>6</v>
@@ -674,19 +674,19 @@
         <v>145</v>
       </c>
       <c r="M4">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N4">
-        <v>4.786209206083992</v>
+        <v>4.836493295413591</v>
       </c>
       <c r="O4">
-        <v>144.1319184452051</v>
+        <v>139.4950682649163</v>
       </c>
       <c r="P4">
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>2.028489328445747</v>
+        <v>1.92283086552391</v>
       </c>
       <c r="R4" t="b">
         <v>1</v>
@@ -697,10 +697,10 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
+        <v>46218</v>
+      </c>
+      <c r="C5" s="2">
         <v>46217</v>
-      </c>
-      <c r="C5" s="2">
-        <v>46216</v>
       </c>
       <c r="D5" t="s">
         <v>28</v>
@@ -709,16 +709,16 @@
         <v>-1</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>0.926654347584107</v>
       </c>
       <c r="G5">
-        <v>1.678908595448022</v>
+        <v>1.567338617969237</v>
       </c>
       <c r="H5">
-        <v>1.3137746863267</v>
+        <v>1.313211688040929</v>
       </c>
       <c r="I5">
-        <v>0.2994669264841681</v>
+        <v>0.29781359473691</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -730,19 +730,19 @@
         <v>225</v>
       </c>
       <c r="M5">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N5">
-        <v>0.2141515298539654</v>
+        <v>0.2209400358791601</v>
       </c>
       <c r="O5">
-        <v>40.21085592751474</v>
+        <v>42.30830942837125</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>1.678908595448022</v>
+        <v>1.567338617969237</v>
       </c>
       <c r="R5" t="b">
         <v>1</v>
@@ -753,10 +753,10 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
+        <v>46218</v>
+      </c>
+      <c r="C6" s="2">
         <v>46217</v>
-      </c>
-      <c r="C6" s="2">
-        <v>46216</v>
       </c>
       <c r="D6" t="s">
         <v>28</v>
@@ -768,13 +768,13 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0.0917218933108295</v>
+        <v>0.1053328644719332</v>
       </c>
       <c r="H6">
-        <v>0.9366427066752979</v>
+        <v>0.9372885367193318</v>
       </c>
       <c r="I6">
-        <v>0.2545638107358331</v>
+        <v>0.2545736998829062</v>
       </c>
       <c r="J6">
         <v>6</v>
@@ -786,19 +786,19 @@
         <v>155</v>
       </c>
       <c r="M6">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N6">
-        <v>1.903027606882467</v>
+        <v>1.909290609702882</v>
       </c>
       <c r="O6">
-        <v>26.87404072742496</v>
+        <v>26.73033583919878</v>
       </c>
       <c r="P6">
-        <v>0.3555823862547436</v>
+        <v>0.2867609465996603</v>
       </c>
       <c r="Q6">
-        <v>0.1423330016970764</v>
+        <v>0.1476824130279502</v>
       </c>
       <c r="R6" t="b">
         <v>1</v>
@@ -809,10 +809,10 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
+        <v>46218</v>
+      </c>
+      <c r="C7" s="2">
         <v>46217</v>
-      </c>
-      <c r="C7" s="2">
-        <v>46216</v>
       </c>
       <c r="D7" t="s">
         <v>28</v>
@@ -824,37 +824,37 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>0.006632915408631916</v>
+        <v>0.015584986259377</v>
       </c>
       <c r="H7">
-        <v>1.355564317725071</v>
+        <v>1.354030653202092</v>
       </c>
       <c r="I7">
-        <v>0.3112918871410577</v>
+        <v>0.3109220771354494</v>
       </c>
       <c r="J7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K7">
-        <v>0.8333333333333334</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L7">
         <v>237</v>
       </c>
       <c r="M7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N7">
-        <v>0.1467203261278615</v>
+        <v>0.1468666218778131</v>
       </c>
       <c r="O7">
-        <v>20.48451324647288</v>
+        <v>21.02170234423258</v>
       </c>
       <c r="P7">
-        <v>0.79978830916189</v>
+        <v>0.722376115585862</v>
       </c>
       <c r="Q7">
-        <v>0.03312951097343888</v>
+        <v>0.0561370513645307</v>
       </c>
       <c r="R7" t="b">
         <v>1</v>
@@ -865,10 +865,10 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
+        <v>46218</v>
+      </c>
+      <c r="C8" s="2">
         <v>46217</v>
-      </c>
-      <c r="C8" s="2">
-        <v>46216</v>
       </c>
       <c r="D8" t="s">
         <v>29</v>
@@ -877,16 +877,16 @@
         <v>1</v>
       </c>
       <c r="F8">
-        <v>0.9944810556946149</v>
+        <v>0.8177768968945478</v>
       </c>
       <c r="G8">
-        <v>1.74281019230603</v>
+        <v>1.614412087797669</v>
       </c>
       <c r="H8">
-        <v>1.391737109727528</v>
+        <v>1.390034588473781</v>
       </c>
       <c r="I8">
-        <v>0.3549914385348268</v>
+        <v>0.3530424985526016</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -898,19 +898,19 @@
         <v>111</v>
       </c>
       <c r="M8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N8">
-        <v>-0.170088617208698</v>
+        <v>-0.1766906274021409</v>
       </c>
       <c r="O8">
-        <v>-33.70475075614682</v>
+        <v>-34.47862267238094</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>1.74281019230603</v>
+        <v>1.614412087797669</v>
       </c>
       <c r="R8" t="b">
         <v>1</v>
@@ -921,52 +921,52 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
+        <v>46218</v>
+      </c>
+      <c r="C9" s="2">
         <v>46217</v>
       </c>
-      <c r="C9" s="2">
-        <v>46216</v>
-      </c>
       <c r="D9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="F9">
         <v>0</v>
       </c>
       <c r="G9">
-        <v>0.349964848679059</v>
+        <v>0.6163803082298828</v>
       </c>
       <c r="H9">
-        <v>2.937314811243364</v>
+        <v>2.937316796436267</v>
       </c>
       <c r="I9">
-        <v>0.6195650322855143</v>
+        <v>0.6207046245458838</v>
       </c>
       <c r="J9">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K9">
-        <v>0.1666666666666667</v>
+        <v>1</v>
       </c>
       <c r="L9">
         <v>75</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>0.003446491167679202</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>0.2356172392875873</v>
       </c>
       <c r="P9">
-        <v>0.02987501255093562</v>
+        <v>0</v>
       </c>
       <c r="Q9">
-        <v>0.3607420210866732</v>
+        <v>0.6163803082298828</v>
       </c>
       <c r="R9" t="b">
         <v>1</v>
@@ -977,10 +977,10 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
+        <v>46218</v>
+      </c>
+      <c r="C10" s="2">
         <v>46217</v>
-      </c>
-      <c r="C10" s="2">
-        <v>46216</v>
       </c>
       <c r="D10" t="s">
         <v>29</v>
@@ -989,16 +989,16 @@
         <v>1</v>
       </c>
       <c r="F10">
-        <v>0.1691622367477087</v>
+        <v>0.1367858210383857</v>
       </c>
       <c r="G10">
-        <v>1.667529779394976</v>
+        <v>1.64378184550154</v>
       </c>
       <c r="H10">
-        <v>1.9541061796288</v>
+        <v>1.958971021339602</v>
       </c>
       <c r="I10">
-        <v>0.4331071480725815</v>
+        <v>0.4338888651582238</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1010,19 +1010,19 @@
         <v>232</v>
       </c>
       <c r="M10">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N10">
-        <v>-28.71822488418185</v>
+        <v>-29.67807362076571</v>
       </c>
       <c r="O10">
-        <v>-38.39701541195165</v>
+        <v>-40.1287454791115</v>
       </c>
       <c r="P10">
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>1.667529779394976</v>
+        <v>1.64378184550154</v>
       </c>
       <c r="R10" t="b">
         <v>1</v>
@@ -1033,10 +1033,10 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
+        <v>46218</v>
+      </c>
+      <c r="C11" s="2">
         <v>46217</v>
-      </c>
-      <c r="C11" s="2">
-        <v>46216</v>
       </c>
       <c r="D11" t="s">
         <v>28</v>
@@ -1048,13 +1048,13 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>1.52672893408051</v>
+        <v>1.601694257357708</v>
       </c>
       <c r="H11">
-        <v>3.105010826467173</v>
+        <v>3.105010717132694</v>
       </c>
       <c r="I11">
-        <v>0.6634812152484243</v>
+        <v>0.6615336493826948</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -1066,19 +1066,19 @@
         <v>211</v>
       </c>
       <c r="M11">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="N11">
-        <v>8836.663396414076</v>
+        <v>8957.59410163818</v>
       </c>
       <c r="O11">
-        <v>83.94911177522582</v>
+        <v>90.79519072034064</v>
       </c>
       <c r="P11">
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>1.52672893408051</v>
+        <v>1.601694257357708</v>
       </c>
       <c r="R11" t="b">
         <v>1</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -529,10 +529,10 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
+        <v>46219</v>
+      </c>
+      <c r="C2" s="2">
         <v>46218</v>
-      </c>
-      <c r="C2" s="2">
-        <v>46217</v>
       </c>
       <c r="D2" t="s">
         <v>28</v>
@@ -541,16 +541,16 @@
         <v>-1</v>
       </c>
       <c r="F2">
-        <v>0.6913151086580912</v>
+        <v>0.2825536779918912</v>
       </c>
       <c r="G2">
-        <v>1.080685084071596</v>
+        <v>0.8838316310306225</v>
       </c>
       <c r="H2">
-        <v>0.9848875514255921</v>
+        <v>0.9932907459164966</v>
       </c>
       <c r="I2">
-        <v>0.2503658318413536</v>
+        <v>0.2516922656475015</v>
       </c>
       <c r="J2">
         <v>6</v>
@@ -562,19 +562,19 @@
         <v>148</v>
       </c>
       <c r="M2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N2">
-        <v>1.270311484681898</v>
+        <v>1.304588758484739</v>
       </c>
       <c r="O2">
-        <v>30.44537402942188</v>
+        <v>31.11084303198308</v>
       </c>
       <c r="P2">
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>1.080685084071596</v>
+        <v>0.8838316310306225</v>
       </c>
       <c r="R2" t="b">
         <v>1</v>
@@ -585,10 +585,10 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
+        <v>46219</v>
+      </c>
+      <c r="C3" s="2">
         <v>46218</v>
-      </c>
-      <c r="C3" s="2">
-        <v>46217</v>
       </c>
       <c r="D3" t="s">
         <v>28</v>
@@ -600,13 +600,13 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>1.286430796385193</v>
+        <v>0.9997032835319883</v>
       </c>
       <c r="H3">
-        <v>1.795316882470563</v>
+        <v>1.799476858476258</v>
       </c>
       <c r="I3">
-        <v>0.4292081118174051</v>
+        <v>0.4297800054947346</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -618,19 +618,19 @@
         <v>224</v>
       </c>
       <c r="M3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N3">
-        <v>0.1491289096965135</v>
+        <v>0.1535722852703702</v>
       </c>
       <c r="O3">
-        <v>34.19547515766435</v>
+        <v>35.97443309269961</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>1.286430796385193</v>
+        <v>0.9997032835319883</v>
       </c>
       <c r="R3" t="b">
         <v>1</v>
@@ -641,10 +641,10 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
+        <v>46219</v>
+      </c>
+      <c r="C4" s="2">
         <v>46218</v>
-      </c>
-      <c r="C4" s="2">
-        <v>46217</v>
       </c>
       <c r="D4" t="s">
         <v>28</v>
@@ -653,16 +653,16 @@
         <v>-1</v>
       </c>
       <c r="F4">
-        <v>0.4204862932025254</v>
+        <v>0.2028434314198591</v>
       </c>
       <c r="G4">
-        <v>1.92283086552391</v>
+        <v>1.712397308278712</v>
       </c>
       <c r="H4">
-        <v>2.000556277438084</v>
+        <v>2.003240928707657</v>
       </c>
       <c r="I4">
-        <v>0.4887548011825462</v>
+        <v>0.489377740863411</v>
       </c>
       <c r="J4">
         <v>6</v>
@@ -674,19 +674,19 @@
         <v>145</v>
       </c>
       <c r="M4">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N4">
-        <v>4.836493295413591</v>
+        <v>4.884594693007449</v>
       </c>
       <c r="O4">
-        <v>139.4950682649163</v>
+        <v>138.3457934495335</v>
       </c>
       <c r="P4">
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>1.92283086552391</v>
+        <v>1.712397308278712</v>
       </c>
       <c r="R4" t="b">
         <v>1</v>
@@ -697,10 +697,10 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
+        <v>46219</v>
+      </c>
+      <c r="C5" s="2">
         <v>46218</v>
-      </c>
-      <c r="C5" s="2">
-        <v>46217</v>
       </c>
       <c r="D5" t="s">
         <v>28</v>
@@ -709,16 +709,16 @@
         <v>-1</v>
       </c>
       <c r="F5">
-        <v>0.926654347584107</v>
+        <v>0.4732606909828342</v>
       </c>
       <c r="G5">
-        <v>1.567338617969237</v>
+        <v>1.296853484456645</v>
       </c>
       <c r="H5">
-        <v>1.313211688040929</v>
+        <v>1.312702308639516</v>
       </c>
       <c r="I5">
-        <v>0.29781359473691</v>
+        <v>0.2963581477123565</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -730,19 +730,19 @@
         <v>225</v>
       </c>
       <c r="M5">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N5">
-        <v>0.2209400358791601</v>
+        <v>0.2269878872221562</v>
       </c>
       <c r="O5">
-        <v>42.30830942837125</v>
+        <v>43.83819038640046</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>1.567338617969237</v>
+        <v>1.296853484456645</v>
       </c>
       <c r="R5" t="b">
         <v>1</v>
@@ -753,28 +753,28 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
+        <v>46219</v>
+      </c>
+      <c r="C6" s="2">
         <v>46218</v>
       </c>
-      <c r="C6" s="2">
-        <v>46217</v>
-      </c>
       <c r="D6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E6">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0.1053328644719332</v>
+        <v>0.04639021614399383</v>
       </c>
       <c r="H6">
-        <v>0.9372885367193318</v>
+        <v>0.9378728591401243</v>
       </c>
       <c r="I6">
-        <v>0.2545736998829062</v>
+        <v>0.2546434919478455</v>
       </c>
       <c r="J6">
         <v>6</v>
@@ -786,19 +786,19 @@
         <v>155</v>
       </c>
       <c r="M6">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N6">
-        <v>1.909290609702882</v>
+        <v>1.909245773778308</v>
       </c>
       <c r="O6">
-        <v>26.73033583919878</v>
+        <v>25.04186926324616</v>
       </c>
       <c r="P6">
-        <v>0.2867609465996603</v>
+        <v>0.6035540971610903</v>
       </c>
       <c r="Q6">
-        <v>0.1476824130279502</v>
+        <v>0.1170152492730991</v>
       </c>
       <c r="R6" t="b">
         <v>1</v>
@@ -809,52 +809,52 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
+        <v>46219</v>
+      </c>
+      <c r="C7" s="2">
         <v>46218</v>
       </c>
-      <c r="C7" s="2">
-        <v>46217</v>
-      </c>
       <c r="D7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E7">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="F7">
         <v>0</v>
       </c>
       <c r="G7">
-        <v>0.015584986259377</v>
+        <v>0.4344475741781855</v>
       </c>
       <c r="H7">
-        <v>1.354030653202092</v>
+        <v>1.352643051967016</v>
       </c>
       <c r="I7">
-        <v>0.3109220771354494</v>
+        <v>0.3105423101160938</v>
       </c>
       <c r="J7">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K7">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="L7">
         <v>237</v>
       </c>
       <c r="M7">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N7">
-        <v>0.1468666218778131</v>
+        <v>0.1456905382721487</v>
       </c>
       <c r="O7">
-        <v>21.02170234423258</v>
+        <v>19.33792401810937</v>
       </c>
       <c r="P7">
-        <v>0.722376115585862</v>
+        <v>0.1042731495366563</v>
       </c>
       <c r="Q7">
-        <v>0.0561370513645307</v>
+        <v>0.4850223859577877</v>
       </c>
       <c r="R7" t="b">
         <v>1</v>
@@ -865,10 +865,10 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
+        <v>46219</v>
+      </c>
+      <c r="C8" s="2">
         <v>46218</v>
-      </c>
-      <c r="C8" s="2">
-        <v>46217</v>
       </c>
       <c r="D8" t="s">
         <v>29</v>
@@ -877,16 +877,16 @@
         <v>1</v>
       </c>
       <c r="F8">
-        <v>0.8177768968945478</v>
+        <v>0.48575500316923</v>
       </c>
       <c r="G8">
-        <v>1.614412087797669</v>
+        <v>1.378364710260847</v>
       </c>
       <c r="H8">
-        <v>1.390034588473781</v>
+        <v>1.388372383848695</v>
       </c>
       <c r="I8">
-        <v>0.3530424985526016</v>
+        <v>0.351269772353712</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -898,19 +898,19 @@
         <v>111</v>
       </c>
       <c r="M8">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N8">
-        <v>-0.1766906274021409</v>
+        <v>-0.1827729989072561</v>
       </c>
       <c r="O8">
-        <v>-34.47862267238094</v>
+        <v>-35.63818920197189</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>1.614412087797669</v>
+        <v>1.378364710260847</v>
       </c>
       <c r="R8" t="b">
         <v>1</v>
@@ -921,10 +921,10 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
+        <v>46219</v>
+      </c>
+      <c r="C9" s="2">
         <v>46218</v>
-      </c>
-      <c r="C9" s="2">
-        <v>46217</v>
       </c>
       <c r="D9" t="s">
         <v>28</v>
@@ -936,13 +936,13 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>0.6163803082298828</v>
+        <v>0.9012854344525589</v>
       </c>
       <c r="H9">
-        <v>2.937316796436267</v>
+        <v>2.93731859256318</v>
       </c>
       <c r="I9">
-        <v>0.6207046245458838</v>
+        <v>0.6217063139589699</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -951,22 +951,22 @@
         <v>1</v>
       </c>
       <c r="L9">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9">
-        <v>0.003446491167679202</v>
+        <v>0</v>
       </c>
       <c r="O9">
-        <v>0.2356172392875873</v>
+        <v>0</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>0.6163803082298828</v>
+        <v>0.9012854344525589</v>
       </c>
       <c r="R9" t="b">
         <v>1</v>
@@ -977,10 +977,10 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
+        <v>46219</v>
+      </c>
+      <c r="C10" s="2">
         <v>46218</v>
-      </c>
-      <c r="C10" s="2">
-        <v>46217</v>
       </c>
       <c r="D10" t="s">
         <v>29</v>
@@ -989,16 +989,16 @@
         <v>1</v>
       </c>
       <c r="F10">
-        <v>0.1367858210383857</v>
+        <v>0.06538241125378751</v>
       </c>
       <c r="G10">
-        <v>1.64378184550154</v>
+        <v>1.585584343636076</v>
       </c>
       <c r="H10">
-        <v>1.958971021339602</v>
+        <v>1.963372544792233</v>
       </c>
       <c r="I10">
-        <v>0.4338888651582238</v>
+        <v>0.4346213900891615</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1010,19 +1010,19 @@
         <v>232</v>
       </c>
       <c r="M10">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N10">
-        <v>-29.67807362076571</v>
+        <v>-30.6026414187916</v>
       </c>
       <c r="O10">
-        <v>-40.1287454791115</v>
+        <v>-42.18975675658123</v>
       </c>
       <c r="P10">
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>1.64378184550154</v>
+        <v>1.585584343636076</v>
       </c>
       <c r="R10" t="b">
         <v>1</v>
@@ -1033,10 +1033,10 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
+        <v>46219</v>
+      </c>
+      <c r="C11" s="2">
         <v>46218</v>
-      </c>
-      <c r="C11" s="2">
-        <v>46217</v>
       </c>
       <c r="D11" t="s">
         <v>28</v>
@@ -1048,13 +1048,13 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>1.601694257357708</v>
+        <v>1.634135471833873</v>
       </c>
       <c r="H11">
-        <v>3.105010717132694</v>
+        <v>3.105010618211022</v>
       </c>
       <c r="I11">
-        <v>0.6615336493826948</v>
+        <v>0.6596490859382422</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -1066,19 +1066,19 @@
         <v>211</v>
       </c>
       <c r="M11">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="N11">
-        <v>8957.59410163818</v>
+        <v>9075.940047572432</v>
       </c>
       <c r="O11">
-        <v>90.79519072034064</v>
+        <v>96.84027823244899</v>
       </c>
       <c r="P11">
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>1.601694257357708</v>
+        <v>1.634135471833873</v>
       </c>
       <c r="R11" t="b">
         <v>1</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -529,10 +529,10 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>46219</v>
+        <v>46221</v>
       </c>
       <c r="C2" s="2">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="D2" t="s">
         <v>28</v>
@@ -541,16 +541,16 @@
         <v>-1</v>
       </c>
       <c r="F2">
-        <v>0.2825536779918912</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>0.8838316310306225</v>
+        <v>0.7226452061373857</v>
       </c>
       <c r="H2">
-        <v>0.9932907459164966</v>
+        <v>1.007772441637783</v>
       </c>
       <c r="I2">
-        <v>0.2516922656475015</v>
+        <v>0.2537972237988029</v>
       </c>
       <c r="J2">
         <v>6</v>
@@ -562,19 +562,19 @@
         <v>148</v>
       </c>
       <c r="M2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N2">
-        <v>1.304588758484739</v>
+        <v>1.360389701196794</v>
       </c>
       <c r="O2">
-        <v>31.11084303198308</v>
+        <v>32.94263641463157</v>
       </c>
       <c r="P2">
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.8838316310306225</v>
+        <v>0.7226452061373857</v>
       </c>
       <c r="R2" t="b">
         <v>1</v>
@@ -585,10 +585,10 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
+        <v>46221</v>
+      </c>
+      <c r="C3" s="2">
         <v>46219</v>
-      </c>
-      <c r="C3" s="2">
-        <v>46218</v>
       </c>
       <c r="D3" t="s">
         <v>28</v>
@@ -600,13 +600,13 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>0.9997032835319883</v>
+        <v>0.819862375895185</v>
       </c>
       <c r="H3">
-        <v>1.799476858476258</v>
+        <v>1.803240646290933</v>
       </c>
       <c r="I3">
-        <v>0.4297800054947346</v>
+        <v>0.4302568749851327</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -618,19 +618,19 @@
         <v>224</v>
       </c>
       <c r="M3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N3">
-        <v>0.1535722852703702</v>
+        <v>0.1571957419814871</v>
       </c>
       <c r="O3">
-        <v>35.97443309269961</v>
+        <v>39.12427355983693</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>0.04516646271494851</v>
       </c>
       <c r="Q3">
-        <v>0.9997032835319883</v>
+        <v>0.8586443017348971</v>
       </c>
       <c r="R3" t="b">
         <v>1</v>
@@ -641,10 +641,10 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
+        <v>46221</v>
+      </c>
+      <c r="C4" s="2">
         <v>46219</v>
-      </c>
-      <c r="C4" s="2">
-        <v>46218</v>
       </c>
       <c r="D4" t="s">
         <v>28</v>
@@ -653,16 +653,16 @@
         <v>-1</v>
       </c>
       <c r="F4">
-        <v>0.2028434314198591</v>
+        <v>0.2273763052166383</v>
       </c>
       <c r="G4">
-        <v>1.712397308278712</v>
+        <v>1.738524582408123</v>
       </c>
       <c r="H4">
-        <v>2.003240928707657</v>
+        <v>2.005669898903937</v>
       </c>
       <c r="I4">
-        <v>0.489377740863411</v>
+        <v>0.489952490571481</v>
       </c>
       <c r="J4">
         <v>6</v>
@@ -674,19 +674,19 @@
         <v>145</v>
       </c>
       <c r="M4">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N4">
-        <v>4.884594693007449</v>
+        <v>4.929691165004351</v>
       </c>
       <c r="O4">
-        <v>138.3457934495335</v>
+        <v>148.4208092689485</v>
       </c>
       <c r="P4">
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>1.712397308278712</v>
+        <v>1.738524582408123</v>
       </c>
       <c r="R4" t="b">
         <v>1</v>
@@ -697,10 +697,10 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
+        <v>46221</v>
+      </c>
+      <c r="C5" s="2">
         <v>46219</v>
-      </c>
-      <c r="C5" s="2">
-        <v>46218</v>
       </c>
       <c r="D5" t="s">
         <v>28</v>
@@ -709,16 +709,16 @@
         <v>-1</v>
       </c>
       <c r="F5">
-        <v>0.4732606909828342</v>
+        <v>0.461548057468464</v>
       </c>
       <c r="G5">
-        <v>1.296853484456645</v>
+        <v>1.289547499566908</v>
       </c>
       <c r="H5">
-        <v>1.312702308639516</v>
+        <v>1.312241441562048</v>
       </c>
       <c r="I5">
-        <v>0.2963581477123565</v>
+        <v>0.2950948703895573</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -730,19 +730,19 @@
         <v>225</v>
       </c>
       <c r="M5">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N5">
-        <v>0.2269878872221562</v>
+        <v>0.2323137641881104</v>
       </c>
       <c r="O5">
-        <v>43.83819038640046</v>
+        <v>48.36631271668578</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>1.296853484456645</v>
+        <v>1.289547499566908</v>
       </c>
       <c r="R5" t="b">
         <v>1</v>
@@ -753,10 +753,10 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
+        <v>46221</v>
+      </c>
+      <c r="C6" s="2">
         <v>46219</v>
-      </c>
-      <c r="C6" s="2">
-        <v>46218</v>
       </c>
       <c r="D6" t="s">
         <v>29</v>
@@ -768,13 +768,13 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0.04639021614399383</v>
+        <v>0.09442998547464578</v>
       </c>
       <c r="H6">
-        <v>0.9378728591401243</v>
+        <v>0.9384015318065557</v>
       </c>
       <c r="I6">
-        <v>0.2546434919478455</v>
+        <v>0.254759400171029</v>
       </c>
       <c r="J6">
         <v>6</v>
@@ -783,22 +783,22 @@
         <v>1</v>
       </c>
       <c r="L6">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M6">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="N6">
-        <v>1.909245773778308</v>
+        <v>0</v>
       </c>
       <c r="O6">
-        <v>25.04186926324616</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>0.6035540971610903</v>
+        <v>0.4671360369619337</v>
       </c>
       <c r="Q6">
-        <v>0.1170152492730991</v>
+        <v>0.1772121817663619</v>
       </c>
       <c r="R6" t="b">
         <v>1</v>
@@ -809,10 +809,10 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
+        <v>46221</v>
+      </c>
+      <c r="C7" s="2">
         <v>46219</v>
-      </c>
-      <c r="C7" s="2">
-        <v>46218</v>
       </c>
       <c r="D7" t="s">
         <v>29</v>
@@ -824,13 +824,13 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>0.4344475741781855</v>
+        <v>0.5881446195461555</v>
       </c>
       <c r="H7">
-        <v>1.352643051967016</v>
+        <v>1.351387603230519</v>
       </c>
       <c r="I7">
-        <v>0.3105423101160938</v>
+        <v>0.3101817438347851</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -839,22 +839,22 @@
         <v>1</v>
       </c>
       <c r="L7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M7">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="N7">
-        <v>0.1456905382721487</v>
+        <v>0</v>
       </c>
       <c r="O7">
-        <v>19.33792401810937</v>
+        <v>0</v>
       </c>
       <c r="P7">
-        <v>0.1042731495366563</v>
+        <v>0.003150142888629249</v>
       </c>
       <c r="Q7">
-        <v>0.4850223859577877</v>
+        <v>0.5900032139749271</v>
       </c>
       <c r="R7" t="b">
         <v>1</v>
@@ -865,10 +865,10 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
+        <v>46221</v>
+      </c>
+      <c r="C8" s="2">
         <v>46219</v>
-      </c>
-      <c r="C8" s="2">
-        <v>46218</v>
       </c>
       <c r="D8" t="s">
         <v>29</v>
@@ -877,16 +877,16 @@
         <v>1</v>
       </c>
       <c r="F8">
-        <v>0.48575500316923</v>
+        <v>0.4621772135232619</v>
       </c>
       <c r="G8">
-        <v>1.378364710260847</v>
+        <v>1.360413208425827</v>
       </c>
       <c r="H8">
-        <v>1.388372383848695</v>
+        <v>1.386868484425998</v>
       </c>
       <c r="I8">
-        <v>0.351269772353712</v>
+        <v>0.3497266920886568</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -898,19 +898,19 @@
         <v>111</v>
       </c>
       <c r="M8">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N8">
-        <v>-0.1827729989072561</v>
+        <v>-0.1883865743874635</v>
       </c>
       <c r="O8">
-        <v>-35.63818920197189</v>
+        <v>-37.10745045971839</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>1.378364710260847</v>
+        <v>1.360413208425827</v>
       </c>
       <c r="R8" t="b">
         <v>1</v>
@@ -921,10 +921,10 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
+        <v>46221</v>
+      </c>
+      <c r="C9" s="2">
         <v>46219</v>
-      </c>
-      <c r="C9" s="2">
-        <v>46218</v>
       </c>
       <c r="D9" t="s">
         <v>28</v>
@@ -936,13 +936,13 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>0.9012854344525589</v>
+        <v>0.9445277784560701</v>
       </c>
       <c r="H9">
-        <v>2.93731859256318</v>
+        <v>2.937320217630386</v>
       </c>
       <c r="I9">
-        <v>0.6217063139589699</v>
+        <v>0.622545113262908</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -954,19 +954,19 @@
         <v>76</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>0.007273518979811114</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>0.5405811207589113</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>0.9012854344525589</v>
+        <v>0.9445277784560701</v>
       </c>
       <c r="R9" t="b">
         <v>1</v>
@@ -977,10 +977,10 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
+        <v>46221</v>
+      </c>
+      <c r="C10" s="2">
         <v>46219</v>
-      </c>
-      <c r="C10" s="2">
-        <v>46218</v>
       </c>
       <c r="D10" t="s">
         <v>29</v>
@@ -989,16 +989,16 @@
         <v>1</v>
       </c>
       <c r="F10">
-        <v>0.06538241125378751</v>
+        <v>0.07588101400851993</v>
       </c>
       <c r="G10">
-        <v>1.585584343636076</v>
+        <v>1.59810554341032</v>
       </c>
       <c r="H10">
-        <v>1.963372544792233</v>
+        <v>1.967354875535089</v>
       </c>
       <c r="I10">
-        <v>0.4346213900891615</v>
+        <v>0.435313372332955</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1010,19 +1010,19 @@
         <v>232</v>
       </c>
       <c r="M10">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N10">
-        <v>-30.6026414187916</v>
+        <v>-31.50388281180314</v>
       </c>
       <c r="O10">
-        <v>-42.18975675658123</v>
+        <v>-43.29155470801378</v>
       </c>
       <c r="P10">
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>1.585584343636076</v>
+        <v>1.59810554341032</v>
       </c>
       <c r="R10" t="b">
         <v>1</v>
@@ -1033,10 +1033,10 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
+        <v>46221</v>
+      </c>
+      <c r="C11" s="2">
         <v>46219</v>
-      </c>
-      <c r="C11" s="2">
-        <v>46218</v>
       </c>
       <c r="D11" t="s">
         <v>28</v>
@@ -1048,13 +1048,13 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>1.634135471833873</v>
+        <v>1.776246315865284</v>
       </c>
       <c r="H11">
-        <v>3.105010618211022</v>
+        <v>3.105010528710462</v>
       </c>
       <c r="I11">
-        <v>0.6596490859382422</v>
+        <v>0.6578670606403103</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -1066,19 +1066,19 @@
         <v>211</v>
       </c>
       <c r="M11">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N11">
-        <v>9075.940047572432</v>
+        <v>9195.268845419265</v>
       </c>
       <c r="O11">
-        <v>96.84027823244899</v>
+        <v>100.3427781781452</v>
       </c>
       <c r="P11">
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>1.634135471833873</v>
+        <v>1.776246315865284</v>
       </c>
       <c r="R11" t="b">
         <v>1</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -529,7 +529,7 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>46221</v>
+        <v>46223</v>
       </c>
       <c r="C2" s="2">
         <v>46220</v>
@@ -585,10 +585,10 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>46221</v>
+        <v>46223</v>
       </c>
       <c r="C3" s="2">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="D3" t="s">
         <v>28</v>
@@ -600,13 +600,13 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>0.819862375895185</v>
+        <v>0.850549069690636</v>
       </c>
       <c r="H3">
-        <v>1.803240646290933</v>
+        <v>1.806645978123259</v>
       </c>
       <c r="I3">
-        <v>0.4302568749851327</v>
+        <v>0.4305378196468256</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -618,19 +618,19 @@
         <v>224</v>
       </c>
       <c r="M3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N3">
-        <v>0.1571957419814871</v>
+        <v>0.1603876629731402</v>
       </c>
       <c r="O3">
-        <v>39.12427355983693</v>
+        <v>39.5774615603062</v>
       </c>
       <c r="P3">
-        <v>0.04516646271494851</v>
+        <v>0</v>
       </c>
       <c r="Q3">
-        <v>0.8586443017348971</v>
+        <v>0.850549069690636</v>
       </c>
       <c r="R3" t="b">
         <v>1</v>
@@ -641,10 +641,10 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>46221</v>
+        <v>46223</v>
       </c>
       <c r="C4" s="2">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="D4" t="s">
         <v>28</v>
@@ -653,16 +653,16 @@
         <v>-1</v>
       </c>
       <c r="F4">
-        <v>0.2273763052166383</v>
+        <v>0.1918544247572201</v>
       </c>
       <c r="G4">
-        <v>1.738524582408123</v>
+        <v>1.705645373883409</v>
       </c>
       <c r="H4">
-        <v>2.005669898903937</v>
+        <v>2.007867538605334</v>
       </c>
       <c r="I4">
-        <v>0.489952490571481</v>
+        <v>0.4903886166202638</v>
       </c>
       <c r="J4">
         <v>6</v>
@@ -674,19 +674,19 @@
         <v>145</v>
       </c>
       <c r="M4">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N4">
-        <v>4.929691165004351</v>
+        <v>4.972430895493572</v>
       </c>
       <c r="O4">
-        <v>148.4208092689485</v>
+        <v>156.2253872013241</v>
       </c>
       <c r="P4">
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>1.738524582408123</v>
+        <v>1.705645373883409</v>
       </c>
       <c r="R4" t="b">
         <v>1</v>
@@ -697,10 +697,10 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>46221</v>
+        <v>46223</v>
       </c>
       <c r="C5" s="2">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="D5" t="s">
         <v>28</v>
@@ -709,16 +709,16 @@
         <v>-1</v>
       </c>
       <c r="F5">
-        <v>0.461548057468464</v>
+        <v>0.5201522974967753</v>
       </c>
       <c r="G5">
-        <v>1.289547499566908</v>
+        <v>1.324320737734512</v>
       </c>
       <c r="H5">
-        <v>1.312241441562048</v>
+        <v>1.312475758643394</v>
       </c>
       <c r="I5">
-        <v>0.2950948703895573</v>
+        <v>0.2938865678469998</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -730,19 +730,19 @@
         <v>225</v>
       </c>
       <c r="M5">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N5">
-        <v>0.2323137641881104</v>
+        <v>0.2372894832481156</v>
       </c>
       <c r="O5">
-        <v>48.36631271668578</v>
+        <v>52.09020408425891</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>1.289547499566908</v>
+        <v>1.324320737734512</v>
       </c>
       <c r="R5" t="b">
         <v>1</v>
@@ -753,10 +753,10 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>46221</v>
+        <v>46223</v>
       </c>
       <c r="C6" s="2">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="D6" t="s">
         <v>29</v>
@@ -768,13 +768,13 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0.09442998547464578</v>
+        <v>0.1161808050671752</v>
       </c>
       <c r="H6">
-        <v>0.9384015318065557</v>
+        <v>0.9388798546952317</v>
       </c>
       <c r="I6">
-        <v>0.254759400171029</v>
+        <v>0.2549085094777718</v>
       </c>
       <c r="J6">
         <v>6</v>
@@ -786,19 +786,19 @@
         <v>156</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>-0.01171650933666294</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>-0.153641867624512</v>
       </c>
       <c r="P6">
-        <v>0.4671360369619337</v>
+        <v>0.4201369786679426</v>
       </c>
       <c r="Q6">
-        <v>0.1772121817663619</v>
+        <v>0.2003590516951493</v>
       </c>
       <c r="R6" t="b">
         <v>1</v>
@@ -809,10 +809,10 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>46221</v>
+        <v>46223</v>
       </c>
       <c r="C7" s="2">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="D7" t="s">
         <v>29</v>
@@ -824,13 +824,13 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>0.5881446195461555</v>
+        <v>0.5906059774087326</v>
       </c>
       <c r="H7">
-        <v>1.351387603230519</v>
+        <v>1.350251721040354</v>
       </c>
       <c r="I7">
-        <v>0.3101817438347851</v>
+        <v>0.3098551159706014</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -842,19 +842,19 @@
         <v>238</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>-0.003110127885464531</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>-0.4267547818926149</v>
       </c>
       <c r="P7">
-        <v>0.003150142888629249</v>
+        <v>0</v>
       </c>
       <c r="Q7">
-        <v>0.5900032139749271</v>
+        <v>0.5906059774087326</v>
       </c>
       <c r="R7" t="b">
         <v>1</v>
@@ -865,10 +865,10 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>46221</v>
+        <v>46223</v>
       </c>
       <c r="C8" s="2">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="D8" t="s">
         <v>29</v>
@@ -877,16 +877,16 @@
         <v>1</v>
       </c>
       <c r="F8">
-        <v>0.4621772135232619</v>
+        <v>0.4719928589526362</v>
       </c>
       <c r="G8">
-        <v>1.360413208425827</v>
+        <v>1.365993379372389</v>
       </c>
       <c r="H8">
-        <v>1.386868484425998</v>
+        <v>1.385507813519748</v>
       </c>
       <c r="I8">
-        <v>0.3497266920886568</v>
+        <v>0.3483831876012803</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -898,19 +898,19 @@
         <v>111</v>
       </c>
       <c r="M8">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="N8">
-        <v>-0.1883865743874635</v>
+        <v>-0.1938116675809375</v>
       </c>
       <c r="O8">
-        <v>-37.10745045971839</v>
+        <v>-39.44128710128827</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>1.360413208425827</v>
+        <v>1.365993379372389</v>
       </c>
       <c r="R8" t="b">
         <v>1</v>
@@ -921,10 +921,10 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>46221</v>
+        <v>46223</v>
       </c>
       <c r="C9" s="2">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="D9" t="s">
         <v>28</v>
@@ -936,13 +936,13 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>0.9445277784560701</v>
+        <v>0.9616218022766068</v>
       </c>
       <c r="H9">
-        <v>2.937320217630386</v>
+        <v>2.937321687929288</v>
       </c>
       <c r="I9">
-        <v>0.622545113262908</v>
+        <v>0.6230881031882546</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -954,19 +954,19 @@
         <v>76</v>
       </c>
       <c r="M9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N9">
-        <v>0.007273518979811114</v>
+        <v>0.01491625474570637</v>
       </c>
       <c r="O9">
-        <v>0.5405811207589113</v>
+        <v>1.172595690043748</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>0.9445277784560701</v>
+        <v>0.9616218022766068</v>
       </c>
       <c r="R9" t="b">
         <v>1</v>
@@ -977,10 +977,10 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>46221</v>
+        <v>46223</v>
       </c>
       <c r="C10" s="2">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="D10" t="s">
         <v>29</v>
@@ -989,16 +989,16 @@
         <v>1</v>
       </c>
       <c r="F10">
-        <v>0.07588101400851993</v>
+        <v>0.1045663857225371</v>
       </c>
       <c r="G10">
-        <v>1.59810554341032</v>
+        <v>1.626162787168392</v>
       </c>
       <c r="H10">
-        <v>1.967354875535089</v>
+        <v>1.970957936683388</v>
       </c>
       <c r="I10">
-        <v>0.435313372332955</v>
+        <v>0.4359709658788186</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1010,19 +1010,19 @@
         <v>232</v>
       </c>
       <c r="M10">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N10">
-        <v>-31.50388281180314</v>
+        <v>-32.4011900669876</v>
       </c>
       <c r="O10">
-        <v>-43.29155470801378</v>
+        <v>-45.4252614598263</v>
       </c>
       <c r="P10">
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>1.59810554341032</v>
+        <v>1.626162787168392</v>
       </c>
       <c r="R10" t="b">
         <v>1</v>
@@ -1033,7 +1033,7 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>46221</v>
+        <v>46223</v>
       </c>
       <c r="C11" s="2">
         <v>46219</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -529,10 +529,10 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
+        <v>46224</v>
+      </c>
+      <c r="C2" s="2">
         <v>46223</v>
-      </c>
-      <c r="C2" s="2">
-        <v>46220</v>
       </c>
       <c r="D2" t="s">
         <v>28</v>
@@ -544,13 +544,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>0.7226452061373857</v>
+        <v>0.6710355043976531</v>
       </c>
       <c r="H2">
-        <v>1.007772441637783</v>
+        <v>1.013996122775145</v>
       </c>
       <c r="I2">
-        <v>0.2537972237988029</v>
+        <v>0.254622123251082</v>
       </c>
       <c r="J2">
         <v>6</v>
@@ -562,19 +562,19 @@
         <v>148</v>
       </c>
       <c r="M2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N2">
-        <v>1.360389701196794</v>
+        <v>1.384301477360491</v>
       </c>
       <c r="O2">
-        <v>32.94263641463157</v>
+        <v>34.06014179797342</v>
       </c>
       <c r="P2">
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.7226452061373857</v>
+        <v>0.6710355043976531</v>
       </c>
       <c r="R2" t="b">
         <v>1</v>
@@ -585,10 +585,10 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
+        <v>46224</v>
+      </c>
+      <c r="C3" s="2">
         <v>46223</v>
-      </c>
-      <c r="C3" s="2">
-        <v>46220</v>
       </c>
       <c r="D3" t="s">
         <v>28</v>
@@ -600,13 +600,13 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>0.850549069690636</v>
+        <v>0.6470560086710306</v>
       </c>
       <c r="H3">
-        <v>1.806645978123259</v>
+        <v>1.80972699263822</v>
       </c>
       <c r="I3">
-        <v>0.4305378196468256</v>
+        <v>0.4306846477473564</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -618,19 +618,19 @@
         <v>224</v>
       </c>
       <c r="M3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N3">
-        <v>0.1603876629731402</v>
+        <v>0.163193487360238</v>
       </c>
       <c r="O3">
-        <v>39.5774615603062</v>
+        <v>42.52994830683809</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>0.07847102189576782</v>
       </c>
       <c r="Q3">
-        <v>0.850549069690636</v>
+        <v>0.7021548144933577</v>
       </c>
       <c r="R3" t="b">
         <v>1</v>
@@ -641,10 +641,10 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
+        <v>46224</v>
+      </c>
+      <c r="C4" s="2">
         <v>46223</v>
-      </c>
-      <c r="C4" s="2">
-        <v>46220</v>
       </c>
       <c r="D4" t="s">
         <v>28</v>
@@ -653,16 +653,16 @@
         <v>-1</v>
       </c>
       <c r="F4">
-        <v>0.1918544247572201</v>
+        <v>0.2983132593948509</v>
       </c>
       <c r="G4">
-        <v>1.705645373883409</v>
+        <v>1.811908380628527</v>
       </c>
       <c r="H4">
-        <v>2.007867538605334</v>
+        <v>2.00985587928755</v>
       </c>
       <c r="I4">
-        <v>0.4903886166202638</v>
+        <v>0.4907300749297983</v>
       </c>
       <c r="J4">
         <v>6</v>
@@ -674,19 +674,19 @@
         <v>145</v>
       </c>
       <c r="M4">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N4">
-        <v>4.972430895493572</v>
+        <v>5.014399656577423</v>
       </c>
       <c r="O4">
-        <v>156.2253872013241</v>
+        <v>159.657937666782</v>
       </c>
       <c r="P4">
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>1.705645373883409</v>
+        <v>1.811908380628527</v>
       </c>
       <c r="R4" t="b">
         <v>1</v>
@@ -697,10 +697,10 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
+        <v>46224</v>
+      </c>
+      <c r="C5" s="2">
         <v>46223</v>
-      </c>
-      <c r="C5" s="2">
-        <v>46220</v>
       </c>
       <c r="D5" t="s">
         <v>28</v>
@@ -709,16 +709,16 @@
         <v>-1</v>
       </c>
       <c r="F5">
-        <v>0.5201522974967753</v>
+        <v>0.6882994163513212</v>
       </c>
       <c r="G5">
-        <v>1.324320737734512</v>
+        <v>1.423627092272378</v>
       </c>
       <c r="H5">
-        <v>1.312475758643394</v>
+        <v>1.313371821192102</v>
       </c>
       <c r="I5">
-        <v>0.2938865678469998</v>
+        <v>0.2927658333113632</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -730,19 +730,19 @@
         <v>225</v>
       </c>
       <c r="M5">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N5">
-        <v>0.2372894832481156</v>
+        <v>0.2421280054148867</v>
       </c>
       <c r="O5">
-        <v>52.09020408425891</v>
+        <v>56.11309511353104</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>1.324320737734512</v>
+        <v>1.423627092272378</v>
       </c>
       <c r="R5" t="b">
         <v>1</v>
@@ -753,10 +753,10 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
+        <v>46224</v>
+      </c>
+      <c r="C6" s="2">
         <v>46223</v>
-      </c>
-      <c r="C6" s="2">
-        <v>46220</v>
       </c>
       <c r="D6" t="s">
         <v>29</v>
@@ -768,13 +768,13 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0.1161808050671752</v>
+        <v>0.05138742086143865</v>
       </c>
       <c r="H6">
-        <v>0.9388798546952317</v>
+        <v>0.9393126230230815</v>
       </c>
       <c r="I6">
-        <v>0.2549085094777718</v>
+        <v>0.2550871414666636</v>
       </c>
       <c r="J6">
         <v>6</v>
@@ -786,19 +786,19 @@
         <v>156</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N6">
-        <v>-0.01171650933666294</v>
+        <v>-0.02345100660482606</v>
       </c>
       <c r="O6">
-        <v>-0.153641867624512</v>
+        <v>-0.3079956213285228</v>
       </c>
       <c r="P6">
-        <v>0.4201369786679426</v>
+        <v>0.6168413584170989</v>
       </c>
       <c r="Q6">
-        <v>0.2003590516951493</v>
+        <v>0.1341152600634229</v>
       </c>
       <c r="R6" t="b">
         <v>1</v>
@@ -809,10 +809,10 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
+        <v>46224</v>
+      </c>
+      <c r="C7" s="2">
         <v>46223</v>
-      </c>
-      <c r="C7" s="2">
-        <v>46220</v>
       </c>
       <c r="D7" t="s">
         <v>29</v>
@@ -824,13 +824,13 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>0.5906059774087326</v>
+        <v>0.5791583796555356</v>
       </c>
       <c r="H7">
-        <v>1.350251721040354</v>
+        <v>1.349224018106396</v>
       </c>
       <c r="I7">
-        <v>0.3098551159706014</v>
+        <v>0.3095201527522953</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -842,19 +842,19 @@
         <v>238</v>
       </c>
       <c r="M7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N7">
-        <v>-0.003110127885464531</v>
+        <v>-0.006283769276739132</v>
       </c>
       <c r="O7">
-        <v>-0.4267547818926149</v>
+        <v>-0.905815175806713</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>0.5906059774087326</v>
+        <v>0.5791583796555356</v>
       </c>
       <c r="R7" t="b">
         <v>1</v>
@@ -865,10 +865,10 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
+        <v>46224</v>
+      </c>
+      <c r="C8" s="2">
         <v>46223</v>
-      </c>
-      <c r="C8" s="2">
-        <v>46220</v>
       </c>
       <c r="D8" t="s">
         <v>29</v>
@@ -877,16 +877,16 @@
         <v>1</v>
       </c>
       <c r="F8">
-        <v>0.4719928589526362</v>
+        <v>0.5585486117996296</v>
       </c>
       <c r="G8">
-        <v>1.365993379372389</v>
+        <v>1.425604946971071</v>
       </c>
       <c r="H8">
-        <v>1.385507813519748</v>
+        <v>1.384949346223931</v>
       </c>
       <c r="I8">
-        <v>0.3483831876012803</v>
+        <v>0.3471952579018946</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -898,19 +898,19 @@
         <v>111</v>
       </c>
       <c r="M8">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N8">
-        <v>-0.1938116675809375</v>
+        <v>-0.1991438290802461</v>
       </c>
       <c r="O8">
-        <v>-39.44128710128827</v>
+        <v>-41.58421369413759</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>1.365993379372389</v>
+        <v>1.425604946971071</v>
       </c>
       <c r="R8" t="b">
         <v>1</v>
@@ -921,10 +921,10 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
+        <v>46224</v>
+      </c>
+      <c r="C9" s="2">
         <v>46223</v>
-      </c>
-      <c r="C9" s="2">
-        <v>46220</v>
       </c>
       <c r="D9" t="s">
         <v>28</v>
@@ -936,13 +936,13 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>0.9616218022766068</v>
+        <v>1.128653120691019</v>
       </c>
       <c r="H9">
-        <v>2.937321687929288</v>
+        <v>2.937323018199722</v>
       </c>
       <c r="I9">
-        <v>0.6230881031882546</v>
+        <v>0.6233717704189171</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -954,19 +954,19 @@
         <v>76</v>
       </c>
       <c r="M9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N9">
-        <v>0.01491625474570637</v>
+        <v>0.02315920383942704</v>
       </c>
       <c r="O9">
-        <v>1.172595690043748</v>
+        <v>1.902918999630138</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>0.9616218022766068</v>
+        <v>1.128653120691019</v>
       </c>
       <c r="R9" t="b">
         <v>1</v>
@@ -977,10 +977,10 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
+        <v>46224</v>
+      </c>
+      <c r="C10" s="2">
         <v>46223</v>
-      </c>
-      <c r="C10" s="2">
-        <v>46220</v>
       </c>
       <c r="D10" t="s">
         <v>29</v>
@@ -989,16 +989,16 @@
         <v>1</v>
       </c>
       <c r="F10">
-        <v>0.1045663857225371</v>
+        <v>0.2357537202218213</v>
       </c>
       <c r="G10">
-        <v>1.626162787168392</v>
+        <v>1.743477961427452</v>
       </c>
       <c r="H10">
-        <v>1.970957936683388</v>
+        <v>1.974217849150896</v>
       </c>
       <c r="I10">
-        <v>0.4359709658788186</v>
+        <v>0.4366000685367047</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1010,19 +1010,19 @@
         <v>232</v>
       </c>
       <c r="M10">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N10">
-        <v>-32.4011900669876</v>
+        <v>-33.29020620986837</v>
       </c>
       <c r="O10">
-        <v>-45.4252614598263</v>
+        <v>-50.39062460137918</v>
       </c>
       <c r="P10">
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>1.626162787168392</v>
+        <v>1.743477961427452</v>
       </c>
       <c r="R10" t="b">
         <v>1</v>
@@ -1033,10 +1033,10 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
+        <v>46224</v>
+      </c>
+      <c r="C11" s="2">
         <v>46223</v>
-      </c>
-      <c r="C11" s="2">
-        <v>46219</v>
       </c>
       <c r="D11" t="s">
         <v>28</v>
@@ -1048,13 +1048,13 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>1.776246315865284</v>
+        <v>1.879864558389473</v>
       </c>
       <c r="H11">
-        <v>3.105010528710462</v>
+        <v>3.105010447733765</v>
       </c>
       <c r="I11">
-        <v>0.6578670606403103</v>
+        <v>0.6562139205345878</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -1066,19 +1066,19 @@
         <v>211</v>
       </c>
       <c r="M11">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="N11">
-        <v>9195.268845419265</v>
+        <v>9317.360388976971</v>
       </c>
       <c r="O11">
-        <v>100.3427781781452</v>
+        <v>107.5091859078211</v>
       </c>
       <c r="P11">
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>1.776246315865284</v>
+        <v>1.879864558389473</v>
       </c>
       <c r="R11" t="b">
         <v>1</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -529,10 +529,10 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
+        <v>46225</v>
+      </c>
+      <c r="C2" s="2">
         <v>46224</v>
-      </c>
-      <c r="C2" s="2">
-        <v>46223</v>
       </c>
       <c r="D2" t="s">
         <v>28</v>
@@ -544,13 +544,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>0.6710355043976531</v>
+        <v>0.6146742369239991</v>
       </c>
       <c r="H2">
-        <v>1.013996122775145</v>
+        <v>1.019627072375616</v>
       </c>
       <c r="I2">
-        <v>0.254622123251082</v>
+        <v>0.2553236364198954</v>
       </c>
       <c r="J2">
         <v>6</v>
@@ -562,19 +562,19 @@
         <v>148</v>
       </c>
       <c r="M2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N2">
-        <v>1.384301477360491</v>
+        <v>1.405823667017329</v>
       </c>
       <c r="O2">
-        <v>34.06014179797342</v>
+        <v>35.02612756178503</v>
       </c>
       <c r="P2">
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.6710355043976531</v>
+        <v>0.6146742369239991</v>
       </c>
       <c r="R2" t="b">
         <v>1</v>
@@ -585,10 +585,10 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
+        <v>46225</v>
+      </c>
+      <c r="C3" s="2">
         <v>46224</v>
-      </c>
-      <c r="C3" s="2">
-        <v>46223</v>
       </c>
       <c r="D3" t="s">
         <v>28</v>
@@ -600,13 +600,13 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>0.6470560086710306</v>
+        <v>0.5011456292692775</v>
       </c>
       <c r="H3">
-        <v>1.80972699263822</v>
+        <v>1.812514577199376</v>
       </c>
       <c r="I3">
-        <v>0.4306846477473564</v>
+        <v>0.4307273584754428</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -618,19 +618,19 @@
         <v>224</v>
       </c>
       <c r="M3">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N3">
-        <v>0.163193487360238</v>
+        <v>0.1654796827999316</v>
       </c>
       <c r="O3">
-        <v>42.52994830683809</v>
+        <v>45.82564650774516</v>
       </c>
       <c r="P3">
-        <v>0.07847102189576782</v>
+        <v>0.1741474368065233</v>
       </c>
       <c r="Q3">
-        <v>0.7021548144933577</v>
+        <v>0.6068221515610548</v>
       </c>
       <c r="R3" t="b">
         <v>1</v>
@@ -641,10 +641,10 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
+        <v>46225</v>
+      </c>
+      <c r="C4" s="2">
         <v>46224</v>
-      </c>
-      <c r="C4" s="2">
-        <v>46223</v>
       </c>
       <c r="D4" t="s">
         <v>28</v>
@@ -653,16 +653,16 @@
         <v>-1</v>
       </c>
       <c r="F4">
-        <v>0.2983132593948509</v>
+        <v>0.4634407824260308</v>
       </c>
       <c r="G4">
-        <v>1.811908380628527</v>
+        <v>1.975753434410489</v>
       </c>
       <c r="H4">
-        <v>2.00985587928755</v>
+        <v>2.011654854190507</v>
       </c>
       <c r="I4">
-        <v>0.4907300749297983</v>
+        <v>0.4910036669600482</v>
       </c>
       <c r="J4">
         <v>6</v>
@@ -674,19 +674,19 @@
         <v>145</v>
       </c>
       <c r="M4">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N4">
-        <v>5.014399656577423</v>
+        <v>5.05780245640053</v>
       </c>
       <c r="O4">
-        <v>159.657937666782</v>
+        <v>165.9072970703082</v>
       </c>
       <c r="P4">
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>1.811908380628527</v>
+        <v>1.975753434410489</v>
       </c>
       <c r="R4" t="b">
         <v>1</v>
@@ -697,10 +697,10 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
+        <v>46225</v>
+      </c>
+      <c r="C5" s="2">
         <v>46224</v>
-      </c>
-      <c r="C5" s="2">
-        <v>46223</v>
       </c>
       <c r="D5" t="s">
         <v>28</v>
@@ -709,16 +709,16 @@
         <v>-1</v>
       </c>
       <c r="F5">
-        <v>0.6882994163513212</v>
+        <v>0.9997503834852586</v>
       </c>
       <c r="G5">
-        <v>1.423627092272378</v>
+        <v>1.607081868208929</v>
       </c>
       <c r="H5">
-        <v>1.313371821192102</v>
+        <v>1.315463401391202</v>
       </c>
       <c r="I5">
-        <v>0.2927658333113632</v>
+        <v>0.2917641251057982</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -730,19 +730,19 @@
         <v>225</v>
       </c>
       <c r="M5">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N5">
-        <v>0.2421280054148867</v>
+        <v>0.2469994654933741</v>
       </c>
       <c r="O5">
-        <v>56.11309511353104</v>
+        <v>61.72231176987483</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>1.423627092272378</v>
+        <v>1.607081868208929</v>
       </c>
       <c r="R5" t="b">
         <v>1</v>
@@ -753,10 +753,10 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
+        <v>46225</v>
+      </c>
+      <c r="C6" s="2">
         <v>46224</v>
-      </c>
-      <c r="C6" s="2">
-        <v>46223</v>
       </c>
       <c r="D6" t="s">
         <v>29</v>
@@ -768,37 +768,37 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0.05138742086143865</v>
+        <v>0.004995935529032214</v>
       </c>
       <c r="H6">
-        <v>0.9393126230230815</v>
+        <v>0.9397041753197074</v>
       </c>
       <c r="I6">
-        <v>0.2550871414666636</v>
+        <v>0.2553073828494136</v>
       </c>
       <c r="J6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L6">
         <v>156</v>
       </c>
       <c r="M6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N6">
-        <v>-0.02345100660482606</v>
+        <v>-0.03093584700108248</v>
       </c>
       <c r="O6">
-        <v>-0.3079956213285228</v>
+        <v>-0.4038622323901113</v>
       </c>
       <c r="P6">
-        <v>0.6168413584170989</v>
+        <v>0.4598935499825785</v>
       </c>
       <c r="Q6">
-        <v>0.1341152600634229</v>
+        <v>0.009249909029731206</v>
       </c>
       <c r="R6" t="b">
         <v>1</v>
@@ -809,10 +809,10 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
+        <v>46225</v>
+      </c>
+      <c r="C7" s="2">
         <v>46224</v>
-      </c>
-      <c r="C7" s="2">
-        <v>46223</v>
       </c>
       <c r="D7" t="s">
         <v>29</v>
@@ -824,13 +824,13 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>0.5791583796555356</v>
+        <v>0.393898797014347</v>
       </c>
       <c r="H7">
-        <v>1.349224018106396</v>
+        <v>1.348294191642339</v>
       </c>
       <c r="I7">
-        <v>0.3095201527522953</v>
+        <v>0.3092055820418288</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -842,19 +842,19 @@
         <v>238</v>
       </c>
       <c r="M7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N7">
-        <v>-0.006283769276739132</v>
+        <v>-0.009093891111777868</v>
       </c>
       <c r="O7">
-        <v>-0.905815175806713</v>
+        <v>-1.330071829971689</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>0.5791583796555356</v>
+        <v>0.393898797014347</v>
       </c>
       <c r="R7" t="b">
         <v>1</v>
@@ -865,10 +865,10 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
+        <v>46225</v>
+      </c>
+      <c r="C8" s="2">
         <v>46224</v>
-      </c>
-      <c r="C8" s="2">
-        <v>46223</v>
       </c>
       <c r="D8" t="s">
         <v>29</v>
@@ -877,16 +877,16 @@
         <v>1</v>
       </c>
       <c r="F8">
-        <v>0.5585486117996296</v>
+        <v>0.7682790670394533</v>
       </c>
       <c r="G8">
-        <v>1.425604946971071</v>
+        <v>1.570669371859712</v>
       </c>
       <c r="H8">
-        <v>1.384949346223931</v>
+        <v>1.384902669655009</v>
       </c>
       <c r="I8">
-        <v>0.3471952579018946</v>
+        <v>0.346219152046969</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -898,19 +898,19 @@
         <v>111</v>
       </c>
       <c r="M8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N8">
-        <v>-0.1991438290802461</v>
+        <v>-0.204623617910121</v>
       </c>
       <c r="O8">
-        <v>-41.58421369413759</v>
+        <v>-43.62312548715857</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>1.425604946971071</v>
+        <v>1.570669371859712</v>
       </c>
       <c r="R8" t="b">
         <v>1</v>
@@ -921,10 +921,10 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
+        <v>46225</v>
+      </c>
+      <c r="C9" s="2">
         <v>46224</v>
-      </c>
-      <c r="C9" s="2">
-        <v>46223</v>
       </c>
       <c r="D9" t="s">
         <v>28</v>
@@ -936,13 +936,13 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>1.128653120691019</v>
+        <v>1.277602445120374</v>
       </c>
       <c r="H9">
-        <v>2.937323018199722</v>
+        <v>2.937324221777735</v>
       </c>
       <c r="I9">
-        <v>0.6233717704189171</v>
+        <v>0.6233904036062473</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -954,19 +954,19 @@
         <v>76</v>
       </c>
       <c r="M9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N9">
-        <v>0.02315920383942704</v>
+        <v>0.03233410476874581</v>
       </c>
       <c r="O9">
-        <v>1.902918999630138</v>
+        <v>2.852949308391263</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>1.128653120691019</v>
+        <v>1.277602445120374</v>
       </c>
       <c r="R9" t="b">
         <v>1</v>
@@ -977,10 +977,10 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
+        <v>46225</v>
+      </c>
+      <c r="C10" s="2">
         <v>46224</v>
-      </c>
-      <c r="C10" s="2">
-        <v>46223</v>
       </c>
       <c r="D10" t="s">
         <v>29</v>
@@ -989,16 +989,16 @@
         <v>1</v>
       </c>
       <c r="F10">
-        <v>0.2357537202218213</v>
+        <v>0.409297788694392</v>
       </c>
       <c r="G10">
-        <v>1.743477961427452</v>
+        <v>1.897848379278704</v>
       </c>
       <c r="H10">
-        <v>1.974217849150896</v>
+        <v>1.977167293764356</v>
       </c>
       <c r="I10">
-        <v>0.4366000685367047</v>
+        <v>0.4372490667200934</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1010,19 +1010,19 @@
         <v>232</v>
       </c>
       <c r="M10">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N10">
-        <v>-33.29020620986837</v>
+        <v>-34.21188265856526</v>
       </c>
       <c r="O10">
-        <v>-50.39062460137918</v>
+        <v>-50.72990067467168</v>
       </c>
       <c r="P10">
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>1.743477961427452</v>
+        <v>1.897848379278704</v>
       </c>
       <c r="R10" t="b">
         <v>1</v>
@@ -1033,10 +1033,10 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
+        <v>46225</v>
+      </c>
+      <c r="C11" s="2">
         <v>46224</v>
-      </c>
-      <c r="C11" s="2">
-        <v>46223</v>
       </c>
       <c r="D11" t="s">
         <v>28</v>
@@ -1048,13 +1048,13 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>1.879864558389473</v>
+        <v>1.744476749522717</v>
       </c>
       <c r="H11">
-        <v>3.105010447733765</v>
+        <v>3.105010374469134</v>
       </c>
       <c r="I11">
-        <v>0.6562139205345878</v>
+        <v>0.6547042365237361</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -1066,19 +1066,19 @@
         <v>211</v>
       </c>
       <c r="M11">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="N11">
-        <v>9317.360388976971</v>
+        <v>9434.382016361316</v>
       </c>
       <c r="O11">
-        <v>107.5091859078211</v>
+        <v>112.8051962874575</v>
       </c>
       <c r="P11">
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>1.879864558389473</v>
+        <v>1.744476749522717</v>
       </c>
       <c r="R11" t="b">
         <v>1</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -529,10 +529,10 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
+        <v>46226</v>
+      </c>
+      <c r="C2" s="2">
         <v>46225</v>
-      </c>
-      <c r="C2" s="2">
-        <v>46224</v>
       </c>
       <c r="D2" t="s">
         <v>28</v>
@@ -544,13 +544,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>0.6146742369239991</v>
+        <v>0.5645803466869699</v>
       </c>
       <c r="H2">
-        <v>1.019627072375616</v>
+        <v>1.024721741061756</v>
       </c>
       <c r="I2">
-        <v>0.2553236364198954</v>
+        <v>0.2559177303522808</v>
       </c>
       <c r="J2">
         <v>6</v>
@@ -562,19 +562,19 @@
         <v>148</v>
       </c>
       <c r="M2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N2">
-        <v>1.405823667017329</v>
+        <v>1.42493093522022</v>
       </c>
       <c r="O2">
-        <v>35.02612756178503</v>
+        <v>36.91325998387047</v>
       </c>
       <c r="P2">
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.6146742369239991</v>
+        <v>0.5645803466869699</v>
       </c>
       <c r="R2" t="b">
         <v>1</v>
@@ -585,10 +585,10 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
+        <v>46226</v>
+      </c>
+      <c r="C3" s="2">
         <v>46225</v>
-      </c>
-      <c r="C3" s="2">
-        <v>46224</v>
       </c>
       <c r="D3" t="s">
         <v>28</v>
@@ -600,13 +600,13 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>0.5011456292692775</v>
+        <v>0.517013818993594</v>
       </c>
       <c r="H3">
-        <v>1.812514577199376</v>
+        <v>1.815036677516612</v>
       </c>
       <c r="I3">
-        <v>0.4307273584754428</v>
+        <v>0.4306836633128541</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -618,19 +618,19 @@
         <v>224</v>
       </c>
       <c r="M3">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="N3">
-        <v>0.1654796827999316</v>
+        <v>0.167408620722124</v>
       </c>
       <c r="O3">
-        <v>45.82564650774516</v>
+        <v>51.40301985107469</v>
       </c>
       <c r="P3">
-        <v>0.1741474368065233</v>
+        <v>0.1464518905880104</v>
       </c>
       <c r="Q3">
-        <v>0.6068221515610548</v>
+        <v>0.6057231142480831</v>
       </c>
       <c r="R3" t="b">
         <v>1</v>
@@ -641,10 +641,10 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
+        <v>46226</v>
+      </c>
+      <c r="C4" s="2">
         <v>46225</v>
-      </c>
-      <c r="C4" s="2">
-        <v>46224</v>
       </c>
       <c r="D4" t="s">
         <v>28</v>
@@ -653,16 +653,16 @@
         <v>-1</v>
       </c>
       <c r="F4">
-        <v>0.4634407824260308</v>
+        <v>0.5769827144540528</v>
       </c>
       <c r="G4">
-        <v>1.975753434410489</v>
+        <v>2.089533310047968</v>
       </c>
       <c r="H4">
-        <v>2.011654854190507</v>
+        <v>2.01389912998688</v>
       </c>
       <c r="I4">
-        <v>0.4910036669600482</v>
+        <v>0.4912413169467449</v>
       </c>
       <c r="J4">
         <v>6</v>
@@ -674,19 +674,19 @@
         <v>145</v>
       </c>
       <c r="M4">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N4">
-        <v>5.05780245640053</v>
+        <v>5.101532840205927</v>
       </c>
       <c r="O4">
-        <v>165.9072970703082</v>
+        <v>182.8974641815184</v>
       </c>
       <c r="P4">
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>1.975753434410489</v>
+        <v>2.089533310047968</v>
       </c>
       <c r="R4" t="b">
         <v>1</v>
@@ -697,10 +697,10 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
+        <v>46226</v>
+      </c>
+      <c r="C5" s="2">
         <v>46225</v>
-      </c>
-      <c r="C5" s="2">
-        <v>46224</v>
       </c>
       <c r="D5" t="s">
         <v>28</v>
@@ -709,16 +709,16 @@
         <v>-1</v>
       </c>
       <c r="F5">
-        <v>0.9997503834852586</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>1.607081868208929</v>
+        <v>1.842751679610346</v>
       </c>
       <c r="H5">
-        <v>1.315463401391202</v>
+        <v>1.32080734197964</v>
       </c>
       <c r="I5">
-        <v>0.2917641251057982</v>
+        <v>0.2909730276283766</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -730,19 +730,19 @@
         <v>225</v>
       </c>
       <c r="M5">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N5">
-        <v>0.2469994654933741</v>
+        <v>0.2518537495121958</v>
       </c>
       <c r="O5">
-        <v>61.72231176987483</v>
+        <v>74.13693215245453</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>1.607081868208929</v>
+        <v>1.842751679610346</v>
       </c>
       <c r="R5" t="b">
         <v>1</v>
@@ -753,10 +753,10 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
+        <v>46226</v>
+      </c>
+      <c r="C6" s="2">
         <v>46225</v>
-      </c>
-      <c r="C6" s="2">
-        <v>46224</v>
       </c>
       <c r="D6" t="s">
         <v>29</v>
@@ -768,37 +768,37 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0.004995935529032214</v>
+        <v>0.0594261786988079</v>
       </c>
       <c r="H6">
-        <v>0.9397041753197074</v>
+        <v>0.9400584369214166</v>
       </c>
       <c r="I6">
-        <v>0.2553073828494136</v>
+        <v>0.2555461592808483</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K6">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="L6">
         <v>156</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N6">
-        <v>-0.03093584700108248</v>
+        <v>-0.03347138845029436</v>
       </c>
       <c r="O6">
-        <v>-0.4038622323901113</v>
+        <v>-0.4646453067437329</v>
       </c>
       <c r="P6">
-        <v>0.4598935499825785</v>
+        <v>0.2606580348996728</v>
       </c>
       <c r="Q6">
-        <v>0.009249909029731206</v>
+        <v>0.08037712114818735</v>
       </c>
       <c r="R6" t="b">
         <v>1</v>
@@ -809,10 +809,10 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
+        <v>46226</v>
+      </c>
+      <c r="C7" s="2">
         <v>46225</v>
-      </c>
-      <c r="C7" s="2">
-        <v>46224</v>
       </c>
       <c r="D7" t="s">
         <v>29</v>
@@ -824,13 +824,13 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>0.393898797014347</v>
+        <v>0.3098825048213359</v>
       </c>
       <c r="H7">
-        <v>1.348294191642339</v>
+        <v>1.34745292007962</v>
       </c>
       <c r="I7">
-        <v>0.3092055820418288</v>
+        <v>0.3089202351428793</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -842,19 +842,19 @@
         <v>238</v>
       </c>
       <c r="M7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N7">
-        <v>-0.009093891111777868</v>
+        <v>-0.01128951886296975</v>
       </c>
       <c r="O7">
-        <v>-1.330071829971689</v>
+        <v>-1.867028103261198</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>0.393898797014347</v>
+        <v>0.3098825048213359</v>
       </c>
       <c r="R7" t="b">
         <v>1</v>
@@ -865,10 +865,10 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
+        <v>46226</v>
+      </c>
+      <c r="C8" s="2">
         <v>46225</v>
-      </c>
-      <c r="C8" s="2">
-        <v>46224</v>
       </c>
       <c r="D8" t="s">
         <v>29</v>
@@ -877,16 +877,16 @@
         <v>1</v>
       </c>
       <c r="F8">
-        <v>0.7682790670394533</v>
+        <v>1</v>
       </c>
       <c r="G8">
-        <v>1.570669371859712</v>
+        <v>1.881072780285014</v>
       </c>
       <c r="H8">
-        <v>1.384902669655009</v>
+        <v>1.385324122809482</v>
       </c>
       <c r="I8">
-        <v>0.346219152046969</v>
+        <v>0.345541311904077</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -898,19 +898,19 @@
         <v>111</v>
       </c>
       <c r="M8">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N8">
-        <v>-0.204623617910121</v>
+        <v>-0.2104041769811501</v>
       </c>
       <c r="O8">
-        <v>-43.62312548715857</v>
+        <v>-50.2586329591557</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>1.570669371859712</v>
+        <v>1.881072780285014</v>
       </c>
       <c r="R8" t="b">
         <v>1</v>
@@ -921,10 +921,10 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
+        <v>46226</v>
+      </c>
+      <c r="C9" s="2">
         <v>46225</v>
-      </c>
-      <c r="C9" s="2">
-        <v>46224</v>
       </c>
       <c r="D9" t="s">
         <v>28</v>
@@ -936,13 +936,13 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>1.277602445120374</v>
+        <v>1.280426642031332</v>
       </c>
       <c r="H9">
-        <v>2.937324221777735</v>
+        <v>2.937325310729269</v>
       </c>
       <c r="I9">
-        <v>0.6233904036062473</v>
+        <v>0.6231572636046062</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -954,19 +954,19 @@
         <v>76</v>
       </c>
       <c r="M9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N9">
-        <v>0.03233410476874581</v>
+        <v>0.04180532464595134</v>
       </c>
       <c r="O9">
-        <v>2.852949308391263</v>
+        <v>3.855309564872656</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>1.277602445120374</v>
+        <v>1.280426642031332</v>
       </c>
       <c r="R9" t="b">
         <v>1</v>
@@ -977,10 +977,10 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
+        <v>46226</v>
+      </c>
+      <c r="C10" s="2">
         <v>46225</v>
-      </c>
-      <c r="C10" s="2">
-        <v>46224</v>
       </c>
       <c r="D10" t="s">
         <v>29</v>
@@ -989,16 +989,16 @@
         <v>1</v>
       </c>
       <c r="F10">
-        <v>0.409297788694392</v>
+        <v>1</v>
       </c>
       <c r="G10">
-        <v>1.897848379278704</v>
+        <v>2.42202431667825</v>
       </c>
       <c r="H10">
-        <v>1.977167293764356</v>
+        <v>1.98090314013549</v>
       </c>
       <c r="I10">
-        <v>0.4372490667200934</v>
+        <v>0.4380572948529177</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1010,19 +1010,19 @@
         <v>232</v>
       </c>
       <c r="M10">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N10">
-        <v>-34.21188265856526</v>
+        <v>-35.18420119184115</v>
       </c>
       <c r="O10">
-        <v>-50.72990067467168</v>
+        <v>-64.7661319684144</v>
       </c>
       <c r="P10">
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>1.897848379278704</v>
+        <v>2.42202431667825</v>
       </c>
       <c r="R10" t="b">
         <v>1</v>
@@ -1033,10 +1033,10 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
+        <v>46226</v>
+      </c>
+      <c r="C11" s="2">
         <v>46225</v>
-      </c>
-      <c r="C11" s="2">
-        <v>46224</v>
       </c>
       <c r="D11" t="s">
         <v>28</v>
@@ -1048,13 +1048,13 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>1.744476749522717</v>
+        <v>1.6162473010679</v>
       </c>
       <c r="H11">
-        <v>3.105010374469134</v>
+        <v>3.105010308182087</v>
       </c>
       <c r="I11">
-        <v>0.6547042365237361</v>
+        <v>0.6533390555545837</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -1066,19 +1066,19 @@
         <v>211</v>
       </c>
       <c r="M11">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N11">
-        <v>9434.382016361316</v>
+        <v>9538.817447101072</v>
       </c>
       <c r="O11">
-        <v>112.8051962874575</v>
+        <v>124.9751481053144</v>
       </c>
       <c r="P11">
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>1.744476749522717</v>
+        <v>1.6162473010679</v>
       </c>
       <c r="R11" t="b">
         <v>1</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -529,10 +529,10 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
+        <v>46227</v>
+      </c>
+      <c r="C2" s="2">
         <v>46226</v>
-      </c>
-      <c r="C2" s="2">
-        <v>46225</v>
       </c>
       <c r="D2" t="s">
         <v>28</v>
@@ -544,13 +544,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>0.5645803466869699</v>
+        <v>0.5862595877272422</v>
       </c>
       <c r="H2">
-        <v>1.024721741061756</v>
+        <v>1.029331203206359</v>
       </c>
       <c r="I2">
-        <v>0.2559177303522808</v>
+        <v>0.2563986777018382</v>
       </c>
       <c r="J2">
         <v>6</v>
@@ -562,19 +562,19 @@
         <v>148</v>
       </c>
       <c r="M2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N2">
-        <v>1.42493093522022</v>
+        <v>1.442897795737395</v>
       </c>
       <c r="O2">
-        <v>36.91325998387047</v>
+        <v>36.43089891670468</v>
       </c>
       <c r="P2">
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.5645803466869699</v>
+        <v>0.5862595877272422</v>
       </c>
       <c r="R2" t="b">
         <v>1</v>
@@ -585,10 +585,10 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
+        <v>46227</v>
+      </c>
+      <c r="C3" s="2">
         <v>46226</v>
-      </c>
-      <c r="C3" s="2">
-        <v>46225</v>
       </c>
       <c r="D3" t="s">
         <v>28</v>
@@ -600,13 +600,13 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>0.517013818993594</v>
+        <v>0.7086979502669031</v>
       </c>
       <c r="H3">
-        <v>1.815036677516612</v>
+        <v>1.817318577803635</v>
       </c>
       <c r="I3">
-        <v>0.4306836633128541</v>
+        <v>0.430544055727907</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -618,19 +618,19 @@
         <v>224</v>
       </c>
       <c r="M3">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N3">
-        <v>0.167408620722124</v>
+        <v>0.1692292765101455</v>
       </c>
       <c r="O3">
-        <v>51.40301985107469</v>
+        <v>53.7601513760393</v>
       </c>
       <c r="P3">
-        <v>0.1464518905880104</v>
+        <v>0</v>
       </c>
       <c r="Q3">
-        <v>0.6057231142480831</v>
+        <v>0.7086979502669031</v>
       </c>
       <c r="R3" t="b">
         <v>1</v>
@@ -641,10 +641,10 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
+        <v>46227</v>
+      </c>
+      <c r="C4" s="2">
         <v>46226</v>
-      </c>
-      <c r="C4" s="2">
-        <v>46225</v>
       </c>
       <c r="D4" t="s">
         <v>28</v>
@@ -653,16 +653,16 @@
         <v>-1</v>
       </c>
       <c r="F4">
-        <v>0.5769827144540528</v>
+        <v>0.5599390518113131</v>
       </c>
       <c r="G4">
-        <v>2.089533310047968</v>
+        <v>2.076735691128985</v>
       </c>
       <c r="H4">
-        <v>2.01389912998688</v>
+        <v>2.017822181847034</v>
       </c>
       <c r="I4">
-        <v>0.4912413169467449</v>
+        <v>0.4914451221835276</v>
       </c>
       <c r="J4">
         <v>6</v>
@@ -674,19 +674,19 @@
         <v>145</v>
       </c>
       <c r="M4">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N4">
-        <v>5.101532840205927</v>
+        <v>5.145317840427196</v>
       </c>
       <c r="O4">
-        <v>182.8974641815184</v>
+        <v>176.5983078352066</v>
       </c>
       <c r="P4">
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>2.089533310047968</v>
+        <v>2.076735691128985</v>
       </c>
       <c r="R4" t="b">
         <v>1</v>
@@ -697,10 +697,10 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
+        <v>46227</v>
+      </c>
+      <c r="C5" s="2">
         <v>46226</v>
-      </c>
-      <c r="C5" s="2">
-        <v>46225</v>
       </c>
       <c r="D5" t="s">
         <v>28</v>
@@ -712,13 +712,13 @@
         <v>1</v>
       </c>
       <c r="G5">
-        <v>1.842751679610346</v>
+        <v>2.019393163375722</v>
       </c>
       <c r="H5">
-        <v>1.32080734197964</v>
+        <v>1.328620429747441</v>
       </c>
       <c r="I5">
-        <v>0.2909730276283766</v>
+        <v>0.2904685834769841</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -730,19 +730,19 @@
         <v>225</v>
       </c>
       <c r="M5">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N5">
-        <v>0.2518537495121958</v>
+        <v>0.2567858157610953</v>
       </c>
       <c r="O5">
-        <v>74.13693215245453</v>
+        <v>76.21372526299214</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>1.842751679610346</v>
+        <v>2.019393163375722</v>
       </c>
       <c r="R5" t="b">
         <v>1</v>
@@ -753,10 +753,10 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
+        <v>46227</v>
+      </c>
+      <c r="C6" s="2">
         <v>46226</v>
-      </c>
-      <c r="C6" s="2">
-        <v>46225</v>
       </c>
       <c r="D6" t="s">
         <v>29</v>
@@ -768,37 +768,37 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0.0594261786988079</v>
+        <v>0.2169207677842748</v>
       </c>
       <c r="H6">
-        <v>0.9400584369214166</v>
+        <v>0.940378959322963</v>
       </c>
       <c r="I6">
-        <v>0.2555461592808483</v>
+        <v>0.2557684959197717</v>
       </c>
       <c r="J6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K6">
-        <v>0.5</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="L6">
         <v>156</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N6">
-        <v>-0.03347138845029436</v>
+        <v>-0.03066774444948191</v>
       </c>
       <c r="O6">
-        <v>-0.4646453067437329</v>
+        <v>-0.4126326727208271</v>
       </c>
       <c r="P6">
-        <v>0.2606580348996728</v>
+        <v>0.01770718828781134</v>
       </c>
       <c r="Q6">
-        <v>0.08037712114818735</v>
+        <v>0.220831065032605</v>
       </c>
       <c r="R6" t="b">
         <v>1</v>
@@ -809,10 +809,10 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
+        <v>46227</v>
+      </c>
+      <c r="C7" s="2">
         <v>46226</v>
-      </c>
-      <c r="C7" s="2">
-        <v>46225</v>
       </c>
       <c r="D7" t="s">
         <v>29</v>
@@ -824,37 +824,37 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>0.3098825048213359</v>
+        <v>0.006122699155397303</v>
       </c>
       <c r="H7">
-        <v>1.34745292007962</v>
+        <v>1.346691769618113</v>
       </c>
       <c r="I7">
-        <v>0.3089202351428793</v>
+        <v>0.3087318097557467</v>
       </c>
       <c r="J7">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K7">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L7">
         <v>238</v>
       </c>
       <c r="M7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N7">
-        <v>-0.01128951886296975</v>
+        <v>-0.01264320799283605</v>
       </c>
       <c r="O7">
-        <v>-1.867028103261198</v>
+        <v>-2.050685418521751</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>0.3520135567994334</v>
       </c>
       <c r="Q7">
-        <v>0.3098825048213359</v>
+        <v>0.00944880748608839</v>
       </c>
       <c r="R7" t="b">
         <v>1</v>
@@ -865,10 +865,10 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
+        <v>46227</v>
+      </c>
+      <c r="C8" s="2">
         <v>46226</v>
-      </c>
-      <c r="C8" s="2">
-        <v>46225</v>
       </c>
       <c r="D8" t="s">
         <v>29</v>
@@ -880,13 +880,13 @@
         <v>1</v>
       </c>
       <c r="G8">
-        <v>1.881072780285014</v>
+        <v>2.077023474180427</v>
       </c>
       <c r="H8">
-        <v>1.385324122809482</v>
+        <v>1.386485868732976</v>
       </c>
       <c r="I8">
-        <v>0.345541311904077</v>
+        <v>0.3452194519443292</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -898,19 +898,19 @@
         <v>111</v>
       </c>
       <c r="M8">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N8">
-        <v>-0.2104041769811501</v>
+        <v>-0.2165862136072001</v>
       </c>
       <c r="O8">
-        <v>-50.2586329591557</v>
+        <v>-52.11768632693043</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>1.881072780285014</v>
+        <v>2.077023474180427</v>
       </c>
       <c r="R8" t="b">
         <v>1</v>
@@ -921,10 +921,10 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
+        <v>46227</v>
+      </c>
+      <c r="C9" s="2">
         <v>46226</v>
-      </c>
-      <c r="C9" s="2">
-        <v>46225</v>
       </c>
       <c r="D9" t="s">
         <v>28</v>
@@ -936,13 +936,13 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>1.280426642031332</v>
+        <v>1.201166085349996</v>
       </c>
       <c r="H9">
-        <v>2.937325310729269</v>
+        <v>2.937326295971134</v>
       </c>
       <c r="I9">
-        <v>0.6231572636046062</v>
+        <v>0.6227019298474805</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -954,19 +954,19 @@
         <v>76</v>
       </c>
       <c r="M9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N9">
-        <v>0.04180532464595134</v>
+        <v>0.05090402305454826</v>
       </c>
       <c r="O9">
-        <v>3.855309564872656</v>
+        <v>4.838128464111866</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>1.280426642031332</v>
+        <v>1.201166085349996</v>
       </c>
       <c r="R9" t="b">
         <v>1</v>
@@ -977,10 +977,10 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
+        <v>46227</v>
+      </c>
+      <c r="C10" s="2">
         <v>46226</v>
-      </c>
-      <c r="C10" s="2">
-        <v>46225</v>
       </c>
       <c r="D10" t="s">
         <v>29</v>
@@ -992,13 +992,13 @@
         <v>1</v>
       </c>
       <c r="G10">
-        <v>2.42202431667825</v>
+        <v>2.778900950289698</v>
       </c>
       <c r="H10">
-        <v>1.98090314013549</v>
+        <v>1.985598720854382</v>
       </c>
       <c r="I10">
-        <v>0.4380572948529177</v>
+        <v>0.4391536669320885</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1010,19 +1010,19 @@
         <v>232</v>
       </c>
       <c r="M10">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N10">
-        <v>-35.18420119184115</v>
+        <v>-36.22259904810715</v>
       </c>
       <c r="O10">
-        <v>-64.7661319684144</v>
+        <v>-68.02366018423892</v>
       </c>
       <c r="P10">
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>2.42202431667825</v>
+        <v>2.778900950289698</v>
       </c>
       <c r="R10" t="b">
         <v>1</v>
@@ -1033,10 +1033,10 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
+        <v>46227</v>
+      </c>
+      <c r="C11" s="2">
         <v>46226</v>
-      </c>
-      <c r="C11" s="2">
-        <v>46225</v>
       </c>
       <c r="D11" t="s">
         <v>28</v>
@@ -1048,13 +1048,13 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>1.6162473010679</v>
+        <v>1.679542508140375</v>
       </c>
       <c r="H11">
-        <v>3.105010308182087</v>
+        <v>3.105010248208092</v>
       </c>
       <c r="I11">
-        <v>0.6533390555545837</v>
+        <v>0.6520912943961745</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -1066,19 +1066,19 @@
         <v>211</v>
       </c>
       <c r="M11">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N11">
-        <v>9538.817447101072</v>
+        <v>9635.262821796561</v>
       </c>
       <c r="O11">
-        <v>124.9751481053144</v>
+        <v>129.6506088819649</v>
       </c>
       <c r="P11">
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>1.6162473010679</v>
+        <v>1.679542508140375</v>
       </c>
       <c r="R11" t="b">
         <v>1</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -529,10 +529,10 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
+        <v>46228</v>
+      </c>
+      <c r="C2" s="2">
         <v>46227</v>
-      </c>
-      <c r="C2" s="2">
-        <v>46226</v>
       </c>
       <c r="D2" t="s">
         <v>28</v>
@@ -544,13 +544,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>0.5862595877272422</v>
+        <v>0.5841023495793738</v>
       </c>
       <c r="H2">
-        <v>1.029331203206359</v>
+        <v>1.033501668956238</v>
       </c>
       <c r="I2">
-        <v>0.2563986777018382</v>
+        <v>0.2567512034392858</v>
       </c>
       <c r="J2">
         <v>6</v>
@@ -562,19 +562,19 @@
         <v>148</v>
       </c>
       <c r="M2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N2">
-        <v>1.442897795737395</v>
+        <v>1.460652550411164</v>
       </c>
       <c r="O2">
-        <v>36.43089891670468</v>
+        <v>37.29620402662158</v>
       </c>
       <c r="P2">
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.5862595877272422</v>
+        <v>0.5841023495793738</v>
       </c>
       <c r="R2" t="b">
         <v>1</v>
@@ -585,7 +585,7 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="C3" s="2">
         <v>46226</v>
@@ -641,10 +641,10 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
+        <v>46228</v>
+      </c>
+      <c r="C4" s="2">
         <v>46227</v>
-      </c>
-      <c r="C4" s="2">
-        <v>46226</v>
       </c>
       <c r="D4" t="s">
         <v>28</v>
@@ -653,16 +653,16 @@
         <v>-1</v>
       </c>
       <c r="F4">
-        <v>0.5599390518113131</v>
+        <v>0.6464114921989814</v>
       </c>
       <c r="G4">
-        <v>2.076735691128985</v>
+        <v>2.167074898742928</v>
       </c>
       <c r="H4">
-        <v>2.017822181847034</v>
+        <v>2.023096667216866</v>
       </c>
       <c r="I4">
-        <v>0.4914451221835276</v>
+        <v>0.4916903357913585</v>
       </c>
       <c r="J4">
         <v>6</v>
@@ -674,19 +674,19 @@
         <v>145</v>
       </c>
       <c r="M4">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N4">
-        <v>5.145317840427196</v>
+        <v>5.190782893822175</v>
       </c>
       <c r="O4">
-        <v>176.5983078352066</v>
+        <v>176.257483661194</v>
       </c>
       <c r="P4">
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>2.076735691128985</v>
+        <v>2.167074898742928</v>
       </c>
       <c r="R4" t="b">
         <v>1</v>
@@ -697,7 +697,7 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="C5" s="2">
         <v>46226</v>
@@ -753,52 +753,52 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
+        <v>46228</v>
+      </c>
+      <c r="C6" s="2">
         <v>46227</v>
       </c>
-      <c r="C6" s="2">
-        <v>46226</v>
-      </c>
       <c r="D6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0.2169207677842748</v>
+        <v>0.3302812254125366</v>
       </c>
       <c r="H6">
-        <v>0.940378959322963</v>
+        <v>0.940668955781505</v>
       </c>
       <c r="I6">
-        <v>0.2557684959197717</v>
+        <v>0.2559731930655917</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K6">
-        <v>0.1666666666666667</v>
+        <v>1</v>
       </c>
       <c r="L6">
         <v>156</v>
       </c>
       <c r="M6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N6">
-        <v>-0.03066774444948191</v>
+        <v>-0.02146218684261974</v>
       </c>
       <c r="O6">
-        <v>-0.4126326727208271</v>
+        <v>-0.2966468380541591</v>
       </c>
       <c r="P6">
-        <v>0.01770718828781134</v>
+        <v>0</v>
       </c>
       <c r="Q6">
-        <v>0.220831065032605</v>
+        <v>0.3302812254125366</v>
       </c>
       <c r="R6" t="b">
         <v>1</v>
@@ -809,7 +809,7 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="C7" s="2">
         <v>46226</v>
@@ -865,7 +865,7 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="C8" s="2">
         <v>46226</v>
@@ -921,7 +921,7 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="C9" s="2">
         <v>46226</v>
@@ -977,7 +977,7 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="C10" s="2">
         <v>46226</v>
@@ -1033,7 +1033,7 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="C11" s="2">
         <v>46226</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -529,10 +529,10 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>46228</v>
+        <v>46231</v>
       </c>
       <c r="C2" s="2">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="D2" t="s">
         <v>28</v>
@@ -544,13 +544,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>0.5841023495793738</v>
+        <v>0.571803579797887</v>
       </c>
       <c r="H2">
-        <v>1.033501668956238</v>
+        <v>1.037274947491843</v>
       </c>
       <c r="I2">
-        <v>0.2567512034392858</v>
+        <v>0.2569922139878648</v>
       </c>
       <c r="J2">
         <v>6</v>
@@ -562,19 +562,19 @@
         <v>148</v>
       </c>
       <c r="M2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N2">
-        <v>1.460652550411164</v>
+        <v>1.477622604937486</v>
       </c>
       <c r="O2">
-        <v>37.29620402662158</v>
+        <v>38.70293071866203</v>
       </c>
       <c r="P2">
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.5841023495793738</v>
+        <v>0.571803579797887</v>
       </c>
       <c r="R2" t="b">
         <v>1</v>
@@ -585,10 +585,10 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>46228</v>
+        <v>46231</v>
       </c>
       <c r="C3" s="2">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="D3" t="s">
         <v>28</v>
@@ -600,13 +600,13 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>0.7086979502669031</v>
+        <v>0.5147098189776956</v>
       </c>
       <c r="H3">
-        <v>1.817318577803635</v>
+        <v>1.821251104375375</v>
       </c>
       <c r="I3">
-        <v>0.430544055727907</v>
+        <v>0.4300080763958445</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -618,19 +618,19 @@
         <v>224</v>
       </c>
       <c r="M3">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="N3">
-        <v>0.1692292765101455</v>
+        <v>0.1722459216346006</v>
       </c>
       <c r="O3">
-        <v>53.7601513760393</v>
+        <v>57.77987068130881</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>0.05705810685182763</v>
       </c>
       <c r="Q3">
-        <v>0.7086979502669031</v>
+        <v>0.5458552883457634</v>
       </c>
       <c r="R3" t="b">
         <v>1</v>
@@ -641,10 +641,10 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>46228</v>
+        <v>46231</v>
       </c>
       <c r="C4" s="2">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="D4" t="s">
         <v>28</v>
@@ -653,16 +653,16 @@
         <v>-1</v>
       </c>
       <c r="F4">
-        <v>0.6464114921989814</v>
+        <v>0.6317203254759612</v>
       </c>
       <c r="G4">
-        <v>2.167074898742928</v>
+        <v>2.158244697090097</v>
       </c>
       <c r="H4">
-        <v>2.023096667216866</v>
+        <v>2.028631732981986</v>
       </c>
       <c r="I4">
-        <v>0.4916903357913585</v>
+        <v>0.4920006219228679</v>
       </c>
       <c r="J4">
         <v>6</v>
@@ -674,19 +674,19 @@
         <v>145</v>
       </c>
       <c r="M4">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N4">
-        <v>5.190782893822175</v>
+        <v>5.238291004306384</v>
       </c>
       <c r="O4">
-        <v>176.257483661194</v>
+        <v>169.5631770180097</v>
       </c>
       <c r="P4">
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>2.167074898742928</v>
+        <v>2.158244697090097</v>
       </c>
       <c r="R4" t="b">
         <v>1</v>
@@ -697,10 +697,10 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>46228</v>
+        <v>46231</v>
       </c>
       <c r="C5" s="2">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="D5" t="s">
         <v>28</v>
@@ -712,13 +712,13 @@
         <v>1</v>
       </c>
       <c r="G5">
-        <v>2.019393163375722</v>
+        <v>2.184951219045213</v>
       </c>
       <c r="H5">
-        <v>1.328620429747441</v>
+        <v>1.34456661023847</v>
       </c>
       <c r="I5">
-        <v>0.2904685834769841</v>
+        <v>0.2904876847166786</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -730,19 +730,19 @@
         <v>225</v>
       </c>
       <c r="M5">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N5">
-        <v>0.2567858157610953</v>
+        <v>0.2669791196863985</v>
       </c>
       <c r="O5">
-        <v>76.21372526299214</v>
+        <v>82.62866531689149</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>2.019393163375722</v>
+        <v>2.184951219045213</v>
       </c>
       <c r="R5" t="b">
         <v>1</v>
@@ -753,10 +753,10 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>46228</v>
+        <v>46231</v>
       </c>
       <c r="C6" s="2">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="D6" t="s">
         <v>28</v>
@@ -768,13 +768,13 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0.3302812254125366</v>
+        <v>0.4771409674339303</v>
       </c>
       <c r="H6">
-        <v>0.940668955781505</v>
+        <v>0.9409313335297097</v>
       </c>
       <c r="I6">
-        <v>0.2559731930655917</v>
+        <v>0.256158515403575</v>
       </c>
       <c r="J6">
         <v>6</v>
@@ -783,22 +783,22 @@
         <v>1</v>
       </c>
       <c r="L6">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N6">
-        <v>-0.02146218684261974</v>
+        <v>0</v>
       </c>
       <c r="O6">
-        <v>-0.2966468380541591</v>
+        <v>0</v>
       </c>
       <c r="P6">
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>0.3302812254125366</v>
+        <v>0.4771409674339303</v>
       </c>
       <c r="R6" t="b">
         <v>1</v>
@@ -809,10 +809,10 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>46228</v>
+        <v>46231</v>
       </c>
       <c r="C7" s="2">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="D7" t="s">
         <v>29</v>
@@ -824,37 +824,37 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>0.006122699155397303</v>
+        <v>0.3302513599941327</v>
       </c>
       <c r="H7">
-        <v>1.346691769618113</v>
+        <v>1.345380036396467</v>
       </c>
       <c r="I7">
-        <v>0.3087318097557467</v>
+        <v>0.3085866010092306</v>
       </c>
       <c r="J7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K7">
-        <v>0.6666666666666666</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="L7">
         <v>238</v>
       </c>
       <c r="M7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N7">
-        <v>-0.01264320799283605</v>
+        <v>-0.01294724406311846</v>
       </c>
       <c r="O7">
-        <v>-2.050685418521751</v>
+        <v>-2.18295197065886</v>
       </c>
       <c r="P7">
-        <v>0.3520135567994334</v>
+        <v>0.006947381048209168</v>
       </c>
       <c r="Q7">
-        <v>0.00944880748608839</v>
+        <v>0.3325617934956226</v>
       </c>
       <c r="R7" t="b">
         <v>1</v>
@@ -865,10 +865,10 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>46228</v>
+        <v>46231</v>
       </c>
       <c r="C8" s="2">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="D8" t="s">
         <v>29</v>
@@ -880,13 +880,13 @@
         <v>1</v>
       </c>
       <c r="G8">
-        <v>2.077023474180427</v>
+        <v>2.475696314671024</v>
       </c>
       <c r="H8">
-        <v>1.386485868732976</v>
+        <v>1.392802531042084</v>
       </c>
       <c r="I8">
-        <v>0.3452194519443292</v>
+        <v>0.3459266858182101</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -898,19 +898,19 @@
         <v>111</v>
       </c>
       <c r="M8">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="N8">
-        <v>-0.2165862136072001</v>
+        <v>-0.2300195150605016</v>
       </c>
       <c r="O8">
-        <v>-52.11768632693043</v>
+        <v>-59.39271875409492</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>2.077023474180427</v>
+        <v>2.475696314671024</v>
       </c>
       <c r="R8" t="b">
         <v>1</v>
@@ -921,10 +921,10 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>46228</v>
+        <v>46231</v>
       </c>
       <c r="C9" s="2">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="D9" t="s">
         <v>28</v>
@@ -936,13 +936,13 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>1.201166085349996</v>
+        <v>1.517345620394397</v>
       </c>
       <c r="H9">
-        <v>2.937326295971134</v>
+        <v>2.937327993893623</v>
       </c>
       <c r="I9">
-        <v>0.6227019298474805</v>
+        <v>0.621166868342472</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -954,19 +954,19 @@
         <v>76</v>
       </c>
       <c r="M9">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N9">
-        <v>0.05090402305454826</v>
+        <v>0.0689818250120566</v>
       </c>
       <c r="O9">
-        <v>4.838128464111866</v>
+        <v>7.484949042191846</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>1.201166085349996</v>
+        <v>1.517345620394397</v>
       </c>
       <c r="R9" t="b">
         <v>1</v>
@@ -977,10 +977,10 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>46228</v>
+        <v>46231</v>
       </c>
       <c r="C10" s="2">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="D10" t="s">
         <v>29</v>
@@ -992,13 +992,13 @@
         <v>1</v>
       </c>
       <c r="G10">
-        <v>2.778900950289698</v>
+        <v>3.569077241700109</v>
       </c>
       <c r="H10">
-        <v>1.985598720854382</v>
+        <v>1.996036001583704</v>
       </c>
       <c r="I10">
-        <v>0.4391536669320885</v>
+        <v>0.4430211660443626</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1010,19 +1010,19 @@
         <v>232</v>
       </c>
       <c r="M10">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="N10">
-        <v>-36.22259904810715</v>
+        <v>-38.48895145839418</v>
       </c>
       <c r="O10">
-        <v>-68.02366018423892</v>
+        <v>-87.25533485831448</v>
       </c>
       <c r="P10">
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>2.778900950289698</v>
+        <v>3.569077241700109</v>
       </c>
       <c r="R10" t="b">
         <v>1</v>
@@ -1033,10 +1033,10 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>46228</v>
+        <v>46231</v>
       </c>
       <c r="C11" s="2">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="D11" t="s">
         <v>28</v>
@@ -1048,13 +1048,13 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>1.679542508140375</v>
+        <v>1.67225064054127</v>
       </c>
       <c r="H11">
-        <v>3.105010248208092</v>
+        <v>3.105010193945906</v>
       </c>
       <c r="I11">
-        <v>0.6520912943961745</v>
+        <v>0.6509203303097993</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -1066,19 +1066,19 @@
         <v>211</v>
       </c>
       <c r="M11">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="N11">
-        <v>9635.262821796561</v>
+        <v>9728.872909110687</v>
       </c>
       <c r="O11">
-        <v>129.6506088819649</v>
+        <v>135.9567793890612</v>
       </c>
       <c r="P11">
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>1.679542508140375</v>
+        <v>1.67225064054127</v>
       </c>
       <c r="R11" t="b">
         <v>1</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -529,10 +529,10 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
+        <v>46232</v>
+      </c>
+      <c r="C2" s="2">
         <v>46231</v>
-      </c>
-      <c r="C2" s="2">
-        <v>46230</v>
       </c>
       <c r="D2" t="s">
         <v>28</v>
@@ -544,13 +544,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>0.571803579797887</v>
+        <v>0.5921660548914897</v>
       </c>
       <c r="H2">
-        <v>1.037274947491843</v>
+        <v>1.040688866166914</v>
       </c>
       <c r="I2">
-        <v>0.2569922139878648</v>
+        <v>0.2571438213704141</v>
       </c>
       <c r="J2">
         <v>6</v>
@@ -562,19 +562,19 @@
         <v>148</v>
       </c>
       <c r="M2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N2">
-        <v>1.477622604937486</v>
+        <v>1.494133544604837</v>
       </c>
       <c r="O2">
-        <v>38.70293071866203</v>
+        <v>39.55425010299486</v>
       </c>
       <c r="P2">
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.571803579797887</v>
+        <v>0.5921660548914897</v>
       </c>
       <c r="R2" t="b">
         <v>1</v>
@@ -585,10 +585,10 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
+        <v>46232</v>
+      </c>
+      <c r="C3" s="2">
         <v>46231</v>
-      </c>
-      <c r="C3" s="2">
-        <v>46230</v>
       </c>
       <c r="D3" t="s">
         <v>28</v>
@@ -600,13 +600,13 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>0.5147098189776956</v>
+        <v>0.650343444575059</v>
       </c>
       <c r="H3">
-        <v>1.821251104375375</v>
+        <v>1.822941154485373</v>
       </c>
       <c r="I3">
-        <v>0.4300080763958445</v>
+        <v>0.4295914250374296</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -618,19 +618,19 @@
         <v>224</v>
       </c>
       <c r="M3">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N3">
-        <v>0.1722459216346006</v>
+        <v>0.173602137219142</v>
       </c>
       <c r="O3">
-        <v>57.77987068130881</v>
+        <v>62.3187159248205</v>
       </c>
       <c r="P3">
-        <v>0.05705810685182763</v>
+        <v>0</v>
       </c>
       <c r="Q3">
-        <v>0.5458552883457634</v>
+        <v>0.650343444575059</v>
       </c>
       <c r="R3" t="b">
         <v>1</v>
@@ -641,10 +641,10 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
+        <v>46232</v>
+      </c>
+      <c r="C4" s="2">
         <v>46231</v>
-      </c>
-      <c r="C4" s="2">
-        <v>46230</v>
       </c>
       <c r="D4" t="s">
         <v>28</v>
@@ -653,16 +653,16 @@
         <v>-1</v>
       </c>
       <c r="F4">
-        <v>0.6317203254759612</v>
+        <v>0.4909375551523664</v>
       </c>
       <c r="G4">
-        <v>2.158244697090097</v>
+        <v>2.024715989915113</v>
       </c>
       <c r="H4">
-        <v>2.028631732981986</v>
+        <v>2.033639649626619</v>
       </c>
       <c r="I4">
-        <v>0.4920006219228679</v>
+        <v>0.4923428424414246</v>
       </c>
       <c r="J4">
         <v>6</v>
@@ -674,19 +674,19 @@
         <v>145</v>
       </c>
       <c r="M4">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N4">
-        <v>5.238291004306384</v>
+        <v>5.286175152194607</v>
       </c>
       <c r="O4">
-        <v>169.5631770180097</v>
+        <v>166.9820670819593</v>
       </c>
       <c r="P4">
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>2.158244697090097</v>
+        <v>2.024715989915113</v>
       </c>
       <c r="R4" t="b">
         <v>1</v>
@@ -697,10 +697,10 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
+        <v>46232</v>
+      </c>
+      <c r="C5" s="2">
         <v>46231</v>
-      </c>
-      <c r="C5" s="2">
-        <v>46230</v>
       </c>
       <c r="D5" t="s">
         <v>28</v>
@@ -712,13 +712,13 @@
         <v>1</v>
       </c>
       <c r="G5">
-        <v>2.184951219045213</v>
+        <v>2.229848045867981</v>
       </c>
       <c r="H5">
-        <v>1.34456661023847</v>
+        <v>1.352866258748792</v>
       </c>
       <c r="I5">
-        <v>0.2904876847166786</v>
+        <v>0.2910993108160414</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -730,19 +730,19 @@
         <v>225</v>
       </c>
       <c r="M5">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N5">
-        <v>0.2669791196863985</v>
+        <v>0.2721798568813517</v>
       </c>
       <c r="O5">
-        <v>82.62866531689149</v>
+        <v>87.75951166142151</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>2.184951219045213</v>
+        <v>2.229848045867981</v>
       </c>
       <c r="R5" t="b">
         <v>1</v>
@@ -753,10 +753,10 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
+        <v>46232</v>
+      </c>
+      <c r="C6" s="2">
         <v>46231</v>
-      </c>
-      <c r="C6" s="2">
-        <v>46230</v>
       </c>
       <c r="D6" t="s">
         <v>28</v>
@@ -768,13 +768,13 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0.4771409674339303</v>
+        <v>0.5766398971767849</v>
       </c>
       <c r="H6">
-        <v>0.9409313335297097</v>
+        <v>0.9411687229209424</v>
       </c>
       <c r="I6">
-        <v>0.256158515403575</v>
+        <v>0.2563174668648399</v>
       </c>
       <c r="J6">
         <v>6</v>
@@ -786,19 +786,19 @@
         <v>157</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>0.02247941273893093</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>0.3197478062941675</v>
       </c>
       <c r="P6">
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>0.4771409674339303</v>
+        <v>0.5766398971767849</v>
       </c>
       <c r="R6" t="b">
         <v>1</v>
@@ -809,52 +809,52 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
+        <v>46232</v>
+      </c>
+      <c r="C7" s="2">
         <v>46231</v>
       </c>
-      <c r="C7" s="2">
-        <v>46230</v>
-      </c>
       <c r="D7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="F7">
         <v>0</v>
       </c>
       <c r="G7">
-        <v>0.3302513599941327</v>
+        <v>0.5577364673232961</v>
       </c>
       <c r="H7">
-        <v>1.345380036396467</v>
+        <v>1.344816303428594</v>
       </c>
       <c r="I7">
-        <v>0.3085866010092306</v>
+        <v>0.3085317604613949</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K7">
-        <v>0.1666666666666667</v>
+        <v>1</v>
       </c>
       <c r="L7">
         <v>238</v>
       </c>
       <c r="M7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N7">
-        <v>-0.01294724406311846</v>
+        <v>-0.01177261687474095</v>
       </c>
       <c r="O7">
-        <v>-2.18295197065886</v>
+        <v>-2.17594080462569</v>
       </c>
       <c r="P7">
-        <v>0.006947381048209168</v>
+        <v>0</v>
       </c>
       <c r="Q7">
-        <v>0.3325617934956226</v>
+        <v>0.5577364673232961</v>
       </c>
       <c r="R7" t="b">
         <v>1</v>
@@ -865,10 +865,10 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
+        <v>46232</v>
+      </c>
+      <c r="C8" s="2">
         <v>46231</v>
-      </c>
-      <c r="C8" s="2">
-        <v>46230</v>
       </c>
       <c r="D8" t="s">
         <v>29</v>
@@ -880,13 +880,13 @@
         <v>1</v>
       </c>
       <c r="G8">
-        <v>2.475696314671024</v>
+        <v>2.744246931337766</v>
       </c>
       <c r="H8">
-        <v>1.392802531042084</v>
+        <v>1.396225104534495</v>
       </c>
       <c r="I8">
-        <v>0.3459266858182101</v>
+        <v>0.3471530561807825</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -898,19 +898,19 @@
         <v>111</v>
       </c>
       <c r="M8">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N8">
-        <v>-0.2300195150605016</v>
+        <v>-0.2373291494140377</v>
       </c>
       <c r="O8">
-        <v>-59.39271875409492</v>
+        <v>-64.85668732767003</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>2.475696314671024</v>
+        <v>2.744246931337766</v>
       </c>
       <c r="R8" t="b">
         <v>1</v>
@@ -921,10 +921,10 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
+        <v>46232</v>
+      </c>
+      <c r="C9" s="2">
         <v>46231</v>
-      </c>
-      <c r="C9" s="2">
-        <v>46230</v>
       </c>
       <c r="D9" t="s">
         <v>28</v>
@@ -936,13 +936,13 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>1.517345620394397</v>
+        <v>1.509101234576306</v>
       </c>
       <c r="H9">
-        <v>2.937327993893623</v>
+        <v>2.937328723596025</v>
       </c>
       <c r="I9">
-        <v>0.621166868342472</v>
+        <v>0.620111281348725</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -954,19 +954,19 @@
         <v>76</v>
       </c>
       <c r="M9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N9">
-        <v>0.0689818250120566</v>
+        <v>0.07851609933033701</v>
       </c>
       <c r="O9">
-        <v>7.484949042191846</v>
+        <v>8.915770870506343</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>1.517345620394397</v>
+        <v>1.509101234576306</v>
       </c>
       <c r="R9" t="b">
         <v>1</v>
@@ -977,10 +977,10 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
+        <v>46232</v>
+      </c>
+      <c r="C10" s="2">
         <v>46231</v>
-      </c>
-      <c r="C10" s="2">
-        <v>46230</v>
       </c>
       <c r="D10" t="s">
         <v>29</v>
@@ -992,13 +992,13 @@
         <v>1</v>
       </c>
       <c r="G10">
-        <v>3.569077241700109</v>
+        <v>3.990078193416717</v>
       </c>
       <c r="H10">
-        <v>1.996036001583704</v>
+        <v>2.001049395254607</v>
       </c>
       <c r="I10">
-        <v>0.4430211660443626</v>
+        <v>0.4461126090969442</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1010,19 +1010,19 @@
         <v>232</v>
       </c>
       <c r="M10">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N10">
-        <v>-38.48895145839418</v>
+        <v>-39.67825494107645</v>
       </c>
       <c r="O10">
-        <v>-87.25533485831448</v>
+        <v>-98.44848368189135</v>
       </c>
       <c r="P10">
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>3.569077241700109</v>
+        <v>3.990078193416717</v>
       </c>
       <c r="R10" t="b">
         <v>1</v>
@@ -1033,10 +1033,10 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
+        <v>46232</v>
+      </c>
+      <c r="C11" s="2">
         <v>46231</v>
-      </c>
-      <c r="C11" s="2">
-        <v>46230</v>
       </c>
       <c r="D11" t="s">
         <v>28</v>
@@ -1048,13 +1048,13 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>1.67225064054127</v>
+        <v>1.777723893238875</v>
       </c>
       <c r="H11">
-        <v>3.105010193945906</v>
+        <v>3.105010144851548</v>
       </c>
       <c r="I11">
-        <v>0.6509203303097993</v>
+        <v>0.6498029449345027</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -1066,19 +1066,19 @@
         <v>211</v>
       </c>
       <c r="M11">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N11">
-        <v>9728.872909110687</v>
+        <v>9821.034735145624</v>
       </c>
       <c r="O11">
-        <v>135.9567793890612</v>
+        <v>140.4251593680497</v>
       </c>
       <c r="P11">
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>1.67225064054127</v>
+        <v>1.777723893238875</v>
       </c>
       <c r="R11" t="b">
         <v>1</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -529,10 +529,10 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
+        <v>46233</v>
+      </c>
+      <c r="C2" s="2">
         <v>46232</v>
-      </c>
-      <c r="C2" s="2">
-        <v>46231</v>
       </c>
       <c r="D2" t="s">
         <v>28</v>
@@ -544,13 +544,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>0.5921660548914897</v>
+        <v>0.6632591236562488</v>
       </c>
       <c r="H2">
-        <v>1.040688866166914</v>
+        <v>1.043777649730073</v>
       </c>
       <c r="I2">
-        <v>0.2571438213704141</v>
+        <v>0.2572268595973431</v>
       </c>
       <c r="J2">
         <v>6</v>
@@ -562,19 +562,19 @@
         <v>148</v>
       </c>
       <c r="M2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N2">
-        <v>1.494133544604837</v>
+        <v>1.511806091415939</v>
       </c>
       <c r="O2">
-        <v>39.55425010299486</v>
+        <v>37.9932599982466</v>
       </c>
       <c r="P2">
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.5921660548914897</v>
+        <v>0.6632591236562488</v>
       </c>
       <c r="R2" t="b">
         <v>1</v>
@@ -585,10 +585,10 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
+        <v>46233</v>
+      </c>
+      <c r="C3" s="2">
         <v>46232</v>
-      </c>
-      <c r="C3" s="2">
-        <v>46231</v>
       </c>
       <c r="D3" t="s">
         <v>28</v>
@@ -600,13 +600,13 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>0.650343444575059</v>
+        <v>0.8276575547104769</v>
       </c>
       <c r="H3">
-        <v>1.822941154485373</v>
+        <v>1.824470247442038</v>
       </c>
       <c r="I3">
-        <v>0.4295914250374296</v>
+        <v>0.4290749374929325</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -618,19 +618,19 @@
         <v>224</v>
       </c>
       <c r="M3">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N3">
-        <v>0.173602137219142</v>
+        <v>0.1751143167646494</v>
       </c>
       <c r="O3">
-        <v>62.3187159248205</v>
+        <v>63.29160796966847</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>0.650343444575059</v>
+        <v>0.8276575547104769</v>
       </c>
       <c r="R3" t="b">
         <v>1</v>
@@ -641,10 +641,10 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
+        <v>46233</v>
+      </c>
+      <c r="C4" s="2">
         <v>46232</v>
-      </c>
-      <c r="C4" s="2">
-        <v>46231</v>
       </c>
       <c r="D4" t="s">
         <v>28</v>
@@ -653,16 +653,16 @@
         <v>-1</v>
       </c>
       <c r="F4">
-        <v>0.4909375551523664</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>2.024715989915113</v>
+        <v>1.541116014666038</v>
       </c>
       <c r="H4">
-        <v>2.033639649626619</v>
+        <v>2.038170621828906</v>
       </c>
       <c r="I4">
-        <v>0.4923428424414246</v>
+        <v>0.4926197824816437</v>
       </c>
       <c r="J4">
         <v>6</v>
@@ -674,19 +674,19 @@
         <v>145</v>
       </c>
       <c r="M4">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="N4">
-        <v>5.286175152194607</v>
+        <v>5.330066196621047</v>
       </c>
       <c r="O4">
-        <v>166.9820670819593</v>
+        <v>155.1370618559138</v>
       </c>
       <c r="P4">
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>2.024715989915113</v>
+        <v>1.541116014666038</v>
       </c>
       <c r="R4" t="b">
         <v>1</v>
@@ -697,10 +697,10 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
+        <v>46233</v>
+      </c>
+      <c r="C5" s="2">
         <v>46232</v>
-      </c>
-      <c r="C5" s="2">
-        <v>46231</v>
       </c>
       <c r="D5" t="s">
         <v>28</v>
@@ -709,16 +709,16 @@
         <v>-1</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>0.7433162552396745</v>
       </c>
       <c r="G5">
-        <v>2.229848045867981</v>
+        <v>1.50386669438296</v>
       </c>
       <c r="H5">
-        <v>1.352866258748792</v>
+        <v>1.361911639918745</v>
       </c>
       <c r="I5">
-        <v>0.2910993108160414</v>
+        <v>0.2917089413619007</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -730,19 +730,19 @@
         <v>225</v>
       </c>
       <c r="M5">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N5">
-        <v>0.2721798568813517</v>
+        <v>0.2768341621742173</v>
       </c>
       <c r="O5">
-        <v>87.75951166142151</v>
+        <v>79.33834739895676</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>2.229848045867981</v>
+        <v>1.50386669438296</v>
       </c>
       <c r="R5" t="b">
         <v>1</v>
@@ -753,10 +753,10 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
+        <v>46233</v>
+      </c>
+      <c r="C6" s="2">
         <v>46232</v>
-      </c>
-      <c r="C6" s="2">
-        <v>46231</v>
       </c>
       <c r="D6" t="s">
         <v>28</v>
@@ -768,13 +768,13 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0.5766398971767849</v>
+        <v>0.4792599117402066</v>
       </c>
       <c r="H6">
-        <v>0.9411687229209424</v>
+        <v>0.9413835037987245</v>
       </c>
       <c r="I6">
-        <v>0.2563174668648399</v>
+        <v>0.2564304644576186</v>
       </c>
       <c r="J6">
         <v>6</v>
@@ -786,19 +786,19 @@
         <v>157</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N6">
-        <v>0.02247941273893093</v>
+        <v>0.04650660223688919</v>
       </c>
       <c r="O6">
-        <v>0.3197478062941675</v>
+        <v>0.6364975426631838</v>
       </c>
       <c r="P6">
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>0.5766398971767849</v>
+        <v>0.4792599117402066</v>
       </c>
       <c r="R6" t="b">
         <v>1</v>
@@ -809,10 +809,10 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
+        <v>46233</v>
+      </c>
+      <c r="C7" s="2">
         <v>46232</v>
-      </c>
-      <c r="C7" s="2">
-        <v>46231</v>
       </c>
       <c r="D7" t="s">
         <v>28</v>
@@ -824,13 +824,13 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>0.5577364673232961</v>
+        <v>0.4014999642724688</v>
       </c>
       <c r="H7">
-        <v>1.344816303428594</v>
+        <v>1.344306259314803</v>
       </c>
       <c r="I7">
-        <v>0.3085317604613949</v>
+        <v>0.3084739218998345</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -839,22 +839,22 @@
         <v>1</v>
       </c>
       <c r="L7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="M7">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N7">
-        <v>-0.01177261687474095</v>
+        <v>0</v>
       </c>
       <c r="O7">
-        <v>-2.17594080462569</v>
+        <v>0</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>0.5577364673232961</v>
+        <v>0.4014999642724688</v>
       </c>
       <c r="R7" t="b">
         <v>1</v>
@@ -865,10 +865,10 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
+        <v>46233</v>
+      </c>
+      <c r="C8" s="2">
         <v>46232</v>
-      </c>
-      <c r="C8" s="2">
-        <v>46231</v>
       </c>
       <c r="D8" t="s">
         <v>29</v>
@@ -880,13 +880,13 @@
         <v>1</v>
       </c>
       <c r="G8">
-        <v>2.744246931337766</v>
+        <v>2.371049492894731</v>
       </c>
       <c r="H8">
-        <v>1.396225104534495</v>
+        <v>1.400437488005619</v>
       </c>
       <c r="I8">
-        <v>0.3471530561807825</v>
+        <v>0.3486407456000498</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -898,19 +898,19 @@
         <v>111</v>
       </c>
       <c r="M8">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N8">
-        <v>-0.2373291494140377</v>
+        <v>-0.2446124891996817</v>
       </c>
       <c r="O8">
-        <v>-64.85668732767003</v>
+        <v>-62.73264057145184</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>2.744246931337766</v>
+        <v>2.371049492894731</v>
       </c>
       <c r="R8" t="b">
         <v>1</v>
@@ -921,10 +921,10 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
+        <v>46233</v>
+      </c>
+      <c r="C9" s="2">
         <v>46232</v>
-      </c>
-      <c r="C9" s="2">
-        <v>46231</v>
       </c>
       <c r="D9" t="s">
         <v>28</v>
@@ -936,13 +936,13 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>1.509101234576306</v>
+        <v>1.699149591905781</v>
       </c>
       <c r="H9">
-        <v>2.937328723596025</v>
+        <v>2.937329383802961</v>
       </c>
       <c r="I9">
-        <v>0.620111281348725</v>
+        <v>0.6188951479283225</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -954,19 +954,19 @@
         <v>76</v>
       </c>
       <c r="M9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N9">
-        <v>0.07851609933033701</v>
+        <v>0.08837305433003372</v>
       </c>
       <c r="O9">
-        <v>8.915770870506343</v>
+        <v>10.16575128894035</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>1.509101234576306</v>
+        <v>1.699149591905781</v>
       </c>
       <c r="R9" t="b">
         <v>1</v>
@@ -977,10 +977,10 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
+        <v>46233</v>
+      </c>
+      <c r="C10" s="2">
         <v>46232</v>
-      </c>
-      <c r="C10" s="2">
-        <v>46231</v>
       </c>
       <c r="D10" t="s">
         <v>29</v>
@@ -992,13 +992,13 @@
         <v>1</v>
       </c>
       <c r="G10">
-        <v>3.990078193416717</v>
+        <v>3.623420612403818</v>
       </c>
       <c r="H10">
-        <v>2.001049395254607</v>
+        <v>2.006175581642303</v>
       </c>
       <c r="I10">
-        <v>0.4461126090969442</v>
+        <v>0.4496817310084089</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1010,19 +1010,19 @@
         <v>232</v>
       </c>
       <c r="M10">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N10">
-        <v>-39.67825494107645</v>
+        <v>-40.86414464366484</v>
       </c>
       <c r="O10">
-        <v>-98.44848368189135</v>
+        <v>-96.70352011685443</v>
       </c>
       <c r="P10">
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>3.990078193416717</v>
+        <v>3.623420612403818</v>
       </c>
       <c r="R10" t="b">
         <v>1</v>
@@ -1033,10 +1033,10 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
+        <v>46233</v>
+      </c>
+      <c r="C11" s="2">
         <v>46232</v>
-      </c>
-      <c r="C11" s="2">
-        <v>46231</v>
       </c>
       <c r="D11" t="s">
         <v>28</v>
@@ -1048,13 +1048,13 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>1.777723893238875</v>
+        <v>1.653939172377564</v>
       </c>
       <c r="H11">
-        <v>3.105010144851548</v>
+        <v>3.105010100432843</v>
       </c>
       <c r="I11">
-        <v>0.6498029449345027</v>
+        <v>0.6487017553671852</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -1066,19 +1066,19 @@
         <v>211</v>
       </c>
       <c r="M11">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N11">
-        <v>9821.034735145624</v>
+        <v>9910.711963184638</v>
       </c>
       <c r="O11">
-        <v>140.4251593680497</v>
+        <v>143.0618516946619</v>
       </c>
       <c r="P11">
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>1.777723893238875</v>
+        <v>1.653939172377564</v>
       </c>
       <c r="R11" t="b">
         <v>1</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -529,10 +529,10 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>46233</v>
+        <v>46235</v>
       </c>
       <c r="C2" s="2">
-        <v>46232</v>
+        <v>46234</v>
       </c>
       <c r="D2" t="s">
         <v>28</v>
@@ -544,13 +544,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>0.6632591236562488</v>
+        <v>0.3886497203685205</v>
       </c>
       <c r="H2">
-        <v>1.043777649730073</v>
+        <v>1.049100723444362</v>
       </c>
       <c r="I2">
-        <v>0.2572268595973431</v>
+        <v>0.2572367998261316</v>
       </c>
       <c r="J2">
         <v>6</v>
@@ -562,19 +562,19 @@
         <v>148</v>
       </c>
       <c r="M2">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="N2">
-        <v>1.511806091415939</v>
+        <v>1.542919704176072</v>
       </c>
       <c r="O2">
-        <v>37.9932599982466</v>
+        <v>36.16964863023903</v>
       </c>
       <c r="P2">
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.6632591236562488</v>
+        <v>0.3886497203685205</v>
       </c>
       <c r="R2" t="b">
         <v>1</v>
@@ -585,10 +585,10 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
+        <v>46235</v>
+      </c>
+      <c r="C3" s="2">
         <v>46233</v>
-      </c>
-      <c r="C3" s="2">
-        <v>46232</v>
       </c>
       <c r="D3" t="s">
         <v>28</v>
@@ -600,37 +600,37 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>0.8276575547104769</v>
+        <v>0.005696016308642093</v>
       </c>
       <c r="H3">
-        <v>1.824470247442038</v>
+        <v>1.825853712498068</v>
       </c>
       <c r="I3">
-        <v>0.4290749374929325</v>
+        <v>0.428905301825991</v>
       </c>
       <c r="J3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L3">
         <v>224</v>
       </c>
       <c r="M3">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N3">
-        <v>0.1751143167646494</v>
+        <v>0.1750899205869593</v>
       </c>
       <c r="O3">
-        <v>63.29160796966847</v>
+        <v>58.05918730974518</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>0.7536071807439759</v>
       </c>
       <c r="Q3">
-        <v>0.8276575547104769</v>
+        <v>0.02311762301288263</v>
       </c>
       <c r="R3" t="b">
         <v>1</v>
@@ -641,10 +641,10 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>46233</v>
+        <v>46235</v>
       </c>
       <c r="C4" s="2">
-        <v>46232</v>
+        <v>46234</v>
       </c>
       <c r="D4" t="s">
         <v>28</v>
@@ -656,13 +656,13 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>1.541116014666038</v>
+        <v>0.6626148758334846</v>
       </c>
       <c r="H4">
-        <v>2.038170621828906</v>
+        <v>2.045979100000647</v>
       </c>
       <c r="I4">
-        <v>0.4926197824816437</v>
+        <v>0.4930079114110131</v>
       </c>
       <c r="J4">
         <v>6</v>
@@ -674,19 +674,19 @@
         <v>145</v>
       </c>
       <c r="M4">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N4">
-        <v>5.330066196621047</v>
+        <v>5.394375462203493</v>
       </c>
       <c r="O4">
-        <v>155.1370618559138</v>
+        <v>145.1215535565886</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>0.1684355450715061</v>
       </c>
       <c r="Q4">
-        <v>1.541116014666038</v>
+        <v>0.796829243850331</v>
       </c>
       <c r="R4" t="b">
         <v>1</v>
@@ -697,10 +697,10 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
+        <v>46235</v>
+      </c>
+      <c r="C5" s="2">
         <v>46233</v>
-      </c>
-      <c r="C5" s="2">
-        <v>46232</v>
       </c>
       <c r="D5" t="s">
         <v>28</v>
@@ -709,16 +709,16 @@
         <v>-1</v>
       </c>
       <c r="F5">
-        <v>0.7433162552396745</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>1.50386669438296</v>
+        <v>0.1854587861281391</v>
       </c>
       <c r="H5">
-        <v>1.361911639918745</v>
+        <v>1.367169507882226</v>
       </c>
       <c r="I5">
-        <v>0.2917089413619007</v>
+        <v>0.29212808542187</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -730,19 +730,19 @@
         <v>225</v>
       </c>
       <c r="M5">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N5">
-        <v>0.2768341621742173</v>
+        <v>0.2789633630470499</v>
       </c>
       <c r="O5">
-        <v>79.33834739895676</v>
+        <v>76.47321485527092</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>0.6415930688074064</v>
       </c>
       <c r="Q5">
-        <v>1.50386669438296</v>
+        <v>0.5174531237747769</v>
       </c>
       <c r="R5" t="b">
         <v>1</v>
@@ -753,10 +753,10 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>46233</v>
+        <v>46235</v>
       </c>
       <c r="C6" s="2">
-        <v>46232</v>
+        <v>46234</v>
       </c>
       <c r="D6" t="s">
         <v>28</v>
@@ -768,13 +768,13 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0.4792599117402066</v>
+        <v>0.05823076207883358</v>
       </c>
       <c r="H6">
-        <v>0.9413835037987245</v>
+        <v>0.9417536477150836</v>
       </c>
       <c r="I6">
-        <v>0.2564304644576186</v>
+        <v>0.2565632406151382</v>
       </c>
       <c r="J6">
         <v>6</v>
@@ -786,19 +786,19 @@
         <v>157</v>
       </c>
       <c r="M6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N6">
-        <v>0.04650660223688919</v>
+        <v>0.07775975060894297</v>
       </c>
       <c r="O6">
-        <v>0.6364975426631838</v>
+        <v>0.9936622688669062</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>0.5374629663181304</v>
       </c>
       <c r="Q6">
-        <v>0.4792599117402066</v>
+        <v>0.125894269730809</v>
       </c>
       <c r="R6" t="b">
         <v>1</v>
@@ -809,28 +809,28 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
+        <v>46235</v>
+      </c>
+      <c r="C7" s="2">
         <v>46233</v>
       </c>
-      <c r="C7" s="2">
-        <v>46232</v>
-      </c>
       <c r="D7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E7">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="F7">
         <v>0</v>
       </c>
       <c r="G7">
-        <v>0.4014999642724688</v>
+        <v>0.274677165007067</v>
       </c>
       <c r="H7">
-        <v>1.344306259314803</v>
+        <v>1.343844790830897</v>
       </c>
       <c r="I7">
-        <v>0.3084739218998345</v>
+        <v>0.3085516252230071</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -839,22 +839,22 @@
         <v>1</v>
       </c>
       <c r="L7">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>-0.01162490552545436</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>-1.919319268310168</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>0.0300713610696452</v>
       </c>
       <c r="Q7">
-        <v>0.4014999642724688</v>
+        <v>0.2831931690459035</v>
       </c>
       <c r="R7" t="b">
         <v>1</v>
@@ -865,10 +865,10 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
+        <v>46235</v>
+      </c>
+      <c r="C8" s="2">
         <v>46233</v>
-      </c>
-      <c r="C8" s="2">
-        <v>46232</v>
       </c>
       <c r="D8" t="s">
         <v>29</v>
@@ -877,16 +877,16 @@
         <v>1</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>0.3762123956723264</v>
       </c>
       <c r="G8">
-        <v>2.371049492894731</v>
+        <v>1.3177803820073</v>
       </c>
       <c r="H8">
-        <v>1.400437488005619</v>
+        <v>1.404248692098541</v>
       </c>
       <c r="I8">
-        <v>0.3486407456000498</v>
+        <v>0.3492607784150749</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -898,19 +898,19 @@
         <v>111</v>
       </c>
       <c r="M8">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N8">
-        <v>-0.2446124891996817</v>
+        <v>-0.2492597347890959</v>
       </c>
       <c r="O8">
-        <v>-62.73264057145184</v>
+        <v>-59.14136576641556</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>2.371049492894731</v>
+        <v>1.3177803820073</v>
       </c>
       <c r="R8" t="b">
         <v>1</v>
@@ -921,10 +921,10 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
+        <v>46235</v>
+      </c>
+      <c r="C9" s="2">
         <v>46233</v>
-      </c>
-      <c r="C9" s="2">
-        <v>46232</v>
       </c>
       <c r="D9" t="s">
         <v>28</v>
@@ -933,16 +933,16 @@
         <v>-1</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>0.02462895362935497</v>
       </c>
       <c r="G9">
-        <v>1.699149591905781</v>
+        <v>2.350152272313951</v>
       </c>
       <c r="H9">
-        <v>2.937329383802961</v>
+        <v>2.937329981133046</v>
       </c>
       <c r="I9">
-        <v>0.6188951479283225</v>
+        <v>0.6175993608593431</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -954,19 +954,19 @@
         <v>76</v>
       </c>
       <c r="M9">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N9">
-        <v>0.08837305433003372</v>
+        <v>0.1021793341753982</v>
       </c>
       <c r="O9">
-        <v>10.16575128894035</v>
+        <v>11.97080065653206</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>1.699149591905781</v>
+        <v>2.350152272313951</v>
       </c>
       <c r="R9" t="b">
         <v>1</v>
@@ -977,10 +977,10 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
+        <v>46235</v>
+      </c>
+      <c r="C10" s="2">
         <v>46233</v>
-      </c>
-      <c r="C10" s="2">
-        <v>46232</v>
       </c>
       <c r="D10" t="s">
         <v>29</v>
@@ -989,40 +989,40 @@
         <v>1</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10">
-        <v>3.623420612403818</v>
+        <v>0.1235639613455076</v>
       </c>
       <c r="H10">
-        <v>2.006175581642303</v>
+        <v>2.009689257363193</v>
       </c>
       <c r="I10">
-        <v>0.4496817310084089</v>
+        <v>0.451558451277253</v>
       </c>
       <c r="J10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K10">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="L10">
         <v>232</v>
       </c>
       <c r="M10">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N10">
-        <v>-40.86414464366484</v>
+        <v>-41.13730456316603</v>
       </c>
       <c r="O10">
-        <v>-96.70352011685443</v>
+        <v>-52.11258778304535</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>0.6858143012487734</v>
       </c>
       <c r="Q10">
-        <v>3.623420612403818</v>
+        <v>0.3932832138338226</v>
       </c>
       <c r="R10" t="b">
         <v>1</v>
@@ -1033,10 +1033,10 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
+        <v>46235</v>
+      </c>
+      <c r="C11" s="2">
         <v>46233</v>
-      </c>
-      <c r="C11" s="2">
-        <v>46232</v>
       </c>
       <c r="D11" t="s">
         <v>28</v>
@@ -1048,13 +1048,13 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>1.653939172377564</v>
+        <v>1.525260554991763</v>
       </c>
       <c r="H11">
-        <v>3.105010100432843</v>
+        <v>3.10501006024449</v>
       </c>
       <c r="I11">
-        <v>0.6487017553671852</v>
+        <v>0.6475599109902876</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -1066,19 +1066,19 @@
         <v>211</v>
       </c>
       <c r="M11">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N11">
-        <v>9910.711963184638</v>
+        <v>9986.970141119098</v>
       </c>
       <c r="O11">
-        <v>143.0618516946619</v>
+        <v>157.3583131415567</v>
       </c>
       <c r="P11">
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>1.653939172377564</v>
+        <v>1.525260554991763</v>
       </c>
       <c r="R11" t="b">
         <v>1</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -529,7 +529,7 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>46235</v>
+        <v>46237</v>
       </c>
       <c r="C2" s="2">
         <v>46234</v>
@@ -585,52 +585,52 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>46235</v>
+        <v>46237</v>
       </c>
       <c r="C3" s="2">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <v>0</v>
       </c>
       <c r="G3">
-        <v>0.005696016308642093</v>
+        <v>0.1551900343993899</v>
       </c>
       <c r="H3">
-        <v>1.825853712498068</v>
+        <v>1.827105418977333</v>
       </c>
       <c r="I3">
-        <v>0.428905301825991</v>
+        <v>0.4286624306233353</v>
       </c>
       <c r="J3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K3">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="L3">
         <v>224</v>
       </c>
       <c r="M3">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N3">
-        <v>0.1750899205869593</v>
+        <v>0.1749638347747864</v>
       </c>
       <c r="O3">
-        <v>58.05918730974518</v>
+        <v>58.80431369216218</v>
       </c>
       <c r="P3">
-        <v>0.7536071807439759</v>
+        <v>0.4285674976757397</v>
       </c>
       <c r="Q3">
-        <v>0.02311762301288263</v>
+        <v>0.2715806919770327</v>
       </c>
       <c r="R3" t="b">
         <v>1</v>
@@ -641,7 +641,7 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>46235</v>
+        <v>46237</v>
       </c>
       <c r="C4" s="2">
         <v>46234</v>
@@ -697,10 +697,10 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>46235</v>
+        <v>46237</v>
       </c>
       <c r="C5" s="2">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="D5" t="s">
         <v>28</v>
@@ -712,37 +712,37 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>0.1854587861281391</v>
+        <v>0.008413607076037008</v>
       </c>
       <c r="H5">
-        <v>1.367169507882226</v>
+        <v>1.373316499474095</v>
       </c>
       <c r="I5">
-        <v>0.29212808542187</v>
+        <v>0.2927416273267189</v>
       </c>
       <c r="J5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K5">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L5">
         <v>225</v>
       </c>
       <c r="M5">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N5">
-        <v>0.2789633630470499</v>
+        <v>0.2801893544031899</v>
       </c>
       <c r="O5">
-        <v>76.47321485527092</v>
+        <v>77.14161183175293</v>
       </c>
       <c r="P5">
-        <v>0.6415930688074064</v>
+        <v>0.6499486840047709</v>
       </c>
       <c r="Q5">
-        <v>0.5174531237747769</v>
+        <v>0.02403535336559534</v>
       </c>
       <c r="R5" t="b">
         <v>1</v>
@@ -753,7 +753,7 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>46235</v>
+        <v>46237</v>
       </c>
       <c r="C6" s="2">
         <v>46234</v>
@@ -809,10 +809,10 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>46235</v>
+        <v>46237</v>
       </c>
       <c r="C7" s="2">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="D7" t="s">
         <v>29</v>
@@ -824,13 +824,13 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>0.274677165007067</v>
+        <v>0.5977178050946401</v>
       </c>
       <c r="H7">
-        <v>1.343844790830897</v>
+        <v>1.343427271726411</v>
       </c>
       <c r="I7">
-        <v>0.3085516252230071</v>
+        <v>0.3084709945267852</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -839,22 +839,22 @@
         <v>1</v>
       </c>
       <c r="L7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="M7">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N7">
-        <v>-0.01162490552545436</v>
+        <v>0</v>
       </c>
       <c r="O7">
-        <v>-1.919319268310168</v>
+        <v>0</v>
       </c>
       <c r="P7">
-        <v>0.0300713610696452</v>
+        <v>0</v>
       </c>
       <c r="Q7">
-        <v>0.2831931690459035</v>
+        <v>0.5977178050946401</v>
       </c>
       <c r="R7" t="b">
         <v>1</v>
@@ -865,10 +865,10 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>46235</v>
+        <v>46237</v>
       </c>
       <c r="C8" s="2">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="D8" t="s">
         <v>29</v>
@@ -877,16 +877,16 @@
         <v>1</v>
       </c>
       <c r="F8">
-        <v>0.3762123956723264</v>
+        <v>0.08687051514847721</v>
       </c>
       <c r="G8">
-        <v>1.3177803820073</v>
+        <v>1.118438100924791</v>
       </c>
       <c r="H8">
-        <v>1.404248692098541</v>
+        <v>1.40769692437309</v>
       </c>
       <c r="I8">
-        <v>0.3492607784150749</v>
+        <v>0.3500825214064031</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -898,19 +898,19 @@
         <v>111</v>
       </c>
       <c r="M8">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N8">
-        <v>-0.2492597347890959</v>
+        <v>-0.2535452593986087</v>
       </c>
       <c r="O8">
-        <v>-59.14136576641556</v>
+        <v>-65.92930222103523</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>0.04215099018869607</v>
       </c>
       <c r="Q8">
-        <v>1.3177803820073</v>
+        <v>1.167655955655394</v>
       </c>
       <c r="R8" t="b">
         <v>1</v>
@@ -921,10 +921,10 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>46235</v>
+        <v>46237</v>
       </c>
       <c r="C9" s="2">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="D9" t="s">
         <v>28</v>
@@ -933,16 +933,16 @@
         <v>-1</v>
       </c>
       <c r="F9">
-        <v>0.02462895362935497</v>
+        <v>0.08643744362619533</v>
       </c>
       <c r="G9">
-        <v>2.350152272313951</v>
+        <v>2.427643560125567</v>
       </c>
       <c r="H9">
-        <v>2.937329981133046</v>
+        <v>2.937330521574551</v>
       </c>
       <c r="I9">
-        <v>0.6175993608593431</v>
+        <v>0.6162150726579501</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -954,19 +954,19 @@
         <v>76</v>
       </c>
       <c r="M9">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N9">
-        <v>0.1021793341753982</v>
+        <v>0.1165428761098963</v>
       </c>
       <c r="O9">
-        <v>11.97080065653206</v>
+        <v>13.41831708161147</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>2.350152272313951</v>
+        <v>2.427643560125567</v>
       </c>
       <c r="R9" t="b">
         <v>1</v>
@@ -977,52 +977,52 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>46235</v>
+        <v>46237</v>
       </c>
       <c r="C10" s="2">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="D10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="F10">
         <v>0</v>
       </c>
       <c r="G10">
-        <v>0.1235639613455076</v>
+        <v>0.4670013583701229</v>
       </c>
       <c r="H10">
-        <v>2.009689257363193</v>
+        <v>2.013402340959859</v>
       </c>
       <c r="I10">
-        <v>0.451558451277253</v>
+        <v>0.4539702165969726</v>
       </c>
       <c r="J10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K10">
-        <v>0.8333333333333334</v>
+        <v>1</v>
       </c>
       <c r="L10">
         <v>232</v>
       </c>
       <c r="M10">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N10">
-        <v>-41.13730456316603</v>
+        <v>-41.20023662165575</v>
       </c>
       <c r="O10">
-        <v>-52.11258778304535</v>
+        <v>-42.69138573778278</v>
       </c>
       <c r="P10">
-        <v>0.6858143012487734</v>
+        <v>0.2563819344122421</v>
       </c>
       <c r="Q10">
-        <v>0.3932832138338226</v>
+        <v>0.6280123896680799</v>
       </c>
       <c r="R10" t="b">
         <v>1</v>
@@ -1033,7 +1033,7 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>46235</v>
+        <v>46237</v>
       </c>
       <c r="C11" s="2">
         <v>46233</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -529,10 +529,10 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
+        <v>46238</v>
+      </c>
+      <c r="C2" s="2">
         <v>46237</v>
-      </c>
-      <c r="C2" s="2">
-        <v>46234</v>
       </c>
       <c r="D2" t="s">
         <v>28</v>
@@ -544,13 +544,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>0.3886497203685205</v>
+        <v>0.3849949008583666</v>
       </c>
       <c r="H2">
-        <v>1.049100723444362</v>
+        <v>1.051388377743002</v>
       </c>
       <c r="I2">
-        <v>0.2572367998261316</v>
+        <v>0.2571494257835192</v>
       </c>
       <c r="J2">
         <v>6</v>
@@ -562,19 +562,19 @@
         <v>148</v>
       </c>
       <c r="M2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N2">
-        <v>1.542919704176072</v>
+        <v>1.555219498054184</v>
       </c>
       <c r="O2">
-        <v>36.16964863023903</v>
+        <v>37.06370409866139</v>
       </c>
       <c r="P2">
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.3886497203685205</v>
+        <v>0.3849949008583666</v>
       </c>
       <c r="R2" t="b">
         <v>1</v>
@@ -585,52 +585,52 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
+        <v>46238</v>
+      </c>
+      <c r="C3" s="2">
         <v>46237</v>
       </c>
-      <c r="C3" s="2">
-        <v>46234</v>
-      </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="F3">
         <v>0</v>
       </c>
       <c r="G3">
-        <v>0.1551900343993899</v>
+        <v>0.0007555498663784668</v>
       </c>
       <c r="H3">
-        <v>1.827105418977333</v>
+        <v>1.828237915315716</v>
       </c>
       <c r="I3">
-        <v>0.4286624306233353</v>
+        <v>0.4279376234989964</v>
       </c>
       <c r="J3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L3">
         <v>224</v>
       </c>
       <c r="M3">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N3">
-        <v>0.1749638347747864</v>
+        <v>0.1768610306923462</v>
       </c>
       <c r="O3">
-        <v>58.80431369216218</v>
+        <v>60.20069121548393</v>
       </c>
       <c r="P3">
-        <v>0.4285674976757397</v>
+        <v>0.8902286813534409</v>
       </c>
       <c r="Q3">
-        <v>0.2715806919770327</v>
+        <v>0.006882944248954327</v>
       </c>
       <c r="R3" t="b">
         <v>1</v>
@@ -641,10 +641,10 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
+        <v>46238</v>
+      </c>
+      <c r="C4" s="2">
         <v>46237</v>
-      </c>
-      <c r="C4" s="2">
-        <v>46234</v>
       </c>
       <c r="D4" t="s">
         <v>28</v>
@@ -656,13 +656,13 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>0.6626148758334846</v>
+        <v>0.5106728317218918</v>
       </c>
       <c r="H4">
-        <v>2.045979100000647</v>
+        <v>2.049334886453026</v>
       </c>
       <c r="I4">
-        <v>0.4930079114110131</v>
+        <v>0.4931808178753695</v>
       </c>
       <c r="J4">
         <v>6</v>
@@ -674,19 +674,19 @@
         <v>145</v>
       </c>
       <c r="M4">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N4">
-        <v>5.394375462203493</v>
+        <v>5.416357573967983</v>
       </c>
       <c r="O4">
-        <v>145.1215535565886</v>
+        <v>150.4842350378084</v>
       </c>
       <c r="P4">
-        <v>0.1684355450715061</v>
+        <v>0.2337197984477865</v>
       </c>
       <c r="Q4">
-        <v>0.796829243850331</v>
+        <v>0.6664309356909506</v>
       </c>
       <c r="R4" t="b">
         <v>1</v>
@@ -697,10 +697,10 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
+        <v>46238</v>
+      </c>
+      <c r="C5" s="2">
         <v>46237</v>
-      </c>
-      <c r="C5" s="2">
-        <v>46234</v>
       </c>
       <c r="D5" t="s">
         <v>28</v>
@@ -712,13 +712,13 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>0.008413607076037008</v>
+        <v>9.410748419536978E-05</v>
       </c>
       <c r="H5">
-        <v>1.373316499474095</v>
+        <v>1.384199357542884</v>
       </c>
       <c r="I5">
-        <v>0.2927416273267189</v>
+        <v>0.2935865410566876</v>
       </c>
       <c r="J5">
         <v>4</v>
@@ -730,19 +730,19 @@
         <v>225</v>
       </c>
       <c r="M5">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N5">
-        <v>0.2801893544031899</v>
+        <v>0.282626555514865</v>
       </c>
       <c r="O5">
-        <v>77.14161183175293</v>
+        <v>78.00437214801543</v>
       </c>
       <c r="P5">
-        <v>0.6499486840047709</v>
+        <v>0.7317663673563798</v>
       </c>
       <c r="Q5">
-        <v>0.02403535336559534</v>
+        <v>0.0003508414782586291</v>
       </c>
       <c r="R5" t="b">
         <v>1</v>
@@ -753,10 +753,10 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
+        <v>46238</v>
+      </c>
+      <c r="C6" s="2">
         <v>46237</v>
-      </c>
-      <c r="C6" s="2">
-        <v>46234</v>
       </c>
       <c r="D6" t="s">
         <v>28</v>
@@ -768,13 +768,13 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0.05823076207883358</v>
+        <v>0.04823018825873739</v>
       </c>
       <c r="H6">
-        <v>0.9417536477150836</v>
+        <v>0.9419127214696141</v>
       </c>
       <c r="I6">
-        <v>0.2565632406151382</v>
+        <v>0.2566528152532248</v>
       </c>
       <c r="J6">
         <v>6</v>
@@ -786,19 +786,19 @@
         <v>157</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N6">
-        <v>0.07775975060894297</v>
+        <v>0.084727353419221</v>
       </c>
       <c r="O6">
-        <v>0.9936622688669062</v>
+        <v>1.098510800853016</v>
       </c>
       <c r="P6">
-        <v>0.5374629663181304</v>
+        <v>0.5165710992184568</v>
       </c>
       <c r="Q6">
-        <v>0.125894269730809</v>
+        <v>0.09976686991771751</v>
       </c>
       <c r="R6" t="b">
         <v>1</v>
@@ -809,10 +809,10 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
+        <v>46238</v>
+      </c>
+      <c r="C7" s="2">
         <v>46237</v>
-      </c>
-      <c r="C7" s="2">
-        <v>46234</v>
       </c>
       <c r="D7" t="s">
         <v>29</v>
@@ -824,13 +824,13 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>0.5977178050946401</v>
+        <v>0.4474181392974408</v>
       </c>
       <c r="H7">
-        <v>1.343427271726411</v>
+        <v>1.343049516346162</v>
       </c>
       <c r="I7">
-        <v>0.3084709945267852</v>
+        <v>0.308242076639734</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -839,22 +839,22 @@
         <v>1</v>
       </c>
       <c r="L7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>-0.001799593068084332</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>-0.2948943987028798</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>0.5977178050946401</v>
+        <v>0.4474181392974408</v>
       </c>
       <c r="R7" t="b">
         <v>1</v>
@@ -865,10 +865,10 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
+        <v>46238</v>
+      </c>
+      <c r="C8" s="2">
         <v>46237</v>
-      </c>
-      <c r="C8" s="2">
-        <v>46234</v>
       </c>
       <c r="D8" t="s">
         <v>29</v>
@@ -877,16 +877,16 @@
         <v>1</v>
       </c>
       <c r="F8">
-        <v>0.08687051514847721</v>
+        <v>0.3801480452828046</v>
       </c>
       <c r="G8">
-        <v>1.118438100924791</v>
+        <v>1.329377158473881</v>
       </c>
       <c r="H8">
-        <v>1.40769692437309</v>
+        <v>1.413832269437584</v>
       </c>
       <c r="I8">
-        <v>0.3500825214064031</v>
+        <v>0.3523309701664192</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -898,19 +898,19 @@
         <v>111</v>
       </c>
       <c r="M8">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N8">
-        <v>-0.2535452593986087</v>
+        <v>-0.2603174721404634</v>
       </c>
       <c r="O8">
-        <v>-65.92930222103523</v>
+        <v>-69.81025974459357</v>
       </c>
       <c r="P8">
-        <v>0.04215099018869607</v>
+        <v>0</v>
       </c>
       <c r="Q8">
-        <v>1.167655955655394</v>
+        <v>1.329377158473881</v>
       </c>
       <c r="R8" t="b">
         <v>1</v>
@@ -921,10 +921,10 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
+        <v>46238</v>
+      </c>
+      <c r="C9" s="2">
         <v>46237</v>
-      </c>
-      <c r="C9" s="2">
-        <v>46234</v>
       </c>
       <c r="D9" t="s">
         <v>28</v>
@@ -933,16 +933,16 @@
         <v>-1</v>
       </c>
       <c r="F9">
-        <v>0.08643744362619533</v>
+        <v>0.06116447076549618</v>
       </c>
       <c r="G9">
-        <v>2.427643560125567</v>
+        <v>2.397867003755076</v>
       </c>
       <c r="H9">
-        <v>2.937330521574551</v>
+        <v>2.937331010545436</v>
       </c>
       <c r="I9">
-        <v>0.6162150726579501</v>
+        <v>0.6146539772331006</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -954,19 +954,19 @@
         <v>76</v>
       </c>
       <c r="M9">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N9">
-        <v>0.1165428761098963</v>
+        <v>0.1271134518795942</v>
       </c>
       <c r="O9">
-        <v>13.41831708161147</v>
+        <v>15.74996306145959</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>2.427643560125567</v>
+        <v>2.397867003755076</v>
       </c>
       <c r="R9" t="b">
         <v>1</v>
@@ -977,10 +977,10 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
+        <v>46238</v>
+      </c>
+      <c r="C10" s="2">
         <v>46237</v>
-      </c>
-      <c r="C10" s="2">
-        <v>46234</v>
       </c>
       <c r="D10" t="s">
         <v>28</v>
@@ -992,13 +992,13 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>0.4670013583701229</v>
+        <v>0.9663643811290482</v>
       </c>
       <c r="H10">
-        <v>2.013402340959859</v>
+        <v>2.018806447335082</v>
       </c>
       <c r="I10">
-        <v>0.4539702165969726</v>
+        <v>0.4584099270070349</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1010,19 +1010,19 @@
         <v>232</v>
       </c>
       <c r="M10">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N10">
-        <v>-41.20023662165575</v>
+        <v>-41.94346585807426</v>
       </c>
       <c r="O10">
-        <v>-42.69138573778278</v>
+        <v>-50.66073005030128</v>
       </c>
       <c r="P10">
-        <v>0.2563819344122421</v>
+        <v>0.1512192767587479</v>
       </c>
       <c r="Q10">
-        <v>0.6280123896680799</v>
+        <v>1.138532432073596</v>
       </c>
       <c r="R10" t="b">
         <v>1</v>
@@ -1033,10 +1033,10 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
+        <v>46238</v>
+      </c>
+      <c r="C11" s="2">
         <v>46237</v>
-      </c>
-      <c r="C11" s="2">
-        <v>46233</v>
       </c>
       <c r="D11" t="s">
         <v>28</v>
@@ -1048,13 +1048,13 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>1.525260554991763</v>
+        <v>1.594074680822617</v>
       </c>
       <c r="H11">
-        <v>3.10501006024449</v>
+        <v>3.1050100238836</v>
       </c>
       <c r="I11">
-        <v>0.6475599109902876</v>
+        <v>0.6463400098500922</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -1066,19 +1066,19 @@
         <v>211</v>
       </c>
       <c r="M11">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N11">
-        <v>9986.970141119098</v>
+        <v>10067.87585546737</v>
       </c>
       <c r="O11">
-        <v>157.3583131415567</v>
+        <v>162.865434896172</v>
       </c>
       <c r="P11">
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>1.525260554991763</v>
+        <v>1.594074680822617</v>
       </c>
       <c r="R11" t="b">
         <v>1</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -591,46 +591,46 @@
         <v>46237</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <v>0</v>
       </c>
       <c r="G3">
-        <v>0.0007555498663784668</v>
+        <v>0.04072730525686864</v>
       </c>
       <c r="H3">
         <v>1.828237915315716</v>
       </c>
       <c r="I3">
-        <v>0.4279376234989964</v>
+        <v>0.4284684019210114</v>
       </c>
       <c r="J3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K3">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M3">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="N3">
-        <v>0.1768610306923462</v>
+        <v>0</v>
       </c>
       <c r="O3">
-        <v>60.20069121548393</v>
+        <v>0</v>
       </c>
       <c r="P3">
-        <v>0.8902286813534409</v>
+        <v>0.6996364564128312</v>
       </c>
       <c r="Q3">
-        <v>0.006882944248954327</v>
+        <v>0.1355933705218428</v>
       </c>
       <c r="R3" t="b">
         <v>1</v>
@@ -712,13 +712,13 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>9.410748419536978E-05</v>
+        <v>0.02721310628042968</v>
       </c>
       <c r="H5">
-        <v>1.384199357542884</v>
+        <v>1.37887806329531</v>
       </c>
       <c r="I5">
-        <v>0.2935865410566876</v>
+        <v>0.2934218902186995</v>
       </c>
       <c r="J5">
         <v>4</v>
@@ -733,16 +733,16 @@
         <v>53</v>
       </c>
       <c r="N5">
-        <v>0.282626555514865</v>
+        <v>0.2804699665537065</v>
       </c>
       <c r="O5">
-        <v>78.00437214801543</v>
+        <v>77.7078870324931</v>
       </c>
       <c r="P5">
-        <v>0.7317663673563798</v>
+        <v>0.7225048458555835</v>
       </c>
       <c r="Q5">
-        <v>0.0003508414782586291</v>
+        <v>0.09806696035588135</v>
       </c>
       <c r="R5" t="b">
         <v>1</v>
@@ -824,13 +824,13 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>0.4474181392974408</v>
+        <v>0.5398017231284329</v>
       </c>
       <c r="H7">
         <v>1.343049516346162</v>
       </c>
       <c r="I7">
-        <v>0.308242076639734</v>
+        <v>0.3083577408386218</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -839,22 +839,22 @@
         <v>1</v>
       </c>
       <c r="L7">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="M7">
         <v>1</v>
       </c>
       <c r="N7">
-        <v>-0.001799593068084332</v>
+        <v>-0.002416521806188178</v>
       </c>
       <c r="O7">
-        <v>-0.2948943987028798</v>
+        <v>-0.397407556521019</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>0.4474181392974408</v>
+        <v>0.5398017231284329</v>
       </c>
       <c r="R7" t="b">
         <v>1</v>
@@ -877,16 +877,16 @@
         <v>1</v>
       </c>
       <c r="F8">
-        <v>0.3801480452828046</v>
+        <v>0.1845477155945729</v>
       </c>
       <c r="G8">
-        <v>1.329377158473881</v>
+        <v>1.189516755040264</v>
       </c>
       <c r="H8">
-        <v>1.413832269437584</v>
+        <v>1.410816753573872</v>
       </c>
       <c r="I8">
-        <v>0.3523309701664192</v>
+        <v>0.3507662005851695</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -901,16 +901,16 @@
         <v>43</v>
       </c>
       <c r="N8">
-        <v>-0.2603174721404634</v>
+        <v>-0.2573128376258687</v>
       </c>
       <c r="O8">
-        <v>-69.81025974459357</v>
+        <v>-68.53842706929554</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>1.329377158473881</v>
+        <v>1.189516755040264</v>
       </c>
       <c r="R8" t="b">
         <v>1</v>
@@ -933,16 +933,16 @@
         <v>-1</v>
       </c>
       <c r="F9">
-        <v>0.06116447076549618</v>
+        <v>0.08246748434534681</v>
       </c>
       <c r="G9">
-        <v>2.397867003755076</v>
+        <v>2.42396697331862</v>
       </c>
       <c r="H9">
         <v>2.937331010545436</v>
       </c>
       <c r="I9">
-        <v>0.6146539772331006</v>
+        <v>0.6147593516422406</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -957,16 +957,16 @@
         <v>13</v>
       </c>
       <c r="N9">
-        <v>0.1271134518795942</v>
+        <v>0.1312336158497857</v>
       </c>
       <c r="O9">
-        <v>15.74996306145959</v>
+        <v>15.88441293301345</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>2.397867003755076</v>
+        <v>2.42396697331862</v>
       </c>
       <c r="R9" t="b">
         <v>1</v>
@@ -992,13 +992,13 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>0.9663643811290482</v>
+        <v>1.064118146134086</v>
       </c>
       <c r="H10">
-        <v>2.018806447335082</v>
+        <v>2.016761797547318</v>
       </c>
       <c r="I10">
-        <v>0.4584099270070349</v>
+        <v>0.4560839521209142</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1007,22 +1007,22 @@
         <v>1</v>
       </c>
       <c r="L10">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M10">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="N10">
-        <v>-41.94346585807426</v>
+        <v>0</v>
       </c>
       <c r="O10">
-        <v>-50.66073005030128</v>
+        <v>0</v>
       </c>
       <c r="P10">
-        <v>0.1512192767587479</v>
+        <v>0.08071498425507712</v>
       </c>
       <c r="Q10">
-        <v>1.138532432073596</v>
+        <v>1.157549756504843</v>
       </c>
       <c r="R10" t="b">
         <v>1</v>
@@ -1048,13 +1048,13 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>1.594074680822617</v>
+        <v>1.569404174446048</v>
       </c>
       <c r="H11">
         <v>3.1050100238836</v>
       </c>
       <c r="I11">
-        <v>0.6463400098500922</v>
+        <v>0.6463497330111228</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -1069,16 +1069,16 @@
         <v>106</v>
       </c>
       <c r="N11">
-        <v>10067.87585546737</v>
+        <v>10060.00142208631</v>
       </c>
       <c r="O11">
-        <v>162.865434896172</v>
+        <v>164.4366840737984</v>
       </c>
       <c r="P11">
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>1.594074680822617</v>
+        <v>1.569404174446048</v>
       </c>
       <c r="R11" t="b">
         <v>1</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -529,10 +529,10 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
+        <v>46239</v>
+      </c>
+      <c r="C2" s="2">
         <v>46238</v>
-      </c>
-      <c r="C2" s="2">
-        <v>46237</v>
       </c>
       <c r="D2" t="s">
         <v>28</v>
@@ -544,13 +544,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>0.3849949008583666</v>
+        <v>0.1900347107390751</v>
       </c>
       <c r="H2">
-        <v>1.051388377743002</v>
+        <v>1.053458160203677</v>
       </c>
       <c r="I2">
-        <v>0.2571494257835192</v>
+        <v>0.2570220137196926</v>
       </c>
       <c r="J2">
         <v>6</v>
@@ -562,19 +562,19 @@
         <v>148</v>
       </c>
       <c r="M2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N2">
-        <v>1.555219498054184</v>
+        <v>1.565351288552612</v>
       </c>
       <c r="O2">
-        <v>37.06370409866139</v>
+        <v>37.25696271694905</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>0.2551049513879201</v>
       </c>
       <c r="Q2">
-        <v>0.3849949008583666</v>
+        <v>0.25511608795515</v>
       </c>
       <c r="R2" t="b">
         <v>1</v>
@@ -585,52 +585,52 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C3" s="2">
         <v>46237</v>
       </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="F3">
         <v>0</v>
       </c>
       <c r="G3">
-        <v>0.04072730525686864</v>
+        <v>0.0007555498663784668</v>
       </c>
       <c r="H3">
         <v>1.828237915315716</v>
       </c>
       <c r="I3">
-        <v>0.4284684019210114</v>
+        <v>0.4279376234989964</v>
       </c>
       <c r="J3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L3">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="M3">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>0.1768610306923462</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>60.20069121548393</v>
       </c>
       <c r="P3">
-        <v>0.6996364564128312</v>
+        <v>0.8902286813534409</v>
       </c>
       <c r="Q3">
-        <v>0.1355933705218428</v>
+        <v>0.006882944248954327</v>
       </c>
       <c r="R3" t="b">
         <v>1</v>
@@ -641,10 +641,10 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
+        <v>46239</v>
+      </c>
+      <c r="C4" s="2">
         <v>46238</v>
-      </c>
-      <c r="C4" s="2">
-        <v>46237</v>
       </c>
       <c r="D4" t="s">
         <v>28</v>
@@ -656,13 +656,13 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>0.5106728317218918</v>
+        <v>0.3959586949593628</v>
       </c>
       <c r="H4">
-        <v>2.049334886453026</v>
+        <v>2.052371074195655</v>
       </c>
       <c r="I4">
-        <v>0.4931808178753695</v>
+        <v>0.493383921881289</v>
       </c>
       <c r="J4">
         <v>6</v>
@@ -674,19 +674,19 @@
         <v>145</v>
       </c>
       <c r="M4">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N4">
-        <v>5.416357573967983</v>
+        <v>5.433774965754309</v>
       </c>
       <c r="O4">
-        <v>150.4842350378084</v>
+        <v>158.9819216730619</v>
       </c>
       <c r="P4">
-        <v>0.2337197984477865</v>
+        <v>0.2948003443010004</v>
       </c>
       <c r="Q4">
-        <v>0.6664309356909506</v>
+        <v>0.5614845267711955</v>
       </c>
       <c r="R4" t="b">
         <v>1</v>
@@ -697,7 +697,7 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C5" s="2">
         <v>46237</v>
@@ -712,13 +712,13 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>0.02721310628042968</v>
+        <v>9.410748419536978E-05</v>
       </c>
       <c r="H5">
-        <v>1.37887806329531</v>
+        <v>1.384199357542884</v>
       </c>
       <c r="I5">
-        <v>0.2934218902186995</v>
+        <v>0.2935865410566876</v>
       </c>
       <c r="J5">
         <v>4</v>
@@ -733,16 +733,16 @@
         <v>53</v>
       </c>
       <c r="N5">
-        <v>0.2804699665537065</v>
+        <v>0.282626555514865</v>
       </c>
       <c r="O5">
-        <v>77.7078870324931</v>
+        <v>78.00437214801543</v>
       </c>
       <c r="P5">
-        <v>0.7225048458555835</v>
+        <v>0.7317663673563798</v>
       </c>
       <c r="Q5">
-        <v>0.09806696035588135</v>
+        <v>0.0003508414782586291</v>
       </c>
       <c r="R5" t="b">
         <v>1</v>
@@ -753,10 +753,10 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
+        <v>46239</v>
+      </c>
+      <c r="C6" s="2">
         <v>46238</v>
-      </c>
-      <c r="C6" s="2">
-        <v>46237</v>
       </c>
       <c r="D6" t="s">
         <v>28</v>
@@ -768,13 +768,13 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0.04823018825873739</v>
+        <v>0.04421110681978428</v>
       </c>
       <c r="H6">
-        <v>0.9419127214696141</v>
+        <v>0.9420566453427608</v>
       </c>
       <c r="I6">
-        <v>0.2566528152532248</v>
+        <v>0.2567819073657074</v>
       </c>
       <c r="J6">
         <v>6</v>
@@ -786,19 +786,19 @@
         <v>157</v>
       </c>
       <c r="M6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N6">
-        <v>0.084727353419221</v>
+        <v>0.08976560514814581</v>
       </c>
       <c r="O6">
-        <v>1.098510800853016</v>
+        <v>1.280928011491228</v>
       </c>
       <c r="P6">
-        <v>0.5165710992184568</v>
+        <v>0.4921621494594797</v>
       </c>
       <c r="Q6">
-        <v>0.09976686991771751</v>
+        <v>0.0870575258869104</v>
       </c>
       <c r="R6" t="b">
         <v>1</v>
@@ -809,7 +809,7 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C7" s="2">
         <v>46237</v>
@@ -824,13 +824,13 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>0.5398017231284329</v>
+        <v>0.4474181392974408</v>
       </c>
       <c r="H7">
         <v>1.343049516346162</v>
       </c>
       <c r="I7">
-        <v>0.3083577408386218</v>
+        <v>0.308242076639734</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -839,22 +839,22 @@
         <v>1</v>
       </c>
       <c r="L7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M7">
         <v>1</v>
       </c>
       <c r="N7">
-        <v>-0.002416521806188178</v>
+        <v>-0.001799593068084332</v>
       </c>
       <c r="O7">
-        <v>-0.397407556521019</v>
+        <v>-0.2948943987028798</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>0.5398017231284329</v>
+        <v>0.4474181392974408</v>
       </c>
       <c r="R7" t="b">
         <v>1</v>
@@ -865,7 +865,7 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C8" s="2">
         <v>46237</v>
@@ -877,16 +877,16 @@
         <v>1</v>
       </c>
       <c r="F8">
-        <v>0.1845477155945729</v>
+        <v>0.3801480452828046</v>
       </c>
       <c r="G8">
-        <v>1.189516755040264</v>
+        <v>1.329377158473881</v>
       </c>
       <c r="H8">
-        <v>1.410816753573872</v>
+        <v>1.413832269437584</v>
       </c>
       <c r="I8">
-        <v>0.3507662005851695</v>
+        <v>0.3523309701664192</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -901,16 +901,16 @@
         <v>43</v>
       </c>
       <c r="N8">
-        <v>-0.2573128376258687</v>
+        <v>-0.2603174721404634</v>
       </c>
       <c r="O8">
-        <v>-68.53842706929554</v>
+        <v>-69.81025974459357</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>1.189516755040264</v>
+        <v>1.329377158473881</v>
       </c>
       <c r="R8" t="b">
         <v>1</v>
@@ -921,7 +921,7 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C9" s="2">
         <v>46237</v>
@@ -933,16 +933,16 @@
         <v>-1</v>
       </c>
       <c r="F9">
-        <v>0.08246748434534681</v>
+        <v>0.06116447076549618</v>
       </c>
       <c r="G9">
-        <v>2.42396697331862</v>
+        <v>2.397867003755076</v>
       </c>
       <c r="H9">
         <v>2.937331010545436</v>
       </c>
       <c r="I9">
-        <v>0.6147593516422406</v>
+        <v>0.6146539772331006</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -957,16 +957,16 @@
         <v>13</v>
       </c>
       <c r="N9">
-        <v>0.1312336158497857</v>
+        <v>0.1271134518795942</v>
       </c>
       <c r="O9">
-        <v>15.88441293301345</v>
+        <v>15.74996306145959</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>2.42396697331862</v>
+        <v>2.397867003755076</v>
       </c>
       <c r="R9" t="b">
         <v>1</v>
@@ -977,7 +977,7 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C10" s="2">
         <v>46237</v>
@@ -992,13 +992,13 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>1.064118146134086</v>
+        <v>0.9663643811290482</v>
       </c>
       <c r="H10">
-        <v>2.016761797547318</v>
+        <v>2.018806447335082</v>
       </c>
       <c r="I10">
-        <v>0.4560839521209142</v>
+        <v>0.4584099270070349</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1007,22 +1007,22 @@
         <v>1</v>
       </c>
       <c r="L10">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>-41.94346585807426</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>-50.66073005030128</v>
       </c>
       <c r="P10">
-        <v>0.08071498425507712</v>
+        <v>0.1512192767587479</v>
       </c>
       <c r="Q10">
-        <v>1.157549756504843</v>
+        <v>1.138532432073596</v>
       </c>
       <c r="R10" t="b">
         <v>1</v>
@@ -1033,7 +1033,7 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C11" s="2">
         <v>46237</v>
@@ -1048,13 +1048,13 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>1.569404174446048</v>
+        <v>1.594074680822617</v>
       </c>
       <c r="H11">
         <v>3.1050100238836</v>
       </c>
       <c r="I11">
-        <v>0.6463497330111228</v>
+        <v>0.6463400098500922</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -1069,16 +1069,16 @@
         <v>106</v>
       </c>
       <c r="N11">
-        <v>10060.00142208631</v>
+        <v>10067.87585546737</v>
       </c>
       <c r="O11">
-        <v>164.4366840737984</v>
+        <v>162.865434896172</v>
       </c>
       <c r="P11">
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>1.569404174446048</v>
+        <v>1.594074680822617</v>
       </c>
       <c r="R11" t="b">
         <v>1</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -529,10 +529,10 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
+        <v>46240</v>
+      </c>
+      <c r="C2" s="2">
         <v>46239</v>
-      </c>
-      <c r="C2" s="2">
-        <v>46238</v>
       </c>
       <c r="D2" t="s">
         <v>28</v>
@@ -544,13 +544,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>0.1900347107390751</v>
+        <v>0.04430240762997241</v>
       </c>
       <c r="H2">
-        <v>1.053458160203677</v>
+        <v>1.05533082052524</v>
       </c>
       <c r="I2">
-        <v>0.2570220137196926</v>
+        <v>0.2569283871976611</v>
       </c>
       <c r="J2">
         <v>6</v>
@@ -562,19 +562,19 @@
         <v>148</v>
       </c>
       <c r="M2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N2">
-        <v>1.565351288552612</v>
+        <v>1.571700003447102</v>
       </c>
       <c r="O2">
-        <v>37.25696271694905</v>
+        <v>37.69516736891963</v>
       </c>
       <c r="P2">
-        <v>0.2551049513879201</v>
+        <v>0.6451671221088325</v>
       </c>
       <c r="Q2">
-        <v>0.25511608795515</v>
+        <v>0.1248542916689941</v>
       </c>
       <c r="R2" t="b">
         <v>1</v>
@@ -585,10 +585,10 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
+        <v>46240</v>
+      </c>
+      <c r="C3" s="2">
         <v>46239</v>
-      </c>
-      <c r="C3" s="2">
-        <v>46237</v>
       </c>
       <c r="D3" t="s">
         <v>29</v>
@@ -600,13 +600,13 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>0.04072730525686864</v>
+        <v>0.4836793528452488</v>
       </c>
       <c r="H3">
-        <v>1.828237915315716</v>
+        <v>1.830189609685718</v>
       </c>
       <c r="I3">
-        <v>0.4284684019210114</v>
+        <v>0.4272415892001022</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -627,10 +627,10 @@
         <v>0</v>
       </c>
       <c r="P3">
-        <v>0.6996364564128312</v>
+        <v>0.1439863488083907</v>
       </c>
       <c r="Q3">
-        <v>0.1355933705218428</v>
+        <v>0.5650369619362327</v>
       </c>
       <c r="R3" t="b">
         <v>1</v>
@@ -641,10 +641,10 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
+        <v>46240</v>
+      </c>
+      <c r="C4" s="2">
         <v>46239</v>
-      </c>
-      <c r="C4" s="2">
-        <v>46238</v>
       </c>
       <c r="D4" t="s">
         <v>28</v>
@@ -656,13 +656,13 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>0.3959586949593628</v>
+        <v>0.189864250044427</v>
       </c>
       <c r="H4">
-        <v>2.052371074195655</v>
+        <v>2.055118101200891</v>
       </c>
       <c r="I4">
-        <v>0.493383921881289</v>
+        <v>0.4936570938672279</v>
       </c>
       <c r="J4">
         <v>6</v>
@@ -674,19 +674,19 @@
         <v>145</v>
       </c>
       <c r="M4">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="N4">
-        <v>5.433774965754309</v>
+        <v>5.446400561097555</v>
       </c>
       <c r="O4">
-        <v>158.9819216730619</v>
+        <v>159.4512920438427</v>
       </c>
       <c r="P4">
-        <v>0.2948003443010004</v>
+        <v>0.4783104915685185</v>
       </c>
       <c r="Q4">
-        <v>0.5614845267711955</v>
+        <v>0.3639410932669038</v>
       </c>
       <c r="R4" t="b">
         <v>1</v>
@@ -697,52 +697,52 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
+        <v>46240</v>
+      </c>
+      <c r="C5" s="2">
         <v>46239</v>
       </c>
-      <c r="C5" s="2">
-        <v>46237</v>
-      </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E5">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>0.02721310628042968</v>
+        <v>0.4279558520887797</v>
       </c>
       <c r="H5">
-        <v>1.37887806329531</v>
+        <v>1.395744646157925</v>
       </c>
       <c r="I5">
-        <v>0.2934218902186995</v>
+        <v>0.2949885828145041</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K5">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M5">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="N5">
-        <v>0.2804699665537065</v>
+        <v>0</v>
       </c>
       <c r="O5">
-        <v>77.7078870324931</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>0.7225048458555835</v>
+        <v>0.3513754261025148</v>
       </c>
       <c r="Q5">
-        <v>0.09806696035588135</v>
+        <v>0.659789760226411</v>
       </c>
       <c r="R5" t="b">
         <v>1</v>
@@ -753,52 +753,52 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
+        <v>46240</v>
+      </c>
+      <c r="C6" s="2">
         <v>46239</v>
       </c>
-      <c r="C6" s="2">
-        <v>46238</v>
-      </c>
       <c r="D6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E6">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0.04421110681978428</v>
+        <v>0.007589455652057173</v>
       </c>
       <c r="H6">
-        <v>0.9420566453427608</v>
+        <v>0.9421868621803696</v>
       </c>
       <c r="I6">
-        <v>0.2567819073657074</v>
+        <v>0.2569545378304415</v>
       </c>
       <c r="J6">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="L6">
         <v>157</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N6">
-        <v>0.08976560514814581</v>
+        <v>0.09249585521649439</v>
       </c>
       <c r="O6">
-        <v>1.280928011491228</v>
+        <v>1.362164806217772</v>
       </c>
       <c r="P6">
-        <v>0.4921621494594797</v>
+        <v>0.764184645284071</v>
       </c>
       <c r="Q6">
-        <v>0.0870575258869104</v>
+        <v>0.03218389091414206</v>
       </c>
       <c r="R6" t="b">
         <v>1</v>
@@ -809,10 +809,10 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
+        <v>46240</v>
+      </c>
+      <c r="C7" s="2">
         <v>46239</v>
-      </c>
-      <c r="C7" s="2">
-        <v>46237</v>
       </c>
       <c r="D7" t="s">
         <v>29</v>
@@ -824,13 +824,13 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>0.5398017231284329</v>
+        <v>0.825697215621753</v>
       </c>
       <c r="H7">
-        <v>1.343049516346162</v>
+        <v>1.342398509341651</v>
       </c>
       <c r="I7">
-        <v>0.3083577408386218</v>
+        <v>0.3079932109919273</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -839,22 +839,22 @@
         <v>1</v>
       </c>
       <c r="L7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N7">
-        <v>-0.002416521806188178</v>
+        <v>-0.006944887393718476</v>
       </c>
       <c r="O7">
-        <v>-0.397407556521019</v>
+        <v>-1.361742626219311</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>0.5398017231284329</v>
+        <v>0.825697215621753</v>
       </c>
       <c r="R7" t="b">
         <v>1</v>
@@ -865,10 +865,10 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
+        <v>46240</v>
+      </c>
+      <c r="C8" s="2">
         <v>46239</v>
-      </c>
-      <c r="C8" s="2">
-        <v>46237</v>
       </c>
       <c r="D8" t="s">
         <v>29</v>
@@ -877,16 +877,16 @@
         <v>1</v>
       </c>
       <c r="F8">
-        <v>0.1845477155945729</v>
+        <v>0</v>
       </c>
       <c r="G8">
-        <v>1.189516755040264</v>
+        <v>0.8295875572996088</v>
       </c>
       <c r="H8">
-        <v>1.410816753573872</v>
+        <v>1.420770917000128</v>
       </c>
       <c r="I8">
-        <v>0.3507662005851695</v>
+        <v>0.3539611103942894</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -898,19 +898,19 @@
         <v>111</v>
       </c>
       <c r="M8">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="N8">
-        <v>-0.2573128376258687</v>
+        <v>-0.2672070318211222</v>
       </c>
       <c r="O8">
-        <v>-68.53842706929554</v>
+        <v>-76.6656101136539</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>0.1282166407634996</v>
       </c>
       <c r="Q8">
-        <v>1.189516755040264</v>
+        <v>0.9515982938997066</v>
       </c>
       <c r="R8" t="b">
         <v>1</v>
@@ -921,10 +921,10 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
+        <v>46240</v>
+      </c>
+      <c r="C9" s="2">
         <v>46239</v>
-      </c>
-      <c r="C9" s="2">
-        <v>46237</v>
       </c>
       <c r="D9" t="s">
         <v>28</v>
@@ -933,16 +933,16 @@
         <v>-1</v>
       </c>
       <c r="F9">
-        <v>0.08246748434534681</v>
+        <v>0.2872454174635685</v>
       </c>
       <c r="G9">
-        <v>2.42396697331862</v>
+        <v>2.677131246811971</v>
       </c>
       <c r="H9">
-        <v>2.937331010545436</v>
+        <v>2.937331853216351</v>
       </c>
       <c r="I9">
-        <v>0.6147593516422406</v>
+        <v>0.6115041173315837</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -954,19 +954,19 @@
         <v>76</v>
       </c>
       <c r="M9">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N9">
-        <v>0.1312336158497857</v>
+        <v>0.1568110605094183</v>
       </c>
       <c r="O9">
-        <v>15.88441293301345</v>
+        <v>19.48309236006245</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>2.42396697331862</v>
+        <v>2.677131246811971</v>
       </c>
       <c r="R9" t="b">
         <v>1</v>
@@ -977,10 +977,10 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
+        <v>46240</v>
+      </c>
+      <c r="C10" s="2">
         <v>46239</v>
-      </c>
-      <c r="C10" s="2">
-        <v>46237</v>
       </c>
       <c r="D10" t="s">
         <v>28</v>
@@ -989,16 +989,16 @@
         <v>-1</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>0.306561496195065</v>
       </c>
       <c r="G10">
-        <v>1.064118146134086</v>
+        <v>1.846346534990227</v>
       </c>
       <c r="H10">
-        <v>2.016761797547318</v>
+        <v>2.025349377945572</v>
       </c>
       <c r="I10">
-        <v>0.4560839521209142</v>
+        <v>0.4626866922416139</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1010,19 +1010,19 @@
         <v>233</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>0.9345878316595067</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>1.107097317191961</v>
       </c>
       <c r="P10">
-        <v>0.08071498425507712</v>
+        <v>0</v>
       </c>
       <c r="Q10">
-        <v>1.157549756504843</v>
+        <v>1.846346534990227</v>
       </c>
       <c r="R10" t="b">
         <v>1</v>
@@ -1033,10 +1033,10 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
+        <v>46240</v>
+      </c>
+      <c r="C11" s="2">
         <v>46239</v>
-      </c>
-      <c r="C11" s="2">
-        <v>46237</v>
       </c>
       <c r="D11" t="s">
         <v>28</v>
@@ -1048,13 +1048,13 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>1.569404174446048</v>
+        <v>0.1282376139516318</v>
       </c>
       <c r="H11">
-        <v>3.1050100238836</v>
+        <v>3.094338397582448</v>
       </c>
       <c r="I11">
-        <v>0.6463497330111228</v>
+        <v>0.6440298617328836</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -1066,19 +1066,19 @@
         <v>211</v>
       </c>
       <c r="M11">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="N11">
-        <v>10060.00142208631</v>
+        <v>10165.42951866877</v>
       </c>
       <c r="O11">
-        <v>164.4366840737984</v>
+        <v>157.1354583371377</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>0.6877361649552232</v>
       </c>
       <c r="Q11">
-        <v>1.569404174446048</v>
+        <v>0.4106707199482235</v>
       </c>
       <c r="R11" t="b">
         <v>1</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -600,13 +600,13 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>0.4836793528452488</v>
+        <v>0.5567459216752554</v>
       </c>
       <c r="H3">
         <v>1.830189609685718</v>
       </c>
       <c r="I3">
-        <v>0.4272415892001022</v>
+        <v>0.4278916309563264</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -618,19 +618,19 @@
         <v>225</v>
       </c>
       <c r="M3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>-0.001810339409526657</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0.579573558961199</v>
       </c>
       <c r="P3">
-        <v>0.1439863488083907</v>
+        <v>0.09075810827134893</v>
       </c>
       <c r="Q3">
-        <v>0.5650369619362327</v>
+        <v>0.6123188193812428</v>
       </c>
       <c r="R3" t="b">
         <v>1</v>
@@ -712,13 +712,13 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>0.4279558520887797</v>
+        <v>0.468749840353423</v>
       </c>
       <c r="H5">
-        <v>1.395744646157925</v>
+        <v>1.388462617726428</v>
       </c>
       <c r="I5">
-        <v>0.2949885828145041</v>
+        <v>0.2947556114573959</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -739,10 +739,10 @@
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0.3513754261025148</v>
+        <v>0.3269732926879658</v>
       </c>
       <c r="Q5">
-        <v>0.659789760226411</v>
+        <v>0.6964802960428395</v>
       </c>
       <c r="R5" t="b">
         <v>1</v>
@@ -824,13 +824,13 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>0.825697215621753</v>
+        <v>0.8655590227027731</v>
       </c>
       <c r="H7">
         <v>1.342398509341651</v>
       </c>
       <c r="I7">
-        <v>0.3079932109919273</v>
+        <v>0.3081077426632159</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -839,22 +839,22 @@
         <v>1</v>
       </c>
       <c r="L7">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="M7">
         <v>3</v>
       </c>
       <c r="N7">
-        <v>-0.006944887393718476</v>
+        <v>-0.008296114356020715</v>
       </c>
       <c r="O7">
-        <v>-1.361742626219311</v>
+        <v>-1.633667641666646</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>0.825697215621753</v>
+        <v>0.8655590227027731</v>
       </c>
       <c r="R7" t="b">
         <v>1</v>
@@ -880,13 +880,13 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>0.8295875572996088</v>
+        <v>0.8173047550643496</v>
       </c>
       <c r="H8">
-        <v>1.420770917000128</v>
+        <v>1.416193329974312</v>
       </c>
       <c r="I8">
-        <v>0.3539611103942894</v>
+        <v>0.3517068626732292</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -901,16 +901,16 @@
         <v>45</v>
       </c>
       <c r="N8">
-        <v>-0.2672070318211222</v>
+        <v>-0.2635487693960183</v>
       </c>
       <c r="O8">
-        <v>-76.6656101136539</v>
+        <v>-75.06984275776765</v>
       </c>
       <c r="P8">
-        <v>0.1282166407634996</v>
+        <v>0.0898213971184247</v>
       </c>
       <c r="Q8">
-        <v>0.9515982938997066</v>
+        <v>0.8979608534817319</v>
       </c>
       <c r="R8" t="b">
         <v>1</v>
@@ -933,16 +933,16 @@
         <v>-1</v>
       </c>
       <c r="F9">
-        <v>0.2872454174635685</v>
+        <v>0.2588874665877943</v>
       </c>
       <c r="G9">
-        <v>2.677131246811971</v>
+        <v>2.642373204981608</v>
       </c>
       <c r="H9">
         <v>2.937331853216351</v>
       </c>
       <c r="I9">
-        <v>0.6115041173315837</v>
+        <v>0.6116617914060934</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -957,16 +957,16 @@
         <v>15</v>
       </c>
       <c r="N9">
-        <v>0.1568110605094183</v>
+        <v>0.161827524563268</v>
       </c>
       <c r="O9">
-        <v>19.48309236006245</v>
+        <v>19.64011394292169</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>2.677131246811971</v>
+        <v>2.642373204981608</v>
       </c>
       <c r="R9" t="b">
         <v>1</v>
@@ -989,16 +989,16 @@
         <v>-1</v>
       </c>
       <c r="F10">
-        <v>0.306561496195065</v>
+        <v>0.06640297558107278</v>
       </c>
       <c r="G10">
-        <v>1.846346534990227</v>
+        <v>1.624084279917644</v>
       </c>
       <c r="H10">
-        <v>2.025349377945572</v>
+        <v>2.022551337244527</v>
       </c>
       <c r="I10">
-        <v>0.4626866922416139</v>
+        <v>0.4594900736010327</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1010,19 +1010,19 @@
         <v>233</v>
       </c>
       <c r="M10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N10">
-        <v>0.9345878316595067</v>
+        <v>1.842377710962194</v>
       </c>
       <c r="O10">
-        <v>1.107097317191961</v>
+        <v>1.842246121953494</v>
       </c>
       <c r="P10">
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>1.846346534990227</v>
+        <v>1.624084279917644</v>
       </c>
       <c r="R10" t="b">
         <v>1</v>
@@ -1048,13 +1048,13 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>0.1282376139516318</v>
+        <v>0.1235224784910224</v>
       </c>
       <c r="H11">
         <v>3.094338397582448</v>
       </c>
       <c r="I11">
-        <v>0.6440298617328836</v>
+        <v>0.6440527123143491</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -1069,16 +1069,16 @@
         <v>108</v>
       </c>
       <c r="N11">
-        <v>10165.42951866877</v>
+        <v>10154.5502798439</v>
       </c>
       <c r="O11">
-        <v>157.1354583371377</v>
+        <v>158.5321482217053</v>
       </c>
       <c r="P11">
-        <v>0.6877361649552232</v>
+        <v>0.6911318557155742</v>
       </c>
       <c r="Q11">
-        <v>0.4106707199482235</v>
+        <v>0.3999197741068268</v>
       </c>
       <c r="R11" t="b">
         <v>1</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -529,10 +529,10 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
+        <v>46241</v>
+      </c>
+      <c r="C2" s="2">
         <v>46240</v>
-      </c>
-      <c r="C2" s="2">
-        <v>46239</v>
       </c>
       <c r="D2" t="s">
         <v>28</v>
@@ -544,13 +544,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>0.04430240762997241</v>
+        <v>0.06525604818593596</v>
       </c>
       <c r="H2">
-        <v>1.05533082052524</v>
+        <v>1.057025132244749</v>
       </c>
       <c r="I2">
-        <v>0.2569283871976611</v>
+        <v>0.2568990958543287</v>
       </c>
       <c r="J2">
         <v>6</v>
@@ -562,19 +562,19 @@
         <v>148</v>
       </c>
       <c r="M2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N2">
-        <v>1.571700003447102</v>
+        <v>1.575756182464201</v>
       </c>
       <c r="O2">
-        <v>37.69516736891963</v>
+        <v>37.86315143913707</v>
       </c>
       <c r="P2">
-        <v>0.6451671221088325</v>
+        <v>0.4838068609820085</v>
       </c>
       <c r="Q2">
-        <v>0.1248542916689941</v>
+        <v>0.1264178913925114</v>
       </c>
       <c r="R2" t="b">
         <v>1</v>
@@ -585,10 +585,10 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
+        <v>46241</v>
+      </c>
+      <c r="C3" s="2">
         <v>46240</v>
-      </c>
-      <c r="C3" s="2">
-        <v>46239</v>
       </c>
       <c r="D3" t="s">
         <v>29</v>
@@ -600,13 +600,13 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>0.5567459216752554</v>
+        <v>0.4555109864156004</v>
       </c>
       <c r="H3">
-        <v>1.830189609685718</v>
+        <v>1.831028373575683</v>
       </c>
       <c r="I3">
-        <v>0.4278916309563264</v>
+        <v>0.4268068087727196</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -618,19 +618,19 @@
         <v>225</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N3">
-        <v>-0.001810339409526657</v>
+        <v>-0.00125767003577907</v>
       </c>
       <c r="O3">
-        <v>-0.579573558961199</v>
+        <v>-0.4000768121087703</v>
       </c>
       <c r="P3">
-        <v>0.09075810827134893</v>
+        <v>0.1234563236086493</v>
       </c>
       <c r="Q3">
-        <v>0.6123188193812428</v>
+        <v>0.5196671867976929</v>
       </c>
       <c r="R3" t="b">
         <v>1</v>
@@ -641,10 +641,10 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
+        <v>46241</v>
+      </c>
+      <c r="C4" s="2">
         <v>46240</v>
-      </c>
-      <c r="C4" s="2">
-        <v>46239</v>
       </c>
       <c r="D4" t="s">
         <v>28</v>
@@ -656,13 +656,13 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>0.189864250044427</v>
+        <v>0.1963517415702094</v>
       </c>
       <c r="H4">
-        <v>2.055118101200891</v>
+        <v>2.05760350658658</v>
       </c>
       <c r="I4">
-        <v>0.4936570938672279</v>
+        <v>0.4939899534632028</v>
       </c>
       <c r="J4">
         <v>6</v>
@@ -674,19 +674,19 @@
         <v>145</v>
       </c>
       <c r="M4">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N4">
-        <v>5.446400561097555</v>
+        <v>5.455447224360125</v>
       </c>
       <c r="O4">
-        <v>159.4512920438427</v>
+        <v>155.3942240916413</v>
       </c>
       <c r="P4">
-        <v>0.4783104915685185</v>
+        <v>0.3978568792301422</v>
       </c>
       <c r="Q4">
-        <v>0.3639410932669038</v>
+        <v>0.326088158773894</v>
       </c>
       <c r="R4" t="b">
         <v>1</v>
@@ -697,10 +697,10 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
+        <v>46241</v>
+      </c>
+      <c r="C5" s="2">
         <v>46240</v>
-      </c>
-      <c r="C5" s="2">
-        <v>46239</v>
       </c>
       <c r="D5" t="s">
         <v>29</v>
@@ -712,13 +712,13 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>0.468749840353423</v>
+        <v>0.405796303637743</v>
       </c>
       <c r="H5">
-        <v>1.388462617726428</v>
+        <v>1.400706371384151</v>
       </c>
       <c r="I5">
-        <v>0.2947556114573959</v>
+        <v>0.2956341188545691</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -730,19 +730,19 @@
         <v>226</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>-0.001632533288271641</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>-0.453436485186046</v>
       </c>
       <c r="P5">
-        <v>0.3269732926879658</v>
+        <v>0.347635201065859</v>
       </c>
       <c r="Q5">
-        <v>0.6964802960428395</v>
+        <v>0.6220389332789703</v>
       </c>
       <c r="R5" t="b">
         <v>1</v>
@@ -753,10 +753,10 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
+        <v>46241</v>
+      </c>
+      <c r="C6" s="2">
         <v>46240</v>
-      </c>
-      <c r="C6" s="2">
-        <v>46239</v>
       </c>
       <c r="D6" t="s">
         <v>29</v>
@@ -768,37 +768,37 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0.007589455652057173</v>
+        <v>0.006939916177066721</v>
       </c>
       <c r="H6">
-        <v>0.9421868621803696</v>
+        <v>0.9423046774143967</v>
       </c>
       <c r="I6">
-        <v>0.2569545378304415</v>
+        <v>0.2571662636217342</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K6">
-        <v>0.1666666666666667</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L6">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M6">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N6">
-        <v>0.09249585521649439</v>
+        <v>0</v>
       </c>
       <c r="O6">
-        <v>1.362164806217772</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>0.764184645284071</v>
+        <v>0.653318528670364</v>
       </c>
       <c r="Q6">
-        <v>0.03218389091414206</v>
+        <v>0.02001813408270679</v>
       </c>
       <c r="R6" t="b">
         <v>1</v>
@@ -809,10 +809,10 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
+        <v>46241</v>
+      </c>
+      <c r="C7" s="2">
         <v>46240</v>
-      </c>
-      <c r="C7" s="2">
-        <v>46239</v>
       </c>
       <c r="D7" t="s">
         <v>29</v>
@@ -824,13 +824,13 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>0.8655590227027731</v>
+        <v>0.8444055334790207</v>
       </c>
       <c r="H7">
-        <v>1.342398509341651</v>
+        <v>1.342118731331378</v>
       </c>
       <c r="I7">
-        <v>0.3081077426632159</v>
+        <v>0.3078565676223621</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -839,22 +839,22 @@
         <v>1</v>
       </c>
       <c r="L7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N7">
-        <v>-0.008296114356020715</v>
+        <v>-0.01012947706056056</v>
       </c>
       <c r="O7">
-        <v>-1.633667641666646</v>
+        <v>-2.022284190343642</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>0.8655590227027731</v>
+        <v>0.8444055334790207</v>
       </c>
       <c r="R7" t="b">
         <v>1</v>
@@ -865,10 +865,10 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
+        <v>46241</v>
+      </c>
+      <c r="C8" s="2">
         <v>46240</v>
-      </c>
-      <c r="C8" s="2">
-        <v>46239</v>
       </c>
       <c r="D8" t="s">
         <v>29</v>
@@ -880,13 +880,13 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>0.8173047550643496</v>
+        <v>1.029249455050077</v>
       </c>
       <c r="H8">
-        <v>1.416193329974312</v>
+        <v>1.423752883393079</v>
       </c>
       <c r="I8">
-        <v>0.3517068626732292</v>
+        <v>0.3545313132497817</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -898,19 +898,19 @@
         <v>111</v>
       </c>
       <c r="M8">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N8">
-        <v>-0.2635487693960183</v>
+        <v>-0.270140268819334</v>
       </c>
       <c r="O8">
-        <v>-75.06984275776765</v>
+        <v>-69.65583872309975</v>
       </c>
       <c r="P8">
-        <v>0.0898213971184247</v>
+        <v>0</v>
       </c>
       <c r="Q8">
-        <v>0.8979608534817319</v>
+        <v>1.029249455050077</v>
       </c>
       <c r="R8" t="b">
         <v>1</v>
@@ -921,10 +921,10 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
+        <v>46241</v>
+      </c>
+      <c r="C9" s="2">
         <v>46240</v>
-      </c>
-      <c r="C9" s="2">
-        <v>46239</v>
       </c>
       <c r="D9" t="s">
         <v>28</v>
@@ -933,16 +933,16 @@
         <v>-1</v>
       </c>
       <c r="F9">
-        <v>0.2588874665877943</v>
+        <v>0.3267611576069867</v>
       </c>
       <c r="G9">
-        <v>2.642373204981608</v>
+        <v>2.726011728951056</v>
       </c>
       <c r="H9">
-        <v>2.937331853216351</v>
+        <v>2.937332215364208</v>
       </c>
       <c r="I9">
-        <v>0.6116617914060934</v>
+        <v>0.6099108129969664</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -954,19 +954,19 @@
         <v>76</v>
       </c>
       <c r="M9">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N9">
-        <v>0.161827524563268</v>
+        <v>0.1726198619768326</v>
       </c>
       <c r="O9">
-        <v>19.64011394292169</v>
+        <v>21.63059357955373</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>2.642373204981608</v>
+        <v>2.726011728951056</v>
       </c>
       <c r="R9" t="b">
         <v>1</v>
@@ -977,10 +977,10 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
+        <v>46241</v>
+      </c>
+      <c r="C10" s="2">
         <v>46240</v>
-      </c>
-      <c r="C10" s="2">
-        <v>46239</v>
       </c>
       <c r="D10" t="s">
         <v>28</v>
@@ -989,16 +989,16 @@
         <v>-1</v>
       </c>
       <c r="F10">
-        <v>0.06640297558107278</v>
+        <v>0.1729772277224456</v>
       </c>
       <c r="G10">
-        <v>1.624084279917644</v>
+        <v>1.724392151632915</v>
       </c>
       <c r="H10">
-        <v>2.022551337244527</v>
+        <v>2.028161280267462</v>
       </c>
       <c r="I10">
-        <v>0.4594900736010327</v>
+        <v>0.4644464459140612</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1013,16 +1013,16 @@
         <v>2</v>
       </c>
       <c r="N10">
-        <v>1.842377710962194</v>
+        <v>2.032449744465744</v>
       </c>
       <c r="O10">
-        <v>1.842246121953494</v>
+        <v>2.258815307019184</v>
       </c>
       <c r="P10">
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>1.624084279917644</v>
+        <v>1.724392151632915</v>
       </c>
       <c r="R10" t="b">
         <v>1</v>
@@ -1033,10 +1033,10 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
+        <v>46241</v>
+      </c>
+      <c r="C11" s="2">
         <v>46240</v>
-      </c>
-      <c r="C11" s="2">
-        <v>46239</v>
       </c>
       <c r="D11" t="s">
         <v>28</v>
@@ -1048,13 +1048,13 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>0.1235224784910224</v>
+        <v>0.02541797099827621</v>
       </c>
       <c r="H11">
-        <v>3.094338397582448</v>
+        <v>3.083204538229779</v>
       </c>
       <c r="I11">
-        <v>0.6440527123143491</v>
+        <v>0.6431068704035958</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -1066,19 +1066,19 @@
         <v>211</v>
       </c>
       <c r="M11">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N11">
-        <v>10154.5502798439</v>
+        <v>10184.15755820537</v>
       </c>
       <c r="O11">
-        <v>158.5321482217053</v>
+        <v>162.9334862523853</v>
       </c>
       <c r="P11">
-        <v>0.6911318557155742</v>
+        <v>0.858720247877089</v>
       </c>
       <c r="Q11">
-        <v>0.3999197741068268</v>
+        <v>0.1799123414101336</v>
       </c>
       <c r="R11" t="b">
         <v>1</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -100,10 +100,10 @@
     <t>XAUUSD</t>
   </si>
   <si>
+    <t>UP</t>
+  </si>
+  <si>
     <t>DOWN</t>
-  </si>
-  <si>
-    <t>UP</t>
   </si>
 </sst>
 </file>
@@ -529,52 +529,52 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
+        <v>46242</v>
+      </c>
+      <c r="C2" s="2">
         <v>46241</v>
-      </c>
-      <c r="C2" s="2">
-        <v>46240</v>
       </c>
       <c r="D2" t="s">
         <v>28</v>
       </c>
       <c r="E2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="F2">
         <v>0</v>
       </c>
       <c r="G2">
-        <v>0.06525604818593596</v>
+        <v>0.0011224821324551</v>
       </c>
       <c r="H2">
-        <v>1.057025132244749</v>
+        <v>1.058558080943353</v>
       </c>
       <c r="I2">
-        <v>0.2568990958543287</v>
+        <v>0.2569624525996657</v>
       </c>
       <c r="J2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L2">
         <v>148</v>
       </c>
       <c r="M2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N2">
-        <v>1.575756182464201</v>
+        <v>1.577834594630436</v>
       </c>
       <c r="O2">
-        <v>37.86315143913707</v>
+        <v>38.04302820085443</v>
       </c>
       <c r="P2">
-        <v>0.4838068609820085</v>
+        <v>0.9296495868811573</v>
       </c>
       <c r="Q2">
-        <v>0.1264178913925114</v>
+        <v>0.01595558693534457</v>
       </c>
       <c r="R2" t="b">
         <v>1</v>
@@ -585,13 +585,13 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="C3" s="2">
         <v>46240</v>
       </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -600,13 +600,13 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>0.4555109864156004</v>
+        <v>0.506860381353027</v>
       </c>
       <c r="H3">
         <v>1.831028373575683</v>
       </c>
       <c r="I3">
-        <v>0.4268068087727196</v>
+        <v>0.4274942133786656</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -618,19 +618,19 @@
         <v>225</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N3">
-        <v>-0.00125767003577907</v>
+        <v>-0.003198585760636296</v>
       </c>
       <c r="O3">
-        <v>-0.4000768121087703</v>
+        <v>-1.030970430503238</v>
       </c>
       <c r="P3">
-        <v>0.1234563236086493</v>
+        <v>0.06843615045030899</v>
       </c>
       <c r="Q3">
-        <v>0.5196671867976929</v>
+        <v>0.5440962330150945</v>
       </c>
       <c r="R3" t="b">
         <v>1</v>
@@ -641,13 +641,13 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
+        <v>46242</v>
+      </c>
+      <c r="C4" s="2">
         <v>46241</v>
       </c>
-      <c r="C4" s="2">
-        <v>46240</v>
-      </c>
       <c r="D4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E4">
         <v>-1</v>
@@ -656,13 +656,13 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>0.1963517415702094</v>
+        <v>0.0873260828937016</v>
       </c>
       <c r="H4">
-        <v>2.05760350658658</v>
+        <v>2.059852206697442</v>
       </c>
       <c r="I4">
-        <v>0.4939899534632028</v>
+        <v>0.4943986208701923</v>
       </c>
       <c r="J4">
         <v>6</v>
@@ -674,19 +674,19 @@
         <v>145</v>
       </c>
       <c r="M4">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N4">
-        <v>5.455447224360125</v>
+        <v>5.46172872331494</v>
       </c>
       <c r="O4">
-        <v>155.3942240916413</v>
+        <v>155.2572632008306</v>
       </c>
       <c r="P4">
-        <v>0.3978568792301422</v>
+        <v>0.5526851454939193</v>
       </c>
       <c r="Q4">
-        <v>0.326088158773894</v>
+        <v>0.195222854805763</v>
       </c>
       <c r="R4" t="b">
         <v>1</v>
@@ -697,13 +697,13 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="C5" s="2">
         <v>46240</v>
       </c>
       <c r="D5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -712,13 +712,13 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>0.405796303637743</v>
+        <v>0.4295741562412449</v>
       </c>
       <c r="H5">
-        <v>1.400706371384151</v>
+        <v>1.392581694095039</v>
       </c>
       <c r="I5">
-        <v>0.2956341188545691</v>
+        <v>0.2953636980720875</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -733,16 +733,16 @@
         <v>1</v>
       </c>
       <c r="N5">
-        <v>-0.001632533288271641</v>
+        <v>-0.001756140887640365</v>
       </c>
       <c r="O5">
-        <v>-0.453436485186046</v>
+        <v>-0.4896628645083618</v>
       </c>
       <c r="P5">
-        <v>0.347635201065859</v>
+        <v>0.3275569644745021</v>
       </c>
       <c r="Q5">
-        <v>0.6220389332789703</v>
+        <v>0.6388260916488534</v>
       </c>
       <c r="R5" t="b">
         <v>1</v>
@@ -753,13 +753,13 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
+        <v>46242</v>
+      </c>
+      <c r="C6" s="2">
         <v>46241</v>
       </c>
-      <c r="C6" s="2">
-        <v>46240</v>
-      </c>
       <c r="D6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -768,37 +768,37 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0.006939916177066721</v>
+        <v>0.00811134348940943</v>
       </c>
       <c r="H6">
-        <v>0.9423046774143967</v>
+        <v>0.942411272149945</v>
       </c>
       <c r="I6">
-        <v>0.2571662636217342</v>
+        <v>0.2573996932821083</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K6">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="L6">
         <v>158</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>-0.001356362960127502</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>-0.02043352750081786</v>
       </c>
       <c r="P6">
-        <v>0.653318528670364</v>
+        <v>0.8096477176842223</v>
       </c>
       <c r="Q6">
-        <v>0.02001813408270679</v>
+        <v>0.04261227336351777</v>
       </c>
       <c r="R6" t="b">
         <v>1</v>
@@ -809,13 +809,13 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="C7" s="2">
         <v>46240</v>
       </c>
       <c r="D7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -824,13 +824,13 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>0.8444055334790207</v>
+        <v>0.8642703280274651</v>
       </c>
       <c r="H7">
         <v>1.342118731331378</v>
       </c>
       <c r="I7">
-        <v>0.3078565676223621</v>
+        <v>0.3079728688947369</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -839,22 +839,22 @@
         <v>1</v>
       </c>
       <c r="L7">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="M7">
         <v>4</v>
       </c>
       <c r="N7">
-        <v>-0.01012947706056056</v>
+        <v>-0.01167417299974652</v>
       </c>
       <c r="O7">
-        <v>-2.022284190343642</v>
+        <v>-2.340853938648687</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>0.8444055334790207</v>
+        <v>0.8642703280274651</v>
       </c>
       <c r="R7" t="b">
         <v>1</v>
@@ -865,13 +865,13 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="C8" s="2">
         <v>46240</v>
       </c>
       <c r="D8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -880,13 +880,13 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>1.029249455050077</v>
+        <v>1.00416763117204</v>
       </c>
       <c r="H8">
-        <v>1.423752883393079</v>
+        <v>1.418503977689263</v>
       </c>
       <c r="I8">
-        <v>0.3545313132497817</v>
+        <v>0.3519796253510297</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -901,16 +901,16 @@
         <v>46</v>
       </c>
       <c r="N8">
-        <v>-0.270140268819334</v>
+        <v>-0.2663097920010292</v>
       </c>
       <c r="O8">
-        <v>-69.65583872309975</v>
+        <v>-68.2220876123408</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>1.029249455050077</v>
+        <v>1.00416763117204</v>
       </c>
       <c r="R8" t="b">
         <v>1</v>
@@ -921,28 +921,28 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="C9" s="2">
         <v>46240</v>
       </c>
       <c r="D9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E9">
         <v>-1</v>
       </c>
       <c r="F9">
-        <v>0.3267611576069867</v>
+        <v>0.2844424786311258</v>
       </c>
       <c r="G9">
-        <v>2.726011728951056</v>
+        <v>2.674320367291286</v>
       </c>
       <c r="H9">
         <v>2.937332215364208</v>
       </c>
       <c r="I9">
-        <v>0.6099108129969664</v>
+        <v>0.6100734653161125</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -957,16 +957,16 @@
         <v>16</v>
       </c>
       <c r="N9">
-        <v>0.1726198619768326</v>
+        <v>0.1778724783928316</v>
       </c>
       <c r="O9">
-        <v>21.63059357955373</v>
+        <v>21.7676109921296</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>2.726011728951056</v>
+        <v>2.674320367291286</v>
       </c>
       <c r="R9" t="b">
         <v>1</v>
@@ -977,28 +977,28 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="C10" s="2">
         <v>46240</v>
       </c>
       <c r="D10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E10">
         <v>-1</v>
       </c>
       <c r="F10">
-        <v>0.1729772277224456</v>
+        <v>0</v>
       </c>
       <c r="G10">
-        <v>1.724392151632915</v>
+        <v>1.496910670713708</v>
       </c>
       <c r="H10">
-        <v>2.028161280267462</v>
+        <v>2.025039460852495</v>
       </c>
       <c r="I10">
-        <v>0.4644464459140612</v>
+        <v>0.4608427065338113</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1010,19 +1010,19 @@
         <v>233</v>
       </c>
       <c r="M10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N10">
-        <v>2.032449744465744</v>
+        <v>3.009003428519464</v>
       </c>
       <c r="O10">
-        <v>2.258815307019184</v>
+        <v>2.850302648890205</v>
       </c>
       <c r="P10">
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>1.724392151632915</v>
+        <v>1.496910670713708</v>
       </c>
       <c r="R10" t="b">
         <v>1</v>
@@ -1033,13 +1033,13 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="C11" s="2">
         <v>46240</v>
       </c>
       <c r="D11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E11">
         <v>-1</v>
@@ -1048,13 +1048,13 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>0.02541797099827621</v>
+        <v>0.0244440950116974</v>
       </c>
       <c r="H11">
         <v>3.083204538229779</v>
       </c>
       <c r="I11">
-        <v>0.6431068704035958</v>
+        <v>0.6431356013447335</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -1069,16 +1069,16 @@
         <v>109</v>
       </c>
       <c r="N11">
-        <v>10184.15755820537</v>
+        <v>10172.42595285628</v>
       </c>
       <c r="O11">
-        <v>162.9334862523853</v>
+        <v>164.4256212577646</v>
       </c>
       <c r="P11">
-        <v>0.858720247877089</v>
+        <v>0.8589160432002305</v>
       </c>
       <c r="Q11">
-        <v>0.1799123414101336</v>
+        <v>0.1732592108001988</v>
       </c>
       <c r="R11" t="b">
         <v>1</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -529,7 +529,7 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>46242</v>
+        <v>46244</v>
       </c>
       <c r="C2" s="2">
         <v>46241</v>
@@ -585,10 +585,10 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>46242</v>
+        <v>46244</v>
       </c>
       <c r="C3" s="2">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="D3" t="s">
         <v>28</v>
@@ -600,13 +600,13 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>0.506860381353027</v>
+        <v>0.7295228455748012</v>
       </c>
       <c r="H3">
-        <v>1.831028373575683</v>
+        <v>1.831787255190413</v>
       </c>
       <c r="I3">
-        <v>0.4274942133786656</v>
+        <v>0.426360226099782</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -618,19 +618,19 @@
         <v>225</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N3">
-        <v>-0.003198585760636296</v>
+        <v>-0.002771774515562242</v>
       </c>
       <c r="O3">
-        <v>-1.030970430503238</v>
+        <v>-0.876747474420954</v>
       </c>
       <c r="P3">
-        <v>0.06843615045030899</v>
+        <v>0</v>
       </c>
       <c r="Q3">
-        <v>0.5440962330150945</v>
+        <v>0.7295228455748012</v>
       </c>
       <c r="R3" t="b">
         <v>1</v>
@@ -641,7 +641,7 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>46242</v>
+        <v>46244</v>
       </c>
       <c r="C4" s="2">
         <v>46241</v>
@@ -697,10 +697,10 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>46242</v>
+        <v>46244</v>
       </c>
       <c r="C5" s="2">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="D5" t="s">
         <v>28</v>
@@ -712,13 +712,13 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>0.4295741562412449</v>
+        <v>0.6714706506544719</v>
       </c>
       <c r="H5">
-        <v>1.392581694095039</v>
+        <v>1.405195551350736</v>
       </c>
       <c r="I5">
-        <v>0.2953636980720875</v>
+        <v>0.2962104428154129</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -730,19 +730,19 @@
         <v>226</v>
       </c>
       <c r="M5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N5">
-        <v>-0.001756140887640365</v>
+        <v>-0.003696466891879712</v>
       </c>
       <c r="O5">
-        <v>-0.4896628645083618</v>
+        <v>-0.9837569905202035</v>
       </c>
       <c r="P5">
-        <v>0.3275569644745021</v>
+        <v>0.1847960370504849</v>
       </c>
       <c r="Q5">
-        <v>0.6388260916488534</v>
+        <v>0.8236842326244376</v>
       </c>
       <c r="R5" t="b">
         <v>1</v>
@@ -753,7 +753,7 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>46242</v>
+        <v>46244</v>
       </c>
       <c r="C6" s="2">
         <v>46241</v>
@@ -809,10 +809,10 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>46242</v>
+        <v>46244</v>
       </c>
       <c r="C7" s="2">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="D7" t="s">
         <v>28</v>
@@ -824,13 +824,13 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>0.8642703280274651</v>
+        <v>0.9941178915224304</v>
       </c>
       <c r="H7">
-        <v>1.342118731331378</v>
+        <v>1.341865598845894</v>
       </c>
       <c r="I7">
-        <v>0.3079728688947369</v>
+        <v>0.3077093670488694</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -839,22 +839,22 @@
         <v>1</v>
       </c>
       <c r="L7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N7">
-        <v>-0.01167417299974652</v>
+        <v>-0.01372690495725911</v>
       </c>
       <c r="O7">
-        <v>-2.340853938648687</v>
+        <v>-2.626261283247387</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>0.8642703280274651</v>
+        <v>0.9941178915224304</v>
       </c>
       <c r="R7" t="b">
         <v>1</v>
@@ -865,7 +865,7 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>46242</v>
+        <v>46244</v>
       </c>
       <c r="C8" s="2">
         <v>46240</v>
@@ -880,13 +880,13 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>1.00416763117204</v>
+        <v>1.029249455050077</v>
       </c>
       <c r="H8">
-        <v>1.418503977689263</v>
+        <v>1.423752883393079</v>
       </c>
       <c r="I8">
-        <v>0.3519796253510297</v>
+        <v>0.3545313132497817</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -901,16 +901,16 @@
         <v>46</v>
       </c>
       <c r="N8">
-        <v>-0.2663097920010292</v>
+        <v>-0.270140268819334</v>
       </c>
       <c r="O8">
-        <v>-68.2220876123408</v>
+        <v>-69.65583872309975</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>1.00416763117204</v>
+        <v>1.029249455050077</v>
       </c>
       <c r="R8" t="b">
         <v>1</v>
@@ -921,10 +921,10 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>46242</v>
+        <v>46244</v>
       </c>
       <c r="C9" s="2">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="D9" t="s">
         <v>29</v>
@@ -933,16 +933,16 @@
         <v>-1</v>
       </c>
       <c r="F9">
-        <v>0.2844424786311258</v>
+        <v>0.4841155937882756</v>
       </c>
       <c r="G9">
-        <v>2.674320367291286</v>
+        <v>2.918005842436935</v>
       </c>
       <c r="H9">
-        <v>2.937332215364208</v>
+        <v>2.937332543021793</v>
       </c>
       <c r="I9">
-        <v>0.6100734653161125</v>
+        <v>0.6083545184897283</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -954,19 +954,19 @@
         <v>76</v>
       </c>
       <c r="M9">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N9">
-        <v>0.1778724783928316</v>
+        <v>0.1889624423221335</v>
       </c>
       <c r="O9">
-        <v>21.7676109921296</v>
+        <v>24.28711675473806</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>2.674320367291286</v>
+        <v>2.918005842436935</v>
       </c>
       <c r="R9" t="b">
         <v>1</v>
@@ -977,10 +977,10 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>46242</v>
+        <v>46244</v>
       </c>
       <c r="C10" s="2">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="D10" t="s">
         <v>29</v>
@@ -989,16 +989,16 @@
         <v>-1</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>0.2546320802678816</v>
       </c>
       <c r="G10">
-        <v>1.496910670713708</v>
+        <v>1.802033117603085</v>
       </c>
       <c r="H10">
-        <v>2.025039460852495</v>
+        <v>2.030705382368219</v>
       </c>
       <c r="I10">
-        <v>0.4608427065338113</v>
+        <v>0.4659783255585894</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1013,16 +1013,16 @@
         <v>3</v>
       </c>
       <c r="N10">
-        <v>3.009003428519464</v>
+        <v>3.245544965929799</v>
       </c>
       <c r="O10">
-        <v>2.850302648890205</v>
+        <v>3.413283467774754</v>
       </c>
       <c r="P10">
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>1.496910670713708</v>
+        <v>1.802033117603085</v>
       </c>
       <c r="R10" t="b">
         <v>1</v>
@@ -1033,7 +1033,7 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>46242</v>
+        <v>46244</v>
       </c>
       <c r="C11" s="2">
         <v>46240</v>
@@ -1048,13 +1048,13 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>0.0244440950116974</v>
+        <v>0.02541797099827621</v>
       </c>
       <c r="H11">
         <v>3.083204538229779</v>
       </c>
       <c r="I11">
-        <v>0.6431356013447335</v>
+        <v>0.6431068704035958</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -1069,16 +1069,16 @@
         <v>109</v>
       </c>
       <c r="N11">
-        <v>10172.42595285628</v>
+        <v>10184.15755820537</v>
       </c>
       <c r="O11">
-        <v>164.4256212577646</v>
+        <v>162.9334862523853</v>
       </c>
       <c r="P11">
-        <v>0.8589160432002305</v>
+        <v>0.858720247877089</v>
       </c>
       <c r="Q11">
-        <v>0.1732592108001988</v>
+        <v>0.1799123414101336</v>
       </c>
       <c r="R11" t="b">
         <v>1</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -600,13 +600,13 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>0.7295228455748012</v>
+        <v>0.7405895944257652</v>
       </c>
       <c r="H3">
         <v>1.831787255190413</v>
       </c>
       <c r="I3">
-        <v>0.426360226099782</v>
+        <v>0.4270807563399017</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -618,19 +618,19 @@
         <v>225</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N3">
-        <v>-0.002771774515562242</v>
+        <v>-0.0047883980642698</v>
       </c>
       <c r="O3">
-        <v>-0.876747474420954</v>
+        <v>-1.534567309139916</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>0.7295228455748012</v>
+        <v>0.7405895944257652</v>
       </c>
       <c r="R3" t="b">
         <v>1</v>
@@ -712,13 +712,13 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>0.6714706506544719</v>
+        <v>0.6887771814529435</v>
       </c>
       <c r="H5">
-        <v>1.405195551350736</v>
+        <v>1.396308477476164</v>
       </c>
       <c r="I5">
-        <v>0.2962104428154129</v>
+        <v>0.2959051399648609</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -733,16 +733,16 @@
         <v>2</v>
       </c>
       <c r="N5">
-        <v>-0.003696466891879712</v>
+        <v>-0.0038917418708637</v>
       </c>
       <c r="O5">
-        <v>-0.9837569905202035</v>
+        <v>-1.039579969320574</v>
       </c>
       <c r="P5">
-        <v>0.1847960370504849</v>
+        <v>0.1680474529140935</v>
       </c>
       <c r="Q5">
-        <v>0.8236842326244376</v>
+        <v>0.8279044085693761</v>
       </c>
       <c r="R5" t="b">
         <v>1</v>
@@ -824,13 +824,13 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>0.9941178915224304</v>
+        <v>0.999579607254382</v>
       </c>
       <c r="H7">
         <v>1.341865598845894</v>
       </c>
       <c r="I7">
-        <v>0.3077093670488694</v>
+        <v>0.307827707802349</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -839,22 +839,22 @@
         <v>1</v>
       </c>
       <c r="L7">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="M7">
         <v>5</v>
       </c>
       <c r="N7">
-        <v>-0.01372690495725911</v>
+        <v>-0.01538377372951454</v>
       </c>
       <c r="O7">
-        <v>-2.626261283247387</v>
+        <v>-2.955576124786655</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>0.9941178915224304</v>
+        <v>0.999579607254382</v>
       </c>
       <c r="R7" t="b">
         <v>1</v>
@@ -880,13 +880,13 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>1.029249455050077</v>
+        <v>1.00416763117204</v>
       </c>
       <c r="H8">
-        <v>1.423752883393079</v>
+        <v>1.418503977689263</v>
       </c>
       <c r="I8">
-        <v>0.3545313132497817</v>
+        <v>0.3519796253510297</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -901,16 +901,16 @@
         <v>46</v>
       </c>
       <c r="N8">
-        <v>-0.270140268819334</v>
+        <v>-0.2663097920010292</v>
       </c>
       <c r="O8">
-        <v>-69.65583872309975</v>
+        <v>-68.2220876123408</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>1.029249455050077</v>
+        <v>1.00416763117204</v>
       </c>
       <c r="R8" t="b">
         <v>1</v>
@@ -933,16 +933,16 @@
         <v>-1</v>
       </c>
       <c r="F9">
-        <v>0.4841155937882756</v>
+        <v>0.4274996118397774</v>
       </c>
       <c r="G9">
-        <v>2.918005842436935</v>
+        <v>2.849099356564458</v>
       </c>
       <c r="H9">
         <v>2.937332543021793</v>
       </c>
       <c r="I9">
-        <v>0.6083545184897283</v>
+        <v>0.6085014763117085</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -957,16 +957,16 @@
         <v>17</v>
       </c>
       <c r="N9">
-        <v>0.1889624423221335</v>
+        <v>0.194351979292141</v>
       </c>
       <c r="O9">
-        <v>24.28711675473806</v>
+        <v>24.3810726710569</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>2.918005842436935</v>
+        <v>2.849099356564458</v>
       </c>
       <c r="R9" t="b">
         <v>1</v>
@@ -989,16 +989,16 @@
         <v>-1</v>
       </c>
       <c r="F10">
-        <v>0.2546320802678816</v>
+        <v>0</v>
       </c>
       <c r="G10">
-        <v>1.802033117603085</v>
+        <v>1.550379514226834</v>
       </c>
       <c r="H10">
-        <v>2.030705382368219</v>
+        <v>2.027290620307323</v>
       </c>
       <c r="I10">
-        <v>0.4659783255585894</v>
+        <v>0.4619799350473117</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1010,19 +1010,19 @@
         <v>233</v>
       </c>
       <c r="M10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N10">
-        <v>3.245544965929799</v>
+        <v>4.261967733470716</v>
       </c>
       <c r="O10">
-        <v>3.413283467774754</v>
+        <v>3.850885686442957</v>
       </c>
       <c r="P10">
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>1.802033117603085</v>
+        <v>1.550379514226834</v>
       </c>
       <c r="R10" t="b">
         <v>1</v>
@@ -1048,13 +1048,13 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>0.02541797099827621</v>
+        <v>0.0244440950116974</v>
       </c>
       <c r="H11">
         <v>3.083204538229779</v>
       </c>
       <c r="I11">
-        <v>0.6431068704035958</v>
+        <v>0.6431356013447335</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -1069,16 +1069,16 @@
         <v>109</v>
       </c>
       <c r="N11">
-        <v>10184.15755820537</v>
+        <v>10172.42595285628</v>
       </c>
       <c r="O11">
-        <v>162.9334862523853</v>
+        <v>164.4256212577646</v>
       </c>
       <c r="P11">
-        <v>0.858720247877089</v>
+        <v>0.8589160432002305</v>
       </c>
       <c r="Q11">
-        <v>0.1799123414101336</v>
+        <v>0.1732592108001988</v>
       </c>
       <c r="R11" t="b">
         <v>1</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -529,10 +529,10 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
+        <v>46245</v>
+      </c>
+      <c r="C2" s="2">
         <v>46244</v>
-      </c>
-      <c r="C2" s="2">
-        <v>46241</v>
       </c>
       <c r="D2" t="s">
         <v>28</v>
@@ -544,37 +544,37 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>0.0011224821324551</v>
+        <v>0.002126301230752134</v>
       </c>
       <c r="H2">
-        <v>1.058558080943353</v>
+        <v>1.059945034527804</v>
       </c>
       <c r="I2">
-        <v>0.2569624525996657</v>
+        <v>0.2571009624886221</v>
       </c>
       <c r="J2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K2">
-        <v>0.3333333333333333</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="L2">
         <v>148</v>
       </c>
       <c r="M2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N2">
-        <v>1.577834594630436</v>
+        <v>1.577535162084516</v>
       </c>
       <c r="O2">
-        <v>38.04302820085443</v>
+        <v>38.59548130853541</v>
       </c>
       <c r="P2">
-        <v>0.9296495868811573</v>
+        <v>0.8851385420952659</v>
       </c>
       <c r="Q2">
-        <v>0.01595558693534457</v>
+        <v>0.01851187743512436</v>
       </c>
       <c r="R2" t="b">
         <v>1</v>
@@ -585,10 +585,10 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
+        <v>46245</v>
+      </c>
+      <c r="C3" s="2">
         <v>46244</v>
-      </c>
-      <c r="C3" s="2">
-        <v>46241</v>
       </c>
       <c r="D3" t="s">
         <v>28</v>
@@ -600,13 +600,13 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>0.7405895944257652</v>
+        <v>0.761784839710452</v>
       </c>
       <c r="H3">
-        <v>1.831787255190413</v>
+        <v>1.832473862365646</v>
       </c>
       <c r="I3">
-        <v>0.4270807563399017</v>
+        <v>0.4266969686517282</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -618,19 +618,19 @@
         <v>225</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N3">
-        <v>-0.0047883980642698</v>
+        <v>-0.006685334300539016</v>
       </c>
       <c r="O3">
-        <v>-1.534567309139916</v>
+        <v>-2.057930523472868</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>0.7405895944257652</v>
+        <v>0.761784839710452</v>
       </c>
       <c r="R3" t="b">
         <v>1</v>
@@ -641,10 +641,10 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
+        <v>46245</v>
+      </c>
+      <c r="C4" s="2">
         <v>46244</v>
-      </c>
-      <c r="C4" s="2">
-        <v>46241</v>
       </c>
       <c r="D4" t="s">
         <v>29</v>
@@ -656,13 +656,13 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>0.0873260828937016</v>
+        <v>0.06508960673084886</v>
       </c>
       <c r="H4">
-        <v>2.059852206697442</v>
+        <v>2.061886744892983</v>
       </c>
       <c r="I4">
-        <v>0.4943986208701923</v>
+        <v>0.4948600701501387</v>
       </c>
       <c r="J4">
         <v>6</v>
@@ -674,19 +674,19 @@
         <v>145</v>
       </c>
       <c r="M4">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="N4">
-        <v>5.46172872331494</v>
+        <v>5.46518107509652</v>
       </c>
       <c r="O4">
-        <v>155.2572632008306</v>
+        <v>156.7558595602361</v>
       </c>
       <c r="P4">
-        <v>0.5526851454939193</v>
+        <v>0.5574830586112703</v>
       </c>
       <c r="Q4">
-        <v>0.195222854805763</v>
+        <v>0.1470895250396093</v>
       </c>
       <c r="R4" t="b">
         <v>1</v>
@@ -697,10 +697,10 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
+        <v>46245</v>
+      </c>
+      <c r="C5" s="2">
         <v>46244</v>
-      </c>
-      <c r="C5" s="2">
-        <v>46241</v>
       </c>
       <c r="D5" t="s">
         <v>28</v>
@@ -712,13 +712,13 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>0.6887771814529435</v>
+        <v>0.734030243305818</v>
       </c>
       <c r="H5">
-        <v>1.396308477476164</v>
+        <v>1.399680329106705</v>
       </c>
       <c r="I5">
-        <v>0.2959051399648609</v>
+        <v>0.2963726799657249</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -730,19 +730,19 @@
         <v>226</v>
       </c>
       <c r="M5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N5">
-        <v>-0.0038917418708637</v>
+        <v>-0.006424002710636185</v>
       </c>
       <c r="O5">
-        <v>-1.039579969320574</v>
+        <v>-1.692913655508806</v>
       </c>
       <c r="P5">
-        <v>0.1680474529140935</v>
+        <v>0.1128794771949314</v>
       </c>
       <c r="Q5">
-        <v>0.8279044085693761</v>
+        <v>0.8274301230060823</v>
       </c>
       <c r="R5" t="b">
         <v>1</v>
@@ -753,10 +753,10 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
+        <v>46245</v>
+      </c>
+      <c r="C6" s="2">
         <v>46244</v>
-      </c>
-      <c r="C6" s="2">
-        <v>46241</v>
       </c>
       <c r="D6" t="s">
         <v>28</v>
@@ -768,13 +768,13 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0.00811134348940943</v>
+        <v>0.07621669096916868</v>
       </c>
       <c r="H6">
-        <v>0.942411272149945</v>
+        <v>0.9425077150059173</v>
       </c>
       <c r="I6">
-        <v>0.2573996932821083</v>
+        <v>0.257600086871517</v>
       </c>
       <c r="J6">
         <v>6</v>
@@ -786,19 +786,19 @@
         <v>158</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N6">
-        <v>-0.001356362960127502</v>
+        <v>-0.006216479054812938</v>
       </c>
       <c r="O6">
-        <v>-0.02043352750081786</v>
+        <v>-0.09652382495134601</v>
       </c>
       <c r="P6">
-        <v>0.8096477176842223</v>
+        <v>0.4229177146501814</v>
       </c>
       <c r="Q6">
-        <v>0.04261227336351777</v>
+        <v>0.1320724841223765</v>
       </c>
       <c r="R6" t="b">
         <v>1</v>
@@ -809,10 +809,10 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
+        <v>46245</v>
+      </c>
+      <c r="C7" s="2">
         <v>46244</v>
-      </c>
-      <c r="C7" s="2">
-        <v>46241</v>
       </c>
       <c r="D7" t="s">
         <v>28</v>
@@ -821,16 +821,16 @@
         <v>1</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>0.2657391701112821</v>
       </c>
       <c r="G7">
-        <v>0.999579607254382</v>
+        <v>1.19749366441393</v>
       </c>
       <c r="H7">
-        <v>1.341865598845894</v>
+        <v>1.34163657421617</v>
       </c>
       <c r="I7">
-        <v>0.307827707802349</v>
+        <v>0.3076547408090226</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -842,19 +842,19 @@
         <v>239</v>
       </c>
       <c r="M7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N7">
-        <v>-0.01538377372951454</v>
+        <v>-0.01964700466571359</v>
       </c>
       <c r="O7">
-        <v>-2.955576124786655</v>
+        <v>-4.017792365176592</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>0.999579607254382</v>
+        <v>1.19749366441393</v>
       </c>
       <c r="R7" t="b">
         <v>1</v>
@@ -865,10 +865,10 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
+        <v>46245</v>
+      </c>
+      <c r="C8" s="2">
         <v>46244</v>
-      </c>
-      <c r="C8" s="2">
-        <v>46240</v>
       </c>
       <c r="D8" t="s">
         <v>28</v>
@@ -880,13 +880,13 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>1.00416763117204</v>
+        <v>0.9743535519187986</v>
       </c>
       <c r="H8">
-        <v>1.418503977689263</v>
+        <v>1.420594563717076</v>
       </c>
       <c r="I8">
-        <v>0.3519796253510297</v>
+        <v>0.3521586459893807</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -898,19 +898,19 @@
         <v>111</v>
       </c>
       <c r="M8">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N8">
-        <v>-0.2663097920010292</v>
+        <v>-0.2692056106908566</v>
       </c>
       <c r="O8">
-        <v>-68.2220876123408</v>
+        <v>-67.50028744823145</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>1.00416763117204</v>
+        <v>0.9743535519187986</v>
       </c>
       <c r="R8" t="b">
         <v>1</v>
@@ -921,10 +921,10 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
+        <v>46245</v>
+      </c>
+      <c r="C9" s="2">
         <v>46244</v>
-      </c>
-      <c r="C9" s="2">
-        <v>46241</v>
       </c>
       <c r="D9" t="s">
         <v>29</v>
@@ -933,16 +933,16 @@
         <v>-1</v>
       </c>
       <c r="F9">
-        <v>0.4274996118397774</v>
+        <v>0.3076041134461021</v>
       </c>
       <c r="G9">
-        <v>2.849099356564458</v>
+        <v>2.703799004582577</v>
       </c>
       <c r="H9">
-        <v>2.937332543021793</v>
+        <v>2.937332839473894</v>
       </c>
       <c r="I9">
-        <v>0.6085014763117085</v>
+        <v>0.6069096358406139</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -954,19 +954,19 @@
         <v>76</v>
       </c>
       <c r="M9">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N9">
-        <v>0.194351979292141</v>
+        <v>0.2110673119754022</v>
       </c>
       <c r="O9">
-        <v>24.3810726710569</v>
+        <v>25.71863325345435</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>2.849099356564458</v>
+        <v>2.703799004582577</v>
       </c>
       <c r="R9" t="b">
         <v>1</v>
@@ -977,10 +977,10 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
+        <v>46245</v>
+      </c>
+      <c r="C10" s="2">
         <v>46244</v>
-      </c>
-      <c r="C10" s="2">
-        <v>46241</v>
       </c>
       <c r="D10" t="s">
         <v>29</v>
@@ -992,13 +992,13 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>1.550379514226834</v>
+        <v>1.266603651507621</v>
       </c>
       <c r="H10">
-        <v>2.027290620307323</v>
+        <v>2.029327383623595</v>
       </c>
       <c r="I10">
-        <v>0.4619799350473117</v>
+        <v>0.4629494856105149</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1010,19 +1010,19 @@
         <v>233</v>
       </c>
       <c r="M10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N10">
-        <v>4.261967733470716</v>
+        <v>5.527731888492495</v>
       </c>
       <c r="O10">
-        <v>3.850885686442957</v>
+        <v>4.727298887565766</v>
       </c>
       <c r="P10">
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>1.550379514226834</v>
+        <v>1.266603651507621</v>
       </c>
       <c r="R10" t="b">
         <v>1</v>
@@ -1033,28 +1033,28 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
+        <v>46245</v>
+      </c>
+      <c r="C11" s="2">
         <v>46244</v>
       </c>
-      <c r="C11" s="2">
-        <v>46240</v>
-      </c>
       <c r="D11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E11">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="F11">
         <v>0</v>
       </c>
       <c r="G11">
-        <v>0.0244440950116974</v>
+        <v>0.1815823354572913</v>
       </c>
       <c r="H11">
-        <v>3.083204538229779</v>
+        <v>3.070801794604331</v>
       </c>
       <c r="I11">
-        <v>0.6431356013447335</v>
+        <v>0.6422779501044444</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -1066,19 +1066,19 @@
         <v>211</v>
       </c>
       <c r="M11">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N11">
-        <v>10172.42595285628</v>
+        <v>10170.06084862066</v>
       </c>
       <c r="O11">
-        <v>164.4256212577646</v>
+        <v>135.9854558901741</v>
       </c>
       <c r="P11">
-        <v>0.8589160432002305</v>
+        <v>0.5139745299739084</v>
       </c>
       <c r="Q11">
-        <v>0.1732592108001988</v>
+        <v>0.3736066248699749</v>
       </c>
       <c r="R11" t="b">
         <v>1</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -529,10 +529,10 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
+        <v>46246</v>
+      </c>
+      <c r="C2" s="2">
         <v>46245</v>
-      </c>
-      <c r="C2" s="2">
-        <v>46244</v>
       </c>
       <c r="D2" t="s">
         <v>28</v>
@@ -544,37 +544,37 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>0.002126301230752134</v>
+        <v>0.01736807487827153</v>
       </c>
       <c r="H2">
-        <v>1.059945034527804</v>
+        <v>1.061199897294688</v>
       </c>
       <c r="I2">
-        <v>0.2571009624886221</v>
+        <v>0.2573022749378317</v>
       </c>
       <c r="J2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K2">
-        <v>0.8333333333333334</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M2">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>1.577535162084516</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>38.59548130853541</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>0.8851385420952659</v>
+        <v>0.7581661069505118</v>
       </c>
       <c r="Q2">
-        <v>0.01851187743512436</v>
+        <v>0.07181819991922048</v>
       </c>
       <c r="R2" t="b">
         <v>1</v>
@@ -585,10 +585,10 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
+        <v>46246</v>
+      </c>
+      <c r="C3" s="2">
         <v>46245</v>
-      </c>
-      <c r="C3" s="2">
-        <v>46244</v>
       </c>
       <c r="D3" t="s">
         <v>28</v>
@@ -600,13 +600,13 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>0.761784839710452</v>
+        <v>0.8499218835129919</v>
       </c>
       <c r="H3">
-        <v>1.832473862365646</v>
+        <v>1.833095078381332</v>
       </c>
       <c r="I3">
-        <v>0.4266969686517282</v>
+        <v>0.4255194976037528</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -618,19 +618,19 @@
         <v>225</v>
       </c>
       <c r="M3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N3">
-        <v>-0.006685334300539016</v>
+        <v>-0.006736622324756462</v>
       </c>
       <c r="O3">
-        <v>-2.057930523472868</v>
+        <v>-2.036551771681938</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>0.761784839710452</v>
+        <v>0.8499218835129919</v>
       </c>
       <c r="R3" t="b">
         <v>1</v>
@@ -641,52 +641,52 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
+        <v>46246</v>
+      </c>
+      <c r="C4" s="2">
         <v>46245</v>
       </c>
-      <c r="C4" s="2">
-        <v>46244</v>
-      </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E4">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="F4">
         <v>0</v>
       </c>
       <c r="G4">
-        <v>0.06508960673084886</v>
+        <v>0.05761258491225919</v>
       </c>
       <c r="H4">
-        <v>2.061886744892983</v>
+        <v>2.063727517546092</v>
       </c>
       <c r="I4">
-        <v>0.4948600701501387</v>
+        <v>0.4953904704109316</v>
       </c>
       <c r="J4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K4">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L4">
         <v>145</v>
       </c>
       <c r="M4">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="N4">
-        <v>5.46518107509652</v>
+        <v>5.466966299856217</v>
       </c>
       <c r="O4">
-        <v>156.7558595602361</v>
+        <v>160.5570132116363</v>
       </c>
       <c r="P4">
-        <v>0.5574830586112703</v>
+        <v>0.5134395888862121</v>
       </c>
       <c r="Q4">
-        <v>0.1470895250396093</v>
+        <v>0.118407876177961</v>
       </c>
       <c r="R4" t="b">
         <v>1</v>
@@ -697,10 +697,10 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
+        <v>46246</v>
+      </c>
+      <c r="C5" s="2">
         <v>46245</v>
-      </c>
-      <c r="C5" s="2">
-        <v>46244</v>
       </c>
       <c r="D5" t="s">
         <v>28</v>
@@ -712,13 +712,13 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>0.734030243305818</v>
+        <v>0.7870207281778198</v>
       </c>
       <c r="H5">
-        <v>1.399680329106705</v>
+        <v>1.412932006621949</v>
       </c>
       <c r="I5">
-        <v>0.2963726799657249</v>
+        <v>0.2971532347515937</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -730,19 +730,19 @@
         <v>226</v>
       </c>
       <c r="M5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N5">
-        <v>-0.006424002710636185</v>
+        <v>-0.008855193393956611</v>
       </c>
       <c r="O5">
-        <v>-1.692913655508806</v>
+        <v>-2.362735039363263</v>
       </c>
       <c r="P5">
-        <v>0.1128794771949314</v>
+        <v>0.07105020922240264</v>
       </c>
       <c r="Q5">
-        <v>0.8274301230060823</v>
+        <v>0.8472155718115046</v>
       </c>
       <c r="R5" t="b">
         <v>1</v>
@@ -753,10 +753,10 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
+        <v>46246</v>
+      </c>
+      <c r="C6" s="2">
         <v>46245</v>
-      </c>
-      <c r="C6" s="2">
-        <v>46244</v>
       </c>
       <c r="D6" t="s">
         <v>28</v>
@@ -768,13 +768,13 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0.07621669096916868</v>
+        <v>0.1432801373781929</v>
       </c>
       <c r="H6">
-        <v>0.9425077150059173</v>
+        <v>0.9425949728279875</v>
       </c>
       <c r="I6">
-        <v>0.257600086871517</v>
+        <v>0.2577781873035978</v>
       </c>
       <c r="J6">
         <v>6</v>
@@ -786,19 +786,19 @@
         <v>158</v>
       </c>
       <c r="M6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N6">
-        <v>-0.006216479054812938</v>
+        <v>-0.01458818406043766</v>
       </c>
       <c r="O6">
-        <v>-0.09652382495134601</v>
+        <v>-0.2311417929652071</v>
       </c>
       <c r="P6">
-        <v>0.4229177146501814</v>
+        <v>0.2634541241232122</v>
       </c>
       <c r="Q6">
-        <v>0.1320724841223765</v>
+        <v>0.19452982098044</v>
       </c>
       <c r="R6" t="b">
         <v>1</v>
@@ -809,10 +809,10 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
+        <v>46246</v>
+      </c>
+      <c r="C7" s="2">
         <v>46245</v>
-      </c>
-      <c r="C7" s="2">
-        <v>46244</v>
       </c>
       <c r="D7" t="s">
         <v>28</v>
@@ -821,16 +821,16 @@
         <v>1</v>
       </c>
       <c r="F7">
-        <v>0.2657391701112821</v>
+        <v>0.435624528851162</v>
       </c>
       <c r="G7">
-        <v>1.19749366441393</v>
+        <v>1.301850308907033</v>
       </c>
       <c r="H7">
-        <v>1.34163657421617</v>
+        <v>1.341429361455944</v>
       </c>
       <c r="I7">
-        <v>0.3076547408090226</v>
+        <v>0.3074078670228536</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -839,22 +839,22 @@
         <v>1</v>
       </c>
       <c r="L7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N7">
-        <v>-0.01964700466571359</v>
+        <v>-0.02261507709918438</v>
       </c>
       <c r="O7">
-        <v>-4.017792365176592</v>
+        <v>-4.670124336434546</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>1.19749366441393</v>
+        <v>1.301850308907033</v>
       </c>
       <c r="R7" t="b">
         <v>1</v>
@@ -865,10 +865,10 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
+        <v>46246</v>
+      </c>
+      <c r="C8" s="2">
         <v>46245</v>
-      </c>
-      <c r="C8" s="2">
-        <v>46244</v>
       </c>
       <c r="D8" t="s">
         <v>28</v>
@@ -880,13 +880,13 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>0.9743535519187986</v>
+        <v>1.04152115130347</v>
       </c>
       <c r="H8">
-        <v>1.420594563717076</v>
+        <v>1.428891873095216</v>
       </c>
       <c r="I8">
-        <v>0.3521586459893807</v>
+        <v>0.3553024013127964</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -898,19 +898,19 @@
         <v>111</v>
       </c>
       <c r="M8">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N8">
-        <v>-0.2692056106908566</v>
+        <v>-0.2760706007353206</v>
       </c>
       <c r="O8">
-        <v>-67.50028744823145</v>
+        <v>-71.90676112175828</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>0.9743535519187986</v>
+        <v>1.04152115130347</v>
       </c>
       <c r="R8" t="b">
         <v>1</v>
@@ -921,10 +921,10 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
+        <v>46246</v>
+      </c>
+      <c r="C9" s="2">
         <v>46245</v>
-      </c>
-      <c r="C9" s="2">
-        <v>46244</v>
       </c>
       <c r="D9" t="s">
         <v>29</v>
@@ -933,16 +933,16 @@
         <v>-1</v>
       </c>
       <c r="F9">
-        <v>0.3076041134461021</v>
+        <v>0.3937945574816273</v>
       </c>
       <c r="G9">
-        <v>2.703799004582577</v>
+        <v>2.808759793747735</v>
       </c>
       <c r="H9">
-        <v>2.937332839473894</v>
+        <v>2.937333107692461</v>
       </c>
       <c r="I9">
-        <v>0.6069096358406139</v>
+        <v>0.6053047324880902</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -954,19 +954,19 @@
         <v>76</v>
       </c>
       <c r="M9">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N9">
-        <v>0.2110673119754022</v>
+        <v>0.2220630293291135</v>
       </c>
       <c r="O9">
-        <v>25.71863325345435</v>
+        <v>28.88490579399404</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>2.703799004582577</v>
+        <v>2.808759793747735</v>
       </c>
       <c r="R9" t="b">
         <v>1</v>
@@ -977,10 +977,10 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
+        <v>46246</v>
+      </c>
+      <c r="C10" s="2">
         <v>46245</v>
-      </c>
-      <c r="C10" s="2">
-        <v>46244</v>
       </c>
       <c r="D10" t="s">
         <v>29</v>
@@ -992,13 +992,13 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>1.266603651507621</v>
+        <v>1.308563355560978</v>
       </c>
       <c r="H10">
-        <v>2.029327383623595</v>
+        <v>2.035089776011247</v>
       </c>
       <c r="I10">
-        <v>0.4629494856105149</v>
+        <v>0.4684032883687994</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1013,16 +1013,16 @@
         <v>5</v>
       </c>
       <c r="N10">
-        <v>5.527731888492495</v>
+        <v>5.658860598150637</v>
       </c>
       <c r="O10">
-        <v>4.727298887565766</v>
+        <v>5.570527940803638</v>
       </c>
       <c r="P10">
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>1.266603651507621</v>
+        <v>1.308563355560978</v>
       </c>
       <c r="R10" t="b">
         <v>1</v>
@@ -1033,10 +1033,10 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
+        <v>46246</v>
+      </c>
+      <c r="C11" s="2">
         <v>46245</v>
-      </c>
-      <c r="C11" s="2">
-        <v>46244</v>
       </c>
       <c r="D11" t="s">
         <v>28</v>
@@ -1048,13 +1048,13 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>0.1815823354572913</v>
+        <v>0.5216109107284753</v>
       </c>
       <c r="H11">
-        <v>3.070801794604331</v>
+        <v>3.05679065692195</v>
       </c>
       <c r="I11">
-        <v>0.6422779501044444</v>
+        <v>0.6413071322051076</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -1063,22 +1063,22 @@
         <v>1</v>
       </c>
       <c r="L11">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M11">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="N11">
-        <v>10170.06084862066</v>
+        <v>0</v>
       </c>
       <c r="O11">
-        <v>135.9854558901741</v>
+        <v>0</v>
       </c>
       <c r="P11">
-        <v>0.5139745299739084</v>
+        <v>0.3107531071481738</v>
       </c>
       <c r="Q11">
-        <v>0.3736066248699749</v>
+        <v>0.7567838406499874</v>
       </c>
       <c r="R11" t="b">
         <v>1</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -600,13 +600,13 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>0.8499218835129919</v>
+        <v>0.8430004673568237</v>
       </c>
       <c r="H3">
         <v>1.833095078381332</v>
       </c>
       <c r="I3">
-        <v>0.4255194976037528</v>
+        <v>0.4262981229665229</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -618,19 +618,19 @@
         <v>225</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N3">
-        <v>-0.006736622324756462</v>
+        <v>-0.00878631363834294</v>
       </c>
       <c r="O3">
-        <v>-2.036551771681938</v>
+        <v>-2.689589831350196</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>0.8499218835129919</v>
+        <v>0.8430004673568237</v>
       </c>
       <c r="R3" t="b">
         <v>1</v>
@@ -712,13 +712,13 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>0.7870207281778198</v>
+        <v>0.7880600803059172</v>
       </c>
       <c r="H5">
-        <v>1.412932006621949</v>
+        <v>1.402731052010528</v>
       </c>
       <c r="I5">
-        <v>0.2971532347515937</v>
+        <v>0.2967879209424962</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -733,16 +733,16 @@
         <v>4</v>
       </c>
       <c r="N5">
-        <v>-0.008855193393956611</v>
+        <v>-0.009081771347165176</v>
       </c>
       <c r="O5">
-        <v>-2.362735039363263</v>
+        <v>-2.432229533434924</v>
       </c>
       <c r="P5">
-        <v>0.07105020922240264</v>
+        <v>0.0571118320438489</v>
       </c>
       <c r="Q5">
-        <v>0.8472155718115046</v>
+        <v>0.8357937951582884</v>
       </c>
       <c r="R5" t="b">
         <v>1</v>
@@ -821,16 +821,16 @@
         <v>1</v>
       </c>
       <c r="F7">
-        <v>0.435624528851162</v>
+        <v>0.4164713617588751</v>
       </c>
       <c r="G7">
-        <v>1.301850308907033</v>
+        <v>1.290055274739505</v>
       </c>
       <c r="H7">
         <v>1.341429361455944</v>
       </c>
       <c r="I7">
-        <v>0.3074078670228536</v>
+        <v>0.3075237894345641</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -839,22 +839,22 @@
         <v>1</v>
       </c>
       <c r="L7">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="M7">
         <v>7</v>
       </c>
       <c r="N7">
-        <v>-0.02261507709918438</v>
+        <v>-0.02432094087197035</v>
       </c>
       <c r="O7">
-        <v>-4.670124336434546</v>
+        <v>-5.045090712810542</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>1.301850308907033</v>
+        <v>1.290055274739505</v>
       </c>
       <c r="R7" t="b">
         <v>1</v>
@@ -880,13 +880,13 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>1.04152115130347</v>
+        <v>1.045407844964561</v>
       </c>
       <c r="H8">
-        <v>1.428891873095216</v>
+        <v>1.422486046313669</v>
       </c>
       <c r="I8">
-        <v>0.3553024013127964</v>
+        <v>0.3522402701311929</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -901,16 +901,16 @@
         <v>48</v>
       </c>
       <c r="N8">
-        <v>-0.2760706007353206</v>
+        <v>-0.2720966275865917</v>
       </c>
       <c r="O8">
-        <v>-71.90676112175828</v>
+        <v>-70.4066682600923</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>1.04152115130347</v>
+        <v>1.045407844964561</v>
       </c>
       <c r="R8" t="b">
         <v>1</v>
@@ -933,16 +933,16 @@
         <v>-1</v>
       </c>
       <c r="F9">
-        <v>0.3937945574816273</v>
+        <v>0.3266418956129878</v>
       </c>
       <c r="G9">
-        <v>2.808759793747735</v>
+        <v>2.727441907511101</v>
       </c>
       <c r="H9">
         <v>2.937333107692461</v>
       </c>
       <c r="I9">
-        <v>0.6053047324880902</v>
+        <v>0.6053688719184135</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -957,16 +957,16 @@
         <v>19</v>
       </c>
       <c r="N9">
-        <v>0.2220630293291135</v>
+        <v>0.2275123706424087</v>
       </c>
       <c r="O9">
-        <v>28.88490579399404</v>
+        <v>28.87605447616801</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>2.808759793747735</v>
+        <v>2.727441907511101</v>
       </c>
       <c r="R9" t="b">
         <v>1</v>
@@ -992,13 +992,13 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>1.308563355560978</v>
+        <v>1.108618118011758</v>
       </c>
       <c r="H10">
-        <v>2.035089776011247</v>
+        <v>2.031170169481175</v>
       </c>
       <c r="I10">
-        <v>0.4684032883687994</v>
+        <v>0.4637209511163596</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1010,19 +1010,19 @@
         <v>233</v>
       </c>
       <c r="M10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N10">
-        <v>5.658860598150637</v>
+        <v>6.692697437469541</v>
       </c>
       <c r="O10">
-        <v>5.570527940803638</v>
+        <v>5.711711062487367</v>
       </c>
       <c r="P10">
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>1.308563355560978</v>
+        <v>1.108618118011758</v>
       </c>
       <c r="R10" t="b">
         <v>1</v>
@@ -1048,13 +1048,13 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>0.5216109107284753</v>
+        <v>0.5282068048872706</v>
       </c>
       <c r="H11">
         <v>3.05679065692195</v>
       </c>
       <c r="I11">
-        <v>0.6413071322051076</v>
+        <v>0.6413405721605206</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -1075,10 +1075,10 @@
         <v>0</v>
       </c>
       <c r="P11">
-        <v>0.3107531071481738</v>
+        <v>0.3085779817708779</v>
       </c>
       <c r="Q11">
-        <v>0.7567838406499874</v>
+        <v>0.7639427020853627</v>
       </c>
       <c r="R11" t="b">
         <v>1</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -529,10 +529,10 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
+        <v>46247</v>
+      </c>
+      <c r="C2" s="2">
         <v>46246</v>
-      </c>
-      <c r="C2" s="2">
-        <v>46245</v>
       </c>
       <c r="D2" t="s">
         <v>28</v>
@@ -544,13 +544,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>0.01736807487827153</v>
+        <v>0.04026990801319719</v>
       </c>
       <c r="H2">
-        <v>1.061199897294688</v>
+        <v>1.062335249321869</v>
       </c>
       <c r="I2">
-        <v>0.2573022749378317</v>
+        <v>0.2575515300889112</v>
       </c>
       <c r="J2">
         <v>6</v>
@@ -562,19 +562,19 @@
         <v>149</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>-0.003508405804337893</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>-0.08960300866652746</v>
       </c>
       <c r="P2">
-        <v>0.7581661069505118</v>
+        <v>0.6368591969603571</v>
       </c>
       <c r="Q2">
-        <v>0.07181819991922048</v>
+        <v>0.1108933715961438</v>
       </c>
       <c r="R2" t="b">
         <v>1</v>
@@ -585,10 +585,10 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
+        <v>46247</v>
+      </c>
+      <c r="C3" s="2">
         <v>46246</v>
-      </c>
-      <c r="C3" s="2">
-        <v>46245</v>
       </c>
       <c r="D3" t="s">
         <v>28</v>
@@ -600,13 +600,13 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>0.8430004673568237</v>
+        <v>0.9434522607322694</v>
       </c>
       <c r="H3">
-        <v>1.833095078381332</v>
+        <v>1.833657130966953</v>
       </c>
       <c r="I3">
-        <v>0.4262981229665229</v>
+        <v>0.4250609350156714</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -618,19 +618,19 @@
         <v>225</v>
       </c>
       <c r="M3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N3">
-        <v>-0.00878631363834294</v>
+        <v>-0.009056949195109902</v>
       </c>
       <c r="O3">
-        <v>-2.689589831350196</v>
+        <v>-2.857403689724818</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>0.8430004673568237</v>
+        <v>0.9434522607322694</v>
       </c>
       <c r="R3" t="b">
         <v>1</v>
@@ -641,10 +641,10 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
+        <v>46247</v>
+      </c>
+      <c r="C4" s="2">
         <v>46246</v>
-      </c>
-      <c r="C4" s="2">
-        <v>46245</v>
       </c>
       <c r="D4" t="s">
         <v>28</v>
@@ -656,13 +656,13 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>0.05761258491225919</v>
+        <v>0.1041141052377663</v>
       </c>
       <c r="H4">
-        <v>2.063727517546092</v>
+        <v>2.065392978517953</v>
       </c>
       <c r="I4">
-        <v>0.4953904704109316</v>
+        <v>0.4959064210793445</v>
       </c>
       <c r="J4">
         <v>2</v>
@@ -671,22 +671,22 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="L4">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M4">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="N4">
-        <v>5.466966299856217</v>
+        <v>0</v>
       </c>
       <c r="O4">
-        <v>160.5570132116363</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>0.5134395888862121</v>
+        <v>0.3575676991466065</v>
       </c>
       <c r="Q4">
-        <v>0.118407876177961</v>
+        <v>0.1620623762215309</v>
       </c>
       <c r="R4" t="b">
         <v>1</v>
@@ -697,10 +697,10 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
+        <v>46247</v>
+      </c>
+      <c r="C5" s="2">
         <v>46246</v>
-      </c>
-      <c r="C5" s="2">
-        <v>46245</v>
       </c>
       <c r="D5" t="s">
         <v>28</v>
@@ -712,13 +712,13 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>0.7880600803059172</v>
+        <v>0.7956531118044045</v>
       </c>
       <c r="H5">
-        <v>1.402731052010528</v>
+        <v>1.416256840375411</v>
       </c>
       <c r="I5">
-        <v>0.2967879209424962</v>
+        <v>0.2975245404191426</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -730,19 +730,19 @@
         <v>226</v>
       </c>
       <c r="M5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N5">
-        <v>-0.009081771347165176</v>
+        <v>-0.01153941049166994</v>
       </c>
       <c r="O5">
-        <v>-2.432229533434924</v>
+        <v>-3.209849928141791</v>
       </c>
       <c r="P5">
-        <v>0.0571118320438489</v>
+        <v>0.03183319849094737</v>
       </c>
       <c r="Q5">
-        <v>0.8357937951582884</v>
+        <v>0.8218140826190732</v>
       </c>
       <c r="R5" t="b">
         <v>1</v>
@@ -753,10 +753,10 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
+        <v>46247</v>
+      </c>
+      <c r="C6" s="2">
         <v>46246</v>
-      </c>
-      <c r="C6" s="2">
-        <v>46245</v>
       </c>
       <c r="D6" t="s">
         <v>28</v>
@@ -768,13 +768,13 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0.1432801373781929</v>
+        <v>0.1693278678201049</v>
       </c>
       <c r="H6">
-        <v>0.9425949728279875</v>
+        <v>0.9426739203812891</v>
       </c>
       <c r="I6">
-        <v>0.2577781873035978</v>
+        <v>0.2579003967070224</v>
       </c>
       <c r="J6">
         <v>6</v>
@@ -786,19 +786,19 @@
         <v>158</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N6">
-        <v>-0.01458818406043766</v>
+        <v>-0.02503253973589563</v>
       </c>
       <c r="O6">
-        <v>-0.2311417929652071</v>
+        <v>-0.4118839248554855</v>
       </c>
       <c r="P6">
-        <v>0.2634541241232122</v>
+        <v>0.2091853437502047</v>
       </c>
       <c r="Q6">
-        <v>0.19452982098044</v>
+        <v>0.2141182721917323</v>
       </c>
       <c r="R6" t="b">
         <v>1</v>
@@ -809,10 +809,10 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
+        <v>46247</v>
+      </c>
+      <c r="C7" s="2">
         <v>46246</v>
-      </c>
-      <c r="C7" s="2">
-        <v>46245</v>
       </c>
       <c r="D7" t="s">
         <v>28</v>
@@ -821,16 +821,16 @@
         <v>1</v>
       </c>
       <c r="F7">
-        <v>0.4164713617588751</v>
+        <v>0.6399191648840915</v>
       </c>
       <c r="G7">
-        <v>1.290055274739505</v>
+        <v>1.427668953276874</v>
       </c>
       <c r="H7">
-        <v>1.341429361455944</v>
+        <v>1.341664228050781</v>
       </c>
       <c r="I7">
-        <v>0.3075237894345641</v>
+        <v>0.3073371875015805</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -839,22 +839,22 @@
         <v>1</v>
       </c>
       <c r="L7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N7">
-        <v>-0.02432094087197035</v>
+        <v>-0.0275464658356021</v>
       </c>
       <c r="O7">
-        <v>-5.045090712810542</v>
+        <v>-6.173371565526299</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>1.290055274739505</v>
+        <v>1.427668953276874</v>
       </c>
       <c r="R7" t="b">
         <v>1</v>
@@ -865,10 +865,10 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
+        <v>46247</v>
+      </c>
+      <c r="C8" s="2">
         <v>46246</v>
-      </c>
-      <c r="C8" s="2">
-        <v>46245</v>
       </c>
       <c r="D8" t="s">
         <v>28</v>
@@ -877,16 +877,16 @@
         <v>1</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>0.05640024919461578</v>
       </c>
       <c r="G8">
-        <v>1.045407844964561</v>
+        <v>1.115643117315203</v>
       </c>
       <c r="H8">
-        <v>1.422486046313669</v>
+        <v>1.431100415098159</v>
       </c>
       <c r="I8">
-        <v>0.3522402701311929</v>
+        <v>0.3555652333102337</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -898,19 +898,19 @@
         <v>111</v>
       </c>
       <c r="M8">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N8">
-        <v>-0.2720966275865917</v>
+        <v>-0.2790888128874402</v>
       </c>
       <c r="O8">
-        <v>-70.4066682600923</v>
+        <v>-72.20259411298488</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>1.045407844964561</v>
+        <v>1.115643117315203</v>
       </c>
       <c r="R8" t="b">
         <v>1</v>
@@ -921,10 +921,10 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
+        <v>46247</v>
+      </c>
+      <c r="C9" s="2">
         <v>46246</v>
-      </c>
-      <c r="C9" s="2">
-        <v>46245</v>
       </c>
       <c r="D9" t="s">
         <v>29</v>
@@ -933,16 +933,16 @@
         <v>-1</v>
       </c>
       <c r="F9">
-        <v>0.3266418956129878</v>
+        <v>0.4174537540470262</v>
       </c>
       <c r="G9">
-        <v>2.727441907511101</v>
+        <v>2.837624712178707</v>
       </c>
       <c r="H9">
-        <v>2.937333107692461</v>
+        <v>2.937333350366403</v>
       </c>
       <c r="I9">
-        <v>0.6053688719184135</v>
+        <v>0.6039562250020385</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -954,19 +954,19 @@
         <v>76</v>
       </c>
       <c r="M9">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N9">
-        <v>0.2275123706424087</v>
+        <v>0.2383922357658709</v>
       </c>
       <c r="O9">
-        <v>28.87605447616801</v>
+        <v>31.20463092629761</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>2.727441907511101</v>
+        <v>2.837624712178707</v>
       </c>
       <c r="R9" t="b">
         <v>1</v>
@@ -977,10 +977,10 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
+        <v>46247</v>
+      </c>
+      <c r="C10" s="2">
         <v>46246</v>
-      </c>
-      <c r="C10" s="2">
-        <v>46245</v>
       </c>
       <c r="D10" t="s">
         <v>29</v>
@@ -992,13 +992,13 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>1.108618118011758</v>
+        <v>1.260122004711455</v>
       </c>
       <c r="H10">
-        <v>2.031170169481175</v>
+        <v>2.0369740213745</v>
       </c>
       <c r="I10">
-        <v>0.4637209511163596</v>
+        <v>0.4692876252201308</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1013,16 +1013,16 @@
         <v>6</v>
       </c>
       <c r="N10">
-        <v>6.692697437469541</v>
+        <v>6.75028365738441</v>
       </c>
       <c r="O10">
-        <v>5.711711062487367</v>
+        <v>6.984514334531778</v>
       </c>
       <c r="P10">
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>1.108618118011758</v>
+        <v>1.260122004711455</v>
       </c>
       <c r="R10" t="b">
         <v>1</v>
@@ -1033,10 +1033,10 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
+        <v>46247</v>
+      </c>
+      <c r="C11" s="2">
         <v>46246</v>
-      </c>
-      <c r="C11" s="2">
-        <v>46245</v>
       </c>
       <c r="D11" t="s">
         <v>28</v>
@@ -1048,13 +1048,13 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>0.5282068048872706</v>
+        <v>0.9067916516445035</v>
       </c>
       <c r="H11">
-        <v>3.05679065692195</v>
+        <v>3.041726796796012</v>
       </c>
       <c r="I11">
-        <v>0.6413405721605206</v>
+        <v>0.6402831821731972</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -1066,19 +1066,19 @@
         <v>212</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>-46.11707686319162</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>-0.643900544614222</v>
       </c>
       <c r="P11">
-        <v>0.3085779817708779</v>
+        <v>0.1611391525933253</v>
       </c>
       <c r="Q11">
-        <v>0.7639427020853627</v>
+        <v>1.080979824541622</v>
       </c>
       <c r="R11" t="b">
         <v>1</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -600,13 +600,13 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>0.9434522607322694</v>
+        <v>0.9314110951776342</v>
       </c>
       <c r="H3">
         <v>1.833657130966953</v>
       </c>
       <c r="I3">
-        <v>0.4250609350156714</v>
+        <v>0.4258658878813403</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -618,19 +618,19 @@
         <v>225</v>
       </c>
       <c r="M3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N3">
-        <v>-0.009056949195109902</v>
+        <v>-0.01108094183180856</v>
       </c>
       <c r="O3">
-        <v>-2.857403689724818</v>
+        <v>-3.541853553546119</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>0.9434522607322694</v>
+        <v>0.9314110951776342</v>
       </c>
       <c r="R3" t="b">
         <v>1</v>
@@ -712,13 +712,13 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>0.7956531118044045</v>
+        <v>0.7896533135781629</v>
       </c>
       <c r="H5">
-        <v>1.416256840375411</v>
+        <v>1.405491229875892</v>
       </c>
       <c r="I5">
-        <v>0.2975245404191426</v>
+        <v>0.2971340718561979</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -733,16 +733,16 @@
         <v>5</v>
       </c>
       <c r="N5">
-        <v>-0.01153941049166994</v>
+        <v>-0.01174166127843149</v>
       </c>
       <c r="O5">
-        <v>-3.209849928141791</v>
+        <v>-3.278812364576415</v>
       </c>
       <c r="P5">
-        <v>0.03183319849094737</v>
+        <v>0.01883175367688475</v>
       </c>
       <c r="Q5">
-        <v>0.8218140826190732</v>
+        <v>0.8048092837669318</v>
       </c>
       <c r="R5" t="b">
         <v>1</v>
@@ -821,16 +821,16 @@
         <v>1</v>
       </c>
       <c r="F7">
-        <v>0.6399191648840915</v>
+        <v>0.6097911851613146</v>
       </c>
       <c r="G7">
-        <v>1.427668953276874</v>
+        <v>1.409173571297483</v>
       </c>
       <c r="H7">
         <v>1.341664228050781</v>
       </c>
       <c r="I7">
-        <v>0.3073371875015805</v>
+        <v>0.3074442777328218</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -839,22 +839,22 @@
         <v>1</v>
       </c>
       <c r="L7">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="M7">
         <v>8</v>
       </c>
       <c r="N7">
-        <v>-0.0275464658356021</v>
+        <v>-0.02921425304977012</v>
       </c>
       <c r="O7">
-        <v>-6.173371565526299</v>
+        <v>-6.579257503366526</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>1.427668953276874</v>
+        <v>1.409173571297483</v>
       </c>
       <c r="R7" t="b">
         <v>1</v>
@@ -877,16 +877,16 @@
         <v>1</v>
       </c>
       <c r="F8">
-        <v>0.05640024919461578</v>
+        <v>0.07942345260201844</v>
       </c>
       <c r="G8">
-        <v>1.115643117315203</v>
+        <v>1.127869704282327</v>
       </c>
       <c r="H8">
-        <v>1.431100415098159</v>
+        <v>1.424197387710586</v>
       </c>
       <c r="I8">
-        <v>0.3555652333102337</v>
+        <v>0.3522874554722269</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -901,16 +901,16 @@
         <v>49</v>
       </c>
       <c r="N8">
-        <v>-0.2790888128874402</v>
+        <v>-0.275114874201946</v>
       </c>
       <c r="O8">
-        <v>-72.20259411298488</v>
+        <v>-70.71063408898935</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>1.115643117315203</v>
+        <v>1.127869704282327</v>
       </c>
       <c r="R8" t="b">
         <v>1</v>
@@ -933,16 +933,16 @@
         <v>-1</v>
       </c>
       <c r="F9">
-        <v>0.4174537540470262</v>
+        <v>0.345520025502779</v>
       </c>
       <c r="G9">
-        <v>2.837624712178707</v>
+        <v>2.75073626477636</v>
       </c>
       <c r="H9">
         <v>2.937333350366403</v>
       </c>
       <c r="I9">
-        <v>0.6039562250020385</v>
+        <v>0.603952344623799</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -957,16 +957,16 @@
         <v>20</v>
       </c>
       <c r="N9">
-        <v>0.2383922357658709</v>
+        <v>0.2437951000190981</v>
       </c>
       <c r="O9">
-        <v>31.20463092629761</v>
+        <v>31.13318799842509</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>2.837624712178707</v>
+        <v>2.75073626477636</v>
       </c>
       <c r="R9" t="b">
         <v>1</v>
@@ -992,13 +992,13 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>1.260122004711455</v>
+        <v>1.049236856438738</v>
       </c>
       <c r="H10">
-        <v>2.0369740213745</v>
+        <v>2.032837451923748</v>
       </c>
       <c r="I10">
-        <v>0.4692876252201308</v>
+        <v>0.4643221970410293</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1010,19 +1010,19 @@
         <v>233</v>
       </c>
       <c r="M10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N10">
-        <v>6.75028365738441</v>
+        <v>7.770587117426889</v>
       </c>
       <c r="O10">
-        <v>6.984514334531778</v>
+        <v>6.923453168966899</v>
       </c>
       <c r="P10">
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>1.260122004711455</v>
+        <v>1.049236856438738</v>
       </c>
       <c r="R10" t="b">
         <v>1</v>
@@ -1048,13 +1048,13 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>0.9067916516445035</v>
+        <v>0.9155470572889849</v>
       </c>
       <c r="H11">
         <v>3.041726796796012</v>
       </c>
       <c r="I11">
-        <v>0.6402831821731972</v>
+        <v>0.6403159703953725</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -1069,16 +1069,16 @@
         <v>1</v>
       </c>
       <c r="N11">
-        <v>-46.11707686319162</v>
+        <v>-46.25704704194525</v>
       </c>
       <c r="O11">
-        <v>-0.643900544614222</v>
+        <v>-0.651665048489808</v>
       </c>
       <c r="P11">
-        <v>0.1611391525933253</v>
+        <v>0.1591480894186804</v>
       </c>
       <c r="Q11">
-        <v>1.080979824541622</v>
+        <v>1.088832701415907</v>
       </c>
       <c r="R11" t="b">
         <v>1</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -529,10 +529,10 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
+        <v>46248</v>
+      </c>
+      <c r="C2" s="2">
         <v>46247</v>
-      </c>
-      <c r="C2" s="2">
-        <v>46246</v>
       </c>
       <c r="D2" t="s">
         <v>28</v>
@@ -544,13 +544,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>0.04026990801319719</v>
+        <v>0.03606032892802228</v>
       </c>
       <c r="H2">
-        <v>1.062335249321869</v>
+        <v>1.063362472584557</v>
       </c>
       <c r="I2">
-        <v>0.2575515300889112</v>
+        <v>0.2578384663348035</v>
       </c>
       <c r="J2">
         <v>6</v>
@@ -562,19 +562,19 @@
         <v>149</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N2">
-        <v>-0.003508405804337893</v>
+        <v>-0.007837329136273228</v>
       </c>
       <c r="O2">
-        <v>-0.08960300866652746</v>
+        <v>-0.2042338766804871</v>
       </c>
       <c r="P2">
-        <v>0.6368591969603571</v>
+        <v>0.6700546023192776</v>
       </c>
       <c r="Q2">
-        <v>0.1108933715961438</v>
+        <v>0.1092918076187767</v>
       </c>
       <c r="R2" t="b">
         <v>1</v>
@@ -585,10 +585,10 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
+        <v>46248</v>
+      </c>
+      <c r="C3" s="2">
         <v>46247</v>
-      </c>
-      <c r="C3" s="2">
-        <v>46246</v>
       </c>
       <c r="D3" t="s">
         <v>28</v>
@@ -600,13 +600,13 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>0.9314110951776342</v>
+        <v>1.100029119360665</v>
       </c>
       <c r="H3">
-        <v>1.833657130966953</v>
+        <v>1.834165654734896</v>
       </c>
       <c r="I3">
-        <v>0.4258658878813403</v>
+        <v>0.4253801929659285</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -618,19 +618,19 @@
         <v>225</v>
       </c>
       <c r="M3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N3">
-        <v>-0.01108094183180856</v>
+        <v>-0.0136279248941097</v>
       </c>
       <c r="O3">
-        <v>-3.541853553546119</v>
+        <v>-4.400160251788182</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>0.9314110951776342</v>
+        <v>1.100029119360665</v>
       </c>
       <c r="R3" t="b">
         <v>1</v>
@@ -641,10 +641,10 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
+        <v>46248</v>
+      </c>
+      <c r="C4" s="2">
         <v>46247</v>
-      </c>
-      <c r="C4" s="2">
-        <v>46246</v>
       </c>
       <c r="D4" t="s">
         <v>28</v>
@@ -656,13 +656,13 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>0.1041141052377663</v>
+        <v>0.1340006740962105</v>
       </c>
       <c r="H4">
-        <v>2.065392978517953</v>
+        <v>2.06689982415916</v>
       </c>
       <c r="I4">
-        <v>0.4959064210793445</v>
+        <v>0.4963691091850378</v>
       </c>
       <c r="J4">
         <v>2</v>
@@ -674,19 +674,19 @@
         <v>146</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>0.001435089976197346</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>0.04418574811252009</v>
       </c>
       <c r="P4">
-        <v>0.3575676991466065</v>
+        <v>0.2801731778496122</v>
       </c>
       <c r="Q4">
-        <v>0.1620623762215309</v>
+        <v>0.1861568226867417</v>
       </c>
       <c r="R4" t="b">
         <v>1</v>
@@ -697,10 +697,10 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
+        <v>46248</v>
+      </c>
+      <c r="C5" s="2">
         <v>46247</v>
-      </c>
-      <c r="C5" s="2">
-        <v>46246</v>
       </c>
       <c r="D5" t="s">
         <v>28</v>
@@ -712,13 +712,13 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>0.7896533135781629</v>
+        <v>0.9511767222416696</v>
       </c>
       <c r="H5">
-        <v>1.405491229875892</v>
+        <v>1.40798853365884</v>
       </c>
       <c r="I5">
-        <v>0.2971340718561979</v>
+        <v>0.2974176591918677</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -730,19 +730,19 @@
         <v>226</v>
       </c>
       <c r="M5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N5">
-        <v>-0.01174166127843149</v>
+        <v>-0.01456937817210849</v>
       </c>
       <c r="O5">
-        <v>-3.278812364576415</v>
+        <v>-3.938430090934857</v>
       </c>
       <c r="P5">
-        <v>0.01883175367688475</v>
+        <v>0</v>
       </c>
       <c r="Q5">
-        <v>0.8048092837669318</v>
+        <v>0.9511767222416696</v>
       </c>
       <c r="R5" t="b">
         <v>1</v>
@@ -753,10 +753,10 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
+        <v>46248</v>
+      </c>
+      <c r="C6" s="2">
         <v>46247</v>
-      </c>
-      <c r="C6" s="2">
-        <v>46246</v>
       </c>
       <c r="D6" t="s">
         <v>28</v>
@@ -768,13 +768,13 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0.1693278678201049</v>
+        <v>0.1591156185073573</v>
       </c>
       <c r="H6">
-        <v>0.9426739203812891</v>
+        <v>0.9427453491199904</v>
       </c>
       <c r="I6">
-        <v>0.2579003967070224</v>
+        <v>0.2579827945830537</v>
       </c>
       <c r="J6">
         <v>6</v>
@@ -786,19 +786,19 @@
         <v>158</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N6">
-        <v>-0.02503253973589563</v>
+        <v>-0.03598230761381923</v>
       </c>
       <c r="O6">
-        <v>-0.4118839248554855</v>
+        <v>-0.5986859353641643</v>
       </c>
       <c r="P6">
-        <v>0.2091853437502047</v>
+        <v>0.2021116417192947</v>
       </c>
       <c r="Q6">
-        <v>0.2141182721917323</v>
+        <v>0.1994209050126018</v>
       </c>
       <c r="R6" t="b">
         <v>1</v>
@@ -809,10 +809,10 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
+        <v>46248</v>
+      </c>
+      <c r="C7" s="2">
         <v>46247</v>
-      </c>
-      <c r="C7" s="2">
-        <v>46246</v>
       </c>
       <c r="D7" t="s">
         <v>28</v>
@@ -821,16 +821,16 @@
         <v>1</v>
       </c>
       <c r="F7">
-        <v>0.6097911851613146</v>
+        <v>0.7766741168202351</v>
       </c>
       <c r="G7">
-        <v>1.409173571297483</v>
+        <v>1.512876196419543</v>
       </c>
       <c r="H7">
-        <v>1.341664228050781</v>
+        <v>1.342750646427247</v>
       </c>
       <c r="I7">
-        <v>0.3074442777328218</v>
+        <v>0.3074475342101342</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -842,19 +842,19 @@
         <v>239</v>
       </c>
       <c r="M7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N7">
-        <v>-0.02921425304977012</v>
+        <v>-0.03443591706752606</v>
       </c>
       <c r="O7">
-        <v>-6.579257503366526</v>
+        <v>-7.395916835857397</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>1.409173571297483</v>
+        <v>1.512876196419543</v>
       </c>
       <c r="R7" t="b">
         <v>1</v>
@@ -865,10 +865,10 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
+        <v>46248</v>
+      </c>
+      <c r="C8" s="2">
         <v>46247</v>
-      </c>
-      <c r="C8" s="2">
-        <v>46246</v>
       </c>
       <c r="D8" t="s">
         <v>28</v>
@@ -877,16 +877,16 @@
         <v>1</v>
       </c>
       <c r="F8">
-        <v>0.07942345260201844</v>
+        <v>0.02359176027187941</v>
       </c>
       <c r="G8">
-        <v>1.127869704282327</v>
+        <v>1.09008008248575</v>
       </c>
       <c r="H8">
-        <v>1.424197387710586</v>
+        <v>1.425745744212559</v>
       </c>
       <c r="I8">
-        <v>0.3522874554722269</v>
+        <v>0.352287842374818</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -898,19 +898,19 @@
         <v>111</v>
       </c>
       <c r="M8">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N8">
-        <v>-0.275114874201946</v>
+        <v>-0.2781896367074291</v>
       </c>
       <c r="O8">
-        <v>-70.71063408898935</v>
+        <v>-71.55346158192205</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>1.127869704282327</v>
+        <v>1.09008008248575</v>
       </c>
       <c r="R8" t="b">
         <v>1</v>
@@ -921,10 +921,10 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
+        <v>46248</v>
+      </c>
+      <c r="C9" s="2">
         <v>46247</v>
-      </c>
-      <c r="C9" s="2">
-        <v>46246</v>
       </c>
       <c r="D9" t="s">
         <v>29</v>
@@ -933,16 +933,16 @@
         <v>-1</v>
       </c>
       <c r="F9">
-        <v>0.345520025502779</v>
+        <v>0.443677755568377</v>
       </c>
       <c r="G9">
-        <v>2.75073626477636</v>
+        <v>2.86943970494218</v>
       </c>
       <c r="H9">
-        <v>2.937333350366403</v>
+        <v>2.937333569928541</v>
       </c>
       <c r="I9">
-        <v>0.603952344623799</v>
+        <v>0.6027269125326258</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -954,19 +954,19 @@
         <v>76</v>
       </c>
       <c r="M9">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N9">
-        <v>0.2437951000190981</v>
+        <v>0.2601434254180223</v>
       </c>
       <c r="O9">
-        <v>31.13318799842509</v>
+        <v>34.42839680344389</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>2.75073626477636</v>
+        <v>2.86943970494218</v>
       </c>
       <c r="R9" t="b">
         <v>1</v>
@@ -977,10 +977,10 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
+        <v>46248</v>
+      </c>
+      <c r="C10" s="2">
         <v>46247</v>
-      </c>
-      <c r="C10" s="2">
-        <v>46246</v>
       </c>
       <c r="D10" t="s">
         <v>29</v>
@@ -992,13 +992,13 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>1.049236856438738</v>
+        <v>0.9972536718580639</v>
       </c>
       <c r="H10">
-        <v>2.032837451923748</v>
+        <v>2.034345945562265</v>
       </c>
       <c r="I10">
-        <v>0.4643221970410293</v>
+        <v>0.4647581807379077</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1010,19 +1010,19 @@
         <v>233</v>
       </c>
       <c r="M10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N10">
-        <v>7.770587117426889</v>
+        <v>8.793993046324708</v>
       </c>
       <c r="O10">
-        <v>6.923453168966899</v>
+        <v>7.700760134389119</v>
       </c>
       <c r="P10">
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>1.049236856438738</v>
+        <v>0.9972536718580639</v>
       </c>
       <c r="R10" t="b">
         <v>1</v>
@@ -1033,10 +1033,10 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
+        <v>46248</v>
+      </c>
+      <c r="C11" s="2">
         <v>46247</v>
-      </c>
-      <c r="C11" s="2">
-        <v>46246</v>
       </c>
       <c r="D11" t="s">
         <v>28</v>
@@ -1048,13 +1048,13 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>0.9155470572889849</v>
+        <v>1.055356092603474</v>
       </c>
       <c r="H11">
-        <v>3.041726796796012</v>
+        <v>3.026679216217086</v>
       </c>
       <c r="I11">
-        <v>0.6403159703953725</v>
+        <v>0.6392292742249845</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -1066,19 +1066,19 @@
         <v>212</v>
       </c>
       <c r="M11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N11">
-        <v>-46.25704704194525</v>
+        <v>-106.6374106038581</v>
       </c>
       <c r="O11">
-        <v>-0.651665048489808</v>
+        <v>-1.464081345939012</v>
       </c>
       <c r="P11">
-        <v>0.1591480894186804</v>
+        <v>0.08612987865545507</v>
       </c>
       <c r="Q11">
-        <v>1.088832701415907</v>
+        <v>1.154820655533377</v>
       </c>
       <c r="R11" t="b">
         <v>1</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -529,10 +529,10 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
+        <v>46249</v>
+      </c>
+      <c r="C2" s="2">
         <v>46248</v>
-      </c>
-      <c r="C2" s="2">
-        <v>46247</v>
       </c>
       <c r="D2" t="s">
         <v>28</v>
@@ -544,13 +544,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>0.03606032892802228</v>
+        <v>0.1333810274471401</v>
       </c>
       <c r="H2">
-        <v>1.063362472584557</v>
+        <v>1.064291865060322</v>
       </c>
       <c r="I2">
-        <v>0.2578384663348035</v>
+        <v>0.2581291505421104</v>
       </c>
       <c r="J2">
         <v>6</v>
@@ -562,19 +562,19 @@
         <v>149</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N2">
-        <v>-0.007837329136273228</v>
+        <v>-0.01358485660878048</v>
       </c>
       <c r="O2">
-        <v>-0.2042338766804871</v>
+        <v>-0.3476165969493462</v>
       </c>
       <c r="P2">
-        <v>0.6700546023192776</v>
+        <v>0.341876991768257</v>
       </c>
       <c r="Q2">
-        <v>0.1092918076187767</v>
+        <v>0.2026688412026662</v>
       </c>
       <c r="R2" t="b">
         <v>1</v>
@@ -585,7 +585,7 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="C3" s="2">
         <v>46247</v>
@@ -641,10 +641,10 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
+        <v>46249</v>
+      </c>
+      <c r="C4" s="2">
         <v>46248</v>
-      </c>
-      <c r="C4" s="2">
-        <v>46247</v>
       </c>
       <c r="D4" t="s">
         <v>28</v>
@@ -656,37 +656,37 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>0.1340006740962105</v>
+        <v>0.006680900891693144</v>
       </c>
       <c r="H4">
-        <v>2.06689982415916</v>
+        <v>2.068263160691681</v>
       </c>
       <c r="I4">
-        <v>0.4963691091850378</v>
+        <v>0.4967974896645426</v>
       </c>
       <c r="J4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K4">
-        <v>0.3333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L4">
         <v>146</v>
       </c>
       <c r="M4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N4">
-        <v>0.001435089976197346</v>
+        <v>0.00116994829972092</v>
       </c>
       <c r="O4">
-        <v>0.04418574811252009</v>
+        <v>0.0358722649936332</v>
       </c>
       <c r="P4">
-        <v>0.2801731778496122</v>
+        <v>0.5376255920597124</v>
       </c>
       <c r="Q4">
-        <v>0.1861568226867417</v>
+        <v>0.01444911478006355</v>
       </c>
       <c r="R4" t="b">
         <v>1</v>
@@ -697,7 +697,7 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="C5" s="2">
         <v>46247</v>
@@ -753,10 +753,10 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
+        <v>46249</v>
+      </c>
+      <c r="C6" s="2">
         <v>46248</v>
-      </c>
-      <c r="C6" s="2">
-        <v>46247</v>
       </c>
       <c r="D6" t="s">
         <v>28</v>
@@ -768,13 +768,13 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0.1591156185073573</v>
+        <v>0.2890510674624616</v>
       </c>
       <c r="H6">
-        <v>0.9427453491199904</v>
+        <v>0.9428099751216726</v>
       </c>
       <c r="I6">
-        <v>0.2579827945830537</v>
+        <v>0.258010567460834</v>
       </c>
       <c r="J6">
         <v>6</v>
@@ -786,19 +786,19 @@
         <v>158</v>
       </c>
       <c r="M6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N6">
-        <v>-0.03598230761381923</v>
+        <v>-0.04872516928208408</v>
       </c>
       <c r="O6">
-        <v>-0.5986859353641643</v>
+        <v>-0.8155522517714283</v>
       </c>
       <c r="P6">
-        <v>0.2021116417192947</v>
+        <v>0.01962168313927069</v>
       </c>
       <c r="Q6">
-        <v>0.1994209050126018</v>
+        <v>0.2948362509567045</v>
       </c>
       <c r="R6" t="b">
         <v>1</v>
@@ -809,7 +809,7 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="C7" s="2">
         <v>46247</v>
@@ -865,7 +865,7 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="C8" s="2">
         <v>46247</v>
@@ -921,7 +921,7 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="C9" s="2">
         <v>46247</v>
@@ -977,7 +977,7 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="C10" s="2">
         <v>46247</v>
@@ -1033,7 +1033,7 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="C11" s="2">
         <v>46247</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -529,7 +529,7 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>46249</v>
+        <v>46251</v>
       </c>
       <c r="C2" s="2">
         <v>46248</v>
@@ -585,10 +585,10 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>46249</v>
+        <v>46251</v>
       </c>
       <c r="C3" s="2">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="D3" t="s">
         <v>28</v>
@@ -600,13 +600,13 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>1.100029119360665</v>
+        <v>1.224029802435517</v>
       </c>
       <c r="H3">
-        <v>1.834165654734896</v>
+        <v>1.834625747667796</v>
       </c>
       <c r="I3">
-        <v>0.4253801929659285</v>
+        <v>0.4247962474671874</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -618,19 +618,19 @@
         <v>225</v>
       </c>
       <c r="M3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N3">
-        <v>-0.0136279248941097</v>
+        <v>-0.01645983772656203</v>
       </c>
       <c r="O3">
-        <v>-4.400160251788182</v>
+        <v>-5.491842902094101</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>1.100029119360665</v>
+        <v>1.224029802435517</v>
       </c>
       <c r="R3" t="b">
         <v>1</v>
@@ -641,7 +641,7 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>46249</v>
+        <v>46251</v>
       </c>
       <c r="C4" s="2">
         <v>46248</v>
@@ -697,10 +697,10 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
-        <v>46249</v>
+        <v>46251</v>
       </c>
       <c r="C5" s="2">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="D5" t="s">
         <v>28</v>
@@ -709,16 +709,16 @@
         <v>1</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>0.006484736928676851</v>
       </c>
       <c r="G5">
-        <v>0.9511767222416696</v>
+        <v>1.116455385346934</v>
       </c>
       <c r="H5">
-        <v>1.40798853365884</v>
+        <v>1.41024799898627</v>
       </c>
       <c r="I5">
-        <v>0.2974176591918677</v>
+        <v>0.2976530166574365</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -730,19 +730,19 @@
         <v>226</v>
       </c>
       <c r="M5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N5">
-        <v>-0.01456937817210849</v>
+        <v>-0.01775813670407353</v>
       </c>
       <c r="O5">
-        <v>-3.938430090934857</v>
+        <v>-5.047998250904079</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>0.9511767222416696</v>
+        <v>1.116455385346934</v>
       </c>
       <c r="R5" t="b">
         <v>1</v>
@@ -753,7 +753,7 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>46249</v>
+        <v>46251</v>
       </c>
       <c r="C6" s="2">
         <v>46248</v>
@@ -809,10 +809,10 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
-        <v>46249</v>
+        <v>46251</v>
       </c>
       <c r="C7" s="2">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="D7" t="s">
         <v>28</v>
@@ -821,16 +821,16 @@
         <v>1</v>
       </c>
       <c r="F7">
-        <v>0.7766741168202351</v>
+        <v>1</v>
       </c>
       <c r="G7">
-        <v>1.512876196419543</v>
+        <v>1.764165814666598</v>
       </c>
       <c r="H7">
-        <v>1.342750646427247</v>
+        <v>1.34473744242276</v>
       </c>
       <c r="I7">
-        <v>0.3074475342101342</v>
+        <v>0.3076352847147892</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -842,19 +842,19 @@
         <v>239</v>
       </c>
       <c r="M7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N7">
-        <v>-0.03443591706752606</v>
+        <v>-0.04010628421231605</v>
       </c>
       <c r="O7">
-        <v>-7.395916835857397</v>
+        <v>-9.458232611343782</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>1.512876196419543</v>
+        <v>1.764165814666598</v>
       </c>
       <c r="R7" t="b">
         <v>1</v>
@@ -865,10 +865,10 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
-        <v>46249</v>
+        <v>46251</v>
       </c>
       <c r="C8" s="2">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="D8" t="s">
         <v>28</v>
@@ -877,16 +877,16 @@
         <v>1</v>
       </c>
       <c r="F8">
-        <v>0.02359176027187941</v>
+        <v>0.1290340153162315</v>
       </c>
       <c r="G8">
-        <v>1.09008008248575</v>
+        <v>1.165785178737804</v>
       </c>
       <c r="H8">
-        <v>1.425745744212559</v>
+        <v>1.427146638190534</v>
       </c>
       <c r="I8">
-        <v>0.352287842374818</v>
+        <v>0.352271461863988</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -898,19 +898,19 @@
         <v>111</v>
       </c>
       <c r="M8">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N8">
-        <v>-0.2781896367074291</v>
+        <v>-0.2812890922387525</v>
       </c>
       <c r="O8">
-        <v>-71.55346158192205</v>
+        <v>-73.52590163074227</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>1.09008008248575</v>
+        <v>1.165785178737804</v>
       </c>
       <c r="R8" t="b">
         <v>1</v>
@@ -921,10 +921,10 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
-        <v>46249</v>
+        <v>46251</v>
       </c>
       <c r="C9" s="2">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="D9" t="s">
         <v>29</v>
@@ -933,16 +933,16 @@
         <v>-1</v>
       </c>
       <c r="F9">
-        <v>0.443677755568377</v>
+        <v>0.5406137321372756</v>
       </c>
       <c r="G9">
-        <v>2.86943970494218</v>
+        <v>2.986639488171212</v>
       </c>
       <c r="H9">
-        <v>2.937333569928541</v>
+        <v>2.937762627882411</v>
       </c>
       <c r="I9">
-        <v>0.6027269125326258</v>
+        <v>0.601728254418916</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -954,19 +954,19 @@
         <v>76</v>
       </c>
       <c r="M9">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N9">
-        <v>0.2601434254180223</v>
+        <v>0.276449953336712</v>
       </c>
       <c r="O9">
-        <v>34.42839680344389</v>
+        <v>38.63731004007178</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>2.86943970494218</v>
+        <v>2.986639488171212</v>
       </c>
       <c r="R9" t="b">
         <v>1</v>
@@ -977,10 +977,10 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>46249</v>
+        <v>46251</v>
       </c>
       <c r="C10" s="2">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="D10" t="s">
         <v>29</v>
@@ -992,13 +992,13 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>0.9972536718580639</v>
+        <v>0.9128855372395723</v>
       </c>
       <c r="H10">
-        <v>2.034345945562265</v>
+        <v>2.035710773139972</v>
       </c>
       <c r="I10">
-        <v>0.4647581807379077</v>
+        <v>0.4650405391502617</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1010,19 +1010,19 @@
         <v>233</v>
       </c>
       <c r="M10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N10">
-        <v>8.793993046324708</v>
+        <v>9.768143742156555</v>
       </c>
       <c r="O10">
-        <v>7.700760134389119</v>
+        <v>8.518906895296318</v>
       </c>
       <c r="P10">
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>0.9972536718580639</v>
+        <v>0.9128855372395723</v>
       </c>
       <c r="R10" t="b">
         <v>1</v>
@@ -1033,10 +1033,10 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>46249</v>
+        <v>46251</v>
       </c>
       <c r="C11" s="2">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="D11" t="s">
         <v>28</v>
@@ -1048,13 +1048,13 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>1.055356092603474</v>
+        <v>1.270338028212634</v>
       </c>
       <c r="H11">
-        <v>3.026679216217086</v>
+        <v>2.999797596763484</v>
       </c>
       <c r="I11">
-        <v>0.6392292742249845</v>
+        <v>0.6380522174341341</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -1066,19 +1066,19 @@
         <v>212</v>
       </c>
       <c r="M11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N11">
-        <v>-106.6374106038581</v>
+        <v>-174.7979408232121</v>
       </c>
       <c r="O11">
-        <v>-1.464081345939012</v>
+        <v>-2.526946884674131</v>
       </c>
       <c r="P11">
-        <v>0.08612987865545507</v>
+        <v>0.01282747127268308</v>
       </c>
       <c r="Q11">
-        <v>1.154820655533377</v>
+        <v>1.286844995423829</v>
       </c>
       <c r="R11" t="b">
         <v>1</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -529,10 +529,10 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
+        <v>46252</v>
+      </c>
+      <c r="C2" s="2">
         <v>46251</v>
-      </c>
-      <c r="C2" s="2">
-        <v>46248</v>
       </c>
       <c r="D2" t="s">
         <v>28</v>
@@ -544,13 +544,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>0.1333810274471401</v>
+        <v>0.2815296005162526</v>
       </c>
       <c r="H2">
-        <v>1.064291865060322</v>
+        <v>1.065132743966966</v>
       </c>
       <c r="I2">
-        <v>0.2581291505421104</v>
+        <v>0.2583860977023259</v>
       </c>
       <c r="J2">
         <v>6</v>
@@ -562,19 +562,19 @@
         <v>149</v>
       </c>
       <c r="M2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N2">
-        <v>-0.01358485660878048</v>
+        <v>-0.02232959519049364</v>
       </c>
       <c r="O2">
-        <v>-0.3476165969493462</v>
+        <v>-0.5541530013771828</v>
       </c>
       <c r="P2">
-        <v>0.341876991768257</v>
+        <v>0.1233139881281631</v>
       </c>
       <c r="Q2">
-        <v>0.2026688412026662</v>
+        <v>0.3211293401558339</v>
       </c>
       <c r="R2" t="b">
         <v>1</v>
@@ -585,10 +585,10 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
+        <v>46252</v>
+      </c>
+      <c r="C3" s="2">
         <v>46251</v>
-      </c>
-      <c r="C3" s="2">
-        <v>46248</v>
       </c>
       <c r="D3" t="s">
         <v>28</v>
@@ -597,16 +597,16 @@
         <v>1</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>0.006645056466970206</v>
       </c>
       <c r="G3">
-        <v>1.224029802435517</v>
+        <v>1.41741649865742</v>
       </c>
       <c r="H3">
-        <v>1.834625747667796</v>
+        <v>1.835042022226135</v>
       </c>
       <c r="I3">
-        <v>0.4247962474671874</v>
+        <v>0.4232505714628106</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -618,19 +618,19 @@
         <v>225</v>
       </c>
       <c r="M3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N3">
-        <v>-0.01645983772656203</v>
+        <v>-0.01779943959706105</v>
       </c>
       <c r="O3">
-        <v>-5.491842902094101</v>
+        <v>-5.631461115454356</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>1.224029802435517</v>
+        <v>1.41741649865742</v>
       </c>
       <c r="R3" t="b">
         <v>1</v>
@@ -641,10 +641,10 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
+        <v>46252</v>
+      </c>
+      <c r="C4" s="2">
         <v>46251</v>
-      </c>
-      <c r="C4" s="2">
-        <v>46248</v>
       </c>
       <c r="D4" t="s">
         <v>28</v>
@@ -656,37 +656,37 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>0.006680900891693144</v>
+        <v>0.03220786753094879</v>
       </c>
       <c r="H4">
-        <v>2.068263160691681</v>
+        <v>2.069496655649676</v>
       </c>
       <c r="I4">
-        <v>0.4967974896645426</v>
+        <v>0.497176761094907</v>
       </c>
       <c r="J4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K4">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="L4">
         <v>146</v>
       </c>
       <c r="M4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N4">
-        <v>0.00116994829972092</v>
+        <v>-0.002406565180206961</v>
       </c>
       <c r="O4">
-        <v>0.0358722649936332</v>
+        <v>-0.07411331395270035</v>
       </c>
       <c r="P4">
-        <v>0.5376255920597124</v>
+        <v>0.7311785995654304</v>
       </c>
       <c r="Q4">
-        <v>0.01444911478006355</v>
+        <v>0.1198113970051581</v>
       </c>
       <c r="R4" t="b">
         <v>1</v>
@@ -697,10 +697,10 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
+        <v>46252</v>
+      </c>
+      <c r="C5" s="2">
         <v>46251</v>
-      </c>
-      <c r="C5" s="2">
-        <v>46248</v>
       </c>
       <c r="D5" t="s">
         <v>28</v>
@@ -709,16 +709,16 @@
         <v>1</v>
       </c>
       <c r="F5">
-        <v>0.006484736928676851</v>
+        <v>0.2206760510344554</v>
       </c>
       <c r="G5">
-        <v>1.116455385346934</v>
+        <v>1.257784563326133</v>
       </c>
       <c r="H5">
-        <v>1.41024799898627</v>
+        <v>1.424449193406427</v>
       </c>
       <c r="I5">
-        <v>0.2976530166574365</v>
+        <v>0.2983357329321816</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -730,19 +730,19 @@
         <v>226</v>
       </c>
       <c r="M5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N5">
-        <v>-0.01775813670407353</v>
+        <v>-0.02121174033489852</v>
       </c>
       <c r="O5">
-        <v>-5.047998250904079</v>
+        <v>-6.048154066977075</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>1.116455385346934</v>
+        <v>1.257784563326133</v>
       </c>
       <c r="R5" t="b">
         <v>1</v>
@@ -753,10 +753,10 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
+        <v>46252</v>
+      </c>
+      <c r="C6" s="2">
         <v>46251</v>
-      </c>
-      <c r="C6" s="2">
-        <v>46248</v>
       </c>
       <c r="D6" t="s">
         <v>28</v>
@@ -768,13 +768,13 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0.2890510674624616</v>
+        <v>0.3703547186083788</v>
       </c>
       <c r="H6">
-        <v>0.9428099751216726</v>
+        <v>0.9428684462660518</v>
       </c>
       <c r="I6">
-        <v>0.258010567460834</v>
+        <v>0.2580029007897943</v>
       </c>
       <c r="J6">
         <v>6</v>
@@ -786,19 +786,19 @@
         <v>158</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N6">
-        <v>-0.04872516928208408</v>
+        <v>-0.06497021475765166</v>
       </c>
       <c r="O6">
-        <v>-0.8155522517714283</v>
+        <v>-1.085706279222611</v>
       </c>
       <c r="P6">
-        <v>0.01962168313927069</v>
+        <v>0</v>
       </c>
       <c r="Q6">
-        <v>0.2948362509567045</v>
+        <v>0.3703547186083788</v>
       </c>
       <c r="R6" t="b">
         <v>1</v>
@@ -809,10 +809,10 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
+        <v>46252</v>
+      </c>
+      <c r="C7" s="2">
         <v>46251</v>
-      </c>
-      <c r="C7" s="2">
-        <v>46248</v>
       </c>
       <c r="D7" t="s">
         <v>28</v>
@@ -824,13 +824,13 @@
         <v>1</v>
       </c>
       <c r="G7">
-        <v>1.764165814666598</v>
+        <v>1.737494928074045</v>
       </c>
       <c r="H7">
-        <v>1.34473744242276</v>
+        <v>1.349273300358433</v>
       </c>
       <c r="I7">
-        <v>0.3076352847147892</v>
+        <v>0.3079460610703557</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -839,22 +839,22 @@
         <v>1</v>
       </c>
       <c r="L7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N7">
-        <v>-0.04010628421231605</v>
+        <v>-0.04459166479556742</v>
       </c>
       <c r="O7">
-        <v>-9.458232611343782</v>
+        <v>-10.14023076647353</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>1.764165814666598</v>
+        <v>1.737494928074045</v>
       </c>
       <c r="R7" t="b">
         <v>1</v>
@@ -865,10 +865,10 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
+        <v>46252</v>
+      </c>
+      <c r="C8" s="2">
         <v>46251</v>
-      </c>
-      <c r="C8" s="2">
-        <v>46248</v>
       </c>
       <c r="D8" t="s">
         <v>28</v>
@@ -877,16 +877,16 @@
         <v>1</v>
       </c>
       <c r="F8">
-        <v>0.1290340153162315</v>
+        <v>0.0599653482459717</v>
       </c>
       <c r="G8">
-        <v>1.165785178737804</v>
+        <v>1.12320607582844</v>
       </c>
       <c r="H8">
-        <v>1.427146638190534</v>
+        <v>1.436542237791728</v>
       </c>
       <c r="I8">
-        <v>0.352271461863988</v>
+        <v>0.3560357811757486</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -898,19 +898,19 @@
         <v>111</v>
       </c>
       <c r="M8">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N8">
-        <v>-0.2812890922387525</v>
+        <v>-0.2882377495371427</v>
       </c>
       <c r="O8">
-        <v>-73.52590163074227</v>
+        <v>-76.11673099160684</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>1.165785178737804</v>
+        <v>1.12320607582844</v>
       </c>
       <c r="R8" t="b">
         <v>1</v>
@@ -921,10 +921,10 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
+        <v>46252</v>
+      </c>
+      <c r="C9" s="2">
         <v>46251</v>
-      </c>
-      <c r="C9" s="2">
-        <v>46248</v>
       </c>
       <c r="D9" t="s">
         <v>29</v>
@@ -933,16 +933,16 @@
         <v>-1</v>
       </c>
       <c r="F9">
-        <v>0.5406137321372756</v>
+        <v>0.5259359401337355</v>
       </c>
       <c r="G9">
-        <v>2.986639488171212</v>
+        <v>2.972216273968399</v>
       </c>
       <c r="H9">
-        <v>2.937762627882411</v>
+        <v>2.941026149708734</v>
       </c>
       <c r="I9">
-        <v>0.601728254418916</v>
+        <v>0.6012915687427639</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -954,19 +954,19 @@
         <v>76</v>
       </c>
       <c r="M9">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N9">
-        <v>0.276449953336712</v>
+        <v>0.2872794861215611</v>
       </c>
       <c r="O9">
-        <v>38.63731004007178</v>
+        <v>41.49724314591308</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>2.986639488171212</v>
+        <v>2.972216273968399</v>
       </c>
       <c r="R9" t="b">
         <v>1</v>
@@ -977,10 +977,10 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
+        <v>46252</v>
+      </c>
+      <c r="C10" s="2">
         <v>46251</v>
-      </c>
-      <c r="C10" s="2">
-        <v>46248</v>
       </c>
       <c r="D10" t="s">
         <v>29</v>
@@ -992,13 +992,13 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>0.9128855372395723</v>
+        <v>0.9408225092317056</v>
       </c>
       <c r="H10">
-        <v>2.035710773139972</v>
+        <v>2.041616780789691</v>
       </c>
       <c r="I10">
-        <v>0.4650405391502617</v>
+        <v>0.4707236940623677</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1013,16 +1013,16 @@
         <v>9</v>
       </c>
       <c r="N10">
-        <v>9.768143742156555</v>
+        <v>9.731366619828716</v>
       </c>
       <c r="O10">
-        <v>8.518906895296318</v>
+        <v>9.579800490637563</v>
       </c>
       <c r="P10">
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>0.9128855372395723</v>
+        <v>0.9408225092317056</v>
       </c>
       <c r="R10" t="b">
         <v>1</v>
@@ -1033,10 +1033,10 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
+        <v>46252</v>
+      </c>
+      <c r="C11" s="2">
         <v>46251</v>
-      </c>
-      <c r="C11" s="2">
-        <v>46248</v>
       </c>
       <c r="D11" t="s">
         <v>28</v>
@@ -1048,13 +1048,13 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>1.270338028212634</v>
+        <v>1.412807215284729</v>
       </c>
       <c r="H11">
-        <v>2.999797596763484</v>
+        <v>2.966377745487705</v>
       </c>
       <c r="I11">
-        <v>0.6380522174341341</v>
+        <v>0.6366632764781077</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -1066,19 +1066,19 @@
         <v>212</v>
       </c>
       <c r="M11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N11">
-        <v>-174.7979408232121</v>
+        <v>-249.8859563975202</v>
       </c>
       <c r="O11">
-        <v>-2.526946884674131</v>
+        <v>-3.673288662801249</v>
       </c>
       <c r="P11">
-        <v>0.01282747127268308</v>
+        <v>0</v>
       </c>
       <c r="Q11">
-        <v>1.286844995423829</v>
+        <v>1.412807215284729</v>
       </c>
       <c r="R11" t="b">
         <v>1</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="77">
   <si>
     <t>Pair</t>
   </si>
@@ -67,6 +67,90 @@
     <t>TerrainBundleSep</t>
   </si>
   <si>
+    <t>MarketPosture</t>
+  </si>
+  <si>
+    <t>MarketPostureCN</t>
+  </si>
+  <si>
+    <t>MarketPostureScore</t>
+  </si>
+  <si>
+    <t>MarketPostureConfidence</t>
+  </si>
+  <si>
+    <t>PhasedDirection</t>
+  </si>
+  <si>
+    <t>PhasedAlignment</t>
+  </si>
+  <si>
+    <t>PhasedRawCoherence</t>
+  </si>
+  <si>
+    <t>PhasedCoherence</t>
+  </si>
+  <si>
+    <t>PhasedSteeringGain</t>
+  </si>
+  <si>
+    <t>PhasedGate</t>
+  </si>
+  <si>
+    <t>PhasedBeamPhaseDeg</t>
+  </si>
+  <si>
+    <t>PhasedGradientDeg</t>
+  </si>
+  <si>
+    <t>PhasedDirectionScore</t>
+  </si>
+  <si>
+    <t>PhasedImpulseScore</t>
+  </si>
+  <si>
+    <t>PhasedAmplitude</t>
+  </si>
+  <si>
+    <t>PhasedPower</t>
+  </si>
+  <si>
+    <t>SurveyTrend</t>
+  </si>
+  <si>
+    <t>SurveyTrendCN</t>
+  </si>
+  <si>
+    <t>TerrainPattern</t>
+  </si>
+  <si>
+    <t>TerrainPatternCN</t>
+  </si>
+  <si>
+    <t>SurveyDirectionScore</t>
+  </si>
+  <si>
+    <t>SurveyConfidence</t>
+  </si>
+  <si>
+    <t>ContourElevation</t>
+  </si>
+  <si>
+    <t>ContourTemporalSlope</t>
+  </si>
+  <si>
+    <t>ContourScaleSlope</t>
+  </si>
+  <si>
+    <t>ContourCurvature</t>
+  </si>
+  <si>
+    <t>ContourRelief</t>
+  </si>
+  <si>
+    <t>ContourRoughness</t>
+  </si>
+  <si>
     <t>FilterEnabled</t>
   </si>
   <si>
@@ -104,6 +188,63 @@
   </si>
   <si>
     <t>DOWN</t>
+  </si>
+  <si>
+    <t>UP_ACCELERATING</t>
+  </si>
+  <si>
+    <t>UP_STEADY</t>
+  </si>
+  <si>
+    <t>DOWN_STEADY</t>
+  </si>
+  <si>
+    <t>DOWN_DECELERATING</t>
+  </si>
+  <si>
+    <t>多头加速</t>
+  </si>
+  <si>
+    <t>多头稳态</t>
+  </si>
+  <si>
+    <t>空头稳态</t>
+  </si>
+  <si>
+    <t>空头减速</t>
+  </si>
+  <si>
+    <t>ALIGNED</t>
+  </si>
+  <si>
+    <t>上涨</t>
+  </si>
+  <si>
+    <t>下跌</t>
+  </si>
+  <si>
+    <t>UP_STEEPENING</t>
+  </si>
+  <si>
+    <t>UP_SLOPE</t>
+  </si>
+  <si>
+    <t>DOWN_SLOPE</t>
+  </si>
+  <si>
+    <t>DOWN_VALLEY_FLATTENING</t>
+  </si>
+  <si>
+    <t>上升陡坡形成</t>
+  </si>
+  <si>
+    <t>上升坡延续</t>
+  </si>
+  <si>
+    <t>下降坡延续</t>
+  </si>
+  <si>
+    <t>下降谷底收敛</t>
   </si>
 </sst>
 </file>
@@ -465,10 +606,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:AT11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:46">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -523,10 +664,94 @@
       <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>45</v>
+      </c>
     </row>
-    <row r="2" spans="1:18">
+    <row r="2" spans="1:46">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="B2" s="2">
         <v>46252</v>
@@ -535,7 +760,7 @@
         <v>46251</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -576,13 +801,97 @@
       <c r="Q2">
         <v>0.3211293401558339</v>
       </c>
-      <c r="R2" t="b">
+      <c r="R2" t="s">
+        <v>58</v>
+      </c>
+      <c r="S2" t="s">
+        <v>62</v>
+      </c>
+      <c r="T2">
+        <v>0.821020732103893</v>
+      </c>
+      <c r="U2">
+        <v>0.7694260500042298</v>
+      </c>
+      <c r="V2" t="s">
+        <v>56</v>
+      </c>
+      <c r="W2" t="s">
+        <v>66</v>
+      </c>
+      <c r="X2">
+        <v>0.9995634808547292</v>
+      </c>
+      <c r="Y2">
+        <v>0.9998668822299118</v>
+      </c>
+      <c r="Z2">
+        <v>0.0003034013751825881</v>
+      </c>
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>61.58851833686625</v>
+      </c>
+      <c r="AC2">
+        <v>5.000000000000007</v>
+      </c>
+      <c r="AD2">
+        <v>0.4758004747819852</v>
+      </c>
+      <c r="AE2">
+        <v>0.8795532435260741</v>
+      </c>
+      <c r="AF2">
+        <v>0.5361635369822872</v>
+      </c>
+      <c r="AG2">
+        <v>0.5360921640878415</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>69</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AL2">
+        <v>0.2378685686418877</v>
+      </c>
+      <c r="AM2">
+        <v>0.6325810595956984</v>
+      </c>
+      <c r="AN2">
+        <v>0.2599542827254005</v>
+      </c>
+      <c r="AO2">
+        <v>0.4686621283756538</v>
+      </c>
+      <c r="AP2">
+        <v>0.3144538402450234</v>
+      </c>
+      <c r="AQ2">
+        <v>-0.3663977492770994</v>
+      </c>
+      <c r="AR2">
+        <v>0.280137922763026</v>
+      </c>
+      <c r="AS2">
+        <v>0.06741661079577493</v>
+      </c>
+      <c r="AT2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:18">
+    <row r="3" spans="1:46">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="B3" s="2">
         <v>46252</v>
@@ -591,22 +900,22 @@
         <v>46251</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3">
-        <v>0.006645056466970206</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>1.41741649865742</v>
+        <v>1.402135618629374</v>
       </c>
       <c r="H3">
         <v>1.835042022226135</v>
       </c>
       <c r="I3">
-        <v>0.4232505714628106</v>
+        <v>0.42412186553201</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -618,27 +927,111 @@
         <v>225</v>
       </c>
       <c r="M3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N3">
-        <v>-0.01779943959706105</v>
+        <v>-0.0196455291286302</v>
       </c>
       <c r="O3">
-        <v>-5.631461115454356</v>
+        <v>-6.297364803682275</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>1.41741649865742</v>
-      </c>
-      <c r="R3" t="b">
+        <v>1.402135618629374</v>
+      </c>
+      <c r="R3" t="s">
+        <v>58</v>
+      </c>
+      <c r="S3" t="s">
+        <v>62</v>
+      </c>
+      <c r="T3">
+        <v>0.8941983235748435</v>
+      </c>
+      <c r="U3">
+        <v>0.8023856606986273</v>
+      </c>
+      <c r="V3" t="s">
+        <v>56</v>
+      </c>
+      <c r="W3" t="s">
+        <v>66</v>
+      </c>
+      <c r="X3">
+        <v>0.9998570954730653</v>
+      </c>
+      <c r="Y3">
+        <v>0.9999856603597906</v>
+      </c>
+      <c r="Z3">
+        <v>0.000128564886725302</v>
+      </c>
+      <c r="AA3">
+        <v>0.2774543884003051</v>
+      </c>
+      <c r="AB3">
+        <v>40.57662685848407</v>
+      </c>
+      <c r="AC3">
+        <v>4.000000000000005</v>
+      </c>
+      <c r="AD3">
+        <v>0.7595367198632174</v>
+      </c>
+      <c r="AE3">
+        <v>0.6504644272974691</v>
+      </c>
+      <c r="AF3">
+        <v>1.437395510874701</v>
+      </c>
+      <c r="AG3">
+        <v>1.437374899140236</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>69</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>73</v>
+      </c>
+      <c r="AL3">
+        <v>0.4851298012836585</v>
+      </c>
+      <c r="AM3">
+        <v>0.7760299076337183</v>
+      </c>
+      <c r="AN3">
+        <v>1.099228157262111</v>
+      </c>
+      <c r="AO3">
+        <v>0.9258578958991305</v>
+      </c>
+      <c r="AP3">
+        <v>1.567559854865407</v>
+      </c>
+      <c r="AQ3">
+        <v>-1.647271930834391</v>
+      </c>
+      <c r="AR3">
+        <v>1.419288914767426</v>
+      </c>
+      <c r="AS3">
+        <v>0.04877978087489713</v>
+      </c>
+      <c r="AT3" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:18">
+    <row r="4" spans="1:46">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="B4" s="2">
         <v>46252</v>
@@ -647,7 +1040,7 @@
         <v>46251</v>
       </c>
       <c r="D4" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -688,13 +1081,97 @@
       <c r="Q4">
         <v>0.1198113970051581</v>
       </c>
-      <c r="R4" t="b">
+      <c r="R4" t="s">
+        <v>58</v>
+      </c>
+      <c r="S4" t="s">
+        <v>62</v>
+      </c>
+      <c r="T4">
+        <v>0.7289133392759884</v>
+      </c>
+      <c r="U4">
+        <v>0.7029458061879691</v>
+      </c>
+      <c r="V4" t="s">
+        <v>56</v>
+      </c>
+      <c r="W4" t="s">
+        <v>66</v>
+      </c>
+      <c r="X4">
+        <v>0.9925721813626439</v>
+      </c>
+      <c r="Y4">
+        <v>0.999739214055097</v>
+      </c>
+      <c r="Z4">
+        <v>0.007167032692453112</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>75.64483922883329</v>
+      </c>
+      <c r="AC4">
+        <v>28.00000000000001</v>
+      </c>
+      <c r="AD4">
+        <v>0.2479318054822442</v>
+      </c>
+      <c r="AE4">
+        <v>0.9687774872643948</v>
+      </c>
+      <c r="AF4">
+        <v>0.4969664031282943</v>
+      </c>
+      <c r="AG4">
+        <v>0.4968368012752694</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>69</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>73</v>
+      </c>
+      <c r="AL4">
+        <v>0.12393357417604</v>
+      </c>
+      <c r="AM4">
+        <v>0.5617788967378223</v>
+      </c>
+      <c r="AN4">
+        <v>0.1575054069166227</v>
+      </c>
+      <c r="AO4">
+        <v>0.4674529910839584</v>
+      </c>
+      <c r="AP4">
+        <v>-0.1615767030443017</v>
+      </c>
+      <c r="AQ4">
+        <v>-0.8461372672257448</v>
+      </c>
+      <c r="AR4">
+        <v>0.2737077062555696</v>
+      </c>
+      <c r="AS4">
+        <v>0.08339579884089887</v>
+      </c>
+      <c r="AT4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:18">
+    <row r="5" spans="1:46">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="B5" s="2">
         <v>46252</v>
@@ -703,22 +1180,22 @@
         <v>46251</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
       <c r="F5">
-        <v>0.2206760510344554</v>
+        <v>0.2009038324667773</v>
       </c>
       <c r="G5">
-        <v>1.257784563326133</v>
+        <v>1.234105502156207</v>
       </c>
       <c r="H5">
-        <v>1.424449193406427</v>
+        <v>1.412292277139658</v>
       </c>
       <c r="I5">
-        <v>0.2983357329321816</v>
+        <v>0.2978753898002699</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -733,24 +1210,108 @@
         <v>8</v>
       </c>
       <c r="N5">
-        <v>-0.02121174033489852</v>
+        <v>-0.02124558251180038</v>
       </c>
       <c r="O5">
-        <v>-6.048154066977075</v>
+        <v>-6.081957983134676</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>1.257784563326133</v>
-      </c>
-      <c r="R5" t="b">
+        <v>1.234105502156207</v>
+      </c>
+      <c r="R5" t="s">
+        <v>58</v>
+      </c>
+      <c r="S5" t="s">
+        <v>62</v>
+      </c>
+      <c r="T5">
+        <v>0.9539800828084271</v>
+      </c>
+      <c r="U5">
+        <v>0.8592457432448537</v>
+      </c>
+      <c r="V5" t="s">
+        <v>56</v>
+      </c>
+      <c r="W5" t="s">
+        <v>66</v>
+      </c>
+      <c r="X5">
+        <v>0.9989713692463792</v>
+      </c>
+      <c r="Y5">
+        <v>0.9992765244441797</v>
+      </c>
+      <c r="Z5">
+        <v>0.0003051551978004996</v>
+      </c>
+      <c r="AA5">
+        <v>0.1653012608324546</v>
+      </c>
+      <c r="AB5">
+        <v>28.42376633486904</v>
+      </c>
+      <c r="AC5">
+        <v>-5.999999999999996</v>
+      </c>
+      <c r="AD5">
+        <v>0.8794512078963892</v>
+      </c>
+      <c r="AE5">
+        <v>0.4759890470689237</v>
+      </c>
+      <c r="AF5">
+        <v>1.19393918180909</v>
+      </c>
+      <c r="AG5">
+        <v>1.193075395995915</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>73</v>
+      </c>
+      <c r="AL5">
+        <v>0.5120420825653471</v>
+      </c>
+      <c r="AM5">
+        <v>0.7901629092290927</v>
+      </c>
+      <c r="AN5">
+        <v>1.040252954443273</v>
+      </c>
+      <c r="AO5">
+        <v>0.5834667613722873</v>
+      </c>
+      <c r="AP5">
+        <v>1.063582433340868</v>
+      </c>
+      <c r="AQ5">
+        <v>-2.613558463854223</v>
+      </c>
+      <c r="AR5">
+        <v>0.8433754074825937</v>
+      </c>
+      <c r="AS5">
+        <v>0.04319659241185132</v>
+      </c>
+      <c r="AT5" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:18">
+    <row r="6" spans="1:46">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="B6" s="2">
         <v>46252</v>
@@ -759,7 +1320,7 @@
         <v>46251</v>
       </c>
       <c r="D6" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -800,13 +1361,97 @@
       <c r="Q6">
         <v>0.3703547186083788</v>
       </c>
-      <c r="R6" t="b">
+      <c r="R6" t="s">
+        <v>58</v>
+      </c>
+      <c r="S6" t="s">
+        <v>62</v>
+      </c>
+      <c r="T6">
+        <v>0.8731485607573917</v>
+      </c>
+      <c r="U6">
+        <v>0.7928641254523829</v>
+      </c>
+      <c r="V6" t="s">
+        <v>56</v>
+      </c>
+      <c r="W6" t="s">
+        <v>66</v>
+      </c>
+      <c r="X6">
+        <v>0.9997749768279037</v>
+      </c>
+      <c r="Y6">
+        <v>0.9997890924462272</v>
+      </c>
+      <c r="Z6">
+        <v>1.411561832342922E-05</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>51.06378098372646</v>
+      </c>
+      <c r="AC6">
+        <v>1.000000000000001</v>
+      </c>
+      <c r="AD6">
+        <v>0.6284548916177507</v>
+      </c>
+      <c r="AE6">
+        <v>0.7778460318094585</v>
+      </c>
+      <c r="AF6">
+        <v>0.4745113001200056</v>
+      </c>
+      <c r="AG6">
+        <v>0.4744112221024597</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>69</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>73</v>
+      </c>
+      <c r="AL6">
+        <v>0.3141611728669515</v>
+      </c>
+      <c r="AM6">
+        <v>0.6803251987760545</v>
+      </c>
+      <c r="AN6">
+        <v>0.2989568369274301</v>
+      </c>
+      <c r="AO6">
+        <v>0.3683537187593863</v>
+      </c>
+      <c r="AP6">
+        <v>0.3782439206868265</v>
+      </c>
+      <c r="AQ6">
+        <v>-0.6540304117206963</v>
+      </c>
+      <c r="AR6">
+        <v>0.31255891441515</v>
+      </c>
+      <c r="AS6">
+        <v>0.05424967376966801</v>
+      </c>
+      <c r="AT6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18">
+    <row r="7" spans="1:46">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="B7" s="2">
         <v>46252</v>
@@ -815,7 +1460,7 @@
         <v>46251</v>
       </c>
       <c r="D7" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -824,13 +1469,13 @@
         <v>1</v>
       </c>
       <c r="G7">
-        <v>1.737494928074045</v>
+        <v>1.71029155165915</v>
       </c>
       <c r="H7">
-        <v>1.349273300358433</v>
+        <v>1.348660710009171</v>
       </c>
       <c r="I7">
-        <v>0.3079460610703557</v>
+        <v>0.307974583364056</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -839,30 +1484,114 @@
         <v>1</v>
       </c>
       <c r="L7">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="M7">
         <v>11</v>
       </c>
       <c r="N7">
-        <v>-0.04459166479556742</v>
+        <v>-0.04599586108478946</v>
       </c>
       <c r="O7">
-        <v>-10.14023076647353</v>
+        <v>-10.51162349309584</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>1.737494928074045</v>
-      </c>
-      <c r="R7" t="b">
+        <v>1.71029155165915</v>
+      </c>
+      <c r="R7" t="s">
+        <v>58</v>
+      </c>
+      <c r="S7" t="s">
+        <v>62</v>
+      </c>
+      <c r="T7">
+        <v>0.9572648565156808</v>
+      </c>
+      <c r="U7">
+        <v>0.9807243820935768</v>
+      </c>
+      <c r="V7" t="s">
+        <v>56</v>
+      </c>
+      <c r="W7" t="s">
+        <v>66</v>
+      </c>
+      <c r="X7">
+        <v>0.9991690124848212</v>
+      </c>
+      <c r="Y7">
+        <v>0.9998207866460816</v>
+      </c>
+      <c r="Z7">
+        <v>0.0006517741612604988</v>
+      </c>
+      <c r="AA7">
+        <v>0.8346070215056901</v>
+      </c>
+      <c r="AB7">
+        <v>24.58108740811132</v>
+      </c>
+      <c r="AC7">
+        <v>-7.999999999999998</v>
+      </c>
+      <c r="AD7">
+        <v>0.909373468387829</v>
+      </c>
+      <c r="AE7">
+        <v>0.4159806425692069</v>
+      </c>
+      <c r="AF7">
+        <v>1.504317616487718</v>
+      </c>
+      <c r="AG7">
+        <v>1.504048022682309</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ7" t="s">
+        <v>69</v>
+      </c>
+      <c r="AK7" t="s">
+        <v>73</v>
+      </c>
+      <c r="AL7">
+        <v>0.8340219804698444</v>
+      </c>
+      <c r="AM7">
+        <v>0.933717606774047</v>
+      </c>
+      <c r="AN7">
+        <v>1.35560633773079</v>
+      </c>
+      <c r="AO7">
+        <v>0.6492638207534683</v>
+      </c>
+      <c r="AP7">
+        <v>1.878176486453671</v>
+      </c>
+      <c r="AQ7">
+        <v>-2.861229809167674</v>
+      </c>
+      <c r="AR7">
+        <v>1.610078382001936</v>
+      </c>
+      <c r="AS7">
+        <v>0.03968742246378829</v>
+      </c>
+      <c r="AT7" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:18">
+    <row r="8" spans="1:46">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="B8" s="2">
         <v>46252</v>
@@ -871,22 +1600,22 @@
         <v>46251</v>
       </c>
       <c r="D8" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E8">
         <v>1</v>
       </c>
       <c r="F8">
-        <v>0.0599653482459717</v>
+        <v>0.1050157412859733</v>
       </c>
       <c r="G8">
-        <v>1.12320607582844</v>
+        <v>1.150148007230601</v>
       </c>
       <c r="H8">
-        <v>1.436542237791728</v>
+        <v>1.428414113694416</v>
       </c>
       <c r="I8">
-        <v>0.3560357811757486</v>
+        <v>0.3522496154274385</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -901,24 +1630,108 @@
         <v>52</v>
       </c>
       <c r="N8">
-        <v>-0.2882377495371427</v>
+        <v>-0.2844375448594371</v>
       </c>
       <c r="O8">
-        <v>-76.11673099160684</v>
+        <v>-74.61355870399382</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>1.12320607582844</v>
-      </c>
-      <c r="R8" t="b">
+        <v>1.150148007230601</v>
+      </c>
+      <c r="R8" t="s">
+        <v>59</v>
+      </c>
+      <c r="S8" t="s">
+        <v>63</v>
+      </c>
+      <c r="T8">
+        <v>0.9937836238698943</v>
+      </c>
+      <c r="U8">
+        <v>0.8626200864699662</v>
+      </c>
+      <c r="V8" t="s">
+        <v>56</v>
+      </c>
+      <c r="W8" t="s">
+        <v>66</v>
+      </c>
+      <c r="X8">
+        <v>0.9958043932686906</v>
+      </c>
+      <c r="Y8">
+        <v>0.9986603781424714</v>
+      </c>
+      <c r="Z8">
+        <v>0.002855984873780804</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>11.13590782729874</v>
+      </c>
+      <c r="AC8">
+        <v>16</v>
+      </c>
+      <c r="AD8">
+        <v>0.9811718158855942</v>
+      </c>
+      <c r="AE8">
+        <v>0.193136914420226</v>
+      </c>
+      <c r="AF8">
+        <v>0.8369167961873116</v>
+      </c>
+      <c r="AG8">
+        <v>0.8357956441542064</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ8" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK8" t="s">
+        <v>74</v>
+      </c>
+      <c r="AL8">
+        <v>0.4899287083375214</v>
+      </c>
+      <c r="AM8">
+        <v>0.7878273821112319</v>
+      </c>
+      <c r="AN8">
+        <v>0.8213535524512496</v>
+      </c>
+      <c r="AO8">
+        <v>0.1412194746989415</v>
+      </c>
+      <c r="AP8">
+        <v>1.676087523665858</v>
+      </c>
+      <c r="AQ8">
+        <v>-0.8608944493337228</v>
+      </c>
+      <c r="AR8">
+        <v>1.575697035069539</v>
+      </c>
+      <c r="AS8">
+        <v>0.04036863336207513</v>
+      </c>
+      <c r="AT8" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:18">
+    <row r="9" spans="1:46">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="B9" s="2">
         <v>46252</v>
@@ -927,22 +1740,22 @@
         <v>46251</v>
       </c>
       <c r="D9" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="E9">
         <v>-1</v>
       </c>
       <c r="F9">
-        <v>0.5259359401337355</v>
+        <v>0.4395265256789536</v>
       </c>
       <c r="G9">
-        <v>2.972216273968399</v>
+        <v>2.865467247385043</v>
       </c>
       <c r="H9">
-        <v>2.941026149708734</v>
+        <v>2.938150823174008</v>
       </c>
       <c r="I9">
-        <v>0.6012915687427639</v>
+        <v>0.6009541919412189</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -957,24 +1770,108 @@
         <v>23</v>
       </c>
       <c r="N9">
-        <v>0.2872794861215611</v>
+        <v>0.2923606056663127</v>
       </c>
       <c r="O9">
-        <v>41.49724314591308</v>
+        <v>41.09692734904784</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>2.972216273968399</v>
-      </c>
-      <c r="R9" t="b">
+        <v>2.865467247385043</v>
+      </c>
+      <c r="R9" t="s">
+        <v>60</v>
+      </c>
+      <c r="S9" t="s">
+        <v>64</v>
+      </c>
+      <c r="T9">
+        <v>-0.9939397852337705</v>
+      </c>
+      <c r="U9">
+        <v>0.9131616694458771</v>
+      </c>
+      <c r="V9" t="s">
+        <v>57</v>
+      </c>
+      <c r="W9" t="s">
+        <v>66</v>
+      </c>
+      <c r="X9">
+        <v>0.9984126809732159</v>
+      </c>
+      <c r="Y9">
+        <v>0.9998391489553492</v>
+      </c>
+      <c r="Z9">
+        <v>0.001426467982133306</v>
+      </c>
+      <c r="AA9">
+        <v>0.8084559137929632</v>
+      </c>
+      <c r="AB9">
+        <v>171.2184960870734</v>
+      </c>
+      <c r="AC9">
+        <v>-12</v>
+      </c>
+      <c r="AD9">
+        <v>-0.988277716476738</v>
+      </c>
+      <c r="AE9">
+        <v>0.1526668107858553</v>
+      </c>
+      <c r="AF9">
+        <v>2.215665005561597</v>
+      </c>
+      <c r="AG9">
+        <v>2.215308613530856</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>57</v>
+      </c>
+      <c r="AI9" t="s">
+        <v>68</v>
+      </c>
+      <c r="AJ9" t="s">
+        <v>71</v>
+      </c>
+      <c r="AK9" t="s">
+        <v>75</v>
+      </c>
+      <c r="AL9">
+        <v>-0.8934845993639957</v>
+      </c>
+      <c r="AM9">
+        <v>0.9532189578065283</v>
+      </c>
+      <c r="AN9">
+        <v>-2.193405750143193</v>
+      </c>
+      <c r="AO9">
+        <v>0.2873502371253457</v>
+      </c>
+      <c r="AP9">
+        <v>-3.503879798910328</v>
+      </c>
+      <c r="AQ9">
+        <v>3.639504824923043</v>
+      </c>
+      <c r="AR9">
+        <v>3.188223828823946</v>
+      </c>
+      <c r="AS9">
+        <v>0.03266161352971927</v>
+      </c>
+      <c r="AT9" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:18">
+    <row r="10" spans="1:46">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="B10" s="2">
         <v>46252</v>
@@ -983,7 +1880,7 @@
         <v>46251</v>
       </c>
       <c r="D10" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="E10">
         <v>-1</v>
@@ -992,13 +1889,13 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>0.9408225092317056</v>
+        <v>0.768059346761379</v>
       </c>
       <c r="H10">
-        <v>2.041616780789691</v>
+        <v>2.03694561713885</v>
       </c>
       <c r="I10">
-        <v>0.4707236940623677</v>
+        <v>0.4651464874058603</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1010,27 +1907,111 @@
         <v>233</v>
       </c>
       <c r="M10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N10">
-        <v>9.731366619828716</v>
+        <v>10.65798314779006</v>
       </c>
       <c r="O10">
-        <v>9.579800490637563</v>
+        <v>9.09605974573646</v>
       </c>
       <c r="P10">
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>0.9408225092317056</v>
-      </c>
-      <c r="R10" t="b">
+        <v>0.768059346761379</v>
+      </c>
+      <c r="R10" t="s">
+        <v>61</v>
+      </c>
+      <c r="S10" t="s">
+        <v>65</v>
+      </c>
+      <c r="T10">
+        <v>-0.8904545610530479</v>
+      </c>
+      <c r="U10">
+        <v>0.8002187525616534</v>
+      </c>
+      <c r="V10" t="s">
+        <v>57</v>
+      </c>
+      <c r="W10" t="s">
+        <v>66</v>
+      </c>
+      <c r="X10">
+        <v>0.974012792743513</v>
+      </c>
+      <c r="Y10">
+        <v>0.9980568003511275</v>
+      </c>
+      <c r="Z10">
+        <v>0.02404400760761449</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>132.7481492757411</v>
+      </c>
+      <c r="AC10">
+        <v>-49</v>
+      </c>
+      <c r="AD10">
+        <v>-0.6787770256571848</v>
+      </c>
+      <c r="AE10">
+        <v>0.7343444351528685</v>
+      </c>
+      <c r="AF10">
+        <v>0.9863181027515535</v>
+      </c>
+      <c r="AG10">
+        <v>0.9844014897606101</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>57</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>68</v>
+      </c>
+      <c r="AJ10" t="s">
+        <v>72</v>
+      </c>
+      <c r="AK10" t="s">
+        <v>76</v>
+      </c>
+      <c r="AL10">
+        <v>-0.3387290131896325</v>
+      </c>
+      <c r="AM10">
+        <v>0.6956222769524339</v>
+      </c>
+      <c r="AN10">
+        <v>-0.7155230982697569</v>
+      </c>
+      <c r="AO10">
+        <v>0.6410500375643496</v>
+      </c>
+      <c r="AP10">
+        <v>-0.3756824104071136</v>
+      </c>
+      <c r="AQ10">
+        <v>2.745967919669226</v>
+      </c>
+      <c r="AR10">
+        <v>0.3989677030250876</v>
+      </c>
+      <c r="AS10">
+        <v>0.04887140578410751</v>
+      </c>
+      <c r="AT10" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:18">
+    <row r="11" spans="1:46">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="B11" s="2">
         <v>46252</v>
@@ -1039,7 +2020,7 @@
         <v>46251</v>
       </c>
       <c r="D11" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -1048,13 +2029,13 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>1.412807215284729</v>
+        <v>1.420548297286022</v>
       </c>
       <c r="H11">
         <v>2.966377745487705</v>
       </c>
       <c r="I11">
-        <v>0.6366632764781077</v>
+        <v>0.6366885101407912</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -1069,18 +2050,102 @@
         <v>4</v>
       </c>
       <c r="N11">
-        <v>-249.8859563975202</v>
+        <v>-249.7247860097312</v>
       </c>
       <c r="O11">
-        <v>-3.673288662801249</v>
+        <v>-3.705704599222256</v>
       </c>
       <c r="P11">
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>1.412807215284729</v>
-      </c>
-      <c r="R11" t="b">
+        <v>1.420548297286022</v>
+      </c>
+      <c r="R11" t="s">
+        <v>58</v>
+      </c>
+      <c r="S11" t="s">
+        <v>62</v>
+      </c>
+      <c r="T11">
+        <v>0.7527343615871123</v>
+      </c>
+      <c r="U11">
+        <v>0.7385681805198869</v>
+      </c>
+      <c r="V11" t="s">
+        <v>56</v>
+      </c>
+      <c r="W11" t="s">
+        <v>66</v>
+      </c>
+      <c r="X11">
+        <v>0.9979840614491202</v>
+      </c>
+      <c r="Y11">
+        <v>0.9993508712227458</v>
+      </c>
+      <c r="Z11">
+        <v>0.001366809773625577</v>
+      </c>
+      <c r="AA11">
+        <v>0.7987276276273882</v>
+      </c>
+      <c r="AB11">
+        <v>55.9038704580633</v>
+      </c>
+      <c r="AC11">
+        <v>-12.99999999999999</v>
+      </c>
+      <c r="AD11">
+        <v>0.560583055956321</v>
+      </c>
+      <c r="AE11">
+        <v>0.8280982051512202</v>
+      </c>
+      <c r="AF11">
+        <v>2.18970256297648</v>
+      </c>
+      <c r="AG11">
+        <v>2.188281164029225</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI11" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ11" t="s">
+        <v>69</v>
+      </c>
+      <c r="AK11" t="s">
+        <v>73</v>
+      </c>
+      <c r="AL11">
+        <v>0.5038408451320852</v>
+      </c>
+      <c r="AM11">
+        <v>0.8199254261792034</v>
+      </c>
+      <c r="AN11">
+        <v>1.162943351370415</v>
+      </c>
+      <c r="AO11">
+        <v>1.850147974732233</v>
+      </c>
+      <c r="AP11">
+        <v>1.39891718585439</v>
+      </c>
+      <c r="AQ11">
+        <v>-3.219612874010256</v>
+      </c>
+      <c r="AR11">
+        <v>1.159805481398617</v>
+      </c>
+      <c r="AS11">
+        <v>0.05178547374087741</v>
+      </c>
+      <c r="AT11" t="b">
         <v>1</v>
       </c>
     </row>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="77">
   <si>
     <t>Pair</t>
   </si>
@@ -67,6 +67,90 @@
     <t>TerrainBundleSep</t>
   </si>
   <si>
+    <t>MarketPosture</t>
+  </si>
+  <si>
+    <t>MarketPostureCN</t>
+  </si>
+  <si>
+    <t>MarketPostureScore</t>
+  </si>
+  <si>
+    <t>MarketPostureConfidence</t>
+  </si>
+  <si>
+    <t>PhasedDirection</t>
+  </si>
+  <si>
+    <t>PhasedAlignment</t>
+  </si>
+  <si>
+    <t>PhasedRawCoherence</t>
+  </si>
+  <si>
+    <t>PhasedCoherence</t>
+  </si>
+  <si>
+    <t>PhasedSteeringGain</t>
+  </si>
+  <si>
+    <t>PhasedGate</t>
+  </si>
+  <si>
+    <t>PhasedBeamPhaseDeg</t>
+  </si>
+  <si>
+    <t>PhasedGradientDeg</t>
+  </si>
+  <si>
+    <t>PhasedDirectionScore</t>
+  </si>
+  <si>
+    <t>PhasedImpulseScore</t>
+  </si>
+  <si>
+    <t>PhasedAmplitude</t>
+  </si>
+  <si>
+    <t>PhasedPower</t>
+  </si>
+  <si>
+    <t>SurveyTrend</t>
+  </si>
+  <si>
+    <t>SurveyTrendCN</t>
+  </si>
+  <si>
+    <t>TerrainPattern</t>
+  </si>
+  <si>
+    <t>TerrainPatternCN</t>
+  </si>
+  <si>
+    <t>SurveyDirectionScore</t>
+  </si>
+  <si>
+    <t>SurveyConfidence</t>
+  </si>
+  <si>
+    <t>ContourElevation</t>
+  </si>
+  <si>
+    <t>ContourTemporalSlope</t>
+  </si>
+  <si>
+    <t>ContourScaleSlope</t>
+  </si>
+  <si>
+    <t>ContourCurvature</t>
+  </si>
+  <si>
+    <t>ContourRelief</t>
+  </si>
+  <si>
+    <t>ContourRoughness</t>
+  </si>
+  <si>
     <t>FilterEnabled</t>
   </si>
   <si>
@@ -104,6 +188,63 @@
   </si>
   <si>
     <t>DOWN</t>
+  </si>
+  <si>
+    <t>UP_ACCELERATING</t>
+  </si>
+  <si>
+    <t>UP_STEADY</t>
+  </si>
+  <si>
+    <t>DOWN_STEADY</t>
+  </si>
+  <si>
+    <t>DOWN_DECELERATING</t>
+  </si>
+  <si>
+    <t>多头加速</t>
+  </si>
+  <si>
+    <t>多头稳态</t>
+  </si>
+  <si>
+    <t>空头稳态</t>
+  </si>
+  <si>
+    <t>空头减速</t>
+  </si>
+  <si>
+    <t>ALIGNED</t>
+  </si>
+  <si>
+    <t>上涨</t>
+  </si>
+  <si>
+    <t>下跌</t>
+  </si>
+  <si>
+    <t>UP_STEEPENING</t>
+  </si>
+  <si>
+    <t>UP_SLOPE</t>
+  </si>
+  <si>
+    <t>DOWN_SLOPE</t>
+  </si>
+  <si>
+    <t>DOWN_VALLEY_FLATTENING</t>
+  </si>
+  <si>
+    <t>上升陡坡形成</t>
+  </si>
+  <si>
+    <t>上升坡延续</t>
+  </si>
+  <si>
+    <t>下降坡延续</t>
+  </si>
+  <si>
+    <t>下降谷底收敛</t>
   </si>
 </sst>
 </file>
@@ -465,10 +606,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:AT11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:46">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -523,10 +664,94 @@
       <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>45</v>
+      </c>
     </row>
-    <row r="2" spans="1:18">
+    <row r="2" spans="1:46">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="B2" s="2">
         <v>46253</v>
@@ -535,7 +760,7 @@
         <v>46252</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -576,13 +801,97 @@
       <c r="Q2">
         <v>0.3705904524197943</v>
       </c>
-      <c r="R2" t="b">
+      <c r="R2" t="s">
+        <v>58</v>
+      </c>
+      <c r="S2" t="s">
+        <v>62</v>
+      </c>
+      <c r="T2">
+        <v>0.8423878998878066</v>
+      </c>
+      <c r="U2">
+        <v>0.7790499211257802</v>
+      </c>
+      <c r="V2" t="s">
+        <v>56</v>
+      </c>
+      <c r="W2" t="s">
+        <v>66</v>
+      </c>
+      <c r="X2">
+        <v>0.9995250262971639</v>
+      </c>
+      <c r="Y2">
+        <v>0.9999014647050692</v>
+      </c>
+      <c r="Z2">
+        <v>0.0003764384079053551</v>
+      </c>
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>57.4257745628755</v>
+      </c>
+      <c r="AC2">
+        <v>6.000000000000009</v>
+      </c>
+      <c r="AD2">
+        <v>0.5383917524642465</v>
+      </c>
+      <c r="AE2">
+        <v>0.8426946783257133</v>
+      </c>
+      <c r="AF2">
+        <v>0.5599800490425162</v>
+      </c>
+      <c r="AG2">
+        <v>0.5599248712432284</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>69</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AL2">
+        <v>0.2691693509370646</v>
+      </c>
+      <c r="AM2">
+        <v>0.6527833795694323</v>
+      </c>
+      <c r="AN2">
+        <v>0.3076008003248081</v>
+      </c>
+      <c r="AO2">
+        <v>0.4676126510565853</v>
+      </c>
+      <c r="AP2">
+        <v>0.3342931389128422</v>
+      </c>
+      <c r="AQ2">
+        <v>-0.6319870952416665</v>
+      </c>
+      <c r="AR2">
+        <v>0.2748281582593743</v>
+      </c>
+      <c r="AS2">
+        <v>0.05799772544410547</v>
+      </c>
+      <c r="AT2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:18">
+    <row r="3" spans="1:46">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="B3" s="2">
         <v>46253</v>
@@ -591,22 +900,22 @@
         <v>46252</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>0.02427946824172759</v>
       </c>
       <c r="G3">
-        <v>1.253548991734727</v>
+        <v>1.432562669526511</v>
       </c>
       <c r="H3">
         <v>1.835418651588441</v>
       </c>
       <c r="I3">
-        <v>0.4225092925541029</v>
+        <v>0.4234166439831452</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -618,27 +927,111 @@
         <v>225</v>
       </c>
       <c r="M3">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N3">
-        <v>-0.02124072877074521</v>
+        <v>-0.02300664381270809</v>
       </c>
       <c r="O3">
-        <v>-6.43937208294571</v>
+        <v>-8.188458456283543</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>1.253548991734727</v>
-      </c>
-      <c r="R3" t="b">
+        <v>1.432562669526511</v>
+      </c>
+      <c r="R3" t="s">
+        <v>58</v>
+      </c>
+      <c r="S3" t="s">
+        <v>62</v>
+      </c>
+      <c r="T3">
+        <v>0.933315875994664</v>
+      </c>
+      <c r="U3">
+        <v>0.823612586994795</v>
+      </c>
+      <c r="V3" t="s">
+        <v>56</v>
+      </c>
+      <c r="W3" t="s">
+        <v>66</v>
+      </c>
+      <c r="X3">
+        <v>0.9998196346814879</v>
+      </c>
+      <c r="Y3">
+        <v>0.9999140902437478</v>
+      </c>
+      <c r="Z3">
+        <v>9.445556225984308E-05</v>
+      </c>
+      <c r="AA3">
+        <v>0.2197037257474797</v>
+      </c>
+      <c r="AB3">
+        <v>32.76443224784209</v>
+      </c>
+      <c r="AC3">
+        <v>-3.000000000000004</v>
+      </c>
+      <c r="AD3">
+        <v>0.8409027200932033</v>
+      </c>
+      <c r="AE3">
+        <v>0.5411863037252992</v>
+      </c>
+      <c r="AF3">
+        <v>1.400414093626556</v>
+      </c>
+      <c r="AG3">
+        <v>1.400293784393121</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>69</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>73</v>
+      </c>
+      <c r="AL3">
+        <v>0.5127820335800138</v>
+      </c>
+      <c r="AM3">
+        <v>0.7900816218130932</v>
+      </c>
+      <c r="AN3">
+        <v>1.172045796002494</v>
+      </c>
+      <c r="AO3">
+        <v>0.7660031978631556</v>
+      </c>
+      <c r="AP3">
+        <v>1.398291002628391</v>
+      </c>
+      <c r="AQ3">
+        <v>-2.637059647908032</v>
+      </c>
+      <c r="AR3">
+        <v>1.164209014676019</v>
+      </c>
+      <c r="AS3">
+        <v>0.04066580633117039</v>
+      </c>
+      <c r="AT3" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:18">
+    <row r="4" spans="1:46">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="B4" s="2">
         <v>46253</v>
@@ -647,7 +1040,7 @@
         <v>46252</v>
       </c>
       <c r="D4" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -688,13 +1081,97 @@
       <c r="Q4">
         <v>0.2343121571043723</v>
       </c>
-      <c r="R4" t="b">
+      <c r="R4" t="s">
+        <v>58</v>
+      </c>
+      <c r="S4" t="s">
+        <v>62</v>
+      </c>
+      <c r="T4">
+        <v>0.7764485855780732</v>
+      </c>
+      <c r="U4">
+        <v>0.749368987564258</v>
+      </c>
+      <c r="V4" t="s">
+        <v>56</v>
+      </c>
+      <c r="W4" t="s">
+        <v>66</v>
+      </c>
+      <c r="X4">
+        <v>0.9935846361542557</v>
+      </c>
+      <c r="Y4">
+        <v>0.9998684962165003</v>
+      </c>
+      <c r="Z4">
+        <v>0.006283860062244573</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>69.80251450562062</v>
+      </c>
+      <c r="AC4">
+        <v>25</v>
+      </c>
+      <c r="AD4">
+        <v>0.3452570115838208</v>
+      </c>
+      <c r="AE4">
+        <v>0.938508175751394</v>
+      </c>
+      <c r="AF4">
+        <v>0.6370166105981927</v>
+      </c>
+      <c r="AG4">
+        <v>0.6369328405037469</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>69</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>73</v>
+      </c>
+      <c r="AL4">
+        <v>0.1726058044902589</v>
+      </c>
+      <c r="AM4">
+        <v>0.5930772642404968</v>
+      </c>
+      <c r="AN4">
+        <v>0.2530756250093301</v>
+      </c>
+      <c r="AO4">
+        <v>0.580131888621675</v>
+      </c>
+      <c r="AP4">
+        <v>-0.05836330496217956</v>
+      </c>
+      <c r="AQ4">
+        <v>-1.093069637526959</v>
+      </c>
+      <c r="AR4">
+        <v>0.2226812473251264</v>
+      </c>
+      <c r="AS4">
+        <v>0.06969208606949671</v>
+      </c>
+      <c r="AT4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:18">
+    <row r="5" spans="1:46">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="B5" s="2">
         <v>46253</v>
@@ -703,22 +1180,22 @@
         <v>46252</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
       <c r="F5">
-        <v>0.8552766994279543</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>1.639723445230607</v>
+        <v>1.877847691186643</v>
       </c>
       <c r="H5">
-        <v>1.427492196530036</v>
+        <v>1.415678037510481</v>
       </c>
       <c r="I5">
-        <v>0.2986844465768417</v>
+        <v>0.298303834643161</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -733,24 +1210,108 @@
         <v>9</v>
       </c>
       <c r="N5">
-        <v>-0.02518237224778981</v>
+        <v>-0.02514031876041445</v>
       </c>
       <c r="O5">
-        <v>-7.984445962383703</v>
+        <v>-9.316158354838455</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>1.639723445230607</v>
-      </c>
-      <c r="R5" t="b">
+        <v>1.877847691186643</v>
+      </c>
+      <c r="R5" t="s">
+        <v>58</v>
+      </c>
+      <c r="S5" t="s">
+        <v>62</v>
+      </c>
+      <c r="T5">
+        <v>0.9038501979646764</v>
+      </c>
+      <c r="U5">
+        <v>0.9566417049698011</v>
+      </c>
+      <c r="V5" t="s">
+        <v>56</v>
+      </c>
+      <c r="W5" t="s">
+        <v>66</v>
+      </c>
+      <c r="X5">
+        <v>0.9988577817515383</v>
+      </c>
+      <c r="Y5">
+        <v>0.999636463542787</v>
+      </c>
+      <c r="Z5">
+        <v>0.0007786817912487365</v>
+      </c>
+      <c r="AA5">
+        <v>1</v>
+      </c>
+      <c r="AB5">
+        <v>36.13153934722025</v>
+      </c>
+      <c r="AC5">
+        <v>9</v>
+      </c>
+      <c r="AD5">
+        <v>0.8076654292592997</v>
+      </c>
+      <c r="AE5">
+        <v>0.5896410385814331</v>
+      </c>
+      <c r="AF5">
+        <v>1.882047699659005</v>
+      </c>
+      <c r="AG5">
+        <v>1.881363506705965</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>73</v>
+      </c>
+      <c r="AL5">
+        <v>0.8073718134305334</v>
+      </c>
+      <c r="AM5">
+        <v>0.9353814439616006</v>
+      </c>
+      <c r="AN5">
+        <v>1.539942938701542</v>
+      </c>
+      <c r="AO5">
+        <v>1.078235688508524</v>
+      </c>
+      <c r="AP5">
+        <v>1.803327626737504</v>
+      </c>
+      <c r="AQ5">
+        <v>-3.260640591164396</v>
+      </c>
+      <c r="AR5">
+        <v>1.525280467253671</v>
+      </c>
+      <c r="AS5">
+        <v>0.04527298037443184</v>
+      </c>
+      <c r="AT5" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:18">
+    <row r="6" spans="1:46">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="B6" s="2">
         <v>46253</v>
@@ -759,7 +1320,7 @@
         <v>46252</v>
       </c>
       <c r="D6" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -800,13 +1361,97 @@
       <c r="Q6">
         <v>0.4332062325661995</v>
       </c>
-      <c r="R6" t="b">
+      <c r="R6" t="s">
+        <v>58</v>
+      </c>
+      <c r="S6" t="s">
+        <v>62</v>
+      </c>
+      <c r="T6">
+        <v>0.9012782753710262</v>
+      </c>
+      <c r="U6">
+        <v>0.805515143226235</v>
+      </c>
+      <c r="V6" t="s">
+        <v>56</v>
+      </c>
+      <c r="W6" t="s">
+        <v>66</v>
+      </c>
+      <c r="X6">
+        <v>0.9997509836640947</v>
+      </c>
+      <c r="Y6">
+        <v>0.9997596772370927</v>
+      </c>
+      <c r="Z6">
+        <v>8.693572998041965E-06</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>44.69664900174041</v>
+      </c>
+      <c r="AC6">
+        <v>-1.000000000000001</v>
+      </c>
+      <c r="AD6">
+        <v>0.7108406113667157</v>
+      </c>
+      <c r="AE6">
+        <v>0.7033531298229886</v>
+      </c>
+      <c r="AF6">
+        <v>0.4991889474575222</v>
+      </c>
+      <c r="AG6">
+        <v>0.4990689809904564</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>69</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>73</v>
+      </c>
+      <c r="AL6">
+        <v>0.3553348900935027</v>
+      </c>
+      <c r="AM6">
+        <v>0.7058015494446936</v>
+      </c>
+      <c r="AN6">
+        <v>0.3539453759008871</v>
+      </c>
+      <c r="AO6">
+        <v>0.3518354544801641</v>
+      </c>
+      <c r="AP6">
+        <v>0.4262722105653874</v>
+      </c>
+      <c r="AQ6">
+        <v>-0.8737501050199816</v>
+      </c>
+      <c r="AR6">
+        <v>0.3413524275817372</v>
+      </c>
+      <c r="AS6">
+        <v>0.0491101399886893</v>
+      </c>
+      <c r="AT6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18">
+    <row r="7" spans="1:46">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="B7" s="2">
         <v>46253</v>
@@ -815,7 +1460,7 @@
         <v>46252</v>
       </c>
       <c r="D7" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -824,13 +1469,13 @@
         <v>1</v>
       </c>
       <c r="G7">
-        <v>2.004240521415301</v>
+        <v>2.393967128640724</v>
       </c>
       <c r="H7">
-        <v>1.356732268591047</v>
+        <v>1.355036430004938</v>
       </c>
       <c r="I7">
-        <v>0.3085961927939687</v>
+        <v>0.3088366076843327</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -839,30 +1484,114 @@
         <v>1</v>
       </c>
       <c r="L7">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="M7">
         <v>12</v>
       </c>
       <c r="N7">
-        <v>-0.05080947986606936</v>
+        <v>-0.05209488526708857</v>
       </c>
       <c r="O7">
-        <v>-12.56327654759749</v>
+        <v>-15.7013647737188</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>2.004240521415301</v>
-      </c>
-      <c r="R7" t="b">
+        <v>2.393967128640724</v>
+      </c>
+      <c r="R7" t="s">
+        <v>58</v>
+      </c>
+      <c r="S7" t="s">
+        <v>62</v>
+      </c>
+      <c r="T7">
+        <v>0.9566516313483018</v>
+      </c>
+      <c r="U7">
+        <v>0.9804757572401196</v>
+      </c>
+      <c r="V7" t="s">
+        <v>56</v>
+      </c>
+      <c r="W7" t="s">
+        <v>66</v>
+      </c>
+      <c r="X7">
+        <v>0.9997441129003783</v>
+      </c>
+      <c r="Y7">
+        <v>0.9999300925335349</v>
+      </c>
+      <c r="Z7">
+        <v>0.0001859796331565855</v>
+      </c>
+      <c r="AA7">
+        <v>1</v>
+      </c>
+      <c r="AB7">
+        <v>24.03452083496258</v>
+      </c>
+      <c r="AC7">
+        <v>-3.999999999999993</v>
+      </c>
+      <c r="AD7">
+        <v>0.9133002321101152</v>
+      </c>
+      <c r="AE7">
+        <v>0.407286982393999</v>
+      </c>
+      <c r="AF7">
+        <v>2.076524918402884</v>
+      </c>
+      <c r="AG7">
+        <v>2.076379753806787</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ7" t="s">
+        <v>69</v>
+      </c>
+      <c r="AK7" t="s">
+        <v>73</v>
+      </c>
+      <c r="AL7">
+        <v>0.9132363856047665</v>
+      </c>
+      <c r="AM7">
+        <v>0.9679745031472357</v>
+      </c>
+      <c r="AN7">
+        <v>1.888659480193469</v>
+      </c>
+      <c r="AO7">
+        <v>0.861808934316782</v>
+      </c>
+      <c r="AP7">
+        <v>2.664250041100024</v>
+      </c>
+      <c r="AQ7">
+        <v>-3.775343999220554</v>
+      </c>
+      <c r="AR7">
+        <v>2.314975851877224</v>
+      </c>
+      <c r="AS7">
+        <v>0.03994065915024112</v>
+      </c>
+      <c r="AT7" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:18">
+    <row r="8" spans="1:46">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="B8" s="2">
         <v>46253</v>
@@ -871,7 +1600,7 @@
         <v>46252</v>
       </c>
       <c r="D8" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -880,13 +1609,13 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>0.9338423918927403</v>
+        <v>0.9633919720979356</v>
       </c>
       <c r="H8">
-        <v>1.438022173633098</v>
+        <v>1.429560877245548</v>
       </c>
       <c r="I8">
-        <v>0.3561321773463297</v>
+        <v>0.3522145932965394</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -901,24 +1630,108 @@
         <v>53</v>
       </c>
       <c r="N8">
-        <v>-0.2910912707877594</v>
+        <v>-0.287385858268409</v>
       </c>
       <c r="O8">
-        <v>-74.65245999319771</v>
+        <v>-73.22598991278093</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>0.9338423918927403</v>
-      </c>
-      <c r="R8" t="b">
+        <v>0.9633919720979356</v>
+      </c>
+      <c r="R8" t="s">
+        <v>59</v>
+      </c>
+      <c r="S8" t="s">
+        <v>63</v>
+      </c>
+      <c r="T8">
+        <v>0.9978251093858237</v>
+      </c>
+      <c r="U8">
+        <v>0.8485278928039384</v>
+      </c>
+      <c r="V8" t="s">
+        <v>56</v>
+      </c>
+      <c r="W8" t="s">
+        <v>66</v>
+      </c>
+      <c r="X8">
+        <v>0.9980163698511929</v>
+      </c>
+      <c r="Y8">
+        <v>0.9980263743212707</v>
+      </c>
+      <c r="Z8">
+        <v>1.000447007781791E-05</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>-6.474376271949135</v>
+      </c>
+      <c r="AC8">
+        <v>-1.000000000000001</v>
+      </c>
+      <c r="AD8">
+        <v>0.9936223828780991</v>
+      </c>
+      <c r="AE8">
+        <v>-0.1127588588255848</v>
+      </c>
+      <c r="AF8">
+        <v>0.7104513933011436</v>
+      </c>
+      <c r="AG8">
+        <v>0.7090492281878354</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ8" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK8" t="s">
+        <v>74</v>
+      </c>
+      <c r="AL8">
+        <v>0.4958306721141454</v>
+      </c>
+      <c r="AM8">
+        <v>0.7927347424177903</v>
+      </c>
+      <c r="AN8">
+        <v>0.7046525863479556</v>
+      </c>
+      <c r="AO8">
+        <v>-0.07877474972109345</v>
+      </c>
+      <c r="AP8">
+        <v>1.341511126839038</v>
+      </c>
+      <c r="AQ8">
+        <v>-1.173495820312121</v>
+      </c>
+      <c r="AR8">
+        <v>1.216869280342908</v>
+      </c>
+      <c r="AS8">
+        <v>0.03107468972056124</v>
+      </c>
+      <c r="AT8" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:18">
+    <row r="9" spans="1:46">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="B9" s="2">
         <v>46253</v>
@@ -927,22 +1740,22 @@
         <v>46252</v>
       </c>
       <c r="D9" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="E9">
         <v>-1</v>
       </c>
       <c r="F9">
-        <v>0.6172540645551702</v>
+        <v>0.9712887148124082</v>
       </c>
       <c r="G9">
-        <v>3.084531080095666</v>
+        <v>3.505577569841422</v>
       </c>
       <c r="H9">
-        <v>2.943610218773843</v>
+        <v>2.939448107460369</v>
       </c>
       <c r="I9">
-        <v>0.6009210079686309</v>
+        <v>0.6006185217127418</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -957,24 +1770,108 @@
         <v>24</v>
       </c>
       <c r="N9">
-        <v>0.3030896856822206</v>
+        <v>0.3080258065336283</v>
       </c>
       <c r="O9">
-        <v>44.74120201972908</v>
+        <v>52.17302391229625</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>3.084531080095666</v>
-      </c>
-      <c r="R9" t="b">
+        <v>3.505577569841422</v>
+      </c>
+      <c r="R9" t="s">
+        <v>60</v>
+      </c>
+      <c r="S9" t="s">
+        <v>64</v>
+      </c>
+      <c r="T9">
+        <v>-0.9986248315635631</v>
+      </c>
+      <c r="U9">
+        <v>0.9950363712852694</v>
+      </c>
+      <c r="V9" t="s">
+        <v>57</v>
+      </c>
+      <c r="W9" t="s">
+        <v>66</v>
+      </c>
+      <c r="X9">
+        <v>0.9997321818437628</v>
+      </c>
+      <c r="Y9">
+        <v>0.9998475594392194</v>
+      </c>
+      <c r="Z9">
+        <v>0.000115377595456656</v>
+      </c>
+      <c r="AA9">
+        <v>1</v>
+      </c>
+      <c r="AB9">
+        <v>175.7593669605106</v>
+      </c>
+      <c r="AC9">
+        <v>-3.000000000000004</v>
+      </c>
+      <c r="AD9">
+        <v>-0.9972622873473986</v>
+      </c>
+      <c r="AE9">
+        <v>0.07394545445552796</v>
+      </c>
+      <c r="AF9">
+        <v>2.670697517648402</v>
+      </c>
+      <c r="AG9">
+        <v>2.670290395021136</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>57</v>
+      </c>
+      <c r="AI9" t="s">
+        <v>68</v>
+      </c>
+      <c r="AJ9" t="s">
+        <v>71</v>
+      </c>
+      <c r="AK9" t="s">
+        <v>75</v>
+      </c>
+      <c r="AL9">
+        <v>-0.9971102641250701</v>
+      </c>
+      <c r="AM9">
+        <v>0.9940172618120188</v>
+      </c>
+      <c r="AN9">
+        <v>-2.663763578722742</v>
+      </c>
+      <c r="AO9">
+        <v>0.1821231615291742</v>
+      </c>
+      <c r="AP9">
+        <v>-4.362469652293859</v>
+      </c>
+      <c r="AQ9">
+        <v>3.935603322726354</v>
+      </c>
+      <c r="AR9">
+        <v>4.026433105590166</v>
+      </c>
+      <c r="AS9">
+        <v>0.03405380130618409</v>
+      </c>
+      <c r="AT9" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:18">
+    <row r="10" spans="1:46">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="B10" s="2">
         <v>46253</v>
@@ -983,7 +1880,7 @@
         <v>46252</v>
       </c>
       <c r="D10" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="E10">
         <v>-1</v>
@@ -992,13 +1889,13 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>0.9513880630347501</v>
+        <v>1.14038771988262</v>
       </c>
       <c r="H10">
-        <v>2.042879406650236</v>
+        <v>2.038062856947358</v>
       </c>
       <c r="I10">
-        <v>0.4707715764760387</v>
+        <v>0.4650382968591397</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1010,27 +1907,111 @@
         <v>233</v>
       </c>
       <c r="M10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N10">
-        <v>10.6054358800599</v>
+        <v>11.48983109908507</v>
       </c>
       <c r="O10">
-        <v>10.42998857229032</v>
+        <v>14.40666655207481</v>
       </c>
       <c r="P10">
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>0.9513880630347501</v>
-      </c>
-      <c r="R10" t="b">
+        <v>1.14038771988262</v>
+      </c>
+      <c r="R10" t="s">
+        <v>61</v>
+      </c>
+      <c r="S10" t="s">
+        <v>65</v>
+      </c>
+      <c r="T10">
+        <v>-0.9196294928912929</v>
+      </c>
+      <c r="U10">
+        <v>0.8132973957830469</v>
+      </c>
+      <c r="V10" t="s">
+        <v>57</v>
+      </c>
+      <c r="W10" t="s">
+        <v>66</v>
+      </c>
+      <c r="X10">
+        <v>0.9888732075440817</v>
+      </c>
+      <c r="Y10">
+        <v>0.9978564959278607</v>
+      </c>
+      <c r="Z10">
+        <v>0.008983288383779042</v>
+      </c>
+      <c r="AA10">
+        <v>0.02617288771994366</v>
+      </c>
+      <c r="AB10">
+        <v>140.4884676350799</v>
+      </c>
+      <c r="AC10">
+        <v>-31.99999999999999</v>
+      </c>
+      <c r="AD10">
+        <v>-0.7714965393726552</v>
+      </c>
+      <c r="AE10">
+        <v>0.6362335182431189</v>
+      </c>
+      <c r="AF10">
+        <v>1.280017397274716</v>
+      </c>
+      <c r="AG10">
+        <v>1.277273674771248</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>57</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>68</v>
+      </c>
+      <c r="AJ10" t="s">
+        <v>72</v>
+      </c>
+      <c r="AK10" t="s">
+        <v>76</v>
+      </c>
+      <c r="AL10">
+        <v>-0.3949959217197102</v>
+      </c>
+      <c r="AM10">
+        <v>0.7286974106680848</v>
+      </c>
+      <c r="AN10">
+        <v>-1.034821703662467</v>
+      </c>
+      <c r="AO10">
+        <v>0.7289239759964443</v>
+      </c>
+      <c r="AP10">
+        <v>-0.6652119309142848</v>
+      </c>
+      <c r="AQ10">
+        <v>3.364540723262911</v>
+      </c>
+      <c r="AR10">
+        <v>0.5719917185265165</v>
+      </c>
+      <c r="AS10">
+        <v>0.04823934841634513</v>
+      </c>
+      <c r="AT10" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:18">
+    <row r="11" spans="1:46">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="B11" s="2">
         <v>46253</v>
@@ -1039,7 +2020,7 @@
         <v>46252</v>
       </c>
       <c r="D11" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -1048,13 +2029,13 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>1.330725565828205</v>
+        <v>1.336874444188156</v>
       </c>
       <c r="H11">
         <v>2.933297564712426</v>
       </c>
       <c r="I11">
-        <v>0.6350728168078831</v>
+        <v>0.6350946885528048</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -1069,18 +2050,102 @@
         <v>5</v>
       </c>
       <c r="N11">
-        <v>-328.9001429974933</v>
+        <v>-328.4828586965857</v>
       </c>
       <c r="O11">
-        <v>-4.670739675773867</v>
+        <v>-4.707503349116804</v>
       </c>
       <c r="P11">
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>1.330725565828205</v>
-      </c>
-      <c r="R11" t="b">
+        <v>1.336874444188156</v>
+      </c>
+      <c r="R11" t="s">
+        <v>58</v>
+      </c>
+      <c r="S11" t="s">
+        <v>62</v>
+      </c>
+      <c r="T11">
+        <v>0.8880681771351673</v>
+      </c>
+      <c r="U11">
+        <v>0.7989147895991404</v>
+      </c>
+      <c r="V11" t="s">
+        <v>56</v>
+      </c>
+      <c r="W11" t="s">
+        <v>66</v>
+      </c>
+      <c r="X11">
+        <v>0.9903685337044204</v>
+      </c>
+      <c r="Y11">
+        <v>0.9971364395532607</v>
+      </c>
+      <c r="Z11">
+        <v>0.00676790584884035</v>
+      </c>
+      <c r="AA11">
+        <v>0.2583244267815755</v>
+      </c>
+      <c r="AB11">
+        <v>42.11784220552273</v>
+      </c>
+      <c r="AC11">
+        <v>-30</v>
+      </c>
+      <c r="AD11">
+        <v>0.7417670306461555</v>
+      </c>
+      <c r="AE11">
+        <v>0.6706576416073893</v>
+      </c>
+      <c r="AF11">
+        <v>1.681810603706029</v>
+      </c>
+      <c r="AG11">
+        <v>1.67699463738235</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI11" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ11" t="s">
+        <v>69</v>
+      </c>
+      <c r="AK11" t="s">
+        <v>73</v>
+      </c>
+      <c r="AL11">
+        <v>0.4653553866800869</v>
+      </c>
+      <c r="AM11">
+        <v>0.7668314562053249</v>
+      </c>
+      <c r="AN11">
+        <v>1.134248265310175</v>
+      </c>
+      <c r="AO11">
+        <v>1.219731614639799</v>
+      </c>
+      <c r="AP11">
+        <v>1.144886056015245</v>
+      </c>
+      <c r="AQ11">
+        <v>-3.613848854316405</v>
+      </c>
+      <c r="AR11">
+        <v>0.9875081275617564</v>
+      </c>
+      <c r="AS11">
+        <v>0.04240861458985336</v>
+      </c>
+      <c r="AT11" t="b">
         <v>1</v>
       </c>
     </row>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="77">
   <si>
     <t>Pair</t>
   </si>
@@ -67,6 +67,90 @@
     <t>TerrainBundleSep</t>
   </si>
   <si>
+    <t>MarketPosture</t>
+  </si>
+  <si>
+    <t>MarketPostureCN</t>
+  </si>
+  <si>
+    <t>MarketPostureScore</t>
+  </si>
+  <si>
+    <t>MarketPostureConfidence</t>
+  </si>
+  <si>
+    <t>PhasedDirection</t>
+  </si>
+  <si>
+    <t>PhasedAlignment</t>
+  </si>
+  <si>
+    <t>PhasedRawCoherence</t>
+  </si>
+  <si>
+    <t>PhasedCoherence</t>
+  </si>
+  <si>
+    <t>PhasedSteeringGain</t>
+  </si>
+  <si>
+    <t>PhasedGate</t>
+  </si>
+  <si>
+    <t>PhasedBeamPhaseDeg</t>
+  </si>
+  <si>
+    <t>PhasedGradientDeg</t>
+  </si>
+  <si>
+    <t>PhasedDirectionScore</t>
+  </si>
+  <si>
+    <t>PhasedImpulseScore</t>
+  </si>
+  <si>
+    <t>PhasedAmplitude</t>
+  </si>
+  <si>
+    <t>PhasedPower</t>
+  </si>
+  <si>
+    <t>SurveyTrend</t>
+  </si>
+  <si>
+    <t>SurveyTrendCN</t>
+  </si>
+  <si>
+    <t>TerrainPattern</t>
+  </si>
+  <si>
+    <t>TerrainPatternCN</t>
+  </si>
+  <si>
+    <t>SurveyDirectionScore</t>
+  </si>
+  <si>
+    <t>SurveyConfidence</t>
+  </si>
+  <si>
+    <t>ContourElevation</t>
+  </si>
+  <si>
+    <t>ContourTemporalSlope</t>
+  </si>
+  <si>
+    <t>ContourScaleSlope</t>
+  </si>
+  <si>
+    <t>ContourCurvature</t>
+  </si>
+  <si>
+    <t>ContourRelief</t>
+  </si>
+  <si>
+    <t>ContourRoughness</t>
+  </si>
+  <si>
     <t>FilterEnabled</t>
   </si>
   <si>
@@ -104,6 +188,63 @@
   </si>
   <si>
     <t>DOWN</t>
+  </si>
+  <si>
+    <t>UP_ACCELERATING</t>
+  </si>
+  <si>
+    <t>UP_DECELERATING</t>
+  </si>
+  <si>
+    <t>DOWN_STEADY</t>
+  </si>
+  <si>
+    <t>DOWN_DECELERATING</t>
+  </si>
+  <si>
+    <t>多头加速</t>
+  </si>
+  <si>
+    <t>多头减速</t>
+  </si>
+  <si>
+    <t>空头稳态</t>
+  </si>
+  <si>
+    <t>空头减速</t>
+  </si>
+  <si>
+    <t>ALIGNED</t>
+  </si>
+  <si>
+    <t>上涨</t>
+  </si>
+  <si>
+    <t>下跌</t>
+  </si>
+  <si>
+    <t>UP_STEEPENING</t>
+  </si>
+  <si>
+    <t>UP_CREST_FLATTENING</t>
+  </si>
+  <si>
+    <t>DOWN_SLOPE</t>
+  </si>
+  <si>
+    <t>DOWN_VALLEY_FLATTENING</t>
+  </si>
+  <si>
+    <t>上升陡坡形成</t>
+  </si>
+  <si>
+    <t>上升坡顶钝化</t>
+  </si>
+  <si>
+    <t>下降坡延续</t>
+  </si>
+  <si>
+    <t>下降谷底收敛</t>
   </si>
 </sst>
 </file>
@@ -465,10 +606,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:AT11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:46">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -523,10 +664,94 @@
       <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>45</v>
+      </c>
     </row>
-    <row r="2" spans="1:18">
+    <row r="2" spans="1:46">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="B2" s="2">
         <v>46254</v>
@@ -535,7 +760,7 @@
         <v>46253</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -576,13 +801,97 @@
       <c r="Q2">
         <v>0.4840309185698284</v>
       </c>
-      <c r="R2" t="b">
+      <c r="R2" t="s">
+        <v>58</v>
+      </c>
+      <c r="S2" t="s">
+        <v>62</v>
+      </c>
+      <c r="T2">
+        <v>0.8497579668037913</v>
+      </c>
+      <c r="U2">
+        <v>0.7823822726760881</v>
+      </c>
+      <c r="V2" t="s">
+        <v>56</v>
+      </c>
+      <c r="W2" t="s">
+        <v>66</v>
+      </c>
+      <c r="X2">
+        <v>0.9993678140071486</v>
+      </c>
+      <c r="Y2">
+        <v>0.9999647504575279</v>
+      </c>
+      <c r="Z2">
+        <v>0.0005969364503792818</v>
+      </c>
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>55.94453004495183</v>
+      </c>
+      <c r="AC2">
+        <v>7.999999999999998</v>
+      </c>
+      <c r="AD2">
+        <v>0.5599952602082706</v>
+      </c>
+      <c r="AE2">
+        <v>0.8284958108187822</v>
+      </c>
+      <c r="AF2">
+        <v>0.6828711292303203</v>
+      </c>
+      <c r="AG2">
+        <v>0.6828470583354476</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>69</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AL2">
+        <v>0.2799877603157809</v>
+      </c>
+      <c r="AM2">
+        <v>0.6594540373169837</v>
+      </c>
+      <c r="AN2">
+        <v>0.3913817078300837</v>
+      </c>
+      <c r="AO2">
+        <v>0.5590562862638696</v>
+      </c>
+      <c r="AP2">
+        <v>0.4842945765041812</v>
+      </c>
+      <c r="AQ2">
+        <v>-0.6991426692546785</v>
+      </c>
+      <c r="AR2">
+        <v>0.4179375416273116</v>
+      </c>
+      <c r="AS2">
+        <v>0.05688135603754795</v>
+      </c>
+      <c r="AT2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:18">
+    <row r="3" spans="1:46">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="B3" s="2">
         <v>46254</v>
@@ -591,22 +900,22 @@
         <v>46253</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3">
-        <v>0.05736538233206671</v>
+        <v>0.01636935260508167</v>
       </c>
       <c r="G3">
-        <v>1.462360520978653</v>
+        <v>1.426871435149012</v>
       </c>
       <c r="H3">
         <v>1.835759411487671</v>
       </c>
       <c r="I3">
-        <v>0.4217913326304084</v>
+        <v>0.4227275282709423</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -618,27 +927,111 @@
         <v>225</v>
       </c>
       <c r="M3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N3">
-        <v>-0.02478284423415636</v>
+        <v>-0.02646270850907976</v>
       </c>
       <c r="O3">
-        <v>-7.842672225998837</v>
+        <v>-8.374274844645482</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>1.462360520978653</v>
-      </c>
-      <c r="R3" t="b">
+        <v>1.426871435149012</v>
+      </c>
+      <c r="R3" t="s">
+        <v>58</v>
+      </c>
+      <c r="S3" t="s">
+        <v>62</v>
+      </c>
+      <c r="T3">
+        <v>0.9252029799917924</v>
+      </c>
+      <c r="U3">
+        <v>0.8187948620166103</v>
+      </c>
+      <c r="V3" t="s">
+        <v>56</v>
+      </c>
+      <c r="W3" t="s">
+        <v>66</v>
+      </c>
+      <c r="X3">
+        <v>0.9998896238994841</v>
+      </c>
+      <c r="Y3">
+        <v>0.999992472518166</v>
+      </c>
+      <c r="Z3">
+        <v>0.0001028486186819277</v>
+      </c>
+      <c r="AA3">
+        <v>0.2038960067893222</v>
+      </c>
+      <c r="AB3">
+        <v>34.9406006058263</v>
+      </c>
+      <c r="AC3">
+        <v>3.000000000000004</v>
+      </c>
+      <c r="AD3">
+        <v>0.8197462392755892</v>
+      </c>
+      <c r="AE3">
+        <v>0.5727269010562788</v>
+      </c>
+      <c r="AF3">
+        <v>1.390963687493974</v>
+      </c>
+      <c r="AG3">
+        <v>1.390953217040084</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>69</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>73</v>
+      </c>
+      <c r="AL3">
+        <v>0.49344089762687</v>
+      </c>
+      <c r="AM3">
+        <v>0.7803073031970221</v>
+      </c>
+      <c r="AN3">
+        <v>1.145284586633104</v>
+      </c>
+      <c r="AO3">
+        <v>0.789098290569426</v>
+      </c>
+      <c r="AP3">
+        <v>1.484843873573096</v>
+      </c>
+      <c r="AQ3">
+        <v>-2.174224443684099</v>
+      </c>
+      <c r="AR3">
+        <v>1.295532618310246</v>
+      </c>
+      <c r="AS3">
+        <v>0.04262090216584771</v>
+      </c>
+      <c r="AT3" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:18">
+    <row r="4" spans="1:46">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="B4" s="2">
         <v>46254</v>
@@ -647,7 +1040,7 @@
         <v>46253</v>
       </c>
       <c r="D4" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -688,13 +1081,97 @@
       <c r="Q4">
         <v>0.6668790474455911</v>
       </c>
-      <c r="R4" t="b">
+      <c r="R4" t="s">
+        <v>58</v>
+      </c>
+      <c r="S4" t="s">
+        <v>62</v>
+      </c>
+      <c r="T4">
+        <v>0.7948947594915265</v>
+      </c>
+      <c r="U4">
+        <v>0.7576991604779089</v>
+      </c>
+      <c r="V4" t="s">
+        <v>56</v>
+      </c>
+      <c r="W4" t="s">
+        <v>66</v>
+      </c>
+      <c r="X4">
+        <v>0.9979039210931534</v>
+      </c>
+      <c r="Y4">
+        <v>0.9999860748268876</v>
+      </c>
+      <c r="Z4">
+        <v>0.002082153733734216</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>66.46375324164961</v>
+      </c>
+      <c r="AC4">
+        <v>13.00000000000001</v>
+      </c>
+      <c r="AD4">
+        <v>0.3993291444769469</v>
+      </c>
+      <c r="AE4">
+        <v>0.9168076321515379</v>
+      </c>
+      <c r="AF4">
+        <v>1.282974819714418</v>
+      </c>
+      <c r="AG4">
+        <v>1.282956954067955</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>69</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>73</v>
+      </c>
+      <c r="AL4">
+        <v>0.1996617918747406</v>
+      </c>
+      <c r="AM4">
+        <v>0.608347542252906</v>
+      </c>
+      <c r="AN4">
+        <v>0.5353949232934802</v>
+      </c>
+      <c r="AO4">
+        <v>1.162963241903283</v>
+      </c>
+      <c r="AP4">
+        <v>0.6691324286627586</v>
+      </c>
+      <c r="AQ4">
+        <v>-0.6677289918141179</v>
+      </c>
+      <c r="AR4">
+        <v>0.6048684398241793</v>
+      </c>
+      <c r="AS4">
+        <v>0.07630884853059125</v>
+      </c>
+      <c r="AT4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:18">
+    <row r="5" spans="1:46">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="B5" s="2">
         <v>46254</v>
@@ -703,7 +1180,7 @@
         <v>46253</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -712,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="G5">
-        <v>2.129642440989339</v>
+        <v>2.098247299854969</v>
       </c>
       <c r="H5">
-        <v>1.431530087839597</v>
+        <v>1.419556388814656</v>
       </c>
       <c r="I5">
-        <v>0.2993641151958319</v>
+        <v>0.2990391935706503</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -733,24 +1210,108 @@
         <v>10</v>
       </c>
       <c r="N5">
-        <v>-0.03008086229714194</v>
+        <v>-0.02995735047859306</v>
       </c>
       <c r="O5">
-        <v>-8.895903509927836</v>
+        <v>-8.859376989866909</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>2.129642440989339</v>
-      </c>
-      <c r="R5" t="b">
+        <v>2.098247299854969</v>
+      </c>
+      <c r="R5" t="s">
+        <v>58</v>
+      </c>
+      <c r="S5" t="s">
+        <v>62</v>
+      </c>
+      <c r="T5">
+        <v>0.8372223440523791</v>
+      </c>
+      <c r="U5">
+        <v>0.926727600597396</v>
+      </c>
+      <c r="V5" t="s">
+        <v>56</v>
+      </c>
+      <c r="W5" t="s">
+        <v>66</v>
+      </c>
+      <c r="X5">
+        <v>0.9976529802611901</v>
+      </c>
+      <c r="Y5">
+        <v>0.9999101830953019</v>
+      </c>
+      <c r="Z5">
+        <v>0.002257202834111793</v>
+      </c>
+      <c r="AA5">
+        <v>1</v>
+      </c>
+      <c r="AB5">
+        <v>47.59009277023014</v>
+      </c>
+      <c r="AC5">
+        <v>14.00000000000001</v>
+      </c>
+      <c r="AD5">
+        <v>0.6744300666062889</v>
+      </c>
+      <c r="AE5">
+        <v>0.7383387334126774</v>
+      </c>
+      <c r="AF5">
+        <v>2.347568443558294</v>
+      </c>
+      <c r="AG5">
+        <v>2.347357592227127</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>73</v>
+      </c>
+      <c r="AL5">
+        <v>0.674369491385271</v>
+      </c>
+      <c r="AM5">
+        <v>0.8942277757563757</v>
+      </c>
+      <c r="AN5">
+        <v>1.620148793511938</v>
+      </c>
+      <c r="AO5">
+        <v>1.691258887943281</v>
+      </c>
+      <c r="AP5">
+        <v>2.448955539854732</v>
+      </c>
+      <c r="AQ5">
+        <v>-2.030293092778862</v>
+      </c>
+      <c r="AR5">
+        <v>2.26216891955886</v>
+      </c>
+      <c r="AS5">
+        <v>0.05379872205911085</v>
+      </c>
+      <c r="AT5" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:18">
+    <row r="6" spans="1:46">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="B6" s="2">
         <v>46254</v>
@@ -759,7 +1320,7 @@
         <v>46253</v>
       </c>
       <c r="D6" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -800,13 +1361,97 @@
       <c r="Q6">
         <v>0.5781780700216143</v>
       </c>
-      <c r="R6" t="b">
+      <c r="R6" t="s">
+        <v>58</v>
+      </c>
+      <c r="S6" t="s">
+        <v>62</v>
+      </c>
+      <c r="T6">
+        <v>0.8843281615246334</v>
+      </c>
+      <c r="U6">
+        <v>0.7979403523348219</v>
+      </c>
+      <c r="V6" t="s">
+        <v>56</v>
+      </c>
+      <c r="W6" t="s">
+        <v>66</v>
+      </c>
+      <c r="X6">
+        <v>0.999495171204298</v>
+      </c>
+      <c r="Y6">
+        <v>0.9999707185949473</v>
+      </c>
+      <c r="Z6">
+        <v>0.0004755473906493668</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>48.6054717682086</v>
+      </c>
+      <c r="AC6">
+        <v>6.999999999999997</v>
+      </c>
+      <c r="AD6">
+        <v>0.6612402264225222</v>
+      </c>
+      <c r="AE6">
+        <v>0.7501742217383183</v>
+      </c>
+      <c r="AF6">
+        <v>0.6768927066919158</v>
+      </c>
+      <c r="AG6">
+        <v>0.676872886322394</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>69</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>73</v>
+      </c>
+      <c r="AL6">
+        <v>0.3306104321898076</v>
+      </c>
+      <c r="AM6">
+        <v>0.6903604912104218</v>
+      </c>
+      <c r="AN6">
+        <v>0.4542375573949776</v>
+      </c>
+      <c r="AO6">
+        <v>0.5013875605815916</v>
+      </c>
+      <c r="AP6">
+        <v>0.6464621698535724</v>
+      </c>
+      <c r="AQ6">
+        <v>-0.836181056609497</v>
+      </c>
+      <c r="AR6">
+        <v>0.5620402351596001</v>
+      </c>
+      <c r="AS6">
+        <v>0.05334218816377579</v>
+      </c>
+      <c r="AT6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18">
+    <row r="7" spans="1:46">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="B7" s="2">
         <v>46254</v>
@@ -815,7 +1460,7 @@
         <v>46253</v>
       </c>
       <c r="D7" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -824,13 +1469,13 @@
         <v>1</v>
       </c>
       <c r="G7">
-        <v>2.518479144418527</v>
+        <v>2.476432103856031</v>
       </c>
       <c r="H7">
-        <v>1.363748106993944</v>
+        <v>1.362206492418323</v>
       </c>
       <c r="I7">
-        <v>0.3098375708661356</v>
+        <v>0.3102325871194744</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -839,30 +1484,114 @@
         <v>1</v>
       </c>
       <c r="L7">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="M7">
         <v>13</v>
       </c>
       <c r="N7">
-        <v>-0.05779815190814176</v>
+        <v>-0.05895605980843035</v>
       </c>
       <c r="O7">
-        <v>-14.62583148149993</v>
+        <v>-14.91884025879844</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>2.518479144418527</v>
-      </c>
-      <c r="R7" t="b">
+        <v>2.476432103856031</v>
+      </c>
+      <c r="R7" t="s">
+        <v>58</v>
+      </c>
+      <c r="S7" t="s">
+        <v>62</v>
+      </c>
+      <c r="T7">
+        <v>0.911331543491438</v>
+      </c>
+      <c r="U7">
+        <v>0.9600891646449576</v>
+      </c>
+      <c r="V7" t="s">
+        <v>56</v>
+      </c>
+      <c r="W7" t="s">
+        <v>66</v>
+      </c>
+      <c r="X7">
+        <v>0.9993878998345654</v>
+      </c>
+      <c r="Y7">
+        <v>0.9999598802952427</v>
+      </c>
+      <c r="Z7">
+        <v>0.0005719804606773016</v>
+      </c>
+      <c r="AA7">
+        <v>1</v>
+      </c>
+      <c r="AB7">
+        <v>34.64808410787485</v>
+      </c>
+      <c r="AC7">
+        <v>6.999999999999997</v>
+      </c>
+      <c r="AD7">
+        <v>0.8226595294878541</v>
+      </c>
+      <c r="AE7">
+        <v>0.5685343424480375</v>
+      </c>
+      <c r="AF7">
+        <v>2.274815151729783</v>
+      </c>
+      <c r="AG7">
+        <v>2.274723886817518</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ7" t="s">
+        <v>69</v>
+      </c>
+      <c r="AK7" t="s">
+        <v>73</v>
+      </c>
+      <c r="AL7">
+        <v>0.8226265246304153</v>
+      </c>
+      <c r="AM7">
+        <v>0.9397469757820209</v>
+      </c>
+      <c r="AN7">
+        <v>1.886753805740311</v>
+      </c>
+      <c r="AO7">
+        <v>1.268310300213958</v>
+      </c>
+      <c r="AP7">
+        <v>3.034765938404792</v>
+      </c>
+      <c r="AQ7">
+        <v>-2.617596247757652</v>
+      </c>
+      <c r="AR7">
+        <v>2.782946818459877</v>
+      </c>
+      <c r="AS7">
+        <v>0.04691227445113542</v>
+      </c>
+      <c r="AT7" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:18">
+    <row r="8" spans="1:46">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="B8" s="2">
         <v>46254</v>
@@ -871,7 +1600,7 @@
         <v>46253</v>
       </c>
       <c r="D8" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -880,19 +1609,19 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>0.02812122986921546</v>
+        <v>0.03701447009399642</v>
       </c>
       <c r="H8">
-        <v>1.439361163203861</v>
+        <v>1.430598425220382</v>
       </c>
       <c r="I8">
-        <v>0.3563285098253159</v>
+        <v>0.3522896653464405</v>
       </c>
       <c r="J8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K8">
-        <v>0.8333333333333334</v>
+        <v>1</v>
       </c>
       <c r="L8">
         <v>111</v>
@@ -901,24 +1630,108 @@
         <v>54</v>
       </c>
       <c r="N8">
-        <v>-0.2928680517107408</v>
+        <v>-0.2892683796623388</v>
       </c>
       <c r="O8">
-        <v>-65.30985543087588</v>
+        <v>-74.61551939701083</v>
       </c>
       <c r="P8">
-        <v>0.8434569334510645</v>
+        <v>0.8490359336455062</v>
       </c>
       <c r="Q8">
-        <v>0.179638935720125</v>
-      </c>
-      <c r="R8" t="b">
+        <v>0.2451872885238733</v>
+      </c>
+      <c r="R8" t="s">
+        <v>59</v>
+      </c>
+      <c r="S8" t="s">
+        <v>63</v>
+      </c>
+      <c r="T8">
+        <v>0.6853787671500985</v>
+      </c>
+      <c r="U8">
+        <v>0.70811771335306</v>
+      </c>
+      <c r="V8" t="s">
+        <v>56</v>
+      </c>
+      <c r="W8" t="s">
+        <v>66</v>
+      </c>
+      <c r="X8">
+        <v>0.9943626590928096</v>
+      </c>
+      <c r="Y8">
+        <v>0.9987890725420626</v>
+      </c>
+      <c r="Z8">
+        <v>0.004426413449252986</v>
+      </c>
+      <c r="AA8">
+        <v>0.1539430924141814</v>
+      </c>
+      <c r="AB8">
+        <v>-77.70524749282117</v>
+      </c>
+      <c r="AC8">
+        <v>-18</v>
+      </c>
+      <c r="AD8">
+        <v>0.2129409016590923</v>
+      </c>
+      <c r="AE8">
+        <v>-0.9770650809442597</v>
+      </c>
+      <c r="AF8">
+        <v>1.12845782350404</v>
+      </c>
+      <c r="AG8">
+        <v>1.127091342940434</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ8" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK8" t="s">
+        <v>74</v>
+      </c>
+      <c r="AL8">
+        <v>0.1227120657147661</v>
+      </c>
+      <c r="AM8">
+        <v>0.576325034692154</v>
+      </c>
+      <c r="AN8">
+        <v>0.257825198952521</v>
+      </c>
+      <c r="AO8">
+        <v>-1.092074321074909</v>
+      </c>
+      <c r="AP8">
+        <v>0.04268234739644627</v>
+      </c>
+      <c r="AQ8">
+        <v>-2.283244132581187</v>
+      </c>
+      <c r="AR8">
+        <v>0.4092268280514446</v>
+      </c>
+      <c r="AS8">
+        <v>0.1194801978542123</v>
+      </c>
+      <c r="AT8" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:18">
+    <row r="9" spans="1:46">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="B9" s="2">
         <v>46254</v>
@@ -927,22 +1740,22 @@
         <v>46253</v>
       </c>
       <c r="D9" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="E9">
         <v>-1</v>
       </c>
       <c r="F9">
-        <v>0.8544308170286511</v>
+        <v>0.8346552579069189</v>
       </c>
       <c r="G9">
-        <v>3.373012898437886</v>
+        <v>3.344028327709457</v>
       </c>
       <c r="H9">
-        <v>2.947062866761466</v>
+        <v>2.942032932254917</v>
       </c>
       <c r="I9">
-        <v>0.6008930533289197</v>
+        <v>0.6006112050484369</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -957,24 +1770,108 @@
         <v>25</v>
       </c>
       <c r="N9">
-        <v>0.3197848231213114</v>
+        <v>0.3245653178023096</v>
       </c>
       <c r="O9">
-        <v>45.69986754145325</v>
+        <v>46.38303934295355</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>3.373012898437886</v>
-      </c>
-      <c r="R9" t="b">
+        <v>3.344028327709457</v>
+      </c>
+      <c r="R9" t="s">
+        <v>60</v>
+      </c>
+      <c r="S9" t="s">
+        <v>64</v>
+      </c>
+      <c r="T9">
+        <v>-0.9954595725036556</v>
+      </c>
+      <c r="U9">
+        <v>0.9730946571918411</v>
+      </c>
+      <c r="V9" t="s">
+        <v>57</v>
+      </c>
+      <c r="W9" t="s">
+        <v>66</v>
+      </c>
+      <c r="X9">
+        <v>0.9991919243572572</v>
+      </c>
+      <c r="Y9">
+        <v>0.9997582435166329</v>
+      </c>
+      <c r="Z9">
+        <v>0.0005663191593756611</v>
+      </c>
+      <c r="AA9">
+        <v>1</v>
+      </c>
+      <c r="AB9">
+        <v>-172.3768816259754</v>
+      </c>
+      <c r="AC9">
+        <v>6.999999999999997</v>
+      </c>
+      <c r="AD9">
+        <v>-0.9911620952036588</v>
+      </c>
+      <c r="AE9">
+        <v>-0.1326563267676789</v>
+      </c>
+      <c r="AF9">
+        <v>2.499947650591717</v>
+      </c>
+      <c r="AG9">
+        <v>2.499343272039108</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>57</v>
+      </c>
+      <c r="AI9" t="s">
+        <v>68</v>
+      </c>
+      <c r="AJ9" t="s">
+        <v>71</v>
+      </c>
+      <c r="AK9" t="s">
+        <v>75</v>
+      </c>
+      <c r="AL9">
+        <v>-0.9909224753410756</v>
+      </c>
+      <c r="AM9">
+        <v>0.9912305746941298</v>
+      </c>
+      <c r="AN9">
+        <v>-2.479793160044495</v>
+      </c>
+      <c r="AO9">
+        <v>-0.3004458313453518</v>
+      </c>
+      <c r="AP9">
+        <v>-4.410775866295087</v>
+      </c>
+      <c r="AQ9">
+        <v>2.520525211740795</v>
+      </c>
+      <c r="AR9">
+        <v>4.188109640161673</v>
+      </c>
+      <c r="AS9">
+        <v>0.04022292731859602</v>
+      </c>
+      <c r="AT9" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:18">
+    <row r="10" spans="1:46">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="B10" s="2">
         <v>46254</v>
@@ -983,7 +1880,7 @@
         <v>46253</v>
       </c>
       <c r="D10" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="E10">
         <v>-1</v>
@@ -992,13 +1889,13 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>1.298314982471483</v>
+        <v>1.224522360957086</v>
       </c>
       <c r="H10">
-        <v>2.044021782428824</v>
+        <v>2.039073692964579</v>
       </c>
       <c r="I10">
-        <v>0.4706022505198748</v>
+        <v>0.4647321926877153</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1010,27 +1907,111 @@
         <v>233</v>
       </c>
       <c r="M10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N10">
-        <v>11.49079771508749</v>
+        <v>12.32987707320468</v>
       </c>
       <c r="O10">
-        <v>14.35772841369319</v>
+        <v>15.4061563679652</v>
       </c>
       <c r="P10">
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>1.298314982471483</v>
-      </c>
-      <c r="R10" t="b">
+        <v>1.224522360957086</v>
+      </c>
+      <c r="R10" t="s">
+        <v>61</v>
+      </c>
+      <c r="S10" t="s">
+        <v>65</v>
+      </c>
+      <c r="T10">
+        <v>-0.9712772551812577</v>
+      </c>
+      <c r="U10">
+        <v>0.8358987908355353</v>
+      </c>
+      <c r="V10" t="s">
+        <v>57</v>
+      </c>
+      <c r="W10" t="s">
+        <v>66</v>
+      </c>
+      <c r="X10">
+        <v>0.9952519461167647</v>
+      </c>
+      <c r="Y10">
+        <v>0.9952961040158775</v>
+      </c>
+      <c r="Z10">
+        <v>4.415789911282886E-05</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>156.2941560896775</v>
+      </c>
+      <c r="AC10">
+        <v>-2.000000000000003</v>
+      </c>
+      <c r="AD10">
+        <v>-0.9156215917218425</v>
+      </c>
+      <c r="AE10">
+        <v>0.4020411680074063</v>
+      </c>
+      <c r="AF10">
+        <v>1.169384690176933</v>
+      </c>
+      <c r="AG10">
+        <v>1.163884026228915</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>57</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>68</v>
+      </c>
+      <c r="AJ10" t="s">
+        <v>72</v>
+      </c>
+      <c r="AK10" t="s">
+        <v>76</v>
+      </c>
+      <c r="AL10">
+        <v>-0.4556573014967832</v>
+      </c>
+      <c r="AM10">
+        <v>0.7664129892859401</v>
+      </c>
+      <c r="AN10">
+        <v>-1.068051724138155</v>
+      </c>
+      <c r="AO10">
+        <v>0.4623541320830815</v>
+      </c>
+      <c r="AP10">
+        <v>-0.893938406614134</v>
+      </c>
+      <c r="AQ10">
+        <v>2.801726646986756</v>
+      </c>
+      <c r="AR10">
+        <v>0.7061852967172343</v>
+      </c>
+      <c r="AS10">
+        <v>0.0441808309077974</v>
+      </c>
+      <c r="AT10" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:18">
+    <row r="11" spans="1:46">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="B11" s="2">
         <v>46254</v>
@@ -1039,7 +2020,7 @@
         <v>46253</v>
       </c>
       <c r="D11" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -1048,13 +2029,13 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>1.419803310739046</v>
+        <v>1.425699501519865</v>
       </c>
       <c r="H11">
         <v>2.895600718595243</v>
       </c>
       <c r="I11">
-        <v>0.6331914023436307</v>
+        <v>0.6332097085444153</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -1069,18 +2050,102 @@
         <v>6</v>
       </c>
       <c r="N11">
-        <v>-414.4376105677134</v>
+        <v>-413.716339274407</v>
       </c>
       <c r="O11">
-        <v>-5.282704616527888</v>
+        <v>-5.316787682813429</v>
       </c>
       <c r="P11">
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>1.419803310739046</v>
-      </c>
-      <c r="R11" t="b">
+        <v>1.425699501519865</v>
+      </c>
+      <c r="R11" t="s">
+        <v>58</v>
+      </c>
+      <c r="S11" t="s">
+        <v>62</v>
+      </c>
+      <c r="T11">
+        <v>0.9387787232160607</v>
+      </c>
+      <c r="U11">
+        <v>0.8220264675511796</v>
+      </c>
+      <c r="V11" t="s">
+        <v>56</v>
+      </c>
+      <c r="W11" t="s">
+        <v>66</v>
+      </c>
+      <c r="X11">
+        <v>0.9913913855410589</v>
+      </c>
+      <c r="Y11">
+        <v>0.9983041684158089</v>
+      </c>
+      <c r="Z11">
+        <v>0.006912782874750056</v>
+      </c>
+      <c r="AA11">
+        <v>0.06825432873385694</v>
+      </c>
+      <c r="AB11">
+        <v>33.50748502364006</v>
+      </c>
+      <c r="AC11">
+        <v>-28</v>
+      </c>
+      <c r="AD11">
+        <v>0.8338137108382806</v>
+      </c>
+      <c r="AE11">
+        <v>0.5520459180340854</v>
+      </c>
+      <c r="AF11">
+        <v>1.497835588717574</v>
+      </c>
+      <c r="AG11">
+        <v>1.495295511818301</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI11" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ11" t="s">
+        <v>69</v>
+      </c>
+      <c r="AK11" t="s">
+        <v>73</v>
+      </c>
+      <c r="AL11">
+        <v>0.4446072930965568</v>
+      </c>
+      <c r="AM11">
+        <v>0.7564924193643786</v>
+      </c>
+      <c r="AN11">
+        <v>1.173589067040108</v>
+      </c>
+      <c r="AO11">
+        <v>0.90980182733142</v>
+      </c>
+      <c r="AP11">
+        <v>1.36601229944368</v>
+      </c>
+      <c r="AQ11">
+        <v>-2.966708736995491</v>
+      </c>
+      <c r="AR11">
+        <v>1.09181223998737</v>
+      </c>
+      <c r="AS11">
+        <v>0.04472679052940127</v>
+      </c>
+      <c r="AT11" t="b">
         <v>1</v>
       </c>
     </row>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="78">
   <si>
     <t>Pair</t>
   </si>
@@ -193,10 +193,7 @@
     <t>UP_ACCELERATING</t>
   </si>
   <si>
-    <t>UP_DECELERATING</t>
-  </si>
-  <si>
-    <t>DOWN_STEADY</t>
+    <t>DOWN_ACCELERATING</t>
   </si>
   <si>
     <t>DOWN_DECELERATING</t>
@@ -205,31 +202,37 @@
     <t>多头加速</t>
   </si>
   <si>
-    <t>多头减速</t>
-  </si>
-  <si>
-    <t>空头稳态</t>
+    <t>空头加速</t>
   </si>
   <si>
     <t>空头减速</t>
   </si>
   <si>
+    <t>NEUTRAL</t>
+  </si>
+  <si>
     <t>ALIGNED</t>
   </si>
   <si>
+    <t>TRANSITION</t>
+  </si>
+  <si>
     <t>上涨</t>
   </si>
   <si>
+    <t>转换</t>
+  </si>
+  <si>
     <t>下跌</t>
   </si>
   <si>
     <t>UP_STEEPENING</t>
   </si>
   <si>
-    <t>UP_CREST_FLATTENING</t>
-  </si>
-  <si>
-    <t>DOWN_SLOPE</t>
+    <t>TRANSITION_ZONE</t>
+  </si>
+  <si>
+    <t>DOWN_STEEPENING</t>
   </si>
   <si>
     <t>DOWN_VALLEY_FLATTENING</t>
@@ -238,10 +241,10 @@
     <t>上升陡坡形成</t>
   </si>
   <si>
-    <t>上升坡顶钝化</t>
-  </si>
-  <si>
-    <t>下降坡延续</t>
+    <t>地形转换区</t>
+  </si>
+  <si>
+    <t>下降陡坡形成</t>
   </si>
   <si>
     <t>下降谷底收敛</t>
@@ -754,10 +757,10 @@
         <v>46</v>
       </c>
       <c r="B2" s="2">
+        <v>46255</v>
+      </c>
+      <c r="C2" s="2">
         <v>46254</v>
-      </c>
-      <c r="C2" s="2">
-        <v>46253</v>
       </c>
       <c r="D2" t="s">
         <v>56</v>
@@ -769,13 +772,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>0.4840309185698284</v>
+        <v>0.4901354772408594</v>
       </c>
       <c r="H2">
-        <v>1.066581877683632</v>
+        <v>1.067204660149961</v>
       </c>
       <c r="I2">
-        <v>0.2586991975303866</v>
+        <v>0.2587418598924733</v>
       </c>
       <c r="J2">
         <v>6</v>
@@ -787,67 +790,67 @@
         <v>149</v>
       </c>
       <c r="M2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N2">
-        <v>-0.04671111831577411</v>
+        <v>-0.06147580441985389</v>
       </c>
       <c r="O2">
-        <v>-1.250728027427682</v>
+        <v>-1.701046054782897</v>
       </c>
       <c r="P2">
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.4840309185698284</v>
+        <v>0.4901354772408594</v>
       </c>
       <c r="R2" t="s">
         <v>58</v>
       </c>
       <c r="S2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="T2">
-        <v>0.8497579668037913</v>
+        <v>0.8504698565259804</v>
       </c>
       <c r="U2">
-        <v>0.7823822726760881</v>
+        <v>0.7827089691119478</v>
       </c>
       <c r="V2" t="s">
         <v>56</v>
       </c>
       <c r="W2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="X2">
-        <v>0.9993678140071486</v>
+        <v>0.9988808947098438</v>
       </c>
       <c r="Y2">
-        <v>0.9999647504575279</v>
+        <v>0.999990134701026</v>
       </c>
       <c r="Z2">
-        <v>0.0005969364503792818</v>
+        <v>0.001109239991182287</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>55.94453004495183</v>
+        <v>55.79971796265564</v>
       </c>
       <c r="AC2">
-        <v>7.999999999999998</v>
+        <v>11</v>
       </c>
       <c r="AD2">
-        <v>0.5599952602082706</v>
+        <v>0.5620874491331316</v>
       </c>
       <c r="AE2">
-        <v>0.8284958108187822</v>
+        <v>0.8270778074202023</v>
       </c>
       <c r="AF2">
-        <v>0.6828711292303203</v>
+        <v>0.7104048331291635</v>
       </c>
       <c r="AG2">
-        <v>0.6828470583354476</v>
+        <v>0.7103978247730921</v>
       </c>
       <c r="AH2" t="s">
         <v>56</v>
@@ -856,34 +859,34 @@
         <v>67</v>
       </c>
       <c r="AJ2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AK2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AL2">
-        <v>0.2799877603157809</v>
+        <v>0.2810409519861982</v>
       </c>
       <c r="AM2">
-        <v>0.6594540373169837</v>
+        <v>0.6614995998291965</v>
       </c>
       <c r="AN2">
-        <v>0.3913817078300837</v>
+        <v>0.4126282140054479</v>
       </c>
       <c r="AO2">
-        <v>0.5590562862638696</v>
+        <v>0.5773075844022497</v>
       </c>
       <c r="AP2">
-        <v>0.4842945765041812</v>
+        <v>0.4232373049617013</v>
       </c>
       <c r="AQ2">
-        <v>-0.6991426692546785</v>
+        <v>-1.03499428405337</v>
       </c>
       <c r="AR2">
-        <v>0.4179375416273116</v>
+        <v>0.3494276594209536</v>
       </c>
       <c r="AS2">
-        <v>0.05688135603754795</v>
+        <v>0.04748788037401379</v>
       </c>
       <c r="AT2" t="b">
         <v>1</v>
@@ -894,10 +897,10 @@
         <v>47</v>
       </c>
       <c r="B3" s="2">
+        <v>46255</v>
+      </c>
+      <c r="C3" s="2">
         <v>46254</v>
-      </c>
-      <c r="C3" s="2">
-        <v>46253</v>
       </c>
       <c r="D3" t="s">
         <v>56</v>
@@ -906,16 +909,16 @@
         <v>1</v>
       </c>
       <c r="F3">
-        <v>0.01636935260508167</v>
+        <v>0.4236656675179737</v>
       </c>
       <c r="G3">
-        <v>1.426871435149012</v>
+        <v>1.77162634908774</v>
       </c>
       <c r="H3">
-        <v>1.835759411487671</v>
+        <v>1.836067718063164</v>
       </c>
       <c r="I3">
-        <v>0.4227275282709423</v>
+        <v>0.4220995119764617</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -927,67 +930,67 @@
         <v>225</v>
       </c>
       <c r="M3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N3">
-        <v>-0.02646270850907976</v>
+        <v>-0.03054736659367293</v>
       </c>
       <c r="O3">
-        <v>-8.374274844645482</v>
+        <v>-9.091478152878832</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>1.426871435149012</v>
+        <v>1.77162634908774</v>
       </c>
       <c r="R3" t="s">
         <v>58</v>
       </c>
       <c r="S3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="T3">
-        <v>0.9252029799917924</v>
+        <v>0.8848405598661534</v>
       </c>
       <c r="U3">
-        <v>0.8187948620166103</v>
+        <v>0.8617267344551464</v>
       </c>
       <c r="V3" t="s">
         <v>56</v>
       </c>
       <c r="W3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="X3">
-        <v>0.9998896238994841</v>
+        <v>0.9994221359182794</v>
       </c>
       <c r="Y3">
-        <v>0.999992472518166</v>
+        <v>0.9999945295507252</v>
       </c>
       <c r="Z3">
-        <v>0.0001028486186819277</v>
+        <v>0.0005723936324457668</v>
       </c>
       <c r="AA3">
-        <v>0.2038960067893222</v>
+        <v>0.728906953090797</v>
       </c>
       <c r="AB3">
-        <v>34.9406006058263</v>
+        <v>39.53535493000027</v>
       </c>
       <c r="AC3">
-        <v>3.000000000000004</v>
+        <v>6.999999999999997</v>
       </c>
       <c r="AD3">
-        <v>0.8197462392755892</v>
+        <v>0.77123193812414</v>
       </c>
       <c r="AE3">
-        <v>0.5727269010562788</v>
+        <v>0.6365542377655518</v>
       </c>
       <c r="AF3">
-        <v>1.390963687493974</v>
+        <v>1.738427390205434</v>
       </c>
       <c r="AG3">
-        <v>1.390953217040084</v>
+        <v>1.738417880226578</v>
       </c>
       <c r="AH3" t="s">
         <v>56</v>
@@ -996,34 +999,34 @@
         <v>67</v>
       </c>
       <c r="AJ3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AK3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AL3">
-        <v>0.49344089762687</v>
+        <v>0.6666904830178377</v>
       </c>
       <c r="AM3">
-        <v>0.7803073031970221</v>
+        <v>0.8695223443438814</v>
       </c>
       <c r="AN3">
-        <v>1.145284586633104</v>
+        <v>1.354231212924323</v>
       </c>
       <c r="AO3">
-        <v>0.789098290569426</v>
+        <v>1.088437348502598</v>
       </c>
       <c r="AP3">
-        <v>1.484843873573096</v>
+        <v>2.132516225977054</v>
       </c>
       <c r="AQ3">
-        <v>-2.174224443684099</v>
+        <v>-1.543205890574448</v>
       </c>
       <c r="AR3">
-        <v>1.295532618310246</v>
+        <v>1.990644408001752</v>
       </c>
       <c r="AS3">
-        <v>0.04262090216584771</v>
+        <v>0.05084475369515897</v>
       </c>
       <c r="AT3" t="b">
         <v>1</v>
@@ -1034,10 +1037,10 @@
         <v>48</v>
       </c>
       <c r="B4" s="2">
+        <v>46255</v>
+      </c>
+      <c r="C4" s="2">
         <v>46254</v>
-      </c>
-      <c r="C4" s="2">
-        <v>46253</v>
       </c>
       <c r="D4" t="s">
         <v>56</v>
@@ -1049,13 +1052,13 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>0.5165323702993595</v>
+        <v>0.8685446894451283</v>
       </c>
       <c r="H4">
-        <v>2.071622406597695</v>
+        <v>2.072535973374165</v>
       </c>
       <c r="I4">
-        <v>0.497690374729404</v>
+        <v>0.4977095437432331</v>
       </c>
       <c r="J4">
         <v>6</v>
@@ -1067,67 +1070,67 @@
         <v>146</v>
       </c>
       <c r="M4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N4">
-        <v>-0.02036889182336925</v>
+        <v>-0.03870213822948498</v>
       </c>
       <c r="O4">
-        <v>-0.6893025997756115</v>
+        <v>-1.422499173569947</v>
       </c>
       <c r="P4">
-        <v>0.225448194424639</v>
+        <v>0.09592243187937763</v>
       </c>
       <c r="Q4">
-        <v>0.6668790474455911</v>
+        <v>0.9606970906828725</v>
       </c>
       <c r="R4" t="s">
         <v>58</v>
       </c>
       <c r="S4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="T4">
-        <v>0.7948947594915265</v>
+        <v>0.6831823310055514</v>
       </c>
       <c r="U4">
-        <v>0.7576991604779089</v>
+        <v>0.7074302466322477</v>
       </c>
       <c r="V4" t="s">
         <v>56</v>
       </c>
       <c r="W4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="X4">
-        <v>0.9979039210931534</v>
+        <v>0.9983119301592075</v>
       </c>
       <c r="Y4">
-        <v>0.9999860748268876</v>
+        <v>0.9999927907189984</v>
       </c>
       <c r="Z4">
-        <v>0.002082153733734216</v>
+        <v>0.001680860559790887</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>0.6442016024401184</v>
       </c>
       <c r="AB4">
-        <v>66.46375324164961</v>
+        <v>66.10936809713229</v>
       </c>
       <c r="AC4">
-        <v>13.00000000000001</v>
+        <v>12</v>
       </c>
       <c r="AD4">
-        <v>0.3993291444769469</v>
+        <v>0.4049920970587502</v>
       </c>
       <c r="AE4">
-        <v>0.9168076321515379</v>
+        <v>0.9143201853398818</v>
       </c>
       <c r="AF4">
-        <v>1.282974819714418</v>
+        <v>1.816145925980495</v>
       </c>
       <c r="AG4">
-        <v>1.282956954067955</v>
+        <v>1.816132832874175</v>
       </c>
       <c r="AH4" t="s">
         <v>56</v>
@@ -1136,34 +1139,34 @@
         <v>67</v>
       </c>
       <c r="AJ4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AK4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AL4">
-        <v>0.1996617918747406</v>
+        <v>0.3329419271905759</v>
       </c>
       <c r="AM4">
-        <v>0.608347542252906</v>
+        <v>0.7400069032371405</v>
       </c>
       <c r="AN4">
-        <v>0.5353949232934802</v>
+        <v>0.7661801512332116</v>
       </c>
       <c r="AO4">
-        <v>1.162963241903283</v>
+        <v>1.64323692369165</v>
       </c>
       <c r="AP4">
-        <v>0.6691324286627586</v>
+        <v>1.00420965457867</v>
       </c>
       <c r="AQ4">
-        <v>-0.6677289918141179</v>
+        <v>-1.246062843434765</v>
       </c>
       <c r="AR4">
-        <v>0.6048684398241793</v>
+        <v>0.8743558278062863</v>
       </c>
       <c r="AS4">
-        <v>0.07630884853059125</v>
+        <v>0.06885682080105154</v>
       </c>
       <c r="AT4" t="b">
         <v>1</v>
@@ -1174,10 +1177,10 @@
         <v>49</v>
       </c>
       <c r="B5" s="2">
+        <v>46255</v>
+      </c>
+      <c r="C5" s="2">
         <v>46254</v>
-      </c>
-      <c r="C5" s="2">
-        <v>46253</v>
       </c>
       <c r="D5" t="s">
         <v>56</v>
@@ -1189,13 +1192,13 @@
         <v>1</v>
       </c>
       <c r="G5">
-        <v>2.098247299854969</v>
+        <v>2.559319104838145</v>
       </c>
       <c r="H5">
-        <v>1.419556388814656</v>
+        <v>1.424350071335205</v>
       </c>
       <c r="I5">
-        <v>0.2990391935706503</v>
+        <v>0.3003249864145023</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -1207,67 +1210,67 @@
         <v>226</v>
       </c>
       <c r="M5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N5">
-        <v>-0.02995735047859306</v>
+        <v>-0.03601760576859788</v>
       </c>
       <c r="O5">
-        <v>-8.859376989866909</v>
+        <v>-10.57896739243401</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>2.098247299854969</v>
+        <v>2.559319104838145</v>
       </c>
       <c r="R5" t="s">
         <v>58</v>
       </c>
       <c r="S5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="T5">
-        <v>0.8372223440523791</v>
+        <v>0.8318112568274303</v>
       </c>
       <c r="U5">
-        <v>0.926727600597396</v>
+        <v>0.9243073098068914</v>
       </c>
       <c r="V5" t="s">
         <v>56</v>
       </c>
       <c r="W5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="X5">
-        <v>0.9976529802611901</v>
+        <v>0.9986584258068262</v>
       </c>
       <c r="Y5">
-        <v>0.9999101830953019</v>
+        <v>0.9999689769381911</v>
       </c>
       <c r="Z5">
-        <v>0.002257202834111793</v>
+        <v>0.001310551131364912</v>
       </c>
       <c r="AA5">
         <v>1</v>
       </c>
       <c r="AB5">
-        <v>47.59009277023014</v>
+        <v>48.42366466301528</v>
       </c>
       <c r="AC5">
-        <v>14.00000000000001</v>
+        <v>11</v>
       </c>
       <c r="AD5">
-        <v>0.6744300666062889</v>
+        <v>0.6636172957632107</v>
       </c>
       <c r="AE5">
-        <v>0.7383387334126774</v>
+        <v>0.7480722456848158</v>
       </c>
       <c r="AF5">
-        <v>2.347568443558294</v>
+        <v>2.883489274778532</v>
       </c>
       <c r="AG5">
-        <v>2.347357592227127</v>
+        <v>2.883399820112535</v>
       </c>
       <c r="AH5" t="s">
         <v>56</v>
@@ -1276,34 +1279,34 @@
         <v>67</v>
       </c>
       <c r="AJ5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AK5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AL5">
-        <v>0.674369491385271</v>
+        <v>0.6635967083228268</v>
       </c>
       <c r="AM5">
-        <v>0.8942277757563757</v>
+        <v>0.8907372185570044</v>
       </c>
       <c r="AN5">
-        <v>1.620148793511938</v>
+        <v>1.950892777410652</v>
       </c>
       <c r="AO5">
-        <v>1.691258887943281</v>
+        <v>2.118073102677476</v>
       </c>
       <c r="AP5">
-        <v>2.448955539854732</v>
+        <v>3.108834761886927</v>
       </c>
       <c r="AQ5">
-        <v>-2.030293092778862</v>
+        <v>-2.378758064309582</v>
       </c>
       <c r="AR5">
-        <v>2.26216891955886</v>
+        <v>2.868011158736149</v>
       </c>
       <c r="AS5">
-        <v>0.05379872205911085</v>
+        <v>0.05558074733550537</v>
       </c>
       <c r="AT5" t="b">
         <v>1</v>
@@ -1314,10 +1317,10 @@
         <v>50</v>
       </c>
       <c r="B6" s="2">
+        <v>46255</v>
+      </c>
+      <c r="C6" s="2">
         <v>46254</v>
-      </c>
-      <c r="C6" s="2">
-        <v>46253</v>
       </c>
       <c r="D6" t="s">
         <v>56</v>
@@ -1326,16 +1329,16 @@
         <v>1</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>0.03993506226774555</v>
       </c>
       <c r="G6">
-        <v>0.5781780700216143</v>
+        <v>0.705768003120097</v>
       </c>
       <c r="H6">
-        <v>0.9429692128640749</v>
+        <v>0.9430125185091777</v>
       </c>
       <c r="I6">
-        <v>0.2579025013916021</v>
+        <v>0.2578380745102016</v>
       </c>
       <c r="J6">
         <v>6</v>
@@ -1347,67 +1350,67 @@
         <v>158</v>
       </c>
       <c r="M6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N6">
-        <v>-0.1058373677489839</v>
+        <v>-0.1326279871106212</v>
       </c>
       <c r="O6">
-        <v>-1.95594105799718</v>
+        <v>-2.511655849079071</v>
       </c>
       <c r="P6">
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>0.5781780700216143</v>
+        <v>0.705768003120097</v>
       </c>
       <c r="R6" t="s">
         <v>58</v>
       </c>
       <c r="S6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="T6">
-        <v>0.8843281615246334</v>
+        <v>0.8135047667508462</v>
       </c>
       <c r="U6">
-        <v>0.7979403523348219</v>
+        <v>0.7720649420737459</v>
       </c>
       <c r="V6" t="s">
         <v>56</v>
       </c>
       <c r="W6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="X6">
-        <v>0.999495171204298</v>
+        <v>0.999050486691007</v>
       </c>
       <c r="Y6">
-        <v>0.9999707185949473</v>
+        <v>0.9999901507828128</v>
       </c>
       <c r="Z6">
-        <v>0.0004755473906493668</v>
+        <v>0.0009396640918057919</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>0.4420779968234593</v>
       </c>
       <c r="AB6">
-        <v>48.6054717682086</v>
+        <v>52.25174269577867</v>
       </c>
       <c r="AC6">
-        <v>6.999999999999997</v>
+        <v>9</v>
       </c>
       <c r="AD6">
-        <v>0.6612402264225222</v>
+        <v>0.6121932303117764</v>
       </c>
       <c r="AE6">
-        <v>0.7501742217383183</v>
+        <v>0.7907081944437102</v>
       </c>
       <c r="AF6">
-        <v>0.6768927066919158</v>
+        <v>0.8797421749058035</v>
       </c>
       <c r="AG6">
-        <v>0.676872886322394</v>
+        <v>0.8797335101340542</v>
       </c>
       <c r="AH6" t="s">
         <v>56</v>
@@ -1416,34 +1419,34 @@
         <v>67</v>
       </c>
       <c r="AJ6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AK6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AL6">
-        <v>0.3306104321898076</v>
+        <v>0.441410846024333</v>
       </c>
       <c r="AM6">
-        <v>0.6903604912104218</v>
+        <v>0.7640742648544088</v>
       </c>
       <c r="AN6">
-        <v>0.4542375573949776</v>
+        <v>0.5492305659924983</v>
       </c>
       <c r="AO6">
-        <v>0.5013875605815916</v>
+        <v>0.6861654558813107</v>
       </c>
       <c r="AP6">
-        <v>0.6464621698535724</v>
+        <v>0.8136425168908916</v>
       </c>
       <c r="AQ6">
-        <v>-0.836181056609497</v>
+        <v>-0.9698468574691853</v>
       </c>
       <c r="AR6">
-        <v>0.5620402351596001</v>
+        <v>0.7139352009881679</v>
       </c>
       <c r="AS6">
-        <v>0.05334218816377579</v>
+        <v>0.05330570918533644</v>
       </c>
       <c r="AT6" t="b">
         <v>1</v>
@@ -1454,10 +1457,10 @@
         <v>51</v>
       </c>
       <c r="B7" s="2">
+        <v>46255</v>
+      </c>
+      <c r="C7" s="2">
         <v>46254</v>
-      </c>
-      <c r="C7" s="2">
-        <v>46253</v>
       </c>
       <c r="D7" t="s">
         <v>56</v>
@@ -1469,13 +1472,13 @@
         <v>1</v>
       </c>
       <c r="G7">
-        <v>2.476432103856031</v>
+        <v>2.799788928978186</v>
       </c>
       <c r="H7">
-        <v>1.362206492418323</v>
+        <v>1.369403592162395</v>
       </c>
       <c r="I7">
-        <v>0.3102325871194744</v>
+        <v>0.3122609620325014</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -1487,67 +1490,67 @@
         <v>239</v>
       </c>
       <c r="M7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N7">
-        <v>-0.05895605980843035</v>
+        <v>-0.06695481300405008</v>
       </c>
       <c r="O7">
-        <v>-14.91884025879844</v>
+        <v>-16.56565135736862</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>2.476432103856031</v>
+        <v>2.799788928978186</v>
       </c>
       <c r="R7" t="s">
         <v>58</v>
       </c>
       <c r="S7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="T7">
-        <v>0.911331543491438</v>
+        <v>0.9038103801512347</v>
       </c>
       <c r="U7">
-        <v>0.9600891646449576</v>
+        <v>0.9567110974963017</v>
       </c>
       <c r="V7" t="s">
         <v>56</v>
       </c>
       <c r="W7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="X7">
-        <v>0.9993878998345654</v>
+        <v>0.9995681382782746</v>
       </c>
       <c r="Y7">
-        <v>0.9999598802952427</v>
+        <v>0.9999857057129841</v>
       </c>
       <c r="Z7">
-        <v>0.0005719804606773016</v>
+        <v>0.0004175674347094427</v>
       </c>
       <c r="AA7">
         <v>1</v>
       </c>
       <c r="AB7">
-        <v>34.64808410787485</v>
+        <v>36.13601322557214</v>
       </c>
       <c r="AC7">
-        <v>6.999999999999997</v>
+        <v>6.000000000000009</v>
       </c>
       <c r="AD7">
-        <v>0.8226595294878541</v>
+        <v>0.807619385320781</v>
       </c>
       <c r="AE7">
-        <v>0.5685343424480375</v>
+        <v>0.5897041024565488</v>
       </c>
       <c r="AF7">
-        <v>2.274815151729783</v>
+        <v>2.597463021301063</v>
       </c>
       <c r="AG7">
-        <v>2.274723886817518</v>
+        <v>2.597425892419124</v>
       </c>
       <c r="AH7" t="s">
         <v>56</v>
@@ -1556,34 +1559,34 @@
         <v>67</v>
       </c>
       <c r="AJ7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AK7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AL7">
-        <v>0.8226265246304153</v>
+        <v>0.8076078409774876</v>
       </c>
       <c r="AM7">
-        <v>0.9397469757820209</v>
+        <v>0.9348738201194033</v>
       </c>
       <c r="AN7">
-        <v>1.886753805740311</v>
+        <v>2.113288595471767</v>
       </c>
       <c r="AO7">
-        <v>1.268310300213958</v>
+        <v>1.508310092799069</v>
       </c>
       <c r="AP7">
-        <v>3.034765938404792</v>
+        <v>3.519860679519747</v>
       </c>
       <c r="AQ7">
-        <v>-2.617596247757652</v>
+        <v>-2.75011321001353</v>
       </c>
       <c r="AR7">
-        <v>2.782946818459877</v>
+        <v>3.240920255412093</v>
       </c>
       <c r="AS7">
-        <v>0.04691227445113542</v>
+        <v>0.04937994984250294</v>
       </c>
       <c r="AT7" t="b">
         <v>1</v>
@@ -1594,136 +1597,136 @@
         <v>52</v>
       </c>
       <c r="B8" s="2">
+        <v>46255</v>
+      </c>
+      <c r="C8" s="2">
         <v>46254</v>
       </c>
-      <c r="C8" s="2">
-        <v>46253</v>
-      </c>
       <c r="D8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="F8">
         <v>0</v>
       </c>
       <c r="G8">
-        <v>0.03701447009399642</v>
+        <v>0.07591293037768411</v>
       </c>
       <c r="H8">
-        <v>1.430598425220382</v>
+        <v>1.431537159102374</v>
       </c>
       <c r="I8">
-        <v>0.3522896653464405</v>
+        <v>0.3524564235158353</v>
       </c>
       <c r="J8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K8">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="L8">
         <v>111</v>
       </c>
       <c r="M8">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N8">
-        <v>-0.2892683796623388</v>
+        <v>-0.2896653614238939</v>
       </c>
       <c r="O8">
-        <v>-74.61551939701083</v>
+        <v>-73.47916397779564</v>
       </c>
       <c r="P8">
-        <v>0.8490359336455062</v>
+        <v>0.575695736555963</v>
       </c>
       <c r="Q8">
-        <v>0.2451872885238733</v>
+        <v>0.1789115427724108</v>
       </c>
       <c r="R8" t="s">
         <v>59</v>
       </c>
       <c r="S8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="T8">
-        <v>0.6853787671500985</v>
+        <v>-0.4092036361630399</v>
       </c>
       <c r="U8">
-        <v>0.70811771335306</v>
+        <v>0.5590639223686202</v>
       </c>
       <c r="V8" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="W8" t="s">
+        <v>64</v>
+      </c>
+      <c r="X8">
+        <v>0.9989058089703045</v>
+      </c>
+      <c r="Y8">
+        <v>0.9996891443810091</v>
+      </c>
+      <c r="Z8">
+        <v>0.0007833354107046331</v>
+      </c>
+      <c r="AA8">
+        <v>0.9943494743949133</v>
+      </c>
+      <c r="AB8">
+        <v>-92.34697423853162</v>
+      </c>
+      <c r="AC8">
+        <v>-7.999999999999998</v>
+      </c>
+      <c r="AD8">
+        <v>-0.04095097359994582</v>
+      </c>
+      <c r="AE8">
+        <v>-0.9991611570518625</v>
+      </c>
+      <c r="AF8">
+        <v>1.645740685676064</v>
+      </c>
+      <c r="AG8">
+        <v>1.64522909793652</v>
+      </c>
+      <c r="AH8" t="s">
         <v>66</v>
       </c>
-      <c r="X8">
-        <v>0.9943626590928096</v>
-      </c>
-      <c r="Y8">
-        <v>0.9987890725420626</v>
-      </c>
-      <c r="Z8">
-        <v>0.004426413449252986</v>
-      </c>
-      <c r="AA8">
-        <v>0.1539430924141814</v>
-      </c>
-      <c r="AB8">
-        <v>-77.70524749282117</v>
-      </c>
-      <c r="AC8">
-        <v>-18</v>
-      </c>
-      <c r="AD8">
-        <v>0.2129409016590923</v>
-      </c>
-      <c r="AE8">
-        <v>-0.9770650809442597</v>
-      </c>
-      <c r="AF8">
-        <v>1.12845782350404</v>
-      </c>
-      <c r="AG8">
-        <v>1.127091342940434</v>
-      </c>
-      <c r="AH8" t="s">
-        <v>56</v>
-      </c>
       <c r="AI8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AJ8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AK8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AL8">
-        <v>0.1227120657147661</v>
+        <v>-0.04082258246240339</v>
       </c>
       <c r="AM8">
-        <v>0.576325034692154</v>
+        <v>0.6547500567402622</v>
       </c>
       <c r="AN8">
-        <v>0.257825198952521</v>
+        <v>-0.05214664521845188</v>
       </c>
       <c r="AO8">
-        <v>-1.092074321074909</v>
+        <v>-1.643112663229438</v>
       </c>
       <c r="AP8">
-        <v>0.04268234739644627</v>
+        <v>-0.5445606754256364</v>
       </c>
       <c r="AQ8">
-        <v>-2.283244132581187</v>
+        <v>-1.72515865826341</v>
       </c>
       <c r="AR8">
-        <v>0.4092268280514446</v>
+        <v>0.6707493927570177</v>
       </c>
       <c r="AS8">
-        <v>0.1194801978542123</v>
+        <v>0.3753088716803816</v>
       </c>
       <c r="AT8" t="b">
         <v>1</v>
@@ -1734,10 +1737,10 @@
         <v>53</v>
       </c>
       <c r="B9" s="2">
+        <v>46255</v>
+      </c>
+      <c r="C9" s="2">
         <v>46254</v>
-      </c>
-      <c r="C9" s="2">
-        <v>46253</v>
       </c>
       <c r="D9" t="s">
         <v>57</v>
@@ -1746,16 +1749,16 @@
         <v>-1</v>
       </c>
       <c r="F9">
-        <v>0.8346552579069189</v>
+        <v>1</v>
       </c>
       <c r="G9">
-        <v>3.344028327709457</v>
+        <v>3.672976609750829</v>
       </c>
       <c r="H9">
-        <v>2.942032932254917</v>
+        <v>2.946528663647374</v>
       </c>
       <c r="I9">
-        <v>0.6006112050484369</v>
+        <v>0.6010243755315756</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -1767,103 +1770,103 @@
         <v>76</v>
       </c>
       <c r="M9">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N9">
-        <v>0.3245653178023096</v>
+        <v>0.3428476196028323</v>
       </c>
       <c r="O9">
-        <v>46.38303934295355</v>
+        <v>48.0467134578553</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>3.344028327709457</v>
+        <v>3.672976609750829</v>
       </c>
       <c r="R9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="S9" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="T9">
-        <v>-0.9954595725036556</v>
+        <v>-0.9773777765031695</v>
       </c>
       <c r="U9">
-        <v>0.9730946571918411</v>
+        <v>0.9897677588998222</v>
       </c>
       <c r="V9" t="s">
         <v>57</v>
       </c>
       <c r="W9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="X9">
-        <v>0.9991919243572572</v>
+        <v>0.9986541480104798</v>
       </c>
       <c r="Y9">
-        <v>0.9997582435166329</v>
+        <v>0.9997910378935834</v>
       </c>
       <c r="Z9">
-        <v>0.0005663191593756611</v>
+        <v>0.001136889883103565</v>
       </c>
       <c r="AA9">
         <v>1</v>
       </c>
       <c r="AB9">
-        <v>-172.3768816259754</v>
+        <v>-162.6980782645607</v>
       </c>
       <c r="AC9">
-        <v>6.999999999999997</v>
+        <v>10</v>
       </c>
       <c r="AD9">
-        <v>-0.9911620952036588</v>
+        <v>-0.9547508248308558</v>
       </c>
       <c r="AE9">
-        <v>-0.1326563267676789</v>
+        <v>-0.2974068971708632</v>
       </c>
       <c r="AF9">
-        <v>2.499947650591717</v>
+        <v>2.809551039274349</v>
       </c>
       <c r="AG9">
-        <v>2.499343272039108</v>
+        <v>2.808963949571097</v>
       </c>
       <c r="AH9" t="s">
         <v>57</v>
       </c>
       <c r="AI9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AJ9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AK9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AL9">
-        <v>-0.9909224753410756</v>
+        <v>-0.9545513180873961</v>
       </c>
       <c r="AM9">
-        <v>0.9912305746941298</v>
+        <v>0.9796547909557933</v>
       </c>
       <c r="AN9">
-        <v>-2.479793160044495</v>
+        <v>-2.692407542451325</v>
       </c>
       <c r="AO9">
-        <v>-0.3004458313453518</v>
+        <v>-0.7894845107283921</v>
       </c>
       <c r="AP9">
-        <v>-4.410775866295087</v>
+        <v>-4.97731983308966</v>
       </c>
       <c r="AQ9">
-        <v>2.520525211740795</v>
+        <v>2.311647954026918</v>
       </c>
       <c r="AR9">
-        <v>4.188109640161673</v>
+        <v>4.75185668384593</v>
       </c>
       <c r="AS9">
-        <v>0.04022292731859602</v>
+        <v>0.04464879837478363</v>
       </c>
       <c r="AT9" t="b">
         <v>1</v>
@@ -1874,10 +1877,10 @@
         <v>54</v>
       </c>
       <c r="B10" s="2">
+        <v>46255</v>
+      </c>
+      <c r="C10" s="2">
         <v>46254</v>
-      </c>
-      <c r="C10" s="2">
-        <v>46253</v>
       </c>
       <c r="D10" t="s">
         <v>57</v>
@@ -1886,16 +1889,16 @@
         <v>-1</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>0.06621278626437836</v>
       </c>
       <c r="G10">
-        <v>1.224522360957086</v>
+        <v>1.637136906626681</v>
       </c>
       <c r="H10">
-        <v>2.039073692964579</v>
+        <v>2.039988258884923</v>
       </c>
       <c r="I10">
-        <v>0.4647321926877153</v>
+        <v>0.4643421238595635</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1907,103 +1910,103 @@
         <v>233</v>
       </c>
       <c r="M10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N10">
-        <v>12.32987707320468</v>
+        <v>13.1938394072181</v>
       </c>
       <c r="O10">
-        <v>15.4061563679652</v>
+        <v>21.16214145627008</v>
       </c>
       <c r="P10">
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>1.224522360957086</v>
+        <v>1.637136906626681</v>
       </c>
       <c r="R10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="S10" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="T10">
-        <v>-0.9712772551812577</v>
+        <v>-0.9844460133251428</v>
       </c>
       <c r="U10">
-        <v>0.8358987908355353</v>
+        <v>0.8520339916907844</v>
       </c>
       <c r="V10" t="s">
         <v>57</v>
       </c>
       <c r="W10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="X10">
-        <v>0.9952519461167647</v>
+        <v>0.9953392811419918</v>
       </c>
       <c r="Y10">
-        <v>0.9952961040158775</v>
+        <v>0.9964054710192536</v>
       </c>
       <c r="Z10">
-        <v>4.415789911282886E-05</v>
+        <v>0.001066189877261814</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>0.2791157243714534</v>
       </c>
       <c r="AB10">
-        <v>156.2941560896775</v>
+        <v>164.5765081209393</v>
       </c>
       <c r="AC10">
-        <v>-2.000000000000003</v>
+        <v>11</v>
       </c>
       <c r="AD10">
-        <v>-0.9156215917218425</v>
+        <v>-0.9639864423678249</v>
       </c>
       <c r="AE10">
-        <v>0.4020411680074063</v>
+        <v>0.2659513845254884</v>
       </c>
       <c r="AF10">
-        <v>1.169384690176933</v>
+        <v>1.471688112905135</v>
       </c>
       <c r="AG10">
-        <v>1.163884026228915</v>
+        <v>1.466398087332678</v>
       </c>
       <c r="AH10" t="s">
         <v>57</v>
       </c>
       <c r="AI10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AJ10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AK10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AL10">
-        <v>-0.4556573014967832</v>
+        <v>-0.6143089908878036</v>
       </c>
       <c r="AM10">
-        <v>0.7664129892859401</v>
+        <v>0.8375106535875269</v>
       </c>
       <c r="AN10">
-        <v>-1.068051724138155</v>
+        <v>-1.400465121071157</v>
       </c>
       <c r="AO10">
-        <v>0.4623541320830815</v>
+        <v>0.4294431392108509</v>
       </c>
       <c r="AP10">
-        <v>-0.893938406614134</v>
+        <v>-1.313231770328659</v>
       </c>
       <c r="AQ10">
-        <v>2.801726646986756</v>
+        <v>3.33070689379288</v>
       </c>
       <c r="AR10">
-        <v>0.7061852967172343</v>
+        <v>1.084636112146913</v>
       </c>
       <c r="AS10">
-        <v>0.0441808309077974</v>
+        <v>0.04166892569233371</v>
       </c>
       <c r="AT10" t="b">
         <v>1</v>
@@ -2014,10 +2017,10 @@
         <v>55</v>
       </c>
       <c r="B11" s="2">
+        <v>46255</v>
+      </c>
+      <c r="C11" s="2">
         <v>46254</v>
-      </c>
-      <c r="C11" s="2">
-        <v>46253</v>
       </c>
       <c r="D11" t="s">
         <v>56</v>
@@ -2029,13 +2032,13 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>1.425699501519865</v>
+        <v>1.842550331079064</v>
       </c>
       <c r="H11">
-        <v>2.895600718595243</v>
+        <v>2.852515119799075</v>
       </c>
       <c r="I11">
-        <v>0.6332097085444153</v>
+        <v>0.6310871020836585</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -2047,67 +2050,67 @@
         <v>212</v>
       </c>
       <c r="M11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N11">
-        <v>-413.716339274407</v>
+        <v>-517.6778802760064</v>
       </c>
       <c r="O11">
-        <v>-5.316787682813429</v>
+        <v>-6.398843680709935</v>
       </c>
       <c r="P11">
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>1.425699501519865</v>
+        <v>1.842550331079064</v>
       </c>
       <c r="R11" t="s">
         <v>58</v>
       </c>
       <c r="S11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="T11">
-        <v>0.9387787232160607</v>
+        <v>0.8739244504506468</v>
       </c>
       <c r="U11">
-        <v>0.8220264675511796</v>
+        <v>0.7932067133357139</v>
       </c>
       <c r="V11" t="s">
         <v>56</v>
       </c>
       <c r="W11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="X11">
-        <v>0.9913913855410589</v>
+        <v>0.9996662425829381</v>
       </c>
       <c r="Y11">
-        <v>0.9983041684158089</v>
+        <v>0.9997628425316913</v>
       </c>
       <c r="Z11">
-        <v>0.006912782874750056</v>
+        <v>9.659994875321765E-05</v>
       </c>
       <c r="AA11">
-        <v>0.06825432873385694</v>
+        <v>0.5359779605829512</v>
       </c>
       <c r="AB11">
-        <v>33.50748502364006</v>
+        <v>41.2324549124319</v>
       </c>
       <c r="AC11">
-        <v>-28</v>
+        <v>-3.000000000000004</v>
       </c>
       <c r="AD11">
-        <v>0.8338137108382806</v>
+        <v>0.7520416768015612</v>
       </c>
       <c r="AE11">
-        <v>0.5520459180340854</v>
+        <v>0.6591155561458827</v>
       </c>
       <c r="AF11">
-        <v>1.497835588717574</v>
+        <v>1.928059071599804</v>
       </c>
       <c r="AG11">
-        <v>1.495295511818301</v>
+        <v>1.927601817991634</v>
       </c>
       <c r="AH11" t="s">
         <v>56</v>
@@ -2116,34 +2119,34 @@
         <v>67</v>
       </c>
       <c r="AJ11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AK11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AL11">
-        <v>0.4446072930965568</v>
+        <v>0.5774227479024108</v>
       </c>
       <c r="AM11">
-        <v>0.7564924193643786</v>
+        <v>0.824966669233184</v>
       </c>
       <c r="AN11">
-        <v>1.173589067040108</v>
+        <v>1.441282703672705</v>
       </c>
       <c r="AO11">
-        <v>0.90980182733142</v>
+        <v>1.279701112861722</v>
       </c>
       <c r="AP11">
-        <v>1.36601229944368</v>
+        <v>2.082580962013676</v>
       </c>
       <c r="AQ11">
-        <v>-2.966708736995491</v>
+        <v>-2.390018558409804</v>
       </c>
       <c r="AR11">
-        <v>1.09181223998737</v>
+        <v>1.855837817997649</v>
       </c>
       <c r="AS11">
-        <v>0.04472679052940127</v>
+        <v>0.0517228053997773</v>
       </c>
       <c r="AT11" t="b">
         <v>1</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -757,10 +757,10 @@
         <v>46</v>
       </c>
       <c r="B2" s="2">
+        <v>46256</v>
+      </c>
+      <c r="C2" s="2">
         <v>46255</v>
-      </c>
-      <c r="C2" s="2">
-        <v>46254</v>
       </c>
       <c r="D2" t="s">
         <v>56</v>
@@ -772,13 +772,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>0.4901354772408594</v>
+        <v>0.6856766544182692</v>
       </c>
       <c r="H2">
-        <v>1.067204660149961</v>
+        <v>1.06776813000045</v>
       </c>
       <c r="I2">
-        <v>0.2587418598924733</v>
+        <v>0.2587272647097029</v>
       </c>
       <c r="J2">
         <v>6</v>
@@ -790,19 +790,19 @@
         <v>149</v>
       </c>
       <c r="M2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N2">
-        <v>-0.06147580441985389</v>
+        <v>-0.07868640654026443</v>
       </c>
       <c r="O2">
-        <v>-1.701046054782897</v>
+        <v>-2.184260006272955</v>
       </c>
       <c r="P2">
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.4901354772408594</v>
+        <v>0.6856766544182692</v>
       </c>
       <c r="R2" t="s">
         <v>58</v>
@@ -811,10 +811,10 @@
         <v>61</v>
       </c>
       <c r="T2">
-        <v>0.8504698565259804</v>
+        <v>0.8229077268110704</v>
       </c>
       <c r="U2">
-        <v>0.7827089691119478</v>
+        <v>0.7703033444583698</v>
       </c>
       <c r="V2" t="s">
         <v>56</v>
@@ -823,34 +823,34 @@
         <v>65</v>
       </c>
       <c r="X2">
-        <v>0.9988808947098438</v>
+        <v>0.9993891298402447</v>
       </c>
       <c r="Y2">
-        <v>0.999990134701026</v>
+        <v>0.9999794695735529</v>
       </c>
       <c r="Z2">
-        <v>0.001109239991182287</v>
+        <v>0.0005903397333081317</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>0.3037884302855449</v>
       </c>
       <c r="AB2">
-        <v>55.79971796265564</v>
+        <v>52.80314866724348</v>
       </c>
       <c r="AC2">
-        <v>11</v>
+        <v>6.999999999999997</v>
       </c>
       <c r="AD2">
-        <v>0.5620874491331316</v>
+        <v>0.6045553409580938</v>
       </c>
       <c r="AE2">
-        <v>0.8270778074202023</v>
+        <v>0.7965631423302505</v>
       </c>
       <c r="AF2">
-        <v>0.7104048331291635</v>
+        <v>0.8805542739972961</v>
       </c>
       <c r="AG2">
-        <v>0.7103978247730921</v>
+        <v>0.8805361958425412</v>
       </c>
       <c r="AH2" t="s">
         <v>56</v>
@@ -865,28 +865,28 @@
         <v>74</v>
       </c>
       <c r="AL2">
-        <v>0.2810409519861982</v>
+        <v>0.3940980383373436</v>
       </c>
       <c r="AM2">
-        <v>0.6614995998291965</v>
+        <v>0.7339695153069584</v>
       </c>
       <c r="AN2">
-        <v>0.4126282140054479</v>
+        <v>0.5415463540732421</v>
       </c>
       <c r="AO2">
-        <v>0.5773075844022497</v>
+        <v>0.6936543499988544</v>
       </c>
       <c r="AP2">
-        <v>0.4232373049617013</v>
+        <v>0.7457365964217691</v>
       </c>
       <c r="AQ2">
-        <v>-1.03499428405337</v>
+        <v>-0.8341788638886329</v>
       </c>
       <c r="AR2">
-        <v>0.3494276594209536</v>
+        <v>0.6672754744244622</v>
       </c>
       <c r="AS2">
-        <v>0.04748788037401379</v>
+        <v>0.05431724925548111</v>
       </c>
       <c r="AT2" t="b">
         <v>1</v>
@@ -897,7 +897,7 @@
         <v>47</v>
       </c>
       <c r="B3" s="2">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="C3" s="2">
         <v>46254</v>
@@ -1037,10 +1037,10 @@
         <v>48</v>
       </c>
       <c r="B4" s="2">
+        <v>46256</v>
+      </c>
+      <c r="C4" s="2">
         <v>46255</v>
-      </c>
-      <c r="C4" s="2">
-        <v>46254</v>
       </c>
       <c r="D4" t="s">
         <v>56</v>
@@ -1052,13 +1052,13 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>0.8685446894451283</v>
+        <v>1.063070255311046</v>
       </c>
       <c r="H4">
-        <v>2.072535973374165</v>
+        <v>2.073362533790971</v>
       </c>
       <c r="I4">
-        <v>0.4977095437432331</v>
+        <v>0.4975699437980066</v>
       </c>
       <c r="J4">
         <v>6</v>
@@ -1070,19 +1070,19 @@
         <v>146</v>
       </c>
       <c r="M4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N4">
-        <v>-0.03870213822948498</v>
+        <v>-0.06101775410008679</v>
       </c>
       <c r="O4">
-        <v>-1.422499173569947</v>
+        <v>-2.258124656096274</v>
       </c>
       <c r="P4">
-        <v>0.09592243187937763</v>
+        <v>0.01433926410251749</v>
       </c>
       <c r="Q4">
-        <v>0.9606970906828725</v>
+        <v>1.078535663027176</v>
       </c>
       <c r="R4" t="s">
         <v>58</v>
@@ -1091,10 +1091,10 @@
         <v>61</v>
       </c>
       <c r="T4">
-        <v>0.6831823310055514</v>
+        <v>0.7103445297546604</v>
       </c>
       <c r="U4">
-        <v>0.7074302466322477</v>
+        <v>0.7196531592295451</v>
       </c>
       <c r="V4" t="s">
         <v>56</v>
@@ -1103,34 +1103,34 @@
         <v>65</v>
       </c>
       <c r="X4">
-        <v>0.9983119301592075</v>
+        <v>0.9987078174553897</v>
       </c>
       <c r="Y4">
-        <v>0.9999927907189984</v>
+        <v>0.9999924833597915</v>
       </c>
       <c r="Z4">
-        <v>0.001680860559790887</v>
+        <v>0.001284665904401794</v>
       </c>
       <c r="AA4">
-        <v>0.6442016024401184</v>
+        <v>0.6711414810589248</v>
       </c>
       <c r="AB4">
-        <v>66.10936809713229</v>
+        <v>62.50512399006986</v>
       </c>
       <c r="AC4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AD4">
-        <v>0.4049920970587502</v>
+        <v>0.461669285568499</v>
       </c>
       <c r="AE4">
-        <v>0.9143201853398818</v>
+        <v>0.8870521240393214</v>
       </c>
       <c r="AF4">
-        <v>1.816145925980495</v>
+        <v>1.836959666186838</v>
       </c>
       <c r="AG4">
-        <v>1.816132832874175</v>
+        <v>1.83694585842195</v>
       </c>
       <c r="AH4" t="s">
         <v>56</v>
@@ -1145,28 +1145,28 @@
         <v>74</v>
       </c>
       <c r="AL4">
-        <v>0.3329419271905759</v>
+        <v>0.3857544472229946</v>
       </c>
       <c r="AM4">
-        <v>0.7400069032371405</v>
+        <v>0.7638367478449776</v>
       </c>
       <c r="AN4">
-        <v>0.7661801512332116</v>
+        <v>0.8802517176106891</v>
       </c>
       <c r="AO4">
-        <v>1.64323692369165</v>
+        <v>1.60961567707343</v>
       </c>
       <c r="AP4">
-        <v>1.00420965457867</v>
+        <v>1.052695289542354</v>
       </c>
       <c r="AQ4">
-        <v>-1.246062843434765</v>
+        <v>-1.963087461817747</v>
       </c>
       <c r="AR4">
-        <v>0.8743558278062863</v>
+        <v>0.8613929497502741</v>
       </c>
       <c r="AS4">
-        <v>0.06885682080105154</v>
+        <v>0.05926468808856026</v>
       </c>
       <c r="AT4" t="b">
         <v>1</v>
@@ -1177,7 +1177,7 @@
         <v>49</v>
       </c>
       <c r="B5" s="2">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="C5" s="2">
         <v>46254</v>
@@ -1317,10 +1317,10 @@
         <v>50</v>
       </c>
       <c r="B6" s="2">
+        <v>46256</v>
+      </c>
+      <c r="C6" s="2">
         <v>46255</v>
-      </c>
-      <c r="C6" s="2">
-        <v>46254</v>
       </c>
       <c r="D6" t="s">
         <v>56</v>
@@ -1329,16 +1329,16 @@
         <v>1</v>
       </c>
       <c r="F6">
-        <v>0.03993506226774555</v>
+        <v>0.1984309268304248</v>
       </c>
       <c r="G6">
-        <v>0.705768003120097</v>
+        <v>0.7875694870461764</v>
       </c>
       <c r="H6">
-        <v>0.9430125185091777</v>
+        <v>0.9430516998071278</v>
       </c>
       <c r="I6">
-        <v>0.2578380745102016</v>
+        <v>0.2577887233707188</v>
       </c>
       <c r="J6">
         <v>6</v>
@@ -1350,19 +1350,19 @@
         <v>158</v>
       </c>
       <c r="M6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N6">
-        <v>-0.1326279871106212</v>
+        <v>-0.1628925646849487</v>
       </c>
       <c r="O6">
-        <v>-2.511655849079071</v>
+        <v>-3.207854588610752</v>
       </c>
       <c r="P6">
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>0.705768003120097</v>
+        <v>0.7875694870461764</v>
       </c>
       <c r="R6" t="s">
         <v>58</v>
@@ -1371,10 +1371,10 @@
         <v>61</v>
       </c>
       <c r="T6">
-        <v>0.8135047667508462</v>
+        <v>0.8428938372814724</v>
       </c>
       <c r="U6">
-        <v>0.7720649420737459</v>
+        <v>0.8090656441841318</v>
       </c>
       <c r="V6" t="s">
         <v>56</v>
@@ -1383,34 +1383,34 @@
         <v>65</v>
       </c>
       <c r="X6">
-        <v>0.999050486691007</v>
+        <v>0.999701783349034</v>
       </c>
       <c r="Y6">
-        <v>0.9999901507828128</v>
+        <v>0.9999951135316221</v>
       </c>
       <c r="Z6">
-        <v>0.0009396640918057919</v>
+        <v>0.0002933301825880363</v>
       </c>
       <c r="AA6">
-        <v>0.4420779968234593</v>
+        <v>0.5210408549913357</v>
       </c>
       <c r="AB6">
-        <v>52.25174269577867</v>
+        <v>47.60834027287718</v>
       </c>
       <c r="AC6">
-        <v>9</v>
+        <v>5.000000000000007</v>
       </c>
       <c r="AD6">
-        <v>0.6121932303117764</v>
+        <v>0.6741948870243686</v>
       </c>
       <c r="AE6">
-        <v>0.7907081944437102</v>
+        <v>0.7385534877787788</v>
       </c>
       <c r="AF6">
-        <v>0.8797421749058035</v>
+        <v>0.9112843628503297</v>
       </c>
       <c r="AG6">
-        <v>0.8797335101340542</v>
+        <v>0.9112799098881073</v>
       </c>
       <c r="AH6" t="s">
         <v>56</v>
@@ -1425,28 +1425,28 @@
         <v>74</v>
       </c>
       <c r="AL6">
-        <v>0.441410846024333</v>
+        <v>0.5127364782123364</v>
       </c>
       <c r="AM6">
-        <v>0.7640742648544088</v>
+        <v>0.7991032687435249</v>
       </c>
       <c r="AN6">
-        <v>0.5492305659924983</v>
+        <v>0.6208640918820814</v>
       </c>
       <c r="AO6">
-        <v>0.6861654558813107</v>
+        <v>0.6666871392583099</v>
       </c>
       <c r="AP6">
-        <v>0.8136425168908916</v>
+        <v>0.8769229157207086</v>
       </c>
       <c r="AQ6">
-        <v>-0.9698468574691853</v>
+        <v>-1.279075352466956</v>
       </c>
       <c r="AR6">
-        <v>0.7139352009881679</v>
+        <v>0.7477836088508186</v>
       </c>
       <c r="AS6">
-        <v>0.05330570918533644</v>
+        <v>0.04907772065413754</v>
       </c>
       <c r="AT6" t="b">
         <v>1</v>
@@ -1457,7 +1457,7 @@
         <v>51</v>
       </c>
       <c r="B7" s="2">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="C7" s="2">
         <v>46254</v>
@@ -1597,7 +1597,7 @@
         <v>52</v>
       </c>
       <c r="B8" s="2">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="C8" s="2">
         <v>46254</v>
@@ -1737,7 +1737,7 @@
         <v>53</v>
       </c>
       <c r="B9" s="2">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="C9" s="2">
         <v>46254</v>
@@ -1877,7 +1877,7 @@
         <v>54</v>
       </c>
       <c r="B10" s="2">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="C10" s="2">
         <v>46254</v>
@@ -2017,7 +2017,7 @@
         <v>55</v>
       </c>
       <c r="B11" s="2">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="C11" s="2">
         <v>46254</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -196,7 +196,7 @@
     <t>DOWN_ACCELERATING</t>
   </si>
   <si>
-    <t>DOWN_DECELERATING</t>
+    <t>DOWN_STEADY</t>
   </si>
   <si>
     <t>多头加速</t>
@@ -205,7 +205,7 @@
     <t>空头加速</t>
   </si>
   <si>
-    <t>空头减速</t>
+    <t>空头稳态</t>
   </si>
   <si>
     <t>NEUTRAL</t>
@@ -235,7 +235,7 @@
     <t>DOWN_STEEPENING</t>
   </si>
   <si>
-    <t>DOWN_VALLEY_FLATTENING</t>
+    <t>DOWN_SLOPE</t>
   </si>
   <si>
     <t>上升陡坡形成</t>
@@ -247,7 +247,7 @@
     <t>下降陡坡形成</t>
   </si>
   <si>
-    <t>下降谷底收敛</t>
+    <t>下降坡延续</t>
   </si>
 </sst>
 </file>
@@ -757,7 +757,7 @@
         <v>46</v>
       </c>
       <c r="B2" s="2">
-        <v>46256</v>
+        <v>46258</v>
       </c>
       <c r="C2" s="2">
         <v>46255</v>
@@ -897,10 +897,10 @@
         <v>47</v>
       </c>
       <c r="B3" s="2">
-        <v>46256</v>
+        <v>46258</v>
       </c>
       <c r="C3" s="2">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="D3" t="s">
         <v>56</v>
@@ -909,16 +909,16 @@
         <v>1</v>
       </c>
       <c r="F3">
-        <v>0.4236656675179737</v>
+        <v>0.87856591911644</v>
       </c>
       <c r="G3">
-        <v>1.77162634908774</v>
+        <v>2.15866004106353</v>
       </c>
       <c r="H3">
-        <v>1.836067718063164</v>
+        <v>1.839405958886057</v>
       </c>
       <c r="I3">
-        <v>0.4220995119764617</v>
+        <v>0.4216624715222663</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -930,19 +930,19 @@
         <v>225</v>
       </c>
       <c r="M3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N3">
-        <v>-0.03054736659367293</v>
+        <v>-0.03536962561879355</v>
       </c>
       <c r="O3">
-        <v>-9.091478152878832</v>
+        <v>-11.47832078495848</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>1.77162634908774</v>
+        <v>2.15866004106353</v>
       </c>
       <c r="R3" t="s">
         <v>58</v>
@@ -951,10 +951,10 @@
         <v>61</v>
       </c>
       <c r="T3">
-        <v>0.8848405598661534</v>
+        <v>0.8752482801329587</v>
       </c>
       <c r="U3">
-        <v>0.8617267344551464</v>
+        <v>0.9256442855531559</v>
       </c>
       <c r="V3" t="s">
         <v>56</v>
@@ -963,34 +963,34 @@
         <v>65</v>
       </c>
       <c r="X3">
-        <v>0.9994221359182794</v>
+        <v>0.9994213616423119</v>
       </c>
       <c r="Y3">
-        <v>0.9999945295507252</v>
+        <v>0.9999906865034341</v>
       </c>
       <c r="Z3">
-        <v>0.0005723936324457668</v>
+        <v>0.0005693248611222668</v>
       </c>
       <c r="AA3">
-        <v>0.728906953090797</v>
+        <v>1</v>
       </c>
       <c r="AB3">
-        <v>39.53535493000027</v>
+        <v>40.93801375300145</v>
       </c>
       <c r="AC3">
         <v>6.999999999999997</v>
       </c>
       <c r="AD3">
-        <v>0.77123193812414</v>
+        <v>0.7554189051286716</v>
       </c>
       <c r="AE3">
-        <v>0.6365542377655518</v>
+        <v>0.6552421520126731</v>
       </c>
       <c r="AF3">
-        <v>1.738427390205434</v>
+        <v>2.165576752305456</v>
       </c>
       <c r="AG3">
-        <v>1.738417880226578</v>
+        <v>2.165556583213811</v>
       </c>
       <c r="AH3" t="s">
         <v>56</v>
@@ -1005,28 +1005,28 @@
         <v>74</v>
       </c>
       <c r="AL3">
-        <v>0.6666904830178377</v>
+        <v>0.7554118695372929</v>
       </c>
       <c r="AM3">
-        <v>0.8695223443438814</v>
+        <v>0.9190808892033182</v>
       </c>
       <c r="AN3">
-        <v>1.354231212924323</v>
+        <v>1.653227085011985</v>
       </c>
       <c r="AO3">
-        <v>1.088437348502598</v>
+        <v>1.396831106070048</v>
       </c>
       <c r="AP3">
-        <v>2.132516225977054</v>
+        <v>2.594682880768611</v>
       </c>
       <c r="AQ3">
-        <v>-1.543205890574448</v>
+        <v>-2.176128171011526</v>
       </c>
       <c r="AR3">
-        <v>1.990644408001752</v>
+        <v>2.382795644339242</v>
       </c>
       <c r="AS3">
-        <v>0.05084475369515897</v>
+        <v>0.05027681740990086</v>
       </c>
       <c r="AT3" t="b">
         <v>1</v>
@@ -1037,7 +1037,7 @@
         <v>48</v>
       </c>
       <c r="B4" s="2">
-        <v>46256</v>
+        <v>46258</v>
       </c>
       <c r="C4" s="2">
         <v>46255</v>
@@ -1177,10 +1177,10 @@
         <v>49</v>
       </c>
       <c r="B5" s="2">
-        <v>46256</v>
+        <v>46258</v>
       </c>
       <c r="C5" s="2">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="D5" t="s">
         <v>56</v>
@@ -1192,13 +1192,13 @@
         <v>1</v>
       </c>
       <c r="G5">
-        <v>2.559319104838145</v>
+        <v>2.759804263225185</v>
       </c>
       <c r="H5">
-        <v>1.424350071335205</v>
+        <v>1.42904967716553</v>
       </c>
       <c r="I5">
-        <v>0.3003249864145023</v>
+        <v>0.3022392040805703</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -1210,19 +1210,19 @@
         <v>226</v>
       </c>
       <c r="M5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N5">
-        <v>-0.03601760576859788</v>
+        <v>-0.04289322562783564</v>
       </c>
       <c r="O5">
-        <v>-10.57896739243401</v>
+        <v>-12.96147547571106</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>2.559319104838145</v>
+        <v>2.759804263225185</v>
       </c>
       <c r="R5" t="s">
         <v>58</v>
@@ -1231,10 +1231,10 @@
         <v>61</v>
       </c>
       <c r="T5">
-        <v>0.8318112568274303</v>
+        <v>0.836991584791107</v>
       </c>
       <c r="U5">
-        <v>0.9243073098068914</v>
+        <v>0.9266418306489912</v>
       </c>
       <c r="V5" t="s">
         <v>56</v>
@@ -1243,34 +1243,34 @@
         <v>65</v>
       </c>
       <c r="X5">
-        <v>0.9986584258068262</v>
+        <v>0.9991271598097229</v>
       </c>
       <c r="Y5">
-        <v>0.9999689769381911</v>
+        <v>0.9999824699719719</v>
       </c>
       <c r="Z5">
-        <v>0.001310551131364912</v>
+        <v>0.0008553101622490455</v>
       </c>
       <c r="AA5">
         <v>1</v>
       </c>
       <c r="AB5">
-        <v>48.42366466301528</v>
+        <v>47.62498444875057</v>
       </c>
       <c r="AC5">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AD5">
-        <v>0.6636172957632107</v>
+        <v>0.6739803119900329</v>
       </c>
       <c r="AE5">
-        <v>0.7480722456848158</v>
+        <v>0.7387493073091966</v>
       </c>
       <c r="AF5">
-        <v>2.883489274778532</v>
+        <v>3.133379890696461</v>
       </c>
       <c r="AG5">
-        <v>2.883399820112535</v>
+        <v>3.133324962459154</v>
       </c>
       <c r="AH5" t="s">
         <v>56</v>
@@ -1285,28 +1285,28 @@
         <v>74</v>
       </c>
       <c r="AL5">
-        <v>0.6635967083228268</v>
+        <v>0.6739684970962734</v>
       </c>
       <c r="AM5">
-        <v>0.8907372185570044</v>
+        <v>0.894632281288783</v>
       </c>
       <c r="AN5">
-        <v>1.950892777410652</v>
+        <v>2.148241999209514</v>
       </c>
       <c r="AO5">
-        <v>2.118073102677476</v>
+        <v>2.277277787354816</v>
       </c>
       <c r="AP5">
-        <v>3.108834761886927</v>
+        <v>3.178570750260458</v>
       </c>
       <c r="AQ5">
-        <v>-2.378758064309582</v>
+        <v>-3.697301711279223</v>
       </c>
       <c r="AR5">
-        <v>2.868011158736149</v>
+        <v>2.80742433655606</v>
       </c>
       <c r="AS5">
-        <v>0.05558074733550537</v>
+        <v>0.05037117865611267</v>
       </c>
       <c r="AT5" t="b">
         <v>1</v>
@@ -1317,7 +1317,7 @@
         <v>50</v>
       </c>
       <c r="B6" s="2">
-        <v>46256</v>
+        <v>46258</v>
       </c>
       <c r="C6" s="2">
         <v>46255</v>
@@ -1457,10 +1457,10 @@
         <v>51</v>
       </c>
       <c r="B7" s="2">
-        <v>46256</v>
+        <v>46258</v>
       </c>
       <c r="C7" s="2">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="D7" t="s">
         <v>56</v>
@@ -1472,13 +1472,13 @@
         <v>1</v>
       </c>
       <c r="G7">
-        <v>2.799788928978186</v>
+        <v>3.10617716041243</v>
       </c>
       <c r="H7">
-        <v>1.369403592162395</v>
+        <v>1.376338921678551</v>
       </c>
       <c r="I7">
-        <v>0.3122609620325014</v>
+        <v>0.3150819612058283</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -1490,19 +1490,19 @@
         <v>239</v>
       </c>
       <c r="M7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N7">
-        <v>-0.06695481300405008</v>
+        <v>-0.07567867333441004</v>
       </c>
       <c r="O7">
-        <v>-16.56565135736862</v>
+        <v>-20.26009038496501</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>2.799788928978186</v>
+        <v>3.10617716041243</v>
       </c>
       <c r="R7" t="s">
         <v>58</v>
@@ -1511,10 +1511,10 @@
         <v>61</v>
       </c>
       <c r="T7">
-        <v>0.9038103801512347</v>
+        <v>0.9099541647101644</v>
       </c>
       <c r="U7">
-        <v>0.9567110974963017</v>
+        <v>0.9594784291707591</v>
       </c>
       <c r="V7" t="s">
         <v>56</v>
@@ -1523,34 +1523,34 @@
         <v>65</v>
       </c>
       <c r="X7">
-        <v>0.9995681382782746</v>
+        <v>0.999828966661148</v>
       </c>
       <c r="Y7">
-        <v>0.9999857057129841</v>
+        <v>0.9999962202047404</v>
       </c>
       <c r="Z7">
-        <v>0.0004175674347094427</v>
+        <v>0.0001672535435924827</v>
       </c>
       <c r="AA7">
         <v>1</v>
       </c>
       <c r="AB7">
-        <v>36.13601322557214</v>
+        <v>34.92441583398459</v>
       </c>
       <c r="AC7">
-        <v>6.000000000000009</v>
+        <v>4.000000000000005</v>
       </c>
       <c r="AD7">
-        <v>0.807619385320781</v>
+        <v>0.8199079890642212</v>
       </c>
       <c r="AE7">
-        <v>0.5897041024565488</v>
+        <v>0.5724953182941017</v>
       </c>
       <c r="AF7">
-        <v>2.597463021301063</v>
+        <v>2.89312062156705</v>
       </c>
       <c r="AG7">
-        <v>2.597425892419124</v>
+        <v>2.893109686163439</v>
       </c>
       <c r="AH7" t="s">
         <v>56</v>
@@ -1565,28 +1565,28 @@
         <v>74</v>
       </c>
       <c r="AL7">
-        <v>0.8076078409774876</v>
+        <v>0.8199048899798909</v>
       </c>
       <c r="AM7">
-        <v>0.9348738201194033</v>
+        <v>0.9391305050586733</v>
       </c>
       <c r="AN7">
-        <v>2.113288595471767</v>
+        <v>2.384313109767851</v>
       </c>
       <c r="AO7">
-        <v>1.508310092799069</v>
+        <v>1.637783569956673</v>
       </c>
       <c r="AP7">
-        <v>3.519860679519747</v>
+        <v>3.747594584664606</v>
       </c>
       <c r="AQ7">
-        <v>-2.75011321001353</v>
+        <v>-4.01477573440989</v>
       </c>
       <c r="AR7">
-        <v>3.240920255412093</v>
+        <v>3.344969589891187</v>
       </c>
       <c r="AS7">
-        <v>0.04937994984250294</v>
+        <v>0.0456037915483485</v>
       </c>
       <c r="AT7" t="b">
         <v>1</v>
@@ -1597,10 +1597,10 @@
         <v>52</v>
       </c>
       <c r="B8" s="2">
-        <v>46256</v>
+        <v>46258</v>
       </c>
       <c r="C8" s="2">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="D8" t="s">
         <v>57</v>
@@ -1612,37 +1612,37 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>0.07591293037768411</v>
+        <v>0.1631055640919626</v>
       </c>
       <c r="H8">
-        <v>1.431537159102374</v>
+        <v>1.43238648975751</v>
       </c>
       <c r="I8">
-        <v>0.3524564235158353</v>
+        <v>0.3526718977586886</v>
       </c>
       <c r="J8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K8">
-        <v>0.8333333333333334</v>
+        <v>1</v>
       </c>
       <c r="L8">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M8">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="N8">
-        <v>-0.2896653614238939</v>
+        <v>0</v>
       </c>
       <c r="O8">
-        <v>-73.47916397779564</v>
+        <v>0</v>
       </c>
       <c r="P8">
-        <v>0.575695736555963</v>
+        <v>0.4815849686663187</v>
       </c>
       <c r="Q8">
-        <v>0.1789115427724108</v>
+        <v>0.3146235240755946</v>
       </c>
       <c r="R8" t="s">
         <v>59</v>
@@ -1651,10 +1651,10 @@
         <v>62</v>
       </c>
       <c r="T8">
-        <v>-0.4092036361630399</v>
+        <v>-0.4632662556503959</v>
       </c>
       <c r="U8">
-        <v>0.5590639223686202</v>
+        <v>0.6084426051572448</v>
       </c>
       <c r="V8" t="s">
         <v>64</v>
@@ -1663,34 +1663,34 @@
         <v>64</v>
       </c>
       <c r="X8">
-        <v>0.9989058089703045</v>
+        <v>0.9998331213620036</v>
       </c>
       <c r="Y8">
-        <v>0.9996891443810091</v>
+        <v>0.9998911604582666</v>
       </c>
       <c r="Z8">
-        <v>0.0007833354107046331</v>
+        <v>5.803909626300729E-05</v>
       </c>
       <c r="AA8">
-        <v>0.9943494743949133</v>
+        <v>1</v>
       </c>
       <c r="AB8">
-        <v>-92.34697423853162</v>
+        <v>-95.79281531210295</v>
       </c>
       <c r="AC8">
-        <v>-7.999999999999998</v>
+        <v>-2.000000000000003</v>
       </c>
       <c r="AD8">
-        <v>-0.04095097359994582</v>
+        <v>-0.1009315418702112</v>
       </c>
       <c r="AE8">
-        <v>-0.9991611570518625</v>
+        <v>-0.9948933731087477</v>
       </c>
       <c r="AF8">
-        <v>1.645740685676064</v>
+        <v>1.96970972574776</v>
       </c>
       <c r="AG8">
-        <v>1.64522909793652</v>
+        <v>1.969495343443862</v>
       </c>
       <c r="AH8" t="s">
         <v>66</v>
@@ -1705,28 +1705,28 @@
         <v>75</v>
       </c>
       <c r="AL8">
-        <v>-0.04082258246240339</v>
+        <v>-0.1009205565274476</v>
       </c>
       <c r="AM8">
-        <v>0.6547500567402622</v>
+        <v>0.6958281889274697</v>
       </c>
       <c r="AN8">
-        <v>-0.05214664521845188</v>
+        <v>-0.1932666252708736</v>
       </c>
       <c r="AO8">
-        <v>-1.643112663229438</v>
+        <v>-1.959874900696018</v>
       </c>
       <c r="AP8">
-        <v>-0.5445606754256364</v>
+        <v>-0.56557184200474</v>
       </c>
       <c r="AQ8">
-        <v>-1.72515865826341</v>
+        <v>-0.5547588968345553</v>
       </c>
       <c r="AR8">
-        <v>0.6707493927570177</v>
+        <v>0.5673804568283902</v>
       </c>
       <c r="AS8">
-        <v>0.3753088716803816</v>
+        <v>0.22942119862658</v>
       </c>
       <c r="AT8" t="b">
         <v>1</v>
@@ -1737,10 +1737,10 @@
         <v>53</v>
       </c>
       <c r="B9" s="2">
-        <v>46256</v>
+        <v>46258</v>
       </c>
       <c r="C9" s="2">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="D9" t="s">
         <v>57</v>
@@ -1752,13 +1752,13 @@
         <v>1</v>
       </c>
       <c r="G9">
-        <v>3.672976609750829</v>
+        <v>4.113377338486962</v>
       </c>
       <c r="H9">
-        <v>2.946528663647374</v>
+        <v>2.951247216140156</v>
       </c>
       <c r="I9">
-        <v>0.6010243755315756</v>
+        <v>0.6020196437764176</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -1770,19 +1770,19 @@
         <v>76</v>
       </c>
       <c r="M9">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N9">
-        <v>0.3428476196028323</v>
+        <v>0.3625646773597508</v>
       </c>
       <c r="O9">
-        <v>48.0467134578553</v>
+        <v>54.36625590999347</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>3.672976609750829</v>
+        <v>4.113377338486962</v>
       </c>
       <c r="R9" t="s">
         <v>59</v>
@@ -1791,10 +1791,10 @@
         <v>62</v>
       </c>
       <c r="T9">
-        <v>-0.9773777765031695</v>
+        <v>-0.9620218799730507</v>
       </c>
       <c r="U9">
-        <v>0.9897677588998222</v>
+        <v>0.9828746937730799</v>
       </c>
       <c r="V9" t="s">
         <v>57</v>
@@ -1803,34 +1803,34 @@
         <v>65</v>
       </c>
       <c r="X9">
-        <v>0.9986541480104798</v>
+        <v>0.9990132339248375</v>
       </c>
       <c r="Y9">
-        <v>0.9997910378935834</v>
+        <v>0.9998593911408282</v>
       </c>
       <c r="Z9">
-        <v>0.001136889883103565</v>
+        <v>0.0008461572159906838</v>
       </c>
       <c r="AA9">
         <v>1</v>
       </c>
       <c r="AB9">
-        <v>-162.6980782645607</v>
+        <v>-157.5238006130807</v>
       </c>
       <c r="AC9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD9">
-        <v>-0.9547508248308558</v>
+        <v>-0.9240384191350055</v>
       </c>
       <c r="AE9">
-        <v>-0.2974068971708632</v>
+        <v>-0.382299620667455</v>
       </c>
       <c r="AF9">
-        <v>2.809551039274349</v>
+        <v>3.264610432336347</v>
       </c>
       <c r="AG9">
-        <v>2.808963949571097</v>
+        <v>3.264151399187816</v>
       </c>
       <c r="AH9" t="s">
         <v>57</v>
@@ -1845,28 +1845,28 @@
         <v>76</v>
       </c>
       <c r="AL9">
-        <v>-0.9545513180873961</v>
+        <v>-0.9239084911470601</v>
       </c>
       <c r="AM9">
-        <v>0.9796547909557933</v>
+        <v>0.9704855814292279</v>
       </c>
       <c r="AN9">
-        <v>-2.692407542451325</v>
+        <v>-3.032250883123614</v>
       </c>
       <c r="AO9">
-        <v>-0.7894845107283921</v>
+        <v>-1.200880076249634</v>
       </c>
       <c r="AP9">
-        <v>-4.97731983308966</v>
+        <v>-5.511255125741923</v>
       </c>
       <c r="AQ9">
-        <v>2.311647954026918</v>
+        <v>3.161310104484486</v>
       </c>
       <c r="AR9">
-        <v>4.75185668384593</v>
+        <v>5.189729054617612</v>
       </c>
       <c r="AS9">
-        <v>0.04464879837478363</v>
+        <v>0.04451154140375793</v>
       </c>
       <c r="AT9" t="b">
         <v>1</v>
@@ -1877,10 +1877,10 @@
         <v>54</v>
       </c>
       <c r="B10" s="2">
-        <v>46256</v>
+        <v>46258</v>
       </c>
       <c r="C10" s="2">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="D10" t="s">
         <v>57</v>
@@ -1889,16 +1889,16 @@
         <v>-1</v>
       </c>
       <c r="F10">
-        <v>0.06621278626437836</v>
+        <v>0</v>
       </c>
       <c r="G10">
-        <v>1.637136906626681</v>
+        <v>1.573807635651196</v>
       </c>
       <c r="H10">
-        <v>2.039988258884923</v>
+        <v>2.040815723289043</v>
       </c>
       <c r="I10">
-        <v>0.4643421238595635</v>
+        <v>0.4638901072967678</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1910,19 +1910,19 @@
         <v>233</v>
       </c>
       <c r="M10">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N10">
-        <v>13.1938394072181</v>
+        <v>14.04769342088444</v>
       </c>
       <c r="O10">
-        <v>21.16214145627008</v>
+        <v>22.94839065255337</v>
       </c>
       <c r="P10">
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>1.637136906626681</v>
+        <v>1.573807635651196</v>
       </c>
       <c r="R10" t="s">
         <v>60</v>
@@ -1931,10 +1931,10 @@
         <v>63</v>
       </c>
       <c r="T10">
-        <v>-0.9844460133251428</v>
+        <v>-0.9908003157508283</v>
       </c>
       <c r="U10">
-        <v>0.8520339916907844</v>
+        <v>0.8452581329310004</v>
       </c>
       <c r="V10" t="s">
         <v>57</v>
@@ -1943,34 +1943,34 @@
         <v>65</v>
       </c>
       <c r="X10">
-        <v>0.9953392811419918</v>
+        <v>0.9955813784875667</v>
       </c>
       <c r="Y10">
-        <v>0.9964054710192536</v>
+        <v>0.9975919633725104</v>
       </c>
       <c r="Z10">
-        <v>0.001066189877261814</v>
+        <v>0.002010584884943767</v>
       </c>
       <c r="AA10">
-        <v>0.2791157243714534</v>
+        <v>0.2007326519985159</v>
       </c>
       <c r="AB10">
-        <v>164.5765081209393</v>
+        <v>167.9168621547007</v>
       </c>
       <c r="AC10">
-        <v>11</v>
+        <v>15.00000000000001</v>
       </c>
       <c r="AD10">
-        <v>-0.9639864423678249</v>
+        <v>-0.9778448851814655</v>
       </c>
       <c r="AE10">
-        <v>0.2659513845254884</v>
+        <v>0.2093307921077227</v>
       </c>
       <c r="AF10">
-        <v>1.471688112905135</v>
+        <v>1.413483113170326</v>
       </c>
       <c r="AG10">
-        <v>1.466398087332678</v>
+        <v>1.410079394061474</v>
       </c>
       <c r="AH10" t="s">
         <v>57</v>
@@ -1985,28 +1985,28 @@
         <v>77</v>
       </c>
       <c r="AL10">
-        <v>-0.6143089908878036</v>
+        <v>-0.585651466751039</v>
       </c>
       <c r="AM10">
-        <v>0.8375106535875269</v>
+        <v>0.8265887448728856</v>
       </c>
       <c r="AN10">
-        <v>-1.400465121071157</v>
+        <v>-1.363355026066289</v>
       </c>
       <c r="AO10">
-        <v>0.4294431392108509</v>
+        <v>0.3486837527031618</v>
       </c>
       <c r="AP10">
-        <v>-1.313231770328659</v>
+        <v>-1.191627563071416</v>
       </c>
       <c r="AQ10">
-        <v>3.33070689379288</v>
+        <v>3.547809695379906</v>
       </c>
       <c r="AR10">
-        <v>1.084636112146913</v>
+        <v>0.9370187811729748</v>
       </c>
       <c r="AS10">
-        <v>0.04166892569233371</v>
+        <v>0.0404562550775729</v>
       </c>
       <c r="AT10" t="b">
         <v>1</v>
@@ -2017,10 +2017,10 @@
         <v>55</v>
       </c>
       <c r="B11" s="2">
-        <v>46256</v>
+        <v>46258</v>
       </c>
       <c r="C11" s="2">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="D11" t="s">
         <v>56</v>
@@ -2032,13 +2032,13 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>1.842550331079064</v>
+        <v>2.154523023899989</v>
       </c>
       <c r="H11">
-        <v>2.852515119799075</v>
+        <v>2.808123031577265</v>
       </c>
       <c r="I11">
-        <v>0.6310871020836585</v>
+        <v>0.6287099087380982</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -2050,19 +2050,19 @@
         <v>212</v>
       </c>
       <c r="M11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N11">
-        <v>-517.6778802760064</v>
+        <v>-643.8018584575588</v>
       </c>
       <c r="O11">
-        <v>-6.398843680709935</v>
+        <v>-7.953606758062891</v>
       </c>
       <c r="P11">
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>1.842550331079064</v>
+        <v>2.154523023899989</v>
       </c>
       <c r="R11" t="s">
         <v>58</v>
@@ -2071,10 +2071,10 @@
         <v>61</v>
       </c>
       <c r="T11">
-        <v>0.8739244504506468</v>
+        <v>0.836488345692881</v>
       </c>
       <c r="U11">
-        <v>0.7932067133357139</v>
+        <v>0.7763963424495952</v>
       </c>
       <c r="V11" t="s">
         <v>56</v>
@@ -2083,34 +2083,34 @@
         <v>65</v>
       </c>
       <c r="X11">
-        <v>0.9996662425829381</v>
+        <v>0.9997922701689504</v>
       </c>
       <c r="Y11">
-        <v>0.9997628425316913</v>
+        <v>0.9999063475511949</v>
       </c>
       <c r="Z11">
-        <v>9.659994875321765E-05</v>
+        <v>0.0001140773822444485</v>
       </c>
       <c r="AA11">
-        <v>0.5359779605829512</v>
+        <v>0.9489870167833568</v>
       </c>
       <c r="AB11">
-        <v>41.2324549124319</v>
+        <v>43.75347121801627</v>
       </c>
       <c r="AC11">
-        <v>-3.000000000000004</v>
+        <v>3.000000000000004</v>
       </c>
       <c r="AD11">
-        <v>0.7520416768015612</v>
+        <v>0.7223220659802616</v>
       </c>
       <c r="AE11">
-        <v>0.6591155561458827</v>
+        <v>0.6915568183439497</v>
       </c>
       <c r="AF11">
-        <v>1.928059071599804</v>
+        <v>2.30731845734591</v>
       </c>
       <c r="AG11">
-        <v>1.927601817991634</v>
+        <v>2.307102371322207</v>
       </c>
       <c r="AH11" t="s">
         <v>56</v>
@@ -2125,28 +2125,28 @@
         <v>74</v>
       </c>
       <c r="AL11">
-        <v>0.5774227479024108</v>
+        <v>0.7038322424790375</v>
       </c>
       <c r="AM11">
-        <v>0.824966669233184</v>
+        <v>0.8986964526771742</v>
       </c>
       <c r="AN11">
-        <v>1.441282703672705</v>
+        <v>1.67578244994257</v>
       </c>
       <c r="AO11">
-        <v>1.279701112861722</v>
+        <v>1.585326491145277</v>
       </c>
       <c r="AP11">
-        <v>2.082580962013676</v>
+        <v>2.481956224500641</v>
       </c>
       <c r="AQ11">
-        <v>-2.390018558409804</v>
+        <v>-2.763643596638051</v>
       </c>
       <c r="AR11">
-        <v>1.855837817997649</v>
+        <v>2.211343105636636</v>
       </c>
       <c r="AS11">
-        <v>0.0517228053997773</v>
+        <v>0.05176528077662528</v>
       </c>
       <c r="AT11" t="b">
         <v>1</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="78">
   <si>
     <t>Pair</t>
   </si>
@@ -67,6 +67,90 @@
     <t>TerrainBundleSep</t>
   </si>
   <si>
+    <t>MarketPosture</t>
+  </si>
+  <si>
+    <t>MarketPostureCN</t>
+  </si>
+  <si>
+    <t>MarketPostureScore</t>
+  </si>
+  <si>
+    <t>MarketPostureConfidence</t>
+  </si>
+  <si>
+    <t>PhasedDirection</t>
+  </si>
+  <si>
+    <t>PhasedAlignment</t>
+  </si>
+  <si>
+    <t>PhasedRawCoherence</t>
+  </si>
+  <si>
+    <t>PhasedCoherence</t>
+  </si>
+  <si>
+    <t>PhasedSteeringGain</t>
+  </si>
+  <si>
+    <t>PhasedGate</t>
+  </si>
+  <si>
+    <t>PhasedBeamPhaseDeg</t>
+  </si>
+  <si>
+    <t>PhasedGradientDeg</t>
+  </si>
+  <si>
+    <t>PhasedDirectionScore</t>
+  </si>
+  <si>
+    <t>PhasedImpulseScore</t>
+  </si>
+  <si>
+    <t>PhasedAmplitude</t>
+  </si>
+  <si>
+    <t>PhasedPower</t>
+  </si>
+  <si>
+    <t>SurveyTrend</t>
+  </si>
+  <si>
+    <t>SurveyTrendCN</t>
+  </si>
+  <si>
+    <t>TerrainPattern</t>
+  </si>
+  <si>
+    <t>TerrainPatternCN</t>
+  </si>
+  <si>
+    <t>SurveyDirectionScore</t>
+  </si>
+  <si>
+    <t>SurveyConfidence</t>
+  </si>
+  <si>
+    <t>ContourElevation</t>
+  </si>
+  <si>
+    <t>ContourTemporalSlope</t>
+  </si>
+  <si>
+    <t>ContourScaleSlope</t>
+  </si>
+  <si>
+    <t>ContourCurvature</t>
+  </si>
+  <si>
+    <t>ContourRelief</t>
+  </si>
+  <si>
+    <t>ContourRoughness</t>
+  </si>
+  <si>
     <t>FilterEnabled</t>
   </si>
   <si>
@@ -104,6 +188,66 @@
   </si>
   <si>
     <t>DOWN</t>
+  </si>
+  <si>
+    <t>UP_ACCELERATING</t>
+  </si>
+  <si>
+    <t>DOWN_ACCELERATING</t>
+  </si>
+  <si>
+    <t>DOWN_STEADY</t>
+  </si>
+  <si>
+    <t>多头加速</t>
+  </si>
+  <si>
+    <t>空头加速</t>
+  </si>
+  <si>
+    <t>空头稳态</t>
+  </si>
+  <si>
+    <t>NEUTRAL</t>
+  </si>
+  <si>
+    <t>ALIGNED</t>
+  </si>
+  <si>
+    <t>TRANSITION</t>
+  </si>
+  <si>
+    <t>上涨</t>
+  </si>
+  <si>
+    <t>转换</t>
+  </si>
+  <si>
+    <t>下跌</t>
+  </si>
+  <si>
+    <t>UP_STEEPENING</t>
+  </si>
+  <si>
+    <t>TRANSITION_ZONE</t>
+  </si>
+  <si>
+    <t>DOWN_STEEPENING</t>
+  </si>
+  <si>
+    <t>DOWN_SLOPE</t>
+  </si>
+  <si>
+    <t>上升陡坡形成</t>
+  </si>
+  <si>
+    <t>地形转换区</t>
+  </si>
+  <si>
+    <t>下降陡坡形成</t>
+  </si>
+  <si>
+    <t>下降坡延续</t>
   </si>
 </sst>
 </file>
@@ -465,10 +609,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:AT11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:46">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -523,10 +667,94 @@
       <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>45</v>
+      </c>
     </row>
-    <row r="2" spans="1:18">
+    <row r="2" spans="1:46">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="B2" s="2">
         <v>46259</v>
@@ -535,7 +763,7 @@
         <v>46258</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -576,13 +804,97 @@
       <c r="Q2">
         <v>0.7544249014873886</v>
       </c>
-      <c r="R2" t="b">
+      <c r="R2" t="s">
+        <v>58</v>
+      </c>
+      <c r="S2" t="s">
+        <v>61</v>
+      </c>
+      <c r="T2">
+        <v>0.8704251670624802</v>
+      </c>
+      <c r="U2">
+        <v>0.7916658304811172</v>
+      </c>
+      <c r="V2" t="s">
+        <v>56</v>
+      </c>
+      <c r="W2" t="s">
+        <v>65</v>
+      </c>
+      <c r="X2">
+        <v>0.9998464281775358</v>
+      </c>
+      <c r="Y2">
+        <v>0.9998980212120042</v>
+      </c>
+      <c r="Z2">
+        <v>5.159303446844454E-05</v>
+      </c>
+      <c r="AA2">
+        <v>0.2572137202752759</v>
+      </c>
+      <c r="AB2">
+        <v>45.46895636211881</v>
+      </c>
+      <c r="AC2">
+        <v>2.000000000000003</v>
+      </c>
+      <c r="AD2">
+        <v>0.70129561026052</v>
+      </c>
+      <c r="AE2">
+        <v>0.7128705822442983</v>
+      </c>
+      <c r="AF2">
+        <v>0.8596966442005326</v>
+      </c>
+      <c r="AG2">
+        <v>0.859608973378713</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AL2">
+        <v>0.4407942753436352</v>
+      </c>
+      <c r="AM2">
+        <v>0.7543727577699688</v>
+      </c>
+      <c r="AN2">
+        <v>0.6054687129152738</v>
+      </c>
+      <c r="AO2">
+        <v>0.6101302909640854</v>
+      </c>
+      <c r="AP2">
+        <v>0.7835889176812064</v>
+      </c>
+      <c r="AQ2">
+        <v>-1.17141656044948</v>
+      </c>
+      <c r="AR2">
+        <v>0.6729008517865356</v>
+      </c>
+      <c r="AS2">
+        <v>0.04948651191629264</v>
+      </c>
+      <c r="AT2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:18">
+    <row r="3" spans="1:46">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="B3" s="2">
         <v>46259</v>
@@ -591,7 +903,7 @@
         <v>46258</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -600,13 +912,13 @@
         <v>1</v>
       </c>
       <c r="G3">
-        <v>2.538324649084723</v>
+        <v>2.498181505869455</v>
       </c>
       <c r="H3">
         <v>1.845830155284659</v>
       </c>
       <c r="I3">
-        <v>0.4205676284032986</v>
+        <v>0.4215137101845002</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -618,27 +930,111 @@
         <v>225</v>
       </c>
       <c r="M3">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N3">
-        <v>-0.03920705883761853</v>
+        <v>-0.04061114583918422</v>
       </c>
       <c r="O3">
-        <v>-14.11413792045924</v>
+        <v>-14.61959479939777</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>2.538324649084723</v>
-      </c>
-      <c r="R3" t="b">
+        <v>2.498181505869455</v>
+      </c>
+      <c r="R3" t="s">
+        <v>58</v>
+      </c>
+      <c r="S3" t="s">
+        <v>61</v>
+      </c>
+      <c r="T3">
+        <v>0.9025922180602828</v>
+      </c>
+      <c r="U3">
+        <v>0.956158207845921</v>
+      </c>
+      <c r="V3" t="s">
+        <v>56</v>
+      </c>
+      <c r="W3" t="s">
+        <v>65</v>
+      </c>
+      <c r="X3">
+        <v>0.9998937889174571</v>
+      </c>
+      <c r="Y3">
+        <v>0.9999668388751755</v>
+      </c>
+      <c r="Z3">
+        <v>7.304995771839629E-05</v>
+      </c>
+      <c r="AA3">
+        <v>1</v>
+      </c>
+      <c r="AB3">
+        <v>36.37224101247428</v>
+      </c>
+      <c r="AC3">
+        <v>3.000000000000004</v>
+      </c>
+      <c r="AD3">
+        <v>0.8051812058618306</v>
+      </c>
+      <c r="AE3">
+        <v>0.593028857414956</v>
+      </c>
+      <c r="AF3">
+        <v>2.398923796411649</v>
+      </c>
+      <c r="AG3">
+        <v>2.398844245400191</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AL3">
+        <v>0.8051545051473566</v>
+      </c>
+      <c r="AM3">
+        <v>0.934530340741347</v>
+      </c>
+      <c r="AN3">
+        <v>1.93989071029883</v>
+      </c>
+      <c r="AO3">
+        <v>1.410828488305417</v>
+      </c>
+      <c r="AP3">
+        <v>2.898749912023796</v>
+      </c>
+      <c r="AQ3">
+        <v>-3.189108757480399</v>
+      </c>
+      <c r="AR3">
+        <v>2.589023724384023</v>
+      </c>
+      <c r="AS3">
+        <v>0.04674943082342426</v>
+      </c>
+      <c r="AT3" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:18">
+    <row r="4" spans="1:46">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="B4" s="2">
         <v>46259</v>
@@ -647,7 +1043,7 @@
         <v>46258</v>
       </c>
       <c r="D4" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -688,13 +1084,97 @@
       <c r="Q4">
         <v>1.056134761727802</v>
       </c>
-      <c r="R4" t="b">
+      <c r="R4" t="s">
+        <v>58</v>
+      </c>
+      <c r="S4" t="s">
+        <v>61</v>
+      </c>
+      <c r="T4">
+        <v>0.7615799839236796</v>
+      </c>
+      <c r="U4">
+        <v>0.7427087014364006</v>
+      </c>
+      <c r="V4" t="s">
+        <v>56</v>
+      </c>
+      <c r="W4" t="s">
+        <v>65</v>
+      </c>
+      <c r="X4">
+        <v>0.9988717610459694</v>
+      </c>
+      <c r="Y4">
+        <v>0.9999908346829788</v>
+      </c>
+      <c r="Z4">
+        <v>0.00111907363700936</v>
+      </c>
+      <c r="AA4">
+        <v>0.4615302609136551</v>
+      </c>
+      <c r="AB4">
+        <v>59.07032033352175</v>
+      </c>
+      <c r="AC4">
+        <v>11</v>
+      </c>
+      <c r="AD4">
+        <v>0.5139856675391538</v>
+      </c>
+      <c r="AE4">
+        <v>0.857798772186304</v>
+      </c>
+      <c r="AF4">
+        <v>1.681103227913302</v>
+      </c>
+      <c r="AG4">
+        <v>1.681087820069273</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>74</v>
+      </c>
+      <c r="AL4">
+        <v>0.3755993608734222</v>
+      </c>
+      <c r="AM4">
+        <v>0.7392270011824164</v>
+      </c>
+      <c r="AN4">
+        <v>0.8966434547389286</v>
+      </c>
+      <c r="AO4">
+        <v>1.41977643485972</v>
+      </c>
+      <c r="AP4">
+        <v>0.888488091291638</v>
+      </c>
+      <c r="AQ4">
+        <v>-2.616449941642473</v>
+      </c>
+      <c r="AR4">
+        <v>0.7766054254501199</v>
+      </c>
+      <c r="AS4">
+        <v>0.04847695600735568</v>
+      </c>
+      <c r="AT4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:18">
+    <row r="5" spans="1:46">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="B5" s="2">
         <v>46259</v>
@@ -703,7 +1183,7 @@
         <v>46258</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -712,13 +1192,13 @@
         <v>1</v>
       </c>
       <c r="G5">
-        <v>2.934327230362023</v>
+        <v>2.900632541281531</v>
       </c>
       <c r="H5">
-        <v>1.443537322862849</v>
+        <v>1.433608782033656</v>
       </c>
       <c r="I5">
-        <v>0.3051177348801311</v>
+        <v>0.3048025720309513</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -733,24 +1213,108 @@
         <v>13</v>
       </c>
       <c r="N5">
-        <v>-0.05045508377138373</v>
+        <v>-0.05007051261267796</v>
       </c>
       <c r="O5">
-        <v>-16.10513389875441</v>
+        <v>-15.98237976692858</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>2.934327230362023</v>
-      </c>
-      <c r="R5" t="b">
+        <v>2.900632541281531</v>
+      </c>
+      <c r="R5" t="s">
+        <v>58</v>
+      </c>
+      <c r="S5" t="s">
+        <v>61</v>
+      </c>
+      <c r="T5">
+        <v>0.8490697911334227</v>
+      </c>
+      <c r="U5">
+        <v>0.9320778333059989</v>
+      </c>
+      <c r="V5" t="s">
+        <v>56</v>
+      </c>
+      <c r="W5" t="s">
+        <v>65</v>
+      </c>
+      <c r="X5">
+        <v>0.999476670861856</v>
+      </c>
+      <c r="Y5">
+        <v>0.9999857091838348</v>
+      </c>
+      <c r="Z5">
+        <v>0.0005090383219787942</v>
+      </c>
+      <c r="AA5">
+        <v>1</v>
+      </c>
+      <c r="AB5">
+        <v>45.72224026683239</v>
+      </c>
+      <c r="AC5">
+        <v>6.999999999999997</v>
+      </c>
+      <c r="AD5">
+        <v>0.6981374253201522</v>
+      </c>
+      <c r="AE5">
+        <v>0.7159637807650251</v>
+      </c>
+      <c r="AF5">
+        <v>3.267380028937886</v>
+      </c>
+      <c r="AG5">
+        <v>3.267333335410551</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>74</v>
+      </c>
+      <c r="AL5">
+        <v>0.6981274483665489</v>
+      </c>
+      <c r="AM5">
+        <v>0.9028232642579117</v>
+      </c>
+      <c r="AN5">
+        <v>2.312721927774895</v>
+      </c>
+      <c r="AO5">
+        <v>2.305627588470507</v>
+      </c>
+      <c r="AP5">
+        <v>3.116674231579814</v>
+      </c>
+      <c r="AQ5">
+        <v>-5.011885829396338</v>
+      </c>
+      <c r="AR5">
+        <v>2.631330194211097</v>
+      </c>
+      <c r="AS5">
+        <v>0.04408641034984021</v>
+      </c>
+      <c r="AT5" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:18">
+    <row r="6" spans="1:46">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="B6" s="2">
         <v>46259</v>
@@ -759,7 +1323,7 @@
         <v>46258</v>
       </c>
       <c r="D6" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -800,13 +1364,97 @@
       <c r="Q6">
         <v>0.8164181951652369</v>
       </c>
-      <c r="R6" t="b">
+      <c r="R6" t="s">
+        <v>58</v>
+      </c>
+      <c r="S6" t="s">
+        <v>61</v>
+      </c>
+      <c r="T6">
+        <v>0.8770486343293822</v>
+      </c>
+      <c r="U6">
+        <v>0.8328079098567494</v>
+      </c>
+      <c r="V6" t="s">
+        <v>56</v>
+      </c>
+      <c r="W6" t="s">
+        <v>65</v>
+      </c>
+      <c r="X6">
+        <v>0.9999336270591276</v>
+      </c>
+      <c r="Y6">
+        <v>0.9999702926164987</v>
+      </c>
+      <c r="Z6">
+        <v>3.666555737114052E-05</v>
+      </c>
+      <c r="AA6">
+        <v>0.4594537397617183</v>
+      </c>
+      <c r="AB6">
+        <v>42.82510553167288</v>
+      </c>
+      <c r="AC6">
+        <v>2.000000000000003</v>
+      </c>
+      <c r="AD6">
+        <v>0.7334320804336835</v>
+      </c>
+      <c r="AE6">
+        <v>0.679762740513717</v>
+      </c>
+      <c r="AF6">
+        <v>0.8871460585597097</v>
+      </c>
+      <c r="AG6">
+        <v>0.8871197037715265</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>74</v>
+      </c>
+      <c r="AL6">
+        <v>0.53518919678203</v>
+      </c>
+      <c r="AM6">
+        <v>0.8052417151162192</v>
+      </c>
+      <c r="AN6">
+        <v>0.6531931769628176</v>
+      </c>
+      <c r="AO6">
+        <v>0.6002185697822302</v>
+      </c>
+      <c r="AP6">
+        <v>0.8699782536556342</v>
+      </c>
+      <c r="AQ6">
+        <v>-1.518310779196472</v>
+      </c>
+      <c r="AR6">
+        <v>0.7210638650693169</v>
+      </c>
+      <c r="AS6">
+        <v>0.04445506254669351</v>
+      </c>
+      <c r="AT6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18">
+    <row r="7" spans="1:46">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="B7" s="2">
         <v>46259</v>
@@ -815,7 +1463,7 @@
         <v>46258</v>
       </c>
       <c r="D7" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -824,13 +1472,13 @@
         <v>1</v>
       </c>
       <c r="G7">
-        <v>3.423687884877389</v>
+        <v>3.376630418212414</v>
       </c>
       <c r="H7">
-        <v>1.384163229096249</v>
+        <v>1.383021458836645</v>
       </c>
       <c r="I7">
-        <v>0.3183101443087978</v>
+        <v>0.3188286305863484</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -839,30 +1487,114 @@
         <v>1</v>
       </c>
       <c r="L7">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="M7">
         <v>16</v>
       </c>
       <c r="N7">
-        <v>-0.08398445880735673</v>
+        <v>-0.08473376008714599</v>
       </c>
       <c r="O7">
-        <v>-23.91989468625772</v>
+        <v>-24.13330569057162</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>3.423687884877389</v>
-      </c>
-      <c r="R7" t="b">
+        <v>3.376630418212414</v>
+      </c>
+      <c r="R7" t="s">
+        <v>58</v>
+      </c>
+      <c r="S7" t="s">
+        <v>61</v>
+      </c>
+      <c r="T7">
+        <v>0.9052059991432598</v>
+      </c>
+      <c r="U7">
+        <v>0.9573412545182542</v>
+      </c>
+      <c r="V7" t="s">
+        <v>56</v>
+      </c>
+      <c r="W7" t="s">
+        <v>65</v>
+      </c>
+      <c r="X7">
+        <v>0.9997983796329584</v>
+      </c>
+      <c r="Y7">
+        <v>0.999994219615149</v>
+      </c>
+      <c r="Z7">
+        <v>0.0001958399821906376</v>
+      </c>
+      <c r="AA7">
+        <v>1</v>
+      </c>
+      <c r="AB7">
+        <v>35.86384927527484</v>
+      </c>
+      <c r="AC7">
+        <v>4.000000000000005</v>
+      </c>
+      <c r="AD7">
+        <v>0.8104114503375457</v>
+      </c>
+      <c r="AE7">
+        <v>0.5858611449497191</v>
+      </c>
+      <c r="AF7">
+        <v>3.217152312080793</v>
+      </c>
+      <c r="AG7">
+        <v>3.217133715702305</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ7" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK7" t="s">
+        <v>74</v>
+      </c>
+      <c r="AL7">
+        <v>0.8104067658474751</v>
+      </c>
+      <c r="AM7">
+        <v>0.9367543457803579</v>
+      </c>
+      <c r="AN7">
+        <v>2.621397111205324</v>
+      </c>
+      <c r="AO7">
+        <v>1.863913365961104</v>
+      </c>
+      <c r="AP7">
+        <v>3.953780588612692</v>
+      </c>
+      <c r="AQ7">
+        <v>-4.968332378490205</v>
+      </c>
+      <c r="AR7">
+        <v>3.466742252617929</v>
+      </c>
+      <c r="AS7">
+        <v>0.04244710790805367</v>
+      </c>
+      <c r="AT7" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:18">
+    <row r="8" spans="1:46">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="B8" s="2">
         <v>46259</v>
@@ -871,7 +1603,7 @@
         <v>46258</v>
       </c>
       <c r="D8" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="E8">
         <v>-1</v>
@@ -880,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>0.2424267865881329</v>
+        <v>0.2098877567079735</v>
       </c>
       <c r="H8">
-        <v>1.442660418469517</v>
+        <v>1.433154931778823</v>
       </c>
       <c r="I8">
-        <v>0.3572132547595961</v>
+        <v>0.3529124887615865</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -901,24 +1633,108 @@
         <v>1</v>
       </c>
       <c r="N8">
-        <v>0.001057763505493801</v>
+        <v>0.0009359745054607138</v>
       </c>
       <c r="O8">
-        <v>0.2723938025735915</v>
+        <v>0.2410308668527559</v>
       </c>
       <c r="P8">
-        <v>0.4196002305576166</v>
+        <v>0.4468338261535981</v>
       </c>
       <c r="Q8">
-        <v>0.4176893226905368</v>
-      </c>
-      <c r="R8" t="b">
+        <v>0.3794298469997431</v>
+      </c>
+      <c r="R8" t="s">
+        <v>59</v>
+      </c>
+      <c r="S8" t="s">
+        <v>62</v>
+      </c>
+      <c r="T8">
+        <v>-0.4786854589865791</v>
+      </c>
+      <c r="U8">
+        <v>0.615396889916729</v>
+      </c>
+      <c r="V8" t="s">
+        <v>64</v>
+      </c>
+      <c r="W8" t="s">
+        <v>64</v>
+      </c>
+      <c r="X8">
+        <v>0.9999388654303956</v>
+      </c>
+      <c r="Y8">
+        <v>0.999953733491074</v>
+      </c>
+      <c r="Z8">
+        <v>1.486806067840796E-05</v>
+      </c>
+      <c r="AA8">
+        <v>1</v>
+      </c>
+      <c r="AB8">
+        <v>-97.28366775253524</v>
+      </c>
+      <c r="AC8">
+        <v>1.000000000000001</v>
+      </c>
+      <c r="AD8">
+        <v>-0.1267818624516298</v>
+      </c>
+      <c r="AE8">
+        <v>-0.9919306222479958</v>
+      </c>
+      <c r="AF8">
+        <v>2.194490406026454</v>
+      </c>
+      <c r="AG8">
+        <v>2.194388874616495</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>66</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>68</v>
+      </c>
+      <c r="AJ8" t="s">
+        <v>71</v>
+      </c>
+      <c r="AK8" t="s">
+        <v>75</v>
+      </c>
+      <c r="AL8">
+        <v>-0.126775996697459</v>
+      </c>
+      <c r="AM8">
+        <v>0.7151617103253179</v>
+      </c>
+      <c r="AN8">
+        <v>-0.2817740179368917</v>
+      </c>
+      <c r="AO8">
+        <v>-2.176189959696946</v>
+      </c>
+      <c r="AP8">
+        <v>-0.4871606582622389</v>
+      </c>
+      <c r="AQ8">
+        <v>0.3878479786061856</v>
+      </c>
+      <c r="AR8">
+        <v>0.4413154083216378</v>
+      </c>
+      <c r="AS8">
+        <v>0.1523777008803119</v>
+      </c>
+      <c r="AT8" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:18">
+    <row r="9" spans="1:46">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="B9" s="2">
         <v>46259</v>
@@ -927,7 +1743,7 @@
         <v>46258</v>
       </c>
       <c r="D9" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="E9">
         <v>-1</v>
@@ -936,13 +1752,13 @@
         <v>1</v>
       </c>
       <c r="G9">
-        <v>4.490804287764481</v>
+        <v>4.458899308317085</v>
       </c>
       <c r="H9">
-        <v>2.964830868468014</v>
+        <v>2.957032442812923</v>
       </c>
       <c r="I9">
-        <v>0.6040366097843416</v>
+        <v>0.6037219052884913</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -957,24 +1773,108 @@
         <v>28</v>
       </c>
       <c r="N9">
-        <v>0.3788601391730193</v>
+        <v>0.3831418798926623</v>
       </c>
       <c r="O9">
-        <v>59.93606360158567</v>
+        <v>60.6134393863758</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>4.490804287764481</v>
-      </c>
-      <c r="R9" t="b">
+        <v>4.458899308317085</v>
+      </c>
+      <c r="R9" t="s">
+        <v>59</v>
+      </c>
+      <c r="S9" t="s">
+        <v>62</v>
+      </c>
+      <c r="T9">
+        <v>-0.9424296120656104</v>
+      </c>
+      <c r="U9">
+        <v>0.9740642884105478</v>
+      </c>
+      <c r="V9" t="s">
+        <v>57</v>
+      </c>
+      <c r="W9" t="s">
+        <v>65</v>
+      </c>
+      <c r="X9">
+        <v>0.9991807365774891</v>
+      </c>
+      <c r="Y9">
+        <v>0.9998838519240926</v>
+      </c>
+      <c r="Z9">
+        <v>0.0007031153466035001</v>
+      </c>
+      <c r="AA9">
+        <v>1</v>
+      </c>
+      <c r="AB9">
+        <v>-152.2333798732249</v>
+      </c>
+      <c r="AC9">
+        <v>7.999999999999998</v>
+      </c>
+      <c r="AD9">
+        <v>-0.8848525366646968</v>
+      </c>
+      <c r="AE9">
+        <v>-0.4658712143479693</v>
+      </c>
+      <c r="AF9">
+        <v>3.719108131618522</v>
+      </c>
+      <c r="AG9">
+        <v>3.718676164364943</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>57</v>
+      </c>
+      <c r="AI9" t="s">
+        <v>69</v>
+      </c>
+      <c r="AJ9" t="s">
+        <v>72</v>
+      </c>
+      <c r="AK9" t="s">
+        <v>76</v>
+      </c>
+      <c r="AL9">
+        <v>-0.8847497627451013</v>
+      </c>
+      <c r="AM9">
+        <v>0.9589348227309553</v>
+      </c>
+      <c r="AN9">
+        <v>-3.311549434642514</v>
+      </c>
+      <c r="AO9">
+        <v>-1.686046025948992</v>
+      </c>
+      <c r="AP9">
+        <v>-5.87752958986212</v>
+      </c>
+      <c r="AQ9">
+        <v>4.054848521620608</v>
+      </c>
+      <c r="AR9">
+        <v>5.465289041106415</v>
+      </c>
+      <c r="AS9">
+        <v>0.04320190961257366</v>
+      </c>
+      <c r="AT9" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:18">
+    <row r="10" spans="1:46">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="B10" s="2">
         <v>46259</v>
@@ -983,7 +1883,7 @@
         <v>46258</v>
       </c>
       <c r="D10" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="E10">
         <v>-1</v>
@@ -992,13 +1892,13 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>1.537751271770883</v>
+        <v>1.440812448376137</v>
       </c>
       <c r="H10">
-        <v>2.046836583518512</v>
+        <v>2.041564381559437</v>
       </c>
       <c r="I10">
-        <v>0.4696265749698216</v>
+        <v>0.46340057313835</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1010,27 +1910,111 @@
         <v>233</v>
       </c>
       <c r="M10">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N10">
-        <v>14.15707618152033</v>
+        <v>14.8509263337744</v>
       </c>
       <c r="O10">
-        <v>23.36977556199568</v>
+        <v>24.51514782134683</v>
       </c>
       <c r="P10">
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>1.537751271770883</v>
-      </c>
-      <c r="R10" t="b">
+        <v>1.440812448376137</v>
+      </c>
+      <c r="R10" t="s">
+        <v>60</v>
+      </c>
+      <c r="S10" t="s">
+        <v>63</v>
+      </c>
+      <c r="T10">
+        <v>-0.9979897629802601</v>
+      </c>
+      <c r="U10">
+        <v>0.848502317540091</v>
+      </c>
+      <c r="V10" t="s">
+        <v>57</v>
+      </c>
+      <c r="W10" t="s">
+        <v>65</v>
+      </c>
+      <c r="X10">
+        <v>0.9927264814093597</v>
+      </c>
+      <c r="Y10">
+        <v>0.9976276967958955</v>
+      </c>
+      <c r="Z10">
+        <v>0.004901215386535762</v>
+      </c>
+      <c r="AA10">
+        <v>0.04922462486363275</v>
+      </c>
+      <c r="AB10">
+        <v>173.9493804213141</v>
+      </c>
+      <c r="AC10">
+        <v>24.00000000000001</v>
+      </c>
+      <c r="AD10">
+        <v>-0.9944291586207727</v>
+      </c>
+      <c r="AE10">
+        <v>0.1054070608867452</v>
+      </c>
+      <c r="AF10">
+        <v>1.30245372717942</v>
+      </c>
+      <c r="AG10">
+        <v>1.299363912029234</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>57</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>69</v>
+      </c>
+      <c r="AJ10" t="s">
+        <v>73</v>
+      </c>
+      <c r="AK10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AL10">
+        <v>-0.5204521741159502</v>
+      </c>
+      <c r="AM10">
+        <v>0.8012011517805757</v>
+      </c>
+      <c r="AN10">
+        <v>-1.274209289886901</v>
+      </c>
+      <c r="AO10">
+        <v>0.2195193766033079</v>
+      </c>
+      <c r="AP10">
+        <v>-0.9792225666673142</v>
+      </c>
+      <c r="AQ10">
+        <v>3.667075126397408</v>
+      </c>
+      <c r="AR10">
+        <v>0.7680871446875039</v>
+      </c>
+      <c r="AS10">
+        <v>0.04094809771297364</v>
+      </c>
+      <c r="AT10" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:18">
+    <row r="11" spans="1:46">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="B11" s="2">
         <v>46259</v>
@@ -1039,22 +2023,22 @@
         <v>46258</v>
       </c>
       <c r="D11" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E11">
         <v>1</v>
       </c>
       <c r="F11">
-        <v>0.1601536574253007</v>
+        <v>0.1558771339693187</v>
       </c>
       <c r="G11">
-        <v>2.338976754730542</v>
+        <v>2.333259364297918</v>
       </c>
       <c r="H11">
-        <v>2.764540263974955</v>
+        <v>2.764186330281507</v>
       </c>
       <c r="I11">
-        <v>0.6261116509601294</v>
+        <v>0.6261237024934693</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -1069,18 +2053,102 @@
         <v>9</v>
       </c>
       <c r="N11">
-        <v>-789.4654362810599</v>
+        <v>-787.6605545491965</v>
       </c>
       <c r="O11">
-        <v>-9.448896618351332</v>
+        <v>-9.427294480868195</v>
       </c>
       <c r="P11">
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>2.338976754730542</v>
-      </c>
-      <c r="R11" t="b">
+        <v>2.333259364297918</v>
+      </c>
+      <c r="R11" t="s">
+        <v>58</v>
+      </c>
+      <c r="S11" t="s">
+        <v>61</v>
+      </c>
+      <c r="T11">
+        <v>0.8326459262956046</v>
+      </c>
+      <c r="U11">
+        <v>0.7980625052793621</v>
+      </c>
+      <c r="V11" t="s">
+        <v>56</v>
+      </c>
+      <c r="W11" t="s">
+        <v>65</v>
+      </c>
+      <c r="X11">
+        <v>0.9996627976922225</v>
+      </c>
+      <c r="Y11">
+        <v>0.9999610734037686</v>
+      </c>
+      <c r="Z11">
+        <v>0.0002982757115460588</v>
+      </c>
+      <c r="AA11">
+        <v>1</v>
+      </c>
+      <c r="AB11">
+        <v>44.667444358273</v>
+      </c>
+      <c r="AC11">
+        <v>5.000000000000007</v>
+      </c>
+      <c r="AD11">
+        <v>0.7111990301865317</v>
+      </c>
+      <c r="AE11">
+        <v>0.7029907107933481</v>
+      </c>
+      <c r="AF11">
+        <v>2.535674462720049</v>
+      </c>
+      <c r="AG11">
+        <v>2.535575757544065</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI11" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ11" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK11" t="s">
+        <v>74</v>
+      </c>
+      <c r="AL11">
+        <v>0.7111713456290435</v>
+      </c>
+      <c r="AM11">
+        <v>0.9058400495282899</v>
+      </c>
+      <c r="AN11">
+        <v>1.820105687051705</v>
+      </c>
+      <c r="AO11">
+        <v>1.76423491000674</v>
+      </c>
+      <c r="AP11">
+        <v>2.671512049342179</v>
+      </c>
+      <c r="AQ11">
+        <v>-3.212159978830436</v>
+      </c>
+      <c r="AR11">
+        <v>2.35473461935825</v>
+      </c>
+      <c r="AS11">
+        <v>0.05004023479325828</v>
+      </c>
+      <c r="AT11" t="b">
         <v>1</v>
       </c>
     </row>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="78">
   <si>
     <t>Pair</t>
   </si>
@@ -67,6 +67,90 @@
     <t>TerrainBundleSep</t>
   </si>
   <si>
+    <t>MarketPosture</t>
+  </si>
+  <si>
+    <t>MarketPostureCN</t>
+  </si>
+  <si>
+    <t>MarketPostureScore</t>
+  </si>
+  <si>
+    <t>MarketPostureConfidence</t>
+  </si>
+  <si>
+    <t>PhasedDirection</t>
+  </si>
+  <si>
+    <t>PhasedAlignment</t>
+  </si>
+  <si>
+    <t>PhasedRawCoherence</t>
+  </si>
+  <si>
+    <t>PhasedCoherence</t>
+  </si>
+  <si>
+    <t>PhasedSteeringGain</t>
+  </si>
+  <si>
+    <t>PhasedGate</t>
+  </si>
+  <si>
+    <t>PhasedBeamPhaseDeg</t>
+  </si>
+  <si>
+    <t>PhasedGradientDeg</t>
+  </si>
+  <si>
+    <t>PhasedDirectionScore</t>
+  </si>
+  <si>
+    <t>PhasedImpulseScore</t>
+  </si>
+  <si>
+    <t>PhasedAmplitude</t>
+  </si>
+  <si>
+    <t>PhasedPower</t>
+  </si>
+  <si>
+    <t>SurveyTrend</t>
+  </si>
+  <si>
+    <t>SurveyTrendCN</t>
+  </si>
+  <si>
+    <t>TerrainPattern</t>
+  </si>
+  <si>
+    <t>TerrainPatternCN</t>
+  </si>
+  <si>
+    <t>SurveyDirectionScore</t>
+  </si>
+  <si>
+    <t>SurveyConfidence</t>
+  </si>
+  <si>
+    <t>ContourElevation</t>
+  </si>
+  <si>
+    <t>ContourTemporalSlope</t>
+  </si>
+  <si>
+    <t>ContourScaleSlope</t>
+  </si>
+  <si>
+    <t>ContourCurvature</t>
+  </si>
+  <si>
+    <t>ContourRelief</t>
+  </si>
+  <si>
+    <t>ContourRoughness</t>
+  </si>
+  <si>
     <t>FilterEnabled</t>
   </si>
   <si>
@@ -104,6 +188,66 @@
   </si>
   <si>
     <t>DOWN</t>
+  </si>
+  <si>
+    <t>UP_ACCELERATING</t>
+  </si>
+  <si>
+    <t>DOWN_ACCELERATING</t>
+  </si>
+  <si>
+    <t>DOWN_STEADY</t>
+  </si>
+  <si>
+    <t>多头加速</t>
+  </si>
+  <si>
+    <t>空头加速</t>
+  </si>
+  <si>
+    <t>空头稳态</t>
+  </si>
+  <si>
+    <t>NEUTRAL</t>
+  </si>
+  <si>
+    <t>ALIGNED</t>
+  </si>
+  <si>
+    <t>TRANSITION</t>
+  </si>
+  <si>
+    <t>上涨</t>
+  </si>
+  <si>
+    <t>转换</t>
+  </si>
+  <si>
+    <t>下跌</t>
+  </si>
+  <si>
+    <t>UP_STEEPENING</t>
+  </si>
+  <si>
+    <t>TRANSITION_ZONE</t>
+  </si>
+  <si>
+    <t>DOWN_STEEPENING</t>
+  </si>
+  <si>
+    <t>DOWN_SLOPE</t>
+  </si>
+  <si>
+    <t>上升陡坡形成</t>
+  </si>
+  <si>
+    <t>地形转换区</t>
+  </si>
+  <si>
+    <t>下降陡坡形成</t>
+  </si>
+  <si>
+    <t>下降坡延续</t>
   </si>
 </sst>
 </file>
@@ -465,10 +609,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:AT11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:46">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -523,10 +667,94 @@
       <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>45</v>
+      </c>
     </row>
-    <row r="2" spans="1:18">
+    <row r="2" spans="1:46">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="B2" s="2">
         <v>46260</v>
@@ -535,7 +763,7 @@
         <v>46259</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -576,13 +804,97 @@
       <c r="Q2">
         <v>0.795598308645689</v>
       </c>
-      <c r="R2" t="b">
+      <c r="R2" t="s">
+        <v>58</v>
+      </c>
+      <c r="S2" t="s">
+        <v>61</v>
+      </c>
+      <c r="T2">
+        <v>0.8709724158689343</v>
+      </c>
+      <c r="U2">
+        <v>0.7919276991632392</v>
+      </c>
+      <c r="V2" t="s">
+        <v>56</v>
+      </c>
+      <c r="W2" t="s">
+        <v>65</v>
+      </c>
+      <c r="X2">
+        <v>0.9997731482654194</v>
+      </c>
+      <c r="Y2">
+        <v>0.9999604480888752</v>
+      </c>
+      <c r="Z2">
+        <v>0.0001872998234557777</v>
+      </c>
+      <c r="AA2">
+        <v>0.3240539114619911</v>
+      </c>
+      <c r="AB2">
+        <v>44.30612101281891</v>
+      </c>
+      <c r="AC2">
+        <v>4.000000000000005</v>
+      </c>
+      <c r="AD2">
+        <v>0.7156181166386435</v>
+      </c>
+      <c r="AE2">
+        <v>0.6984917402078287</v>
+      </c>
+      <c r="AF2">
+        <v>0.8909277083529237</v>
+      </c>
+      <c r="AG2">
+        <v>0.8908924704593842</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AL2">
+        <v>0.4737397451708066</v>
+      </c>
+      <c r="AM2">
+        <v>0.7725345957569094</v>
+      </c>
+      <c r="AN2">
+        <v>0.6427796943077172</v>
+      </c>
+      <c r="AO2">
+        <v>0.6166249742153718</v>
+      </c>
+      <c r="AP2">
+        <v>0.8103174576174301</v>
+      </c>
+      <c r="AQ2">
+        <v>-1.343859367270114</v>
+      </c>
+      <c r="AR2">
+        <v>0.6849813451994347</v>
+      </c>
+      <c r="AS2">
+        <v>0.04631852238792044</v>
+      </c>
+      <c r="AT2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:18">
+    <row r="3" spans="1:46">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="B3" s="2">
         <v>46260</v>
@@ -591,7 +903,7 @@
         <v>46259</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -600,13 +912,13 @@
         <v>1</v>
       </c>
       <c r="G3">
-        <v>2.646988262876885</v>
+        <v>2.609871596674189</v>
       </c>
       <c r="H3">
         <v>1.853330676903088</v>
       </c>
       <c r="I3">
-        <v>0.4207779026683111</v>
+        <v>0.4216940605038454</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -618,27 +930,111 @@
         <v>225</v>
       </c>
       <c r="M3">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="N3">
-        <v>-0.04497468038119797</v>
+        <v>-0.04628519515894085</v>
       </c>
       <c r="O3">
-        <v>-15.21250363220035</v>
+        <v>-15.65577995228734</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>2.646988262876885</v>
-      </c>
-      <c r="R3" t="b">
+        <v>2.609871596674189</v>
+      </c>
+      <c r="R3" t="s">
+        <v>58</v>
+      </c>
+      <c r="S3" t="s">
+        <v>61</v>
+      </c>
+      <c r="T3">
+        <v>0.8675991539142461</v>
+      </c>
+      <c r="U3">
+        <v>0.9404164441058944</v>
+      </c>
+      <c r="V3" t="s">
+        <v>56</v>
+      </c>
+      <c r="W3" t="s">
+        <v>65</v>
+      </c>
+      <c r="X3">
+        <v>0.9992798359880024</v>
+      </c>
+      <c r="Y3">
+        <v>0.9999872993779348</v>
+      </c>
+      <c r="Z3">
+        <v>0.000707463389932439</v>
+      </c>
+      <c r="AA3">
+        <v>1</v>
+      </c>
+      <c r="AB3">
+        <v>42.67616662423193</v>
+      </c>
+      <c r="AC3">
+        <v>7.999999999999998</v>
+      </c>
+      <c r="AD3">
+        <v>0.7351966262340277</v>
+      </c>
+      <c r="AE3">
+        <v>0.6778539081351552</v>
+      </c>
+      <c r="AF3">
+        <v>2.706885419526051</v>
+      </c>
+      <c r="AG3">
+        <v>2.706851040397364</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AL3">
+        <v>0.7351872887795343</v>
+      </c>
+      <c r="AM3">
+        <v>0.9135148561148612</v>
+      </c>
+      <c r="AN3">
+        <v>2.015729191342458</v>
+      </c>
+      <c r="AO3">
+        <v>1.803750173660602</v>
+      </c>
+      <c r="AP3">
+        <v>3.077224726278764</v>
+      </c>
+      <c r="AQ3">
+        <v>-3.182921922031068</v>
+      </c>
+      <c r="AR3">
+        <v>2.767059520123484</v>
+      </c>
+      <c r="AS3">
+        <v>0.04693124358416298</v>
+      </c>
+      <c r="AT3" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:18">
+    <row r="4" spans="1:46">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="B4" s="2">
         <v>46260</v>
@@ -647,7 +1043,7 @@
         <v>46259</v>
       </c>
       <c r="D4" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -688,13 +1084,97 @@
       <c r="Q4">
         <v>1.0925661464973</v>
       </c>
-      <c r="R4" t="b">
+      <c r="R4" t="s">
+        <v>58</v>
+      </c>
+      <c r="S4" t="s">
+        <v>61</v>
+      </c>
+      <c r="T4">
+        <v>0.7913175097708476</v>
+      </c>
+      <c r="U4">
+        <v>0.7560899607813154</v>
+      </c>
+      <c r="V4" t="s">
+        <v>56</v>
+      </c>
+      <c r="W4" t="s">
+        <v>65</v>
+      </c>
+      <c r="X4">
+        <v>0.9989735078829162</v>
+      </c>
+      <c r="Y4">
+        <v>0.999988325537736</v>
+      </c>
+      <c r="Z4">
+        <v>0.001014817654819811</v>
+      </c>
+      <c r="AA4">
+        <v>0.401314667508557</v>
+      </c>
+      <c r="AB4">
+        <v>55.89448443459531</v>
+      </c>
+      <c r="AC4">
+        <v>10</v>
+      </c>
+      <c r="AD4">
+        <v>0.5607187050083993</v>
+      </c>
+      <c r="AE4">
+        <v>0.8280063609983341</v>
+      </c>
+      <c r="AF4">
+        <v>1.636880032338598</v>
+      </c>
+      <c r="AG4">
+        <v>1.63686092264443</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>74</v>
+      </c>
+      <c r="AL4">
+        <v>0.3928670862718177</v>
+      </c>
+      <c r="AM4">
+        <v>0.7421273585218244</v>
+      </c>
+      <c r="AN4">
+        <v>0.9475600812747735</v>
+      </c>
+      <c r="AO4">
+        <v>1.332669590966227</v>
+      </c>
+      <c r="AP4">
+        <v>0.834662849186111</v>
+      </c>
+      <c r="AQ4">
+        <v>-3.02249665137887</v>
+      </c>
+      <c r="AR4">
+        <v>0.7483760603816799</v>
+      </c>
+      <c r="AS4">
+        <v>0.04231400280409587</v>
+      </c>
+      <c r="AT4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:18">
+    <row r="5" spans="1:46">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="B5" s="2">
         <v>46260</v>
@@ -703,7 +1183,7 @@
         <v>46259</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -712,13 +1192,13 @@
         <v>1</v>
       </c>
       <c r="G5">
-        <v>2.881508613948418</v>
+        <v>2.84909425193396</v>
       </c>
       <c r="H5">
-        <v>1.448280628557377</v>
+        <v>1.438219567414882</v>
       </c>
       <c r="I5">
-        <v>0.3082550617361647</v>
+        <v>0.307898189495003</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -733,24 +1213,108 @@
         <v>14</v>
       </c>
       <c r="N5">
-        <v>-0.05785491561086088</v>
+        <v>-0.05738176607616784</v>
       </c>
       <c r="O5">
-        <v>-18.05346748137857</v>
+        <v>-17.90582246888102</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>2.881508613948418</v>
-      </c>
-      <c r="R5" t="b">
+        <v>2.84909425193396</v>
+      </c>
+      <c r="R5" t="s">
+        <v>58</v>
+      </c>
+      <c r="S5" t="s">
+        <v>61</v>
+      </c>
+      <c r="T5">
+        <v>0.8744470211803734</v>
+      </c>
+      <c r="U5">
+        <v>0.9434904413132446</v>
+      </c>
+      <c r="V5" t="s">
+        <v>56</v>
+      </c>
+      <c r="W5" t="s">
+        <v>65</v>
+      </c>
+      <c r="X5">
+        <v>0.9998510080070387</v>
+      </c>
+      <c r="Y5">
+        <v>0.9999571271283061</v>
+      </c>
+      <c r="Z5">
+        <v>0.0001061191212673451</v>
+      </c>
+      <c r="AA5">
+        <v>1</v>
+      </c>
+      <c r="AB5">
+        <v>41.50579837541022</v>
+      </c>
+      <c r="AC5">
+        <v>3.000000000000004</v>
+      </c>
+      <c r="AD5">
+        <v>0.7488886593132085</v>
+      </c>
+      <c r="AE5">
+        <v>0.6626958396972665</v>
+      </c>
+      <c r="AF5">
+        <v>3.056795997873015</v>
+      </c>
+      <c r="AG5">
+        <v>3.056664944250403</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>74</v>
+      </c>
+      <c r="AL5">
+        <v>0.7488565523058047</v>
+      </c>
+      <c r="AM5">
+        <v>0.9186281690292669</v>
+      </c>
+      <c r="AN5">
+        <v>2.301997397202923</v>
+      </c>
+      <c r="AO5">
+        <v>2.010478948015788</v>
+      </c>
+      <c r="AP5">
+        <v>2.933383030925631</v>
+      </c>
+      <c r="AQ5">
+        <v>-5.417584511771893</v>
+      </c>
+      <c r="AR5">
+        <v>2.426649573297757</v>
+      </c>
+      <c r="AS5">
+        <v>0.04015615506401868</v>
+      </c>
+      <c r="AT5" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:18">
+    <row r="6" spans="1:46">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="B6" s="2">
         <v>46260</v>
@@ -759,7 +1323,7 @@
         <v>46259</v>
       </c>
       <c r="D6" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -800,13 +1364,97 @@
       <c r="Q6">
         <v>0.8629951360537029</v>
       </c>
-      <c r="R6" t="b">
+      <c r="R6" t="s">
+        <v>58</v>
+      </c>
+      <c r="S6" t="s">
+        <v>61</v>
+      </c>
+      <c r="T6">
+        <v>0.8805742450343832</v>
+      </c>
+      <c r="U6">
+        <v>0.8479408764376916</v>
+      </c>
+      <c r="V6" t="s">
+        <v>56</v>
+      </c>
+      <c r="W6" t="s">
+        <v>65</v>
+      </c>
+      <c r="X6">
+        <v>0.9999022048839805</v>
+      </c>
+      <c r="Y6">
+        <v>0.9999868886233635</v>
+      </c>
+      <c r="Z6">
+        <v>8.468373938297358E-05</v>
+      </c>
+      <c r="AA6">
+        <v>0.5477510107761134</v>
+      </c>
+      <c r="AB6">
+        <v>41.62964068025791</v>
+      </c>
+      <c r="AC6">
+        <v>3.000000000000004</v>
+      </c>
+      <c r="AD6">
+        <v>0.7474545231848799</v>
+      </c>
+      <c r="AE6">
+        <v>0.6643129802814813</v>
+      </c>
+      <c r="AF6">
+        <v>0.922652263866525</v>
+      </c>
+      <c r="AG6">
+        <v>0.9226401666251889</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>74</v>
+      </c>
+      <c r="AL6">
+        <v>0.5784291627822391</v>
+      </c>
+      <c r="AM6">
+        <v>0.8274681041271014</v>
+      </c>
+      <c r="AN6">
+        <v>0.6935027086703082</v>
+      </c>
+      <c r="AO6">
+        <v>0.6084198367620823</v>
+      </c>
+      <c r="AP6">
+        <v>0.9067300443565722</v>
+      </c>
+      <c r="AQ6">
+        <v>-1.64238262985989</v>
+      </c>
+      <c r="AR6">
+        <v>0.7494457056626387</v>
+      </c>
+      <c r="AS6">
+        <v>0.04209244001175027</v>
+      </c>
+      <c r="AT6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18">
+    <row r="7" spans="1:46">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="B7" s="2">
         <v>46260</v>
@@ -815,7 +1463,7 @@
         <v>46259</v>
       </c>
       <c r="D7" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -824,13 +1472,13 @@
         <v>1</v>
       </c>
       <c r="G7">
-        <v>3.259009253985194</v>
+        <v>3.21473373001301</v>
       </c>
       <c r="H7">
-        <v>1.390906810287543</v>
+        <v>1.389873780052663</v>
       </c>
       <c r="I7">
-        <v>0.3227720543243077</v>
+        <v>0.3232336634877695</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -839,30 +1487,114 @@
         <v>1</v>
       </c>
       <c r="L7">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="M7">
         <v>17</v>
       </c>
       <c r="N7">
-        <v>-0.09336610952464096</v>
+        <v>-0.09397676910388937</v>
       </c>
       <c r="O7">
-        <v>-25.42551124965911</v>
+        <v>-25.59180640837293</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>3.259009253985194</v>
-      </c>
-      <c r="R7" t="b">
+        <v>3.21473373001301</v>
+      </c>
+      <c r="R7" t="s">
+        <v>58</v>
+      </c>
+      <c r="S7" t="s">
+        <v>61</v>
+      </c>
+      <c r="T7">
+        <v>0.9186938755791447</v>
+      </c>
+      <c r="U7">
+        <v>0.9634091384850991</v>
+      </c>
+      <c r="V7" t="s">
+        <v>56</v>
+      </c>
+      <c r="W7" t="s">
+        <v>65</v>
+      </c>
+      <c r="X7">
+        <v>0.999972514222352</v>
+      </c>
+      <c r="Y7">
+        <v>0.9999875778979358</v>
+      </c>
+      <c r="Z7">
+        <v>1.506367558379296E-05</v>
+      </c>
+      <c r="AA7">
+        <v>1</v>
+      </c>
+      <c r="AB7">
+        <v>33.13481389077527</v>
+      </c>
+      <c r="AC7">
+        <v>1.000000000000001</v>
+      </c>
+      <c r="AD7">
+        <v>0.837386741152767</v>
+      </c>
+      <c r="AE7">
+        <v>0.5466108723228515</v>
+      </c>
+      <c r="AF7">
+        <v>3.014583619265697</v>
+      </c>
+      <c r="AG7">
+        <v>3.014546171800297</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ7" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK7" t="s">
+        <v>74</v>
+      </c>
+      <c r="AL7">
+        <v>0.8373763390492012</v>
+      </c>
+      <c r="AM7">
+        <v>0.9453642512955005</v>
+      </c>
+      <c r="AN7">
+        <v>2.527708178710714</v>
+      </c>
+      <c r="AO7">
+        <v>1.642530426474649</v>
+      </c>
+      <c r="AP7">
+        <v>3.630900095404568</v>
+      </c>
+      <c r="AQ7">
+        <v>-5.305839159353135</v>
+      </c>
+      <c r="AR7">
+        <v>3.125769804913606</v>
+      </c>
+      <c r="AS7">
+        <v>0.03898282209738079</v>
+      </c>
+      <c r="AT7" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:18">
+    <row r="8" spans="1:46">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="B8" s="2">
         <v>46260</v>
@@ -871,7 +1603,7 @@
         <v>46259</v>
       </c>
       <c r="D8" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="E8">
         <v>-1</v>
@@ -880,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>0.2273156060492538</v>
+        <v>0.1929018080286625</v>
       </c>
       <c r="H8">
-        <v>1.443557670436812</v>
+        <v>1.433850188845725</v>
       </c>
       <c r="I8">
-        <v>0.3575216783472204</v>
+        <v>0.3531642707697492</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -901,24 +1633,108 @@
         <v>2</v>
       </c>
       <c r="N8">
-        <v>0.002324647049096809</v>
+        <v>0.002079600949611913</v>
       </c>
       <c r="O8">
-        <v>0.6016834662110458</v>
+        <v>0.5382587039113867</v>
       </c>
       <c r="P8">
-        <v>0.4334049153738571</v>
+        <v>0.4687800928647571</v>
       </c>
       <c r="Q8">
-        <v>0.4011958667083103</v>
-      </c>
-      <c r="R8" t="b">
+        <v>0.3631298553341898</v>
+      </c>
+      <c r="R8" t="s">
+        <v>59</v>
+      </c>
+      <c r="S8" t="s">
+        <v>62</v>
+      </c>
+      <c r="T8">
+        <v>-0.4874151685407133</v>
+      </c>
+      <c r="U8">
+        <v>0.6193303928731442</v>
+      </c>
+      <c r="V8" t="s">
+        <v>64</v>
+      </c>
+      <c r="W8" t="s">
+        <v>64</v>
+      </c>
+      <c r="X8">
+        <v>0.9998149293921575</v>
+      </c>
+      <c r="Y8">
+        <v>0.9999742681192927</v>
+      </c>
+      <c r="Z8">
+        <v>0.0001593387271351387</v>
+      </c>
+      <c r="AA8">
+        <v>1</v>
+      </c>
+      <c r="AB8">
+        <v>-98.12953213079992</v>
+      </c>
+      <c r="AC8">
+        <v>4.000000000000005</v>
+      </c>
+      <c r="AD8">
+        <v>-0.1414115039806741</v>
+      </c>
+      <c r="AE8">
+        <v>-0.9899509010763735</v>
+      </c>
+      <c r="AF8">
+        <v>2.0726984447467</v>
+      </c>
+      <c r="AG8">
+        <v>2.072645110317578</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>66</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>68</v>
+      </c>
+      <c r="AJ8" t="s">
+        <v>71</v>
+      </c>
+      <c r="AK8" t="s">
+        <v>75</v>
+      </c>
+      <c r="AL8">
+        <v>-0.141407865196723</v>
+      </c>
+      <c r="AM8">
+        <v>0.7270645026194514</v>
+      </c>
+      <c r="AN8">
+        <v>-0.308798224276107</v>
+      </c>
+      <c r="AO8">
+        <v>-2.049178491698392</v>
+      </c>
+      <c r="AP8">
+        <v>-0.3035029589787233</v>
+      </c>
+      <c r="AQ8">
+        <v>1.108818956787369</v>
+      </c>
+      <c r="AR8">
+        <v>0.3427606841431051</v>
+      </c>
+      <c r="AS8">
+        <v>0.1023329494433545</v>
+      </c>
+      <c r="AT8" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:18">
+    <row r="9" spans="1:46">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="B9" s="2">
         <v>46260</v>
@@ -927,7 +1743,7 @@
         <v>46259</v>
       </c>
       <c r="D9" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="E9">
         <v>-1</v>
@@ -936,13 +1752,13 @@
         <v>1</v>
       </c>
       <c r="G9">
-        <v>4.350557600567822</v>
+        <v>4.320280435854132</v>
       </c>
       <c r="H9">
-        <v>2.971639541138721</v>
+        <v>2.964435220140667</v>
       </c>
       <c r="I9">
-        <v>0.6063268842428025</v>
+        <v>0.605970524410009</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -957,24 +1773,108 @@
         <v>29</v>
       </c>
       <c r="N9">
-        <v>0.4001097563017769</v>
+        <v>0.4042222680028851</v>
       </c>
       <c r="O9">
-        <v>61.04219024927693</v>
+        <v>61.66960989528048</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>4.350557600567822</v>
-      </c>
-      <c r="R9" t="b">
+        <v>4.320280435854132</v>
+      </c>
+      <c r="R9" t="s">
+        <v>59</v>
+      </c>
+      <c r="S9" t="s">
+        <v>62</v>
+      </c>
+      <c r="T9">
+        <v>-0.9422444375907327</v>
+      </c>
+      <c r="U9">
+        <v>0.9739933996829925</v>
+      </c>
+      <c r="V9" t="s">
+        <v>57</v>
+      </c>
+      <c r="W9" t="s">
+        <v>65</v>
+      </c>
+      <c r="X9">
+        <v>0.9997609063179718</v>
+      </c>
+      <c r="Y9">
+        <v>0.9999336110686508</v>
+      </c>
+      <c r="Z9">
+        <v>0.0001727047506789869</v>
+      </c>
+      <c r="AA9">
+        <v>1</v>
+      </c>
+      <c r="AB9">
+        <v>-152.1882166930073</v>
+      </c>
+      <c r="AC9">
+        <v>4.000000000000005</v>
+      </c>
+      <c r="AD9">
+        <v>-0.8844850405968239</v>
+      </c>
+      <c r="AE9">
+        <v>-0.4665685511909636</v>
+      </c>
+      <c r="AF9">
+        <v>3.648728355451729</v>
+      </c>
+      <c r="AG9">
+        <v>3.648486120275427</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>57</v>
+      </c>
+      <c r="AI9" t="s">
+        <v>69</v>
+      </c>
+      <c r="AJ9" t="s">
+        <v>72</v>
+      </c>
+      <c r="AK9" t="s">
+        <v>76</v>
+      </c>
+      <c r="AL9">
+        <v>-0.8844263205801842</v>
+      </c>
+      <c r="AM9">
+        <v>0.9591859356744106</v>
+      </c>
+      <c r="AN9">
+        <v>-3.238656349017095</v>
+      </c>
+      <c r="AO9">
+        <v>-1.678677519059057</v>
+      </c>
+      <c r="AP9">
+        <v>-5.572981133540885</v>
+      </c>
+      <c r="AQ9">
+        <v>4.573862365234136</v>
+      </c>
+      <c r="AR9">
+        <v>5.117223636090469</v>
+      </c>
+      <c r="AS9">
+        <v>0.04090893585776281</v>
+      </c>
+      <c r="AT9" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:18">
+    <row r="10" spans="1:46">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="B10" s="2">
         <v>46260</v>
@@ -983,7 +1883,7 @@
         <v>46259</v>
       </c>
       <c r="D10" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="E10">
         <v>-1</v>
@@ -992,13 +1892,13 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>1.444326957065765</v>
+        <v>1.350857931248715</v>
       </c>
       <c r="H10">
-        <v>2.047602085309645</v>
+        <v>2.042241739042175</v>
       </c>
       <c r="I10">
-        <v>0.4691567374649707</v>
+        <v>0.4628345714032919</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1010,27 +1910,111 @@
         <v>233</v>
       </c>
       <c r="M10">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N10">
-        <v>14.96088523229924</v>
+        <v>15.60545859103373</v>
       </c>
       <c r="O10">
-        <v>24.19876301221069</v>
+        <v>25.24134022003033</v>
       </c>
       <c r="P10">
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>1.444326957065765</v>
-      </c>
-      <c r="R10" t="b">
+        <v>1.350857931248715</v>
+      </c>
+      <c r="R10" t="s">
+        <v>60</v>
+      </c>
+      <c r="S10" t="s">
+        <v>63</v>
+      </c>
+      <c r="T10">
+        <v>-0.9934151936915365</v>
+      </c>
+      <c r="U10">
+        <v>0.8468742604282196</v>
+      </c>
+      <c r="V10" t="s">
+        <v>57</v>
+      </c>
+      <c r="W10" t="s">
+        <v>65</v>
+      </c>
+      <c r="X10">
+        <v>0.9977949569699115</v>
+      </c>
+      <c r="Y10">
+        <v>0.9993496930681123</v>
+      </c>
+      <c r="Z10">
+        <v>0.001554736098200782</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>168.7272267062853</v>
+      </c>
+      <c r="AC10">
+        <v>14.00000000000001</v>
+      </c>
+      <c r="AD10">
+        <v>-0.9807076605854906</v>
+      </c>
+      <c r="AE10">
+        <v>0.1954801382978182</v>
+      </c>
+      <c r="AF10">
+        <v>1.228671354395001</v>
+      </c>
+      <c r="AG10">
+        <v>1.227872340896226</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>57</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>69</v>
+      </c>
+      <c r="AJ10" t="s">
+        <v>73</v>
+      </c>
+      <c r="AK10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AL10">
+        <v>-0.4900349497978282</v>
+      </c>
+      <c r="AM10">
+        <v>0.7878084775699078</v>
+      </c>
+      <c r="AN10">
+        <v>-1.192344083615091</v>
+      </c>
+      <c r="AO10">
+        <v>0.2851291124748079</v>
+      </c>
+      <c r="AP10">
+        <v>-0.9258819156013174</v>
+      </c>
+      <c r="AQ10">
+        <v>3.337842491725659</v>
+      </c>
+      <c r="AR10">
+        <v>0.7162938844265543</v>
+      </c>
+      <c r="AS10">
+        <v>0.04117475453052491</v>
+      </c>
+      <c r="AT10" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:18">
+    <row r="11" spans="1:46">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="B11" s="2">
         <v>46260</v>
@@ -1039,22 +2023,22 @@
         <v>46259</v>
       </c>
       <c r="D11" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E11">
         <v>1</v>
       </c>
       <c r="F11">
-        <v>0.5644185106544457</v>
+        <v>0.5597410687947183</v>
       </c>
       <c r="G11">
-        <v>2.805421503219524</v>
+        <v>2.798916656102842</v>
       </c>
       <c r="H11">
-        <v>2.725108236144294</v>
+        <v>2.724434076728202</v>
       </c>
       <c r="I11">
-        <v>0.6233710331029453</v>
+        <v>0.6233783633046124</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -1069,18 +2053,102 @@
         <v>10</v>
       </c>
       <c r="N11">
-        <v>-946.8910086524462</v>
+        <v>-944.6955643205774</v>
       </c>
       <c r="O11">
-        <v>-12.92778518286002</v>
+        <v>-12.89781105442921</v>
       </c>
       <c r="P11">
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>2.805421503219524</v>
-      </c>
-      <c r="R11" t="b">
+        <v>2.798916656102842</v>
+      </c>
+      <c r="R11" t="s">
+        <v>58</v>
+      </c>
+      <c r="S11" t="s">
+        <v>61</v>
+      </c>
+      <c r="T11">
+        <v>0.8326070425837431</v>
+      </c>
+      <c r="U11">
+        <v>0.8586278603302148</v>
+      </c>
+      <c r="V11" t="s">
+        <v>56</v>
+      </c>
+      <c r="W11" t="s">
+        <v>65</v>
+      </c>
+      <c r="X11">
+        <v>0.9994213650171135</v>
+      </c>
+      <c r="Y11">
+        <v>0.9999741233932906</v>
+      </c>
+      <c r="Z11">
+        <v>0.000552758376177076</v>
+      </c>
+      <c r="AA11">
+        <v>1</v>
+      </c>
+      <c r="AB11">
+        <v>46.43621699480563</v>
+      </c>
+      <c r="AC11">
+        <v>6.999999999999997</v>
+      </c>
+      <c r="AD11">
+        <v>0.6891616527576454</v>
+      </c>
+      <c r="AE11">
+        <v>0.7246076292507212</v>
+      </c>
+      <c r="AF11">
+        <v>3.165685192484152</v>
+      </c>
+      <c r="AG11">
+        <v>3.16560327529346</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI11" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ11" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK11" t="s">
+        <v>74</v>
+      </c>
+      <c r="AL11">
+        <v>0.6891438195925979</v>
+      </c>
+      <c r="AM11">
+        <v>0.8998011015298744</v>
+      </c>
+      <c r="AN11">
+        <v>2.211741814241879</v>
+      </c>
+      <c r="AO11">
+        <v>2.262336532632756</v>
+      </c>
+      <c r="AP11">
+        <v>3.090439349926507</v>
+      </c>
+      <c r="AQ11">
+        <v>-4.467622972231291</v>
+      </c>
+      <c r="AR11">
+        <v>2.657151356611917</v>
+      </c>
+      <c r="AS11">
+        <v>0.04625558323380603</v>
+      </c>
+      <c r="AT11" t="b">
         <v>1</v>
       </c>
     </row>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="77">
   <si>
     <t>Pair</t>
   </si>
@@ -193,61 +193,58 @@
     <t>UP_ACCELERATING</t>
   </si>
   <si>
+    <t>UP_STEADY</t>
+  </si>
+  <si>
     <t>DOWN_ACCELERATING</t>
   </si>
   <si>
-    <t>DOWN_STEADY</t>
+    <t>DOWN_DECELERATING</t>
   </si>
   <si>
     <t>多头加速</t>
   </si>
   <si>
+    <t>多头稳态</t>
+  </si>
+  <si>
     <t>空头加速</t>
   </si>
   <si>
-    <t>空头稳态</t>
-  </si>
-  <si>
-    <t>NEUTRAL</t>
+    <t>空头减速</t>
   </si>
   <si>
     <t>ALIGNED</t>
   </si>
   <si>
-    <t>TRANSITION</t>
-  </si>
-  <si>
     <t>上涨</t>
   </si>
   <si>
-    <t>转换</t>
-  </si>
-  <si>
     <t>下跌</t>
   </si>
   <si>
     <t>UP_STEEPENING</t>
   </si>
   <si>
-    <t>TRANSITION_ZONE</t>
+    <t>UP_SLOPE</t>
   </si>
   <si>
     <t>DOWN_STEEPENING</t>
   </si>
   <si>
-    <t>DOWN_SLOPE</t>
+    <t>DOWN_VALLEY_FLATTENING</t>
   </si>
   <si>
     <t>上升陡坡形成</t>
   </si>
   <si>
-    <t>地形转换区</t>
+    <t>上升坡延续</t>
   </si>
   <si>
     <t>下降陡坡形成</t>
   </si>
   <si>
-    <t>下降坡延续</t>
+    <t>下降谷底收敛</t>
   </si>
 </sst>
 </file>
@@ -757,10 +754,10 @@
         <v>46</v>
       </c>
       <c r="B2" s="2">
+        <v>46261</v>
+      </c>
+      <c r="C2" s="2">
         <v>46260</v>
-      </c>
-      <c r="C2" s="2">
-        <v>46259</v>
       </c>
       <c r="D2" t="s">
         <v>56</v>
@@ -769,16 +766,16 @@
         <v>1</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.1261518495267923</v>
       </c>
       <c r="G2">
-        <v>0.795598308645689</v>
+        <v>0.875980393372361</v>
       </c>
       <c r="H2">
-        <v>1.068739189153218</v>
+        <v>1.069156513384349</v>
       </c>
       <c r="I2">
-        <v>0.2585098622997503</v>
+        <v>0.2583617436216686</v>
       </c>
       <c r="J2">
         <v>6</v>
@@ -790,67 +787,67 @@
         <v>149</v>
       </c>
       <c r="M2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N2">
-        <v>-0.1209259172451924</v>
+        <v>-0.1447025682667413</v>
       </c>
       <c r="O2">
-        <v>-3.417296464408656</v>
+        <v>-4.114374986259342</v>
       </c>
       <c r="P2">
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.795598308645689</v>
+        <v>0.875980393372361</v>
       </c>
       <c r="R2" t="s">
         <v>58</v>
       </c>
       <c r="S2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="T2">
-        <v>0.8709724158689343</v>
+        <v>0.8959285542412345</v>
       </c>
       <c r="U2">
-        <v>0.7919276991632392</v>
+        <v>0.8220726005090663</v>
       </c>
       <c r="V2" t="s">
         <v>56</v>
       </c>
       <c r="W2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="X2">
-        <v>0.9997731482654194</v>
+        <v>0.9999002727330402</v>
       </c>
       <c r="Y2">
-        <v>0.9999604480888752</v>
+        <v>0.9999278946859675</v>
       </c>
       <c r="Z2">
-        <v>0.0001872998234557777</v>
+        <v>2.762195292738134E-05</v>
       </c>
       <c r="AA2">
-        <v>0.3240539114619911</v>
+        <v>0.370999677594759</v>
       </c>
       <c r="AB2">
-        <v>44.30612101281891</v>
+        <v>39.65793137016246</v>
       </c>
       <c r="AC2">
-        <v>4.000000000000005</v>
+        <v>2.000000000000003</v>
       </c>
       <c r="AD2">
-        <v>0.7156181166386435</v>
+        <v>0.7698683540048074</v>
       </c>
       <c r="AE2">
-        <v>0.6984917402078287</v>
+        <v>0.6382027244551128</v>
       </c>
       <c r="AF2">
-        <v>0.8909277083529237</v>
+        <v>0.9129798533396085</v>
       </c>
       <c r="AG2">
-        <v>0.8908924704593842</v>
+        <v>0.9129140226405782</v>
       </c>
       <c r="AH2" t="s">
         <v>56</v>
@@ -859,34 +856,34 @@
         <v>67</v>
       </c>
       <c r="AJ2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AK2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AL2">
-        <v>0.4737397451708066</v>
+        <v>0.5277065793730392</v>
       </c>
       <c r="AM2">
-        <v>0.7725345957569094</v>
+        <v>0.798358978726025</v>
       </c>
       <c r="AN2">
-        <v>0.6427796943077172</v>
+        <v>0.7053632159031246</v>
       </c>
       <c r="AO2">
-        <v>0.6166249742153718</v>
+        <v>0.5795072931083447</v>
       </c>
       <c r="AP2">
-        <v>0.8103174576174301</v>
+        <v>0.9034501968403217</v>
       </c>
       <c r="AQ2">
-        <v>-1.343859367270114</v>
+        <v>-1.450857766759146</v>
       </c>
       <c r="AR2">
-        <v>0.6849813451994347</v>
+        <v>0.7694802905024996</v>
       </c>
       <c r="AS2">
-        <v>0.04631852238792044</v>
+        <v>0.04517484089638418</v>
       </c>
       <c r="AT2" t="b">
         <v>1</v>
@@ -897,10 +894,10 @@
         <v>47</v>
       </c>
       <c r="B3" s="2">
+        <v>46261</v>
+      </c>
+      <c r="C3" s="2">
         <v>46260</v>
-      </c>
-      <c r="C3" s="2">
-        <v>46259</v>
       </c>
       <c r="D3" t="s">
         <v>56</v>
@@ -912,13 +909,13 @@
         <v>1</v>
       </c>
       <c r="G3">
-        <v>2.609871596674189</v>
+        <v>2.83106416497062</v>
       </c>
       <c r="H3">
-        <v>1.853330676903088</v>
+        <v>1.862542214486854</v>
       </c>
       <c r="I3">
-        <v>0.4216940605038454</v>
+        <v>0.4223158551181721</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -930,67 +927,67 @@
         <v>225</v>
       </c>
       <c r="M3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N3">
-        <v>-0.04628519515894085</v>
+        <v>-0.05245310391779137</v>
       </c>
       <c r="O3">
-        <v>-15.65577995228734</v>
+        <v>-18.06725193379457</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>2.609871596674189</v>
+        <v>2.83106416497062</v>
       </c>
       <c r="R3" t="s">
         <v>58</v>
       </c>
       <c r="S3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="T3">
-        <v>0.8675991539142461</v>
+        <v>0.8743636068761635</v>
       </c>
       <c r="U3">
-        <v>0.9404164441058944</v>
+        <v>0.9434596239456097</v>
       </c>
       <c r="V3" t="s">
         <v>56</v>
       </c>
       <c r="W3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="X3">
-        <v>0.9992798359880024</v>
+        <v>0.9996514162958083</v>
       </c>
       <c r="Y3">
-        <v>0.9999872993779348</v>
+        <v>0.9999840034053441</v>
       </c>
       <c r="Z3">
-        <v>0.000707463389932439</v>
+        <v>0.0003325871095357646</v>
       </c>
       <c r="AA3">
         <v>1</v>
       </c>
       <c r="AB3">
-        <v>42.67616662423193</v>
+        <v>41.51992853322866</v>
       </c>
       <c r="AC3">
-        <v>7.999999999999998</v>
+        <v>6.000000000000009</v>
       </c>
       <c r="AD3">
-        <v>0.7351966262340277</v>
+        <v>0.7487252039657223</v>
       </c>
       <c r="AE3">
-        <v>0.6778539081351552</v>
+        <v>0.6628805087996534</v>
       </c>
       <c r="AF3">
-        <v>2.706885419526051</v>
+        <v>2.904822118838112</v>
       </c>
       <c r="AG3">
-        <v>2.706851040397364</v>
+        <v>2.904775651576129</v>
       </c>
       <c r="AH3" t="s">
         <v>56</v>
@@ -999,34 +996,34 @@
         <v>67</v>
       </c>
       <c r="AJ3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AK3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AL3">
-        <v>0.7351872887795343</v>
+        <v>0.7487132269121258</v>
       </c>
       <c r="AM3">
-        <v>0.9135148561148612</v>
+        <v>0.9178241762706055</v>
       </c>
       <c r="AN3">
-        <v>2.015729191342458</v>
+        <v>2.196344298638227</v>
       </c>
       <c r="AO3">
-        <v>1.803750173660602</v>
+        <v>1.899521412498563</v>
       </c>
       <c r="AP3">
-        <v>3.077224726278764</v>
+        <v>3.301326116560213</v>
       </c>
       <c r="AQ3">
-        <v>-3.182921922031068</v>
+        <v>-3.718322556980598</v>
       </c>
       <c r="AR3">
-        <v>2.767059520123484</v>
+        <v>2.941160267909104</v>
       </c>
       <c r="AS3">
-        <v>0.04693124358416298</v>
+        <v>0.04525190740654354</v>
       </c>
       <c r="AT3" t="b">
         <v>1</v>
@@ -1037,10 +1034,10 @@
         <v>48</v>
       </c>
       <c r="B4" s="2">
+        <v>46261</v>
+      </c>
+      <c r="C4" s="2">
         <v>46260</v>
-      </c>
-      <c r="C4" s="2">
-        <v>46259</v>
       </c>
       <c r="D4" t="s">
         <v>56</v>
@@ -1052,13 +1049,13 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>1.0925661464973</v>
+        <v>1.04051712694808</v>
       </c>
       <c r="H4">
-        <v>2.074786991652134</v>
+        <v>2.0753991693758</v>
       </c>
       <c r="I4">
-        <v>0.4968670291877077</v>
+        <v>0.4963546695007598</v>
       </c>
       <c r="J4">
         <v>6</v>
@@ -1070,67 +1067,67 @@
         <v>146</v>
       </c>
       <c r="M4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N4">
-        <v>-0.1100920431068562</v>
+        <v>-0.1349227370570981</v>
       </c>
       <c r="O4">
-        <v>-4.131033512452412</v>
+        <v>-5.176536910932803</v>
       </c>
       <c r="P4">
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>1.0925661464973</v>
+        <v>1.04051712694808</v>
       </c>
       <c r="R4" t="s">
         <v>58</v>
       </c>
       <c r="S4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="T4">
-        <v>0.7913175097708476</v>
+        <v>0.9521692634294723</v>
       </c>
       <c r="U4">
-        <v>0.7560899607813154</v>
+        <v>0.8272200878467397</v>
       </c>
       <c r="V4" t="s">
         <v>56</v>
       </c>
       <c r="W4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="X4">
-        <v>0.9989735078829162</v>
+        <v>0.9899469434896756</v>
       </c>
       <c r="Y4">
-        <v>0.999988325537736</v>
+        <v>0.9949756772139089</v>
       </c>
       <c r="Z4">
-        <v>0.001014817654819811</v>
+        <v>0.005028733724233292</v>
       </c>
       <c r="AA4">
-        <v>0.401314667508557</v>
+        <v>0</v>
       </c>
       <c r="AB4">
-        <v>55.89448443459531</v>
+        <v>30.74416663981834</v>
       </c>
       <c r="AC4">
-        <v>10</v>
+        <v>-26</v>
       </c>
       <c r="AD4">
-        <v>0.5607187050083993</v>
+        <v>0.8594584624823099</v>
       </c>
       <c r="AE4">
-        <v>0.8280063609983341</v>
+        <v>0.5112055861075306</v>
       </c>
       <c r="AF4">
-        <v>1.636880032338598</v>
+        <v>1.156737044978005</v>
       </c>
       <c r="AG4">
-        <v>1.63686092264443</v>
+        <v>1.150925224685406</v>
       </c>
       <c r="AH4" t="s">
         <v>56</v>
@@ -1139,34 +1136,34 @@
         <v>67</v>
       </c>
       <c r="AJ4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AK4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AL4">
-        <v>0.3928670862718177</v>
+        <v>0.4275701328727806</v>
       </c>
       <c r="AM4">
-        <v>0.7421273585218244</v>
+        <v>0.7504341533594796</v>
       </c>
       <c r="AN4">
-        <v>0.9475600812747735</v>
+        <v>0.9364888031876001</v>
       </c>
       <c r="AO4">
-        <v>1.332669590966227</v>
+        <v>0.6589853906091667</v>
       </c>
       <c r="AP4">
-        <v>0.834662849186111</v>
+        <v>0.6485359375533768</v>
       </c>
       <c r="AQ4">
-        <v>-3.02249665137887</v>
+        <v>-3.403238792602049</v>
       </c>
       <c r="AR4">
-        <v>0.7483760603816799</v>
+        <v>0.6298769457858703</v>
       </c>
       <c r="AS4">
-        <v>0.04231400280409587</v>
+        <v>0.03763248273387594</v>
       </c>
       <c r="AT4" t="b">
         <v>1</v>
@@ -1177,10 +1174,10 @@
         <v>49</v>
       </c>
       <c r="B5" s="2">
+        <v>46261</v>
+      </c>
+      <c r="C5" s="2">
         <v>46260</v>
-      </c>
-      <c r="C5" s="2">
-        <v>46259</v>
       </c>
       <c r="D5" t="s">
         <v>56</v>
@@ -1192,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="G5">
-        <v>2.84909425193396</v>
+        <v>2.690260366791259</v>
       </c>
       <c r="H5">
-        <v>1.438219567414882</v>
+        <v>1.443899880884415</v>
       </c>
       <c r="I5">
-        <v>0.307898189495003</v>
+        <v>0.3113483734664703</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -1210,67 +1207,67 @@
         <v>226</v>
       </c>
       <c r="M5">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N5">
-        <v>-0.05738176607616784</v>
+        <v>-0.06461890912527177</v>
       </c>
       <c r="O5">
-        <v>-17.90582246888102</v>
+        <v>-20.31128710718016</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>2.84909425193396</v>
+        <v>2.690260366791259</v>
       </c>
       <c r="R5" t="s">
         <v>58</v>
       </c>
       <c r="S5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="T5">
-        <v>0.8744470211803734</v>
+        <v>0.965625020563757</v>
       </c>
       <c r="U5">
-        <v>0.9434904413132446</v>
+        <v>0.9840963157027116</v>
       </c>
       <c r="V5" t="s">
         <v>56</v>
       </c>
       <c r="W5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="X5">
-        <v>0.9998510080070387</v>
+        <v>0.9940205274659585</v>
       </c>
       <c r="Y5">
-        <v>0.9999571271283061</v>
+        <v>0.9982602257960844</v>
       </c>
       <c r="Z5">
-        <v>0.0001061191212673451</v>
+        <v>0.004239698330125941</v>
       </c>
       <c r="AA5">
         <v>1</v>
       </c>
       <c r="AB5">
-        <v>41.50579837541022</v>
+        <v>21.37889869301764</v>
       </c>
       <c r="AC5">
-        <v>3.000000000000004</v>
+        <v>-21.99999999999999</v>
       </c>
       <c r="AD5">
-        <v>0.7488886593132085</v>
+        <v>0.9311901321970188</v>
       </c>
       <c r="AE5">
-        <v>0.6626958396972665</v>
+        <v>0.3645338635832049</v>
       </c>
       <c r="AF5">
-        <v>3.056795997873015</v>
+        <v>2.466725406689849</v>
       </c>
       <c r="AG5">
-        <v>3.056664944250403</v>
+        <v>2.462433861459147</v>
       </c>
       <c r="AH5" t="s">
         <v>56</v>
@@ -1279,34 +1276,34 @@
         <v>67</v>
       </c>
       <c r="AJ5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AK5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AL5">
-        <v>0.7488565523058047</v>
+        <v>0.9295700716260817</v>
       </c>
       <c r="AM5">
-        <v>0.9186281690292669</v>
+        <v>0.9734605719932714</v>
       </c>
       <c r="AN5">
-        <v>2.301997397202923</v>
+        <v>2.230823802186806</v>
       </c>
       <c r="AO5">
-        <v>2.010478948015788</v>
+        <v>1.017649226068463</v>
       </c>
       <c r="AP5">
-        <v>2.933383030925631</v>
+        <v>2.527524070383912</v>
       </c>
       <c r="AQ5">
-        <v>-5.417584511771893</v>
+        <v>-6.060745165159029</v>
       </c>
       <c r="AR5">
-        <v>2.426649573297757</v>
+        <v>1.983460633076612</v>
       </c>
       <c r="AS5">
-        <v>0.04015615506401868</v>
+        <v>0.03525031129642582</v>
       </c>
       <c r="AT5" t="b">
         <v>1</v>
@@ -1317,10 +1314,10 @@
         <v>50</v>
       </c>
       <c r="B6" s="2">
+        <v>46261</v>
+      </c>
+      <c r="C6" s="2">
         <v>46260</v>
-      </c>
-      <c r="C6" s="2">
-        <v>46259</v>
       </c>
       <c r="D6" t="s">
         <v>56</v>
@@ -1329,16 +1326,16 @@
         <v>1</v>
       </c>
       <c r="F6">
-        <v>0.3445716267758546</v>
+        <v>0.08103574803148193</v>
       </c>
       <c r="G6">
-        <v>0.8629951360537029</v>
+        <v>0.7271882964430165</v>
       </c>
       <c r="H6">
-        <v>0.9431192231323933</v>
+        <v>0.9431482420852753</v>
       </c>
       <c r="I6">
-        <v>0.2577524470488483</v>
+        <v>0.2577307546259179</v>
       </c>
       <c r="J6">
         <v>6</v>
@@ -1350,67 +1347,67 @@
         <v>158</v>
       </c>
       <c r="M6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N6">
-        <v>-0.2292391469758999</v>
+        <v>-0.2628163749800797</v>
       </c>
       <c r="O6">
-        <v>-4.545561239678465</v>
+        <v>-5.007933974467963</v>
       </c>
       <c r="P6">
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>0.8629951360537029</v>
+        <v>0.7271882964430165</v>
       </c>
       <c r="R6" t="s">
         <v>58</v>
       </c>
       <c r="S6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="T6">
-        <v>0.8805742450343832</v>
+        <v>0.9756602641724341</v>
       </c>
       <c r="U6">
-        <v>0.8479408764376916</v>
+        <v>0.8508118461795943</v>
       </c>
       <c r="V6" t="s">
         <v>56</v>
       </c>
       <c r="W6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="X6">
-        <v>0.9999022048839805</v>
+        <v>0.9942301468446519</v>
       </c>
       <c r="Y6">
-        <v>0.9999868886233635</v>
+        <v>0.9984374603891069</v>
       </c>
       <c r="Z6">
-        <v>8.468373938297358E-05</v>
+        <v>0.004207313544454916</v>
       </c>
       <c r="AA6">
-        <v>0.5477510107761134</v>
+        <v>0</v>
       </c>
       <c r="AB6">
-        <v>41.62964068025791</v>
+        <v>22.05687944870195</v>
       </c>
       <c r="AC6">
-        <v>3.000000000000004</v>
+        <v>-21.99999999999999</v>
       </c>
       <c r="AD6">
-        <v>0.7474545231848799</v>
+        <v>0.9268115131754834</v>
       </c>
       <c r="AE6">
-        <v>0.6643129802814813</v>
+        <v>0.3755268552918298</v>
       </c>
       <c r="AF6">
-        <v>0.922652263866525</v>
+        <v>0.6821023189050246</v>
       </c>
       <c r="AG6">
-        <v>0.9226401666251889</v>
+        <v>0.6810365070130534</v>
       </c>
       <c r="AH6" t="s">
         <v>56</v>
@@ -1419,34 +1416,34 @@
         <v>67</v>
       </c>
       <c r="AJ6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AK6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AL6">
-        <v>0.5784291627822391</v>
+        <v>0.4626816667371574</v>
       </c>
       <c r="AM6">
-        <v>0.8274681041271014</v>
+        <v>0.7724548536611346</v>
       </c>
       <c r="AN6">
-        <v>0.6935027086703082</v>
+        <v>0.6131883325449783</v>
       </c>
       <c r="AO6">
-        <v>0.6084198367620823</v>
+        <v>0.2896724468719512</v>
       </c>
       <c r="AP6">
-        <v>0.9067300443565722</v>
+        <v>0.6435247504965964</v>
       </c>
       <c r="AQ6">
-        <v>-1.64238262985989</v>
+        <v>-1.916506852904554</v>
       </c>
       <c r="AR6">
-        <v>0.7494457056626387</v>
+        <v>0.5205519366919027</v>
       </c>
       <c r="AS6">
-        <v>0.04209244001175027</v>
+        <v>0.03361140951798543</v>
       </c>
       <c r="AT6" t="b">
         <v>1</v>
@@ -1457,10 +1454,10 @@
         <v>51</v>
       </c>
       <c r="B7" s="2">
+        <v>46261</v>
+      </c>
+      <c r="C7" s="2">
         <v>46260</v>
-      </c>
-      <c r="C7" s="2">
-        <v>46259</v>
       </c>
       <c r="D7" t="s">
         <v>56</v>
@@ -1472,13 +1469,13 @@
         <v>1</v>
       </c>
       <c r="G7">
-        <v>3.21473373001301</v>
+        <v>2.708687702918872</v>
       </c>
       <c r="H7">
-        <v>1.389873780052663</v>
+        <v>1.396499424362516</v>
       </c>
       <c r="I7">
-        <v>0.3232336634877695</v>
+        <v>0.3278294776286338</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -1490,67 +1487,67 @@
         <v>239</v>
       </c>
       <c r="M7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N7">
-        <v>-0.09397676910388937</v>
+        <v>-0.1029352608872846</v>
       </c>
       <c r="O7">
-        <v>-25.59180640837293</v>
+        <v>-26.21123412917394</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>3.21473373001301</v>
+        <v>2.708687702918872</v>
       </c>
       <c r="R7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="T7">
-        <v>0.9186938755791447</v>
+        <v>0.9889433237128176</v>
       </c>
       <c r="U7">
-        <v>0.9634091384850991</v>
+        <v>0.9946869358558421</v>
       </c>
       <c r="V7" t="s">
         <v>56</v>
       </c>
       <c r="W7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="X7">
-        <v>0.999972514222352</v>
+        <v>0.9931571798489566</v>
       </c>
       <c r="Y7">
-        <v>0.9999875778979358</v>
+        <v>0.9986497607402968</v>
       </c>
       <c r="Z7">
-        <v>1.506367558379296E-05</v>
+        <v>0.005492580891340193</v>
       </c>
       <c r="AA7">
         <v>1</v>
       </c>
       <c r="AB7">
-        <v>33.13481389077527</v>
+        <v>12.07579670877786</v>
       </c>
       <c r="AC7">
-        <v>1.000000000000001</v>
+        <v>-24</v>
       </c>
       <c r="AD7">
-        <v>0.837386741152767</v>
+        <v>0.9778716980820399</v>
       </c>
       <c r="AE7">
-        <v>0.5466108723228515</v>
+        <v>0.2092055020551513</v>
       </c>
       <c r="AF7">
-        <v>3.014583619265697</v>
+        <v>2.294959088590425</v>
       </c>
       <c r="AG7">
-        <v>3.014546171800297</v>
+        <v>2.291860344729597</v>
       </c>
       <c r="AH7" t="s">
         <v>56</v>
@@ -1565,28 +1562,28 @@
         <v>74</v>
       </c>
       <c r="AL7">
-        <v>0.8373763390492012</v>
+        <v>0.9765513373243369</v>
       </c>
       <c r="AM7">
-        <v>0.9453642512955005</v>
+        <v>0.9880039742067772</v>
       </c>
       <c r="AN7">
-        <v>2.527708178710714</v>
+        <v>2.198768506139468</v>
       </c>
       <c r="AO7">
-        <v>1.642530426474649</v>
+        <v>0.6003506062191748</v>
       </c>
       <c r="AP7">
-        <v>3.630900095404568</v>
+        <v>2.771189737850693</v>
       </c>
       <c r="AQ7">
-        <v>-5.305839159353135</v>
+        <v>-5.718498980371929</v>
       </c>
       <c r="AR7">
-        <v>3.125769804913606</v>
+        <v>2.25088029421262</v>
       </c>
       <c r="AS7">
-        <v>0.03898282209738079</v>
+        <v>0.03256634317959076</v>
       </c>
       <c r="AT7" t="b">
         <v>1</v>
@@ -1597,10 +1594,10 @@
         <v>52</v>
       </c>
       <c r="B8" s="2">
+        <v>46261</v>
+      </c>
+      <c r="C8" s="2">
         <v>46260</v>
-      </c>
-      <c r="C8" s="2">
-        <v>46259</v>
       </c>
       <c r="D8" t="s">
         <v>57</v>
@@ -1612,13 +1609,13 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>0.1929018080286625</v>
+        <v>0.1261631252607943</v>
       </c>
       <c r="H8">
-        <v>1.433850188845725</v>
+        <v>1.434479230953875</v>
       </c>
       <c r="I8">
-        <v>0.3531642707697492</v>
+        <v>0.35346442553752</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -1630,70 +1627,70 @@
         <v>112</v>
       </c>
       <c r="M8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N8">
-        <v>0.002079600949611913</v>
+        <v>0.003237800807623908</v>
       </c>
       <c r="O8">
-        <v>0.5382587039113867</v>
+        <v>0.8228957303573557</v>
       </c>
       <c r="P8">
-        <v>0.4687800928647571</v>
+        <v>0.5636031487753461</v>
       </c>
       <c r="Q8">
-        <v>0.3631298553341898</v>
+        <v>0.2891018230464877</v>
       </c>
       <c r="R8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="S8" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="T8">
-        <v>-0.4874151685407133</v>
+        <v>-0.7127559234209312</v>
       </c>
       <c r="U8">
-        <v>0.6193303928731442</v>
+        <v>0.7206487230502867</v>
       </c>
       <c r="V8" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="W8" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="X8">
-        <v>0.9998149293921575</v>
+        <v>0.9996342300434707</v>
       </c>
       <c r="Y8">
-        <v>0.9999742681192927</v>
+        <v>0.999634230043471</v>
       </c>
       <c r="Z8">
-        <v>0.0001593387271351387</v>
+        <v>2.220446049250313E-16</v>
       </c>
       <c r="AA8">
-        <v>1</v>
+        <v>0.1145271272153768</v>
       </c>
       <c r="AB8">
-        <v>-98.12953213079992</v>
+        <v>-104.819720377167</v>
       </c>
       <c r="AC8">
-        <v>4.000000000000005</v>
+        <v>0</v>
       </c>
       <c r="AD8">
-        <v>-0.1414115039806741</v>
+        <v>-0.2557785094010437</v>
       </c>
       <c r="AE8">
-        <v>-0.9899509010763735</v>
+        <v>-0.9667354106106697</v>
       </c>
       <c r="AF8">
-        <v>2.0726984447467</v>
+        <v>1.116603743232776</v>
       </c>
       <c r="AG8">
-        <v>2.072645110317578</v>
+        <v>1.116195323130153</v>
       </c>
       <c r="AH8" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="AI8" t="s">
         <v>68</v>
@@ -1705,28 +1702,28 @@
         <v>75</v>
       </c>
       <c r="AL8">
-        <v>-0.141407865196723</v>
+        <v>-0.1424839082406011</v>
       </c>
       <c r="AM8">
-        <v>0.7270645026194514</v>
+        <v>0.5903223581442516</v>
       </c>
       <c r="AN8">
-        <v>-0.308798224276107</v>
+        <v>-0.285498775950647</v>
       </c>
       <c r="AO8">
-        <v>-2.049178491698392</v>
+        <v>-1.079065544027938</v>
       </c>
       <c r="AP8">
-        <v>-0.3035029589787233</v>
+        <v>-0.07200371151468893</v>
       </c>
       <c r="AQ8">
-        <v>1.108818956787369</v>
+        <v>1.547167950764386</v>
       </c>
       <c r="AR8">
-        <v>0.3427606841431051</v>
+        <v>0.282332973518135</v>
       </c>
       <c r="AS8">
-        <v>0.1023329494433545</v>
+        <v>0.06125733756234435</v>
       </c>
       <c r="AT8" t="b">
         <v>1</v>
@@ -1737,10 +1734,10 @@
         <v>53</v>
       </c>
       <c r="B9" s="2">
+        <v>46261</v>
+      </c>
+      <c r="C9" s="2">
         <v>46260</v>
-      </c>
-      <c r="C9" s="2">
-        <v>46259</v>
       </c>
       <c r="D9" t="s">
         <v>57</v>
@@ -1752,13 +1749,13 @@
         <v>1</v>
       </c>
       <c r="G9">
-        <v>4.320280435854132</v>
+        <v>4.249948049987226</v>
       </c>
       <c r="H9">
-        <v>2.964435220140667</v>
+        <v>2.971281573604455</v>
       </c>
       <c r="I9">
-        <v>0.605970524410009</v>
+        <v>0.6086651381628984</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -1770,103 +1767,103 @@
         <v>76</v>
       </c>
       <c r="M9">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N9">
-        <v>0.4042222680028851</v>
+        <v>0.4255250423695253</v>
       </c>
       <c r="O9">
-        <v>61.66960989528048</v>
+        <v>63.87894695660844</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>4.320280435854132</v>
+        <v>4.249948049987226</v>
       </c>
       <c r="R9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="S9" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="T9">
-        <v>-0.9422444375907327</v>
+        <v>-0.9695963118088188</v>
       </c>
       <c r="U9">
-        <v>0.9739933996829925</v>
+        <v>0.9862865319439547</v>
       </c>
       <c r="V9" t="s">
         <v>57</v>
       </c>
       <c r="W9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="X9">
-        <v>0.9997609063179718</v>
+        <v>0.999589882917146</v>
       </c>
       <c r="Y9">
-        <v>0.9999336110686508</v>
+        <v>0.9998727665199451</v>
       </c>
       <c r="Z9">
-        <v>0.0001727047506789869</v>
+        <v>0.0002828836027990445</v>
       </c>
       <c r="AA9">
         <v>1</v>
       </c>
       <c r="AB9">
-        <v>-152.1882166930073</v>
+        <v>-159.9157616381709</v>
       </c>
       <c r="AC9">
-        <v>4.000000000000005</v>
+        <v>-4.999999999999995</v>
       </c>
       <c r="AD9">
-        <v>-0.8844850405968239</v>
+        <v>-0.9391887547583342</v>
       </c>
       <c r="AE9">
-        <v>-0.4665685511909636</v>
+        <v>-0.3434013438172449</v>
       </c>
       <c r="AF9">
-        <v>3.648728355451729</v>
+        <v>3.43051209759231</v>
       </c>
       <c r="AG9">
-        <v>3.648486120275427</v>
+        <v>3.430075621599763</v>
       </c>
       <c r="AH9" t="s">
         <v>57</v>
       </c>
       <c r="AI9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AJ9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AK9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AL9">
-        <v>-0.8844263205801842</v>
+        <v>-0.9390692585046378</v>
       </c>
       <c r="AM9">
-        <v>0.9591859356744106</v>
+        <v>0.9758814106211259</v>
       </c>
       <c r="AN9">
-        <v>-3.238656349017095</v>
+        <v>-3.209118404443168</v>
       </c>
       <c r="AO9">
-        <v>-1.678677519059057</v>
+        <v>-1.20843760400212</v>
       </c>
       <c r="AP9">
-        <v>-5.572981133540885</v>
+        <v>-5.385848528467055</v>
       </c>
       <c r="AQ9">
-        <v>4.573862365234136</v>
+        <v>4.921420857592676</v>
       </c>
       <c r="AR9">
-        <v>5.117223636090469</v>
+        <v>4.907000436350013</v>
       </c>
       <c r="AS9">
-        <v>0.04090893585776281</v>
+        <v>0.03887122725570041</v>
       </c>
       <c r="AT9" t="b">
         <v>1</v>
@@ -1877,10 +1874,10 @@
         <v>54</v>
       </c>
       <c r="B10" s="2">
+        <v>46261</v>
+      </c>
+      <c r="C10" s="2">
         <v>46260</v>
-      </c>
-      <c r="C10" s="2">
-        <v>46259</v>
       </c>
       <c r="D10" t="s">
         <v>57</v>
@@ -1892,13 +1889,13 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>1.350857931248715</v>
+        <v>1.23355299901812</v>
       </c>
       <c r="H10">
-        <v>2.042241739042175</v>
+        <v>2.042854586288462</v>
       </c>
       <c r="I10">
-        <v>0.4628345714032919</v>
+        <v>0.4621777643993528</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1910,103 +1907,103 @@
         <v>233</v>
       </c>
       <c r="M10">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N10">
-        <v>15.60545859103373</v>
+        <v>16.30361797369248</v>
       </c>
       <c r="O10">
-        <v>25.24134022003033</v>
+        <v>27.68016633903654</v>
       </c>
       <c r="P10">
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>1.350857931248715</v>
+        <v>1.23355299901812</v>
       </c>
       <c r="R10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="T10">
-        <v>-0.9934151936915365</v>
+        <v>-0.9402232032276575</v>
       </c>
       <c r="U10">
-        <v>0.8468742604282196</v>
+        <v>0.8230208482594078</v>
       </c>
       <c r="V10" t="s">
         <v>57</v>
       </c>
       <c r="W10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="X10">
-        <v>0.9977949569699115</v>
+        <v>0.9968387951044699</v>
       </c>
       <c r="Y10">
-        <v>0.9993496930681123</v>
+        <v>0.9996816272278478</v>
       </c>
       <c r="Z10">
-        <v>0.001554736098200782</v>
+        <v>0.002842832123377881</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>0.05329663574516484</v>
       </c>
       <c r="AB10">
-        <v>168.7272267062853</v>
+        <v>146.6459426028197</v>
       </c>
       <c r="AC10">
-        <v>14.00000000000001</v>
+        <v>-18</v>
       </c>
       <c r="AD10">
-        <v>-0.9807076605854906</v>
+        <v>-0.8352889976366736</v>
       </c>
       <c r="AE10">
-        <v>0.1954801382978182</v>
+        <v>0.5498111406902565</v>
       </c>
       <c r="AF10">
-        <v>1.228671354395001</v>
+        <v>1.30553811752063</v>
       </c>
       <c r="AG10">
-        <v>1.227872340896226</v>
+        <v>1.305122469731005</v>
       </c>
       <c r="AH10" t="s">
         <v>57</v>
       </c>
       <c r="AI10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AJ10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AK10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AL10">
-        <v>-0.4900349497978282</v>
+        <v>-0.4397634922315555</v>
       </c>
       <c r="AM10">
-        <v>0.7878084775699078</v>
+        <v>0.7545171401498888</v>
       </c>
       <c r="AN10">
-        <v>-1.192344083615091</v>
+        <v>-1.119103625844617</v>
       </c>
       <c r="AO10">
-        <v>0.2851291124748079</v>
+        <v>0.6642874228453168</v>
       </c>
       <c r="AP10">
-        <v>-0.9258819156013174</v>
+        <v>-0.7139241194381309</v>
       </c>
       <c r="AQ10">
-        <v>3.337842491725659</v>
+        <v>3.485564902555253</v>
       </c>
       <c r="AR10">
-        <v>0.7162938844265543</v>
+        <v>0.5998485066956332</v>
       </c>
       <c r="AS10">
-        <v>0.04117475453052491</v>
+        <v>0.04411637213261986</v>
       </c>
       <c r="AT10" t="b">
         <v>1</v>
@@ -2017,10 +2014,10 @@
         <v>55</v>
       </c>
       <c r="B11" s="2">
+        <v>46261</v>
+      </c>
+      <c r="C11" s="2">
         <v>46260</v>
-      </c>
-      <c r="C11" s="2">
-        <v>46259</v>
       </c>
       <c r="D11" t="s">
         <v>56</v>
@@ -2029,16 +2026,16 @@
         <v>1</v>
       </c>
       <c r="F11">
-        <v>0.5597410687947183</v>
+        <v>0.4964453354005751</v>
       </c>
       <c r="G11">
-        <v>2.798916656102842</v>
+        <v>2.684056757071201</v>
       </c>
       <c r="H11">
-        <v>2.724434076728202</v>
+        <v>2.688467752084736</v>
       </c>
       <c r="I11">
-        <v>0.6233783633046124</v>
+        <v>0.620451647428112</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -2050,67 +2047,67 @@
         <v>212</v>
       </c>
       <c r="M11">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N11">
-        <v>-944.6955643205774</v>
+        <v>-1107.854435120412</v>
       </c>
       <c r="O11">
-        <v>-12.89781105442921</v>
+        <v>-14.59314759408724</v>
       </c>
       <c r="P11">
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>2.798916656102842</v>
+        <v>2.684056757071201</v>
       </c>
       <c r="R11" t="s">
         <v>58</v>
       </c>
       <c r="S11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="T11">
-        <v>0.8326070425837431</v>
+        <v>0.8601785474463165</v>
       </c>
       <c r="U11">
-        <v>0.8586278603302148</v>
+        <v>0.8615464852802278</v>
       </c>
       <c r="V11" t="s">
         <v>56</v>
       </c>
       <c r="W11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="X11">
-        <v>0.9994213650171135</v>
+        <v>0.9998890689459234</v>
       </c>
       <c r="Y11">
-        <v>0.9999741233932906</v>
+        <v>0.9999973544771966</v>
       </c>
       <c r="Z11">
-        <v>0.000552758376177076</v>
+        <v>0.0001082855312731779</v>
       </c>
       <c r="AA11">
         <v>1</v>
       </c>
       <c r="AB11">
-        <v>46.43621699480563</v>
+        <v>41.99190955964302</v>
       </c>
       <c r="AC11">
-        <v>6.999999999999997</v>
+        <v>3.000000000000004</v>
       </c>
       <c r="AD11">
-        <v>0.6891616527576454</v>
+        <v>0.743239302536648</v>
       </c>
       <c r="AE11">
-        <v>0.7246076292507212</v>
+        <v>0.6690256640554508</v>
       </c>
       <c r="AF11">
-        <v>3.165685192484152</v>
+        <v>2.895747816788325</v>
       </c>
       <c r="AG11">
-        <v>3.16560327529346</v>
+        <v>2.895740156021442</v>
       </c>
       <c r="AH11" t="s">
         <v>56</v>
@@ -2119,34 +2116,34 @@
         <v>67</v>
       </c>
       <c r="AJ11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AK11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AL11">
-        <v>0.6891438195925979</v>
+        <v>0.7432373362801248</v>
       </c>
       <c r="AM11">
-        <v>0.8998011015298744</v>
+        <v>0.9167894555072333</v>
       </c>
       <c r="AN11">
-        <v>2.211741814241879</v>
+        <v>2.164489010445173</v>
       </c>
       <c r="AO11">
-        <v>2.262336532632756</v>
+        <v>1.923143898062059</v>
       </c>
       <c r="AP11">
-        <v>3.090439349926507</v>
+        <v>2.782581731070048</v>
       </c>
       <c r="AQ11">
-        <v>-4.467622972231291</v>
+        <v>-5.089988147742164</v>
       </c>
       <c r="AR11">
-        <v>2.657151356611917</v>
+        <v>2.304315077947849</v>
       </c>
       <c r="AS11">
-        <v>0.04625558323380603</v>
+        <v>0.04120939547186553</v>
       </c>
       <c r="AT11" t="b">
         <v>1</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="81">
   <si>
     <t>Pair</t>
   </si>
@@ -199,6 +199,9 @@
     <t>DOWN_ACCELERATING</t>
   </si>
   <si>
+    <t>DOWN_STEADY</t>
+  </si>
+  <si>
     <t>DOWN_DECELERATING</t>
   </si>
   <si>
@@ -211,6 +214,9 @@
     <t>空头加速</t>
   </si>
   <si>
+    <t>空头稳态</t>
+  </si>
+  <si>
     <t>空头减速</t>
   </si>
   <si>
@@ -232,6 +238,9 @@
     <t>DOWN_STEEPENING</t>
   </si>
   <si>
+    <t>DOWN_SLOPE</t>
+  </si>
+  <si>
     <t>DOWN_VALLEY_FLATTENING</t>
   </si>
   <si>
@@ -242,6 +251,9 @@
   </si>
   <si>
     <t>下降陡坡形成</t>
+  </si>
+  <si>
+    <t>下降坡延续</t>
   </si>
   <si>
     <t>下降谷底收敛</t>
@@ -754,10 +766,10 @@
         <v>46</v>
       </c>
       <c r="B2" s="2">
+        <v>46262</v>
+      </c>
+      <c r="C2" s="2">
         <v>46261</v>
-      </c>
-      <c r="C2" s="2">
-        <v>46260</v>
       </c>
       <c r="D2" t="s">
         <v>56</v>
@@ -766,16 +778,16 @@
         <v>1</v>
       </c>
       <c r="F2">
-        <v>0.1261518495267923</v>
+        <v>0.4595482013309128</v>
       </c>
       <c r="G2">
-        <v>0.875980393372361</v>
+        <v>1.048640216297192</v>
       </c>
       <c r="H2">
-        <v>1.069156513384349</v>
+        <v>1.06953409245061</v>
       </c>
       <c r="I2">
-        <v>0.2583617436216686</v>
+        <v>0.258256453864242</v>
       </c>
       <c r="J2">
         <v>6</v>
@@ -787,103 +799,103 @@
         <v>149</v>
       </c>
       <c r="M2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N2">
-        <v>-0.1447025682667413</v>
+        <v>-0.1711681524247574</v>
       </c>
       <c r="O2">
-        <v>-4.114374986259342</v>
+        <v>-5.055172841841609</v>
       </c>
       <c r="P2">
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.875980393372361</v>
+        <v>1.048640216297192</v>
       </c>
       <c r="R2" t="s">
         <v>58</v>
       </c>
       <c r="S2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="T2">
-        <v>0.8959285542412345</v>
+        <v>0.851751852769192</v>
       </c>
       <c r="U2">
-        <v>0.8220726005090663</v>
+        <v>0.8522204848239956</v>
       </c>
       <c r="V2" t="s">
         <v>56</v>
       </c>
       <c r="W2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="X2">
-        <v>0.9999002727330402</v>
+        <v>0.999330122716826</v>
       </c>
       <c r="Y2">
-        <v>0.9999278946859675</v>
+        <v>0.9999996835128889</v>
       </c>
       <c r="Z2">
-        <v>2.762195292738134E-05</v>
+        <v>0.0006695607960629513</v>
       </c>
       <c r="AA2">
-        <v>0.370999677594759</v>
+        <v>0.8651902268400773</v>
       </c>
       <c r="AB2">
-        <v>39.65793137016246</v>
+        <v>44.12638265258064</v>
       </c>
       <c r="AC2">
-        <v>2.000000000000003</v>
+        <v>7.999999999999998</v>
       </c>
       <c r="AD2">
-        <v>0.7698683540048074</v>
+        <v>0.7178057787469425</v>
       </c>
       <c r="AE2">
-        <v>0.6382027244551128</v>
+        <v>0.6962433942218018</v>
       </c>
       <c r="AF2">
-        <v>0.9129798533396085</v>
+        <v>1.140412653048889</v>
       </c>
       <c r="AG2">
-        <v>0.9129140226405782</v>
+        <v>1.140412292122983</v>
       </c>
       <c r="AH2" t="s">
         <v>56</v>
       </c>
       <c r="AI2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="AJ2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AK2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AL2">
-        <v>0.5277065793730392</v>
+        <v>0.669421949780578</v>
       </c>
       <c r="AM2">
-        <v>0.798358978726025</v>
+        <v>0.8813770168541892</v>
       </c>
       <c r="AN2">
-        <v>0.7053632159031246</v>
+        <v>0.8305831072864501</v>
       </c>
       <c r="AO2">
-        <v>0.5795072931083447</v>
+        <v>0.7803402456327442</v>
       </c>
       <c r="AP2">
-        <v>0.9034501968403217</v>
+        <v>1.141388827682592</v>
       </c>
       <c r="AQ2">
-        <v>-1.450857766759146</v>
+        <v>-1.508657092508388</v>
       </c>
       <c r="AR2">
-        <v>0.7694802905024996</v>
+        <v>1.001079687308742</v>
       </c>
       <c r="AS2">
-        <v>0.04517484089638418</v>
+        <v>0.04668434244946713</v>
       </c>
       <c r="AT2" t="b">
         <v>1</v>
@@ -894,10 +906,10 @@
         <v>47</v>
       </c>
       <c r="B3" s="2">
+        <v>46262</v>
+      </c>
+      <c r="C3" s="2">
         <v>46261</v>
-      </c>
-      <c r="C3" s="2">
-        <v>46260</v>
       </c>
       <c r="D3" t="s">
         <v>56</v>
@@ -909,13 +921,13 @@
         <v>1</v>
       </c>
       <c r="G3">
-        <v>2.83106416497062</v>
+        <v>3.11960411317304</v>
       </c>
       <c r="H3">
-        <v>1.862542214486854</v>
+        <v>1.871477190332932</v>
       </c>
       <c r="I3">
-        <v>0.4223158551181721</v>
+        <v>0.4235078409527687</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -927,103 +939,103 @@
         <v>225</v>
       </c>
       <c r="M3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N3">
-        <v>-0.05245310391779137</v>
+        <v>-0.05898165736660619</v>
       </c>
       <c r="O3">
-        <v>-18.06725193379457</v>
+        <v>-21.52054217181356</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>2.83106416497062</v>
+        <v>3.11960411317304</v>
       </c>
       <c r="R3" t="s">
         <v>58</v>
       </c>
       <c r="S3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="T3">
-        <v>0.8743636068761635</v>
+        <v>0.9238267595471897</v>
       </c>
       <c r="U3">
-        <v>0.9434596239456097</v>
+        <v>0.9656775331195359</v>
       </c>
       <c r="V3" t="s">
         <v>56</v>
       </c>
       <c r="W3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="X3">
-        <v>0.9996514162958083</v>
+        <v>0.9996675345594338</v>
       </c>
       <c r="Y3">
-        <v>0.9999840034053441</v>
+        <v>0.9998219652932022</v>
       </c>
       <c r="Z3">
-        <v>0.0003325871095357646</v>
+        <v>0.0001544307337684181</v>
       </c>
       <c r="AA3">
         <v>1</v>
       </c>
       <c r="AB3">
-        <v>41.51992853322866</v>
+        <v>32.04410174202717</v>
       </c>
       <c r="AC3">
-        <v>6.000000000000009</v>
+        <v>-3.999999999999993</v>
       </c>
       <c r="AD3">
-        <v>0.7487252039657223</v>
+        <v>0.8476399551990053</v>
       </c>
       <c r="AE3">
-        <v>0.6628805087996534</v>
+        <v>0.5305718672811708</v>
       </c>
       <c r="AF3">
-        <v>2.904822118838112</v>
+        <v>2.892092319420074</v>
       </c>
       <c r="AG3">
-        <v>2.904775651576129</v>
+        <v>2.891577426611954</v>
       </c>
       <c r="AH3" t="s">
         <v>56</v>
       </c>
       <c r="AI3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="AJ3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AK3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AL3">
-        <v>0.7487132269121258</v>
+        <v>0.8474890458681114</v>
       </c>
       <c r="AM3">
-        <v>0.9178241762706055</v>
+        <v>0.9477808728007524</v>
       </c>
       <c r="AN3">
-        <v>2.196344298638227</v>
+        <v>2.437557533194274</v>
       </c>
       <c r="AO3">
-        <v>1.899521412498563</v>
+        <v>1.55465448489466</v>
       </c>
       <c r="AP3">
-        <v>3.301326116560213</v>
+        <v>3.568085769401152</v>
       </c>
       <c r="AQ3">
-        <v>-3.718322556980598</v>
+        <v>-4.467541592149739</v>
       </c>
       <c r="AR3">
-        <v>2.941160267909104</v>
+        <v>3.141719990070078</v>
       </c>
       <c r="AS3">
-        <v>0.04525190740654354</v>
+        <v>0.04299201074379971</v>
       </c>
       <c r="AT3" t="b">
         <v>1</v>
@@ -1034,10 +1046,10 @@
         <v>48</v>
       </c>
       <c r="B4" s="2">
+        <v>46262</v>
+      </c>
+      <c r="C4" s="2">
         <v>46261</v>
-      </c>
-      <c r="C4" s="2">
-        <v>46260</v>
       </c>
       <c r="D4" t="s">
         <v>56</v>
@@ -1049,13 +1061,13 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>1.04051712694808</v>
+        <v>1.027987060729755</v>
       </c>
       <c r="H4">
-        <v>2.0753991693758</v>
+        <v>2.075953044459117</v>
       </c>
       <c r="I4">
-        <v>0.4963546695007598</v>
+        <v>0.4957464067330279</v>
       </c>
       <c r="J4">
         <v>6</v>
@@ -1067,103 +1079,103 @@
         <v>146</v>
       </c>
       <c r="M4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N4">
-        <v>-0.1349227370570981</v>
+        <v>-0.1588518159006455</v>
       </c>
       <c r="O4">
-        <v>-5.176536910932803</v>
+        <v>-6.434969394123401</v>
       </c>
       <c r="P4">
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>1.04051712694808</v>
+        <v>1.027987060729755</v>
       </c>
       <c r="R4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="T4">
-        <v>0.9521692634294723</v>
+        <v>0.9997463834963941</v>
       </c>
       <c r="U4">
-        <v>0.8272200878467397</v>
+        <v>0.8474145119182691</v>
       </c>
       <c r="V4" t="s">
         <v>56</v>
       </c>
       <c r="W4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="X4">
-        <v>0.9899469434896756</v>
+        <v>0.9568870048078872</v>
       </c>
       <c r="Y4">
-        <v>0.9949756772139089</v>
+        <v>0.990114557379567</v>
       </c>
       <c r="Z4">
-        <v>0.005028733724233292</v>
+        <v>0.03322755257167975</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>30.74416663981834</v>
+        <v>2.21566659560143</v>
       </c>
       <c r="AC4">
-        <v>-26</v>
+        <v>-63</v>
       </c>
       <c r="AD4">
-        <v>0.8594584624823099</v>
+        <v>0.9992523825355735</v>
       </c>
       <c r="AE4">
-        <v>0.5112055861075306</v>
+        <v>0.03866103978141239</v>
       </c>
       <c r="AF4">
-        <v>1.156737044978005</v>
+        <v>1.016893277512718</v>
       </c>
       <c r="AG4">
-        <v>1.150925224685406</v>
+        <v>1.006840837366762</v>
       </c>
       <c r="AH4" t="s">
         <v>56</v>
       </c>
       <c r="AI4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="AJ4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="AK4" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="AL4">
-        <v>0.4275701328727806</v>
+        <v>0.4946871652223435</v>
       </c>
       <c r="AM4">
-        <v>0.7504341533594796</v>
+        <v>0.7906084581925497</v>
       </c>
       <c r="AN4">
-        <v>0.9364888031876001</v>
+        <v>0.9499115837273622</v>
       </c>
       <c r="AO4">
-        <v>0.6589853906091667</v>
+        <v>0.2109457391866109</v>
       </c>
       <c r="AP4">
-        <v>0.6485359375533768</v>
+        <v>0.5312930792731672</v>
       </c>
       <c r="AQ4">
-        <v>-3.403238792602049</v>
+        <v>-3.652187981281552</v>
       </c>
       <c r="AR4">
-        <v>0.6298769457858703</v>
+        <v>0.5496652155182299</v>
       </c>
       <c r="AS4">
-        <v>0.03763248273387594</v>
+        <v>0.03804901100647201</v>
       </c>
       <c r="AT4" t="b">
         <v>1</v>
@@ -1174,10 +1186,10 @@
         <v>49</v>
       </c>
       <c r="B5" s="2">
+        <v>46262</v>
+      </c>
+      <c r="C5" s="2">
         <v>46261</v>
-      </c>
-      <c r="C5" s="2">
-        <v>46260</v>
       </c>
       <c r="D5" t="s">
         <v>56</v>
@@ -1189,13 +1201,13 @@
         <v>1</v>
       </c>
       <c r="G5">
-        <v>2.690260366791259</v>
+        <v>2.728267187158335</v>
       </c>
       <c r="H5">
-        <v>1.443899880884415</v>
+        <v>1.45106701164125</v>
       </c>
       <c r="I5">
-        <v>0.3113483734664703</v>
+        <v>0.315124499165984</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -1207,103 +1219,103 @@
         <v>226</v>
       </c>
       <c r="M5">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N5">
-        <v>-0.06461890912527177</v>
+        <v>-0.0715966356119441</v>
       </c>
       <c r="O5">
-        <v>-20.31128710718016</v>
+        <v>-23.95394667384919</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>2.690260366791259</v>
+        <v>2.728267187158335</v>
       </c>
       <c r="R5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="T5">
-        <v>0.965625020563757</v>
+        <v>0.999577091632214</v>
       </c>
       <c r="U5">
-        <v>0.9840963157027116</v>
+        <v>0.9989688622160841</v>
       </c>
       <c r="V5" t="s">
         <v>56</v>
       </c>
       <c r="W5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="X5">
-        <v>0.9940205274659585</v>
+        <v>0.9777074462237517</v>
       </c>
       <c r="Y5">
-        <v>0.9982602257960844</v>
+        <v>0.9966366839263512</v>
       </c>
       <c r="Z5">
-        <v>0.004239698330125941</v>
+        <v>0.01892923770259947</v>
       </c>
       <c r="AA5">
         <v>1</v>
       </c>
       <c r="AB5">
-        <v>21.37889869301764</v>
+        <v>-2.358699015199895</v>
       </c>
       <c r="AC5">
-        <v>-21.99999999999999</v>
+        <v>-44</v>
       </c>
       <c r="AD5">
-        <v>0.9311901321970188</v>
+        <v>0.9991527560898776</v>
       </c>
       <c r="AE5">
-        <v>0.3645338635832049</v>
+        <v>-0.04115543704058305</v>
       </c>
       <c r="AF5">
-        <v>2.466725406689849</v>
+        <v>2.351525635725401</v>
       </c>
       <c r="AG5">
-        <v>2.462433861459147</v>
+        <v>2.343616711757169</v>
       </c>
       <c r="AH5" t="s">
         <v>56</v>
       </c>
       <c r="AI5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="AJ5" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="AK5" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="AL5">
-        <v>0.9295700716260817</v>
+        <v>0.9957922895652901</v>
       </c>
       <c r="AM5">
-        <v>0.9734605719932714</v>
+        <v>0.9935058136678155</v>
       </c>
       <c r="AN5">
-        <v>2.230823802186806</v>
+        <v>2.294550112974665</v>
       </c>
       <c r="AO5">
-        <v>1.017649226068463</v>
+        <v>0.1446359298432478</v>
       </c>
       <c r="AP5">
-        <v>2.527524070383912</v>
+        <v>2.420551647623656</v>
       </c>
       <c r="AQ5">
-        <v>-6.060745165159029</v>
+        <v>-6.49877877332037</v>
       </c>
       <c r="AR5">
-        <v>1.983460633076612</v>
+        <v>1.873226976578128</v>
       </c>
       <c r="AS5">
-        <v>0.03525031129642582</v>
+        <v>0.03375235022247104</v>
       </c>
       <c r="AT5" t="b">
         <v>1</v>
@@ -1314,10 +1326,10 @@
         <v>50</v>
       </c>
       <c r="B6" s="2">
+        <v>46262</v>
+      </c>
+      <c r="C6" s="2">
         <v>46261</v>
-      </c>
-      <c r="C6" s="2">
-        <v>46260</v>
       </c>
       <c r="D6" t="s">
         <v>56</v>
@@ -1326,16 +1338,16 @@
         <v>1</v>
       </c>
       <c r="F6">
-        <v>0.08103574803148193</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>0.7271882964430165</v>
+        <v>0.6682190548559425</v>
       </c>
       <c r="H6">
-        <v>0.9431482420852753</v>
+        <v>0.9431744973283589</v>
       </c>
       <c r="I6">
-        <v>0.2577307546259179</v>
+        <v>0.2576860402814104</v>
       </c>
       <c r="J6">
         <v>6</v>
@@ -1347,103 +1359,103 @@
         <v>158</v>
       </c>
       <c r="M6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N6">
-        <v>-0.2628163749800797</v>
+        <v>-0.2935490016796831</v>
       </c>
       <c r="O6">
-        <v>-5.007933974467963</v>
+        <v>-5.862772152580025</v>
       </c>
       <c r="P6">
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>0.7271882964430165</v>
+        <v>0.6682190548559425</v>
       </c>
       <c r="R6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="T6">
-        <v>0.9756602641724341</v>
+        <v>0.9978388812563632</v>
       </c>
       <c r="U6">
-        <v>0.8508118461795943</v>
+        <v>0.847817217923593</v>
       </c>
       <c r="V6" t="s">
         <v>56</v>
       </c>
       <c r="W6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="X6">
-        <v>0.9942301468446519</v>
+        <v>0.9672614372492453</v>
       </c>
       <c r="Y6">
-        <v>0.9984374603891069</v>
+        <v>0.995158885432918</v>
       </c>
       <c r="Z6">
-        <v>0.004207313544454916</v>
+        <v>0.02789744818367268</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>22.05687944870195</v>
+        <v>-6.459954269721915</v>
       </c>
       <c r="AC6">
-        <v>-21.99999999999999</v>
+        <v>-54</v>
       </c>
       <c r="AD6">
-        <v>0.9268115131754834</v>
+        <v>0.9936507340933957</v>
       </c>
       <c r="AE6">
-        <v>0.3755268552918298</v>
+        <v>-0.1125087491515919</v>
       </c>
       <c r="AF6">
-        <v>0.6821023189050246</v>
+        <v>0.6047930484193282</v>
       </c>
       <c r="AG6">
-        <v>0.6810365070130534</v>
+        <v>0.6018651759825555</v>
       </c>
       <c r="AH6" t="s">
         <v>56</v>
       </c>
       <c r="AI6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="AJ6" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="AK6" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="AL6">
-        <v>0.4626816667371574</v>
+        <v>0.4944201785249922</v>
       </c>
       <c r="AM6">
-        <v>0.7724548536611346</v>
+        <v>0.79161477440737</v>
       </c>
       <c r="AN6">
-        <v>0.6131883325449783</v>
+        <v>0.584883756885283</v>
       </c>
       <c r="AO6">
-        <v>0.2896724468719512</v>
+        <v>0.01130456041590575</v>
       </c>
       <c r="AP6">
-        <v>0.6435247504965964</v>
+        <v>0.4990531969617066</v>
       </c>
       <c r="AQ6">
-        <v>-1.916506852904554</v>
+        <v>-2.079923857443279</v>
       </c>
       <c r="AR6">
-        <v>0.5205519366919027</v>
+        <v>0.4236009838695852</v>
       </c>
       <c r="AS6">
-        <v>0.03361140951798543</v>
+        <v>0.03190703814779901</v>
       </c>
       <c r="AT6" t="b">
         <v>1</v>
@@ -1454,10 +1466,10 @@
         <v>51</v>
       </c>
       <c r="B7" s="2">
+        <v>46262</v>
+      </c>
+      <c r="C7" s="2">
         <v>46261</v>
-      </c>
-      <c r="C7" s="2">
-        <v>46260</v>
       </c>
       <c r="D7" t="s">
         <v>56</v>
@@ -1469,13 +1481,13 @@
         <v>1</v>
       </c>
       <c r="G7">
-        <v>2.708687702918872</v>
+        <v>2.657425042408513</v>
       </c>
       <c r="H7">
-        <v>1.396499424362516</v>
+        <v>1.403286293935856</v>
       </c>
       <c r="I7">
-        <v>0.3278294776286338</v>
+        <v>0.332553994872276</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -1487,103 +1499,103 @@
         <v>239</v>
       </c>
       <c r="M7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N7">
-        <v>-0.1029352608872846</v>
+        <v>-0.1113341157341253</v>
       </c>
       <c r="O7">
-        <v>-26.21123412917394</v>
+        <v>-29.84828840056969</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>2.708687702918872</v>
+        <v>2.657425042408513</v>
       </c>
       <c r="R7" t="s">
         <v>59</v>
       </c>
       <c r="S7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="T7">
-        <v>0.9889433237128176</v>
+        <v>0.991895502751434</v>
       </c>
       <c r="U7">
-        <v>0.9946869358558421</v>
+        <v>0.9957843543883421</v>
       </c>
       <c r="V7" t="s">
         <v>56</v>
       </c>
       <c r="W7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="X7">
-        <v>0.9931571798489566</v>
+        <v>0.9808067239079912</v>
       </c>
       <c r="Y7">
-        <v>0.9986497607402968</v>
+        <v>0.9977255126007871</v>
       </c>
       <c r="Z7">
-        <v>0.005492580891340193</v>
+        <v>0.01691878869279595</v>
       </c>
       <c r="AA7">
         <v>1</v>
       </c>
       <c r="AB7">
-        <v>12.07579670877786</v>
+        <v>-10.33599012645593</v>
       </c>
       <c r="AC7">
-        <v>-24</v>
+        <v>-41</v>
       </c>
       <c r="AD7">
-        <v>0.9778716980820399</v>
+        <v>0.9837725299034812</v>
       </c>
       <c r="AE7">
-        <v>0.2092055020551513</v>
+        <v>-0.179420203453525</v>
       </c>
       <c r="AF7">
-        <v>2.294959088590425</v>
+        <v>2.240832310512667</v>
       </c>
       <c r="AG7">
-        <v>2.291860344729597</v>
+        <v>2.235735565658657</v>
       </c>
       <c r="AH7" t="s">
         <v>56</v>
       </c>
       <c r="AI7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="AJ7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="AK7" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="AL7">
-        <v>0.9765513373243369</v>
+        <v>0.981534951680524</v>
       </c>
       <c r="AM7">
-        <v>0.9880039742067772</v>
+        <v>0.9897031014416999</v>
       </c>
       <c r="AN7">
-        <v>2.198768506139468</v>
+        <v>2.188426718575088</v>
       </c>
       <c r="AO7">
-        <v>0.6003506062191748</v>
+        <v>-0.2030176917188164</v>
       </c>
       <c r="AP7">
-        <v>2.771189737850693</v>
+        <v>2.580792136150472</v>
       </c>
       <c r="AQ7">
-        <v>-5.718498980371929</v>
+        <v>-5.957422268418081</v>
       </c>
       <c r="AR7">
-        <v>2.25088029421262</v>
+        <v>2.063421195497497</v>
       </c>
       <c r="AS7">
-        <v>0.03256634317959076</v>
+        <v>0.03088391293079938</v>
       </c>
       <c r="AT7" t="b">
         <v>1</v>
@@ -1594,10 +1606,10 @@
         <v>52</v>
       </c>
       <c r="B8" s="2">
+        <v>46262</v>
+      </c>
+      <c r="C8" s="2">
         <v>46261</v>
-      </c>
-      <c r="C8" s="2">
-        <v>46260</v>
       </c>
       <c r="D8" t="s">
         <v>57</v>
@@ -1609,13 +1621,13 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>0.1261631252607943</v>
+        <v>0.1688806419123562</v>
       </c>
       <c r="H8">
-        <v>1.434479230953875</v>
+        <v>1.43504836428982</v>
       </c>
       <c r="I8">
-        <v>0.35346442553752</v>
+        <v>0.3538128480621394</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -1627,103 +1639,103 @@
         <v>112</v>
       </c>
       <c r="M8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N8">
-        <v>0.003237800807623908</v>
+        <v>0.00441069340694911</v>
       </c>
       <c r="O8">
-        <v>0.8228957303573557</v>
+        <v>1.210778582299763</v>
       </c>
       <c r="P8">
-        <v>0.5636031487753461</v>
+        <v>0.4967241147218076</v>
       </c>
       <c r="Q8">
-        <v>0.2891018230464877</v>
+        <v>0.3355627536554929</v>
       </c>
       <c r="R8" t="s">
         <v>60</v>
       </c>
       <c r="S8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="T8">
-        <v>-0.7127559234209312</v>
+        <v>-0.9277088794389501</v>
       </c>
       <c r="U8">
-        <v>0.7206487230502867</v>
+        <v>0.8031362218831346</v>
       </c>
       <c r="V8" t="s">
         <v>57</v>
       </c>
       <c r="W8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="X8">
-        <v>0.9996342300434707</v>
+        <v>0.8992203129224055</v>
       </c>
       <c r="Y8">
-        <v>0.999634230043471</v>
+        <v>0.9426689045424286</v>
       </c>
       <c r="Z8">
-        <v>2.220446049250313E-16</v>
+        <v>0.04344859162002312</v>
       </c>
       <c r="AA8">
-        <v>0.1145271272153768</v>
+        <v>0</v>
       </c>
       <c r="AB8">
-        <v>-104.819720377167</v>
+        <v>-141.2432878169698</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="AD8">
-        <v>-0.2557785094010437</v>
+        <v>-0.7798111509983079</v>
       </c>
       <c r="AE8">
-        <v>-0.9667354106106697</v>
+        <v>-0.6260148311171984</v>
       </c>
       <c r="AF8">
-        <v>1.116603743232776</v>
+        <v>0.7243819612639005</v>
       </c>
       <c r="AG8">
-        <v>1.116195323130153</v>
+        <v>0.682852349894937</v>
       </c>
       <c r="AH8" t="s">
         <v>57</v>
       </c>
       <c r="AI8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="AJ8" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="AK8" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="AL8">
-        <v>-0.1424839082406011</v>
+        <v>-0.3675518617307726</v>
       </c>
       <c r="AM8">
-        <v>0.5903223581442516</v>
+        <v>0.7067980543227322</v>
       </c>
       <c r="AN8">
-        <v>-0.285498775950647</v>
+        <v>-0.3355743668208713</v>
       </c>
       <c r="AO8">
-        <v>-1.079065544027938</v>
+        <v>-0.5582870336571798</v>
       </c>
       <c r="AP8">
-        <v>-0.07200371151468893</v>
+        <v>-0.06107190201638424</v>
       </c>
       <c r="AQ8">
-        <v>1.547167950764386</v>
+        <v>1.6928265853255</v>
       </c>
       <c r="AR8">
-        <v>0.282332973518135</v>
+        <v>0.2779852756397786</v>
       </c>
       <c r="AS8">
-        <v>0.06125733756234435</v>
+        <v>0.04719605044406718</v>
       </c>
       <c r="AT8" t="b">
         <v>1</v>
@@ -1734,10 +1746,10 @@
         <v>53</v>
       </c>
       <c r="B9" s="2">
+        <v>46262</v>
+      </c>
+      <c r="C9" s="2">
         <v>46261</v>
-      </c>
-      <c r="C9" s="2">
-        <v>46260</v>
       </c>
       <c r="D9" t="s">
         <v>57</v>
@@ -1749,13 +1761,13 @@
         <v>1</v>
       </c>
       <c r="G9">
-        <v>4.249948049987226</v>
+        <v>4.200028847746982</v>
       </c>
       <c r="H9">
-        <v>2.971281573604455</v>
+        <v>2.977708752071287</v>
       </c>
       <c r="I9">
-        <v>0.6086651381628984</v>
+        <v>0.6117257074536422</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -1767,103 +1779,103 @@
         <v>76</v>
       </c>
       <c r="M9">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N9">
-        <v>0.4255250423695253</v>
+        <v>0.4466813232343693</v>
       </c>
       <c r="O9">
-        <v>63.87894695660844</v>
+        <v>68.41945870110679</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>4.249948049987226</v>
+        <v>4.200028847746982</v>
       </c>
       <c r="R9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S9" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="T9">
-        <v>-0.9695963118088188</v>
+        <v>-0.9956832798643895</v>
       </c>
       <c r="U9">
-        <v>0.9862865319439547</v>
+        <v>0.9979427101257972</v>
       </c>
       <c r="V9" t="s">
         <v>57</v>
       </c>
       <c r="W9" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="X9">
-        <v>0.999589882917146</v>
+        <v>0.9967856581932435</v>
       </c>
       <c r="Y9">
-        <v>0.9998727665199451</v>
+        <v>0.9995409367472872</v>
       </c>
       <c r="Z9">
-        <v>0.0002828836027990445</v>
+        <v>0.002755278554043672</v>
       </c>
       <c r="AA9">
         <v>1</v>
       </c>
       <c r="AB9">
-        <v>-159.9157616381709</v>
+        <v>-172.4648403848067</v>
       </c>
       <c r="AC9">
-        <v>-4.999999999999995</v>
+        <v>-16</v>
       </c>
       <c r="AD9">
-        <v>-0.9391887547583342</v>
+        <v>-0.9913645771710732</v>
       </c>
       <c r="AE9">
-        <v>-0.3434013438172449</v>
+        <v>-0.131134568784967</v>
       </c>
       <c r="AF9">
-        <v>3.43051209759231</v>
+        <v>3.260342912738567</v>
       </c>
       <c r="AG9">
-        <v>3.430075621599763</v>
+        <v>3.258846209116086</v>
       </c>
       <c r="AH9" t="s">
         <v>57</v>
       </c>
       <c r="AI9" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="AJ9" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="AK9" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AL9">
-        <v>-0.9390692585046378</v>
+        <v>-0.9909094781236527</v>
       </c>
       <c r="AM9">
-        <v>0.9758814106211259</v>
+        <v>0.9918758055597627</v>
       </c>
       <c r="AN9">
-        <v>-3.209118404443168</v>
+        <v>-3.20671205489344</v>
       </c>
       <c r="AO9">
-        <v>-1.20843760400212</v>
+        <v>-0.5278330049535788</v>
       </c>
       <c r="AP9">
-        <v>-5.385848528467055</v>
+        <v>-5.17559930178544</v>
       </c>
       <c r="AQ9">
-        <v>4.921420857592676</v>
+        <v>5.49292428904988</v>
       </c>
       <c r="AR9">
-        <v>4.907000436350013</v>
+        <v>4.657868320299822</v>
       </c>
       <c r="AS9">
-        <v>0.03887122725570041</v>
+        <v>0.03581930302073087</v>
       </c>
       <c r="AT9" t="b">
         <v>1</v>
@@ -1874,10 +1886,10 @@
         <v>54</v>
       </c>
       <c r="B10" s="2">
+        <v>46262</v>
+      </c>
+      <c r="C10" s="2">
         <v>46261</v>
-      </c>
-      <c r="C10" s="2">
-        <v>46260</v>
       </c>
       <c r="D10" t="s">
         <v>57</v>
@@ -1889,13 +1901,13 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>1.23355299901812</v>
+        <v>1.07338862476908</v>
       </c>
       <c r="H10">
-        <v>2.042854586288462</v>
+        <v>2.04340906713034</v>
       </c>
       <c r="I10">
-        <v>0.4621777643993528</v>
+        <v>0.4614250367241567</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1907,103 +1919,103 @@
         <v>233</v>
       </c>
       <c r="M10">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N10">
-        <v>16.30361797369248</v>
+        <v>16.91647993108354</v>
       </c>
       <c r="O10">
-        <v>27.68016633903654</v>
+        <v>30.21763560257356</v>
       </c>
       <c r="P10">
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>1.23355299901812</v>
+        <v>1.07338862476908</v>
       </c>
       <c r="R10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="S10" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="T10">
-        <v>-0.9402232032276575</v>
+        <v>-0.8320553347889856</v>
       </c>
       <c r="U10">
-        <v>0.8230208482594078</v>
+        <v>0.7742723007858487</v>
       </c>
       <c r="V10" t="s">
         <v>57</v>
       </c>
       <c r="W10" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="X10">
-        <v>0.9968387951044699</v>
+        <v>0.9908072786304687</v>
       </c>
       <c r="Y10">
-        <v>0.9996816272278478</v>
+        <v>0.9993896005232207</v>
       </c>
       <c r="Z10">
-        <v>0.002842832123377881</v>
+        <v>0.008582321892751987</v>
       </c>
       <c r="AA10">
-        <v>0.05329663574516484</v>
+        <v>0.3199984626790244</v>
       </c>
       <c r="AB10">
-        <v>146.6459426028197</v>
+        <v>128.9595822289384</v>
       </c>
       <c r="AC10">
-        <v>-18</v>
+        <v>-29</v>
       </c>
       <c r="AD10">
-        <v>-0.8352889976366736</v>
+        <v>-0.6287720177370196</v>
       </c>
       <c r="AE10">
-        <v>0.5498111406902565</v>
+        <v>0.777589705250087</v>
       </c>
       <c r="AF10">
-        <v>1.30553811752063</v>
+        <v>1.505077624233367</v>
       </c>
       <c r="AG10">
-        <v>1.305122469731005</v>
+        <v>1.504158925639022</v>
       </c>
       <c r="AH10" t="s">
         <v>57</v>
       </c>
       <c r="AI10" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="AJ10" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="AK10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AL10">
-        <v>-0.4397634922315555</v>
+        <v>-0.4147357392962181</v>
       </c>
       <c r="AM10">
-        <v>0.7545171401498888</v>
+        <v>0.7446872215128757</v>
       </c>
       <c r="AN10">
-        <v>-1.119103625844617</v>
+        <v>-1.012058221146405</v>
       </c>
       <c r="AO10">
-        <v>0.6642874228453168</v>
+        <v>1.095235343166743</v>
       </c>
       <c r="AP10">
-        <v>-0.7139241194381309</v>
+        <v>-0.4528363004562632</v>
       </c>
       <c r="AQ10">
-        <v>3.485564902555253</v>
+        <v>3.524255776461361</v>
       </c>
       <c r="AR10">
-        <v>0.5998485066956332</v>
+        <v>0.5011887373469135</v>
       </c>
       <c r="AS10">
-        <v>0.04411637213261986</v>
+        <v>0.05153624351441453</v>
       </c>
       <c r="AT10" t="b">
         <v>1</v>
@@ -2014,10 +2026,10 @@
         <v>55</v>
       </c>
       <c r="B11" s="2">
+        <v>46262</v>
+      </c>
+      <c r="C11" s="2">
         <v>46261</v>
-      </c>
-      <c r="C11" s="2">
-        <v>46260</v>
       </c>
       <c r="D11" t="s">
         <v>56</v>
@@ -2026,16 +2038,16 @@
         <v>1</v>
       </c>
       <c r="F11">
-        <v>0.4964453354005751</v>
+        <v>0.4697420678723502</v>
       </c>
       <c r="G11">
-        <v>2.684056757071201</v>
+        <v>2.618565437526386</v>
       </c>
       <c r="H11">
-        <v>2.688467752084736</v>
+        <v>2.655926791693029</v>
       </c>
       <c r="I11">
-        <v>0.620451647428112</v>
+        <v>0.6173811549484833</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -2047,103 +2059,103 @@
         <v>212</v>
       </c>
       <c r="M11">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N11">
-        <v>-1107.854435120412</v>
+        <v>-1272.218901912979</v>
       </c>
       <c r="O11">
-        <v>-14.59314759408724</v>
+        <v>-16.59428842781236</v>
       </c>
       <c r="P11">
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>2.684056757071201</v>
+        <v>2.618565437526386</v>
       </c>
       <c r="R11" t="s">
         <v>58</v>
       </c>
       <c r="S11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="T11">
-        <v>0.8601785474463165</v>
+        <v>0.9329484855842582</v>
       </c>
       <c r="U11">
-        <v>0.8615464852802278</v>
+        <v>0.8901824479127239</v>
       </c>
       <c r="V11" t="s">
         <v>56</v>
       </c>
       <c r="W11" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="X11">
-        <v>0.9998890689459234</v>
+        <v>0.9983810294675523</v>
       </c>
       <c r="Y11">
-        <v>0.9999973544771966</v>
+        <v>0.9995772768758208</v>
       </c>
       <c r="Z11">
-        <v>0.0001082855312731779</v>
+        <v>0.001196247408268514</v>
       </c>
       <c r="AA11">
         <v>1</v>
       </c>
       <c r="AB11">
-        <v>41.99190955964302</v>
+        <v>28.66626680083258</v>
       </c>
       <c r="AC11">
-        <v>3.000000000000004</v>
+        <v>-11</v>
       </c>
       <c r="AD11">
-        <v>0.743239302536648</v>
+        <v>0.8774287458392165</v>
       </c>
       <c r="AE11">
-        <v>0.6690256640554508</v>
+        <v>0.4797069897083215</v>
       </c>
       <c r="AF11">
-        <v>2.895747816788325</v>
+        <v>2.484791317115895</v>
       </c>
       <c r="AG11">
-        <v>2.895740156021442</v>
+        <v>2.483740938367391</v>
       </c>
       <c r="AH11" t="s">
         <v>56</v>
       </c>
       <c r="AI11" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="AJ11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AK11" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AL11">
-        <v>0.7432373362801248</v>
+        <v>0.8770578364185306</v>
       </c>
       <c r="AM11">
-        <v>0.9167894555072333</v>
+        <v>0.9574293864880095</v>
       </c>
       <c r="AN11">
-        <v>2.164489010445173</v>
+        <v>2.144487492293096</v>
       </c>
       <c r="AO11">
-        <v>1.923143898062059</v>
+        <v>1.247151078039161</v>
       </c>
       <c r="AP11">
-        <v>2.782581731070048</v>
+        <v>2.57433094526332</v>
       </c>
       <c r="AQ11">
-        <v>-5.089988147742164</v>
+        <v>-5.461487894355134</v>
       </c>
       <c r="AR11">
-        <v>2.304315077947849</v>
+        <v>2.078465428757228</v>
       </c>
       <c r="AS11">
-        <v>0.04120939547186553</v>
+        <v>0.03767522780195163</v>
       </c>
       <c r="AT11" t="b">
         <v>1</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="85">
   <si>
     <t>Pair</t>
   </si>
@@ -193,6 +193,9 @@
     <t>UP_ACCELERATING</t>
   </si>
   <si>
+    <t>UP_DECELERATING</t>
+  </si>
+  <si>
     <t>UP_STEADY</t>
   </si>
   <si>
@@ -208,6 +211,9 @@
     <t>多头加速</t>
   </si>
   <si>
+    <t>多头减速</t>
+  </si>
+  <si>
     <t>多头稳态</t>
   </si>
   <si>
@@ -232,6 +238,9 @@
     <t>UP_STEEPENING</t>
   </si>
   <si>
+    <t>UP_CREST_FLATTENING</t>
+  </si>
+  <si>
     <t>UP_SLOPE</t>
   </si>
   <si>
@@ -245,6 +254,9 @@
   </si>
   <si>
     <t>上升陡坡形成</t>
+  </si>
+  <si>
+    <t>上升坡顶钝化</t>
   </si>
   <si>
     <t>上升坡延续</t>
@@ -766,10 +778,10 @@
         <v>46</v>
       </c>
       <c r="B2" s="2">
+        <v>46263</v>
+      </c>
+      <c r="C2" s="2">
         <v>46262</v>
-      </c>
-      <c r="C2" s="2">
-        <v>46261</v>
       </c>
       <c r="D2" t="s">
         <v>56</v>
@@ -778,16 +790,16 @@
         <v>1</v>
       </c>
       <c r="F2">
-        <v>0.4595482013309128</v>
+        <v>0.3251179412996309</v>
       </c>
       <c r="G2">
-        <v>1.048640216297192</v>
+        <v>0.9795677792001615</v>
       </c>
       <c r="H2">
-        <v>1.06953409245061</v>
+        <v>1.069875711605798</v>
       </c>
       <c r="I2">
-        <v>0.258256453864242</v>
+        <v>0.2581966757389444</v>
       </c>
       <c r="J2">
         <v>6</v>
@@ -799,103 +811,103 @@
         <v>149</v>
       </c>
       <c r="M2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N2">
-        <v>-0.1711681524247574</v>
+        <v>-0.199436859484536</v>
       </c>
       <c r="O2">
-        <v>-5.055172841841609</v>
+        <v>-5.571417804616382</v>
       </c>
       <c r="P2">
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>1.048640216297192</v>
+        <v>0.9795677792001615</v>
       </c>
       <c r="R2" t="s">
         <v>58</v>
       </c>
       <c r="S2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="T2">
-        <v>0.851751852769192</v>
+        <v>0.9348943950044755</v>
       </c>
       <c r="U2">
-        <v>0.8522204848239956</v>
+        <v>0.869403865563667</v>
       </c>
       <c r="V2" t="s">
         <v>56</v>
       </c>
       <c r="W2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="X2">
-        <v>0.999330122716826</v>
+        <v>0.9995055931747207</v>
       </c>
       <c r="Y2">
-        <v>0.9999996835128889</v>
+        <v>0.9997347864668334</v>
       </c>
       <c r="Z2">
-        <v>0.0006695607960629513</v>
+        <v>0.0002291932921127948</v>
       </c>
       <c r="AA2">
-        <v>0.8651902268400773</v>
+        <v>0.4210383443117264</v>
       </c>
       <c r="AB2">
-        <v>44.12638265258064</v>
+        <v>31.41887591160275</v>
       </c>
       <c r="AC2">
-        <v>7.999999999999998</v>
+        <v>-4.999999999999995</v>
       </c>
       <c r="AD2">
-        <v>0.7178057787469425</v>
+        <v>0.8533791059987669</v>
       </c>
       <c r="AE2">
-        <v>0.6962433942218018</v>
+        <v>0.5212908031461377</v>
       </c>
       <c r="AF2">
-        <v>1.140412653048889</v>
+        <v>0.9372684580136335</v>
       </c>
       <c r="AG2">
-        <v>1.140412292122983</v>
+        <v>0.9370198817343581</v>
       </c>
       <c r="AH2" t="s">
         <v>56</v>
       </c>
       <c r="AI2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AJ2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="AK2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="AL2">
-        <v>0.669421949780578</v>
+        <v>0.6061814057679599</v>
       </c>
       <c r="AM2">
-        <v>0.8813770168541892</v>
+        <v>0.8338938525549414</v>
       </c>
       <c r="AN2">
-        <v>0.8305831072864501</v>
+        <v>0.7937627087613108</v>
       </c>
       <c r="AO2">
-        <v>0.7803402456327442</v>
+        <v>0.497538434729851</v>
       </c>
       <c r="AP2">
-        <v>1.141388827682592</v>
+        <v>0.9930987930889017</v>
       </c>
       <c r="AQ2">
-        <v>-1.508657092508388</v>
+        <v>-1.779687287994747</v>
       </c>
       <c r="AR2">
-        <v>1.001079687308742</v>
+        <v>0.8299194021373156</v>
       </c>
       <c r="AS2">
-        <v>0.04668434244946713</v>
+        <v>0.04156482246950464</v>
       </c>
       <c r="AT2" t="b">
         <v>1</v>
@@ -906,7 +918,7 @@
         <v>47</v>
       </c>
       <c r="B3" s="2">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="C3" s="2">
         <v>46261</v>
@@ -957,7 +969,7 @@
         <v>58</v>
       </c>
       <c r="S3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="T3">
         <v>0.9238267595471897</v>
@@ -969,7 +981,7 @@
         <v>56</v>
       </c>
       <c r="W3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="X3">
         <v>0.9996675345594338</v>
@@ -1005,13 +1017,13 @@
         <v>56</v>
       </c>
       <c r="AI3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AJ3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="AK3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="AL3">
         <v>0.8474890458681114</v>
@@ -1046,10 +1058,10 @@
         <v>48</v>
       </c>
       <c r="B4" s="2">
+        <v>46263</v>
+      </c>
+      <c r="C4" s="2">
         <v>46262</v>
-      </c>
-      <c r="C4" s="2">
-        <v>46261</v>
       </c>
       <c r="D4" t="s">
         <v>56</v>
@@ -1061,13 +1073,13 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>1.027987060729755</v>
+        <v>0.6559145524169097</v>
       </c>
       <c r="H4">
-        <v>2.075953044459117</v>
+        <v>2.076454169534499</v>
       </c>
       <c r="I4">
-        <v>0.4957464067330279</v>
+        <v>0.4950588986188687</v>
       </c>
       <c r="J4">
         <v>6</v>
@@ -1079,103 +1091,103 @@
         <v>146</v>
       </c>
       <c r="M4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N4">
-        <v>-0.1588518159006455</v>
+        <v>-0.1798131877478552</v>
       </c>
       <c r="O4">
-        <v>-6.434969394123401</v>
+        <v>-6.794560400728689</v>
       </c>
       <c r="P4">
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>1.027987060729755</v>
+        <v>0.6559145524169097</v>
       </c>
       <c r="R4" t="s">
         <v>59</v>
       </c>
       <c r="S4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="T4">
-        <v>0.9997463834963941</v>
+        <v>0.9252464837641814</v>
       </c>
       <c r="U4">
-        <v>0.8474145119182691</v>
+        <v>0.8148710873515739</v>
       </c>
       <c r="V4" t="s">
         <v>56</v>
       </c>
       <c r="W4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="X4">
-        <v>0.9568870048078872</v>
+        <v>0.911360855534196</v>
       </c>
       <c r="Y4">
-        <v>0.990114557379567</v>
+        <v>0.9940406786307691</v>
       </c>
       <c r="Z4">
-        <v>0.03322755257167975</v>
+        <v>0.08267982309657307</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>2.21566659560143</v>
+        <v>-38.7197629256312</v>
       </c>
       <c r="AC4">
-        <v>-63</v>
+        <v>-83</v>
       </c>
       <c r="AD4">
-        <v>0.9992523825355735</v>
+        <v>0.7802146971412918</v>
       </c>
       <c r="AE4">
-        <v>0.03866103978141239</v>
+        <v>-0.6255118115309433</v>
       </c>
       <c r="AF4">
-        <v>1.016893277512718</v>
+        <v>0.8835830245188717</v>
       </c>
       <c r="AG4">
-        <v>1.006840837366762</v>
+        <v>0.8783174693193667</v>
       </c>
       <c r="AH4" t="s">
         <v>56</v>
       </c>
       <c r="AI4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AJ4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AK4" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="AL4">
-        <v>0.4946871652223435</v>
+        <v>0.3877825735120148</v>
       </c>
       <c r="AM4">
-        <v>0.7906084581925497</v>
+        <v>0.7238488767039348</v>
       </c>
       <c r="AN4">
-        <v>0.9499115837273622</v>
+        <v>0.6980538957778561</v>
       </c>
       <c r="AO4">
-        <v>0.2109457391866109</v>
+        <v>-0.4014588738808464</v>
       </c>
       <c r="AP4">
-        <v>0.5312930792731672</v>
+        <v>-0.0584462836456533</v>
       </c>
       <c r="AQ4">
-        <v>-3.652187981281552</v>
+        <v>-3.762317656626231</v>
       </c>
       <c r="AR4">
-        <v>0.5496652155182299</v>
+        <v>0.6570452047627353</v>
       </c>
       <c r="AS4">
-        <v>0.03804901100647201</v>
+        <v>0.05419846639481267</v>
       </c>
       <c r="AT4" t="b">
         <v>1</v>
@@ -1186,7 +1198,7 @@
         <v>49</v>
       </c>
       <c r="B5" s="2">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="C5" s="2">
         <v>46261</v>
@@ -1234,10 +1246,10 @@
         <v>2.728267187158335</v>
       </c>
       <c r="R5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="S5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="T5">
         <v>0.999577091632214</v>
@@ -1249,7 +1261,7 @@
         <v>56</v>
       </c>
       <c r="W5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="X5">
         <v>0.9777074462237517</v>
@@ -1285,13 +1297,13 @@
         <v>56</v>
       </c>
       <c r="AI5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AJ5" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="AK5" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AL5">
         <v>0.9957922895652901</v>
@@ -1326,10 +1338,10 @@
         <v>50</v>
       </c>
       <c r="B6" s="2">
+        <v>46263</v>
+      </c>
+      <c r="C6" s="2">
         <v>46262</v>
-      </c>
-      <c r="C6" s="2">
-        <v>46261</v>
       </c>
       <c r="D6" t="s">
         <v>56</v>
@@ -1341,13 +1353,13 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0.6682190548559425</v>
+        <v>0.4895064991989366</v>
       </c>
       <c r="H6">
-        <v>0.9431744973283589</v>
+        <v>0.9431982520721013</v>
       </c>
       <c r="I6">
-        <v>0.2576860402814104</v>
+        <v>0.2576135998378419</v>
       </c>
       <c r="J6">
         <v>6</v>
@@ -1359,103 +1371,103 @@
         <v>158</v>
       </c>
       <c r="M6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N6">
-        <v>-0.2935490016796831</v>
+        <v>-0.3201884124755589</v>
       </c>
       <c r="O6">
-        <v>-5.862772152580025</v>
+        <v>-6.185764243942505</v>
       </c>
       <c r="P6">
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>0.6682190548559425</v>
+        <v>0.4895064991989366</v>
       </c>
       <c r="R6" t="s">
         <v>59</v>
       </c>
       <c r="S6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="T6">
-        <v>0.9978388812563632</v>
+        <v>0.9252729325247658</v>
       </c>
       <c r="U6">
-        <v>0.847817217923593</v>
+        <v>0.815482632944722</v>
       </c>
       <c r="V6" t="s">
         <v>56</v>
       </c>
       <c r="W6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="X6">
-        <v>0.9672614372492453</v>
+        <v>0.9499318349226392</v>
       </c>
       <c r="Y6">
-        <v>0.995158885432918</v>
+        <v>0.9964392532343094</v>
       </c>
       <c r="Z6">
-        <v>0.02789744818367268</v>
+        <v>0.04650741831167016</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>-6.459954269721915</v>
+        <v>-38.68065654295471</v>
       </c>
       <c r="AC6">
-        <v>-54</v>
+        <v>-64</v>
       </c>
       <c r="AD6">
-        <v>0.9936507340933957</v>
+        <v>0.7806414491645082</v>
       </c>
       <c r="AE6">
-        <v>-0.1125087491515919</v>
+        <v>-0.6249791419290219</v>
       </c>
       <c r="AF6">
-        <v>0.6047930484193282</v>
+        <v>0.5761990817658589</v>
       </c>
       <c r="AG6">
-        <v>0.6018651759825555</v>
+        <v>0.5741473827490672</v>
       </c>
       <c r="AH6" t="s">
         <v>56</v>
       </c>
       <c r="AI6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AJ6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AK6" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="AL6">
-        <v>0.4944201785249922</v>
+        <v>0.3889308913246158</v>
       </c>
       <c r="AM6">
-        <v>0.79161477440737</v>
+        <v>0.7266105836153767</v>
       </c>
       <c r="AN6">
-        <v>0.584883756885283</v>
+        <v>0.4635374534382177</v>
       </c>
       <c r="AO6">
-        <v>0.01130456041590575</v>
+        <v>-0.2910754003251648</v>
       </c>
       <c r="AP6">
-        <v>0.4990531969617066</v>
+        <v>0.2150259437815997</v>
       </c>
       <c r="AQ6">
-        <v>-2.079923857443279</v>
+        <v>-2.071350336448071</v>
       </c>
       <c r="AR6">
-        <v>0.4236009838695852</v>
+        <v>0.2712958284126735</v>
       </c>
       <c r="AS6">
-        <v>0.03190703814779901</v>
+        <v>0.04223726510655999</v>
       </c>
       <c r="AT6" t="b">
         <v>1</v>
@@ -1466,7 +1478,7 @@
         <v>51</v>
       </c>
       <c r="B7" s="2">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="C7" s="2">
         <v>46261</v>
@@ -1514,10 +1526,10 @@
         <v>2.657425042408513</v>
       </c>
       <c r="R7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="S7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="T7">
         <v>0.991895502751434</v>
@@ -1529,7 +1541,7 @@
         <v>56</v>
       </c>
       <c r="W7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="X7">
         <v>0.9808067239079912</v>
@@ -1565,13 +1577,13 @@
         <v>56</v>
       </c>
       <c r="AI7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AJ7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="AK7" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AL7">
         <v>0.981534951680524</v>
@@ -1606,7 +1618,7 @@
         <v>52</v>
       </c>
       <c r="B8" s="2">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="C8" s="2">
         <v>46261</v>
@@ -1654,10 +1666,10 @@
         <v>0.3355627536554929</v>
       </c>
       <c r="R8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S8" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="T8">
         <v>-0.9277088794389501</v>
@@ -1669,7 +1681,7 @@
         <v>57</v>
       </c>
       <c r="W8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="X8">
         <v>0.8992203129224055</v>
@@ -1705,13 +1717,13 @@
         <v>57</v>
       </c>
       <c r="AI8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="AJ8" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AK8" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="AL8">
         <v>-0.3675518617307726</v>
@@ -1746,7 +1758,7 @@
         <v>53</v>
       </c>
       <c r="B9" s="2">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="C9" s="2">
         <v>46261</v>
@@ -1794,10 +1806,10 @@
         <v>4.200028847746982</v>
       </c>
       <c r="R9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="S9" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="T9">
         <v>-0.9956832798643895</v>
@@ -1809,7 +1821,7 @@
         <v>57</v>
       </c>
       <c r="W9" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="X9">
         <v>0.9967856581932435</v>
@@ -1845,13 +1857,13 @@
         <v>57</v>
       </c>
       <c r="AI9" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="AJ9" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="AK9" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="AL9">
         <v>-0.9909094781236527</v>
@@ -1886,7 +1898,7 @@
         <v>54</v>
       </c>
       <c r="B10" s="2">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="C10" s="2">
         <v>46261</v>
@@ -1934,10 +1946,10 @@
         <v>1.07338862476908</v>
       </c>
       <c r="R10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="S10" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="T10">
         <v>-0.8320553347889856</v>
@@ -1949,7 +1961,7 @@
         <v>57</v>
       </c>
       <c r="W10" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="X10">
         <v>0.9908072786304687</v>
@@ -1985,13 +1997,13 @@
         <v>57</v>
       </c>
       <c r="AI10" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="AJ10" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="AK10" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="AL10">
         <v>-0.4147357392962181</v>
@@ -2026,7 +2038,7 @@
         <v>55</v>
       </c>
       <c r="B11" s="2">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="C11" s="2">
         <v>46261</v>
@@ -2077,7 +2089,7 @@
         <v>58</v>
       </c>
       <c r="S11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="T11">
         <v>0.9329484855842582</v>
@@ -2089,7 +2101,7 @@
         <v>56</v>
       </c>
       <c r="W11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="X11">
         <v>0.9983810294675523</v>
@@ -2125,13 +2137,13 @@
         <v>56</v>
       </c>
       <c r="AI11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AJ11" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="AK11" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="AL11">
         <v>0.8770578364185306</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="81">
   <si>
     <t>Pair</t>
   </si>
@@ -196,36 +196,30 @@
     <t>UP_DECELERATING</t>
   </si>
   <si>
+    <t>DOWN_DECELERATING</t>
+  </si>
+  <si>
+    <t>DOWN_STEADY</t>
+  </si>
+  <si>
     <t>UP_STEADY</t>
   </si>
   <si>
-    <t>DOWN_ACCELERATING</t>
-  </si>
-  <si>
-    <t>DOWN_STEADY</t>
-  </si>
-  <si>
-    <t>DOWN_DECELERATING</t>
-  </si>
-  <si>
     <t>多头加速</t>
   </si>
   <si>
     <t>多头减速</t>
   </si>
   <si>
+    <t>空头减速</t>
+  </si>
+  <si>
+    <t>空头稳态</t>
+  </si>
+  <si>
     <t>多头稳态</t>
   </si>
   <si>
-    <t>空头加速</t>
-  </si>
-  <si>
-    <t>空头稳态</t>
-  </si>
-  <si>
-    <t>空头减速</t>
-  </si>
-  <si>
     <t>ALIGNED</t>
   </si>
   <si>
@@ -241,34 +235,28 @@
     <t>UP_CREST_FLATTENING</t>
   </si>
   <si>
+    <t>DOWN_VALLEY_FLATTENING</t>
+  </si>
+  <si>
+    <t>DOWN_SLOPE</t>
+  </si>
+  <si>
     <t>UP_SLOPE</t>
   </si>
   <si>
-    <t>DOWN_STEEPENING</t>
-  </si>
-  <si>
-    <t>DOWN_SLOPE</t>
-  </si>
-  <si>
-    <t>DOWN_VALLEY_FLATTENING</t>
-  </si>
-  <si>
     <t>上升陡坡形成</t>
   </si>
   <si>
     <t>上升坡顶钝化</t>
   </si>
   <si>
+    <t>下降谷底收敛</t>
+  </si>
+  <si>
+    <t>下降坡延续</t>
+  </si>
+  <si>
     <t>上升坡延续</t>
-  </si>
-  <si>
-    <t>下降陡坡形成</t>
-  </si>
-  <si>
-    <t>下降坡延续</t>
-  </si>
-  <si>
-    <t>下降谷底收敛</t>
   </si>
 </sst>
 </file>
@@ -778,7 +766,7 @@
         <v>46</v>
       </c>
       <c r="B2" s="2">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="C2" s="2">
         <v>46262</v>
@@ -829,7 +817,7 @@
         <v>58</v>
       </c>
       <c r="S2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="T2">
         <v>0.9348943950044755</v>
@@ -841,7 +829,7 @@
         <v>56</v>
       </c>
       <c r="W2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="X2">
         <v>0.9995055931747207</v>
@@ -877,13 +865,13 @@
         <v>56</v>
       </c>
       <c r="AI2" t="s">
+        <v>69</v>
+      </c>
+      <c r="AJ2" t="s">
         <v>71</v>
       </c>
-      <c r="AJ2" t="s">
-        <v>73</v>
-      </c>
       <c r="AK2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="AL2">
         <v>0.6061814057679599</v>
@@ -918,10 +906,10 @@
         <v>47</v>
       </c>
       <c r="B3" s="2">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="C3" s="2">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="D3" t="s">
         <v>56</v>
@@ -933,13 +921,13 @@
         <v>1</v>
       </c>
       <c r="G3">
-        <v>3.11960411317304</v>
+        <v>2.780310782846937</v>
       </c>
       <c r="H3">
-        <v>1.871477190332932</v>
+        <v>1.880299178025882</v>
       </c>
       <c r="I3">
-        <v>0.4235078409527687</v>
+        <v>0.4250181075804823</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -951,103 +939,103 @@
         <v>225</v>
       </c>
       <c r="M3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N3">
-        <v>-0.05898165736660619</v>
+        <v>-0.06551246910444915</v>
       </c>
       <c r="O3">
-        <v>-21.52054217181356</v>
+        <v>-22.99835926435024</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>3.11960411317304</v>
+        <v>2.780310782846937</v>
       </c>
       <c r="R3" t="s">
         <v>58</v>
       </c>
       <c r="S3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="T3">
-        <v>0.9238267595471897</v>
+        <v>0.9703334336358443</v>
       </c>
       <c r="U3">
-        <v>0.9656775331195359</v>
+        <v>0.9864553205390064</v>
       </c>
       <c r="V3" t="s">
         <v>56</v>
       </c>
       <c r="W3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="X3">
-        <v>0.9996675345594338</v>
+        <v>0.9967654329550666</v>
       </c>
       <c r="Y3">
-        <v>0.9998219652932022</v>
+        <v>0.9992211016115058</v>
       </c>
       <c r="Z3">
-        <v>0.0001544307337684181</v>
+        <v>0.002455668656439203</v>
       </c>
       <c r="AA3">
         <v>1</v>
       </c>
       <c r="AB3">
-        <v>32.04410174202717</v>
+        <v>19.84005300651215</v>
       </c>
       <c r="AC3">
-        <v>-3.999999999999993</v>
+        <v>-16</v>
       </c>
       <c r="AD3">
-        <v>0.8476399551990053</v>
+        <v>0.9406437420187334</v>
       </c>
       <c r="AE3">
-        <v>0.5305718672811708</v>
+        <v>0.3393955665606059</v>
       </c>
       <c r="AF3">
-        <v>2.892092319420074</v>
+        <v>2.423199913035678</v>
       </c>
       <c r="AG3">
-        <v>2.891577426611954</v>
+        <v>2.421312486528415</v>
       </c>
       <c r="AH3" t="s">
         <v>56</v>
       </c>
       <c r="AI3" t="s">
+        <v>69</v>
+      </c>
+      <c r="AJ3" t="s">
         <v>71</v>
       </c>
-      <c r="AJ3" t="s">
-        <v>73</v>
-      </c>
       <c r="AK3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="AL3">
-        <v>0.8474890458681114</v>
+        <v>0.9399110761239278</v>
       </c>
       <c r="AM3">
-        <v>0.9477808728007524</v>
+        <v>0.9764628933496899</v>
       </c>
       <c r="AN3">
-        <v>2.437557533194274</v>
+        <v>2.240061336783815</v>
       </c>
       <c r="AO3">
-        <v>1.55465448489466</v>
+        <v>0.9033816280602533</v>
       </c>
       <c r="AP3">
-        <v>3.568085769401152</v>
+        <v>2.899004921740559</v>
       </c>
       <c r="AQ3">
-        <v>-4.467541592149739</v>
+        <v>-5.257395196758583</v>
       </c>
       <c r="AR3">
-        <v>3.141719990070078</v>
+        <v>2.416652610783764</v>
       </c>
       <c r="AS3">
-        <v>0.04299201074379971</v>
+        <v>0.03638409879971379</v>
       </c>
       <c r="AT3" t="b">
         <v>1</v>
@@ -1058,7 +1046,7 @@
         <v>48</v>
       </c>
       <c r="B4" s="2">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="C4" s="2">
         <v>46262</v>
@@ -1109,7 +1097,7 @@
         <v>59</v>
       </c>
       <c r="S4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T4">
         <v>0.9252464837641814</v>
@@ -1121,7 +1109,7 @@
         <v>56</v>
       </c>
       <c r="W4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="X4">
         <v>0.911360855534196</v>
@@ -1157,13 +1145,13 @@
         <v>56</v>
       </c>
       <c r="AI4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="AJ4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AK4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="AL4">
         <v>0.3877825735120148</v>
@@ -1198,10 +1186,10 @@
         <v>49</v>
       </c>
       <c r="B5" s="2">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="C5" s="2">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="D5" t="s">
         <v>56</v>
@@ -1213,13 +1201,13 @@
         <v>1</v>
       </c>
       <c r="G5">
-        <v>2.728267187158335</v>
+        <v>1.985211862947266</v>
       </c>
       <c r="H5">
-        <v>1.45106701164125</v>
+        <v>1.458296112700348</v>
       </c>
       <c r="I5">
-        <v>0.315124499165984</v>
+        <v>0.3187574056272627</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -1231,103 +1219,103 @@
         <v>226</v>
       </c>
       <c r="M5">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N5">
-        <v>-0.0715966356119441</v>
+        <v>-0.07793652217100289</v>
       </c>
       <c r="O5">
-        <v>-23.95394667384919</v>
+        <v>-23.80000677051037</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>2.728267187158335</v>
+        <v>1.985211862947266</v>
       </c>
       <c r="R5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="S5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="T5">
-        <v>0.999577091632214</v>
+        <v>0.9318137970852972</v>
       </c>
       <c r="U5">
-        <v>0.9989688622160841</v>
+        <v>0.9685020822574847</v>
       </c>
       <c r="V5" t="s">
         <v>56</v>
       </c>
       <c r="W5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="X5">
-        <v>0.9777074462237517</v>
+        <v>0.9606397525010582</v>
       </c>
       <c r="Y5">
-        <v>0.9966366839263512</v>
+        <v>0.9967434942764036</v>
       </c>
       <c r="Z5">
-        <v>0.01892923770259947</v>
+        <v>0.03610374177534548</v>
       </c>
       <c r="AA5">
         <v>1</v>
       </c>
       <c r="AB5">
-        <v>-2.358699015199895</v>
+        <v>-30.29894732759313</v>
       </c>
       <c r="AC5">
-        <v>-44</v>
+        <v>-57</v>
       </c>
       <c r="AD5">
-        <v>0.9991527560898776</v>
+        <v>0.8634048199449916</v>
       </c>
       <c r="AE5">
-        <v>-0.04115543704058305</v>
+        <v>-0.5045117609092542</v>
       </c>
       <c r="AF5">
-        <v>2.351525635725401</v>
+        <v>2.023583436391713</v>
       </c>
       <c r="AG5">
-        <v>2.343616711757169</v>
+        <v>2.016993625348928</v>
       </c>
       <c r="AH5" t="s">
         <v>56</v>
       </c>
       <c r="AI5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="AJ5" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="AK5" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AL5">
-        <v>0.9957922895652901</v>
+        <v>0.8605931372070601</v>
       </c>
       <c r="AM5">
-        <v>0.9935058136678155</v>
+        <v>0.9525777900775656</v>
       </c>
       <c r="AN5">
-        <v>2.294550112974665</v>
+        <v>1.777759279664566</v>
       </c>
       <c r="AO5">
-        <v>0.1446359298432478</v>
+        <v>-0.7864184817169323</v>
       </c>
       <c r="AP5">
-        <v>2.420551647623656</v>
+        <v>1.299479478083904</v>
       </c>
       <c r="AQ5">
-        <v>-6.49877877332037</v>
+        <v>-6.473876457646504</v>
       </c>
       <c r="AR5">
-        <v>1.873226976578128</v>
+        <v>1.113264888823018</v>
       </c>
       <c r="AS5">
-        <v>0.03375235022247104</v>
+        <v>0.03535919268448668</v>
       </c>
       <c r="AT5" t="b">
         <v>1</v>
@@ -1338,7 +1326,7 @@
         <v>50</v>
       </c>
       <c r="B6" s="2">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="C6" s="2">
         <v>46262</v>
@@ -1389,7 +1377,7 @@
         <v>59</v>
       </c>
       <c r="S6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T6">
         <v>0.9252729325247658</v>
@@ -1401,7 +1389,7 @@
         <v>56</v>
       </c>
       <c r="W6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="X6">
         <v>0.9499318349226392</v>
@@ -1437,13 +1425,13 @@
         <v>56</v>
       </c>
       <c r="AI6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="AJ6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AK6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="AL6">
         <v>0.3889308913246158</v>
@@ -1478,10 +1466,10 @@
         <v>51</v>
       </c>
       <c r="B7" s="2">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="C7" s="2">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="D7" t="s">
         <v>56</v>
@@ -1493,13 +1481,13 @@
         <v>1</v>
       </c>
       <c r="G7">
-        <v>2.657425042408513</v>
+        <v>2.065352552866162</v>
       </c>
       <c r="H7">
-        <v>1.403286293935856</v>
+        <v>1.410888817761677</v>
       </c>
       <c r="I7">
-        <v>0.332553994872276</v>
+        <v>0.3370633745033623</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -1511,103 +1499,103 @@
         <v>239</v>
       </c>
       <c r="M7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N7">
-        <v>-0.1113341157341253</v>
+        <v>-0.1189648280438466</v>
       </c>
       <c r="O7">
-        <v>-29.84828840056969</v>
+        <v>-29.65911481816141</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>2.657425042408513</v>
+        <v>2.065352552866162</v>
       </c>
       <c r="R7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="S7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="T7">
-        <v>0.991895502751434</v>
+        <v>0.9243705953802875</v>
       </c>
       <c r="U7">
-        <v>0.9957843543883421</v>
+        <v>0.9654357356096457</v>
       </c>
       <c r="V7" t="s">
         <v>56</v>
       </c>
       <c r="W7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="X7">
-        <v>0.9808067239079912</v>
+        <v>0.9751241142646272</v>
       </c>
       <c r="Y7">
-        <v>0.9977255126007871</v>
+        <v>0.9978758707540648</v>
       </c>
       <c r="Z7">
-        <v>0.01691878869279595</v>
+        <v>0.02275175648943761</v>
       </c>
       <c r="AA7">
         <v>1</v>
       </c>
       <c r="AB7">
-        <v>-10.33599012645593</v>
+        <v>-31.94242147592362</v>
       </c>
       <c r="AC7">
-        <v>-41</v>
+        <v>-46</v>
       </c>
       <c r="AD7">
-        <v>0.9837725299034812</v>
+        <v>0.8485802021697957</v>
       </c>
       <c r="AE7">
-        <v>-0.179420203453525</v>
+        <v>-0.5290667637316377</v>
       </c>
       <c r="AF7">
-        <v>2.240832310512667</v>
+        <v>2.03672342464955</v>
       </c>
       <c r="AG7">
-        <v>2.235735565658657</v>
+        <v>2.032397160857371</v>
       </c>
       <c r="AH7" t="s">
         <v>56</v>
       </c>
       <c r="AI7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="AJ7" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="AK7" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AL7">
-        <v>0.981534951680524</v>
+        <v>0.8467777081448452</v>
       </c>
       <c r="AM7">
-        <v>0.9897031014416999</v>
+        <v>0.9490899162399291</v>
       </c>
       <c r="AN7">
-        <v>2.188426718575088</v>
+        <v>1.769749825094938</v>
       </c>
       <c r="AO7">
-        <v>-0.2030176917188164</v>
+        <v>-0.9013392448438455</v>
       </c>
       <c r="AP7">
-        <v>2.580792136150472</v>
+        <v>1.711719197888291</v>
       </c>
       <c r="AQ7">
-        <v>-5.957422268418081</v>
+        <v>-5.706922387981857</v>
       </c>
       <c r="AR7">
-        <v>2.063421195497497</v>
+        <v>1.312622839986435</v>
       </c>
       <c r="AS7">
-        <v>0.03088391293079938</v>
+        <v>0.03160466116621462</v>
       </c>
       <c r="AT7" t="b">
         <v>1</v>
@@ -1618,10 +1606,10 @@
         <v>52</v>
       </c>
       <c r="B8" s="2">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="C8" s="2">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="D8" t="s">
         <v>57</v>
@@ -1633,121 +1621,121 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>0.1688806419123562</v>
+        <v>0.03129653978359413</v>
       </c>
       <c r="H8">
-        <v>1.43504836428982</v>
+        <v>1.435563294450914</v>
       </c>
       <c r="I8">
-        <v>0.3538128480621394</v>
+        <v>0.3542409547493119</v>
       </c>
       <c r="J8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K8">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="L8">
         <v>112</v>
       </c>
       <c r="M8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N8">
-        <v>0.00441069340694911</v>
+        <v>0.005338075962783961</v>
       </c>
       <c r="O8">
-        <v>1.210778582299763</v>
+        <v>1.400938484937214</v>
       </c>
       <c r="P8">
-        <v>0.4967241147218076</v>
+        <v>0.4026730539323848</v>
       </c>
       <c r="Q8">
-        <v>0.3355627536554929</v>
+        <v>0.05239432104918212</v>
       </c>
       <c r="R8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="S8" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="T8">
-        <v>-0.9277088794389501</v>
+        <v>-0.96686717777381</v>
       </c>
       <c r="U8">
-        <v>0.8031362218831346</v>
+        <v>0.7697178953989755</v>
       </c>
       <c r="V8" t="s">
         <v>57</v>
       </c>
       <c r="W8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="X8">
-        <v>0.8992203129224055</v>
+        <v>0.4904552472291694</v>
       </c>
       <c r="Y8">
-        <v>0.9426689045424286</v>
+        <v>0.8385106616030441</v>
       </c>
       <c r="Z8">
-        <v>0.04344859162002312</v>
+        <v>0.3480554143738747</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>-141.2432878169698</v>
+        <v>153.7376070546685</v>
       </c>
       <c r="AC8">
         <v>-90</v>
       </c>
       <c r="AD8">
-        <v>-0.7798111509983079</v>
+        <v>-0.8967770545270213</v>
       </c>
       <c r="AE8">
-        <v>-0.6260148311171984</v>
+        <v>0.4424826713825525</v>
       </c>
       <c r="AF8">
-        <v>0.7243819612639005</v>
+        <v>0.3724385986291912</v>
       </c>
       <c r="AG8">
-        <v>0.682852349894937</v>
+        <v>0.3122937357430737</v>
       </c>
       <c r="AH8" t="s">
         <v>57</v>
       </c>
       <c r="AI8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="AJ8" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="AK8" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AL8">
-        <v>-0.3675518617307726</v>
+        <v>-0.3759785606509409</v>
       </c>
       <c r="AM8">
-        <v>0.7067980543227322</v>
+        <v>0.6981555557858671</v>
       </c>
       <c r="AN8">
-        <v>-0.3355743668208713</v>
+        <v>-0.165946552732431</v>
       </c>
       <c r="AO8">
-        <v>-0.5582870336571798</v>
+        <v>0.07634165572216554</v>
       </c>
       <c r="AP8">
-        <v>-0.06107190201638424</v>
+        <v>0.4819514082908494</v>
       </c>
       <c r="AQ8">
-        <v>1.6928265853255</v>
+        <v>2.135274964074843</v>
       </c>
       <c r="AR8">
-        <v>0.2779852756397786</v>
+        <v>0.7150847495479273</v>
       </c>
       <c r="AS8">
-        <v>0.04719605044406718</v>
+        <v>0.09570861422203129</v>
       </c>
       <c r="AT8" t="b">
         <v>1</v>
@@ -1758,10 +1746,10 @@
         <v>53</v>
       </c>
       <c r="B9" s="2">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="C9" s="2">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="D9" t="s">
         <v>57</v>
@@ -1770,16 +1758,16 @@
         <v>-1</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>0.9977480549270116</v>
       </c>
       <c r="G9">
-        <v>4.200028847746982</v>
+        <v>3.596004773033763</v>
       </c>
       <c r="H9">
-        <v>2.977708752071287</v>
+        <v>2.98393561777218</v>
       </c>
       <c r="I9">
-        <v>0.6117257074536422</v>
+        <v>0.6148383195101931</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -1791,103 +1779,103 @@
         <v>76</v>
       </c>
       <c r="M9">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="N9">
-        <v>0.4466813232343693</v>
+        <v>0.4667769843375754</v>
       </c>
       <c r="O9">
-        <v>68.41945870110679</v>
+        <v>68.08582809674994</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>4.200028847746982</v>
+        <v>3.596004773033763</v>
       </c>
       <c r="R9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="S9" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="T9">
-        <v>-0.9956832798643895</v>
+        <v>-0.9941871490978429</v>
       </c>
       <c r="U9">
-        <v>0.9979427101257972</v>
+        <v>0.996800010265797</v>
       </c>
       <c r="V9" t="s">
         <v>57</v>
       </c>
       <c r="W9" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="X9">
-        <v>0.9967856581932435</v>
+        <v>0.9913577622788545</v>
       </c>
       <c r="Y9">
-        <v>0.9995409367472872</v>
+        <v>0.9990143397308635</v>
       </c>
       <c r="Z9">
-        <v>0.002755278554043672</v>
+        <v>0.007656577452008984</v>
       </c>
       <c r="AA9">
         <v>1</v>
       </c>
       <c r="AB9">
-        <v>-172.4648403848067</v>
+        <v>171.2542612435548</v>
       </c>
       <c r="AC9">
-        <v>-16</v>
+        <v>-27</v>
       </c>
       <c r="AD9">
-        <v>-0.9913645771710732</v>
+        <v>-0.9883728215658543</v>
       </c>
       <c r="AE9">
-        <v>-0.131134568784967</v>
+        <v>0.1520498786252458</v>
       </c>
       <c r="AF9">
-        <v>3.260342912738567</v>
+        <v>2.847466757773598</v>
       </c>
       <c r="AG9">
-        <v>3.258846209116086</v>
+        <v>2.844660122922773</v>
       </c>
       <c r="AH9" t="s">
         <v>57</v>
       </c>
       <c r="AI9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="AJ9" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="AK9" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="AL9">
-        <v>-0.9909094781236527</v>
+        <v>-0.9873986217445425</v>
       </c>
       <c r="AM9">
-        <v>0.9918758055597627</v>
+        <v>0.9916044735582022</v>
       </c>
       <c r="AN9">
-        <v>-3.20671205489344</v>
+        <v>-2.808762545035531</v>
       </c>
       <c r="AO9">
-        <v>-0.5278330049535788</v>
+        <v>0.2817477522468126</v>
       </c>
       <c r="AP9">
-        <v>-5.17559930178544</v>
+        <v>-4.168811817399995</v>
       </c>
       <c r="AQ9">
-        <v>5.49292428904988</v>
+        <v>5.846921502275215</v>
       </c>
       <c r="AR9">
-        <v>4.657868320299822</v>
+        <v>3.643133555044059</v>
       </c>
       <c r="AS9">
-        <v>0.03581930302073087</v>
+        <v>0.03041594544904188</v>
       </c>
       <c r="AT9" t="b">
         <v>1</v>
@@ -1898,10 +1886,10 @@
         <v>54</v>
       </c>
       <c r="B10" s="2">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="C10" s="2">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="D10" t="s">
         <v>57</v>
@@ -1913,13 +1901,13 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>1.07338862476908</v>
+        <v>0.8742685934430834</v>
       </c>
       <c r="H10">
-        <v>2.04340906713034</v>
+        <v>2.043910740272992</v>
       </c>
       <c r="I10">
-        <v>0.4614250367241567</v>
+        <v>0.4605955191246818</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1931,103 +1919,103 @@
         <v>233</v>
       </c>
       <c r="M10">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N10">
-        <v>16.91647993108354</v>
+        <v>17.41888558021623</v>
       </c>
       <c r="O10">
-        <v>30.21763560257356</v>
+        <v>36.18434574123132</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>0.005220213602015803</v>
       </c>
       <c r="Q10">
-        <v>1.07338862476908</v>
+        <v>0.8788564116373314</v>
       </c>
       <c r="R10" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="S10" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="T10">
-        <v>-0.8320553347889856</v>
+        <v>-0.6712964160116982</v>
       </c>
       <c r="U10">
-        <v>0.7742723007858487</v>
+        <v>0.7019307209075971</v>
       </c>
       <c r="V10" t="s">
         <v>57</v>
       </c>
       <c r="W10" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="X10">
-        <v>0.9908072786304687</v>
+        <v>0.989208995562361</v>
       </c>
       <c r="Y10">
-        <v>0.9993896005232207</v>
+        <v>0.9993893348093316</v>
       </c>
       <c r="Z10">
-        <v>0.008582321892751987</v>
+        <v>0.01018033924697059</v>
       </c>
       <c r="AA10">
-        <v>0.3199984626790244</v>
+        <v>0.8536811385896879</v>
       </c>
       <c r="AB10">
-        <v>128.9595822289384</v>
+        <v>115.2109289295812</v>
       </c>
       <c r="AC10">
-        <v>-29</v>
+        <v>-30.99999999999999</v>
       </c>
       <c r="AD10">
-        <v>-0.6287720177370196</v>
+        <v>-0.4259518757826853</v>
       </c>
       <c r="AE10">
-        <v>0.777589705250087</v>
+        <v>0.9047458203922314</v>
       </c>
       <c r="AF10">
-        <v>1.505077624233367</v>
+        <v>1.902016816671712</v>
       </c>
       <c r="AG10">
-        <v>1.504158925639022</v>
+        <v>1.900855321209705</v>
       </c>
       <c r="AH10" t="s">
         <v>57</v>
       </c>
       <c r="AI10" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="AJ10" t="s">
+        <v>73</v>
+      </c>
+      <c r="AK10" t="s">
         <v>78</v>
       </c>
-      <c r="AK10" t="s">
-        <v>84</v>
-      </c>
       <c r="AL10">
-        <v>-0.4147357392962181</v>
+        <v>-0.3945483948501372</v>
       </c>
       <c r="AM10">
-        <v>0.7446872215128757</v>
+        <v>0.7873112823858313</v>
       </c>
       <c r="AN10">
-        <v>-1.012058221146405</v>
+        <v>-0.910357128493263</v>
       </c>
       <c r="AO10">
-        <v>1.095235343166743</v>
+        <v>1.646591202880866</v>
       </c>
       <c r="AP10">
-        <v>-0.4528363004562632</v>
+        <v>-0.01141619691061446</v>
       </c>
       <c r="AQ10">
-        <v>3.524255776461361</v>
+        <v>3.950967184139676</v>
       </c>
       <c r="AR10">
-        <v>0.5011887373469135</v>
+        <v>0.6168233305910883</v>
       </c>
       <c r="AS10">
-        <v>0.05153624351441453</v>
+        <v>0.07331183500118622</v>
       </c>
       <c r="AT10" t="b">
         <v>1</v>
@@ -2038,10 +2026,10 @@
         <v>55</v>
       </c>
       <c r="B11" s="2">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="C11" s="2">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="D11" t="s">
         <v>56</v>
@@ -2050,16 +2038,16 @@
         <v>1</v>
       </c>
       <c r="F11">
-        <v>0.4697420678723502</v>
+        <v>0.2540639152737681</v>
       </c>
       <c r="G11">
-        <v>2.618565437526386</v>
+        <v>2.322852469405903</v>
       </c>
       <c r="H11">
-        <v>2.655926791693029</v>
+        <v>2.624859300124137</v>
       </c>
       <c r="I11">
-        <v>0.6173811549484833</v>
+        <v>0.6139945487349256</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -2071,103 +2059,103 @@
         <v>212</v>
       </c>
       <c r="M11">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N11">
-        <v>-1272.218901912979</v>
+        <v>-1427.349256983209</v>
       </c>
       <c r="O11">
-        <v>-16.59428842781236</v>
+        <v>-19.64528536870374</v>
       </c>
       <c r="P11">
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>2.618565437526386</v>
+        <v>2.322852469405903</v>
       </c>
       <c r="R11" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="S11" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="T11">
-        <v>0.9329484855842582</v>
+        <v>0.9998966016244263</v>
       </c>
       <c r="U11">
-        <v>0.8901824479127239</v>
+        <v>0.8870599242088987</v>
       </c>
       <c r="V11" t="s">
         <v>56</v>
       </c>
       <c r="W11" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="X11">
-        <v>0.9983810294675523</v>
+        <v>0.975987933793338</v>
       </c>
       <c r="Y11">
-        <v>0.9995772768758208</v>
+        <v>0.9959874647473664</v>
       </c>
       <c r="Z11">
-        <v>0.001196247408268514</v>
+        <v>0.0199995309540284</v>
       </c>
       <c r="AA11">
-        <v>1</v>
+        <v>0.7105143746728754</v>
       </c>
       <c r="AB11">
-        <v>28.66626680083258</v>
+        <v>1.146720127689915</v>
       </c>
       <c r="AC11">
-        <v>-11</v>
+        <v>-46.99999999999999</v>
       </c>
       <c r="AD11">
-        <v>0.8774287458392165</v>
+        <v>0.9997997257501915</v>
       </c>
       <c r="AE11">
-        <v>0.4797069897083215</v>
+        <v>0.02001270571016804</v>
       </c>
       <c r="AF11">
-        <v>2.484791317115895</v>
+        <v>2.076852186058759</v>
       </c>
       <c r="AG11">
-        <v>2.483740938367391</v>
+        <v>2.068518743447689</v>
       </c>
       <c r="AH11" t="s">
         <v>56</v>
       </c>
       <c r="AI11" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="AJ11" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="AK11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL11">
-        <v>0.8770578364185306</v>
+        <v>0.8516548390216744</v>
       </c>
       <c r="AM11">
-        <v>0.9574293864880095</v>
+        <v>0.9357741059129674</v>
       </c>
       <c r="AN11">
-        <v>2.144487492293096</v>
+        <v>2.007420384984957</v>
       </c>
       <c r="AO11">
-        <v>1.247151078039161</v>
+        <v>0.2809308777946071</v>
       </c>
       <c r="AP11">
-        <v>2.57433094526332</v>
+        <v>1.838264412003431</v>
       </c>
       <c r="AQ11">
-        <v>-5.461487894355134</v>
+        <v>-6.635317247010361</v>
       </c>
       <c r="AR11">
-        <v>2.078465428757228</v>
+        <v>1.509129104110315</v>
       </c>
       <c r="AS11">
-        <v>0.03767522780195163</v>
+        <v>0.03242866272162204</v>
       </c>
       <c r="AT11" t="b">
         <v>1</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="82">
   <si>
     <t>Pair</t>
   </si>
@@ -193,70 +193,73 @@
     <t>UP_ACCELERATING</t>
   </si>
   <si>
+    <t>UP_STEADY</t>
+  </si>
+  <si>
     <t>UP_DECELERATING</t>
   </si>
   <si>
     <t>DOWN_DECELERATING</t>
   </si>
   <si>
-    <t>DOWN_STEADY</t>
-  </si>
-  <si>
-    <t>UP_STEADY</t>
-  </si>
-  <si>
     <t>多头加速</t>
   </si>
   <si>
+    <t>多头稳态</t>
+  </si>
+  <si>
     <t>多头减速</t>
   </si>
   <si>
     <t>空头减速</t>
   </si>
   <si>
-    <t>空头稳态</t>
-  </si>
-  <si>
-    <t>多头稳态</t>
+    <t>NEUTRAL</t>
   </si>
   <si>
     <t>ALIGNED</t>
   </si>
   <si>
+    <t>TRANSITION</t>
+  </si>
+  <si>
     <t>上涨</t>
   </si>
   <si>
+    <t>转换</t>
+  </si>
+  <si>
     <t>下跌</t>
   </si>
   <si>
     <t>UP_STEEPENING</t>
   </si>
   <si>
+    <t>UP_SLOPE</t>
+  </si>
+  <si>
     <t>UP_CREST_FLATTENING</t>
   </si>
   <si>
+    <t>TRANSITION_ZONE</t>
+  </si>
+  <si>
     <t>DOWN_VALLEY_FLATTENING</t>
   </si>
   <si>
-    <t>DOWN_SLOPE</t>
-  </si>
-  <si>
-    <t>UP_SLOPE</t>
-  </si>
-  <si>
     <t>上升陡坡形成</t>
   </si>
   <si>
+    <t>上升坡延续</t>
+  </si>
+  <si>
     <t>上升坡顶钝化</t>
   </si>
   <si>
+    <t>地形转换区</t>
+  </si>
+  <si>
     <t>下降谷底收敛</t>
-  </si>
-  <si>
-    <t>下降坡延续</t>
-  </si>
-  <si>
-    <t>上升坡延续</t>
   </si>
 </sst>
 </file>
@@ -766,10 +769,10 @@
         <v>46</v>
       </c>
       <c r="B2" s="2">
+        <v>46266</v>
+      </c>
+      <c r="C2" s="2">
         <v>46265</v>
-      </c>
-      <c r="C2" s="2">
-        <v>46262</v>
       </c>
       <c r="D2" t="s">
         <v>56</v>
@@ -778,16 +781,16 @@
         <v>1</v>
       </c>
       <c r="F2">
-        <v>0.3251179412996309</v>
+        <v>0.2455061550918489</v>
       </c>
       <c r="G2">
-        <v>0.9795677792001615</v>
+        <v>0.9387777012599231</v>
       </c>
       <c r="H2">
-        <v>1.069875711605798</v>
+        <v>1.070184795603349</v>
       </c>
       <c r="I2">
-        <v>0.2581966757389444</v>
+        <v>0.2581734233903618</v>
       </c>
       <c r="J2">
         <v>6</v>
@@ -799,67 +802,67 @@
         <v>149</v>
       </c>
       <c r="M2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N2">
-        <v>-0.199436859484536</v>
+        <v>-0.2275907190055462</v>
       </c>
       <c r="O2">
-        <v>-5.571417804616382</v>
+        <v>-6.345761020648159</v>
       </c>
       <c r="P2">
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.9795677792001615</v>
+        <v>0.9387777012599231</v>
       </c>
       <c r="R2" t="s">
         <v>58</v>
       </c>
       <c r="S2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="T2">
-        <v>0.9348943950044755</v>
+        <v>0.962668202750775</v>
       </c>
       <c r="U2">
-        <v>0.869403865563667</v>
+        <v>0.8699317471802042</v>
       </c>
       <c r="V2" t="s">
         <v>56</v>
       </c>
       <c r="W2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="X2">
-        <v>0.9995055931747207</v>
+        <v>0.9989287828465166</v>
       </c>
       <c r="Y2">
-        <v>0.9997347864668334</v>
+        <v>0.9996205307143123</v>
       </c>
       <c r="Z2">
-        <v>0.0002291932921127948</v>
+        <v>0.000691747867795689</v>
       </c>
       <c r="AA2">
-        <v>0.4210383443117264</v>
+        <v>0.2642609496788249</v>
       </c>
       <c r="AB2">
-        <v>31.41887591160275</v>
+        <v>24.68141158507205</v>
       </c>
       <c r="AC2">
-        <v>-4.999999999999995</v>
+        <v>-9</v>
       </c>
       <c r="AD2">
-        <v>0.8533791059987669</v>
+        <v>0.9086436979271377</v>
       </c>
       <c r="AE2">
-        <v>0.5212908031461377</v>
+        <v>0.4175723053763222</v>
       </c>
       <c r="AF2">
-        <v>0.9372684580136335</v>
+        <v>0.8657413474775171</v>
       </c>
       <c r="AG2">
-        <v>0.9370198817343581</v>
+        <v>0.8654128252267995</v>
       </c>
       <c r="AH2" t="s">
         <v>56</v>
@@ -868,34 +871,34 @@
         <v>69</v>
       </c>
       <c r="AJ2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AK2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AL2">
-        <v>0.6061814057679599</v>
+        <v>0.5741634121414886</v>
       </c>
       <c r="AM2">
-        <v>0.8338938525549414</v>
+        <v>0.8197247638198008</v>
       </c>
       <c r="AN2">
-        <v>0.7937627087613108</v>
+        <v>0.7777456834011567</v>
       </c>
       <c r="AO2">
-        <v>0.497538434729851</v>
+        <v>0.3781730039581188</v>
       </c>
       <c r="AP2">
-        <v>0.9930987930889017</v>
+        <v>0.8800205794973315</v>
       </c>
       <c r="AQ2">
-        <v>-1.779687287994747</v>
+        <v>-1.999957880853437</v>
       </c>
       <c r="AR2">
-        <v>0.8299194021373156</v>
+        <v>0.7022301505912301</v>
       </c>
       <c r="AS2">
-        <v>0.04156482246950464</v>
+        <v>0.03725147496076583</v>
       </c>
       <c r="AT2" t="b">
         <v>1</v>
@@ -906,10 +909,10 @@
         <v>47</v>
       </c>
       <c r="B3" s="2">
+        <v>46266</v>
+      </c>
+      <c r="C3" s="2">
         <v>46265</v>
-      </c>
-      <c r="C3" s="2">
-        <v>46262</v>
       </c>
       <c r="D3" t="s">
         <v>56</v>
@@ -921,13 +924,13 @@
         <v>1</v>
       </c>
       <c r="G3">
-        <v>2.780310782846937</v>
+        <v>2.357008280689713</v>
       </c>
       <c r="H3">
-        <v>1.880299178025882</v>
+        <v>1.888396249417202</v>
       </c>
       <c r="I3">
-        <v>0.4250181075804823</v>
+        <v>0.4266218809673987</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -939,67 +942,67 @@
         <v>225</v>
       </c>
       <c r="M3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N3">
-        <v>-0.06551246910444915</v>
+        <v>-0.07167742586342712</v>
       </c>
       <c r="O3">
-        <v>-22.99835926435024</v>
+        <v>-23.51180792146154</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>2.780310782846937</v>
+        <v>2.357008280689713</v>
       </c>
       <c r="R3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S3" t="s">
         <v>63</v>
       </c>
       <c r="T3">
-        <v>0.9703334336358443</v>
+        <v>0.9963132940739925</v>
       </c>
       <c r="U3">
-        <v>0.9864553205390064</v>
+        <v>0.9979759806877972</v>
       </c>
       <c r="V3" t="s">
         <v>56</v>
       </c>
       <c r="W3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="X3">
-        <v>0.9967654329550666</v>
+        <v>0.9917238475174125</v>
       </c>
       <c r="Y3">
-        <v>0.9992211016115058</v>
+        <v>0.9985399934180026</v>
       </c>
       <c r="Z3">
-        <v>0.002455668656439203</v>
+        <v>0.006816145900590098</v>
       </c>
       <c r="AA3">
         <v>1</v>
       </c>
       <c r="AB3">
-        <v>19.84005300651215</v>
+        <v>6.964628862871207</v>
       </c>
       <c r="AC3">
-        <v>-16</v>
+        <v>-27</v>
       </c>
       <c r="AD3">
-        <v>0.9406437420187334</v>
+        <v>0.9926211976629232</v>
       </c>
       <c r="AE3">
-        <v>0.3393955665606059</v>
+        <v>0.1212565789976934</v>
       </c>
       <c r="AF3">
-        <v>2.423199913035678</v>
+        <v>2.002263451485957</v>
       </c>
       <c r="AG3">
-        <v>2.421312486528415</v>
+        <v>1.999340133667894</v>
       </c>
       <c r="AH3" t="s">
         <v>56</v>
@@ -1008,34 +1011,34 @@
         <v>69</v>
       </c>
       <c r="AJ3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="AK3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="AL3">
-        <v>0.9399110761239278</v>
+        <v>0.9911719641809053</v>
       </c>
       <c r="AM3">
-        <v>0.9764628933496899</v>
+        <v>0.9924379518313606</v>
       </c>
       <c r="AN3">
-        <v>2.240061336783815</v>
+        <v>1.95138573431219</v>
       </c>
       <c r="AO3">
-        <v>0.9033816280602533</v>
+        <v>0.3675160926393132</v>
       </c>
       <c r="AP3">
-        <v>2.899004921740559</v>
+        <v>2.234160975303228</v>
       </c>
       <c r="AQ3">
-        <v>-5.257395196758583</v>
+        <v>-5.277364052359466</v>
       </c>
       <c r="AR3">
-        <v>2.416652610783764</v>
+        <v>1.772855811275774</v>
       </c>
       <c r="AS3">
-        <v>0.03638409879971379</v>
+        <v>0.03224936775878195</v>
       </c>
       <c r="AT3" t="b">
         <v>1</v>
@@ -1046,10 +1049,10 @@
         <v>48</v>
       </c>
       <c r="B4" s="2">
+        <v>46266</v>
+      </c>
+      <c r="C4" s="2">
         <v>46265</v>
-      </c>
-      <c r="C4" s="2">
-        <v>46262</v>
       </c>
       <c r="D4" t="s">
         <v>56</v>
@@ -1061,13 +1064,13 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>0.6559145524169097</v>
+        <v>0.4982468642130711</v>
       </c>
       <c r="H4">
-        <v>2.076454169534499</v>
+        <v>2.076907568412226</v>
       </c>
       <c r="I4">
-        <v>0.4950588986188687</v>
+        <v>0.4943330624677803</v>
       </c>
       <c r="J4">
         <v>6</v>
@@ -1079,67 +1082,67 @@
         <v>146</v>
       </c>
       <c r="M4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N4">
-        <v>-0.1798131877478552</v>
+        <v>-0.1968360124749769</v>
       </c>
       <c r="O4">
-        <v>-6.794560400728689</v>
+        <v>-7.242323717870397</v>
       </c>
       <c r="P4">
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>0.6559145524169097</v>
+        <v>0.4982468642130711</v>
       </c>
       <c r="R4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="S4" t="s">
         <v>64</v>
       </c>
       <c r="T4">
-        <v>0.9252464837641814</v>
+        <v>0.8527697797965434</v>
       </c>
       <c r="U4">
-        <v>0.8148710873515739</v>
+        <v>0.78304519093951</v>
       </c>
       <c r="V4" t="s">
         <v>56</v>
       </c>
       <c r="W4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="X4">
-        <v>0.911360855534196</v>
+        <v>0.9445701415459703</v>
       </c>
       <c r="Y4">
-        <v>0.9940406786307691</v>
+        <v>0.9971951601242616</v>
       </c>
       <c r="Z4">
-        <v>0.08267982309657307</v>
+        <v>0.05262501857829127</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>-38.7197629256312</v>
+        <v>-55.38723447248298</v>
       </c>
       <c r="AC4">
-        <v>-83</v>
+        <v>-67</v>
       </c>
       <c r="AD4">
-        <v>0.7802146971412918</v>
+        <v>0.568027126140579</v>
       </c>
       <c r="AE4">
-        <v>-0.6255118115309433</v>
+        <v>-0.8230098322428929</v>
       </c>
       <c r="AF4">
-        <v>0.8835830245188717</v>
+        <v>0.9261230567611998</v>
       </c>
       <c r="AG4">
-        <v>0.8783174693193667</v>
+        <v>0.9235254298817552</v>
       </c>
       <c r="AH4" t="s">
         <v>56</v>
@@ -1148,34 +1151,34 @@
         <v>69</v>
       </c>
       <c r="AJ4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AK4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AL4">
-        <v>0.3877825735120148</v>
+        <v>0.2832169505033394</v>
       </c>
       <c r="AM4">
-        <v>0.7238488767039348</v>
+        <v>0.6582138723089472</v>
       </c>
       <c r="AN4">
-        <v>0.6980538957778561</v>
+        <v>0.5729569618231657</v>
       </c>
       <c r="AO4">
-        <v>-0.4014588738808464</v>
+        <v>-0.6610406127368735</v>
       </c>
       <c r="AP4">
-        <v>-0.0584462836456533</v>
+        <v>-0.237629103424416</v>
       </c>
       <c r="AQ4">
-        <v>-3.762317656626231</v>
+        <v>-3.295696083902773</v>
       </c>
       <c r="AR4">
-        <v>0.6570452047627353</v>
+        <v>0.7004886741879799</v>
       </c>
       <c r="AS4">
-        <v>0.05419846639481267</v>
+        <v>0.07475047717812013</v>
       </c>
       <c r="AT4" t="b">
         <v>1</v>
@@ -1186,10 +1189,10 @@
         <v>49</v>
       </c>
       <c r="B5" s="2">
+        <v>46266</v>
+      </c>
+      <c r="C5" s="2">
         <v>46265</v>
-      </c>
-      <c r="C5" s="2">
-        <v>46262</v>
       </c>
       <c r="D5" t="s">
         <v>56</v>
@@ -1198,16 +1201,16 @@
         <v>1</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>0.6733171134152426</v>
       </c>
       <c r="G5">
-        <v>1.985211862947266</v>
+        <v>1.577163080923131</v>
       </c>
       <c r="H5">
-        <v>1.458296112700348</v>
+        <v>1.465502527619505</v>
       </c>
       <c r="I5">
-        <v>0.3187574056272627</v>
+        <v>0.3221278934991939</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -1219,67 +1222,67 @@
         <v>226</v>
       </c>
       <c r="M5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N5">
-        <v>-0.07793652217100289</v>
+        <v>-0.08341454003277697</v>
       </c>
       <c r="O5">
-        <v>-23.80000677051037</v>
+        <v>-23.58484419789727</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>1.985211862947266</v>
+        <v>1.577163080923131</v>
       </c>
       <c r="R5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="S5" t="s">
         <v>64</v>
       </c>
       <c r="T5">
-        <v>0.9318137970852972</v>
+        <v>0.8482807790637419</v>
       </c>
       <c r="U5">
-        <v>0.9685020822574847</v>
+        <v>0.8822403817970099</v>
       </c>
       <c r="V5" t="s">
         <v>56</v>
       </c>
       <c r="W5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="X5">
-        <v>0.9606397525010582</v>
+        <v>0.9719926297188407</v>
       </c>
       <c r="Y5">
-        <v>0.9967434942764036</v>
+        <v>0.9980658568241588</v>
       </c>
       <c r="Z5">
-        <v>0.03610374177534548</v>
+        <v>0.02607322710531812</v>
       </c>
       <c r="AA5">
         <v>1</v>
       </c>
       <c r="AB5">
-        <v>-30.29894732759313</v>
+        <v>-44.56889879536623</v>
       </c>
       <c r="AC5">
-        <v>-57</v>
+        <v>-49</v>
       </c>
       <c r="AD5">
-        <v>0.8634048199449916</v>
+        <v>0.7124070826847565</v>
       </c>
       <c r="AE5">
-        <v>-0.5045117609092542</v>
+        <v>-0.701766448713954</v>
       </c>
       <c r="AF5">
-        <v>2.023583436391713</v>
+        <v>1.933641576264389</v>
       </c>
       <c r="AG5">
-        <v>2.016993625348928</v>
+        <v>1.929901636605135</v>
       </c>
       <c r="AH5" t="s">
         <v>56</v>
@@ -1288,34 +1291,34 @@
         <v>69</v>
       </c>
       <c r="AJ5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AK5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AL5">
-        <v>0.8605931372070601</v>
+        <v>0.7110291853873608</v>
       </c>
       <c r="AM5">
-        <v>0.9525777900775656</v>
+        <v>0.9064883387998787</v>
       </c>
       <c r="AN5">
-        <v>1.777759279664566</v>
+        <v>1.451744440138403</v>
       </c>
       <c r="AO5">
-        <v>-0.7864184817169323</v>
+        <v>-1.19369313536322</v>
       </c>
       <c r="AP5">
-        <v>1.299479478083904</v>
+        <v>0.8528741753204199</v>
       </c>
       <c r="AQ5">
-        <v>-6.473876457646504</v>
+        <v>-5.464492559598415</v>
       </c>
       <c r="AR5">
-        <v>1.113264888823018</v>
+        <v>0.8401805960891837</v>
       </c>
       <c r="AS5">
-        <v>0.03535919268448668</v>
+        <v>0.04371223929335861</v>
       </c>
       <c r="AT5" t="b">
         <v>1</v>
@@ -1326,10 +1329,10 @@
         <v>50</v>
       </c>
       <c r="B6" s="2">
+        <v>46266</v>
+      </c>
+      <c r="C6" s="2">
         <v>46265</v>
-      </c>
-      <c r="C6" s="2">
-        <v>46262</v>
       </c>
       <c r="D6" t="s">
         <v>56</v>
@@ -1341,13 +1344,13 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0.4895064991989366</v>
+        <v>0.3381349937883492</v>
       </c>
       <c r="H6">
-        <v>0.9431982520721013</v>
+        <v>0.9432197444592968</v>
       </c>
       <c r="I6">
-        <v>0.2576135998378419</v>
+        <v>0.2575148963825653</v>
       </c>
       <c r="J6">
         <v>6</v>
@@ -1359,67 +1362,67 @@
         <v>158</v>
       </c>
       <c r="M6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N6">
-        <v>-0.3201884124755589</v>
+        <v>-0.341622074507047</v>
       </c>
       <c r="O6">
-        <v>-6.185764243942505</v>
+        <v>-6.354070736148071</v>
       </c>
       <c r="P6">
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>0.4895064991989366</v>
+        <v>0.3381349937883492</v>
       </c>
       <c r="R6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="S6" t="s">
         <v>64</v>
       </c>
       <c r="T6">
-        <v>0.9252729325247658</v>
+        <v>0.8276196807370453</v>
       </c>
       <c r="U6">
-        <v>0.815482632944722</v>
+        <v>0.7720022983650371</v>
       </c>
       <c r="V6" t="s">
         <v>56</v>
       </c>
       <c r="W6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="X6">
-        <v>0.9499318349226392</v>
+        <v>0.970496857109534</v>
       </c>
       <c r="Y6">
-        <v>0.9964392532343094</v>
+        <v>0.998293768133467</v>
       </c>
       <c r="Z6">
-        <v>0.04650741831167016</v>
+        <v>0.027796911023933</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>-38.68065654295471</v>
+        <v>-60.35637743724338</v>
       </c>
       <c r="AC6">
-        <v>-64</v>
+        <v>-48</v>
       </c>
       <c r="AD6">
-        <v>0.7806414491645082</v>
+        <v>0.4946037197137273</v>
       </c>
       <c r="AE6">
-        <v>-0.6249791419290219</v>
+        <v>-0.8691186112639314</v>
       </c>
       <c r="AF6">
-        <v>0.5761990817658589</v>
+        <v>0.6542321358757778</v>
       </c>
       <c r="AG6">
-        <v>0.5741473827490672</v>
+        <v>0.6531158641574366</v>
       </c>
       <c r="AH6" t="s">
         <v>56</v>
@@ -1428,34 +1431,34 @@
         <v>69</v>
       </c>
       <c r="AJ6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AK6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AL6">
-        <v>0.3889308913246158</v>
+        <v>0.246879905542923</v>
       </c>
       <c r="AM6">
-        <v>0.7266105836153767</v>
+        <v>0.6377217949702869</v>
       </c>
       <c r="AN6">
-        <v>0.4635374534382177</v>
+        <v>0.3510440421131827</v>
       </c>
       <c r="AO6">
-        <v>-0.2910754003251648</v>
+        <v>-0.5290599962268745</v>
       </c>
       <c r="AP6">
-        <v>0.2150259437815997</v>
+        <v>0.01365710079836685</v>
       </c>
       <c r="AQ6">
-        <v>-2.071350336448071</v>
+        <v>-1.847197037629132</v>
       </c>
       <c r="AR6">
-        <v>0.2712958284126735</v>
+        <v>0.2990371479138045</v>
       </c>
       <c r="AS6">
-        <v>0.04223726510655999</v>
+        <v>0.06708093193696447</v>
       </c>
       <c r="AT6" t="b">
         <v>1</v>
@@ -1466,10 +1469,10 @@
         <v>51</v>
       </c>
       <c r="B7" s="2">
+        <v>46266</v>
+      </c>
+      <c r="C7" s="2">
         <v>46265</v>
-      </c>
-      <c r="C7" s="2">
-        <v>46262</v>
       </c>
       <c r="D7" t="s">
         <v>56</v>
@@ -1478,16 +1481,16 @@
         <v>1</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>0.9249089002246725</v>
       </c>
       <c r="G7">
-        <v>2.065352552866162</v>
+        <v>1.709277318020987</v>
       </c>
       <c r="H7">
-        <v>1.410888817761677</v>
+        <v>1.419268226816636</v>
       </c>
       <c r="I7">
-        <v>0.3370633745033623</v>
+        <v>0.341260316094824</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -1499,67 +1502,67 @@
         <v>239</v>
       </c>
       <c r="M7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N7">
-        <v>-0.1189648280438466</v>
+        <v>-0.125630372110077</v>
       </c>
       <c r="O7">
-        <v>-29.65911481816141</v>
+        <v>-30.18665081165511</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>2.065352552866162</v>
+        <v>1.709277318020987</v>
       </c>
       <c r="R7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="S7" t="s">
         <v>64</v>
       </c>
       <c r="T7">
-        <v>0.9243705953802875</v>
+        <v>0.8368257802676098</v>
       </c>
       <c r="U7">
-        <v>0.9654357356096457</v>
+        <v>0.9149637481144606</v>
       </c>
       <c r="V7" t="s">
         <v>56</v>
       </c>
       <c r="W7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="X7">
-        <v>0.9751241142646272</v>
+        <v>0.9821595569213214</v>
       </c>
       <c r="Y7">
-        <v>0.9978758707540648</v>
+        <v>0.9986232478413414</v>
       </c>
       <c r="Z7">
-        <v>0.02275175648943761</v>
+        <v>0.01646369092001998</v>
       </c>
       <c r="AA7">
         <v>1</v>
       </c>
       <c r="AB7">
-        <v>-31.94242147592362</v>
+        <v>-47.35808427063051</v>
       </c>
       <c r="AC7">
-        <v>-46</v>
+        <v>-37.99999999999999</v>
       </c>
       <c r="AD7">
-        <v>0.8485802021697957</v>
+        <v>0.6774142932010584</v>
       </c>
       <c r="AE7">
-        <v>-0.5290667637316377</v>
+        <v>-0.735601709736261</v>
       </c>
       <c r="AF7">
-        <v>2.03672342464955</v>
+        <v>2.106817154537951</v>
       </c>
       <c r="AG7">
-        <v>2.032397160857371</v>
+        <v>2.103916589472542</v>
       </c>
       <c r="AH7" t="s">
         <v>56</v>
@@ -1568,34 +1571,34 @@
         <v>69</v>
       </c>
       <c r="AJ7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AK7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AL7">
-        <v>0.8467777081448452</v>
+        <v>0.6764816616105876</v>
       </c>
       <c r="AM7">
-        <v>0.9490899162399291</v>
+        <v>0.8970653254974047</v>
       </c>
       <c r="AN7">
-        <v>1.769749825094938</v>
+        <v>1.497553118102561</v>
       </c>
       <c r="AO7">
-        <v>-0.9013392448438455</v>
+        <v>-1.427953061874262</v>
       </c>
       <c r="AP7">
-        <v>1.711719197888291</v>
+        <v>1.26868837003566</v>
       </c>
       <c r="AQ7">
-        <v>-5.706922387981857</v>
+        <v>-5.021632800297462</v>
       </c>
       <c r="AR7">
-        <v>1.312622839986435</v>
+        <v>0.9836571668798069</v>
       </c>
       <c r="AS7">
-        <v>0.03160466116621462</v>
+        <v>0.03784732804921472</v>
       </c>
       <c r="AT7" t="b">
         <v>1</v>
@@ -1606,10 +1609,10 @@
         <v>52</v>
       </c>
       <c r="B8" s="2">
+        <v>46266</v>
+      </c>
+      <c r="C8" s="2">
         <v>46265</v>
-      </c>
-      <c r="C8" s="2">
-        <v>46262</v>
       </c>
       <c r="D8" t="s">
         <v>57</v>
@@ -1621,121 +1624,121 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>0.03129653978359413</v>
+        <v>0.1429648552517508</v>
       </c>
       <c r="H8">
-        <v>1.435563294450914</v>
+        <v>1.436029183644284</v>
       </c>
       <c r="I8">
-        <v>0.3542409547493119</v>
+        <v>0.3547096858897256</v>
       </c>
       <c r="J8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K8">
-        <v>0.8333333333333334</v>
+        <v>0.5</v>
       </c>
       <c r="L8">
         <v>112</v>
       </c>
       <c r="M8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N8">
-        <v>0.005338075962783961</v>
+        <v>0.005672731105796846</v>
       </c>
       <c r="O8">
-        <v>1.400938484937214</v>
+        <v>1.428770990036089</v>
       </c>
       <c r="P8">
-        <v>0.4026730539323848</v>
+        <v>0.2001075835396299</v>
       </c>
       <c r="Q8">
-        <v>0.05239432104918212</v>
+        <v>0.1787301045863007</v>
       </c>
       <c r="R8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S8" t="s">
         <v>65</v>
       </c>
       <c r="T8">
-        <v>-0.96686717777381</v>
+        <v>-0.6201778950448263</v>
       </c>
       <c r="U8">
-        <v>0.7697178953989755</v>
+        <v>0.601919395810813</v>
       </c>
       <c r="V8" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="W8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="X8">
-        <v>0.4904552472291694</v>
+        <v>0.9575211503436823</v>
       </c>
       <c r="Y8">
-        <v>0.8385106616030441</v>
+        <v>0.9913573721625646</v>
       </c>
       <c r="Z8">
-        <v>0.3480554143738747</v>
+        <v>0.03383622181888224</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>153.7376070546685</v>
+        <v>93.39166488928133</v>
       </c>
       <c r="AC8">
-        <v>-90</v>
+        <v>-49</v>
       </c>
       <c r="AD8">
-        <v>-0.8967770545270213</v>
+        <v>-0.05916115388461772</v>
       </c>
       <c r="AE8">
-        <v>0.4424826713825525</v>
+        <v>0.9982484449629965</v>
       </c>
       <c r="AF8">
-        <v>0.3724385986291912</v>
+        <v>0.5562541942820731</v>
       </c>
       <c r="AG8">
-        <v>0.3122937357430737</v>
+        <v>0.5514466962978807</v>
       </c>
       <c r="AH8" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="AI8" t="s">
         <v>70</v>
       </c>
       <c r="AJ8" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="AK8" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AL8">
-        <v>-0.3759785606509409</v>
+        <v>-0.02932492302457986</v>
       </c>
       <c r="AM8">
-        <v>0.6981555557858671</v>
+        <v>0.4872407800166885</v>
       </c>
       <c r="AN8">
-        <v>-0.165946552732431</v>
+        <v>-0.009317714290712358</v>
       </c>
       <c r="AO8">
-        <v>0.07634165572216554</v>
+        <v>0.5325436479730074</v>
       </c>
       <c r="AP8">
-        <v>0.4819514082908494</v>
+        <v>0.8537150535838751</v>
       </c>
       <c r="AQ8">
-        <v>2.135274964074843</v>
+        <v>2.033923594703019</v>
       </c>
       <c r="AR8">
-        <v>0.7150847495479273</v>
+        <v>1.006044530891176</v>
       </c>
       <c r="AS8">
-        <v>0.09570861422203129</v>
+        <v>0.1832176427039627</v>
       </c>
       <c r="AT8" t="b">
         <v>1</v>
@@ -1746,10 +1749,10 @@
         <v>53</v>
       </c>
       <c r="B9" s="2">
+        <v>46266</v>
+      </c>
+      <c r="C9" s="2">
         <v>46265</v>
-      </c>
-      <c r="C9" s="2">
-        <v>46262</v>
       </c>
       <c r="D9" t="s">
         <v>57</v>
@@ -1758,16 +1761,16 @@
         <v>-1</v>
       </c>
       <c r="F9">
-        <v>0.9977480549270116</v>
+        <v>0.613693052969797</v>
       </c>
       <c r="G9">
-        <v>3.596004773033763</v>
+        <v>3.130855031823335</v>
       </c>
       <c r="H9">
-        <v>2.98393561777218</v>
+        <v>2.990366067032187</v>
       </c>
       <c r="I9">
-        <v>0.6148383195101931</v>
+        <v>0.617843224020335</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -1779,103 +1782,103 @@
         <v>76</v>
       </c>
       <c r="M9">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N9">
-        <v>0.4667769843375754</v>
+        <v>0.485792468378674</v>
       </c>
       <c r="O9">
-        <v>68.08582809674994</v>
+        <v>63.0431456924495</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>3.596004773033763</v>
+        <v>3.130855031823335</v>
       </c>
       <c r="R9" t="s">
         <v>61</v>
       </c>
       <c r="S9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T9">
-        <v>-0.9941871490978429</v>
+        <v>-0.9807340999738899</v>
       </c>
       <c r="U9">
-        <v>0.996800010265797</v>
+        <v>0.933220768597572</v>
       </c>
       <c r="V9" t="s">
         <v>57</v>
       </c>
       <c r="W9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="X9">
-        <v>0.9913577622788545</v>
+        <v>0.9938529822882581</v>
       </c>
       <c r="Y9">
-        <v>0.9990143397308635</v>
+        <v>0.9993458626554078</v>
       </c>
       <c r="Z9">
-        <v>0.007656577452008984</v>
+        <v>0.005492880367149677</v>
       </c>
       <c r="AA9">
         <v>1</v>
       </c>
       <c r="AB9">
-        <v>171.2542612435548</v>
+        <v>164.5527329500758</v>
       </c>
       <c r="AC9">
-        <v>-27</v>
+        <v>-22.99999999999999</v>
       </c>
       <c r="AD9">
-        <v>-0.9883728215658543</v>
+        <v>-0.9638760015178054</v>
       </c>
       <c r="AE9">
-        <v>0.1520498786252458</v>
+        <v>0.2663513726227963</v>
       </c>
       <c r="AF9">
-        <v>2.847466757773598</v>
+        <v>2.515481932094923</v>
       </c>
       <c r="AG9">
-        <v>2.844660122922773</v>
+        <v>2.513836461423493</v>
       </c>
       <c r="AH9" t="s">
         <v>57</v>
       </c>
       <c r="AI9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AJ9" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AK9" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AL9">
-        <v>-0.9873986217445425</v>
+        <v>-0.9632454942296564</v>
       </c>
       <c r="AM9">
-        <v>0.9916044735582022</v>
+        <v>0.984330072905957</v>
       </c>
       <c r="AN9">
-        <v>-2.808762545035531</v>
+        <v>-2.436489841288945</v>
       </c>
       <c r="AO9">
-        <v>0.2817477522468126</v>
+        <v>0.5600119232561305</v>
       </c>
       <c r="AP9">
-        <v>-4.168811817399995</v>
+        <v>-3.658733271157453</v>
       </c>
       <c r="AQ9">
-        <v>5.846921502275215</v>
+        <v>4.67317868047154</v>
       </c>
       <c r="AR9">
-        <v>3.643133555044059</v>
+        <v>3.256155795327658</v>
       </c>
       <c r="AS9">
-        <v>0.03041594544904188</v>
+        <v>0.03069186319184907</v>
       </c>
       <c r="AT9" t="b">
         <v>1</v>
@@ -1886,10 +1889,10 @@
         <v>54</v>
       </c>
       <c r="B10" s="2">
+        <v>46266</v>
+      </c>
+      <c r="C10" s="2">
         <v>46265</v>
-      </c>
-      <c r="C10" s="2">
-        <v>46262</v>
       </c>
       <c r="D10" t="s">
         <v>57</v>
@@ -1901,13 +1904,13 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>0.8742685934430834</v>
+        <v>0.3914372693095814</v>
       </c>
       <c r="H10">
-        <v>2.043910740272992</v>
+        <v>2.044364635021106</v>
       </c>
       <c r="I10">
-        <v>0.4605955191246818</v>
+        <v>0.4597554514113256</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1919,103 +1922,103 @@
         <v>233</v>
       </c>
       <c r="M10">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N10">
-        <v>17.41888558021623</v>
+        <v>17.80406340439667</v>
       </c>
       <c r="O10">
-        <v>36.18434574123132</v>
+        <v>35.2206991184901</v>
       </c>
       <c r="P10">
-        <v>0.005220213602015803</v>
+        <v>0.3195878488697548</v>
       </c>
       <c r="Q10">
-        <v>0.8788564116373314</v>
+        <v>0.5752943545457819</v>
       </c>
       <c r="R10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S10" t="s">
         <v>65</v>
       </c>
       <c r="T10">
-        <v>-0.6712964160116982</v>
+        <v>-0.6025422823773516</v>
       </c>
       <c r="U10">
-        <v>0.7019307209075971</v>
+        <v>0.6710216148983386</v>
       </c>
       <c r="V10" t="s">
         <v>57</v>
       </c>
       <c r="W10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="X10">
-        <v>0.989208995562361</v>
+        <v>0.9911587078763782</v>
       </c>
       <c r="Y10">
-        <v>0.9993893348093316</v>
+        <v>0.9995103513141212</v>
       </c>
       <c r="Z10">
-        <v>0.01018033924697059</v>
+        <v>0.008351643437743084</v>
       </c>
       <c r="AA10">
-        <v>0.8536811385896879</v>
+        <v>0.8157668775973641</v>
       </c>
       <c r="AB10">
-        <v>115.2109289295812</v>
+        <v>107.3141642160327</v>
       </c>
       <c r="AC10">
-        <v>-30.99999999999999</v>
+        <v>-28</v>
       </c>
       <c r="AD10">
-        <v>-0.4259518757826853</v>
+        <v>-0.2976108935117098</v>
       </c>
       <c r="AE10">
-        <v>0.9047458203922314</v>
+        <v>0.9546872556304299</v>
       </c>
       <c r="AF10">
-        <v>1.902016816671712</v>
+        <v>1.876485355944348</v>
       </c>
       <c r="AG10">
-        <v>1.900855321209705</v>
+        <v>1.875566537355739</v>
       </c>
       <c r="AH10" t="s">
         <v>57</v>
       </c>
       <c r="AI10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AJ10" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AK10" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="AL10">
-        <v>-0.3945483948501372</v>
+        <v>-0.2700637003083318</v>
       </c>
       <c r="AM10">
-        <v>0.7873112823858313</v>
+        <v>0.7371073176647642</v>
       </c>
       <c r="AN10">
-        <v>-0.910357128493263</v>
+        <v>-0.6570053991199679</v>
       </c>
       <c r="AO10">
-        <v>1.646591202880866</v>
+        <v>1.739986372179963</v>
       </c>
       <c r="AP10">
-        <v>-0.01141619691061446</v>
+        <v>0.2679365437725663</v>
       </c>
       <c r="AQ10">
-        <v>3.950967184139676</v>
+        <v>3.202963338620034</v>
       </c>
       <c r="AR10">
-        <v>0.6168233305910883</v>
+        <v>0.6943018735228209</v>
       </c>
       <c r="AS10">
-        <v>0.07331183500118622</v>
+        <v>0.1010529924544266</v>
       </c>
       <c r="AT10" t="b">
         <v>1</v>
@@ -2026,10 +2029,10 @@
         <v>55</v>
       </c>
       <c r="B11" s="2">
+        <v>46266</v>
+      </c>
+      <c r="C11" s="2">
         <v>46265</v>
-      </c>
-      <c r="C11" s="2">
-        <v>46262</v>
       </c>
       <c r="D11" t="s">
         <v>56</v>
@@ -2038,16 +2041,16 @@
         <v>1</v>
       </c>
       <c r="F11">
-        <v>0.2540639152737681</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>2.322852469405903</v>
+        <v>1.658640382260779</v>
       </c>
       <c r="H11">
-        <v>2.624859300124137</v>
+        <v>2.596262039566437</v>
       </c>
       <c r="I11">
-        <v>0.6139945487349256</v>
+        <v>0.6103860231431462</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -2059,67 +2062,67 @@
         <v>212</v>
       </c>
       <c r="M11">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N11">
-        <v>-1427.349256983209</v>
+        <v>-1560.489095242467</v>
       </c>
       <c r="O11">
-        <v>-19.64528536870374</v>
+        <v>-19.99555854546284</v>
       </c>
       <c r="P11">
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>2.322852469405903</v>
+        <v>1.658640382260779</v>
       </c>
       <c r="R11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="S11" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="T11">
-        <v>0.9998966016244263</v>
+        <v>0.91368862002438</v>
       </c>
       <c r="U11">
-        <v>0.8870599242088987</v>
+        <v>0.810210554549776</v>
       </c>
       <c r="V11" t="s">
         <v>56</v>
       </c>
       <c r="W11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="X11">
-        <v>0.975987933793338</v>
+        <v>0.9476599975949288</v>
       </c>
       <c r="Y11">
-        <v>0.9959874647473664</v>
+        <v>0.9962027021552202</v>
       </c>
       <c r="Z11">
-        <v>0.0199995309540284</v>
+        <v>0.04854270456029142</v>
       </c>
       <c r="AA11">
-        <v>0.7105143746728754</v>
+        <v>0.455518198324221</v>
       </c>
       <c r="AB11">
-        <v>1.146720127689915</v>
+        <v>-34.59650768776844</v>
       </c>
       <c r="AC11">
-        <v>-46.99999999999999</v>
+        <v>-65</v>
       </c>
       <c r="AD11">
-        <v>0.9997997257501915</v>
+        <v>0.823170978414328</v>
       </c>
       <c r="AE11">
-        <v>0.02001270571016804</v>
+        <v>-0.5677935719047883</v>
       </c>
       <c r="AF11">
-        <v>2.076852186058759</v>
+        <v>1.839511489799635</v>
       </c>
       <c r="AG11">
-        <v>2.068518743447689</v>
+        <v>1.832526316783971</v>
       </c>
       <c r="AH11" t="s">
         <v>56</v>
@@ -2128,34 +2131,34 @@
         <v>69</v>
       </c>
       <c r="AJ11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AK11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AL11">
-        <v>0.8516548390216744</v>
+        <v>0.5967953218429034</v>
       </c>
       <c r="AM11">
-        <v>0.9357741059129674</v>
+        <v>0.8306557873808735</v>
       </c>
       <c r="AN11">
-        <v>2.007420384984957</v>
+        <v>1.543127140641979</v>
       </c>
       <c r="AO11">
-        <v>0.2809308777946071</v>
+        <v>-0.8109343561761674</v>
       </c>
       <c r="AP11">
-        <v>1.838264412003431</v>
+        <v>0.8401398349996683</v>
       </c>
       <c r="AQ11">
-        <v>-6.635317247010361</v>
+        <v>-6.406028587750404</v>
       </c>
       <c r="AR11">
-        <v>1.509129104110315</v>
+        <v>0.911840991057953</v>
       </c>
       <c r="AS11">
-        <v>0.03242866272162204</v>
+        <v>0.04046727708397353</v>
       </c>
       <c r="AT11" t="b">
         <v>1</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="77">
   <si>
     <t>Pair</t>
   </si>
@@ -190,73 +190,58 @@
     <t>DOWN</t>
   </si>
   <si>
+    <t>UP_STEADY</t>
+  </si>
+  <si>
+    <t>UP_DECELERATING</t>
+  </si>
+  <si>
     <t>UP_ACCELERATING</t>
   </si>
   <si>
-    <t>UP_STEADY</t>
-  </si>
-  <si>
-    <t>UP_DECELERATING</t>
-  </si>
-  <si>
     <t>DOWN_DECELERATING</t>
   </si>
   <si>
+    <t>多头稳态</t>
+  </si>
+  <si>
+    <t>多头减速</t>
+  </si>
+  <si>
     <t>多头加速</t>
   </si>
   <si>
-    <t>多头稳态</t>
-  </si>
-  <si>
-    <t>多头减速</t>
-  </si>
-  <si>
     <t>空头减速</t>
   </si>
   <si>
-    <t>NEUTRAL</t>
-  </si>
-  <si>
     <t>ALIGNED</t>
   </si>
   <si>
-    <t>TRANSITION</t>
-  </si>
-  <si>
     <t>上涨</t>
   </si>
   <si>
-    <t>转换</t>
-  </si>
-  <si>
     <t>下跌</t>
   </si>
   <si>
+    <t>UP_SLOPE</t>
+  </si>
+  <si>
+    <t>UP_CREST_FLATTENING</t>
+  </si>
+  <si>
     <t>UP_STEEPENING</t>
   </si>
   <si>
-    <t>UP_SLOPE</t>
-  </si>
-  <si>
-    <t>UP_CREST_FLATTENING</t>
-  </si>
-  <si>
-    <t>TRANSITION_ZONE</t>
-  </si>
-  <si>
     <t>DOWN_VALLEY_FLATTENING</t>
   </si>
   <si>
+    <t>上升坡延续</t>
+  </si>
+  <si>
+    <t>上升坡顶钝化</t>
+  </si>
+  <si>
     <t>上升陡坡形成</t>
-  </si>
-  <si>
-    <t>上升坡延续</t>
-  </si>
-  <si>
-    <t>上升坡顶钝化</t>
-  </si>
-  <si>
-    <t>地形转换区</t>
   </si>
   <si>
     <t>下降谷底收敛</t>
@@ -769,11 +754,11 @@
         <v>46</v>
       </c>
       <c r="B2" s="2">
+        <v>46267</v>
+      </c>
+      <c r="C2" s="2">
         <v>46266</v>
       </c>
-      <c r="C2" s="2">
-        <v>46265</v>
-      </c>
       <c r="D2" t="s">
         <v>56</v>
       </c>
@@ -781,16 +766,16 @@
         <v>1</v>
       </c>
       <c r="F2">
-        <v>0.2455061550918489</v>
+        <v>0.03664263525046552</v>
       </c>
       <c r="G2">
-        <v>0.9387777012599231</v>
+        <v>0.8312212830193545</v>
       </c>
       <c r="H2">
-        <v>1.070184795603349</v>
+        <v>1.070464443029705</v>
       </c>
       <c r="I2">
-        <v>0.2581734233903618</v>
+        <v>0.2581626819934897</v>
       </c>
       <c r="J2">
         <v>6</v>
@@ -802,19 +787,19 @@
         <v>149</v>
       </c>
       <c r="M2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N2">
-        <v>-0.2275907190055462</v>
+        <v>-0.2544460973324824</v>
       </c>
       <c r="O2">
-        <v>-6.345761020648159</v>
+        <v>-7.031811450393333</v>
       </c>
       <c r="P2">
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.9387777012599231</v>
+        <v>0.8312212830193545</v>
       </c>
       <c r="R2" t="s">
         <v>58</v>
@@ -823,82 +808,82 @@
         <v>62</v>
       </c>
       <c r="T2">
-        <v>0.962668202750775</v>
+        <v>0.9951932929486321</v>
       </c>
       <c r="U2">
-        <v>0.8699317471802042</v>
+        <v>0.852947854274856</v>
       </c>
       <c r="V2" t="s">
         <v>56</v>
       </c>
       <c r="W2" t="s">
+        <v>66</v>
+      </c>
+      <c r="X2">
+        <v>0.9930000993732632</v>
+      </c>
+      <c r="Y2">
+        <v>0.9984579086416064</v>
+      </c>
+      <c r="Z2">
+        <v>0.005457809268343272</v>
+      </c>
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>9.685834486095624</v>
+      </c>
+      <c r="AC2">
+        <v>-25</v>
+      </c>
+      <c r="AD2">
+        <v>0.9857450954106393</v>
+      </c>
+      <c r="AE2">
+        <v>0.1682456741609418</v>
+      </c>
+      <c r="AF2">
+        <v>0.7385557067263675</v>
+      </c>
+      <c r="AG2">
+        <v>0.7374167863533325</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI2" t="s">
         <v>67</v>
       </c>
-      <c r="X2">
-        <v>0.9989287828465166</v>
-      </c>
-      <c r="Y2">
-        <v>0.9996205307143123</v>
-      </c>
-      <c r="Z2">
-        <v>0.000691747867795689</v>
-      </c>
-      <c r="AA2">
-        <v>0.2642609496788249</v>
-      </c>
-      <c r="AB2">
-        <v>24.68141158507205</v>
-      </c>
-      <c r="AC2">
-        <v>-9</v>
-      </c>
-      <c r="AD2">
-        <v>0.9086436979271377</v>
-      </c>
-      <c r="AE2">
-        <v>0.4175723053763222</v>
-      </c>
-      <c r="AF2">
-        <v>0.8657413474775171</v>
-      </c>
-      <c r="AG2">
-        <v>0.8654128252267995</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>56</v>
-      </c>
-      <c r="AI2" t="s">
+      <c r="AJ2" t="s">
         <v>69</v>
       </c>
-      <c r="AJ2" t="s">
-        <v>72</v>
-      </c>
       <c r="AK2" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="AL2">
-        <v>0.5741634121414886</v>
+        <v>0.4921124932087139</v>
       </c>
       <c r="AM2">
-        <v>0.8197247638198008</v>
+        <v>0.7901023295729401</v>
       </c>
       <c r="AN2">
-        <v>0.7777456834011567</v>
+        <v>0.7134698830645207</v>
       </c>
       <c r="AO2">
-        <v>0.3781730039581188</v>
+        <v>0.1697515533455793</v>
       </c>
       <c r="AP2">
-        <v>0.8800205794973315</v>
+        <v>0.6730914030811401</v>
       </c>
       <c r="AQ2">
-        <v>-1.999957880853437</v>
+        <v>-2.166764662218398</v>
       </c>
       <c r="AR2">
-        <v>0.7022301505912301</v>
+        <v>0.5403099453966469</v>
       </c>
       <c r="AS2">
-        <v>0.03725147496076583</v>
+        <v>0.03387644716542595</v>
       </c>
       <c r="AT2" t="b">
         <v>1</v>
@@ -909,11 +894,11 @@
         <v>47</v>
       </c>
       <c r="B3" s="2">
+        <v>46267</v>
+      </c>
+      <c r="C3" s="2">
         <v>46266</v>
       </c>
-      <c r="C3" s="2">
-        <v>46265</v>
-      </c>
       <c r="D3" t="s">
         <v>56</v>
       </c>
@@ -921,16 +906,16 @@
         <v>1</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>0.7158954326081945</v>
       </c>
       <c r="G3">
-        <v>2.357008280689713</v>
+        <v>2.081674623598277</v>
       </c>
       <c r="H3">
-        <v>1.888396249417202</v>
+        <v>1.896778626505637</v>
       </c>
       <c r="I3">
-        <v>0.4266218809673987</v>
+        <v>0.4282072919721926</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -942,103 +927,103 @@
         <v>225</v>
       </c>
       <c r="M3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N3">
-        <v>-0.07167742586342712</v>
+        <v>-0.07746335392602528</v>
       </c>
       <c r="O3">
-        <v>-23.51180792146154</v>
+        <v>-24.027627228633</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>2.357008280689713</v>
+        <v>2.081674623598277</v>
       </c>
       <c r="R3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="S3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="T3">
-        <v>0.9963132940739925</v>
+        <v>0.9898330321665639</v>
       </c>
       <c r="U3">
-        <v>0.9979759806877972</v>
+        <v>0.9523022662502993</v>
       </c>
       <c r="V3" t="s">
         <v>56</v>
       </c>
       <c r="W3" t="s">
+        <v>66</v>
+      </c>
+      <c r="X3">
+        <v>0.9826967538231927</v>
+      </c>
+      <c r="Y3">
+        <v>0.9979723475364658</v>
+      </c>
+      <c r="Z3">
+        <v>0.01527559371327314</v>
+      </c>
+      <c r="AA3">
+        <v>0.7552851486783748</v>
+      </c>
+      <c r="AB3">
+        <v>-11.80851420014053</v>
+      </c>
+      <c r="AC3">
+        <v>-39</v>
+      </c>
+      <c r="AD3">
+        <v>0.9788369896718806</v>
+      </c>
+      <c r="AE3">
+        <v>-0.2046415100855414</v>
+      </c>
+      <c r="AF3">
+        <v>1.7874930413671</v>
+      </c>
+      <c r="AG3">
+        <v>1.783868626698222</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI3" t="s">
         <v>67</v>
       </c>
-      <c r="X3">
-        <v>0.9917238475174125</v>
-      </c>
-      <c r="Y3">
-        <v>0.9985399934180026</v>
-      </c>
-      <c r="Z3">
-        <v>0.006816145900590098</v>
-      </c>
-      <c r="AA3">
-        <v>1</v>
-      </c>
-      <c r="AB3">
-        <v>6.964628862871207</v>
-      </c>
-      <c r="AC3">
-        <v>-27</v>
-      </c>
-      <c r="AD3">
-        <v>0.9926211976629232</v>
-      </c>
-      <c r="AE3">
-        <v>0.1212565789976934</v>
-      </c>
-      <c r="AF3">
-        <v>2.002263451485957</v>
-      </c>
-      <c r="AG3">
-        <v>1.999340133667894</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>56</v>
-      </c>
-      <c r="AI3" t="s">
+      <c r="AJ3" t="s">
         <v>69</v>
       </c>
-      <c r="AJ3" t="s">
+      <c r="AK3" t="s">
         <v>73</v>
       </c>
-      <c r="AK3" t="s">
-        <v>78</v>
-      </c>
       <c r="AL3">
-        <v>0.9911719641809053</v>
+        <v>0.8573271220684781</v>
       </c>
       <c r="AM3">
-        <v>0.9924379518313606</v>
+        <v>0.9391655211154649</v>
       </c>
       <c r="AN3">
-        <v>1.95138573431219</v>
+        <v>1.74411969895434</v>
       </c>
       <c r="AO3">
-        <v>0.3675160926393132</v>
+        <v>-0.2087155696182473</v>
       </c>
       <c r="AP3">
-        <v>2.234160975303228</v>
+        <v>1.878970786235352</v>
       </c>
       <c r="AQ3">
-        <v>-5.277364052359466</v>
+        <v>-4.810729408825131</v>
       </c>
       <c r="AR3">
-        <v>1.772855811275774</v>
+        <v>1.478835874889411</v>
       </c>
       <c r="AS3">
-        <v>0.03224936775878195</v>
+        <v>0.03221951439691526</v>
       </c>
       <c r="AT3" t="b">
         <v>1</v>
@@ -1049,10 +1034,10 @@
         <v>48</v>
       </c>
       <c r="B4" s="2">
+        <v>46267</v>
+      </c>
+      <c r="C4" s="2">
         <v>46266</v>
-      </c>
-      <c r="C4" s="2">
-        <v>46265</v>
       </c>
       <c r="D4" t="s">
         <v>56</v>
@@ -1064,121 +1049,121 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>0.4982468642130711</v>
+        <v>0.1548758298373375</v>
       </c>
       <c r="H4">
-        <v>2.076907568412226</v>
+        <v>2.077317786444455</v>
       </c>
       <c r="I4">
-        <v>0.4943330624677803</v>
+        <v>0.4936721050111056</v>
       </c>
       <c r="J4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K4">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="L4">
         <v>146</v>
       </c>
       <c r="M4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N4">
-        <v>-0.1968360124749769</v>
+        <v>-0.2105537239034255</v>
       </c>
       <c r="O4">
-        <v>-7.242323717870397</v>
+        <v>-7.771558488394321</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>0.5095550171948624</v>
       </c>
       <c r="Q4">
-        <v>0.4982468642130711</v>
+        <v>0.3157863476378396</v>
       </c>
       <c r="R4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="S4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="T4">
-        <v>0.8527697797965434</v>
+        <v>0.7604757577322193</v>
       </c>
       <c r="U4">
-        <v>0.78304519093951</v>
+        <v>0.7168727981111971</v>
       </c>
       <c r="V4" t="s">
         <v>56</v>
       </c>
       <c r="W4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="X4">
-        <v>0.9445701415459703</v>
+        <v>0.9692786445408872</v>
       </c>
       <c r="Y4">
-        <v>0.9971951601242616</v>
+        <v>0.9986348285267936</v>
       </c>
       <c r="Z4">
-        <v>0.05262501857829127</v>
+        <v>0.02935618398590645</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>-55.38723447248298</v>
+        <v>-70.4259684600639</v>
       </c>
       <c r="AC4">
-        <v>-67</v>
+        <v>-50</v>
       </c>
       <c r="AD4">
-        <v>0.568027126140579</v>
+        <v>0.3350245617784124</v>
       </c>
       <c r="AE4">
-        <v>-0.8230098322428929</v>
+        <v>-0.9422093944581442</v>
       </c>
       <c r="AF4">
-        <v>0.9261230567611998</v>
+        <v>1.115307815442161</v>
       </c>
       <c r="AG4">
-        <v>0.9235254298817552</v>
+        <v>1.113785229028676</v>
       </c>
       <c r="AH4" t="s">
         <v>56</v>
       </c>
       <c r="AI4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="AJ4" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK4" t="s">
         <v>74</v>
       </c>
-      <c r="AK4" t="s">
-        <v>79</v>
-      </c>
       <c r="AL4">
-        <v>0.2832169505033394</v>
+        <v>0.1672835979019245</v>
       </c>
       <c r="AM4">
-        <v>0.6582138723089472</v>
+        <v>0.583630877243415</v>
       </c>
       <c r="AN4">
-        <v>0.5729569618231657</v>
+        <v>0.4378744951828293</v>
       </c>
       <c r="AO4">
-        <v>-0.6610406127368735</v>
+        <v>-0.9883937268693395</v>
       </c>
       <c r="AP4">
-        <v>-0.237629103424416</v>
+        <v>-0.4835141276740909</v>
       </c>
       <c r="AQ4">
-        <v>-3.295696083902773</v>
+        <v>-3.009890836088064</v>
       </c>
       <c r="AR4">
-        <v>0.7004886741879799</v>
+        <v>0.8282266851857534</v>
       </c>
       <c r="AS4">
-        <v>0.07475047717812013</v>
+        <v>0.1093245418299093</v>
       </c>
       <c r="AT4" t="b">
         <v>1</v>
@@ -1189,11 +1174,11 @@
         <v>49</v>
       </c>
       <c r="B5" s="2">
+        <v>46267</v>
+      </c>
+      <c r="C5" s="2">
         <v>46266</v>
       </c>
-      <c r="C5" s="2">
-        <v>46265</v>
-      </c>
       <c r="D5" t="s">
         <v>56</v>
       </c>
@@ -1201,16 +1186,16 @@
         <v>1</v>
       </c>
       <c r="F5">
-        <v>0.6733171134152426</v>
+        <v>0.1980425254034911</v>
       </c>
       <c r="G5">
-        <v>1.577163080923131</v>
+        <v>1.275627528407026</v>
       </c>
       <c r="H5">
-        <v>1.465502527619505</v>
+        <v>1.472022617308266</v>
       </c>
       <c r="I5">
-        <v>0.3221278934991939</v>
+        <v>0.3252032246654484</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -1222,103 +1207,103 @@
         <v>226</v>
       </c>
       <c r="M5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N5">
-        <v>-0.08341454003277697</v>
+        <v>-0.08818406830950198</v>
       </c>
       <c r="O5">
-        <v>-23.58484419789727</v>
+        <v>-24.32903648306311</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>1.577163080923131</v>
+        <v>1.275627528407026</v>
       </c>
       <c r="R5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="S5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="T5">
-        <v>0.8482807790637419</v>
+        <v>0.73544020757439</v>
       </c>
       <c r="U5">
-        <v>0.8822403817970099</v>
+        <v>0.7603640563596267</v>
       </c>
       <c r="V5" t="s">
         <v>56</v>
       </c>
       <c r="W5" t="s">
+        <v>66</v>
+      </c>
+      <c r="X5">
+        <v>0.9818420376115305</v>
+      </c>
+      <c r="Y5">
+        <v>0.99883833656251</v>
+      </c>
+      <c r="Z5">
+        <v>0.01699629895097943</v>
+      </c>
+      <c r="AA5">
+        <v>1</v>
+      </c>
+      <c r="AB5">
+        <v>-57.34312559698115</v>
+      </c>
+      <c r="AC5">
+        <v>-39</v>
+      </c>
+      <c r="AD5">
+        <v>0.5396067760909485</v>
+      </c>
+      <c r="AE5">
+        <v>-0.8419171735965082</v>
+      </c>
+      <c r="AF5">
+        <v>2.079029838419099</v>
+      </c>
+      <c r="AG5">
+        <v>2.076614705470357</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI5" t="s">
         <v>67</v>
       </c>
-      <c r="X5">
-        <v>0.9719926297188407</v>
-      </c>
-      <c r="Y5">
-        <v>0.9980658568241588</v>
-      </c>
-      <c r="Z5">
-        <v>0.02607322710531812</v>
-      </c>
-      <c r="AA5">
-        <v>1</v>
-      </c>
-      <c r="AB5">
-        <v>-44.56889879536623</v>
-      </c>
-      <c r="AC5">
-        <v>-49</v>
-      </c>
-      <c r="AD5">
-        <v>0.7124070826847565</v>
-      </c>
-      <c r="AE5">
-        <v>-0.701766448713954</v>
-      </c>
-      <c r="AF5">
-        <v>1.933641576264389</v>
-      </c>
-      <c r="AG5">
-        <v>1.929901636605135</v>
-      </c>
-      <c r="AH5" t="s">
-        <v>56</v>
-      </c>
-      <c r="AI5" t="s">
-        <v>69</v>
-      </c>
       <c r="AJ5" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK5" t="s">
         <v>74</v>
       </c>
-      <c r="AK5" t="s">
-        <v>79</v>
-      </c>
       <c r="AL5">
-        <v>0.7110291853873608</v>
+        <v>0.5389799346285418</v>
       </c>
       <c r="AM5">
-        <v>0.9064883387998787</v>
+        <v>0.8532150844212933</v>
       </c>
       <c r="AN5">
-        <v>1.451744440138403</v>
+        <v>1.215167322787437</v>
       </c>
       <c r="AO5">
-        <v>-1.19369313536322</v>
+        <v>-1.640179226747929</v>
       </c>
       <c r="AP5">
-        <v>0.8528741753204199</v>
+        <v>0.5036293875768525</v>
       </c>
       <c r="AQ5">
-        <v>-5.464492559598415</v>
+        <v>-4.781891157326882</v>
       </c>
       <c r="AR5">
-        <v>0.8401805960891837</v>
+        <v>0.6431416081451213</v>
       </c>
       <c r="AS5">
-        <v>0.04371223929335861</v>
+        <v>0.05506910801913067</v>
       </c>
       <c r="AT5" t="b">
         <v>1</v>
@@ -1329,10 +1314,10 @@
         <v>50</v>
       </c>
       <c r="B6" s="2">
+        <v>46267</v>
+      </c>
+      <c r="C6" s="2">
         <v>46266</v>
-      </c>
-      <c r="C6" s="2">
-        <v>46265</v>
       </c>
       <c r="D6" t="s">
         <v>56</v>
@@ -1344,121 +1329,121 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0.3381349937883492</v>
+        <v>0.1374119100697148</v>
       </c>
       <c r="H6">
-        <v>0.9432197444592968</v>
+        <v>0.9432391899524737</v>
       </c>
       <c r="I6">
-        <v>0.2575148963825653</v>
+        <v>0.2574035808191225</v>
       </c>
       <c r="J6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="L6">
         <v>158</v>
       </c>
       <c r="M6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N6">
-        <v>-0.341622074507047</v>
+        <v>-0.3575195131343776</v>
       </c>
       <c r="O6">
-        <v>-6.354070736148071</v>
+        <v>-6.637677117351549</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>0.2627987542719751</v>
       </c>
       <c r="Q6">
-        <v>0.3381349937883492</v>
+        <v>0.1863967415491998</v>
       </c>
       <c r="R6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="S6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="T6">
-        <v>0.8276196807370453</v>
+        <v>0.6248165648010945</v>
       </c>
       <c r="U6">
-        <v>0.7720022983650371</v>
+        <v>0.6559895011842651</v>
       </c>
       <c r="V6" t="s">
         <v>56</v>
       </c>
       <c r="W6" t="s">
+        <v>66</v>
+      </c>
+      <c r="X6">
+        <v>0.9870036233670173</v>
+      </c>
+      <c r="Y6">
+        <v>0.9992881880950903</v>
+      </c>
+      <c r="Z6">
+        <v>0.01228456472807304</v>
+      </c>
+      <c r="AA6">
+        <v>0.3930108121593393</v>
+      </c>
+      <c r="AB6">
+        <v>-76.12344219304276</v>
+      </c>
+      <c r="AC6">
+        <v>-31.99999999999999</v>
+      </c>
+      <c r="AD6">
+        <v>0.2398308600887976</v>
+      </c>
+      <c r="AE6">
+        <v>-0.9708146880579566</v>
+      </c>
+      <c r="AF6">
+        <v>0.8645234585851871</v>
+      </c>
+      <c r="AG6">
+        <v>0.8639080804952924</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI6" t="s">
         <v>67</v>
       </c>
-      <c r="X6">
-        <v>0.970496857109534</v>
-      </c>
-      <c r="Y6">
-        <v>0.998293768133467</v>
-      </c>
-      <c r="Z6">
-        <v>0.027796911023933</v>
-      </c>
-      <c r="AA6">
-        <v>0</v>
-      </c>
-      <c r="AB6">
-        <v>-60.35637743724338</v>
-      </c>
-      <c r="AC6">
-        <v>-48</v>
-      </c>
-      <c r="AD6">
-        <v>0.4946037197137273</v>
-      </c>
-      <c r="AE6">
-        <v>-0.8691186112639314</v>
-      </c>
-      <c r="AF6">
-        <v>0.6542321358757778</v>
-      </c>
-      <c r="AG6">
-        <v>0.6531158641574366</v>
-      </c>
-      <c r="AH6" t="s">
-        <v>56</v>
-      </c>
-      <c r="AI6" t="s">
-        <v>69</v>
-      </c>
       <c r="AJ6" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK6" t="s">
         <v>74</v>
       </c>
-      <c r="AK6" t="s">
-        <v>79</v>
-      </c>
       <c r="AL6">
-        <v>0.246879905542923</v>
+        <v>0.1669245870513401</v>
       </c>
       <c r="AM6">
-        <v>0.6377217949702869</v>
+        <v>0.6325858123246292</v>
       </c>
       <c r="AN6">
-        <v>0.3510440421131827</v>
+        <v>0.2398947459342808</v>
       </c>
       <c r="AO6">
-        <v>-0.5290599962268745</v>
+        <v>-0.8188715142173091</v>
       </c>
       <c r="AP6">
-        <v>0.01365710079836685</v>
+        <v>-0.1948822532947811</v>
       </c>
       <c r="AQ6">
-        <v>-1.847197037629132</v>
+        <v>-1.659886776115244</v>
       </c>
       <c r="AR6">
-        <v>0.2990371479138045</v>
+        <v>0.4050154083840715</v>
       </c>
       <c r="AS6">
-        <v>0.06708093193696447</v>
+        <v>0.1181098264477304</v>
       </c>
       <c r="AT6" t="b">
         <v>1</v>
@@ -1469,11 +1454,11 @@
         <v>51</v>
       </c>
       <c r="B7" s="2">
+        <v>46267</v>
+      </c>
+      <c r="C7" s="2">
         <v>46266</v>
       </c>
-      <c r="C7" s="2">
-        <v>46265</v>
-      </c>
       <c r="D7" t="s">
         <v>56</v>
       </c>
@@ -1481,16 +1466,16 @@
         <v>1</v>
       </c>
       <c r="F7">
-        <v>0.9249089002246725</v>
+        <v>0.1478072069554337</v>
       </c>
       <c r="G7">
-        <v>1.709277318020987</v>
+        <v>1.183791461618007</v>
       </c>
       <c r="H7">
-        <v>1.419268226816636</v>
+        <v>1.426849596913979</v>
       </c>
       <c r="I7">
-        <v>0.341260316094824</v>
+        <v>0.3450640389242944</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -1502,103 +1487,103 @@
         <v>239</v>
       </c>
       <c r="M7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N7">
-        <v>-0.125630372110077</v>
+        <v>-0.1312072082391334</v>
       </c>
       <c r="O7">
-        <v>-30.18665081165511</v>
+        <v>-29.50844843932332</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>1.709277318020987</v>
+        <v>1.183791461618007</v>
       </c>
       <c r="R7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="S7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="T7">
-        <v>0.8368257802676098</v>
+        <v>0.67988918989935</v>
       </c>
       <c r="U7">
-        <v>0.9149637481144606</v>
+        <v>0.7279088527254214</v>
       </c>
       <c r="V7" t="s">
         <v>56</v>
       </c>
       <c r="W7" t="s">
+        <v>66</v>
+      </c>
+      <c r="X7">
+        <v>0.9882511727317382</v>
+      </c>
+      <c r="Y7">
+        <v>0.9991505449095957</v>
+      </c>
+      <c r="Z7">
+        <v>0.01089937217785741</v>
+      </c>
+      <c r="AA7">
+        <v>1</v>
+      </c>
+      <c r="AB7">
+        <v>-63.36915774106748</v>
+      </c>
+      <c r="AC7">
+        <v>-30.99999999999999</v>
+      </c>
+      <c r="AD7">
+        <v>0.4482403452450372</v>
+      </c>
+      <c r="AE7">
+        <v>-0.893913079048858</v>
+      </c>
+      <c r="AF7">
+        <v>2.279016647207451</v>
+      </c>
+      <c r="AG7">
+        <v>2.277080724915364</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI7" t="s">
         <v>67</v>
       </c>
-      <c r="X7">
-        <v>0.9821595569213214</v>
-      </c>
-      <c r="Y7">
-        <v>0.9986232478413414</v>
-      </c>
-      <c r="Z7">
-        <v>0.01646369092001998</v>
-      </c>
-      <c r="AA7">
-        <v>1</v>
-      </c>
-      <c r="AB7">
-        <v>-47.35808427063051</v>
-      </c>
-      <c r="AC7">
-        <v>-37.99999999999999</v>
-      </c>
-      <c r="AD7">
-        <v>0.6774142932010584</v>
-      </c>
-      <c r="AE7">
-        <v>-0.735601709736261</v>
-      </c>
-      <c r="AF7">
-        <v>2.106817154537951</v>
-      </c>
-      <c r="AG7">
-        <v>2.103916589472542</v>
-      </c>
-      <c r="AH7" t="s">
-        <v>56</v>
-      </c>
-      <c r="AI7" t="s">
-        <v>69</v>
-      </c>
       <c r="AJ7" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK7" t="s">
         <v>74</v>
       </c>
-      <c r="AK7" t="s">
-        <v>79</v>
-      </c>
       <c r="AL7">
-        <v>0.6764816616105876</v>
+        <v>0.4478595852020442</v>
       </c>
       <c r="AM7">
-        <v>0.8970653254974047</v>
+        <v>0.8257786813782142</v>
       </c>
       <c r="AN7">
-        <v>1.497553118102561</v>
+        <v>1.10677074999734</v>
       </c>
       <c r="AO7">
-        <v>-1.427953061874262</v>
+        <v>-1.961542113419563</v>
       </c>
       <c r="AP7">
-        <v>1.26868837003566</v>
+        <v>0.5773795043339081</v>
       </c>
       <c r="AQ7">
-        <v>-5.021632800297462</v>
+        <v>-4.452091786721666</v>
       </c>
       <c r="AR7">
-        <v>0.9836571668798069</v>
+        <v>0.6579648247921243</v>
       </c>
       <c r="AS7">
-        <v>0.03784732804921472</v>
+        <v>0.05597408609103618</v>
       </c>
       <c r="AT7" t="b">
         <v>1</v>
@@ -1609,136 +1594,136 @@
         <v>52</v>
       </c>
       <c r="B8" s="2">
+        <v>46267</v>
+      </c>
+      <c r="C8" s="2">
         <v>46266</v>
       </c>
-      <c r="C8" s="2">
-        <v>46265</v>
-      </c>
       <c r="D8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E8">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="F8">
         <v>0</v>
       </c>
       <c r="G8">
-        <v>0.1429648552517508</v>
+        <v>0.4967688813717854</v>
       </c>
       <c r="H8">
-        <v>1.436029183644284</v>
+        <v>1.436450702438285</v>
       </c>
       <c r="I8">
-        <v>0.3547096858897256</v>
+        <v>0.3551488100669746</v>
       </c>
       <c r="J8">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K8">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L8">
         <v>112</v>
       </c>
       <c r="M8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N8">
-        <v>0.005672731105796846</v>
+        <v>0.005249229949467661</v>
       </c>
       <c r="O8">
-        <v>1.428770990036089</v>
+        <v>1.255153190308239</v>
       </c>
       <c r="P8">
-        <v>0.2001075835396299</v>
+        <v>0</v>
       </c>
       <c r="Q8">
-        <v>0.1787301045863007</v>
+        <v>0.4967688813717854</v>
       </c>
       <c r="R8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="S8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T8">
-        <v>-0.6201778950448263</v>
+        <v>0.7324350881533757</v>
       </c>
       <c r="U8">
-        <v>0.601919395810813</v>
+        <v>0.7295077626680786</v>
       </c>
       <c r="V8" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="W8" t="s">
         <v>66</v>
       </c>
       <c r="X8">
-        <v>0.9575211503436823</v>
+        <v>0.9943729754813324</v>
       </c>
       <c r="Y8">
-        <v>0.9913573721625646</v>
+        <v>0.999647891996238</v>
       </c>
       <c r="Z8">
-        <v>0.03383622181888224</v>
+        <v>0.005274916514905637</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>93.39166488928133</v>
+        <v>77.51199110577859</v>
       </c>
       <c r="AC8">
-        <v>-49</v>
+        <v>-20</v>
       </c>
       <c r="AD8">
-        <v>-0.05916115388461772</v>
+        <v>0.2162352857957925</v>
       </c>
       <c r="AE8">
-        <v>0.9982484449629965</v>
+        <v>0.9763412831468369</v>
       </c>
       <c r="AF8">
-        <v>0.5562541942820731</v>
+        <v>1.021287877484621</v>
       </c>
       <c r="AG8">
-        <v>0.5514466962978807</v>
+        <v>1.020928273848814</v>
       </c>
       <c r="AH8" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="AI8" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="AJ8" t="s">
+        <v>71</v>
+      </c>
+      <c r="AK8" t="s">
         <v>75</v>
       </c>
-      <c r="AK8" t="s">
-        <v>80</v>
-      </c>
       <c r="AL8">
-        <v>-0.02932492302457986</v>
+        <v>0.108079573810484</v>
       </c>
       <c r="AM8">
-        <v>0.4872407800166885</v>
+        <v>0.5418974456834689</v>
       </c>
       <c r="AN8">
-        <v>-0.009317714290712358</v>
+        <v>0.211374167823509</v>
       </c>
       <c r="AO8">
-        <v>0.5325436479730074</v>
+        <v>0.9932998625844931</v>
       </c>
       <c r="AP8">
-        <v>0.8537150535838751</v>
+        <v>1.340440313245824</v>
       </c>
       <c r="AQ8">
-        <v>2.033923594703019</v>
+        <v>1.901223347815873</v>
       </c>
       <c r="AR8">
-        <v>1.006044530891176</v>
+        <v>1.461326171464674</v>
       </c>
       <c r="AS8">
-        <v>0.1832176427039627</v>
+        <v>0.1523326816930144</v>
       </c>
       <c r="AT8" t="b">
         <v>1</v>
@@ -1749,10 +1734,10 @@
         <v>53</v>
       </c>
       <c r="B9" s="2">
+        <v>46267</v>
+      </c>
+      <c r="C9" s="2">
         <v>46266</v>
-      </c>
-      <c r="C9" s="2">
-        <v>46265</v>
       </c>
       <c r="D9" t="s">
         <v>57</v>
@@ -1761,16 +1746,16 @@
         <v>-1</v>
       </c>
       <c r="F9">
-        <v>0.613693052969797</v>
+        <v>0.5718920027090993</v>
       </c>
       <c r="G9">
-        <v>3.130855031823335</v>
+        <v>3.085912441598675</v>
       </c>
       <c r="H9">
-        <v>2.990366067032187</v>
+        <v>2.996660631167433</v>
       </c>
       <c r="I9">
-        <v>0.617843224020335</v>
+        <v>0.6207353187279173</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -1782,19 +1767,19 @@
         <v>76</v>
       </c>
       <c r="M9">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N9">
-        <v>0.485792468378674</v>
+        <v>0.5044492443705563</v>
       </c>
       <c r="O9">
-        <v>63.0431456924495</v>
+        <v>64.93462137907112</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>3.130855031823335</v>
+        <v>3.085912441598675</v>
       </c>
       <c r="R9" t="s">
         <v>61</v>
@@ -1803,82 +1788,82 @@
         <v>65</v>
       </c>
       <c r="T9">
-        <v>-0.9807340999738899</v>
+        <v>-0.9739263676089753</v>
       </c>
       <c r="U9">
-        <v>0.933220768597572</v>
+        <v>0.9239505181732065</v>
       </c>
       <c r="V9" t="s">
         <v>57</v>
       </c>
       <c r="W9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="X9">
-        <v>0.9938529822882581</v>
+        <v>0.996933682565361</v>
       </c>
       <c r="Y9">
-        <v>0.9993458626554078</v>
+        <v>0.9995994093712112</v>
       </c>
       <c r="Z9">
-        <v>0.005492880367149677</v>
+        <v>0.002665726805850199</v>
       </c>
       <c r="AA9">
         <v>1</v>
       </c>
       <c r="AB9">
-        <v>164.5527329500758</v>
+        <v>162.0771026016102</v>
       </c>
       <c r="AC9">
-        <v>-22.99999999999999</v>
+        <v>-16</v>
       </c>
       <c r="AD9">
-        <v>-0.9638760015178054</v>
+        <v>-0.9514714974345199</v>
       </c>
       <c r="AE9">
-        <v>0.2663513726227963</v>
+        <v>0.3077368836680329</v>
       </c>
       <c r="AF9">
-        <v>2.515481932094923</v>
+        <v>2.492435818576734</v>
       </c>
       <c r="AG9">
-        <v>2.513836461423493</v>
+        <v>2.491437372144954</v>
       </c>
       <c r="AH9" t="s">
         <v>57</v>
       </c>
       <c r="AI9" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AJ9" t="s">
+        <v>72</v>
+      </c>
+      <c r="AK9" t="s">
         <v>76</v>
       </c>
-      <c r="AK9" t="s">
-        <v>81</v>
-      </c>
       <c r="AL9">
-        <v>-0.9632454942296564</v>
+        <v>-0.9510903468690879</v>
       </c>
       <c r="AM9">
-        <v>0.984330072905957</v>
+        <v>0.9805607637144046</v>
       </c>
       <c r="AN9">
-        <v>-2.436489841288945</v>
+        <v>-2.38636634511265</v>
       </c>
       <c r="AO9">
-        <v>0.5600119232561305</v>
+        <v>0.692425453716444</v>
       </c>
       <c r="AP9">
-        <v>-3.658733271157453</v>
+        <v>-3.663836892110755</v>
       </c>
       <c r="AQ9">
-        <v>4.67317868047154</v>
+        <v>4.166204129562628</v>
       </c>
       <c r="AR9">
-        <v>3.256155795327658</v>
+        <v>3.314172727289706</v>
       </c>
       <c r="AS9">
-        <v>0.03069186319184907</v>
+        <v>0.03160319197250212</v>
       </c>
       <c r="AT9" t="b">
         <v>1</v>
@@ -1889,10 +1874,10 @@
         <v>54</v>
       </c>
       <c r="B10" s="2">
+        <v>46267</v>
+      </c>
+      <c r="C10" s="2">
         <v>46266</v>
-      </c>
-      <c r="C10" s="2">
-        <v>46265</v>
       </c>
       <c r="D10" t="s">
         <v>57</v>
@@ -1904,13 +1889,13 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>0.3914372693095814</v>
+        <v>0.5475949992913479</v>
       </c>
       <c r="H10">
-        <v>2.044364635021106</v>
+        <v>2.044775301697971</v>
       </c>
       <c r="I10">
-        <v>0.4597554514113256</v>
+        <v>0.4588968231056106</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1922,19 +1907,19 @@
         <v>233</v>
       </c>
       <c r="M10">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N10">
-        <v>17.80406340439667</v>
+        <v>18.12835099241988</v>
       </c>
       <c r="O10">
-        <v>35.2206991184901</v>
+        <v>32.21999668577872</v>
       </c>
       <c r="P10">
-        <v>0.3195878488697548</v>
+        <v>0</v>
       </c>
       <c r="Q10">
-        <v>0.5752943545457819</v>
+        <v>0.5475949992913479</v>
       </c>
       <c r="R10" t="s">
         <v>61</v>
@@ -1943,82 +1928,82 @@
         <v>65</v>
       </c>
       <c r="T10">
-        <v>-0.6025422823773516</v>
+        <v>-0.6638504049446032</v>
       </c>
       <c r="U10">
-        <v>0.6710216148983386</v>
+        <v>0.698655475988894</v>
       </c>
       <c r="V10" t="s">
         <v>57</v>
       </c>
       <c r="W10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="X10">
-        <v>0.9911587078763782</v>
+        <v>0.9957317554008226</v>
       </c>
       <c r="Y10">
-        <v>0.9995103513141212</v>
+        <v>0.99969117505529</v>
       </c>
       <c r="Z10">
-        <v>0.008351643437743084</v>
+        <v>0.003959419654467444</v>
       </c>
       <c r="AA10">
-        <v>0.8157668775973641</v>
+        <v>0.4447421088578876</v>
       </c>
       <c r="AB10">
-        <v>107.3141642160327</v>
+        <v>107.9808371594463</v>
       </c>
       <c r="AC10">
-        <v>-28</v>
+        <v>-20</v>
       </c>
       <c r="AD10">
-        <v>-0.2976108935117098</v>
+        <v>-0.3086988918121568</v>
       </c>
       <c r="AE10">
-        <v>0.9546872556304299</v>
+        <v>0.9511598152749864</v>
       </c>
       <c r="AF10">
-        <v>1.876485355944348</v>
+        <v>1.604591491765379</v>
       </c>
       <c r="AG10">
-        <v>1.875566537355739</v>
+        <v>1.604095953886653</v>
       </c>
       <c r="AH10" t="s">
         <v>57</v>
       </c>
       <c r="AI10" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AJ10" t="s">
+        <v>72</v>
+      </c>
+      <c r="AK10" t="s">
         <v>76</v>
       </c>
-      <c r="AK10" t="s">
-        <v>81</v>
-      </c>
       <c r="AL10">
-        <v>-0.2700637003083318</v>
+        <v>-0.2229262775163841</v>
       </c>
       <c r="AM10">
-        <v>0.7371073176647642</v>
+        <v>0.6683567585864898</v>
       </c>
       <c r="AN10">
-        <v>-0.6570053991199679</v>
+        <v>-0.5624508385271039</v>
       </c>
       <c r="AO10">
-        <v>1.739986372179963</v>
+        <v>1.495470092840533</v>
       </c>
       <c r="AP10">
-        <v>0.2679365437725663</v>
+        <v>-0.009403424691524442</v>
       </c>
       <c r="AQ10">
-        <v>3.202963338620034</v>
+        <v>1.90094011641255</v>
       </c>
       <c r="AR10">
-        <v>0.6943018735228209</v>
+        <v>0.282263743606916</v>
       </c>
       <c r="AS10">
-        <v>0.1010529924544266</v>
+        <v>0.08728827998724183</v>
       </c>
       <c r="AT10" t="b">
         <v>1</v>
@@ -2029,10 +2014,10 @@
         <v>55</v>
       </c>
       <c r="B11" s="2">
+        <v>46267</v>
+      </c>
+      <c r="C11" s="2">
         <v>46266</v>
-      </c>
-      <c r="C11" s="2">
-        <v>46265</v>
       </c>
       <c r="D11" t="s">
         <v>56</v>
@@ -2044,13 +2029,13 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>1.658640382260779</v>
+        <v>1.158556464871536</v>
       </c>
       <c r="H11">
-        <v>2.596262039566437</v>
+        <v>2.569154114874816</v>
       </c>
       <c r="I11">
-        <v>0.6103860231431462</v>
+        <v>0.6065146064261379</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -2062,103 +2047,103 @@
         <v>212</v>
       </c>
       <c r="M11">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N11">
-        <v>-1560.489095242467</v>
+        <v>-1668.683112213251</v>
       </c>
       <c r="O11">
-        <v>-19.99555854546284</v>
+        <v>-20.33748172577187</v>
       </c>
       <c r="P11">
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>1.658640382260779</v>
+        <v>1.158556464871536</v>
       </c>
       <c r="R11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="S11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="T11">
-        <v>0.91368862002438</v>
+        <v>0.7444548970353234</v>
       </c>
       <c r="U11">
-        <v>0.810210554549776</v>
+        <v>0.734529101741221</v>
       </c>
       <c r="V11" t="s">
         <v>56</v>
       </c>
       <c r="W11" t="s">
+        <v>66</v>
+      </c>
+      <c r="X11">
+        <v>0.9682094888358406</v>
+      </c>
+      <c r="Y11">
+        <v>0.9980975923013019</v>
+      </c>
+      <c r="Z11">
+        <v>0.02988810346546134</v>
+      </c>
+      <c r="AA11">
+        <v>0.6978802222612099</v>
+      </c>
+      <c r="AB11">
+        <v>-58.03497867404825</v>
+      </c>
+      <c r="AC11">
+        <v>-50</v>
+      </c>
+      <c r="AD11">
+        <v>0.5294014380625385</v>
+      </c>
+      <c r="AE11">
+        <v>-0.8483714501191776</v>
+      </c>
+      <c r="AF11">
+        <v>2.055058021800826</v>
+      </c>
+      <c r="AG11">
+        <v>2.051148463598881</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI11" t="s">
         <v>67</v>
       </c>
-      <c r="X11">
-        <v>0.9476599975949288</v>
-      </c>
-      <c r="Y11">
-        <v>0.9962027021552202</v>
-      </c>
-      <c r="Z11">
-        <v>0.04854270456029142</v>
-      </c>
-      <c r="AA11">
-        <v>0.455518198324221</v>
-      </c>
-      <c r="AB11">
-        <v>-34.59650768776844</v>
-      </c>
-      <c r="AC11">
-        <v>-65</v>
-      </c>
-      <c r="AD11">
-        <v>0.823170978414328</v>
-      </c>
-      <c r="AE11">
-        <v>-0.5677935719047883</v>
-      </c>
-      <c r="AF11">
-        <v>1.839511489799635</v>
-      </c>
-      <c r="AG11">
-        <v>1.832526316783971</v>
-      </c>
-      <c r="AH11" t="s">
-        <v>56</v>
-      </c>
-      <c r="AI11" t="s">
-        <v>69</v>
-      </c>
       <c r="AJ11" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK11" t="s">
         <v>74</v>
       </c>
-      <c r="AK11" t="s">
-        <v>79</v>
-      </c>
       <c r="AL11">
-        <v>0.5967953218429034</v>
+        <v>0.4485751163494522</v>
       </c>
       <c r="AM11">
-        <v>0.8306557873808735</v>
+        <v>0.7883113653737266</v>
       </c>
       <c r="AN11">
-        <v>1.543127140641979</v>
+        <v>1.169531431949854</v>
       </c>
       <c r="AO11">
-        <v>-0.8109343561761674</v>
+        <v>-1.609723106038321</v>
       </c>
       <c r="AP11">
-        <v>0.8401398349996683</v>
+        <v>0.1836477920776949</v>
       </c>
       <c r="AQ11">
-        <v>-6.406028587750404</v>
+        <v>-5.643773605844696</v>
       </c>
       <c r="AR11">
-        <v>0.911840991057953</v>
+        <v>0.8261312368576572</v>
       </c>
       <c r="AS11">
-        <v>0.04046727708397353</v>
+        <v>0.06279511868488416</v>
       </c>
       <c r="AT11" t="b">
         <v>1</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="86">
   <si>
     <t>Pair</t>
   </si>
@@ -202,6 +202,9 @@
     <t>DOWN_DECELERATING</t>
   </si>
   <si>
+    <t>DOWN_ACCELERATING</t>
+  </si>
+  <si>
     <t>多头稳态</t>
   </si>
   <si>
@@ -214,12 +217,24 @@
     <t>空头减速</t>
   </si>
   <si>
+    <t>空头加速</t>
+  </si>
+  <si>
+    <t>NEUTRAL</t>
+  </si>
+  <si>
     <t>ALIGNED</t>
   </si>
   <si>
+    <t>TRANSITION</t>
+  </si>
+  <si>
     <t>上涨</t>
   </si>
   <si>
+    <t>转换</t>
+  </si>
+  <si>
     <t>下跌</t>
   </si>
   <si>
@@ -229,22 +244,34 @@
     <t>UP_CREST_FLATTENING</t>
   </si>
   <si>
+    <t>TRANSITION_ZONE</t>
+  </si>
+  <si>
     <t>UP_STEEPENING</t>
   </si>
   <si>
     <t>DOWN_VALLEY_FLATTENING</t>
   </si>
   <si>
+    <t>DOWN_STEEPENING</t>
+  </si>
+  <si>
     <t>上升坡延续</t>
   </si>
   <si>
     <t>上升坡顶钝化</t>
   </si>
   <si>
+    <t>地形转换区</t>
+  </si>
+  <si>
     <t>上升陡坡形成</t>
   </si>
   <si>
     <t>下降谷底收敛</t>
+  </si>
+  <si>
+    <t>下降陡坡形成</t>
   </si>
 </sst>
 </file>
@@ -754,10 +781,10 @@
         <v>46</v>
       </c>
       <c r="B2" s="2">
+        <v>46268</v>
+      </c>
+      <c r="C2" s="2">
         <v>46267</v>
-      </c>
-      <c r="C2" s="2">
-        <v>46266</v>
       </c>
       <c r="D2" t="s">
         <v>56</v>
@@ -766,16 +793,16 @@
         <v>1</v>
       </c>
       <c r="F2">
-        <v>0.03664263525046552</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>0.8312212830193545</v>
+        <v>0.797310286257369</v>
       </c>
       <c r="H2">
-        <v>1.070464443029705</v>
+        <v>1.070717457367837</v>
       </c>
       <c r="I2">
-        <v>0.2581626819934897</v>
+        <v>0.2581495851151141</v>
       </c>
       <c r="J2">
         <v>6</v>
@@ -787,103 +814,103 @@
         <v>149</v>
       </c>
       <c r="M2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N2">
-        <v>-0.2544460973324824</v>
+        <v>-0.2802134099406536</v>
       </c>
       <c r="O2">
-        <v>-7.031811450393333</v>
+        <v>-7.405216964605016</v>
       </c>
       <c r="P2">
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.8312212830193545</v>
+        <v>0.797310286257369</v>
       </c>
       <c r="R2" t="s">
         <v>58</v>
       </c>
       <c r="S2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="T2">
-        <v>0.9951932929486321</v>
+        <v>0.9999979933270501</v>
       </c>
       <c r="U2">
-        <v>0.852947854274856</v>
+        <v>0.8496871184512037</v>
       </c>
       <c r="V2" t="s">
         <v>56</v>
       </c>
       <c r="W2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="X2">
-        <v>0.9930000993732632</v>
+        <v>0.9920757282495903</v>
       </c>
       <c r="Y2">
-        <v>0.9984579086416064</v>
+        <v>0.9987520858161244</v>
       </c>
       <c r="Z2">
-        <v>0.005457809268343272</v>
+        <v>0.006676357566534064</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>9.685834486095624</v>
+        <v>0.1965090935215599</v>
       </c>
       <c r="AC2">
-        <v>-25</v>
+        <v>-27</v>
       </c>
       <c r="AD2">
-        <v>0.9857450954106393</v>
+        <v>0.9999941184794554</v>
       </c>
       <c r="AE2">
-        <v>0.1682456741609418</v>
+        <v>0.003429723968047533</v>
       </c>
       <c r="AF2">
-        <v>0.7385557067263675</v>
+        <v>0.6867860800075224</v>
       </c>
       <c r="AG2">
-        <v>0.7374167863533325</v>
+        <v>0.6859290299169927</v>
       </c>
       <c r="AH2" t="s">
         <v>56</v>
       </c>
       <c r="AI2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="AJ2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="AK2" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="AL2">
-        <v>0.4921124932087139</v>
+        <v>0.4993731058176064</v>
       </c>
       <c r="AM2">
-        <v>0.7901023295729401</v>
+        <v>0.794264840990984</v>
       </c>
       <c r="AN2">
-        <v>0.7134698830645207</v>
+        <v>0.6796436970838524</v>
       </c>
       <c r="AO2">
-        <v>0.1697515533455793</v>
+        <v>0.04810217729069901</v>
       </c>
       <c r="AP2">
-        <v>0.6730914030811401</v>
+        <v>0.6624250267471837</v>
       </c>
       <c r="AQ2">
-        <v>-2.166764662218398</v>
+        <v>-1.900361716088309</v>
       </c>
       <c r="AR2">
-        <v>0.5403099453966469</v>
+        <v>0.5123757546429626</v>
       </c>
       <c r="AS2">
-        <v>0.03387644716542595</v>
+        <v>0.03531083058997365</v>
       </c>
       <c r="AT2" t="b">
         <v>1</v>
@@ -894,10 +921,10 @@
         <v>47</v>
       </c>
       <c r="B3" s="2">
+        <v>46268</v>
+      </c>
+      <c r="C3" s="2">
         <v>46267</v>
-      </c>
-      <c r="C3" s="2">
-        <v>46266</v>
       </c>
       <c r="D3" t="s">
         <v>56</v>
@@ -906,16 +933,16 @@
         <v>1</v>
       </c>
       <c r="F3">
-        <v>0.7158954326081945</v>
+        <v>0.7858935505114415</v>
       </c>
       <c r="G3">
-        <v>2.081674623598277</v>
+        <v>2.152585530024997</v>
       </c>
       <c r="H3">
-        <v>1.896778626505637</v>
+        <v>1.906840250666997</v>
       </c>
       <c r="I3">
-        <v>0.4282072919721926</v>
+        <v>0.4297845805167367</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -927,103 +954,103 @@
         <v>225</v>
       </c>
       <c r="M3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N3">
-        <v>-0.07746335392602528</v>
+        <v>-0.08322037597512554</v>
       </c>
       <c r="O3">
-        <v>-24.027627228633</v>
+        <v>-24.73641748729839</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>2.081674623598277</v>
+        <v>2.152585530024997</v>
       </c>
       <c r="R3" t="s">
         <v>58</v>
       </c>
       <c r="S3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="T3">
-        <v>0.9898330321665639</v>
+        <v>0.9890520500648153</v>
       </c>
       <c r="U3">
-        <v>0.9523022662502993</v>
+        <v>0.9627612877784943</v>
       </c>
       <c r="V3" t="s">
         <v>56</v>
       </c>
       <c r="W3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="X3">
-        <v>0.9826967538231927</v>
+        <v>0.9932132549039878</v>
       </c>
       <c r="Y3">
-        <v>0.9979723475364658</v>
+        <v>0.9992153306904448</v>
       </c>
       <c r="Z3">
-        <v>0.01527559371327314</v>
+        <v>0.006002075786456951</v>
       </c>
       <c r="AA3">
-        <v>0.7552851486783748</v>
+        <v>0.7520566950343766</v>
       </c>
       <c r="AB3">
-        <v>-11.80851420014053</v>
+        <v>-12.33926865519214</v>
       </c>
       <c r="AC3">
-        <v>-39</v>
+        <v>-24</v>
       </c>
       <c r="AD3">
-        <v>0.9788369896718806</v>
+        <v>0.976899340907506</v>
       </c>
       <c r="AE3">
-        <v>-0.2046415100855414</v>
+        <v>-0.2136999713020115</v>
       </c>
       <c r="AF3">
-        <v>1.7874930413671</v>
+        <v>1.786814758132728</v>
       </c>
       <c r="AG3">
-        <v>1.783868626698222</v>
+        <v>1.78541269943016</v>
       </c>
       <c r="AH3" t="s">
         <v>56</v>
       </c>
       <c r="AI3" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="AJ3" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="AK3" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="AL3">
-        <v>0.8573271220684781</v>
+        <v>0.8551200019683945</v>
       </c>
       <c r="AM3">
-        <v>0.9391655211154649</v>
+        <v>0.9379709570187473</v>
       </c>
       <c r="AN3">
-        <v>1.74411969895434</v>
+        <v>1.751078020435302</v>
       </c>
       <c r="AO3">
-        <v>-0.2087155696182473</v>
+        <v>-0.2885197136156094</v>
       </c>
       <c r="AP3">
-        <v>1.878970786235352</v>
+        <v>2.155908779025148</v>
       </c>
       <c r="AQ3">
-        <v>-4.810729408825131</v>
+        <v>-3.819122034080421</v>
       </c>
       <c r="AR3">
-        <v>1.478835874889411</v>
+        <v>1.850068786225984</v>
       </c>
       <c r="AS3">
-        <v>0.03221951439691526</v>
+        <v>0.03490366668023578</v>
       </c>
       <c r="AT3" t="b">
         <v>1</v>
@@ -1034,10 +1061,10 @@
         <v>48</v>
       </c>
       <c r="B4" s="2">
+        <v>46268</v>
+      </c>
+      <c r="C4" s="2">
         <v>46267</v>
-      </c>
-      <c r="C4" s="2">
-        <v>46266</v>
       </c>
       <c r="D4" t="s">
         <v>56</v>
@@ -1049,121 +1076,121 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>0.1548758298373375</v>
+        <v>0.04460804836341198</v>
       </c>
       <c r="H4">
-        <v>2.077317786444455</v>
+        <v>2.077688936092662</v>
       </c>
       <c r="I4">
-        <v>0.4936721050111056</v>
+        <v>0.4931335537796923</v>
       </c>
       <c r="J4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K4">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L4">
         <v>146</v>
       </c>
       <c r="M4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N4">
-        <v>-0.2105537239034255</v>
+        <v>-0.2204507280948902</v>
       </c>
       <c r="O4">
-        <v>-7.771558488394321</v>
+        <v>-8.064568051550731</v>
       </c>
       <c r="P4">
-        <v>0.5095550171948624</v>
+        <v>0.6442415930170223</v>
       </c>
       <c r="Q4">
-        <v>0.3157863476378396</v>
+        <v>0.1253885993635742</v>
       </c>
       <c r="R4" t="s">
         <v>59</v>
       </c>
       <c r="S4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="T4">
-        <v>0.7604757577322193</v>
+        <v>0.6838259636023329</v>
       </c>
       <c r="U4">
-        <v>0.7168727981111971</v>
+        <v>0.6575443334106572</v>
       </c>
       <c r="V4" t="s">
         <v>56</v>
       </c>
       <c r="W4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="X4">
-        <v>0.9692786445408872</v>
+        <v>0.9811625148859606</v>
       </c>
       <c r="Y4">
-        <v>0.9986348285267936</v>
+        <v>0.9992905991584297</v>
       </c>
       <c r="Z4">
-        <v>0.02935618398590645</v>
+        <v>0.01812808427246904</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>-70.4259684600639</v>
+        <v>-80.12136553617742</v>
       </c>
       <c r="AC4">
-        <v>-50</v>
+        <v>-40</v>
       </c>
       <c r="AD4">
-        <v>0.3350245617784124</v>
+        <v>0.1715617420981733</v>
       </c>
       <c r="AE4">
-        <v>-0.9422093944581442</v>
+        <v>-0.9851733698432169</v>
       </c>
       <c r="AF4">
-        <v>1.115307815442161</v>
+        <v>1.263839583614147</v>
       </c>
       <c r="AG4">
-        <v>1.113785229028676</v>
+        <v>1.262943014749921</v>
       </c>
       <c r="AH4" t="s">
         <v>56</v>
       </c>
       <c r="AI4" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="AJ4" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AK4" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AL4">
-        <v>0.1672835979019245</v>
+        <v>0.08572001802697378</v>
       </c>
       <c r="AM4">
-        <v>0.583630877243415</v>
+        <v>0.5268596365484934</v>
       </c>
       <c r="AN4">
-        <v>0.4378744951828293</v>
+        <v>0.2901236512625224</v>
       </c>
       <c r="AO4">
-        <v>-0.9883937268693395</v>
+        <v>-1.205615066344327</v>
       </c>
       <c r="AP4">
-        <v>-0.4835141276740909</v>
+        <v>-0.709973585536663</v>
       </c>
       <c r="AQ4">
-        <v>-3.009890836088064</v>
+        <v>-2.633424001619929</v>
       </c>
       <c r="AR4">
-        <v>0.8282266851857534</v>
+        <v>0.9481025885323628</v>
       </c>
       <c r="AS4">
-        <v>0.1093245418299093</v>
+        <v>0.1624039719093927</v>
       </c>
       <c r="AT4" t="b">
         <v>1</v>
@@ -1174,10 +1201,10 @@
         <v>49</v>
       </c>
       <c r="B5" s="2">
+        <v>46268</v>
+      </c>
+      <c r="C5" s="2">
         <v>46267</v>
-      </c>
-      <c r="C5" s="2">
-        <v>46266</v>
       </c>
       <c r="D5" t="s">
         <v>56</v>
@@ -1186,16 +1213,16 @@
         <v>1</v>
       </c>
       <c r="F5">
-        <v>0.1980425254034911</v>
+        <v>0.2343500295492417</v>
       </c>
       <c r="G5">
-        <v>1.275627528407026</v>
+        <v>1.303647111221324</v>
       </c>
       <c r="H5">
-        <v>1.472022617308266</v>
+        <v>1.477921746074287</v>
       </c>
       <c r="I5">
-        <v>0.3252032246654484</v>
+        <v>0.3280155359273167</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -1207,103 +1234,103 @@
         <v>226</v>
       </c>
       <c r="M5">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N5">
-        <v>-0.08818406830950198</v>
+        <v>-0.09251092846166663</v>
       </c>
       <c r="O5">
-        <v>-24.32903648306311</v>
+        <v>-26.00186706411044</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>1.275627528407026</v>
+        <v>1.303647111221324</v>
       </c>
       <c r="R5" t="s">
         <v>59</v>
       </c>
       <c r="S5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="T5">
-        <v>0.73544020757439</v>
+        <v>0.7438361268944865</v>
       </c>
       <c r="U5">
-        <v>0.7603640563596267</v>
+        <v>0.7696840462715696</v>
       </c>
       <c r="V5" t="s">
         <v>56</v>
       </c>
       <c r="W5" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="X5">
-        <v>0.9818420376115305</v>
+        <v>0.9910936278314159</v>
       </c>
       <c r="Y5">
-        <v>0.99883833656251</v>
+        <v>0.9992211389466578</v>
       </c>
       <c r="Z5">
-        <v>0.01699629895097943</v>
+        <v>0.008127511115241903</v>
       </c>
       <c r="AA5">
         <v>1</v>
       </c>
       <c r="AB5">
-        <v>-57.34312559698115</v>
+        <v>-56.54615095759976</v>
       </c>
       <c r="AC5">
-        <v>-39</v>
+        <v>-28</v>
       </c>
       <c r="AD5">
-        <v>0.5396067760909485</v>
+        <v>0.5512651228428953</v>
       </c>
       <c r="AE5">
-        <v>-0.8419171735965082</v>
+        <v>-0.8343301291077816</v>
       </c>
       <c r="AF5">
-        <v>2.079029838419099</v>
+        <v>2.015326054507508</v>
       </c>
       <c r="AG5">
-        <v>2.076614705470357</v>
+        <v>2.013756395533866</v>
       </c>
       <c r="AH5" t="s">
         <v>56</v>
       </c>
       <c r="AI5" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="AJ5" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AK5" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AL5">
-        <v>0.5389799346285418</v>
+        <v>0.5508357639086471</v>
       </c>
       <c r="AM5">
-        <v>0.8532150844212933</v>
+        <v>0.8572077745584886</v>
       </c>
       <c r="AN5">
-        <v>1.215167322787437</v>
+        <v>1.1943067349079</v>
       </c>
       <c r="AO5">
-        <v>-1.640179226747929</v>
+        <v>-1.600982681535377</v>
       </c>
       <c r="AP5">
-        <v>0.5036293875768525</v>
+        <v>0.7056569399605981</v>
       </c>
       <c r="AQ5">
-        <v>-4.781891157326882</v>
+        <v>-3.79157348477345</v>
       </c>
       <c r="AR5">
-        <v>0.6431416081451213</v>
+        <v>0.6368284989665858</v>
       </c>
       <c r="AS5">
-        <v>0.05506910801913067</v>
+        <v>0.05266107283806797</v>
       </c>
       <c r="AT5" t="b">
         <v>1</v>
@@ -1314,10 +1341,10 @@
         <v>50</v>
       </c>
       <c r="B6" s="2">
+        <v>46268</v>
+      </c>
+      <c r="C6" s="2">
         <v>46267</v>
-      </c>
-      <c r="C6" s="2">
-        <v>46266</v>
       </c>
       <c r="D6" t="s">
         <v>56</v>
@@ -1329,121 +1356,121 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0.1374119100697148</v>
+        <v>0.01481739457292504</v>
       </c>
       <c r="H6">
-        <v>0.9432391899524737</v>
+        <v>0.9432567834939194</v>
       </c>
       <c r="I6">
-        <v>0.2574035808191225</v>
+        <v>0.2573003166455595</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K6">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L6">
         <v>158</v>
       </c>
       <c r="M6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N6">
-        <v>-0.3575195131343776</v>
+        <v>-0.3664880736341721</v>
       </c>
       <c r="O6">
-        <v>-6.637677117351549</v>
+        <v>-6.706795941123629</v>
       </c>
       <c r="P6">
-        <v>0.2627987542719751</v>
+        <v>0.1278926178349663</v>
       </c>
       <c r="Q6">
-        <v>0.1863967415491998</v>
+        <v>0.01699033269978795</v>
       </c>
       <c r="R6" t="s">
         <v>59</v>
       </c>
       <c r="S6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="T6">
-        <v>0.6248165648010945</v>
+        <v>0.4361491949284066</v>
       </c>
       <c r="U6">
-        <v>0.6559895011842651</v>
+        <v>0.5461788310456028</v>
       </c>
       <c r="V6" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="W6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="X6">
-        <v>0.9870036233670173</v>
+        <v>0.9924801081348495</v>
       </c>
       <c r="Y6">
-        <v>0.9992881880950903</v>
+        <v>0.9996467733112795</v>
       </c>
       <c r="Z6">
-        <v>0.01228456472807304</v>
+        <v>0.007166665176429943</v>
       </c>
       <c r="AA6">
-        <v>0.3930108121593393</v>
+        <v>0.7531789111823489</v>
       </c>
       <c r="AB6">
-        <v>-76.12344219304276</v>
+        <v>-86.82173875942046</v>
       </c>
       <c r="AC6">
-        <v>-31.99999999999999</v>
+        <v>-25</v>
       </c>
       <c r="AD6">
-        <v>0.2398308600887976</v>
+        <v>0.0554426796514236</v>
       </c>
       <c r="AE6">
-        <v>-0.9708146880579566</v>
+        <v>-0.9984618717172277</v>
       </c>
       <c r="AF6">
-        <v>0.8645234585851871</v>
+        <v>1.006014431667909</v>
       </c>
       <c r="AG6">
-        <v>0.8639080804952924</v>
+        <v>1.005659080521406</v>
       </c>
       <c r="AH6" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="AI6" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="AJ6" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="AK6" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="AL6">
-        <v>0.1669245870513401</v>
+        <v>0.04858330138964393</v>
       </c>
       <c r="AM6">
-        <v>0.6325858123246292</v>
+        <v>0.6296226630292223</v>
       </c>
       <c r="AN6">
-        <v>0.2398947459342808</v>
+        <v>0.09179140797310192</v>
       </c>
       <c r="AO6">
-        <v>-0.8188715142173091</v>
+        <v>-0.9942209844444976</v>
       </c>
       <c r="AP6">
-        <v>-0.1948822532947811</v>
+        <v>-0.4761183589433012</v>
       </c>
       <c r="AQ6">
-        <v>-1.659886776115244</v>
+        <v>-1.481136417429724</v>
       </c>
       <c r="AR6">
-        <v>0.4050154083840715</v>
+        <v>0.5900852033350962</v>
       </c>
       <c r="AS6">
-        <v>0.1181098264477304</v>
+        <v>0.2501486250774816</v>
       </c>
       <c r="AT6" t="b">
         <v>1</v>
@@ -1454,10 +1481,10 @@
         <v>51</v>
       </c>
       <c r="B7" s="2">
+        <v>46268</v>
+      </c>
+      <c r="C7" s="2">
         <v>46267</v>
-      </c>
-      <c r="C7" s="2">
-        <v>46266</v>
       </c>
       <c r="D7" t="s">
         <v>56</v>
@@ -1466,16 +1493,16 @@
         <v>1</v>
       </c>
       <c r="F7">
-        <v>0.1478072069554337</v>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>1.183791461618007</v>
+        <v>0.9047384985029333</v>
       </c>
       <c r="H7">
-        <v>1.426849596913979</v>
+        <v>1.433708931763957</v>
       </c>
       <c r="I7">
-        <v>0.3450640389242944</v>
+        <v>0.3485003583960764</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -1487,103 +1514,103 @@
         <v>239</v>
       </c>
       <c r="M7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N7">
-        <v>-0.1312072082391334</v>
+        <v>-0.1356747235399634</v>
       </c>
       <c r="O7">
-        <v>-29.50844843932332</v>
+        <v>-32.24866094328517</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>0.08798859307214553</v>
       </c>
       <c r="Q7">
-        <v>1.183791461618007</v>
+        <v>0.9920254194523507</v>
       </c>
       <c r="R7" t="s">
         <v>59</v>
       </c>
       <c r="S7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="T7">
-        <v>0.67988918989935</v>
+        <v>0.6173183882512728</v>
       </c>
       <c r="U7">
-        <v>0.7279088527254214</v>
+        <v>0.6776520818360448</v>
       </c>
       <c r="V7" t="s">
         <v>56</v>
       </c>
       <c r="W7" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="X7">
-        <v>0.9882511727317382</v>
+        <v>0.9931009916357078</v>
       </c>
       <c r="Y7">
-        <v>0.9991505449095957</v>
+        <v>0.9994352284918875</v>
       </c>
       <c r="Z7">
-        <v>0.01089937217785741</v>
+        <v>0.006334236856179731</v>
       </c>
       <c r="AA7">
         <v>1</v>
       </c>
       <c r="AB7">
-        <v>-63.36915774106748</v>
+        <v>-68.96965564906534</v>
       </c>
       <c r="AC7">
-        <v>-30.99999999999999</v>
+        <v>-24</v>
       </c>
       <c r="AD7">
-        <v>0.4482403452450372</v>
+        <v>0.3588623317040449</v>
       </c>
       <c r="AE7">
-        <v>-0.893913079048858</v>
+        <v>-0.9333905007465718</v>
       </c>
       <c r="AF7">
-        <v>2.279016647207451</v>
+        <v>2.411620750927922</v>
       </c>
       <c r="AG7">
-        <v>2.277080724915364</v>
+        <v>2.410258736239425</v>
       </c>
       <c r="AH7" t="s">
         <v>56</v>
       </c>
       <c r="AI7" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="AJ7" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AK7" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AL7">
-        <v>0.4478595852020442</v>
+        <v>0.3586596564837636</v>
       </c>
       <c r="AM7">
-        <v>0.8257786813782142</v>
+        <v>0.7966654376667648</v>
       </c>
       <c r="AN7">
-        <v>1.10677074999734</v>
+        <v>0.9540568630883743</v>
       </c>
       <c r="AO7">
-        <v>-1.961542113419563</v>
+        <v>-2.196751892415731</v>
       </c>
       <c r="AP7">
-        <v>0.5773795043339081</v>
+        <v>0.3591457068435773</v>
       </c>
       <c r="AQ7">
-        <v>-4.452091786721666</v>
+        <v>-3.824661056089581</v>
       </c>
       <c r="AR7">
-        <v>0.6579648247921243</v>
+        <v>0.5187948123520039</v>
       </c>
       <c r="AS7">
-        <v>0.05597408609103618</v>
+        <v>0.07197061211072805</v>
       </c>
       <c r="AT7" t="b">
         <v>1</v>
@@ -1594,10 +1621,10 @@
         <v>52</v>
       </c>
       <c r="B8" s="2">
+        <v>46268</v>
+      </c>
+      <c r="C8" s="2">
         <v>46267</v>
-      </c>
-      <c r="C8" s="2">
-        <v>46266</v>
       </c>
       <c r="D8" t="s">
         <v>56</v>
@@ -1609,13 +1636,13 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>0.4967688813717854</v>
+        <v>0.4164529723958093</v>
       </c>
       <c r="H8">
-        <v>1.436450702438285</v>
+        <v>1.436832076585239</v>
       </c>
       <c r="I8">
-        <v>0.3551488100669746</v>
+        <v>0.3555677089636515</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -1624,106 +1651,106 @@
         <v>1</v>
       </c>
       <c r="L8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M8">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N8">
-        <v>0.005249229949467661</v>
+        <v>0</v>
       </c>
       <c r="O8">
-        <v>1.255153190308239</v>
+        <v>0</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>0.4967688813717854</v>
+        <v>0.4164529723958093</v>
       </c>
       <c r="R8" t="s">
         <v>60</v>
       </c>
       <c r="S8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="T8">
-        <v>0.7324350881533757</v>
+        <v>0.7391035841743484</v>
       </c>
       <c r="U8">
-        <v>0.7295077626680786</v>
+        <v>0.7325530400365784</v>
       </c>
       <c r="V8" t="s">
         <v>56</v>
       </c>
       <c r="W8" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="X8">
-        <v>0.9943729754813324</v>
+        <v>0.9944046836876371</v>
       </c>
       <c r="Y8">
-        <v>0.999647891996238</v>
+        <v>0.9998257086324864</v>
       </c>
       <c r="Z8">
-        <v>0.005274916514905637</v>
+        <v>0.005421024944849306</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>77.51199110577859</v>
+        <v>76.35776622500063</v>
       </c>
       <c r="AC8">
-        <v>-20</v>
+        <v>-21.99999999999999</v>
       </c>
       <c r="AD8">
-        <v>0.2162352857957925</v>
+        <v>0.2358584995223076</v>
       </c>
       <c r="AE8">
-        <v>0.9763412831468369</v>
+        <v>0.971787408954801</v>
       </c>
       <c r="AF8">
-        <v>1.021287877484621</v>
+        <v>0.9386792964905228</v>
       </c>
       <c r="AG8">
-        <v>1.020928273848814</v>
+        <v>0.9385156927922809</v>
       </c>
       <c r="AH8" t="s">
         <v>56</v>
       </c>
       <c r="AI8" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="AJ8" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="AK8" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AL8">
-        <v>0.108079573810484</v>
+        <v>0.1179086957109431</v>
       </c>
       <c r="AM8">
-        <v>0.5418974456834689</v>
+        <v>0.5488031704417413</v>
       </c>
       <c r="AN8">
-        <v>0.211374167823509</v>
+        <v>0.1986122585894139</v>
       </c>
       <c r="AO8">
-        <v>0.9932998625844931</v>
+        <v>0.9120522468863762</v>
       </c>
       <c r="AP8">
-        <v>1.340440313245824</v>
+        <v>1.048129045407561</v>
       </c>
       <c r="AQ8">
-        <v>1.901223347815873</v>
+        <v>0.8457893045172541</v>
       </c>
       <c r="AR8">
-        <v>1.461326171464674</v>
+        <v>1.06708464664955</v>
       </c>
       <c r="AS8">
-        <v>0.1523326816930144</v>
+        <v>0.1459558495754748</v>
       </c>
       <c r="AT8" t="b">
         <v>1</v>
@@ -1734,10 +1761,10 @@
         <v>53</v>
       </c>
       <c r="B9" s="2">
+        <v>46268</v>
+      </c>
+      <c r="C9" s="2">
         <v>46267</v>
-      </c>
-      <c r="C9" s="2">
-        <v>46266</v>
       </c>
       <c r="D9" t="s">
         <v>57</v>
@@ -1746,16 +1773,16 @@
         <v>-1</v>
       </c>
       <c r="F9">
-        <v>0.5718920027090993</v>
+        <v>0.553384687846852</v>
       </c>
       <c r="G9">
-        <v>3.085912441598675</v>
+        <v>3.0698123554791</v>
       </c>
       <c r="H9">
-        <v>2.996660631167433</v>
+        <v>3.003239549367671</v>
       </c>
       <c r="I9">
-        <v>0.6207353187279173</v>
+        <v>0.6235196719929369</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -1767,103 +1794,103 @@
         <v>76</v>
       </c>
       <c r="M9">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N9">
-        <v>0.5044492443705563</v>
+        <v>0.5229505065359541</v>
       </c>
       <c r="O9">
-        <v>64.93462137907112</v>
+        <v>66.79719986773674</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>3.085912441598675</v>
+        <v>3.0698123554791</v>
       </c>
       <c r="R9" t="s">
         <v>61</v>
       </c>
       <c r="S9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="T9">
-        <v>-0.9739263676089753</v>
+        <v>-0.9723817589067877</v>
       </c>
       <c r="U9">
-        <v>0.9239505181732065</v>
+        <v>0.9205140010772777</v>
       </c>
       <c r="V9" t="s">
         <v>57</v>
       </c>
       <c r="W9" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="X9">
-        <v>0.996933682565361</v>
+        <v>0.9987893284261056</v>
       </c>
       <c r="Y9">
-        <v>0.9995994093712112</v>
+        <v>0.9997380255687813</v>
       </c>
       <c r="Z9">
-        <v>0.002665726805850199</v>
+        <v>0.0009486971426757584</v>
       </c>
       <c r="AA9">
-        <v>1</v>
+        <v>0.9713837045358507</v>
       </c>
       <c r="AB9">
-        <v>162.0771026016102</v>
+        <v>161.4990741687712</v>
       </c>
       <c r="AC9">
-        <v>-16</v>
+        <v>-9</v>
       </c>
       <c r="AD9">
-        <v>-0.9514714974345199</v>
+        <v>-0.9483185278188759</v>
       </c>
       <c r="AE9">
-        <v>0.3077368836680329</v>
+        <v>0.3173199801390387</v>
       </c>
       <c r="AF9">
-        <v>2.492435818576734</v>
+        <v>2.47606711768403</v>
       </c>
       <c r="AG9">
-        <v>2.491437372144954</v>
+        <v>2.475418451409216</v>
       </c>
       <c r="AH9" t="s">
         <v>57</v>
       </c>
       <c r="AI9" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="AJ9" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="AK9" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AL9">
-        <v>-0.9510903468690879</v>
+        <v>-0.9345049656664831</v>
       </c>
       <c r="AM9">
-        <v>0.9805607637144046</v>
+        <v>0.973784845770583</v>
       </c>
       <c r="AN9">
-        <v>-2.38636634511265</v>
+        <v>-2.358415555281981</v>
       </c>
       <c r="AO9">
-        <v>0.692425453716444</v>
+        <v>0.744277094323944</v>
       </c>
       <c r="AP9">
-        <v>-3.663836892110755</v>
+        <v>-3.706585817956542</v>
       </c>
       <c r="AQ9">
-        <v>4.166204129562628</v>
+        <v>3.784644911069871</v>
       </c>
       <c r="AR9">
-        <v>3.314172727289706</v>
+        <v>3.391580680390451</v>
       </c>
       <c r="AS9">
-        <v>0.03160319197250212</v>
+        <v>0.03263841620882221</v>
       </c>
       <c r="AT9" t="b">
         <v>1</v>
@@ -1874,10 +1901,10 @@
         <v>54</v>
       </c>
       <c r="B10" s="2">
+        <v>46268</v>
+      </c>
+      <c r="C10" s="2">
         <v>46267</v>
-      </c>
-      <c r="C10" s="2">
-        <v>46266</v>
       </c>
       <c r="D10" t="s">
         <v>57</v>
@@ -1889,13 +1916,13 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>0.5475949992913479</v>
+        <v>1.28836685428672</v>
       </c>
       <c r="H10">
-        <v>2.044775301697971</v>
+        <v>2.045146857262753</v>
       </c>
       <c r="I10">
-        <v>0.4588968231056106</v>
+        <v>0.4579228488431169</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1907,103 +1934,103 @@
         <v>233</v>
       </c>
       <c r="M10">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N10">
-        <v>18.12835099241988</v>
+        <v>18.65490415375874</v>
       </c>
       <c r="O10">
-        <v>32.21999668577872</v>
+        <v>23.48005557427162</v>
       </c>
       <c r="P10">
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>0.5475949992913479</v>
+        <v>1.28836685428672</v>
       </c>
       <c r="R10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="S10" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="T10">
-        <v>-0.6638504049446032</v>
+        <v>-0.986519251726429</v>
       </c>
       <c r="U10">
-        <v>0.698655475988894</v>
+        <v>0.8430583285751643</v>
       </c>
       <c r="V10" t="s">
         <v>57</v>
       </c>
       <c r="W10" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="X10">
-        <v>0.9957317554008226</v>
+        <v>0.9417828297073885</v>
       </c>
       <c r="Y10">
-        <v>0.99969117505529</v>
+        <v>0.9964986611930852</v>
       </c>
       <c r="Z10">
-        <v>0.003959419654467444</v>
+        <v>0.0547158314856967</v>
       </c>
       <c r="AA10">
-        <v>0.4447421088578876</v>
+        <v>0</v>
       </c>
       <c r="AB10">
-        <v>107.9808371594463</v>
+        <v>-163.8278774543612</v>
       </c>
       <c r="AC10">
-        <v>-20</v>
+        <v>63</v>
       </c>
       <c r="AD10">
-        <v>-0.3086988918121568</v>
+        <v>-0.9604293160660587</v>
       </c>
       <c r="AE10">
-        <v>0.9511598152749864</v>
+        <v>-0.2785238389094954</v>
       </c>
       <c r="AF10">
-        <v>1.604591491765379</v>
+        <v>1.006053330670172</v>
       </c>
       <c r="AG10">
-        <v>1.604095953886653</v>
+        <v>1.002530797101671</v>
       </c>
       <c r="AH10" t="s">
         <v>57</v>
       </c>
       <c r="AI10" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="AJ10" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="AK10" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AL10">
-        <v>-0.2229262775163841</v>
+        <v>-0.478533263815209</v>
       </c>
       <c r="AM10">
-        <v>0.6683567585864898</v>
+        <v>0.777810784463951</v>
       </c>
       <c r="AN10">
-        <v>-0.5624508385271039</v>
+        <v>-0.9271836071572588</v>
       </c>
       <c r="AO10">
-        <v>1.495470092840533</v>
+        <v>-0.1950795223762414</v>
       </c>
       <c r="AP10">
-        <v>-0.009403424691524442</v>
+        <v>-1.768245498035377</v>
       </c>
       <c r="AQ10">
-        <v>1.90094011641255</v>
+        <v>-0.6033737375842941</v>
       </c>
       <c r="AR10">
-        <v>0.282263743606916</v>
+        <v>1.84789289916817</v>
       </c>
       <c r="AS10">
-        <v>0.08728827998724183</v>
+        <v>0.06061694515630939</v>
       </c>
       <c r="AT10" t="b">
         <v>1</v>
@@ -2014,10 +2041,10 @@
         <v>55</v>
       </c>
       <c r="B11" s="2">
+        <v>46268</v>
+      </c>
+      <c r="C11" s="2">
         <v>46267</v>
-      </c>
-      <c r="C11" s="2">
-        <v>46266</v>
       </c>
       <c r="D11" t="s">
         <v>56</v>
@@ -2029,13 +2056,13 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>1.158556464871536</v>
+        <v>1.137858591651362</v>
       </c>
       <c r="H11">
-        <v>2.569154114874816</v>
+        <v>2.542893602080119</v>
       </c>
       <c r="I11">
-        <v>0.6065146064261379</v>
+        <v>0.602306131570605</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -2047,103 +2074,103 @@
         <v>212</v>
       </c>
       <c r="M11">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N11">
-        <v>-1668.683112213251</v>
+        <v>-1762.020333206901</v>
       </c>
       <c r="O11">
-        <v>-20.33748172577187</v>
+        <v>-21.3462712081312</v>
       </c>
       <c r="P11">
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>1.158556464871536</v>
+        <v>1.137858591651362</v>
       </c>
       <c r="R11" t="s">
         <v>59</v>
       </c>
       <c r="S11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="T11">
-        <v>0.7444548970353234</v>
+        <v>0.703790963191243</v>
       </c>
       <c r="U11">
-        <v>0.734529101741221</v>
+        <v>0.716435062025275</v>
       </c>
       <c r="V11" t="s">
         <v>56</v>
       </c>
       <c r="W11" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="X11">
-        <v>0.9682094888358406</v>
+        <v>0.9841370377624933</v>
       </c>
       <c r="Y11">
-        <v>0.9980975923013019</v>
+        <v>0.9989165143568625</v>
       </c>
       <c r="Z11">
-        <v>0.02988810346546134</v>
+        <v>0.01477947659436918</v>
       </c>
       <c r="AA11">
-        <v>0.6978802222612099</v>
+        <v>0.783708993523034</v>
       </c>
       <c r="AB11">
-        <v>-58.03497867404825</v>
+        <v>-61.90794290002168</v>
       </c>
       <c r="AC11">
-        <v>-50</v>
+        <v>-37</v>
       </c>
       <c r="AD11">
-        <v>0.5294014380625385</v>
+        <v>0.470889587660248</v>
       </c>
       <c r="AE11">
-        <v>-0.8483714501191776</v>
+        <v>-0.8821921538038987</v>
       </c>
       <c r="AF11">
-        <v>2.055058021800826</v>
+        <v>2.128577844088565</v>
       </c>
       <c r="AG11">
-        <v>2.051148463598881</v>
+        <v>2.126271560554195</v>
       </c>
       <c r="AH11" t="s">
         <v>56</v>
       </c>
       <c r="AI11" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="AJ11" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AK11" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AL11">
-        <v>0.4485751163494522</v>
+        <v>0.41950997018893</v>
       </c>
       <c r="AM11">
-        <v>0.7883113653737266</v>
+        <v>0.7881622110680928</v>
       </c>
       <c r="AN11">
-        <v>1.169531431949854</v>
+        <v>1.09897871679703</v>
       </c>
       <c r="AO11">
-        <v>-1.609723106038321</v>
+        <v>-1.783391243574383</v>
       </c>
       <c r="AP11">
-        <v>0.1836477920776949</v>
+        <v>0.3734730847471686</v>
       </c>
       <c r="AQ11">
-        <v>-5.643773605844696</v>
+        <v>-4.22392389318487</v>
       </c>
       <c r="AR11">
-        <v>0.8261312368576572</v>
+        <v>0.5414619015077295</v>
       </c>
       <c r="AS11">
-        <v>0.06279511868488416</v>
+        <v>0.06311495972993471</v>
       </c>
       <c r="AT11" t="b">
         <v>1</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -199,7 +199,7 @@
     <t>UP_ACCELERATING</t>
   </si>
   <si>
-    <t>DOWN_DECELERATING</t>
+    <t>DOWN_STEADY</t>
   </si>
   <si>
     <t>DOWN_ACCELERATING</t>
@@ -214,7 +214,7 @@
     <t>多头加速</t>
   </si>
   <si>
-    <t>空头减速</t>
+    <t>空头稳态</t>
   </si>
   <si>
     <t>空头加速</t>
@@ -250,7 +250,7 @@
     <t>UP_STEEPENING</t>
   </si>
   <si>
-    <t>DOWN_VALLEY_FLATTENING</t>
+    <t>DOWN_SLOPE</t>
   </si>
   <si>
     <t>DOWN_STEEPENING</t>
@@ -268,7 +268,7 @@
     <t>上升陡坡形成</t>
   </si>
   <si>
-    <t>下降谷底收敛</t>
+    <t>下降坡延续</t>
   </si>
   <si>
     <t>下降陡坡形成</t>
@@ -781,10 +781,10 @@
         <v>46</v>
       </c>
       <c r="B2" s="2">
+        <v>46269</v>
+      </c>
+      <c r="C2" s="2">
         <v>46268</v>
-      </c>
-      <c r="C2" s="2">
-        <v>46267</v>
       </c>
       <c r="D2" t="s">
         <v>56</v>
@@ -793,16 +793,16 @@
         <v>1</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.1577926271651403</v>
       </c>
       <c r="G2">
-        <v>0.797310286257369</v>
+        <v>0.8942615635687848</v>
       </c>
       <c r="H2">
-        <v>1.070717457367837</v>
+        <v>1.070946375102337</v>
       </c>
       <c r="I2">
-        <v>0.2581495851151141</v>
+        <v>0.2581545950776691</v>
       </c>
       <c r="J2">
         <v>6</v>
@@ -814,19 +814,19 @@
         <v>149</v>
       </c>
       <c r="M2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N2">
-        <v>-0.2802134099406536</v>
+        <v>-0.3070653100611083</v>
       </c>
       <c r="O2">
-        <v>-7.405216964605016</v>
+        <v>-8.057040147041594</v>
       </c>
       <c r="P2">
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.797310286257369</v>
+        <v>0.8942615635687848</v>
       </c>
       <c r="R2" t="s">
         <v>58</v>
@@ -835,10 +835,10 @@
         <v>63</v>
       </c>
       <c r="T2">
-        <v>0.9999979933270501</v>
+        <v>0.999570170617093</v>
       </c>
       <c r="U2">
-        <v>0.8496871184512037</v>
+        <v>0.8733456880869649</v>
       </c>
       <c r="V2" t="s">
         <v>56</v>
@@ -847,34 +847,34 @@
         <v>69</v>
       </c>
       <c r="X2">
-        <v>0.9920757282495903</v>
+        <v>0.9962913508420332</v>
       </c>
       <c r="Y2">
-        <v>0.9987520858161244</v>
+        <v>0.999480868938008</v>
       </c>
       <c r="Z2">
-        <v>0.006676357566534064</v>
+        <v>0.003189518095974786</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.1965090935215599</v>
+        <v>-2.946719377017498</v>
       </c>
       <c r="AC2">
-        <v>-27</v>
+        <v>-18</v>
       </c>
       <c r="AD2">
-        <v>0.9999941184794554</v>
+        <v>0.9986777713351352</v>
       </c>
       <c r="AE2">
-        <v>0.003429723968047533</v>
+        <v>-0.05140728587551786</v>
       </c>
       <c r="AF2">
-        <v>0.6867860800075224</v>
+        <v>0.7370916301218147</v>
       </c>
       <c r="AG2">
-        <v>0.6859290299169927</v>
+        <v>0.7367089829610841</v>
       </c>
       <c r="AH2" t="s">
         <v>56</v>
@@ -889,28 +889,28 @@
         <v>80</v>
       </c>
       <c r="AL2">
-        <v>0.4993731058176064</v>
+        <v>0.4990796633415571</v>
       </c>
       <c r="AM2">
-        <v>0.794264840990984</v>
+        <v>0.7937168756135116</v>
       </c>
       <c r="AN2">
-        <v>0.6796436970838524</v>
+        <v>0.7343225849118935</v>
       </c>
       <c r="AO2">
-        <v>0.04810217729069901</v>
+        <v>-0.007213650845189866</v>
       </c>
       <c r="AP2">
-        <v>0.6624250267471837</v>
+        <v>0.8596755130829734</v>
       </c>
       <c r="AQ2">
-        <v>-1.900361716088309</v>
+        <v>-1.593221833858711</v>
       </c>
       <c r="AR2">
-        <v>0.5123757546429626</v>
+        <v>0.7323288057932779</v>
       </c>
       <c r="AS2">
-        <v>0.03531083058997365</v>
+        <v>0.03803173276887899</v>
       </c>
       <c r="AT2" t="b">
         <v>1</v>
@@ -921,10 +921,10 @@
         <v>47</v>
       </c>
       <c r="B3" s="2">
+        <v>46269</v>
+      </c>
+      <c r="C3" s="2">
         <v>46268</v>
-      </c>
-      <c r="C3" s="2">
-        <v>46267</v>
       </c>
       <c r="D3" t="s">
         <v>56</v>
@@ -933,16 +933,16 @@
         <v>1</v>
       </c>
       <c r="F3">
-        <v>0.7858935505114415</v>
+        <v>0.8534647213814789</v>
       </c>
       <c r="G3">
-        <v>2.152585530024997</v>
+        <v>2.222467764607518</v>
       </c>
       <c r="H3">
-        <v>1.906840250666997</v>
+        <v>1.917535924931897</v>
       </c>
       <c r="I3">
-        <v>0.4297845805167367</v>
+        <v>0.4313469226629286</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -954,19 +954,19 @@
         <v>225</v>
       </c>
       <c r="M3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N3">
-        <v>-0.08322037597512554</v>
+        <v>-0.08925980789073162</v>
       </c>
       <c r="O3">
-        <v>-24.73641748729839</v>
+        <v>-25.6125704134093</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>2.152585530024997</v>
+        <v>2.222467764607518</v>
       </c>
       <c r="R3" t="s">
         <v>58</v>
@@ -975,10 +975,10 @@
         <v>63</v>
       </c>
       <c r="T3">
-        <v>0.9890520500648153</v>
+        <v>0.9918750949342574</v>
       </c>
       <c r="U3">
-        <v>0.9627612877784943</v>
+        <v>0.9742663912120111</v>
       </c>
       <c r="V3" t="s">
         <v>56</v>
@@ -987,34 +987,34 @@
         <v>69</v>
       </c>
       <c r="X3">
-        <v>0.9932132549039878</v>
+        <v>0.9980269655042503</v>
       </c>
       <c r="Y3">
-        <v>0.9992153306904448</v>
+        <v>0.9996115611374938</v>
       </c>
       <c r="Z3">
-        <v>0.006002075786456951</v>
+        <v>0.001584595633243535</v>
       </c>
       <c r="AA3">
-        <v>0.7520566950343766</v>
+        <v>0.7699287088893266</v>
       </c>
       <c r="AB3">
-        <v>-12.33926865519214</v>
+        <v>-10.6504711470484</v>
       </c>
       <c r="AC3">
-        <v>-24</v>
+        <v>-12.99999999999999</v>
       </c>
       <c r="AD3">
-        <v>0.976899340907506</v>
+        <v>0.982772927328829</v>
       </c>
       <c r="AE3">
-        <v>-0.2136999713020115</v>
+        <v>-0.1848171347833424</v>
       </c>
       <c r="AF3">
-        <v>1.786814758132728</v>
+        <v>1.801481244684184</v>
       </c>
       <c r="AG3">
-        <v>1.78541269943016</v>
+        <v>1.800781479358673</v>
       </c>
       <c r="AH3" t="s">
         <v>56</v>
@@ -1029,28 +1029,28 @@
         <v>80</v>
       </c>
       <c r="AL3">
-        <v>0.8551200019683945</v>
+        <v>0.8693811765366158</v>
       </c>
       <c r="AM3">
-        <v>0.9379709570187473</v>
+        <v>0.9431664961641471</v>
       </c>
       <c r="AN3">
-        <v>1.751078020435302</v>
+        <v>1.775534307736559</v>
       </c>
       <c r="AO3">
-        <v>-0.2885197136156094</v>
+        <v>-0.2828761497928835</v>
       </c>
       <c r="AP3">
-        <v>2.155908779025148</v>
+        <v>2.361775434609422</v>
       </c>
       <c r="AQ3">
-        <v>-3.819122034080421</v>
+        <v>-3.357562199673891</v>
       </c>
       <c r="AR3">
-        <v>1.850068786225984</v>
+        <v>2.09144541419215</v>
       </c>
       <c r="AS3">
-        <v>0.03490366668023578</v>
+        <v>0.03676780140326514</v>
       </c>
       <c r="AT3" t="b">
         <v>1</v>
@@ -1061,10 +1061,10 @@
         <v>48</v>
       </c>
       <c r="B4" s="2">
+        <v>46269</v>
+      </c>
+      <c r="C4" s="2">
         <v>46268</v>
-      </c>
-      <c r="C4" s="2">
-        <v>46267</v>
       </c>
       <c r="D4" t="s">
         <v>56</v>
@@ -1076,37 +1076,37 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>0.04460804836341198</v>
+        <v>0.05764535383154411</v>
       </c>
       <c r="H4">
-        <v>2.077688936092662</v>
+        <v>2.078024738155326</v>
       </c>
       <c r="I4">
-        <v>0.4931335537796923</v>
+        <v>0.4927621324296236</v>
       </c>
       <c r="J4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K4">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="L4">
         <v>146</v>
       </c>
       <c r="M4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N4">
-        <v>-0.2204507280948902</v>
+        <v>-0.2284194127345987</v>
       </c>
       <c r="O4">
-        <v>-8.064568051550731</v>
+        <v>-8.395567808570171</v>
       </c>
       <c r="P4">
-        <v>0.6442415930170223</v>
+        <v>0.687248932653498</v>
       </c>
       <c r="Q4">
-        <v>0.1253885993635742</v>
+        <v>0.1843170490851687</v>
       </c>
       <c r="R4" t="s">
         <v>59</v>
@@ -1115,10 +1115,10 @@
         <v>64</v>
       </c>
       <c r="T4">
-        <v>0.6838259636023329</v>
+        <v>0.7054168237883192</v>
       </c>
       <c r="U4">
-        <v>0.6575443334106572</v>
+        <v>0.6923306965985752</v>
       </c>
       <c r="V4" t="s">
         <v>56</v>
@@ -1127,34 +1127,34 @@
         <v>69</v>
       </c>
       <c r="X4">
-        <v>0.9811625148859606</v>
+        <v>0.9873678227964382</v>
       </c>
       <c r="Y4">
-        <v>0.9992905991584297</v>
+        <v>0.9995725035753258</v>
       </c>
       <c r="Z4">
-        <v>0.01812808427246904</v>
+        <v>0.01220468077888759</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>-80.12136553617742</v>
+        <v>-79.47532814710343</v>
       </c>
       <c r="AC4">
-        <v>-40</v>
+        <v>-35</v>
       </c>
       <c r="AD4">
-        <v>0.1715617420981733</v>
+        <v>0.1826589031279279</v>
       </c>
       <c r="AE4">
-        <v>-0.9851733698432169</v>
+        <v>-0.9831763448680517</v>
       </c>
       <c r="AF4">
-        <v>1.263839583614147</v>
+        <v>1.187716306056873</v>
       </c>
       <c r="AG4">
-        <v>1.262943014749921</v>
+        <v>1.187208561582506</v>
       </c>
       <c r="AH4" t="s">
         <v>56</v>
@@ -1169,28 +1169,28 @@
         <v>81</v>
       </c>
       <c r="AL4">
-        <v>0.08572001802697378</v>
+        <v>0.09129040854995292</v>
       </c>
       <c r="AM4">
-        <v>0.5268596365484934</v>
+        <v>0.5329784401976526</v>
       </c>
       <c r="AN4">
-        <v>0.2901236512625224</v>
+        <v>0.2942841915822243</v>
       </c>
       <c r="AO4">
-        <v>-1.205615066344327</v>
+        <v>-1.135188210882148</v>
       </c>
       <c r="AP4">
-        <v>-0.709973585536663</v>
+        <v>-0.4721122970282957</v>
       </c>
       <c r="AQ4">
-        <v>-2.633424001619929</v>
+        <v>-1.814032101144755</v>
       </c>
       <c r="AR4">
-        <v>0.9481025885323628</v>
+        <v>0.6345298529005211</v>
       </c>
       <c r="AS4">
-        <v>0.1624039719093927</v>
+        <v>0.1444640466139318</v>
       </c>
       <c r="AT4" t="b">
         <v>1</v>
@@ -1201,10 +1201,10 @@
         <v>49</v>
       </c>
       <c r="B5" s="2">
+        <v>46269</v>
+      </c>
+      <c r="C5" s="2">
         <v>46268</v>
-      </c>
-      <c r="C5" s="2">
-        <v>46267</v>
       </c>
       <c r="D5" t="s">
         <v>56</v>
@@ -1213,16 +1213,16 @@
         <v>1</v>
       </c>
       <c r="F5">
-        <v>0.2343500295492417</v>
+        <v>0.2636007990743293</v>
       </c>
       <c r="G5">
-        <v>1.303647111221324</v>
+        <v>1.326965625014153</v>
       </c>
       <c r="H5">
-        <v>1.477921746074287</v>
+        <v>1.483259053053068</v>
       </c>
       <c r="I5">
-        <v>0.3280155359273167</v>
+        <v>0.3305709736473645</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -1234,19 +1234,19 @@
         <v>226</v>
       </c>
       <c r="M5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N5">
-        <v>-0.09251092846166663</v>
+        <v>-0.09677239805276622</v>
       </c>
       <c r="O5">
-        <v>-26.00186706411044</v>
+        <v>-26.35055086528715</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>1.303647111221324</v>
+        <v>1.326965625014153</v>
       </c>
       <c r="R5" t="s">
         <v>59</v>
@@ -1255,10 +1255,10 @@
         <v>64</v>
       </c>
       <c r="T5">
-        <v>0.7438361268944865</v>
+        <v>0.7768253538447389</v>
       </c>
       <c r="U5">
-        <v>0.7696840462715696</v>
+        <v>0.7889382675797985</v>
       </c>
       <c r="V5" t="s">
         <v>56</v>
@@ -1267,34 +1267,34 @@
         <v>69</v>
       </c>
       <c r="X5">
-        <v>0.9910936278314159</v>
+        <v>0.9967642457646022</v>
       </c>
       <c r="Y5">
-        <v>0.9992211389466578</v>
+        <v>0.9993069539540662</v>
       </c>
       <c r="Z5">
-        <v>0.008127511115241903</v>
+        <v>0.002542708189464005</v>
       </c>
       <c r="AA5">
         <v>1</v>
       </c>
       <c r="AB5">
-        <v>-56.54615095759976</v>
+        <v>-52.63104527986711</v>
       </c>
       <c r="AC5">
-        <v>-28</v>
+        <v>-17</v>
       </c>
       <c r="AD5">
-        <v>0.5512651228428953</v>
+        <v>0.6069453030980961</v>
       </c>
       <c r="AE5">
-        <v>-0.8343301291077816</v>
+        <v>-0.7947436058548444</v>
       </c>
       <c r="AF5">
-        <v>2.015326054507508</v>
+        <v>1.832192258354971</v>
       </c>
       <c r="AG5">
-        <v>2.013756395533866</v>
+        <v>1.830922464754927</v>
       </c>
       <c r="AH5" t="s">
         <v>56</v>
@@ -1309,28 +1309,28 @@
         <v>81</v>
       </c>
       <c r="AL5">
-        <v>0.5508357639086471</v>
+        <v>0.6065246620556859</v>
       </c>
       <c r="AM5">
-        <v>0.8572077745584886</v>
+        <v>0.874887377985875</v>
       </c>
       <c r="AN5">
-        <v>1.1943067349079</v>
+        <v>1.163721289215734</v>
       </c>
       <c r="AO5">
-        <v>-1.600982681535377</v>
+        <v>-1.407477171735819</v>
       </c>
       <c r="AP5">
-        <v>0.7056569399605981</v>
+        <v>0.9366970932541001</v>
       </c>
       <c r="AQ5">
-        <v>-3.79157348477345</v>
+        <v>-2.934195662306072</v>
       </c>
       <c r="AR5">
-        <v>0.6368284989665858</v>
+        <v>0.756058952806959</v>
       </c>
       <c r="AS5">
-        <v>0.05266107283806797</v>
+        <v>0.04635764551651293</v>
       </c>
       <c r="AT5" t="b">
         <v>1</v>
@@ -1341,10 +1341,10 @@
         <v>50</v>
       </c>
       <c r="B6" s="2">
+        <v>46269</v>
+      </c>
+      <c r="C6" s="2">
         <v>46268</v>
-      </c>
-      <c r="C6" s="2">
-        <v>46267</v>
       </c>
       <c r="D6" t="s">
         <v>56</v>
@@ -1356,37 +1356,37 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0.01481739457292504</v>
+        <v>0.04963096558809204</v>
       </c>
       <c r="H6">
-        <v>0.9432567834939194</v>
+        <v>0.9432727014599893</v>
       </c>
       <c r="I6">
-        <v>0.2573003166455595</v>
+        <v>0.2572182908824683</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K6">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="L6">
         <v>158</v>
       </c>
       <c r="M6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N6">
-        <v>-0.3664880736341721</v>
+        <v>-0.3700872881106118</v>
       </c>
       <c r="O6">
-        <v>-6.706795941123629</v>
+        <v>-6.849119650947221</v>
       </c>
       <c r="P6">
-        <v>0.1278926178349663</v>
+        <v>0.1312586283933356</v>
       </c>
       <c r="Q6">
-        <v>0.01699033269978795</v>
+        <v>0.0571297364327242</v>
       </c>
       <c r="R6" t="s">
         <v>59</v>
@@ -1395,10 +1395,10 @@
         <v>64</v>
       </c>
       <c r="T6">
-        <v>0.4361491949284066</v>
+        <v>0.3800217109181101</v>
       </c>
       <c r="U6">
-        <v>0.5461788310456028</v>
+        <v>0.4959530829115417</v>
       </c>
       <c r="V6" t="s">
         <v>68</v>
@@ -1407,34 +1407,34 @@
         <v>68</v>
       </c>
       <c r="X6">
-        <v>0.9924801081348495</v>
+        <v>0.9951554275551574</v>
       </c>
       <c r="Y6">
-        <v>0.9996467733112795</v>
+        <v>0.9997732519935685</v>
       </c>
       <c r="Z6">
-        <v>0.007166665176429943</v>
+        <v>0.004617824438411078</v>
       </c>
       <c r="AA6">
-        <v>0.7531789111823489</v>
+        <v>0.7594277410916164</v>
       </c>
       <c r="AB6">
-        <v>-86.82173875942046</v>
+        <v>-89.81078372213135</v>
       </c>
       <c r="AC6">
-        <v>-25</v>
+        <v>-21</v>
       </c>
       <c r="AD6">
-        <v>0.0554426796514236</v>
+        <v>0.003302441044345807</v>
       </c>
       <c r="AE6">
-        <v>-0.9984618717172277</v>
+        <v>-0.9999945469267063</v>
       </c>
       <c r="AF6">
-        <v>1.006014431667909</v>
+        <v>1.008862571808215</v>
       </c>
       <c r="AG6">
-        <v>1.005659080521406</v>
+        <v>1.008633814231294</v>
       </c>
       <c r="AH6" t="s">
         <v>70</v>
@@ -1449,28 +1449,28 @@
         <v>82</v>
       </c>
       <c r="AL6">
-        <v>0.04858330138964393</v>
+        <v>0.002904544444338415</v>
       </c>
       <c r="AM6">
-        <v>0.6296226630292223</v>
+        <v>0.6072325850525373</v>
       </c>
       <c r="AN6">
-        <v>0.09179140797310192</v>
+        <v>0.04039200297791072</v>
       </c>
       <c r="AO6">
-        <v>-0.9942209844444976</v>
+        <v>-1.003162207827614</v>
       </c>
       <c r="AP6">
-        <v>-0.4761183589433012</v>
+        <v>-0.4428336141694431</v>
       </c>
       <c r="AQ6">
-        <v>-1.481136417429724</v>
+        <v>-0.9311116567284768</v>
       </c>
       <c r="AR6">
-        <v>0.5900852033350962</v>
+        <v>0.485309960457533</v>
       </c>
       <c r="AS6">
-        <v>0.2501486250774816</v>
+        <v>0.3037622245122577</v>
       </c>
       <c r="AT6" t="b">
         <v>1</v>
@@ -1481,10 +1481,10 @@
         <v>51</v>
       </c>
       <c r="B7" s="2">
+        <v>46269</v>
+      </c>
+      <c r="C7" s="2">
         <v>46268</v>
-      </c>
-      <c r="C7" s="2">
-        <v>46267</v>
       </c>
       <c r="D7" t="s">
         <v>56</v>
@@ -1496,13 +1496,13 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>0.9047384985029333</v>
+        <v>0.9186078254815326</v>
       </c>
       <c r="H7">
-        <v>1.433708931763957</v>
+        <v>1.439914996628222</v>
       </c>
       <c r="I7">
-        <v>0.3485003583960764</v>
+        <v>0.3516104592594048</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -1514,19 +1514,19 @@
         <v>239</v>
       </c>
       <c r="M7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N7">
-        <v>-0.1356747235399634</v>
+        <v>-0.1395470923613386</v>
       </c>
       <c r="O7">
-        <v>-32.24866094328517</v>
+        <v>-31.2835755493794</v>
       </c>
       <c r="P7">
-        <v>0.08798859307214553</v>
+        <v>0</v>
       </c>
       <c r="Q7">
-        <v>0.9920254194523507</v>
+        <v>0.9186078254815326</v>
       </c>
       <c r="R7" t="s">
         <v>59</v>
@@ -1535,10 +1535,10 @@
         <v>64</v>
       </c>
       <c r="T7">
-        <v>0.6173183882512728</v>
+        <v>0.6167893698679255</v>
       </c>
       <c r="U7">
-        <v>0.6776520818360448</v>
+        <v>0.6774518439681305</v>
       </c>
       <c r="V7" t="s">
         <v>56</v>
@@ -1547,34 +1547,34 @@
         <v>69</v>
       </c>
       <c r="X7">
-        <v>0.9931009916357078</v>
+        <v>0.9968937128708948</v>
       </c>
       <c r="Y7">
-        <v>0.9994352284918875</v>
+        <v>0.9995865101102562</v>
       </c>
       <c r="Z7">
-        <v>0.006334236856179731</v>
+        <v>0.002692797239361444</v>
       </c>
       <c r="AA7">
         <v>1</v>
       </c>
       <c r="AB7">
-        <v>-68.96965564906534</v>
+        <v>-69.0216477734084</v>
       </c>
       <c r="AC7">
-        <v>-24</v>
+        <v>-16</v>
       </c>
       <c r="AD7">
-        <v>0.3588623317040449</v>
+        <v>0.3580151940233368</v>
       </c>
       <c r="AE7">
-        <v>-0.9333905007465718</v>
+        <v>-0.9337157602013755</v>
       </c>
       <c r="AF7">
-        <v>2.411620750927922</v>
+        <v>2.162667432598103</v>
       </c>
       <c r="AG7">
-        <v>2.410258736239425</v>
+        <v>2.161773191479845</v>
       </c>
       <c r="AH7" t="s">
         <v>56</v>
@@ -1589,28 +1589,28 @@
         <v>81</v>
       </c>
       <c r="AL7">
-        <v>0.3586596564837636</v>
+        <v>0.3578671583602335</v>
       </c>
       <c r="AM7">
-        <v>0.7966654376667648</v>
+        <v>0.7973894243064548</v>
       </c>
       <c r="AN7">
-        <v>0.9540568630883743</v>
+        <v>0.8363871539247474</v>
       </c>
       <c r="AO7">
-        <v>-2.196751892415731</v>
+        <v>-1.987102177146234</v>
       </c>
       <c r="AP7">
-        <v>0.3591457068435773</v>
+        <v>0.5224674247282514</v>
       </c>
       <c r="AQ7">
-        <v>-3.824661056089581</v>
+        <v>-2.490430584919363</v>
       </c>
       <c r="AR7">
-        <v>0.5187948123520039</v>
+        <v>0.4621968101108876</v>
       </c>
       <c r="AS7">
-        <v>0.07197061211072805</v>
+        <v>0.06580274959423874</v>
       </c>
       <c r="AT7" t="b">
         <v>1</v>
@@ -1621,10 +1621,10 @@
         <v>52</v>
       </c>
       <c r="B8" s="2">
+        <v>46269</v>
+      </c>
+      <c r="C8" s="2">
         <v>46268</v>
-      </c>
-      <c r="C8" s="2">
-        <v>46267</v>
       </c>
       <c r="D8" t="s">
         <v>56</v>
@@ -1636,13 +1636,13 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>0.4164529723958093</v>
+        <v>0.3948205979537826</v>
       </c>
       <c r="H8">
-        <v>1.436832076585239</v>
+        <v>1.437177129384864</v>
       </c>
       <c r="I8">
-        <v>0.3555677089636515</v>
+        <v>0.355963254388616</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -1654,19 +1654,19 @@
         <v>113</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>-0.0008900411076108866</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>-0.2002985935790458</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>0.4164529723958093</v>
+        <v>0.3948205979537826</v>
       </c>
       <c r="R8" t="s">
         <v>60</v>
@@ -1675,10 +1675,10 @@
         <v>65</v>
       </c>
       <c r="T8">
-        <v>0.7391035841743484</v>
+        <v>0.7395504278905823</v>
       </c>
       <c r="U8">
-        <v>0.7325530400365784</v>
+        <v>0.7327718985221117</v>
       </c>
       <c r="V8" t="s">
         <v>56</v>
@@ -1687,34 +1687,34 @@
         <v>69</v>
       </c>
       <c r="X8">
-        <v>0.9944046836876371</v>
+        <v>0.9955479898089094</v>
       </c>
       <c r="Y8">
-        <v>0.9998257086324864</v>
+        <v>0.9998968238853981</v>
       </c>
       <c r="Z8">
-        <v>0.005421024944849306</v>
+        <v>0.004348834076488783</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>76.35776622500063</v>
+        <v>76.2784825904794</v>
       </c>
       <c r="AC8">
-        <v>-21.99999999999999</v>
+        <v>-20</v>
       </c>
       <c r="AD8">
-        <v>0.2358584995223076</v>
+        <v>0.2372029942803253</v>
       </c>
       <c r="AE8">
-        <v>0.971787408954801</v>
+        <v>0.9714601070061745</v>
       </c>
       <c r="AF8">
-        <v>0.9386792964905228</v>
+        <v>0.9874249012701115</v>
       </c>
       <c r="AG8">
-        <v>0.9385156927922809</v>
+        <v>0.9873230226053373</v>
       </c>
       <c r="AH8" t="s">
         <v>56</v>
@@ -1729,28 +1729,28 @@
         <v>83</v>
       </c>
       <c r="AL8">
-        <v>0.1179086957109431</v>
+        <v>0.1185892602985018</v>
       </c>
       <c r="AM8">
-        <v>0.5488031704417413</v>
+        <v>0.5518979704898639</v>
       </c>
       <c r="AN8">
-        <v>0.1986122585894139</v>
+        <v>0.2055446885482178</v>
       </c>
       <c r="AO8">
-        <v>0.9120522468863762</v>
+        <v>0.9612997197379524</v>
       </c>
       <c r="AP8">
-        <v>1.048129045407561</v>
+        <v>0.9259332079045794</v>
       </c>
       <c r="AQ8">
-        <v>0.8457893045172541</v>
+        <v>0.3837967364151892</v>
       </c>
       <c r="AR8">
-        <v>1.06708464664955</v>
+        <v>0.9065788629734597</v>
       </c>
       <c r="AS8">
-        <v>0.1459558495754748</v>
+        <v>0.1281787743608199</v>
       </c>
       <c r="AT8" t="b">
         <v>1</v>
@@ -1761,10 +1761,10 @@
         <v>53</v>
       </c>
       <c r="B9" s="2">
+        <v>46269</v>
+      </c>
+      <c r="C9" s="2">
         <v>46268</v>
-      </c>
-      <c r="C9" s="2">
-        <v>46267</v>
       </c>
       <c r="D9" t="s">
         <v>57</v>
@@ -1773,16 +1773,16 @@
         <v>-1</v>
       </c>
       <c r="F9">
-        <v>0.553384687846852</v>
+        <v>0.549014817771017</v>
       </c>
       <c r="G9">
-        <v>3.0698123554791</v>
+        <v>3.070870196303257</v>
       </c>
       <c r="H9">
-        <v>3.003239549367671</v>
+        <v>3.009483551875388</v>
       </c>
       <c r="I9">
-        <v>0.6235196719929369</v>
+        <v>0.6262049643298595</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -1794,19 +1794,19 @@
         <v>76</v>
       </c>
       <c r="M9">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N9">
-        <v>0.5229505065359541</v>
+        <v>0.5419150963951063</v>
       </c>
       <c r="O9">
-        <v>66.79719986773674</v>
+        <v>64.51095913890873</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>3.0698123554791</v>
+        <v>3.070870196303257</v>
       </c>
       <c r="R9" t="s">
         <v>61</v>
@@ -1815,10 +1815,10 @@
         <v>66</v>
       </c>
       <c r="T9">
-        <v>-0.9723817589067877</v>
+        <v>-0.9948881507480453</v>
       </c>
       <c r="U9">
-        <v>0.9205140010772777</v>
+        <v>0.9299900733444458</v>
       </c>
       <c r="V9" t="s">
         <v>57</v>
@@ -1827,34 +1827,34 @@
         <v>69</v>
       </c>
       <c r="X9">
-        <v>0.9987893284261056</v>
+        <v>0.9995618646400203</v>
       </c>
       <c r="Y9">
-        <v>0.9997380255687813</v>
+        <v>0.9997527313686917</v>
       </c>
       <c r="Z9">
-        <v>0.0009486971426757584</v>
+        <v>0.0001908667286714127</v>
       </c>
       <c r="AA9">
-        <v>0.9713837045358507</v>
+        <v>0.8060787105429703</v>
       </c>
       <c r="AB9">
-        <v>161.4990741687712</v>
+        <v>171.8478895639152</v>
       </c>
       <c r="AC9">
-        <v>-9</v>
+        <v>4.000000000000005</v>
       </c>
       <c r="AD9">
-        <v>-0.9483185278188759</v>
+        <v>-0.9898950987814116</v>
       </c>
       <c r="AE9">
-        <v>0.3173199801390387</v>
+        <v>0.1418015987517047</v>
       </c>
       <c r="AF9">
-        <v>2.47606711768403</v>
+        <v>2.344507022383358</v>
       </c>
       <c r="AG9">
-        <v>2.475418451409216</v>
+        <v>2.34392729934084</v>
       </c>
       <c r="AH9" t="s">
         <v>57</v>
@@ -1869,28 +1869,28 @@
         <v>84</v>
       </c>
       <c r="AL9">
-        <v>-0.9345049656664831</v>
+        <v>-0.8936931948413673</v>
       </c>
       <c r="AM9">
-        <v>0.973784845770583</v>
+        <v>0.9526322926880262</v>
       </c>
       <c r="AN9">
-        <v>-2.358415555281981</v>
+        <v>-2.317200621738648</v>
       </c>
       <c r="AO9">
-        <v>0.744277094323944</v>
+        <v>0.3499698600855806</v>
       </c>
       <c r="AP9">
-        <v>-3.706585817956542</v>
+        <v>-3.880769218498545</v>
       </c>
       <c r="AQ9">
-        <v>3.784644911069871</v>
+        <v>2.975008256556966</v>
       </c>
       <c r="AR9">
-        <v>3.391580680390451</v>
+        <v>3.628535748176443</v>
       </c>
       <c r="AS9">
-        <v>0.03263841620882221</v>
+        <v>0.03643623356022297</v>
       </c>
       <c r="AT9" t="b">
         <v>1</v>
@@ -1901,10 +1901,10 @@
         <v>54</v>
       </c>
       <c r="B10" s="2">
+        <v>46269</v>
+      </c>
+      <c r="C10" s="2">
         <v>46268</v>
-      </c>
-      <c r="C10" s="2">
-        <v>46267</v>
       </c>
       <c r="D10" t="s">
         <v>57</v>
@@ -1913,16 +1913,16 @@
         <v>-1</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>0.06357175292922376</v>
       </c>
       <c r="G10">
-        <v>1.28836685428672</v>
+        <v>1.646754074149344</v>
       </c>
       <c r="H10">
-        <v>2.045146857262753</v>
+        <v>2.045483026583271</v>
       </c>
       <c r="I10">
-        <v>0.4579228488431169</v>
+        <v>0.4568092866469108</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1934,19 +1934,19 @@
         <v>233</v>
       </c>
       <c r="M10">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N10">
-        <v>18.65490415375874</v>
+        <v>19.53008378016131</v>
       </c>
       <c r="O10">
-        <v>23.48005557427162</v>
+        <v>22.52604818934422</v>
       </c>
       <c r="P10">
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>1.28836685428672</v>
+        <v>1.646754074149344</v>
       </c>
       <c r="R10" t="s">
         <v>62</v>
@@ -1955,10 +1955,10 @@
         <v>67</v>
       </c>
       <c r="T10">
-        <v>-0.986519251726429</v>
+        <v>-0.8744581198095189</v>
       </c>
       <c r="U10">
-        <v>0.8430583285751643</v>
+        <v>0.8028025154358138</v>
       </c>
       <c r="V10" t="s">
         <v>57</v>
@@ -1967,34 +1967,34 @@
         <v>69</v>
       </c>
       <c r="X10">
-        <v>0.9417828297073885</v>
+        <v>0.9862320846376967</v>
       </c>
       <c r="Y10">
-        <v>0.9964986611930852</v>
+        <v>0.999042394328587</v>
       </c>
       <c r="Z10">
-        <v>0.0547158314856967</v>
+        <v>0.01281030969089025</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>0.4045172305550302</v>
       </c>
       <c r="AB10">
-        <v>-163.8278774543612</v>
+        <v>-137.0405313824414</v>
       </c>
       <c r="AC10">
-        <v>63</v>
+        <v>31.00000000000001</v>
       </c>
       <c r="AD10">
-        <v>-0.9604293160660587</v>
+        <v>-0.7318359683680616</v>
       </c>
       <c r="AE10">
-        <v>-0.2785238389094954</v>
+        <v>-0.6814808254109439</v>
       </c>
       <c r="AF10">
-        <v>1.006053330670172</v>
+        <v>1.580929354749255</v>
       </c>
       <c r="AG10">
-        <v>1.002530797101671</v>
+        <v>1.579415447833044</v>
       </c>
       <c r="AH10" t="s">
         <v>57</v>
@@ -2009,28 +2009,28 @@
         <v>85</v>
       </c>
       <c r="AL10">
-        <v>-0.478533263815209</v>
+        <v>-0.5134459637039459</v>
       </c>
       <c r="AM10">
-        <v>0.777810784463951</v>
+        <v>0.7900713387179813</v>
       </c>
       <c r="AN10">
-        <v>-0.9271836071572588</v>
+        <v>-1.169217851117298</v>
       </c>
       <c r="AO10">
-        <v>-0.1950795223762414</v>
+        <v>-1.031464816053185</v>
       </c>
       <c r="AP10">
-        <v>-1.768245498035377</v>
+        <v>-2.357658758448784</v>
       </c>
       <c r="AQ10">
-        <v>-0.6033737375842941</v>
+        <v>-0.2336889736355396</v>
       </c>
       <c r="AR10">
-        <v>1.84789289916817</v>
+        <v>2.360102963382795</v>
       </c>
       <c r="AS10">
-        <v>0.06061694515630939</v>
+        <v>0.06698490612299135</v>
       </c>
       <c r="AT10" t="b">
         <v>1</v>
@@ -2041,10 +2041,10 @@
         <v>55</v>
       </c>
       <c r="B11" s="2">
+        <v>46269</v>
+      </c>
+      <c r="C11" s="2">
         <v>46268</v>
-      </c>
-      <c r="C11" s="2">
-        <v>46267</v>
       </c>
       <c r="D11" t="s">
         <v>56</v>
@@ -2056,13 +2056,13 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>1.137858591651362</v>
+        <v>1.119541820677235</v>
       </c>
       <c r="H11">
-        <v>2.542893602080119</v>
+        <v>2.517460754662237</v>
       </c>
       <c r="I11">
-        <v>0.602306131570605</v>
+        <v>0.5977485504520954</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -2074,19 +2074,19 @@
         <v>212</v>
       </c>
       <c r="M11">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N11">
-        <v>-1762.020333206901</v>
+        <v>-1851.678855060292</v>
       </c>
       <c r="O11">
-        <v>-21.3462712081312</v>
+        <v>-21.60553064398952</v>
       </c>
       <c r="P11">
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>1.137858591651362</v>
+        <v>1.119541820677235</v>
       </c>
       <c r="R11" t="s">
         <v>59</v>
@@ -2095,10 +2095,10 @@
         <v>64</v>
       </c>
       <c r="T11">
-        <v>0.703790963191243</v>
+        <v>0.7040538250039452</v>
       </c>
       <c r="U11">
-        <v>0.716435062025275</v>
+        <v>0.7166488838727829</v>
       </c>
       <c r="V11" t="s">
         <v>56</v>
@@ -2107,34 +2107,34 @@
         <v>69</v>
       </c>
       <c r="X11">
-        <v>0.9841370377624933</v>
+        <v>0.9919968081445537</v>
       </c>
       <c r="Y11">
-        <v>0.9989165143568625</v>
+        <v>0.9992986504840303</v>
       </c>
       <c r="Z11">
-        <v>0.01477947659436918</v>
+        <v>0.007301842339476616</v>
       </c>
       <c r="AA11">
-        <v>0.783708993523034</v>
+        <v>0.7180225199428284</v>
       </c>
       <c r="AB11">
-        <v>-61.90794290002168</v>
+        <v>-62.65883005435044</v>
       </c>
       <c r="AC11">
-        <v>-37</v>
+        <v>-27</v>
       </c>
       <c r="AD11">
-        <v>0.470889587660248</v>
+        <v>0.4592879529193528</v>
       </c>
       <c r="AE11">
-        <v>-0.8821921538038987</v>
+        <v>-0.8882874401358777</v>
       </c>
       <c r="AF11">
-        <v>2.128577844088565</v>
+        <v>2.06550865302153</v>
       </c>
       <c r="AG11">
-        <v>2.126271560554195</v>
+        <v>2.064060009527502</v>
       </c>
       <c r="AH11" t="s">
         <v>56</v>
@@ -2149,28 +2149,28 @@
         <v>81</v>
       </c>
       <c r="AL11">
-        <v>0.41950997018893</v>
+        <v>0.3942568172314658</v>
       </c>
       <c r="AM11">
-        <v>0.7881622110680928</v>
+        <v>0.7725565058440367</v>
       </c>
       <c r="AN11">
-        <v>1.09897871679703</v>
+        <v>1.033817696551966</v>
       </c>
       <c r="AO11">
-        <v>-1.783391243574383</v>
+        <v>-1.76904826894771</v>
       </c>
       <c r="AP11">
-        <v>0.3734730847471686</v>
+        <v>0.5619524885783533</v>
       </c>
       <c r="AQ11">
-        <v>-4.22392389318487</v>
+        <v>-3.17769607539686</v>
       </c>
       <c r="AR11">
-        <v>0.5414619015077295</v>
+        <v>0.5214568482096681</v>
       </c>
       <c r="AS11">
-        <v>0.06311495972993471</v>
+        <v>0.05725941126497041</v>
       </c>
       <c r="AT11" t="b">
         <v>1</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -241,12 +241,12 @@
     <t>UP_SLOPE</t>
   </si>
   <si>
+    <t>TRANSITION_ZONE</t>
+  </si>
+  <si>
     <t>UP_CREST_FLATTENING</t>
   </si>
   <si>
-    <t>TRANSITION_ZONE</t>
-  </si>
-  <si>
     <t>UP_STEEPENING</t>
   </si>
   <si>
@@ -259,10 +259,10 @@
     <t>上升坡延续</t>
   </si>
   <si>
+    <t>地形转换区</t>
+  </si>
+  <si>
     <t>上升坡顶钝化</t>
-  </si>
-  <si>
-    <t>地形转换区</t>
   </si>
   <si>
     <t>上升陡坡形成</t>
@@ -781,10 +781,10 @@
         <v>46</v>
       </c>
       <c r="B2" s="2">
+        <v>46270</v>
+      </c>
+      <c r="C2" s="2">
         <v>46269</v>
-      </c>
-      <c r="C2" s="2">
-        <v>46268</v>
       </c>
       <c r="D2" t="s">
         <v>56</v>
@@ -793,16 +793,16 @@
         <v>1</v>
       </c>
       <c r="F2">
-        <v>0.1577926271651403</v>
+        <v>0.2433881329000335</v>
       </c>
       <c r="G2">
-        <v>0.8942615635687848</v>
+        <v>0.9386445228628102</v>
       </c>
       <c r="H2">
-        <v>1.070946375102337</v>
+        <v>1.071153491147837</v>
       </c>
       <c r="I2">
-        <v>0.2581545950776691</v>
+        <v>0.2581894784963443</v>
       </c>
       <c r="J2">
         <v>6</v>
@@ -814,19 +814,19 @@
         <v>149</v>
       </c>
       <c r="M2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N2">
-        <v>-0.3070653100611083</v>
+        <v>-0.3354238807107995</v>
       </c>
       <c r="O2">
-        <v>-8.057040147041594</v>
+        <v>-8.968895545955128</v>
       </c>
       <c r="P2">
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.8942615635687848</v>
+        <v>0.9386445228628102</v>
       </c>
       <c r="R2" t="s">
         <v>58</v>
@@ -835,10 +835,10 @@
         <v>63</v>
       </c>
       <c r="T2">
-        <v>0.999570170617093</v>
+        <v>0.9999886134501064</v>
       </c>
       <c r="U2">
-        <v>0.8733456880869649</v>
+        <v>0.8864448097489284</v>
       </c>
       <c r="V2" t="s">
         <v>56</v>
@@ -847,34 +847,34 @@
         <v>69</v>
       </c>
       <c r="X2">
-        <v>0.9962913508420332</v>
+        <v>0.9994281823122664</v>
       </c>
       <c r="Y2">
-        <v>0.999480868938008</v>
+        <v>0.9997668550455016</v>
       </c>
       <c r="Z2">
-        <v>0.003189518095974786</v>
+        <v>0.0003386727332351791</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>0.05397374160614632</v>
       </c>
       <c r="AB2">
-        <v>-2.946719377017498</v>
+        <v>0.4703143851624944</v>
       </c>
       <c r="AC2">
-        <v>-18</v>
+        <v>-5.999999999999996</v>
       </c>
       <c r="AD2">
-        <v>0.9986777713351352</v>
+        <v>0.9999663101695172</v>
       </c>
       <c r="AE2">
-        <v>-0.05140728587551786</v>
+        <v>0.00820844235899219</v>
       </c>
       <c r="AF2">
-        <v>0.7370916301218147</v>
+        <v>0.7688663605380142</v>
       </c>
       <c r="AG2">
-        <v>0.7367089829610841</v>
+        <v>0.7686871032253711</v>
       </c>
       <c r="AH2" t="s">
         <v>56</v>
@@ -889,28 +889,28 @@
         <v>80</v>
       </c>
       <c r="AL2">
-        <v>0.4990796633415571</v>
+        <v>0.526846256513993</v>
       </c>
       <c r="AM2">
-        <v>0.7937168756135116</v>
+        <v>0.8050287699562102</v>
       </c>
       <c r="AN2">
-        <v>0.7343225849118935</v>
+        <v>0.7682394663389822</v>
       </c>
       <c r="AO2">
-        <v>-0.007213650845189866</v>
+        <v>0.01696259708175796</v>
       </c>
       <c r="AP2">
-        <v>0.8596755130829734</v>
+        <v>0.9143838870640846</v>
       </c>
       <c r="AQ2">
-        <v>-1.593221833858711</v>
+        <v>-1.661593666137039</v>
       </c>
       <c r="AR2">
-        <v>0.7323288057932779</v>
+        <v>0.7790072515078634</v>
       </c>
       <c r="AS2">
-        <v>0.03803173276887899</v>
+        <v>0.03782847121199816</v>
       </c>
       <c r="AT2" t="b">
         <v>1</v>
@@ -921,7 +921,7 @@
         <v>47</v>
       </c>
       <c r="B3" s="2">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="C3" s="2">
         <v>46268</v>
@@ -1061,10 +1061,10 @@
         <v>48</v>
       </c>
       <c r="B4" s="2">
+        <v>46270</v>
+      </c>
+      <c r="C4" s="2">
         <v>46269</v>
-      </c>
-      <c r="C4" s="2">
-        <v>46268</v>
       </c>
       <c r="D4" t="s">
         <v>56</v>
@@ -1076,37 +1076,37 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>0.05764535383154411</v>
+        <v>0.02266680764321327</v>
       </c>
       <c r="H4">
-        <v>2.078024738155326</v>
+        <v>2.078328559069164</v>
       </c>
       <c r="I4">
-        <v>0.4927621324296236</v>
+        <v>0.4925510102636658</v>
       </c>
       <c r="J4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K4">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L4">
         <v>146</v>
       </c>
       <c r="M4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N4">
-        <v>-0.2284194127345987</v>
+        <v>-0.2351986705510734</v>
       </c>
       <c r="O4">
-        <v>-8.395567808570171</v>
+        <v>-8.47999327250842</v>
       </c>
       <c r="P4">
-        <v>0.687248932653498</v>
+        <v>0.6741866724274798</v>
       </c>
       <c r="Q4">
-        <v>0.1843170490851687</v>
+        <v>0.06956992156242608</v>
       </c>
       <c r="R4" t="s">
         <v>59</v>
@@ -1115,52 +1115,52 @@
         <v>64</v>
       </c>
       <c r="T4">
-        <v>0.7054168237883192</v>
+        <v>0.6602921187952704</v>
       </c>
       <c r="U4">
-        <v>0.6923306965985752</v>
+        <v>0.6470492783123629</v>
       </c>
       <c r="V4" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="W4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="X4">
-        <v>0.9873678227964382</v>
+        <v>0.9844391095736416</v>
       </c>
       <c r="Y4">
-        <v>0.9995725035753258</v>
+        <v>0.9996712994179653</v>
       </c>
       <c r="Z4">
-        <v>0.01220468077888759</v>
+        <v>0.01523218984432373</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>-79.47532814710343</v>
+        <v>-83.67845655133443</v>
       </c>
       <c r="AC4">
-        <v>-35</v>
+        <v>-41.99999999999999</v>
       </c>
       <c r="AD4">
-        <v>0.1826589031279279</v>
+        <v>0.1101080367310409</v>
       </c>
       <c r="AE4">
-        <v>-0.9831763448680517</v>
+        <v>-0.993919624641367</v>
       </c>
       <c r="AF4">
-        <v>1.187716306056873</v>
+        <v>0.9680903059088</v>
       </c>
       <c r="AG4">
-        <v>1.187208561582506</v>
+        <v>0.9677720940617855</v>
       </c>
       <c r="AH4" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="AI4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ4" t="s">
         <v>75</v>
@@ -1169,28 +1169,28 @@
         <v>81</v>
       </c>
       <c r="AL4">
-        <v>0.09129040854995292</v>
+        <v>0.05503592207764033</v>
       </c>
       <c r="AM4">
-        <v>0.5329784401976526</v>
+        <v>0.5061050693369583</v>
       </c>
       <c r="AN4">
-        <v>0.2942841915822243</v>
+        <v>0.2001709252836051</v>
       </c>
       <c r="AO4">
-        <v>-1.135188210882148</v>
+        <v>-0.9317671805205791</v>
       </c>
       <c r="AP4">
-        <v>-0.4721122970282957</v>
+        <v>-0.5822557722998513</v>
       </c>
       <c r="AQ4">
-        <v>-1.814032101144755</v>
+        <v>-1.636158976104565</v>
       </c>
       <c r="AR4">
-        <v>0.6345298529005211</v>
+        <v>0.7054265234644145</v>
       </c>
       <c r="AS4">
-        <v>0.1444640466139318</v>
+        <v>0.1787486431909451</v>
       </c>
       <c r="AT4" t="b">
         <v>1</v>
@@ -1201,7 +1201,7 @@
         <v>49</v>
       </c>
       <c r="B5" s="2">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="C5" s="2">
         <v>46268</v>
@@ -1303,10 +1303,10 @@
         <v>71</v>
       </c>
       <c r="AJ5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AK5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL5">
         <v>0.6065246620556859</v>
@@ -1341,10 +1341,10 @@
         <v>50</v>
       </c>
       <c r="B6" s="2">
+        <v>46270</v>
+      </c>
+      <c r="C6" s="2">
         <v>46269</v>
-      </c>
-      <c r="C6" s="2">
-        <v>46268</v>
       </c>
       <c r="D6" t="s">
         <v>56</v>
@@ -1356,37 +1356,37 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0.04963096558809204</v>
+        <v>0.1215937009524473</v>
       </c>
       <c r="H6">
-        <v>0.9432727014599893</v>
+        <v>0.9432871034292907</v>
       </c>
       <c r="I6">
-        <v>0.2572182908824683</v>
+        <v>0.2571431839511639</v>
       </c>
       <c r="J6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K6">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L6">
         <v>158</v>
       </c>
       <c r="M6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N6">
-        <v>-0.3700872881106118</v>
+        <v>-0.3703216696044252</v>
       </c>
       <c r="O6">
-        <v>-6.849119650947221</v>
+        <v>-6.667399753677326</v>
       </c>
       <c r="P6">
-        <v>0.1312586283933356</v>
+        <v>0.09735158169315852</v>
       </c>
       <c r="Q6">
-        <v>0.0571297364327242</v>
+        <v>0.1347077095426909</v>
       </c>
       <c r="R6" t="s">
         <v>59</v>
@@ -1395,10 +1395,10 @@
         <v>64</v>
       </c>
       <c r="T6">
-        <v>0.3800217109181101</v>
+        <v>0.3461365148896858</v>
       </c>
       <c r="U6">
-        <v>0.4959530829115417</v>
+        <v>0.455716061937822</v>
       </c>
       <c r="V6" t="s">
         <v>68</v>
@@ -1407,34 +1407,34 @@
         <v>68</v>
       </c>
       <c r="X6">
-        <v>0.9951554275551574</v>
+        <v>0.995551228104561</v>
       </c>
       <c r="Y6">
-        <v>0.9997732519935685</v>
+        <v>0.9998185209498537</v>
       </c>
       <c r="Z6">
-        <v>0.004617824438411078</v>
+        <v>0.004267292845292703</v>
       </c>
       <c r="AA6">
-        <v>0.7594277410916164</v>
+        <v>0.5563029909034597</v>
       </c>
       <c r="AB6">
-        <v>-89.81078372213135</v>
+        <v>-94.30625840196588</v>
       </c>
       <c r="AC6">
         <v>-21</v>
       </c>
       <c r="AD6">
-        <v>0.003302441044345807</v>
+        <v>-0.07508764863196088</v>
       </c>
       <c r="AE6">
-        <v>-0.9999945469267063</v>
+        <v>-0.9971769376710049</v>
       </c>
       <c r="AF6">
-        <v>1.008862571808215</v>
+        <v>0.9303458402562511</v>
       </c>
       <c r="AG6">
-        <v>1.008633814231294</v>
+        <v>0.9301770019768538</v>
       </c>
       <c r="AH6" t="s">
         <v>70</v>
@@ -1443,34 +1443,34 @@
         <v>72</v>
       </c>
       <c r="AJ6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AK6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AL6">
-        <v>0.002904544444338415</v>
+        <v>-0.05841896233076303</v>
       </c>
       <c r="AM6">
-        <v>0.6072325850525373</v>
+        <v>0.5927124787755713</v>
       </c>
       <c r="AN6">
-        <v>0.04039200297791072</v>
+        <v>-0.03085567019374423</v>
       </c>
       <c r="AO6">
-        <v>-1.003162207827614</v>
+        <v>-0.9256928380483996</v>
       </c>
       <c r="AP6">
-        <v>-0.4428336141694431</v>
+        <v>-0.4875919132620308</v>
       </c>
       <c r="AQ6">
-        <v>-0.9311116567284768</v>
+        <v>-0.617506360995302</v>
       </c>
       <c r="AR6">
-        <v>0.485309960457533</v>
+        <v>0.499935264061904</v>
       </c>
       <c r="AS6">
-        <v>0.3037622245122577</v>
+        <v>0.2734059755143843</v>
       </c>
       <c r="AT6" t="b">
         <v>1</v>
@@ -1481,7 +1481,7 @@
         <v>51</v>
       </c>
       <c r="B7" s="2">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="C7" s="2">
         <v>46268</v>
@@ -1583,10 +1583,10 @@
         <v>71</v>
       </c>
       <c r="AJ7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AK7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL7">
         <v>0.3578671583602335</v>
@@ -1621,7 +1621,7 @@
         <v>52</v>
       </c>
       <c r="B8" s="2">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="C8" s="2">
         <v>46268</v>
@@ -1761,7 +1761,7 @@
         <v>53</v>
       </c>
       <c r="B9" s="2">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="C9" s="2">
         <v>46268</v>
@@ -1901,7 +1901,7 @@
         <v>54</v>
       </c>
       <c r="B10" s="2">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="C10" s="2">
         <v>46268</v>
@@ -2041,7 +2041,7 @@
         <v>55</v>
       </c>
       <c r="B11" s="2">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="C11" s="2">
         <v>46268</v>
@@ -2143,10 +2143,10 @@
         <v>71</v>
       </c>
       <c r="AJ11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AK11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL11">
         <v>0.3942568172314658</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -781,7 +781,7 @@
         <v>46</v>
       </c>
       <c r="B2" s="2">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="C2" s="2">
         <v>46269</v>
@@ -921,7 +921,7 @@
         <v>47</v>
       </c>
       <c r="B3" s="2">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="C3" s="2">
         <v>46268</v>
@@ -1061,7 +1061,7 @@
         <v>48</v>
       </c>
       <c r="B4" s="2">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="C4" s="2">
         <v>46269</v>
@@ -1201,7 +1201,7 @@
         <v>49</v>
       </c>
       <c r="B5" s="2">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="C5" s="2">
         <v>46268</v>
@@ -1341,7 +1341,7 @@
         <v>50</v>
       </c>
       <c r="B6" s="2">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="C6" s="2">
         <v>46269</v>
@@ -1481,7 +1481,7 @@
         <v>51</v>
       </c>
       <c r="B7" s="2">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="C7" s="2">
         <v>46268</v>
@@ -1621,7 +1621,7 @@
         <v>52</v>
       </c>
       <c r="B8" s="2">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="C8" s="2">
         <v>46268</v>
@@ -1761,7 +1761,7 @@
         <v>53</v>
       </c>
       <c r="B9" s="2">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="C9" s="2">
         <v>46268</v>
@@ -1901,7 +1901,7 @@
         <v>54</v>
       </c>
       <c r="B10" s="2">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="C10" s="2">
         <v>46268</v>
@@ -2041,7 +2041,7 @@
         <v>55</v>
       </c>
       <c r="B11" s="2">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="C11" s="2">
         <v>46268</v>
